--- a/data/bist_screener_latest.xlsx
+++ b/data/bist_screener_latest.xlsx
@@ -99,7 +99,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -583,31 +583,31 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13.64</v>
+        <v>13.24</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0.0044</v>
+        <v>-0.0293</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.0243</v>
+        <v>-0.05230000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.1464</v>
+        <v>-0.1572</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-0.2526</v>
+        <v>-0.2587</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.1512</v>
+        <v>-0.2072</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.2987</v>
+        <v>-0.3622</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0.22</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>6.34</v>
+        <v>6.15</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>0.9854999999999999</v>
@@ -641,31 +641,31 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>0.028</v>
+        <v>0.0136</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>-0.004500000000000001</v>
+        <v>-0.0219</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>-0.1165</v>
+        <v>-0.108</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>-0.1698</v>
+        <v>-0.1648</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>-0.2971</v>
+        <v>-0.3009</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-0.2971</v>
+        <v>-0.2712</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0.23</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>2.7227</v>
@@ -695,57 +695,57 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HLGYO</t>
+          <t>IHEVA</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4.12</v>
+        <v>1.6</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.0072</v>
+        <v>-0.0244</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.0144</v>
+        <v>-0.0361</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.0965</v>
+        <v>-0.1795</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.2256</v>
+        <v>-0.2233</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.2797</v>
+        <v>-0.2627</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.1046</v>
+        <v>-0.387</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0.24</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.23</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1.7259</v>
+        <v>0.2518</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1.4642</v>
+        <v>0.322</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>2.8476</v>
+        <v>0.2038</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>2.0883</v>
+        <v>0.1672</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.1249</v>
+        <v>0.078</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.2374</v>
+        <v>0.0331</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr"/>
@@ -753,57 +753,57 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IHEVA</t>
+          <t>HLGYO</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>1.64</v>
+        <v>4.15</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>0.0123</v>
+        <v>0.0073</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-0.012</v>
+        <v>0.0073</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-0.159</v>
+        <v>-0.0919</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>-0.1961</v>
+        <v>-0.2642</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-0.2336</v>
+        <v>-0.2745</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>-0.374</v>
+        <v>0.1496</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0.24</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>9.18</v>
+        <v>1.24</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.2518</v>
+        <v>1.7259</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>0.322</v>
+        <v>1.4642</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>0.2038</v>
+        <v>2.8476</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>0.1672</v>
+        <v>2.0883</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>0.078</v>
+        <v>0.1249</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>0.0331</v>
+        <v>0.2374</v>
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R5" s="5" t="inlineStr"/>
@@ -815,31 +815,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.025</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0277</v>
+        <v>-0.0541</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.05019999999999999</v>
+        <v>-0.1667</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.1058</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1214</v>
+        <v>-0.125</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.0391</v>
+        <v>-0.0392</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0.25</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>5.78</v>
+        <v>5.76</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>0.3848</v>
@@ -873,25 +873,25 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>16.43</v>
+        <v>16.4</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>0.0399</v>
+        <v>-0.0018</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.1012</v>
+        <v>0.0594</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-0.4263</v>
+        <v>-0.4403</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>-0.2286</v>
+        <v>-0.2407</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-0.5385</v>
+        <v>-0.5312</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>-0.2358</v>
+        <v>-0.2257</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0.25</v>
@@ -925,57 +925,55 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GSDHO</t>
+          <t>SNICA</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>4.32</v>
+        <v>2.25</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.0141</v>
+        <v>-0.0343</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.0667</v>
+        <v>-0.026</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1074</v>
+        <v>-0.2947</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1818</v>
+        <v>-0.4458</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1394</v>
+        <v>-0.4403</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.0226</v>
+        <v>-0.5588000000000001</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>15.48</v>
-      </c>
+        <v>0.26</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="n">
-        <v>0.1479</v>
+        <v>0.2451</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2201</v>
+        <v>0.1328</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.3072</v>
+        <v>0.7476999999999999</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.5201</v>
+        <v>0.4518</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.6869</v>
+        <v>0.0576</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.0197</v>
+        <v>-0.1748</v>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr"/>
@@ -983,55 +981,55 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>SNICA</t>
+          <t>PNSUT</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>2.33</v>
+        <v>10.19</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.04019999999999999</v>
+        <v>-0.0314</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.0219</v>
+        <v>0.0039</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-0.2696</v>
+        <v>-0.1769</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>-0.4426</v>
+        <v>-0.07780000000000001</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-0.4071</v>
+        <v>-0.2413</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-0.5545</v>
+        <v>-0.2933</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="J9" s="5" t="inlineStr"/>
       <c r="K9" s="7" t="n">
-        <v>0.2451</v>
+        <v>0.049</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.1328</v>
+        <v>0.8042</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.7476999999999999</v>
+        <v>1.0075</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>0.4518</v>
+        <v>0.2634</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>0.0576</v>
+        <v>0.0384</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>-0.1748</v>
+        <v>-0.09359999999999999</v>
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R9" s="5" t="inlineStr"/>
@@ -1039,55 +1037,57 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PNSUT</t>
+          <t>GSDHO</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10.52</v>
+        <v>4.29</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.0283</v>
+        <v>-0.0069</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.0233</v>
+        <v>0.0413</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1349</v>
+        <v>-0.08529999999999999</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.0607</v>
+        <v>-0.1813</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.182</v>
+        <v>-0.1454</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2486</v>
+        <v>-0.0228</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.27</v>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
+        <v>15.37</v>
+      </c>
       <c r="K10" s="4" t="n">
-        <v>0.049</v>
+        <v>0.1479</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.8042</v>
+        <v>0.2201</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.0075</v>
+        <v>0.3072</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2634</v>
+        <v>0.5201</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.0384</v>
+        <v>0.6869</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.09359999999999999</v>
+        <v>0.0197</v>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr"/>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>6.8</v>
+        <v>6.75</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.04940000000000001</v>
+        <v>-0.0074</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.07769999999999999</v>
+        <v>0.0212</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.1083</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>-0.1338</v>
+        <v>-0.0766</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-0.2047</v>
+        <v>-0.1758</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.1176</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0.27</v>
@@ -1155,31 +1155,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>10.2</v>
+        <v>9.99</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.0159</v>
+        <v>-0.0206</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.0039</v>
+        <v>-0.0187</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1542</v>
+        <v>-0.1805</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.0941</v>
+        <v>-0.1144</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1639</v>
+        <v>-0.2065</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2075</v>
+        <v>-0.2298</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>12.14</v>
+        <v>11.89</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0.3203</v>
@@ -1209,57 +1209,55 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>MHRGY</t>
+          <t>BIENY</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>1.8</v>
+        <v>13.9</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>0.0286</v>
+        <v>-0.0327</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>-0.0164</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>-0.1964</v>
+        <v>-0.3226</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>-0.2458</v>
+        <v>-0.3394</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-0.2082</v>
+        <v>-0.4431</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.3215999999999999</v>
+        <v>-0.6557999999999999</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0.35</v>
       </c>
-      <c r="J13" s="6" t="n">
-        <v>8.49</v>
-      </c>
+      <c r="J13" s="5" t="inlineStr"/>
       <c r="K13" s="7" t="n">
-        <v>0.9460999999999999</v>
+        <v>0.7363</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.9873000000000001</v>
+        <v>1.3916</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.3702</v>
+        <v>2.2545</v>
       </c>
       <c r="N13" s="7" t="n">
-        <v>2464.8944</v>
+        <v>0.6645</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>0.8395999999999999</v>
+        <v>0.1599</v>
       </c>
       <c r="P13" s="7" t="n">
-        <v>0.0472</v>
+        <v>-0.0699</v>
       </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R13" s="5" t="inlineStr"/>
@@ -1267,55 +1265,57 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BIENY</t>
+          <t>BESLR</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>14.37</v>
+        <v>11.16</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.0368</v>
+        <v>-0.015</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.0356</v>
+        <v>0.0136</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3254</v>
+        <v>-0.1545</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3222</v>
+        <v>-0.1356</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.4061999999999999</v>
+        <v>-0.1782</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.6464</v>
+        <v>-0.1812</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr"/>
+        <v>0.37</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>5.95</v>
+      </c>
       <c r="K14" s="4" t="n">
-        <v>0.7363</v>
+        <v>0.3789</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.3916</v>
+        <v>0.3175</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.2545</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6645</v>
+        <v>0.5778</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.1599</v>
+        <v>0.1173</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.0699</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr"/>
@@ -1323,57 +1323,55 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>BESLR</t>
+          <t>KRTEK</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>11.33</v>
+        <v>5.92</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.0291</v>
+        <v>-0.0199</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.0309</v>
+        <v>-0.039</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-0.1519</v>
+        <v>-0.005</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>-0.1468</v>
+        <v>-0.0696</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-0.1638</v>
+        <v>-0.1577</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.1907</v>
+        <v>-0.351</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0.38</v>
       </c>
-      <c r="J15" s="6" t="n">
-        <v>6.04</v>
-      </c>
+      <c r="J15" s="5" t="inlineStr"/>
       <c r="K15" s="7" t="n">
-        <v>0.3789</v>
+        <v>0.1651</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.3175</v>
+        <v>0.5547</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.07240000000000001</v>
+        <v>3.1915</v>
       </c>
       <c r="N15" s="7" t="n">
-        <v>0.5778</v>
+        <v>0.7</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>0.1173</v>
+        <v>0.0396</v>
       </c>
       <c r="P15" s="7" t="n">
-        <v>0.07580000000000001</v>
+        <v>-0.0461</v>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R15" s="5" t="inlineStr"/>
@@ -1381,55 +1379,57 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KRTEK</t>
+          <t>MHRGY</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>6.04</v>
+        <v>1.98</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.0396</v>
+        <v>0.1</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.0237</v>
+        <v>0.0206</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1483</v>
+        <v>-0.12</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.0702</v>
+        <v>-0.1563</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.1291</v>
+        <v>-0.1818</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3535</v>
+        <v>-0.2538</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
+        <v>0.38</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>9.34</v>
+      </c>
       <c r="K16" s="4" t="n">
-        <v>0.1651</v>
+        <v>0.9460999999999999</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5547</v>
+        <v>0.9873000000000001</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.1915</v>
+        <v>0.3702</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.7</v>
+        <v>2464.8944</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.0396</v>
+        <v>0.8395999999999999</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.0461</v>
+        <v>0.0472</v>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr"/>
@@ -1441,25 +1441,25 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>193.2</v>
+        <v>193.3</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>0.026</v>
+        <v>0.0005</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.004699999999999999</v>
+        <v>-0.0118</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>-0.0267</v>
+        <v>-0.0359</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>-0.0223</v>
+        <v>-0.0218</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.111</v>
+        <v>0.06150000000000001</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0.2562</v>
+        <v>0.2818</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0.39</v>
@@ -1499,31 +1499,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>38.04</v>
+        <v>37.6</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.0058</v>
+        <v>-0.0116</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.0187</v>
+        <v>0.0053</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1558</v>
+        <v>-0.1458</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.0977</v>
+        <v>-0.1256</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1875</v>
+        <v>-0.2206</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0746</v>
+        <v>0.0731</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>0.42</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>9.56</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>0.2329</v>
@@ -1557,31 +1557,31 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>7.69</v>
+        <v>7.46</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>0.0159</v>
+        <v>-0.0299</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.0491</v>
+        <v>-0.0184</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>-0.2461</v>
+        <v>-0.2614</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>-0.2806</v>
+        <v>-0.2995</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>-0.3009</v>
+        <v>-0.3773</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-0.2461</v>
+        <v>-0.2708</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>0.9081</v>
@@ -1611,57 +1611,55 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>18.66</v>
+        <v>1.83</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.0158</v>
+        <v>-0.09849999999999999</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.0101</v>
+        <v>-0.1117</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1425</v>
+        <v>-0.4116</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.0808</v>
+        <v>-0.4845</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.1003</v>
+        <v>-0.4874</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.0442</v>
+        <v>-0.8170000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>7.54</v>
-      </c>
+        <v>0.45</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="4" t="n">
-        <v>0.1285</v>
+        <v>0.2334</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.8243</v>
+        <v>0.1468</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.9048</v>
+        <v>0.1104</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.2086</v>
+        <v>0.4322</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.1116</v>
+        <v>0.1786</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.1027</v>
+        <v>-0.1088</v>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr"/>
@@ -1673,28 +1671,28 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0.07769999999999999</v>
+        <v>-0.05769999999999999</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.0833</v>
+        <v>-0.07980000000000001</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-0.4424</v>
+        <v>-0.4974</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>-0.6104999999999999</v>
+        <v>-0.65</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-0.6848000000000001</v>
+        <v>-0.7121999999999999</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.5388000000000001</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="J21" s="5" t="inlineStr"/>
       <c r="K21" s="7" t="n">
@@ -1725,55 +1723,57 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TRILC</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>18.63</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.0505</v>
+        <v>-0.0016</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2533</v>
+        <v>-0.02</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1215</v>
+        <v>-0.1391</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.2295</v>
+        <v>-0.1154</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6175</v>
+        <v>-0.1509</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.733</v>
+        <v>0.0373</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
+        <v>0.47</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>7.53</v>
+      </c>
       <c r="K22" s="4" t="n">
-        <v>0.8809</v>
+        <v>0.1285</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.1988</v>
+        <v>0.8243</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.821</v>
+        <v>1.9048</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.7378</v>
+        <v>2.2086</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.249</v>
+        <v>0.1116</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.0291</v>
+        <v>0.1027</v>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr"/>
@@ -1781,55 +1781,55 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>TRILC</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>2.03</v>
+        <v>0.91</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>0.0305</v>
+        <v>-0.0319</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.015</v>
+        <v>0.1519</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>-0.3472999999999999</v>
+        <v>-0.1574</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>-0.4116</v>
+        <v>-0.3974</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-0.4266</v>
+        <v>-0.6353</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-0.7711</v>
+        <v>-0.7384999999999999</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="J23" s="5" t="inlineStr"/>
       <c r="K23" s="7" t="n">
-        <v>0.2334</v>
+        <v>0.8809</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.1468</v>
+        <v>1.1988</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.1104</v>
+        <v>1.821</v>
       </c>
       <c r="N23" s="7" t="n">
-        <v>0.4322</v>
+        <v>0.7378</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>0.1786</v>
+        <v>0.249</v>
       </c>
       <c r="P23" s="7" t="n">
-        <v>-0.1088</v>
+        <v>-0.0291</v>
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R23" s="5" t="inlineStr"/>
@@ -1841,31 +1841,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>11.07</v>
+        <v>10.73</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.0346</v>
+        <v>-0.0307</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.0027</v>
+        <v>-0.042</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.1739</v>
+        <v>-0.1784</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.258</v>
+        <v>-0.287</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3767</v>
+        <v>-0.3779999999999999</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2525</v>
+        <v>-0.3109</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>4.16</v>
+        <v>4.04</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>0.4985</v>
@@ -1899,31 +1899,31 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>6.29</v>
+        <v>6.17</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>0.0194</v>
+        <v>-0.0191</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>-0.0293</v>
+        <v>-0.0537</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-0.1863</v>
+        <v>-0.1828</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>-0.3011</v>
+        <v>-0.316</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>-0.244</v>
+        <v>-0.2892</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-0.1078</v>
+        <v>-0.156</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>7.55</v>
+        <v>7.41</v>
       </c>
       <c r="K25" s="7" t="n">
         <v>0.6883</v>
@@ -1957,28 +1957,28 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.0113</v>
+        <v>-0.0086</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.0309</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.222</v>
+        <v>-0.2256</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3103</v>
+        <v>-0.2936</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4188</v>
+        <v>-0.4327</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3644</v>
+        <v>-0.3699</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="4" t="n">
@@ -2009,57 +2009,57 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>OYYAT</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>32.68</v>
+        <v>26.66</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>0.0168</v>
+        <v>-0.0305</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>0.0277</v>
+        <v>-0.0499</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-0.0825</v>
+        <v>-0.2112</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>0.0245</v>
+        <v>-0.3358</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>0.1169</v>
+        <v>-0.5222</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>0.2716</v>
+        <v>-0.446</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>17.87</v>
+        <v>3.42</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.3105</v>
+        <v>0.045</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.3107</v>
+        <v>0.4061999999999999</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.4787</v>
+        <v>0.4311</v>
       </c>
       <c r="N27" s="7" t="n">
-        <v>1.4985</v>
+        <v>3.0744</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>0.0693</v>
+        <v>0.2671</v>
       </c>
       <c r="P27" s="7" t="n">
-        <v>-0.0718</v>
+        <v>0.2126</v>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R27" s="5" t="inlineStr"/>
@@ -2067,57 +2067,57 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>OYYAT</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>27.5</v>
+        <v>34.18</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.0148</v>
+        <v>0.0459</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.0269</v>
+        <v>0.0517</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.224</v>
+        <v>0.0059</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3049</v>
+        <v>0.0364</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.4991</v>
+        <v>0.1047</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4083</v>
+        <v>0.3531</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.52</v>
+        <v>18.69</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.045</v>
+        <v>0.3105</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.4061999999999999</v>
+        <v>0.3107</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.4311</v>
+        <v>0.4787</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.0744</v>
+        <v>1.4985</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.2671</v>
+        <v>0.0693</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.2126</v>
+        <v>-0.0718</v>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr"/>
@@ -2129,28 +2129,28 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>-0.0256</v>
+        <v>-0.0164</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>0.0704</v>
+        <v>-0.0229</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-0.2834</v>
+        <v>-0.2661</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>-0.2878</v>
+        <v>-0.2791</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>-0.0333</v>
+        <v>-0.1367</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>0.0019</v>
+        <v>-0.0034</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="7" t="n">
@@ -2185,28 +2185,28 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>7.92</v>
+        <v>7.8</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0152</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.2733</v>
+        <v>0.2112</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3231</v>
+        <v>-0.3079</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5099</v>
+        <v>-0.5329</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.4923</v>
+        <v>-0.5667</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3394</v>
+        <v>-0.3362</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="4" t="n">
@@ -2241,31 +2241,31 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>7.76</v>
+        <v>7.66</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>0.0251</v>
+        <v>-0.0129</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>-0.0263</v>
+        <v>-0.0328</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-0.132</v>
+        <v>-0.1325</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>-0.2429</v>
+        <v>-0.2446</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>-0.1425</v>
+        <v>-0.1628</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>-0.237</v>
+        <v>-0.2541</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="K31" s="7" t="n">
         <v>0.3806</v>
@@ -2295,57 +2295,55 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>BAKAB</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>208</v>
+        <v>30.34</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.0207</v>
+        <v>-0.0219</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.0043</v>
+        <v>-0.0607</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.2066</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1237</v>
+        <v>-0.401</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.0359</v>
+        <v>-0.3992</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2164</v>
+        <v>-0.2197</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>14.82</v>
-      </c>
+        <v>0.66</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="4" t="n">
-        <v>0.3261</v>
+        <v>0.3479</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.5440999999999999</v>
+        <v>0.5443</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.9423</v>
+        <v>0.7171</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.083299999999999</v>
+        <v>0.97</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.0646</v>
+        <v>0.0552</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.0771</v>
+        <v>-0.0031</v>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr"/>
@@ -2353,55 +2351,57 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>BAKAB</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>31.02</v>
+        <v>206.9</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>0.0032</v>
+        <v>-0.0053</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>-0.0208</v>
+        <v>-0.0043</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-0.1934</v>
+        <v>-0.08039999999999999</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>-0.4153</v>
+        <v>0.0832</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>-0.3265</v>
+        <v>0</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>-0.1798</v>
+        <v>0.2345</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J33" s="5" t="inlineStr"/>
+        <v>0.66</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>14.75</v>
+      </c>
       <c r="K33" s="7" t="n">
-        <v>0.3479</v>
+        <v>0.3261</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.5443</v>
+        <v>0.5440999999999999</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.7171</v>
+        <v>0.9423</v>
       </c>
       <c r="N33" s="7" t="n">
-        <v>0.97</v>
+        <v>5.083299999999999</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>0.0552</v>
+        <v>0.0646</v>
       </c>
       <c r="P33" s="7" t="n">
-        <v>-0.0031</v>
+        <v>0.0771</v>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="R33" s="5" t="inlineStr"/>
@@ -2409,57 +2409,55 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>OSMEN</t>
+          <t>DOKTA</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>5.51</v>
+        <v>15.37</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0018</v>
+        <v>-0.0333</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.0495</v>
+        <v>-0.0071</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.225</v>
+        <v>-0.342</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.36</v>
+        <v>-0.3364</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2503</v>
+        <v>-0.3574</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3448</v>
+        <v>-0.3832</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>9.449999999999999</v>
-      </c>
+        <v>0.67</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="4" t="n">
-        <v>1.6512</v>
+        <v>0.2983</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.1052</v>
+        <v>1.25</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.04969999999999999</v>
+        <v>3.5566</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.9134</v>
+        <v>0.6970000000000001</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.0852</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.0863</v>
+        <v>-0.0451</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr"/>
@@ -2467,55 +2465,57 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>DOKTA</t>
+          <t>OSMEN</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>15.9</v>
+        <v>5.53</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>0.0318</v>
+        <v>0.0036</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.0399</v>
+        <v>0.0279</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-0.3063</v>
+        <v>-0.2167</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>-0.3263</v>
+        <v>-0.3297</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>-0.3263</v>
+        <v>-0.2818</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>-0.3715</v>
+        <v>-0.3393</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J35" s="5" t="inlineStr"/>
+        <v>0.68</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>9.49</v>
+      </c>
       <c r="K35" s="7" t="n">
-        <v>0.2983</v>
+        <v>1.6512</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>1.25</v>
+        <v>0.1052</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>3.5566</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="N35" s="7" t="n">
-        <v>0.6970000000000001</v>
+        <v>5.9134</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>0.0852</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="P35" s="7" t="n">
-        <v>-0.0451</v>
+        <v>0.0863</v>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R35" s="5" t="inlineStr"/>
@@ -2527,31 +2527,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>52.3</v>
+        <v>51.85</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>-0.0019</v>
+        <v>-0.0086</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0</v>
+        <v>-0.0152</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>-0.0395</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>-0.07919999999999999</v>
+        <v>-0.1014</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.1612</v>
+        <v>-0.1822</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.0185</v>
+        <v>0.0019</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>6.47</v>
+        <v>6.41</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>0.4498</v>
@@ -2585,31 +2585,31 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>0.0291</v>
+        <v>-0.0141</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0.0316</v>
+        <v>-0.0048</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-0.0428</v>
+        <v>-0.04769999999999999</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>-0.2123</v>
+        <v>-0.2495</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>-0.2995</v>
+        <v>-0.3106</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>-0.07440000000000001</v>
+        <v>-0.0764</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="K37" s="7" t="n">
         <v>0.208</v>
@@ -2643,31 +2643,31 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>97.25</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>-0.0165</v>
+        <v>-0.0132</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>0.0072</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>-0.0357</v>
+        <v>-0.04190000000000001</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-0.0596</v>
+        <v>-0.1078</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.1512</v>
+        <v>-0.166</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.0095</v>
+        <v>-0.0371</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>11.07</v>
+        <v>10.92</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>0.3971</v>
@@ -2701,31 +2701,31 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>5.88</v>
+        <v>5.79</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>0.0138</v>
+        <v>-0.0153</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>-0.0313</v>
+        <v>-0.043</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-0.0408</v>
+        <v>-0.057</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>-0.1441</v>
+        <v>-0.1485</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>-0.2604</v>
+        <v>-0.2982</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>-0.2829</v>
+        <v>-0.2965</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>11.05</v>
+        <v>10.89</v>
       </c>
       <c r="K39" s="7" t="n">
         <v>0.4159</v>
@@ -2755,57 +2755,57 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AKMGY</t>
+          <t>PNLSN</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>212.1</v>
+        <v>32.88</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.0114</v>
+        <v>-0.0403</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>-0.0116</v>
+        <v>-0.0335</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>-0.1633</v>
+        <v>-0.1933</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>-0.1286</v>
+        <v>-0.2713</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-0.3034</v>
+        <v>-0.2628</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.0677</v>
+        <v>-0.2077</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>10.45</v>
+        <v>9.27</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.3886</v>
+        <v>0.306</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.3887</v>
+        <v>0.6481</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.3141</v>
+        <v>0.5497</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.5958</v>
+        <v>7.793600000000001</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.6443000000000001</v>
+        <v>0.1302</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0.0781</v>
+        <v>0.08839999999999999</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr"/>
@@ -2817,31 +2817,31 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>5.34</v>
+        <v>5.27</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>0.0038</v>
+        <v>-0.0131</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>-0.0599</v>
+        <v>-0.06059999999999999</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-0.1721</v>
+        <v>-0.1701</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>-0.1159</v>
+        <v>-0.1217</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>-0.1897</v>
+        <v>-0.2087</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>-0.2065</v>
+        <v>-0.2015</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>4.94</v>
+        <v>4.88</v>
       </c>
       <c r="K41" s="7" t="n">
         <v>0.2654</v>
@@ -2871,57 +2871,57 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>PNLSN</t>
+          <t>AKMGY</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>34.26</v>
+        <v>210.5</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.0264</v>
+        <v>-0.0075</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>0.0282</v>
+        <v>-0.0291</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-0.1764</v>
+        <v>-0.1614</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-0.2474</v>
+        <v>-0.1512</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-0.2217</v>
+        <v>-0.303</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-0.1725</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>9.66</v>
+        <v>10.37</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0.306</v>
+        <v>0.3886</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.6481</v>
+        <v>0.3887</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.5497</v>
+        <v>0.3141</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>7.793600000000001</v>
+        <v>0.5958</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>0.1302</v>
+        <v>0.6443000000000001</v>
       </c>
       <c r="P42" s="4" t="n">
-        <v>0.08839999999999999</v>
+        <v>0.0781</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr"/>
@@ -2933,31 +2933,31 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>11.03</v>
+        <v>10.68</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>0.0318</v>
+        <v>-0.0317</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>-0.0152</v>
+        <v>-0.0761</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-0.43</v>
+        <v>-0.4283</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>-0.5278</v>
+        <v>-0.5594</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>-0.3359</v>
+        <v>-0.3743</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>-0.6587000000000001</v>
+        <v>-0.633</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>12.67</v>
+        <v>12.27</v>
       </c>
       <c r="K43" s="7" t="n">
         <v>0.2374</v>
@@ -2991,31 +2991,31 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>291.5</v>
+        <v>288.5</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>-0.0119</v>
+        <v>-0.0103</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>-0.0119</v>
+        <v>-0.0052</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>-0.1031</v>
+        <v>-0.1258</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.2495</v>
+        <v>0.1713</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>0.05230000000000001</v>
+        <v>0.0185</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.5765</v>
+        <v>0.537</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>7.66</v>
+        <v>7.58</v>
       </c>
       <c r="K44" s="4" t="n">
         <v>0.1662</v>
@@ -3045,57 +3045,57 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>BASGZ</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>37.32</v>
+        <v>39.88</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>0.0197</v>
+        <v>-0.0124</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0.0208</v>
+        <v>-0.0182</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-0.0604</v>
+        <v>-0.1216</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>-0.067</v>
+        <v>-0.139</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0.2325</v>
+        <v>-0.2316</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>0.3281</v>
+        <v>0.0358</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>32.53</v>
+        <v>7.22</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.1998</v>
+        <v>0.3163</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>0.3838</v>
+        <v>0.5275</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>0.4877</v>
+        <v>0.4513</v>
       </c>
       <c r="N45" s="7" t="n">
-        <v>0.4752</v>
+        <v>0.3789</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>0.104</v>
+        <v>0.1301</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>0.0274</v>
+        <v>-0.245</v>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R45" s="5" t="inlineStr"/>
@@ -3103,57 +3103,57 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>BASGZ</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>40.38</v>
+        <v>37.6</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.0338</v>
+        <v>0.0075</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>-0.027</v>
+        <v>0.0118</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>-0.1066</v>
+        <v>-0.0359</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-0.1342</v>
+        <v>-0.07980000000000001</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-0.2345</v>
+        <v>0.1854</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.0354</v>
+        <v>0.34</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>0.79</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>7.31</v>
+        <v>32.77</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0.3163</v>
+        <v>0.1998</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.5275</v>
+        <v>0.3838</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.4513</v>
+        <v>0.4877</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.3789</v>
+        <v>0.4752</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0.1301</v>
+        <v>0.104</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>-0.245</v>
+        <v>0.0274</v>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr"/>
@@ -3165,31 +3165,31 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>8.84</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>0.0091</v>
+        <v>-0.0158</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>-0.021</v>
+        <v>-0.0169</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-0.1475</v>
+        <v>-0.157</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>-0.1376</v>
+        <v>-0.1675</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>-0.2521</v>
+        <v>-0.3349</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>-0.2211</v>
+        <v>-0.2169</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>18.63</v>
+        <v>18.34</v>
       </c>
       <c r="K47" s="7" t="n">
         <v>0.2802</v>
@@ -3223,31 +3223,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>16.71</v>
+        <v>16.77</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.006</v>
+        <v>0.0036</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>-0.0397</v>
+        <v>-0.0323</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>-0.1457</v>
+        <v>-0.1275</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-0.1364</v>
+        <v>-0.1338</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-0.1535</v>
+        <v>-0.1739</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.0018</v>
+        <v>-0.0042</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>0.5749</v>
@@ -3277,57 +3277,55 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>DESA</t>
+          <t>AYES</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>8.65</v>
+        <v>7.25</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>0.0023</v>
+        <v>-0.0473</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>-0.0303</v>
+        <v>-0.1038</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>-0.1341</v>
+        <v>-0.1597</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>-0.1762</v>
+        <v>-0.2352</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>-0.3564</v>
+        <v>-0.2328</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>-0.4354</v>
+        <v>0.6004</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>8.199999999999999</v>
+        <v>1.99</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.2088</v>
+        <v>0.4183</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>0.2301</v>
+        <v>0.314</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0.0037</v>
+        <v>0.8128</v>
       </c>
       <c r="N49" s="7" t="n">
-        <v>0.3571</v>
+        <v>42.7724</v>
       </c>
       <c r="O49" s="7" t="n">
-        <v>0.2399</v>
-      </c>
-      <c r="P49" s="7" t="n">
-        <v>0.1277</v>
-      </c>
+        <v>0.0208</v>
+      </c>
+      <c r="P49" s="5" t="inlineStr"/>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R49" s="5" t="inlineStr"/>
@@ -3335,55 +3333,57 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AYES</t>
+          <t>DESA</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>7.61</v>
+        <v>8.5</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>-0.0487</v>
+        <v>-0.0173</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.0476</v>
+        <v>-0.0751</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>-0.1544</v>
+        <v>-0.1318</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>-0.229</v>
+        <v>-0.1889</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.1721</v>
+        <v>-0.3732</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0.8119</v>
+        <v>-0.4382</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>2.09</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0.4183</v>
+        <v>0.2088</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.314</v>
+        <v>0.2301</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.8128</v>
+        <v>0.0037</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>42.7724</v>
+        <v>0.3571</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>0.0208</v>
-      </c>
-      <c r="P50" s="2" t="inlineStr"/>
+        <v>0.2399</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>0.1277</v>
+      </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr"/>
@@ -3391,57 +3391,57 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>ZRGYO</t>
+          <t>EGGUB</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>19</v>
+        <v>92.5</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>-0.0026</v>
+        <v>-0.0542</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>-0.0206</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-0.0281</v>
+        <v>-0.1763</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>0.0722</v>
+        <v>-0.0299</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>-0.1212</v>
+        <v>-0.2324</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>-0.1852</v>
+        <v>-0.1998</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>14.38</v>
+        <v>12.94</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>2.3363</v>
+        <v>0.4926</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>3.5944</v>
+        <v>0.6905</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>3.6478</v>
+        <v>0.7726999999999999</v>
       </c>
       <c r="N51" s="7" t="n">
-        <v>0.2899</v>
+        <v>0.5777</v>
       </c>
       <c r="O51" s="7" t="n">
-        <v>0.5917</v>
+        <v>0.4324</v>
       </c>
       <c r="P51" s="7" t="n">
-        <v>0.0776</v>
+        <v>0.0886</v>
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R51" s="5" t="inlineStr"/>
@@ -3449,57 +3449,57 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>EGGUB</t>
+          <t>ZRGYO</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>97.8</v>
+        <v>19</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>-0.0166</v>
+        <v>0</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.0215</v>
+        <v>-0.0063</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>-0.1011</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.0051</v>
+        <v>0.09380000000000001</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.183</v>
+        <v>-0.1196</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>-0.1353</v>
+        <v>-0.2024</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>13.68</v>
+        <v>14.38</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0.4926</v>
+        <v>2.3363</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.6905</v>
+        <v>3.5944</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.7726999999999999</v>
+        <v>3.6478</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.5777</v>
+        <v>0.2899</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>0.4324</v>
+        <v>0.5917</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>0.0886</v>
+        <v>0.0776</v>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr"/>
@@ -3511,31 +3511,31 @@
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>0.004</v>
+        <v>-0.004</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0.004</v>
+        <v>-0.0262</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-0.0616</v>
+        <v>-0.0765</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>-0.1965</v>
+        <v>-0.1984</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>-0.2208</v>
+        <v>-0.2316</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>0.0917</v>
+        <v>0.1078</v>
       </c>
       <c r="I53" s="6" t="n">
         <v>0.96</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>15.07</v>
+        <v>15.01</v>
       </c>
       <c r="K53" s="7" t="n">
         <v>0.3804</v>
@@ -3565,57 +3565,57 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ARASE</t>
+          <t>KARSN</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>98</v>
+        <v>8.81</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.0108</v>
+        <v>-0.035</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>-0.0091</v>
+        <v>-0.0476</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>-0.1928</v>
+        <v>-0.4644</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>-0.1709</v>
+        <v>-0.1962</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-0.0364</v>
+        <v>-0.1728</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>0.8702</v>
+        <v>-0.1704</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>8.93</v>
+        <v>32.79</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0.1264</v>
+        <v>0.8458</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.596</v>
+        <v>1.2698</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.7123999999999999</v>
+        <v>1.2002</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>4.0303</v>
+        <v>2.1122</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>0.25</v>
+        <v>0.1667</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>0.1463</v>
+        <v>0.07339999999999999</v>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr"/>
@@ -3623,57 +3623,57 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>KARSN</t>
+          <t>ARASE</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>9.130000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>0.0178</v>
+        <v>-0.0235</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>-0.0172</v>
+        <v>-0.0235</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-0.3552</v>
+        <v>-0.2226</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>-0.2047</v>
+        <v>-0.2117</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0868</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>-0.1387</v>
+        <v>0.8006</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>33.98</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>0.8458</v>
+        <v>0.1264</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>1.2698</v>
+        <v>0.596</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>1.2002</v>
+        <v>0.7123999999999999</v>
       </c>
       <c r="N55" s="7" t="n">
-        <v>2.1122</v>
+        <v>4.0303</v>
       </c>
       <c r="O55" s="7" t="n">
-        <v>0.1667</v>
+        <v>0.25</v>
       </c>
       <c r="P55" s="7" t="n">
-        <v>0.07339999999999999</v>
+        <v>0.1463</v>
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R55" s="5" t="inlineStr"/>
@@ -3681,57 +3681,57 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>TNZTP</t>
+          <t>CIMSA</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>24.4</v>
+        <v>40.22</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.0073</v>
+        <v>-0.0257</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.0608</v>
+        <v>-0.0396</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>-0.1712</v>
+        <v>-0.1129</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.0655</v>
+        <v>-0.1351</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>0.0702</v>
+        <v>-0.2552</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>0.09119999999999999</v>
+        <v>-0.08800000000000001</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>1.02</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>18.06</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0.4327</v>
+        <v>0.3754999999999999</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.4143</v>
+        <v>0.3037</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.5201</v>
+        <v>0.4933</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.0702</v>
+        <v>1.15</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>0.3617</v>
+        <v>0.1807</v>
       </c>
       <c r="P56" s="4" t="n">
-        <v>0.0551</v>
+        <v>0.2729</v>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>Sağlık hizmetleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr"/>
@@ -3743,31 +3743,31 @@
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>11.72</v>
+        <v>11.54</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>0.0455</v>
+        <v>-0.0154</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.0492</v>
+        <v>-0.0103</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-0.0126</v>
+        <v>-0.0237</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.1088</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>0.2535</v>
+        <v>0.2135</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>0.4206</v>
+        <v>0.416</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>9.880000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="K57" s="7" t="n">
         <v>0.6297</v>
@@ -3797,53 +3797,53 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>CIMSA</t>
+          <t>CMENT</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>41.28</v>
+        <v>227.9</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>0.0039</v>
+        <v>-0.042</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>0.001</v>
+        <v>-0.0555</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>-0.1014</v>
+        <v>-0.05</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>-0.0987</v>
+        <v>-0.2397</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-0.2137</v>
+        <v>-0.2878</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>-0.0558</v>
+        <v>-0.376</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>9.779999999999999</v>
+        <v>22.49</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0.3754999999999999</v>
+        <v>0.0934</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.3037</v>
+        <v>0.1109</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.4933</v>
+        <v>0.1008</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>1.15</v>
+        <v>0.4922</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>0.1807</v>
+        <v>0.1647</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
@@ -3855,57 +3855,57 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>CMENT</t>
+          <t>TNZTP</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>237.9</v>
+        <v>25.66</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0516</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>0.0285</v>
+        <v>0.0039</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-0.0226</v>
+        <v>-0.1378</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>-0.174</v>
+        <v>0.1334</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>-0.2691</v>
+        <v>0.08449999999999999</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>-0.3531</v>
+        <v>0.1538</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>23.48</v>
+        <v>18.99</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>0.0934</v>
+        <v>0.4327</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>0.1109</v>
+        <v>0.4143</v>
       </c>
       <c r="M59" s="7" t="n">
-        <v>0.1008</v>
+        <v>0.5201</v>
       </c>
       <c r="N59" s="7" t="n">
-        <v>0.4922</v>
+        <v>0.0702</v>
       </c>
       <c r="O59" s="7" t="n">
-        <v>0.1647</v>
+        <v>0.3617</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0551</v>
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Sağlık hizmetleri</t>
         </is>
       </c>
       <c r="R59" s="5" t="inlineStr"/>
@@ -3913,57 +3913,57 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>GESAN</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>10.55</v>
+        <v>40.4</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>0.005699999999999999</v>
+        <v>-0.0367</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>0.0038</v>
+        <v>-0.1133</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>-0.0866</v>
+        <v>-0.3484</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>-0.1014</v>
+        <v>-0.4886</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>0.0283</v>
+        <v>-0.1928</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>-0.1245</v>
+        <v>-0.0717</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>7.08</v>
+        <v>10.86</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0.423</v>
+        <v>0.2641</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.5552</v>
+        <v>0.2931</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.8170999999999999</v>
+        <v>0.3273</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>10.0728</v>
+        <v>0.4479</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>0.179</v>
+        <v>0.1778</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>0.2236</v>
+        <v>0.1266</v>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr"/>
@@ -3971,57 +3971,57 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>GESAN</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>41.94</v>
+        <v>10.43</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>0.0305</v>
+        <v>-0.0114</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>-0.0155</v>
+        <v>-0.0298</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>-0.3192</v>
+        <v>-0.0827</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>-0.4711</v>
+        <v>-0.0993</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>-0.1548</v>
+        <v>0.0068</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>-0.0385</v>
+        <v>-0.1394</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>11.27</v>
+        <v>7</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>0.2641</v>
+        <v>0.423</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>0.2931</v>
+        <v>0.5552</v>
       </c>
       <c r="M61" s="7" t="n">
-        <v>0.3273</v>
+        <v>0.8170999999999999</v>
       </c>
       <c r="N61" s="7" t="n">
-        <v>0.4479</v>
+        <v>10.0728</v>
       </c>
       <c r="O61" s="7" t="n">
-        <v>0.1778</v>
+        <v>0.179</v>
       </c>
       <c r="P61" s="7" t="n">
-        <v>0.1266</v>
+        <v>0.2236</v>
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R61" s="5" t="inlineStr"/>
@@ -4029,57 +4029,57 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>MOBTL</t>
+          <t>CWENE</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>10.59</v>
+        <v>18.32</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0.004699999999999999</v>
+        <v>-0.0393</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>0.0282</v>
+        <v>-0.1011</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>-0.2144</v>
+        <v>-0.4094</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>-0.2977</v>
+        <v>-0.5141</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-0.223</v>
+        <v>-0.479</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>0.433</v>
+        <v>-0.303</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>15.01</v>
+        <v>6.81</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0.5631</v>
+        <v>0.5809000000000001</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.4406</v>
+        <v>0.9067000000000001</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.5064</v>
+        <v>0.8432999999999999</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1.6818</v>
+        <v>5.095899999999999</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.1918</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>0.08689999999999999</v>
+        <v>0.2052</v>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr"/>
@@ -4087,57 +4087,55 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>CWENE</t>
+          <t>YKSLN</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>19.07</v>
+        <v>2.26</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>-0.0114</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>-0.0295</v>
+        <v>0.08130000000000001</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-0.429</v>
+        <v>-0.4619</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>-0.5218</v>
+        <v>-0.2848</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>-0.42</v>
+        <v>-0.2871</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>-0.2566</v>
+        <v>-0.3694</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="J63" s="6" t="n">
-        <v>7.09</v>
-      </c>
+        <v>1.12</v>
+      </c>
+      <c r="J63" s="5" t="inlineStr"/>
       <c r="K63" s="7" t="n">
-        <v>0.5809000000000001</v>
+        <v>0.1126</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>0.9067000000000001</v>
+        <v>0.0263</v>
       </c>
       <c r="M63" s="7" t="n">
-        <v>0.8432999999999999</v>
+        <v>0.6127</v>
       </c>
       <c r="N63" s="7" t="n">
-        <v>5.095899999999999</v>
+        <v>0.8754000000000001</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>0.1918</v>
+        <v>0.1443</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>0.2052</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R63" s="5" t="inlineStr"/>
@@ -4149,28 +4147,28 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>23.8</v>
+        <v>22.86</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.0998</v>
+        <v>-0.0395</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>0.1655</v>
+        <v>0.1184</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>-0.32</v>
+        <v>-0.3685</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>-0.3554</v>
+        <v>-0.3933</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.4287</v>
+        <v>-0.4141</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>0.1464</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="4" t="n">
@@ -4201,55 +4199,57 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>DAGI</t>
+          <t>MOBTL</t>
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>5.55</v>
+        <v>10.52</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>-0.0464</v>
+        <v>-0.0066</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>0.0128</v>
+        <v>0.0253</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>-0.4237</v>
+        <v>-0.2006</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>-0.4267</v>
+        <v>-0.2669</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>-0.0593</v>
+        <v>-0.2371</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>-0.3123</v>
+        <v>0.4672</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="J65" s="5" t="inlineStr"/>
+        <v>1.14</v>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>14.91</v>
+      </c>
       <c r="K65" s="7" t="n">
-        <v>0.5429999999999999</v>
+        <v>0.5631</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>1.1389</v>
+        <v>0.4406</v>
       </c>
       <c r="M65" s="7" t="n">
-        <v>1.8634</v>
+        <v>0.5064</v>
       </c>
       <c r="N65" s="7" t="n">
-        <v>0.5748</v>
+        <v>1.6818</v>
       </c>
       <c r="O65" s="7" t="n">
-        <v>0.1561</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="P65" s="7" t="n">
-        <v>-0.0597</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R65" s="5" t="inlineStr"/>
@@ -4257,55 +4257,57 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>YKSLN</t>
+          <t>ISDMR</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>2.43</v>
+        <v>63.15</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.0565</v>
+        <v>-0.0417</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>0.1912</v>
+        <v>0.0352</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>-0.243</v>
+        <v>0.0429</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>-0.2136</v>
+        <v>0.1503</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.231</v>
+        <v>0.4352</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>-0.2811</v>
+        <v>0.6858</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>14.89</v>
+      </c>
       <c r="K66" s="4" t="n">
-        <v>0.1126</v>
+        <v>0.1859</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.0263</v>
+        <v>0.3543</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.6127</v>
+        <v>0.4035</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.8754000000000001</v>
+        <v>0.208</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>0.1443</v>
+        <v>0.1056</v>
       </c>
       <c r="P66" s="4" t="n">
-        <v>-0.04969999999999999</v>
+        <v>0.0859</v>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr"/>
@@ -4317,31 +4319,31 @@
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>274.75</v>
+        <v>266.5</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>-0.0036</v>
+        <v>-0.03</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>0.0507</v>
+        <v>-0.0037</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>-0.0009</v>
+        <v>-0.0318</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.0309</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>-0.1972</v>
+        <v>-0.1955</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>0.1568</v>
+        <v>0.1283</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>18.93</v>
+        <v>18.36</v>
       </c>
       <c r="K67" s="7" t="n">
         <v>0.3707</v>
@@ -4371,57 +4373,55 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ENKAI</t>
+          <t>DAGI</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>83.5</v>
+        <v>5.46</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0.0233</v>
+        <v>-0.0162</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>0.0103</v>
+        <v>-0.0197</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>-0.0809</v>
+        <v>-0.4191</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>-0.0602</v>
+        <v>-0.4167</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-0.1261</v>
+        <v>-0.102</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>0.1895</v>
+        <v>-0.3166</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="J68" s="3" t="n">
-        <v>12.54</v>
-      </c>
+        <v>1.19</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="4" t="n">
-        <v>0.4381</v>
+        <v>0.5429999999999999</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.1539</v>
+        <v>1.1389</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>0.1373</v>
+        <v>1.8634</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.3376</v>
+        <v>0.5748</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>0.2166</v>
+        <v>0.1561</v>
       </c>
       <c r="P68" s="4" t="n">
-        <v>0.1059</v>
+        <v>-0.0597</v>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr"/>
@@ -4429,57 +4429,57 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>ISDMR</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>65.90000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>0.05860000000000001</v>
+        <v>-0.0305</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>0.1122</v>
+        <v>-0.0375</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>0.0983</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>0.2204</v>
+        <v>-0.09960000000000001</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>0.4977</v>
+        <v>-0.2268</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>0.7947</v>
+        <v>0.1843</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>15.54</v>
+        <v>12.16</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>0.1859</v>
+        <v>0.4381</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>0.3543</v>
+        <v>0.1539</v>
       </c>
       <c r="M69" s="7" t="n">
-        <v>0.4035</v>
+        <v>0.1373</v>
       </c>
       <c r="N69" s="7" t="n">
-        <v>0.208</v>
+        <v>0.3376</v>
       </c>
       <c r="O69" s="7" t="n">
-        <v>0.1056</v>
+        <v>0.2166</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>0.0859</v>
+        <v>0.1059</v>
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R69" s="5" t="inlineStr"/>
@@ -4487,57 +4487,57 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GEDIK</t>
+          <t>MAALT</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>4.92</v>
+        <v>814.5</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>-0.0219</v>
+        <v>-0.0181</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>-0.0409</v>
+        <v>-0.0479</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>-0.159</v>
+        <v>-0.1952</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>-0.3214</v>
+        <v>-0.2568</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>-0.09230000000000001</v>
+        <v>-0.468</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>-0.2971</v>
+        <v>-0.2649</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>5.21</v>
+        <v>1755.01</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0.6583</v>
+        <v>0.248</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>0.6568000000000001</v>
+        <v>3.5256</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.7293999999999999</v>
+        <v>0.3863</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.3481</v>
+        <v>0.9832</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>0.6628000000000001</v>
+        <v>0.4575</v>
       </c>
       <c r="P70" s="4" t="n">
-        <v>0.275</v>
+        <v>-0</v>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr"/>
@@ -4545,57 +4545,57 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>MAALT</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>829.5</v>
+        <v>28.82</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>0.0122</v>
+        <v>-0.0322</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>-0.0287</v>
+        <v>-0.0463</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>-0.1852</v>
+        <v>-0.1972</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>-0.2452</v>
+        <v>-0.1699</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>-0.3673</v>
+        <v>-0.3598</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>-0.2692</v>
+        <v>-0.2901</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>1787.33</v>
+        <v>6.44</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>0.248</v>
+        <v>0.4021</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>3.5256</v>
+        <v>0.2915</v>
       </c>
       <c r="M71" s="7" t="n">
-        <v>0.3863</v>
+        <v>0.201</v>
       </c>
       <c r="N71" s="7" t="n">
-        <v>0.9832</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="O71" s="7" t="n">
-        <v>0.4575</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="P71" s="7" t="n">
-        <v>-0</v>
+        <v>0.298</v>
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R71" s="5" t="inlineStr"/>
@@ -4603,57 +4603,57 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>NTGAZ</t>
+          <t>GEDIK</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>10.88</v>
+        <v>4.9</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>0.0028</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.022</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>-0.0372</v>
+        <v>-0.1404</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>-0.07719999999999999</v>
+        <v>-0.2919</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>-0.1016</v>
+        <v>-0.1312</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>0.1636</v>
+        <v>-0.2909</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>6.91</v>
+        <v>5.19</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0.3448</v>
+        <v>0.6583</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.3645</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.4084</v>
+        <v>0.7293999999999999</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0.5755</v>
+        <v>0.3481</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>0.2148</v>
+        <v>0.6628000000000001</v>
       </c>
       <c r="P72" s="4" t="n">
-        <v>0.2137</v>
+        <v>0.275</v>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr"/>
@@ -4661,53 +4661,53 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>29.78</v>
+        <v>6.5</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>0.0095</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>-0.0356</v>
+        <v>-0.408</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-0.1841</v>
+        <v>-0.8683</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>-0.1398</v>
+        <v>-0.8415</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>-0.2789</v>
+        <v>-0.6937000000000001</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>-0.2852</v>
+        <v>-0.7434999999999999</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>6.65</v>
+        <v>4.13</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>0.4021</v>
+        <v>7.8666</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>0.2915</v>
+        <v>3.1929</v>
       </c>
       <c r="M73" s="7" t="n">
-        <v>0.201</v>
+        <v>4.946499999999999</v>
       </c>
       <c r="N73" s="7" t="n">
-        <v>0.07690000000000001</v>
+        <v>1.0979</v>
       </c>
       <c r="O73" s="7" t="n">
-        <v>0.8484999999999999</v>
+        <v>0.4854</v>
       </c>
       <c r="P73" s="7" t="n">
-        <v>0.298</v>
+        <v>0.586</v>
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
@@ -4719,57 +4719,57 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GLCVY</t>
+          <t>NTGAZ</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>39.16</v>
+        <v>10.69</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>0.0036</v>
+        <v>-0.0175</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>-0.0564</v>
+        <v>-0.0255</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>-0.2625</v>
+        <v>-0.0664</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>-0.2834</v>
+        <v>-0.0506</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-0.3709</v>
+        <v>-0.1908</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>-0.4357</v>
+        <v>0.1532</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>3.79</v>
+        <v>6.79</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0.265</v>
+        <v>0.3448</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.2739</v>
+        <v>0.3645</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.2851</v>
+        <v>0.4084</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.0788</v>
+        <v>0.5755</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>0.7251000000000001</v>
+        <v>0.2148</v>
       </c>
       <c r="P74" s="4" t="n">
-        <v>0.4011</v>
+        <v>0.2137</v>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr"/>
@@ -4777,57 +4777,57 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>GLCVY</t>
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>73.84999999999999</v>
+        <v>38.2</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>0.0221</v>
+        <v>-0.0245</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>-0.0101</v>
+        <v>-0.0591</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-0.0866</v>
+        <v>-0.2939</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>-0.1744</v>
+        <v>-0.2965</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>-0.0911</v>
+        <v>-0.3617</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>0.8782</v>
+        <v>-0.4264</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>27.18</v>
+        <v>3.7</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.265</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>0.3716</v>
+        <v>0.2739</v>
       </c>
       <c r="M75" s="7" t="n">
-        <v>0.4119</v>
+        <v>0.2851</v>
       </c>
       <c r="N75" s="7" t="n">
-        <v>0.9691</v>
+        <v>0.0788</v>
       </c>
       <c r="O75" s="7" t="n">
-        <v>0.3037</v>
+        <v>0.7251000000000001</v>
       </c>
       <c r="P75" s="7" t="n">
-        <v>0.0601</v>
+        <v>0.4011</v>
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R75" s="5" t="inlineStr"/>
@@ -4835,57 +4835,57 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GARFA</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>23.2</v>
+        <v>71.75</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>0.0265</v>
+        <v>-0.0284</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>0.0113</v>
+        <v>-0.0401</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>-0.1375</v>
+        <v>-0.1037</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>-0.1464</v>
+        <v>-0.221</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.1477</v>
+        <v>-0.1479</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>-0.1042</v>
+        <v>0.7331</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>3.52</v>
+        <v>26.41</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0.9562999999999999</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.9506</v>
+        <v>0.3716</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.4119</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.5365</v>
+        <v>0.9691</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>0.914</v>
+        <v>0.3037</v>
       </c>
       <c r="P76" s="4" t="n">
-        <v>0.496</v>
+        <v>0.0601</v>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R76" s="2" t="inlineStr"/>
@@ -4893,57 +4893,57 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>SELEC</t>
         </is>
       </c>
       <c r="B77" s="6" t="n">
-        <v>7.22</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>-0.0998</v>
+        <v>-0.0276</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>-0.4077</v>
+        <v>0.0566</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-0.8451000000000001</v>
+        <v>-0.8026000000000001</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>-0.8214</v>
+        <v>-0.6112</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>-0.6718000000000001</v>
+        <v>-0.1074</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>-0.7088</v>
+        <v>0.0173</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>4.59</v>
+        <v>24.19</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>7.8666</v>
+        <v>0.3781</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>3.1929</v>
+        <v>0.6063000000000001</v>
       </c>
       <c r="M77" s="7" t="n">
-        <v>4.946499999999999</v>
+        <v>1.4267</v>
       </c>
       <c r="N77" s="7" t="n">
-        <v>1.0979</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="O77" s="7" t="n">
-        <v>0.4854</v>
+        <v>0.0158</v>
       </c>
       <c r="P77" s="7" t="n">
-        <v>0.586</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="Q77" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R77" s="5" t="inlineStr"/>
@@ -4951,57 +4951,55 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SELEC</t>
+          <t>OBASE</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>23.82</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>0.09970000000000001</v>
+        <v>-0.0767</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>0.0953</v>
+        <v>-0.1275</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-0.3387</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>-0.593</v>
+        <v>-0.4042</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>-0.0462</v>
+        <v>-0.3648</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>0.0264</v>
+        <v>-0.3383</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J78" s="3" t="n">
-        <v>24.87</v>
-      </c>
+        <v>1.33</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="4" t="n">
-        <v>0.3781</v>
+        <v>0.2041</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>0.6063000000000001</v>
+        <v>0.3021</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>1.4267</v>
+        <v>0.5156000000000001</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.4873</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>0.0158</v>
+        <v>0.2465</v>
       </c>
       <c r="P78" s="4" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.1432</v>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr"/>
@@ -5009,55 +5007,57 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>OZYSR</t>
+          <t>GARFA</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
-        <v>11.74</v>
+        <v>22.9</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>0.0218</v>
+        <v>-0.0129</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>0.0034</v>
+        <v>0.016</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.1417</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1365</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>0.0725</v>
+        <v>-0.1804</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>0.4586</v>
+        <v>-0.102</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J79" s="5" t="inlineStr"/>
+        <v>1.35</v>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>3.47</v>
+      </c>
       <c r="K79" s="7" t="n">
-        <v>0.161</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="L79" s="7" t="n">
-        <v>0.1742</v>
+        <v>0.9506</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>0.6839</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="N79" s="7" t="n">
-        <v>0.5105</v>
+        <v>0.5365</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>0.042</v>
+        <v>0.914</v>
       </c>
       <c r="P79" s="7" t="n">
-        <v>-0.0335</v>
+        <v>0.496</v>
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R79" s="5" t="inlineStr"/>
@@ -5069,31 +5069,31 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>30.4</v>
+        <v>30.22</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.0059</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>-0.0588</v>
+        <v>-0.0702</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>-0.0318</v>
+        <v>-0.0131</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>-0.0594</v>
+        <v>-0.058</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>0.0857</v>
+        <v>0.09179999999999999</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>0.3252</v>
+        <v>0.3952000000000001</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>6.98</v>
+        <v>6.94</v>
       </c>
       <c r="K80" s="4" t="n">
         <v>0.763</v>
@@ -5123,55 +5123,57 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>KCAER</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>6.61</v>
+        <v>10.63</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>0.0061</v>
+        <v>-0.0203</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>-0.0294</v>
+        <v>0.0124</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-0.1427</v>
+        <v>-0.2519</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>-0.1536</v>
+        <v>-0.1817</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>-0.1978</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>-0.2205</v>
+        <v>-0.2149</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="J81" s="5" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>30.96</v>
+      </c>
       <c r="K81" s="7" t="n">
-        <v>0.3952000000000001</v>
+        <v>0.1522</v>
       </c>
       <c r="L81" s="7" t="n">
-        <v>0.4088000000000001</v>
+        <v>0.2873</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>0.4094</v>
+        <v>0.3247</v>
       </c>
       <c r="N81" s="7" t="n">
-        <v>0.7489</v>
+        <v>1.1982</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>0.7836</v>
+        <v>0.1199</v>
       </c>
       <c r="P81" s="7" t="n">
-        <v>-0.0106</v>
+        <v>0.0508</v>
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>Çeşitli Hizmetler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R81" s="5" t="inlineStr"/>
@@ -5179,57 +5181,55 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>KCAER</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>10.85</v>
+        <v>6.56</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>0.0353</v>
+        <v>-0.0076</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>0.0037</v>
+        <v>-0.0296</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>-0.2568</v>
+        <v>-0.123</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>-0.1842</v>
+        <v>-0.1665</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.2077</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>-0.178</v>
+        <v>-0.2227</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>31.6</v>
-      </c>
+        <v>1.37</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="4" t="n">
-        <v>0.1522</v>
+        <v>0.3952000000000001</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>0.2873</v>
+        <v>0.4088000000000001</v>
       </c>
       <c r="M82" s="4" t="n">
-        <v>0.3247</v>
+        <v>0.4094</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>1.1982</v>
+        <v>0.7489</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>0.1199</v>
+        <v>0.7836</v>
       </c>
       <c r="P82" s="4" t="n">
-        <v>0.0508</v>
+        <v>-0.0106</v>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Çeşitli Hizmetler</t>
         </is>
       </c>
       <c r="R82" s="2" t="inlineStr"/>
@@ -5237,55 +5237,57 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>GRTHO</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>89.7</v>
+        <v>109.8</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>0.0455</v>
+        <v>-0.1</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>-0.0033</v>
+        <v>-0.0926</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-0.2132</v>
+        <v>-0.5085000000000001</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>-0.3163</v>
+        <v>-0.5599000000000001</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>-0.2138</v>
+        <v>-0.5871999999999999</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>-0.1465</v>
+        <v>-0.8162</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="J83" s="5" t="inlineStr"/>
+        <v>1.38</v>
+      </c>
+      <c r="J83" s="6" t="n">
+        <v>7.64</v>
+      </c>
       <c r="K83" s="7" t="n">
-        <v>0.3957</v>
+        <v>0.5085000000000001</v>
       </c>
       <c r="L83" s="7" t="n">
-        <v>2.0344</v>
+        <v>0.4487</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>3.8494</v>
+        <v>0.2298</v>
       </c>
       <c r="N83" s="7" t="n">
-        <v>0.889</v>
+        <v>0.9399</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>0.0349</v>
+        <v>0.1089</v>
       </c>
       <c r="P83" s="7" t="n">
-        <v>-0.0175</v>
+        <v>0.2287</v>
       </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R83" s="5" t="inlineStr"/>
@@ -5293,55 +5295,55 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>OBASE</t>
+          <t>ACSEL</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>25.8</v>
+        <v>86.95</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>-0.0054</v>
+        <v>-0.0307</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.023</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>-0.2974</v>
+        <v>-0.2359</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>-0.3281</v>
+        <v>-0.3233</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>-0.3175</v>
+        <v>-0.2556</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>-0.2829</v>
+        <v>-0.1859</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="4" t="n">
-        <v>0.2041</v>
+        <v>0.3957</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.3021</v>
+        <v>2.0344</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>0.5156000000000001</v>
+        <v>3.8494</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>0.4873</v>
+        <v>0.889</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>0.2465</v>
+        <v>0.0349</v>
       </c>
       <c r="P84" s="4" t="n">
-        <v>0.1432</v>
+        <v>-0.0175</v>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr"/>
@@ -5349,53 +5351,51 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>SARKY</t>
+          <t>OZYSR</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>19.93</v>
+        <v>11.84</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>0.0284</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>-0.0537</v>
+        <v>0.0395</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-0.2422</v>
+        <v>-0.015</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>-0.2299</v>
+        <v>-0.0588</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>-0.2933</v>
+        <v>0.0735</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0.3521</v>
+        <v>0.3941</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="J85" s="6" t="n">
-        <v>73.03</v>
-      </c>
+        <v>1.38</v>
+      </c>
+      <c r="J85" s="5" t="inlineStr"/>
       <c r="K85" s="7" t="n">
-        <v>0.5590999999999999</v>
+        <v>0.161</v>
       </c>
       <c r="L85" s="7" t="n">
-        <v>0.3671</v>
+        <v>0.1742</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>0.2342</v>
+        <v>0.6839</v>
       </c>
       <c r="N85" s="7" t="n">
-        <v>0.8034</v>
+        <v>0.5105</v>
       </c>
       <c r="O85" s="7" t="n">
-        <v>0.0217</v>
+        <v>0.042</v>
       </c>
       <c r="P85" s="7" t="n">
-        <v>0.0229</v>
+        <v>-0.0335</v>
       </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
@@ -5407,57 +5407,57 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GRTHO</t>
+          <t>SARKY</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>122</v>
+        <v>18.88</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>0.004099999999999999</v>
+        <v>-0.0527</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>-0.0476</v>
+        <v>-0.0949</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>-0.3629</v>
+        <v>-0.2356</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>-0.4844</v>
+        <v>-0.2676</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>-0.5149</v>
+        <v>-0.338</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>-0.7959999999999999</v>
+        <v>0.2173</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>8.49</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0.5085000000000001</v>
+        <v>0.5590999999999999</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>0.4487</v>
+        <v>0.3671</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>0.2298</v>
+        <v>0.2342</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>0.9399</v>
+        <v>0.8034</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>0.1089</v>
+        <v>0.0217</v>
       </c>
       <c r="P86" s="4" t="n">
-        <v>0.2287</v>
+        <v>0.0229</v>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr"/>
@@ -5465,57 +5465,57 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>GENIL</t>
+          <t>RALYH</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>4.67</v>
+        <v>36.84</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>0.09880000000000001</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>-0.1586</v>
+        <v>-0.4087</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>-0.5981000000000001</v>
+        <v>-0.8642</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>-0.4805</v>
+        <v>-0.8228</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>-0.5492</v>
+        <v>-0.8694</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>-0.6598999999999999</v>
+        <v>-0.7774</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>17.03</v>
+        <v>4.77</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>0.5049</v>
+        <v>0.7070000000000001</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>0.7672</v>
+        <v>1.4848</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>1.1622</v>
+        <v>1.5369</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>1.2274</v>
+        <v>0.5434</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>0.0922</v>
+        <v>0.2854</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>0.1305</v>
+        <v>0.3914</v>
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R87" s="5" t="inlineStr"/>
@@ -5523,57 +5523,57 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>ALFAS</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>14.16</v>
+        <v>28.76</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>0.09939999999999999</v>
+        <v>-0.029</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>0.7678</v>
+        <v>-0.08810000000000001</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>-0.4309000000000001</v>
+        <v>-0.2682</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>-0.6078</v>
+        <v>-0.3654</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>-0.4616</v>
+        <v>-0.2507</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>0.4648</v>
+        <v>-0.347</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>1.83</v>
+        <v>34.46</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>2.1748</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>2.2285</v>
+        <v>0.4331</v>
       </c>
       <c r="M88" s="4" t="n">
-        <v>2.5519</v>
+        <v>0.8572</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>7.8348</v>
+        <v>40.5101</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>0.887</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="P88" s="4" t="n">
-        <v>1.1538</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R88" s="2" t="inlineStr"/>
@@ -5581,57 +5581,57 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>RALYH</t>
+          <t>TUPRS</t>
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>40.92</v>
+        <v>384.75</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>-0.0999</v>
+        <v>-0.0039</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>-0.4087</v>
+        <v>0.0192</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-0.8506999999999999</v>
+        <v>-0.08560000000000001</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>-0.8023</v>
+        <v>0.425</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>-0.8309000000000001</v>
+        <v>0.4492</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>-0.7504999999999999</v>
+        <v>1.1013</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>5.3</v>
+        <v>10.67</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>0.7070000000000001</v>
+        <v>0.465</v>
       </c>
       <c r="L89" s="7" t="n">
-        <v>1.4848</v>
+        <v>1.0453</v>
       </c>
       <c r="M89" s="7" t="n">
-        <v>1.5369</v>
+        <v>1.1002</v>
       </c>
       <c r="N89" s="7" t="n">
-        <v>0.5434</v>
+        <v>2.2351</v>
       </c>
       <c r="O89" s="7" t="n">
-        <v>0.2854</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="P89" s="7" t="n">
-        <v>0.3914</v>
+        <v>0.187</v>
       </c>
       <c r="Q89" s="5" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="R89" s="5" t="inlineStr"/>
@@ -5639,57 +5639,55 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>TUPRS</t>
+          <t>KNFRT</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>386.25</v>
+        <v>9.94</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>-0.0153</v>
+        <v>-0.0596</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>-0.0039</v>
+        <v>-0.2155</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>-0.032</v>
+        <v>-0.1859</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>0.4617</v>
+        <v>-0.164</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>0.5236999999999999</v>
+        <v>-0.1792</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>1.1246</v>
+        <v>-0.43</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="J90" s="3" t="n">
-        <v>10.72</v>
-      </c>
+        <v>1.65</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="4" t="n">
-        <v>0.465</v>
+        <v>0.7798</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>1.0453</v>
+        <v>1.3764</v>
       </c>
       <c r="M90" s="4" t="n">
-        <v>1.1002</v>
+        <v>26.3063</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>2.2351</v>
+        <v>0.625</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0124</v>
       </c>
       <c r="P90" s="4" t="n">
-        <v>0.187</v>
+        <v>-0.1091</v>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R90" s="2" t="inlineStr"/>
@@ -5697,57 +5695,57 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>ALFAS</t>
+          <t>EGPRO</t>
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>29.62</v>
+        <v>32.5</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>0.0109</v>
+        <v>-0.0407</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>-0.1094</v>
+        <v>-0.0672</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-0.2636</v>
+        <v>-0.1393</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>-0.3365</v>
+        <v>-0.1042</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>-0.2226</v>
+        <v>0.0559</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>-0.3476</v>
+        <v>0.1887</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>35.49</v>
+        <v>11.57</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>0.05019999999999999</v>
+        <v>0.3776</v>
       </c>
       <c r="L91" s="7" t="n">
-        <v>0.4331</v>
+        <v>0.5127</v>
       </c>
       <c r="M91" s="7" t="n">
-        <v>0.8572</v>
+        <v>0.5197999999999999</v>
       </c>
       <c r="N91" s="7" t="n">
-        <v>40.5101</v>
+        <v>1.3047</v>
       </c>
       <c r="O91" s="7" t="n">
-        <v>0.08410000000000001</v>
+        <v>0.2228</v>
       </c>
       <c r="P91" s="7" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.1742</v>
       </c>
       <c r="Q91" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R91" s="5" t="inlineStr"/>
@@ -5755,57 +5753,57 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>KTLEV</t>
+          <t>SAFKR</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>0.0989</v>
+        <v>-0.0453</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>-0.1992</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>-0.7431</v>
+        <v>-0.1519</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>-0.8613</v>
+        <v>-0.4</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>-0.6464</v>
+        <v>-0.5522</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>1.1185</v>
+        <v>-0.4575</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>1.95</v>
+        <v>17.45</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>3.5578</v>
+        <v>0.7861</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>3.6471</v>
+        <v>0.4555</v>
       </c>
       <c r="M92" s="4" t="n">
-        <v>5.174600000000001</v>
+        <v>0.3309</v>
       </c>
       <c r="N92" s="4" t="n">
-        <v>5.7649</v>
+        <v>0.5716</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>0.7222</v>
+        <v>0.2109</v>
       </c>
       <c r="P92" s="4" t="n">
-        <v>1.5072</v>
+        <v>0.1216</v>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R92" s="2" t="inlineStr"/>
@@ -5813,57 +5811,57 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>EGPRO</t>
+          <t>MEGMT</t>
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>33.88</v>
+        <v>3.45</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>0.0024</v>
+        <v>-0.0522</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>-0.0111</v>
+        <v>-0.1154</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>-0.1317</v>
+        <v>-0.2959</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>-0.0667</v>
+        <v>-0.5097</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>0.1469</v>
+        <v>-0.5951</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>0.2302</v>
+        <v>-0</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>12.07</v>
+        <v>7.37</v>
       </c>
       <c r="K93" s="7" t="n">
-        <v>0.3776</v>
+        <v>0.51</v>
       </c>
       <c r="L93" s="7" t="n">
-        <v>0.5127</v>
+        <v>0.4203</v>
       </c>
       <c r="M93" s="7" t="n">
-        <v>0.5197999999999999</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="N93" s="7" t="n">
-        <v>1.3047</v>
+        <v>0.2482</v>
       </c>
       <c r="O93" s="7" t="n">
-        <v>0.2228</v>
+        <v>0.0483</v>
       </c>
       <c r="P93" s="7" t="n">
-        <v>0.1742</v>
+        <v>0.2852</v>
       </c>
       <c r="Q93" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R93" s="5" t="inlineStr"/>
@@ -5871,55 +5869,57 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>KNFRT</t>
+          <t>ORGE</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>10.57</v>
+        <v>22.8</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>-0.0028</v>
+        <v>-0.0155</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>-0.105</v>
+        <v>-0.0256</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>-0.1844</v>
+        <v>-0.0215</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>-0.1279</v>
+        <v>0.0765</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>-0.0443</v>
+        <v>0.4970000000000001</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>-0.3855</v>
+        <v>0.6102000000000001</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="J94" s="2" t="inlineStr"/>
+      <c r="J94" s="3" t="n">
+        <v>10.58</v>
+      </c>
       <c r="K94" s="4" t="n">
-        <v>0.7798</v>
+        <v>0.251</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>1.3764</v>
+        <v>0.257</v>
       </c>
       <c r="M94" s="4" t="n">
-        <v>26.3063</v>
+        <v>0.2421</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>0.625</v>
+        <v>0.2676</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>0.0124</v>
+        <v>0.4943</v>
       </c>
       <c r="P94" s="4" t="n">
-        <v>-0.1091</v>
+        <v>0.2029</v>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr"/>
@@ -5927,57 +5927,57 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>ORGE</t>
+          <t>GENIL</t>
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>23.16</v>
+        <v>5.13</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>0.0203</v>
+        <v>0.09849999999999999</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>0.0395</v>
+        <v>0.0118</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>-0.0069</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>0.1081</v>
+        <v>-0.421</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>0.4686</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>0.6321</v>
+        <v>-0.6335999999999999</v>
       </c>
       <c r="I95" s="6" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>10.75</v>
+        <v>18.7</v>
       </c>
       <c r="K95" s="7" t="n">
-        <v>0.251</v>
+        <v>0.5049</v>
       </c>
       <c r="L95" s="7" t="n">
-        <v>0.257</v>
+        <v>0.7672</v>
       </c>
       <c r="M95" s="7" t="n">
-        <v>0.2421</v>
+        <v>1.1622</v>
       </c>
       <c r="N95" s="7" t="n">
-        <v>0.2676</v>
+        <v>1.2274</v>
       </c>
       <c r="O95" s="7" t="n">
-        <v>0.4943</v>
+        <v>0.0922</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>0.2029</v>
+        <v>0.1305</v>
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R95" s="5" t="inlineStr"/>
@@ -5985,57 +5985,57 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SAFKR</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>12.57</v>
+        <v>15.57</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>0.0475</v>
+        <v>0.6068</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>-0.106</v>
+        <v>-0.3722</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>-0.4197</v>
+        <v>-0.5792</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>-0.5165</v>
+        <v>-0.4686</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>-0.3915999999999999</v>
+        <v>0.4372</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>18.28</v>
+        <v>2.01</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0.7861</v>
+        <v>2.1748</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>0.4555</v>
+        <v>2.2285</v>
       </c>
       <c r="M96" s="4" t="n">
-        <v>0.3309</v>
+        <v>2.5519</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>0.5716</v>
+        <v>7.8348</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>0.2109</v>
+        <v>0.887</v>
       </c>
       <c r="P96" s="4" t="n">
-        <v>0.1216</v>
+        <v>1.1538</v>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr"/>
@@ -6043,57 +6043,55 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>MEGMT</t>
+          <t>KRPLS</t>
         </is>
       </c>
       <c r="B97" s="6" t="n">
-        <v>3.64</v>
+        <v>11.03</v>
       </c>
       <c r="C97" s="7" t="n">
-        <v>-0.005500000000000001</v>
+        <v>-0.0375</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>0.0028</v>
+        <v>-0.1083</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>-0.2612</v>
+        <v>-0.2287</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>-0.5019</v>
+        <v>0.2635</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>-0.5643</v>
+        <v>0.2534</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>0.0437</v>
+        <v>0.2379</v>
       </c>
       <c r="I97" s="6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="J97" s="6" t="n">
-        <v>7.77</v>
-      </c>
+        <v>1.82</v>
+      </c>
+      <c r="J97" s="5" t="inlineStr"/>
       <c r="K97" s="7" t="n">
-        <v>0.51</v>
+        <v>0.3576</v>
       </c>
       <c r="L97" s="7" t="n">
-        <v>0.4203</v>
+        <v>0.6872</v>
       </c>
       <c r="M97" s="7" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.9115000000000001</v>
       </c>
       <c r="N97" s="7" t="n">
-        <v>0.2482</v>
+        <v>0.7781999999999999</v>
       </c>
       <c r="O97" s="7" t="n">
-        <v>0.0483</v>
+        <v>0.166</v>
       </c>
       <c r="P97" s="7" t="n">
-        <v>0.2852</v>
+        <v>-0.0342</v>
       </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R97" s="5" t="inlineStr"/>
@@ -6101,57 +6099,57 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>FONET</t>
+          <t>KTLEV</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>4.19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>0.0072</v>
+        <v>0.1</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>-0.0668</v>
+        <v>-0.019</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>-0.1197</v>
+        <v>-0.7889</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>-0.1307</v>
+        <v>-0.848</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>-0.08710000000000001</v>
+        <v>-0.6423000000000001</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>0.7010999999999999</v>
+        <v>1.2175</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>13.61</v>
+        <v>2.14</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1.0251</v>
+        <v>3.5578</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>2.0469</v>
+        <v>3.6471</v>
       </c>
       <c r="M98" s="4" t="n">
-        <v>1.6971</v>
+        <v>5.174600000000001</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>1.6785</v>
+        <v>5.7649</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>0.4396</v>
+        <v>0.7222</v>
       </c>
       <c r="P98" s="4" t="n">
-        <v>0.8814</v>
+        <v>1.5072</v>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr"/>
@@ -6159,57 +6157,57 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>ENERY</t>
+          <t>FONET</t>
         </is>
       </c>
       <c r="B99" s="6" t="n">
-        <v>14.28</v>
+        <v>4.2</v>
       </c>
       <c r="C99" s="7" t="n">
-        <v>0.0092</v>
+        <v>0.0024</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>0.0547</v>
+        <v>-0.0708</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>0.3041</v>
+        <v>-0.1006</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>0.5015999999999999</v>
+        <v>-0.1549</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>0.5902000000000001</v>
+        <v>-0.0929</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>0.3797</v>
+        <v>0.505</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>22.77</v>
+        <v>13.65</v>
       </c>
       <c r="K99" s="7" t="n">
-        <v>0.4279</v>
+        <v>1.0251</v>
       </c>
       <c r="L99" s="7" t="n">
-        <v>0.7162999999999999</v>
+        <v>2.0469</v>
       </c>
       <c r="M99" s="7" t="n">
-        <v>0.8373999999999999</v>
+        <v>1.6971</v>
       </c>
       <c r="N99" s="7" t="n">
-        <v>0.6103000000000001</v>
+        <v>1.6785</v>
       </c>
       <c r="O99" s="7" t="n">
-        <v>0.2099</v>
+        <v>0.4396</v>
       </c>
       <c r="P99" s="7" t="n">
-        <v>0.1017</v>
+        <v>0.8814</v>
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R99" s="5" t="inlineStr"/>
@@ -6217,55 +6215,57 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>KRPLS</t>
+          <t>MPARK</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>11.46</v>
+        <v>432</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>0.0447</v>
+        <v>-0.012</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0092</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>-0.0434</v>
+        <v>-0.0226</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>0.2691</v>
+        <v>0.0403</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>0.3326</v>
+        <v>-0.0614</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>0.2935</v>
+        <v>0.2255</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr"/>
+        <v>1.88</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>13.49</v>
+      </c>
       <c r="K100" s="4" t="n">
-        <v>0.3576</v>
+        <v>0.3601</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>0.6872</v>
+        <v>0.3635</v>
       </c>
       <c r="M100" s="4" t="n">
-        <v>0.9115000000000001</v>
+        <v>0.5899</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>0.7781999999999999</v>
+        <v>0.1175</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>0.166</v>
+        <v>0.2737</v>
       </c>
       <c r="P100" s="4" t="n">
-        <v>-0.0342</v>
+        <v>0.2987</v>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Sağlık hizmetleri</t>
         </is>
       </c>
       <c r="R100" s="2" t="inlineStr"/>
@@ -6273,57 +6273,55 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>DURDO</t>
         </is>
       </c>
       <c r="B101" s="6" t="n">
-        <v>437.25</v>
+        <v>6.4</v>
       </c>
       <c r="C101" s="7" t="n">
-        <v>0.0405</v>
+        <v>-0.0244</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>0.0133</v>
+        <v>0.2774</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>0.0228</v>
+        <v>0.2308</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>0.0461</v>
+        <v>0.2774</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.5311</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>0.2592</v>
+        <v>0.8234</v>
       </c>
       <c r="I101" s="6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="J101" s="6" t="n">
-        <v>13.65</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="J101" s="5" t="inlineStr"/>
       <c r="K101" s="7" t="n">
-        <v>0.3601</v>
+        <v>0.3099</v>
       </c>
       <c r="L101" s="7" t="n">
-        <v>0.3635</v>
+        <v>0.2862</v>
       </c>
       <c r="M101" s="7" t="n">
-        <v>0.5899</v>
+        <v>0.3279</v>
       </c>
       <c r="N101" s="7" t="n">
-        <v>0.1175</v>
+        <v>0.1519</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>0.2737</v>
+        <v>0.0876</v>
       </c>
       <c r="P101" s="7" t="n">
-        <v>0.2987</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
-          <t>Sağlık hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R101" s="5" t="inlineStr"/>
@@ -6331,55 +6329,57 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>DURDO</t>
+          <t>DERIM</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>6.56</v>
+        <v>25.52</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>0.0202</v>
+        <v>-0.0478</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>0.3526</v>
+        <v>-0.08070000000000001</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>0.2788</v>
+        <v>-0.2827</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>0.312</v>
+        <v>-0.322</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>0.665</v>
+        <v>-0.314</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>0.8905</v>
+        <v>-0.361</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>14.06</v>
+      </c>
       <c r="K102" s="4" t="n">
-        <v>0.3099</v>
+        <v>0.1436</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>0.2862</v>
+        <v>0.2539</v>
       </c>
       <c r="M102" s="4" t="n">
-        <v>0.3279</v>
+        <v>0.0263</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>0.1519</v>
+        <v>0.0576</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>0.0876</v>
+        <v>0.0602</v>
       </c>
       <c r="P102" s="4" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.1637</v>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr"/>
@@ -6387,57 +6387,57 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>SAYAS</t>
+          <t>ENERY</t>
         </is>
       </c>
       <c r="B103" s="6" t="n">
-        <v>40.08</v>
+        <v>14.6</v>
       </c>
       <c r="C103" s="7" t="n">
-        <v>0.0152</v>
+        <v>0.0224</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>-0.0538</v>
+        <v>0.0665</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>-0.2836</v>
+        <v>0.2685</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>-0.1141</v>
+        <v>0.4571</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>-0.0191</v>
+        <v>0.5904</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>-0.2912</v>
+        <v>0.4038</v>
       </c>
       <c r="I103" s="6" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>15.97</v>
+        <v>23.28</v>
       </c>
       <c r="K103" s="7" t="n">
-        <v>0.486</v>
+        <v>0.4279</v>
       </c>
       <c r="L103" s="7" t="n">
-        <v>1.4655</v>
+        <v>0.7162999999999999</v>
       </c>
       <c r="M103" s="7" t="n">
-        <v>2.3632</v>
+        <v>0.8373999999999999</v>
       </c>
       <c r="N103" s="7" t="n">
-        <v>6.118200000000001</v>
+        <v>0.6103000000000001</v>
       </c>
       <c r="O103" s="7" t="n">
-        <v>0.1798</v>
+        <v>0.2099</v>
       </c>
       <c r="P103" s="7" t="n">
-        <v>0.1493</v>
+        <v>0.1017</v>
       </c>
       <c r="Q103" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R103" s="5" t="inlineStr"/>
@@ -6445,57 +6445,57 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>GLYHO</t>
+          <t>SAYAS</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>17.33</v>
+        <v>40.02</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>-0.0125</v>
+        <v>-0.0015</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>0.1038</v>
+        <v>-0.0561</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>0.023</v>
+        <v>-0.2513</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>-0.0125</v>
+        <v>-0.1281</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>0.1623</v>
+        <v>-0.0398</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>0.8919</v>
+        <v>-0.3112</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>5.79</v>
+        <v>15.95</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0.2312</v>
+        <v>0.486</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>0.317</v>
+        <v>1.4655</v>
       </c>
       <c r="M104" s="4" t="n">
-        <v>0.3503</v>
+        <v>2.3632</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>0.4888</v>
+        <v>6.118200000000001</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>0.3457</v>
+        <v>0.1798</v>
       </c>
       <c r="P104" s="4" t="n">
-        <v>-0.2226</v>
+        <v>0.1493</v>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr"/>
@@ -6503,57 +6503,57 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>DERIM</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B105" s="6" t="n">
-        <v>26.8</v>
+        <v>259.25</v>
       </c>
       <c r="C105" s="7" t="n">
-        <v>-0.003</v>
+        <v>-0.0217</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>-0.0074</v>
+        <v>-0.0038</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>-0.2434</v>
+        <v>-0.1045</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>-0.2992</v>
+        <v>-0.1351</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>-0.2584</v>
+        <v>-0.1322</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>-0.3379</v>
+        <v>-0.0512</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="J105" s="6" t="n">
-        <v>14.77</v>
+        <v>10.2</v>
       </c>
       <c r="K105" s="7" t="n">
-        <v>0.1436</v>
+        <v>1.7224</v>
       </c>
       <c r="L105" s="7" t="n">
-        <v>0.2539</v>
+        <v>1.8184</v>
       </c>
       <c r="M105" s="7" t="n">
-        <v>0.0263</v>
+        <v>1.3297</v>
       </c>
       <c r="N105" s="7" t="n">
-        <v>0.0576</v>
+        <v>5.0053</v>
       </c>
       <c r="O105" s="7" t="n">
-        <v>0.0602</v>
+        <v>0.0381</v>
       </c>
       <c r="P105" s="7" t="n">
-        <v>0.1637</v>
+        <v>0.2862</v>
       </c>
       <c r="Q105" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="R105" s="5" t="inlineStr"/>
@@ -6561,57 +6561,57 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>GLYHO</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>265</v>
+        <v>17.78</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>-0.0149</v>
+        <v>0.026</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.064</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>-0.1017</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>-0.04849999999999999</v>
+        <v>0.0552</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>-0.0694</v>
+        <v>0.8521</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>10.42</v>
+        <v>5.94</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1.7224</v>
+        <v>0.2312</v>
       </c>
       <c r="L106" s="4" t="n">
-        <v>1.8184</v>
+        <v>0.317</v>
       </c>
       <c r="M106" s="4" t="n">
-        <v>1.3297</v>
+        <v>0.3503</v>
       </c>
       <c r="N106" s="4" t="n">
-        <v>5.0053</v>
+        <v>0.4888</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>0.0381</v>
+        <v>0.3457</v>
       </c>
       <c r="P106" s="4" t="n">
-        <v>0.2862</v>
+        <v>-0.2226</v>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr"/>
@@ -6619,57 +6619,57 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>AHGAZ</t>
+          <t>GRSEL</t>
         </is>
       </c>
       <c r="B107" s="6" t="n">
-        <v>48.38</v>
+        <v>280.25</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>0.0075</v>
+        <v>-0.0009</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>0.0823</v>
+        <v>0.0399</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>0.2612</v>
+        <v>-0.0611</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>0.2901</v>
+        <v>-0.0916</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>1.098</v>
+        <v>-0.1159</v>
       </c>
       <c r="H107" s="7" t="n">
-        <v>0.6787000000000001</v>
+        <v>-0.1947</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="J107" s="6" t="n">
-        <v>22.89</v>
+        <v>8.51</v>
       </c>
       <c r="K107" s="7" t="n">
-        <v>0.659</v>
+        <v>0.3337</v>
       </c>
       <c r="L107" s="7" t="n">
-        <v>1.7979</v>
+        <v>0.6940999999999999</v>
       </c>
       <c r="M107" s="7" t="n">
-        <v>2.1313</v>
+        <v>0.2722</v>
       </c>
       <c r="N107" s="7" t="n">
-        <v>2.8917</v>
+        <v>0.7318000000000001</v>
       </c>
       <c r="O107" s="7" t="n">
-        <v>0.1977</v>
+        <v>0.3275</v>
       </c>
       <c r="P107" s="7" t="n">
-        <v>0.1152</v>
+        <v>0.3613</v>
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R107" s="5" t="inlineStr"/>
@@ -6677,57 +6677,57 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GRSEL</t>
+          <t>AHGAZ</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>280.5</v>
+        <v>48.7</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>0.0219</v>
+        <v>0.0066</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>0.0036</v>
+        <v>0.0633</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>-0.0571</v>
+        <v>0.2392</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>-0.0516</v>
+        <v>0.2994</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>-0.1221</v>
+        <v>1.0445</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>-0.181</v>
+        <v>0.7319</v>
       </c>
       <c r="I108" s="3" t="n">
         <v>2.05</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>8.52</v>
+        <v>23.05</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0.3337</v>
+        <v>0.659</v>
       </c>
       <c r="L108" s="4" t="n">
-        <v>0.6940999999999999</v>
+        <v>1.7979</v>
       </c>
       <c r="M108" s="4" t="n">
-        <v>0.2722</v>
+        <v>2.1313</v>
       </c>
       <c r="N108" s="4" t="n">
-        <v>0.7318000000000001</v>
+        <v>2.8917</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>0.3275</v>
+        <v>0.1977</v>
       </c>
       <c r="P108" s="4" t="n">
-        <v>0.3613</v>
+        <v>0.1152</v>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr"/>
@@ -6735,57 +6735,57 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>SANEL</t>
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>228</v>
+        <v>30.46</v>
       </c>
       <c r="C109" s="7" t="n">
-        <v>0.0179</v>
+        <v>-0.0457</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>0.0411</v>
+        <v>-0.0361</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>-0.0547</v>
+        <v>-0.3699</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>0.0133</v>
+        <v>-0.6347999999999999</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>-0.09699999999999999</v>
+        <v>-0.1856</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>-0.0061</v>
+        <v>0.0554</v>
       </c>
       <c r="I109" s="6" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="J109" s="6" t="n">
-        <v>21.31</v>
+        <v>2.94</v>
       </c>
       <c r="K109" s="7" t="n">
-        <v>0.493</v>
+        <v>0.309</v>
       </c>
       <c r="L109" s="7" t="n">
-        <v>0.3835</v>
+        <v>1.4614</v>
       </c>
       <c r="M109" s="7" t="n">
-        <v>0.4282</v>
+        <v>1.5381</v>
       </c>
       <c r="N109" s="7" t="n">
-        <v>0.1825</v>
+        <v>2.2148</v>
       </c>
       <c r="O109" s="7" t="n">
-        <v>0.2029</v>
+        <v>0.1491</v>
       </c>
       <c r="P109" s="7" t="n">
-        <v>0.1296</v>
+        <v>1.0947</v>
       </c>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R109" s="5" t="inlineStr"/>
@@ -6793,57 +6793,57 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>SANEL</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>31.92</v>
+        <v>221.7</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>0.0999</v>
+        <v>-0.0276</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>-0.0362</v>
+        <v>-0.0276</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>-0.3890999999999999</v>
+        <v>-0.04190000000000001</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>-0.6409</v>
+        <v>-0.0509</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>-0.0534</v>
+        <v>-0.1365</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>0.0733</v>
+        <v>-0.0793</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>3.08</v>
+        <v>20.72</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0.309</v>
+        <v>0.493</v>
       </c>
       <c r="L110" s="4" t="n">
-        <v>1.4614</v>
+        <v>0.3835</v>
       </c>
       <c r="M110" s="4" t="n">
-        <v>1.5381</v>
+        <v>0.4282</v>
       </c>
       <c r="N110" s="4" t="n">
-        <v>2.2148</v>
+        <v>0.1825</v>
       </c>
       <c r="O110" s="4" t="n">
-        <v>0.1491</v>
+        <v>0.2029</v>
       </c>
       <c r="P110" s="4" t="n">
-        <v>1.0947</v>
+        <v>0.1296</v>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr"/>
@@ -6851,57 +6851,57 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>BIMAS</t>
+          <t>VBTYZ</t>
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>402.75</v>
+        <v>22.96</v>
       </c>
       <c r="C111" s="7" t="n">
-        <v>0.0044</v>
+        <v>-0.0449</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>-0.0141</v>
+        <v>-0.0757</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>-0.0428</v>
+        <v>-0.3795</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>0.0974</v>
+        <v>-0.2055</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>0.0827</v>
+        <v>0.0581</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>0.4333</v>
+        <v>0.2021</v>
       </c>
       <c r="I111" s="6" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="J111" s="6" t="n">
-        <v>17.61</v>
+        <v>15.03</v>
       </c>
       <c r="K111" s="7" t="n">
-        <v>0.4214</v>
+        <v>0.5342</v>
       </c>
       <c r="L111" s="7" t="n">
-        <v>0.5271</v>
+        <v>0.9976999999999999</v>
       </c>
       <c r="M111" s="7" t="n">
-        <v>0.8381000000000001</v>
+        <v>3.6408</v>
       </c>
       <c r="N111" s="7" t="n">
-        <v>0.8737999999999999</v>
+        <v>1.3528</v>
       </c>
       <c r="O111" s="7" t="n">
-        <v>0.0611</v>
+        <v>0.2074</v>
       </c>
       <c r="P111" s="7" t="n">
-        <v>0.1613</v>
+        <v>-9.062000000000001</v>
       </c>
       <c r="Q111" s="5" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R111" s="5" t="inlineStr"/>
@@ -6909,57 +6909,57 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>VBTYZ</t>
+          <t>BIMAS</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>24.04</v>
+        <v>396.5</v>
       </c>
       <c r="C112" s="4" t="n">
-        <v>0.0152</v>
+        <v>-0.0155</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>-0.0491</v>
+        <v>-0.0428</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>-0.3657</v>
+        <v>-0.0779</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>-0.2164</v>
+        <v>0.0595</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>0.158</v>
+        <v>0.0496</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>0.2534</v>
+        <v>0.4524</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>15.73</v>
+        <v>17.34</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0.5342</v>
+        <v>0.4214</v>
       </c>
       <c r="L112" s="4" t="n">
-        <v>0.9976999999999999</v>
+        <v>0.5271</v>
       </c>
       <c r="M112" s="4" t="n">
-        <v>3.6408</v>
+        <v>0.8381000000000001</v>
       </c>
       <c r="N112" s="4" t="n">
-        <v>1.3528</v>
+        <v>0.8737999999999999</v>
       </c>
       <c r="O112" s="4" t="n">
-        <v>0.2074</v>
+        <v>0.0611</v>
       </c>
       <c r="P112" s="4" t="n">
-        <v>-9.062000000000001</v>
+        <v>0.1613</v>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr"/>
@@ -6971,31 +6971,31 @@
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>49.62</v>
+        <v>48.96</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>-0.0072</v>
+        <v>-0.0133</v>
       </c>
       <c r="D113" s="7" t="n">
-        <v>-0.08449999999999999</v>
+        <v>-0.1178</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>-0.2977</v>
+        <v>-0.3238</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>-0.424</v>
+        <v>-0.4446</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>0.1381</v>
+        <v>0.1178</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>0.8337</v>
+        <v>0.8228</v>
       </c>
       <c r="I113" s="6" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="J113" s="6" t="n">
-        <v>35.17</v>
+        <v>34.7</v>
       </c>
       <c r="K113" s="7" t="n">
         <v>0.8139</v>
@@ -7029,31 +7029,31 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>83.75</v>
+        <v>82.45</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>0.0417</v>
+        <v>-0.0155</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>0.0827</v>
+        <v>0.0391</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>0.0257</v>
+        <v>0.0319</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>0.0152</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>0.1746</v>
+        <v>0.095</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>0.7661</v>
+        <v>0.7543000000000001</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>11.31</v>
+        <v>11.14</v>
       </c>
       <c r="K114" s="4" t="n">
         <v>0.4257</v>
@@ -7087,31 +7087,31 @@
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>43.9</v>
+        <v>43.48</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>0.0393</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>0.0073</v>
+        <v>-0.0132</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-0.1802</v>
+        <v>-0.1804</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>-0.1833</v>
+        <v>-0.1598</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>-0.0036</v>
+        <v>-0.0548</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>0.7175</v>
+        <v>0.7091</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J115" s="6" t="n">
-        <v>28.03</v>
+        <v>27.77</v>
       </c>
       <c r="K115" s="7" t="n">
         <v>1.2681</v>
@@ -7141,57 +7141,57 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>TCKRC</t>
+          <t>HTTBT</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>123.3</v>
+        <v>31.98</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>-0.004</v>
+        <v>-0.0367</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>-0.0552</v>
+        <v>-0.0594</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>-0.1193</v>
+        <v>-0.0941</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>0.0232</v>
+        <v>-0.1495</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>0.3431</v>
+        <v>-0.2313</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>1.6123</v>
+        <v>-0.342</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>11.05</v>
+        <v>23.33</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>2.4396</v>
+        <v>0.3957</v>
       </c>
       <c r="L116" s="4" t="n">
-        <v>2.6112</v>
+        <v>0.3631</v>
       </c>
       <c r="M116" s="4" t="n">
-        <v>2.6298</v>
+        <v>0.3492</v>
       </c>
       <c r="N116" s="4" t="n">
-        <v>2.7617</v>
+        <v>0.2572</v>
       </c>
       <c r="O116" s="4" t="n">
-        <v>0.4116</v>
+        <v>0.4235</v>
       </c>
       <c r="P116" s="4" t="n">
-        <v>0.3455</v>
+        <v>0.5921</v>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr"/>
@@ -7199,57 +7199,57 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>HTTBT</t>
+          <t>TCKRC</t>
         </is>
       </c>
       <c r="B117" s="6" t="n">
-        <v>33.2</v>
+        <v>123.9</v>
       </c>
       <c r="C117" s="7" t="n">
-        <v>0.0012</v>
+        <v>0.0049</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>-0.0095</v>
+        <v>-0.0206</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>-0.0653</v>
+        <v>-0.09630000000000001</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>-0.1226</v>
+        <v>0.0257</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>-0.1496</v>
+        <v>0.2846</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>-0.3265999999999999</v>
+        <v>1.6508</v>
       </c>
       <c r="I117" s="6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>24.22</v>
+        <v>11.11</v>
       </c>
       <c r="K117" s="7" t="n">
-        <v>0.3957</v>
+        <v>2.4396</v>
       </c>
       <c r="L117" s="7" t="n">
-        <v>0.3631</v>
+        <v>2.6112</v>
       </c>
       <c r="M117" s="7" t="n">
-        <v>0.3492</v>
+        <v>2.6298</v>
       </c>
       <c r="N117" s="7" t="n">
-        <v>0.2572</v>
+        <v>2.7617</v>
       </c>
       <c r="O117" s="7" t="n">
-        <v>0.4235</v>
+        <v>0.4116</v>
       </c>
       <c r="P117" s="7" t="n">
-        <v>0.5921</v>
+        <v>0.3455</v>
       </c>
       <c r="Q117" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R117" s="5" t="inlineStr"/>
@@ -7261,31 +7261,31 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>142.5</v>
+        <v>141.1</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>-0.0273</v>
+        <v>-0.0098</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>-0.0166</v>
+        <v>-0.0587</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>0.0326</v>
+        <v>-0.0147</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>0.0493</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>0.0493</v>
+        <v>0.0247</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>-0.1441</v>
+        <v>-0.1526</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>15.5</v>
+        <v>15.34</v>
       </c>
       <c r="K118" s="4" t="n">
         <v>0.5617</v>
@@ -7319,31 +7319,31 @@
         </is>
       </c>
       <c r="B119" s="6" t="n">
-        <v>67.09999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="C119" s="7" t="n">
-        <v>0.0379</v>
+        <v>-0.0119</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>0.0205</v>
+        <v>-0.0785</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>-0.1881</v>
+        <v>-0.1784</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>-0.0067</v>
+        <v>-0.017</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>0.6414</v>
+        <v>0.5490999999999999</v>
       </c>
       <c r="H119" s="7" t="n">
-        <v>1.5417</v>
+        <v>1.5422</v>
       </c>
       <c r="I119" s="6" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>16.71</v>
+        <v>16.51</v>
       </c>
       <c r="K119" s="7" t="n">
         <v>2.0657</v>
@@ -7373,57 +7373,57 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ATATP</t>
+          <t>PKART</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>236.1</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>-0.0304</v>
+        <v>-0.0624</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>-0.0594</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>-0.1969</v>
+        <v>-0.2369</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>0.0931</v>
+        <v>-0.3007</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>0.6182</v>
+        <v>0.1244</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>0.6396000000000001</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>4.86</v>
+        <v>19.59</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0.3072</v>
+        <v>0.5093</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>0.2985</v>
+        <v>1.5572</v>
       </c>
       <c r="M120" s="4" t="n">
-        <v>0.3487</v>
+        <v>1.6598</v>
       </c>
       <c r="N120" s="4" t="n">
-        <v>0.6609999999999999</v>
+        <v>4.8022</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>0.3268</v>
+        <v>0.083</v>
       </c>
       <c r="P120" s="4" t="n">
-        <v>0.7543000000000001</v>
+        <v>0.2041</v>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr"/>
@@ -7435,31 +7435,31 @@
         </is>
       </c>
       <c r="B121" s="6" t="n">
-        <v>418</v>
+        <v>403.75</v>
       </c>
       <c r="C121" s="7" t="n">
-        <v>0.0258</v>
+        <v>-0.0341</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>0.007800000000000001</v>
+        <v>-0.0393</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-0.1706</v>
+        <v>-0.2013</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>-0.0413</v>
+        <v>-0.0152</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>-0.1504</v>
+        <v>-0.1856</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>0.4414</v>
+        <v>0.3863</v>
       </c>
       <c r="I121" s="6" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="J121" s="6" t="n">
-        <v>18.12</v>
+        <v>17.5</v>
       </c>
       <c r="K121" s="7" t="n">
         <v>0.1897</v>
@@ -7489,57 +7489,57 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>PKART</t>
+          <t>ATATP</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>94.5</v>
+        <v>233.5</v>
       </c>
       <c r="C122" s="4" t="n">
-        <v>0.08500000000000001</v>
+        <v>-0.011</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>0.1144</v>
+        <v>-0.08070000000000001</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>-0.2292</v>
+        <v>-0.1814</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>-0.2494</v>
+        <v>0.1237</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>0.2023</v>
+        <v>0.6238</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>0.0919</v>
+        <v>0.6092</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>20.89</v>
+        <v>4.8</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0.5093</v>
+        <v>0.3072</v>
       </c>
       <c r="L122" s="4" t="n">
-        <v>1.5572</v>
+        <v>0.2985</v>
       </c>
       <c r="M122" s="4" t="n">
-        <v>1.6598</v>
+        <v>0.3487</v>
       </c>
       <c r="N122" s="4" t="n">
-        <v>4.8022</v>
+        <v>0.6609999999999999</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>0.083</v>
+        <v>0.3268</v>
       </c>
       <c r="P122" s="4" t="n">
-        <v>0.2041</v>
+        <v>0.7543000000000001</v>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr"/>
@@ -7551,31 +7551,31 @@
         </is>
       </c>
       <c r="B123" s="6" t="n">
-        <v>19.27</v>
+        <v>18.9</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>0.0164</v>
+        <v>-0.0192</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>-0.0138</v>
+        <v>-0.1</v>
       </c>
       <c r="E123" s="7" t="n">
-        <v>-0.1585</v>
+        <v>-0.1393</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>-0.1715</v>
+        <v>-0.2476</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>-0.0563</v>
+        <v>-0.1076</v>
       </c>
       <c r="H123" s="7" t="n">
-        <v>0.2779</v>
+        <v>0.2418</v>
       </c>
       <c r="I123" s="6" t="n">
-        <v>3.59</v>
+        <v>3.52</v>
       </c>
       <c r="J123" s="6" t="n">
-        <v>25.38</v>
+        <v>24.89</v>
       </c>
       <c r="K123" s="7" t="n">
         <v>0.6388</v>
@@ -7609,28 +7609,28 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>31.46</v>
+        <v>31.26</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>0.0148</v>
+        <v>-0.0064</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>-0.009399999999999999</v>
+        <v>0.0216</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>-0.2684</v>
+        <v>-0.2467</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>-0.3332</v>
+        <v>-0.326</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>-0.4461</v>
+        <v>-0.4378</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>-0.1063</v>
+        <v>-0.1033</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="4" t="n">
@@ -7665,31 +7665,31 @@
         </is>
       </c>
       <c r="B125" s="6" t="n">
-        <v>129.5</v>
+        <v>129</v>
       </c>
       <c r="C125" s="7" t="n">
-        <v>0.0133</v>
+        <v>-0.0039</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>0.2298</v>
+        <v>0.2124</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-0.3255</v>
+        <v>-0.3246</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>-0.2519</v>
+        <v>-0.265</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>-0.1202</v>
+        <v>-0.1389</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>2.7954</v>
+        <v>2.783</v>
       </c>
       <c r="I125" s="6" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="J125" s="6" t="n">
-        <v>14.42</v>
+        <v>14.37</v>
       </c>
       <c r="K125" s="7" t="n">
         <v>1.164</v>
@@ -7723,31 +7723,31 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>27.96</v>
+        <v>27.1</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>0.0123</v>
+        <v>-0.0308</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>-0.0425</v>
+        <v>-0.0757</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>-0.1594</v>
+        <v>-0.1429</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>-0.2622</v>
+        <v>-0.3224</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>0.2706</v>
+        <v>0.1921</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>0.8108</v>
+        <v>0.7698</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>4.21</v>
+        <v>4.09</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>10.42</v>
+        <v>10.1</v>
       </c>
       <c r="K126" s="4" t="n">
         <v>1.4662</v>
@@ -7781,31 +7781,31 @@
         </is>
       </c>
       <c r="B127" s="6" t="n">
-        <v>10817.5</v>
+        <v>10712.5</v>
       </c>
       <c r="C127" s="7" t="n">
-        <v>0.0191</v>
+        <v>-0.0097</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>0.029</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>-0.06280000000000001</v>
+        <v>-0.0452</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>-0.0488</v>
+        <v>-0.0297</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>0.09960000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>-0.0281</v>
+        <v>-0.0444</v>
       </c>
       <c r="I127" s="6" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="J127" s="6" t="n">
-        <v>19.86</v>
+        <v>19.67</v>
       </c>
       <c r="K127" s="7" t="n">
         <v>0.2032</v>
@@ -7839,31 +7839,31 @@
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>204.4</v>
+        <v>197.5</v>
       </c>
       <c r="C128" s="4" t="n">
-        <v>0.0349</v>
+        <v>-0.0338</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>-0.0253</v>
+        <v>-0.1071</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>-0.3221</v>
+        <v>-0.3064</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>-0.3293</v>
+        <v>-0.3779999999999999</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>-0.022</v>
+        <v>0.0165</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>1.2014</v>
+        <v>1.162</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>4.66</v>
+        <v>4.5</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>20.05</v>
+        <v>19.37</v>
       </c>
       <c r="K128" s="4" t="n">
         <v>0.4338</v>
@@ -7893,57 +7893,57 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>DMRGD</t>
+          <t>ONCSM</t>
         </is>
       </c>
       <c r="B129" s="6" t="n">
-        <v>7.13</v>
+        <v>95.5</v>
       </c>
       <c r="C129" s="7" t="n">
-        <v>-0.0975</v>
+        <v>-0.0999</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>0.1141</v>
+        <v>-0.061</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>-0.3215999999999999</v>
+        <v>-0.4552</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>-0.4408</v>
+        <v>-0.6188</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>0.3453</v>
+        <v>-0.669</v>
       </c>
       <c r="H129" s="7" t="n">
-        <v>1.2528</v>
+        <v>-0.2682</v>
       </c>
       <c r="I129" s="6" t="n">
-        <v>5</v>
+        <v>4.51</v>
       </c>
       <c r="J129" s="6" t="n">
-        <v>60.99</v>
+        <v>31.54</v>
       </c>
       <c r="K129" s="7" t="n">
-        <v>0.4591</v>
+        <v>0.5028</v>
       </c>
       <c r="L129" s="7" t="n">
-        <v>0.4162</v>
+        <v>1.6135</v>
       </c>
       <c r="M129" s="7" t="n">
-        <v>3.3554</v>
+        <v>2.0025</v>
       </c>
       <c r="N129" s="7" t="n">
-        <v>0.2283</v>
+        <v>9.2562</v>
       </c>
       <c r="O129" s="7" t="n">
-        <v>0.2808</v>
+        <v>0.3063</v>
       </c>
       <c r="P129" s="7" t="n">
-        <v>0.0866</v>
+        <v>0.1832</v>
       </c>
       <c r="Q129" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R129" s="5" t="inlineStr"/>
@@ -7951,57 +7951,57 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>ONCSM</t>
+          <t>DMRGD</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>106.1</v>
+        <v>6.96</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>0.0392</v>
+        <v>-0.0238</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>0.1743</v>
+        <v>-0.1111</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>-0.3958</v>
+        <v>-0.3434</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>-0.5704</v>
+        <v>-0.4625</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.3647</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>-0.1613</v>
+        <v>1.1415</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>5.01</v>
+        <v>4.88</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>35.04</v>
+        <v>59.54</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0.5028</v>
+        <v>0.4591</v>
       </c>
       <c r="L130" s="4" t="n">
-        <v>1.6135</v>
+        <v>0.4162</v>
       </c>
       <c r="M130" s="4" t="n">
-        <v>2.0025</v>
+        <v>3.3554</v>
       </c>
       <c r="N130" s="4" t="n">
-        <v>9.2562</v>
+        <v>0.2283</v>
       </c>
       <c r="O130" s="4" t="n">
-        <v>0.3063</v>
+        <v>0.2808</v>
       </c>
       <c r="P130" s="4" t="n">
-        <v>0.1832</v>
+        <v>0.0866</v>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr"/>
@@ -8013,31 +8013,31 @@
         </is>
       </c>
       <c r="B131" s="6" t="n">
-        <v>351.25</v>
+        <v>341.75</v>
       </c>
       <c r="C131" s="7" t="n">
-        <v>0.0072</v>
+        <v>-0.027</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>-0.0633</v>
+        <v>-0.0959</v>
       </c>
       <c r="E131" s="7" t="n">
-        <v>-0.104</v>
+        <v>-0.1424</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>-0.0216</v>
+        <v>-0.0312</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>-0.0683</v>
+        <v>-0.171</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>0.6336999999999999</v>
+        <v>0.5590999999999999</v>
       </c>
       <c r="I131" s="6" t="n">
-        <v>5.22</v>
+        <v>5.08</v>
       </c>
       <c r="J131" s="6" t="n">
-        <v>43.16</v>
+        <v>41.99</v>
       </c>
       <c r="K131" s="7" t="n">
         <v>0.5623</v>
@@ -8071,31 +8071,31 @@
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>267.5</v>
+        <v>260</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>0.0009</v>
+        <v>-0.028</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>-0.0201</v>
+        <v>-0.058</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>-0.1039</v>
+        <v>-0.1042</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.1042</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>-0.0463</v>
+        <v>-0.0877</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>-0.1208</v>
+        <v>-0.1545</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>5.36</v>
+        <v>5.21</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>27.06</v>
+        <v>26.3</v>
       </c>
       <c r="K132" s="4" t="n">
         <v>0.2837</v>
@@ -8129,28 +8129,28 @@
         </is>
       </c>
       <c r="B133" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>0.0414</v>
+        <v>-0.0153</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>0.0426</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="E133" s="7" t="n">
-        <v>-0.2741</v>
+        <v>-0.2956</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>-0.2222</v>
+        <v>-0.2366</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>0.3352000000000001</v>
+        <v>0.3972</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>0.8654999999999999</v>
+        <v>0.9109</v>
       </c>
       <c r="I133" s="6" t="n">
-        <v>7.08</v>
+        <v>6.98</v>
       </c>
       <c r="J133" s="5" t="inlineStr"/>
       <c r="K133" s="7" t="n">
@@ -8185,28 +8185,28 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>25.04</v>
+        <v>24.12</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>0.0313</v>
+        <v>-0.0367</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>0.0064</v>
+        <v>-0.0429</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>-0.2771</v>
+        <v>-0.25</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>-0.2946</v>
+        <v>-0.3017</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>-0.374</v>
+        <v>-0.4091</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>-0.2525</v>
+        <v>-0.2787</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>7.27</v>
+        <v>7</v>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="4" t="n">
@@ -8241,28 +8241,28 @@
         </is>
       </c>
       <c r="B135" s="6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>0.09519999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>0.1711</v>
+        <v>0.2994</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>-0.2744</v>
+        <v>-0.1097</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>-0.1667</v>
+        <v>-0.0566</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>0.5333</v>
+        <v>0.6770999999999999</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>0.4681</v>
+        <v>0.5534</v>
       </c>
       <c r="I135" s="6" t="n">
-        <v>9.34</v>
+        <v>10.15</v>
       </c>
       <c r="J135" s="5" t="inlineStr"/>
       <c r="K135" s="7" t="n">
@@ -8293,55 +8293,55 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>KENT</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="n">
-        <v>273.5</v>
+          <t>MRSHL</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="n">
+        <v>1298</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>-0.0009</v>
+        <v>-0.0248</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>-0.076</v>
+        <v>-0.0328</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>-0.2163</v>
+        <v>-0.2162</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>-0.2424</v>
+        <v>-0.3497</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>-0.3465</v>
+        <v>-0.117</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>-0.4862</v>
+        <v>-0.314</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>11.77</v>
+        <v>11.53</v>
       </c>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="4" t="n">
-        <v>0.2234</v>
+        <v>0.2605</v>
       </c>
       <c r="L136" s="4" t="n">
-        <v>0.3229</v>
+        <v>0.5011</v>
       </c>
       <c r="M136" s="4" t="n">
-        <v>0.5381</v>
+        <v>0.4026</v>
       </c>
       <c r="N136" s="4" t="n">
-        <v>0.0256</v>
+        <v>0.7501000000000001</v>
       </c>
       <c r="O136" s="4" t="n">
-        <v>0.051</v>
+        <v>0.1503</v>
       </c>
       <c r="P136" s="4" t="n">
-        <v>-0.1222</v>
+        <v>-0.0529</v>
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R136" s="2" t="inlineStr"/>
@@ -8349,55 +8349,55 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>MRSHL</t>
-        </is>
-      </c>
-      <c r="B137" s="8" t="n">
-        <v>1331</v>
+          <t>KENT</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="n">
+        <v>273.5</v>
       </c>
       <c r="C137" s="7" t="n">
-        <v>0.0538</v>
+        <v>0</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>-0.006</v>
+        <v>-0.0745</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>-0.1829</v>
+        <v>-0.2296</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>-0.3411</v>
+        <v>-0.2307</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>-0.0574</v>
+        <v>-0.341</v>
       </c>
       <c r="H137" s="7" t="n">
-        <v>-0.3071</v>
+        <v>-0.4675</v>
       </c>
       <c r="I137" s="6" t="n">
-        <v>11.82</v>
+        <v>11.77</v>
       </c>
       <c r="J137" s="5" t="inlineStr"/>
       <c r="K137" s="7" t="n">
-        <v>0.2605</v>
+        <v>0.2234</v>
       </c>
       <c r="L137" s="7" t="n">
-        <v>0.5011</v>
+        <v>0.3229</v>
       </c>
       <c r="M137" s="7" t="n">
-        <v>0.4026</v>
+        <v>0.5381</v>
       </c>
       <c r="N137" s="7" t="n">
-        <v>0.7501000000000001</v>
+        <v>0.0256</v>
       </c>
       <c r="O137" s="7" t="n">
-        <v>0.1503</v>
+        <v>0.051</v>
       </c>
       <c r="P137" s="7" t="n">
-        <v>-0.0529</v>
+        <v>-0.1222</v>
       </c>
       <c r="Q137" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R137" s="5" t="inlineStr"/>
@@ -8409,31 +8409,31 @@
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>43.86</v>
+        <v>41</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>0.0453</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>0.2482</v>
+        <v>-0.0116</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>0.0625</v>
+        <v>-0.0024</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>-0.1598</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>0.0115</v>
+        <v>-0.08810000000000001</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>-0.2622</v>
+        <v>-0.1924</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>13.44</v>
+        <v>12.57</v>
       </c>
       <c r="J138" s="3" t="n">
-        <v>48.37</v>
+        <v>45.21</v>
       </c>
       <c r="K138" s="4" t="n">
         <v>0.2618</v>
@@ -8467,28 +8467,28 @@
         </is>
       </c>
       <c r="B139" s="6" t="n">
-        <v>39.06</v>
+        <v>38.54</v>
       </c>
       <c r="C139" s="7" t="n">
-        <v>-0.0051</v>
+        <v>-0.0133</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>-0.0308</v>
+        <v>-0.0418</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>-0.1098</v>
+        <v>-0.1257</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>-0.08869999999999999</v>
+        <v>-0.164</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>-0.09</v>
+        <v>-0.0969</v>
       </c>
       <c r="H139" s="7" t="n">
-        <v>0.1322</v>
+        <v>0.0713</v>
       </c>
       <c r="I139" s="6" t="n">
-        <v>14.58</v>
+        <v>14.39</v>
       </c>
       <c r="J139" s="5" t="inlineStr"/>
       <c r="K139" s="7" t="n">
@@ -8523,31 +8523,31 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>107.9</v>
+        <v>105.4</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>0.0179</v>
+        <v>-0.0232</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>-0.0279</v>
+        <v>-0.0572</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>-0.1597</v>
+        <v>-0.1867</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>-0.1776</v>
+        <v>-0.1861</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>-0.232</v>
+        <v>-0.3290999999999999</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>-0.3645</v>
+        <v>-0.3726</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>16.42</v>
+        <v>16.04</v>
       </c>
       <c r="J140" s="3" t="n">
-        <v>61.83</v>
+        <v>60.39</v>
       </c>
       <c r="K140" s="4" t="n">
         <v>0.3045</v>
@@ -8581,25 +8581,25 @@
         </is>
       </c>
       <c r="B141" s="6" t="n">
-        <v>83</v>
+        <v>82.05</v>
       </c>
       <c r="C141" s="7" t="n">
-        <v>0.0097</v>
+        <v>-0.0114</v>
       </c>
       <c r="D141" s="7" t="n">
-        <v>0.0247</v>
+        <v>-0.0168</v>
       </c>
       <c r="E141" s="7" t="n">
-        <v>-0.135</v>
+        <v>-0.1576</v>
       </c>
       <c r="F141" s="7" t="n">
-        <v>0.3822</v>
+        <v>0.316</v>
       </c>
       <c r="G141" s="7" t="n">
-        <v>0.3651</v>
+        <v>0.2711</v>
       </c>
       <c r="H141" s="7" t="n">
-        <v>0.0116</v>
+        <v>0.0231</v>
       </c>
       <c r="I141" s="5" t="inlineStr"/>
       <c r="J141" s="5" t="inlineStr"/>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>09.10.2026 20:12</t>
+          <t>12.10.2026 22:32</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_latest.xlsx
+++ b/data/bist_screener_latest.xlsx
@@ -76,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +97,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -583,31 +586,31 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13.24</v>
+        <v>13.1</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-0.0293</v>
+        <v>-0.0106</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.05230000000000001</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.1572</v>
+        <v>-0.1661</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-0.2587</v>
+        <v>-0.2665</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.2072</v>
+        <v>-0.2375</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.3622</v>
+        <v>-0.3597</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0.22</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>6.15</v>
+        <v>6.09</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>0.9854999999999999</v>
@@ -641,31 +644,31 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>0.0136</v>
+        <v>-0.0224</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>-0.0219</v>
+        <v>-0.0644</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>-0.108</v>
+        <v>-0.128</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>-0.1648</v>
+        <v>-0.1835</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>-0.3009</v>
+        <v>-0.323</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-0.2712</v>
+        <v>-0.2899</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0.23</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>2.7227</v>
@@ -695,57 +698,55 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IHEVA</t>
+          <t>RUBNS</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1.6</v>
+        <v>15.33</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.0244</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.0361</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.1795</v>
+        <v>-0.4768</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.2233</v>
+        <v>-0.2903</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.2627</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.387</v>
+        <v>-0.2623</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>8.949999999999999</v>
-      </c>
+        <v>0.23</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="4" t="n">
-        <v>0.2518</v>
+        <v>0.5189</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.322</v>
+        <v>0.4172999999999999</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.2038</v>
+        <v>2.5836</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.1672</v>
+        <v>0.7992</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.078</v>
+        <v>0.1688</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.0331</v>
+        <v>-0.0061</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr"/>
@@ -753,57 +754,57 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>HLGYO</t>
+          <t>IHEVA</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>4.15</v>
+        <v>1.56</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>0.0073</v>
+        <v>-0.025</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0.0073</v>
+        <v>-0.0488</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-0.0919</v>
+        <v>-0.2</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>-0.2642</v>
+        <v>-0.2427</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-0.2745</v>
+        <v>-0.2941</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.1496</v>
+        <v>-0.393</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1.24</v>
+        <v>8.73</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>1.7259</v>
+        <v>0.2518</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.4642</v>
+        <v>0.322</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>2.8476</v>
+        <v>0.2038</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>2.0883</v>
+        <v>0.1672</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>0.1249</v>
+        <v>0.078</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>0.2374</v>
+        <v>0.0331</v>
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="R5" s="5" t="inlineStr"/>
@@ -811,53 +812,53 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AKFGY</t>
+          <t>HLGYO</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2.45</v>
+        <v>4.21</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.0145</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0541</v>
+        <v>-0.0071</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1667</v>
+        <v>-0.0788</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1058</v>
+        <v>-0.2535</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.125</v>
+        <v>-0.2716</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.0392</v>
+        <v>0.1534</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>5.76</v>
+        <v>1.26</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.3848</v>
+        <v>1.7259</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.3326</v>
+        <v>1.4642</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.3901</v>
+        <v>2.8476</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3812</v>
+        <v>2.0883</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.8458</v>
+        <v>0.1249</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.0496</v>
+        <v>0.2374</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
@@ -869,55 +870,57 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>RUBNS</t>
+          <t>AKFGY</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>16.4</v>
+        <v>2.49</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>-0.0018</v>
+        <v>0.0163</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.0594</v>
+        <v>-0.0311</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-0.4403</v>
+        <v>-0.1531</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>-0.2407</v>
+        <v>-0.09119999999999999</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-0.5312</v>
+        <v>-0.117</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>-0.2257</v>
+        <v>-0.0197</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0.25</v>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="J7" s="6" t="n">
+        <v>5.85</v>
+      </c>
       <c r="K7" s="7" t="n">
-        <v>0.5189</v>
+        <v>0.3848</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.4172999999999999</v>
+        <v>0.3326</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>2.5836</v>
+        <v>0.3901</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>0.7992</v>
+        <v>0.3812</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>0.1688</v>
+        <v>0.8458</v>
       </c>
       <c r="P7" s="7" t="n">
-        <v>-0.0061</v>
+        <v>0.0496</v>
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr"/>
@@ -929,28 +932,28 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.0343</v>
+        <v>-0.0178</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.026</v>
+        <v>-0.0391</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2947</v>
+        <v>-0.3072</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.4458</v>
+        <v>-0.4557</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.4403</v>
+        <v>-0.4597</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.5588000000000001</v>
+        <v>-0.5846</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="n">
@@ -985,25 +988,25 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>10.19</v>
+        <v>10.1</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>-0.0314</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.0039</v>
+        <v>-0.0326</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-0.1769</v>
+        <v>-0.1842</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>-0.07780000000000001</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-0.2413</v>
+        <v>-0.2372</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-0.2933</v>
+        <v>-0.2882</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0.26</v>
@@ -1037,57 +1040,57 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GSDHO</t>
+          <t>PETUN</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4.29</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.0069</v>
+        <v>-0.029</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.0413</v>
+        <v>-0.0509</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.08529999999999999</v>
+        <v>-0.2043</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1813</v>
+        <v>-0.1401</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1454</v>
+        <v>-0.2283</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.0228</v>
+        <v>-0.2469</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>15.37</v>
+        <v>11.55</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1479</v>
+        <v>0.3203</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2201</v>
+        <v>0.0458</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3072</v>
+        <v>0.0347</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.5201</v>
+        <v>0.0183</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.6869</v>
+        <v>0.1414</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.0197</v>
+        <v>0.0274</v>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr"/>
@@ -1099,28 +1102,28 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>6.75</v>
+        <v>6.63</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>-0.0074</v>
+        <v>-0.0178</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.0212</v>
+        <v>0.0015</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-0.1083</v>
+        <v>-0.1242</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>-0.0766</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-0.1758</v>
+        <v>-0.1954</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-0.1176</v>
+        <v>-0.1242</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="7" t="n">
@@ -1151,57 +1154,57 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>PETUN</t>
+          <t>GSDHO</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>9.99</v>
+        <v>4.36</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.0206</v>
+        <v>0.0163</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.0187</v>
+        <v>0.066</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1805</v>
+        <v>-0.0704</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1144</v>
+        <v>-0.1679</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2065</v>
+        <v>-0.1349</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2298</v>
+        <v>-0.0046</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0.27</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>11.89</v>
+        <v>15.62</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.3203</v>
+        <v>0.1479</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.0458</v>
+        <v>0.2201</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.0347</v>
+        <v>0.3072</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.0183</v>
+        <v>0.5201</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.1414</v>
+        <v>0.6869</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.0274</v>
+        <v>0.0197</v>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr"/>
@@ -1213,25 +1216,25 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.0327</v>
+        <v>0.0072</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0547</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>-0.3226</v>
+        <v>-0.3177</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>-0.3394</v>
+        <v>-0.3346</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-0.4431</v>
+        <v>-0.4677</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.6557999999999999</v>
+        <v>-0.6481999999999999</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0.35</v>
@@ -1269,31 +1272,31 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>11.16</v>
+        <v>11.01</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.015</v>
+        <v>-0.0134</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.0136</v>
+        <v>0.0036</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1545</v>
+        <v>-0.1659</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.1356</v>
+        <v>-0.1472</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1782</v>
+        <v>-0.1964</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1812</v>
+        <v>-0.1844</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.37</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>5.95</v>
+        <v>5.87</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>0.3789</v>
@@ -1327,28 +1330,28 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>5.92</v>
+        <v>5.82</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>-0.0199</v>
+        <v>-0.0169</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>-0.039</v>
+        <v>-0.0284</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-0.005</v>
+        <v>-0.0218</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>-0.0696</v>
+        <v>-0.08529999999999999</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-0.1577</v>
+        <v>-0.2103</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.351</v>
+        <v>-0.3815999999999999</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="J15" s="5" t="inlineStr"/>
       <c r="K15" s="7" t="n">
@@ -1379,53 +1382,53 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MHRGY</t>
+          <t>RGYAS</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.98</v>
+        <v>193.6</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1</v>
+        <v>0.0016</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.0206</v>
+        <v>-0.0222</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.12</v>
+        <v>-0.0344</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.1563</v>
+        <v>-0.0202</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.1818</v>
+        <v>0.0442</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2538</v>
+        <v>0.2821</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>9.34</v>
+        <v>3.22</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9460999999999999</v>
+        <v>0.5672999999999999</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.9873000000000001</v>
+        <v>0.5787</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.3702</v>
+        <v>0.5573</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2464.8944</v>
+        <v>8.1502</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8395999999999999</v>
+        <v>0.6512</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.0472</v>
+        <v>0.1467</v>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
@@ -1437,53 +1440,53 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>RGYAS</t>
+          <t>MHRGY</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>193.3</v>
+        <v>2.07</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>0.0005</v>
+        <v>0.0455</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>-0.0118</v>
+        <v>0.15</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>-0.0359</v>
+        <v>-0.08</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>-0.0218</v>
+        <v>-0.1179</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.06150000000000001</v>
+        <v>-0.1935</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0.2818</v>
+        <v>-0.2018</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>3.21</v>
+        <v>9.76</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.5672999999999999</v>
+        <v>0.9460999999999999</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.5787</v>
+        <v>0.9873000000000001</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.5573</v>
+        <v>0.3702</v>
       </c>
       <c r="N17" s="7" t="n">
-        <v>8.1502</v>
+        <v>2464.8944</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>0.6512</v>
+        <v>0.8395999999999999</v>
       </c>
       <c r="P17" s="7" t="n">
-        <v>0.1467</v>
+        <v>0.0472</v>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
@@ -1499,31 +1502,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>37.6</v>
+        <v>37.88</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.0116</v>
+        <v>0.0074</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.0053</v>
+        <v>-0.0042</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1458</v>
+        <v>-0.1395</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1256</v>
+        <v>-0.1191</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2206</v>
+        <v>-0.2203</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0731</v>
+        <v>0.0916</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>0.42</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>0.2329</v>
@@ -1560,10 +1563,10 @@
         <v>7.46</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>-0.0299</v>
+        <v>0</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>-0.0184</v>
+        <v>-0.0171</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>-0.2614</v>
@@ -1572,10 +1575,10 @@
         <v>-0.2995</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>-0.3773</v>
+        <v>-0.385</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-0.2708</v>
+        <v>-0.2636</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0.45</v>
@@ -1611,51 +1614,51 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.09849999999999999</v>
+        <v>-0.0051</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.1117</v>
+        <v>-0.0152</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.4116</v>
+        <v>-0.5</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.4845</v>
+        <v>-0.6518</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.4874</v>
+        <v>-0.7068000000000001</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.8170000000000001</v>
+        <v>-0.5278</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>0.45</v>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="4" t="n">
-        <v>0.2334</v>
+        <v>0.1726</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1468</v>
+        <v>0.3081</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1104</v>
+        <v>0.1357</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.4322</v>
+        <v>0.2328</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.1786</v>
+        <v>0.0837</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1088</v>
+        <v>-0.0244</v>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
@@ -1667,51 +1670,51 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>-0.05769999999999999</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>-0.07980000000000001</v>
+        <v>-0.098</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-0.4974</v>
+        <v>-0.4084</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>-0.65</v>
+        <v>-0.4817</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-0.7121999999999999</v>
+        <v>-0.5245000000000001</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-0.5388000000000001</v>
+        <v>-0.8111</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0.45</v>
       </c>
       <c r="J21" s="5" t="inlineStr"/>
       <c r="K21" s="7" t="n">
-        <v>0.1726</v>
+        <v>0.2334</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.3081</v>
+        <v>0.1468</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.1357</v>
+        <v>0.1104</v>
       </c>
       <c r="N21" s="7" t="n">
-        <v>0.2328</v>
+        <v>0.4322</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>0.0837</v>
+        <v>0.1786</v>
       </c>
       <c r="P21" s="7" t="n">
-        <v>-0.0244</v>
+        <v>-0.1088</v>
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
@@ -1727,31 +1730,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>18.63</v>
+        <v>18.41</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.0016</v>
+        <v>-0.0118</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.0446</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1391</v>
+        <v>-0.1493</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1154</v>
+        <v>-0.1258</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1509</v>
+        <v>-0.1555</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0373</v>
+        <v>0.049</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>7.53</v>
+        <v>7.44</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>0.1285</v>
@@ -1785,28 +1788,28 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>-0.0319</v>
+        <v>-0.011</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.1519</v>
+        <v>0.07139999999999999</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>-0.1574</v>
+        <v>-0.1667</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>-0.3974</v>
+        <v>-0.404</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-0.6353</v>
+        <v>-0.6591</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-0.7384999999999999</v>
+        <v>-0.7383</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="J23" s="5" t="inlineStr"/>
       <c r="K23" s="7" t="n">
@@ -1841,31 +1844,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>10.73</v>
+        <v>10.77</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.0307</v>
+        <v>0.0037</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.042</v>
+        <v>-0.0227</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.1784</v>
+        <v>-0.1753</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.287</v>
+        <v>-0.2844</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3779999999999999</v>
+        <v>-0.3771</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3109</v>
+        <v>-0.2723</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>0.49</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>0.4985</v>
@@ -1899,31 +1902,31 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>6.17</v>
+        <v>6.1</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>-0.0191</v>
+        <v>-0.0113</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>-0.0537</v>
+        <v>-0.05860000000000001</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-0.1828</v>
+        <v>-0.1921</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>-0.316</v>
+        <v>-0.3237</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>-0.2892</v>
+        <v>-0.298</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-0.156</v>
+        <v>-0.1963</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0.57</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>7.41</v>
+        <v>7.32</v>
       </c>
       <c r="K25" s="7" t="n">
         <v>0.6883</v>
@@ -1957,28 +1960,28 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>115</v>
+        <v>112.6</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.0086</v>
+        <v>-0.0209</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0474</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2256</v>
+        <v>-0.2418</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2936</v>
+        <v>-0.3084</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4327</v>
+        <v>-0.4445</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.3699</v>
+        <v>-0.383</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="4" t="n">
@@ -2013,31 +2016,31 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>26.66</v>
+        <v>26.54</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>-0.0305</v>
+        <v>-0.004500000000000001</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>-0.0499</v>
+        <v>-0.046</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-0.2112</v>
+        <v>-0.2148</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>-0.3358</v>
+        <v>-0.3388</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>-0.5222</v>
+        <v>-0.5218</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>-0.446</v>
+        <v>-0.4482</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="K27" s="7" t="n">
         <v>0.045</v>
@@ -2071,31 +2074,31 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>34.18</v>
+        <v>33.06</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.0459</v>
+        <v>-0.0328</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.0517</v>
+        <v>0.0267</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.0059</v>
+        <v>-0.0271</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.0364</v>
+        <v>0.0024</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1047</v>
+        <v>0.0495</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.3531</v>
+        <v>0.3277</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>18.69</v>
+        <v>18.07</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>0.3105</v>
@@ -2129,28 +2132,28 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>2.99</v>
+        <v>2.91</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>-0.0164</v>
+        <v>-0.0268</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>-0.0229</v>
+        <v>-0.0703</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-0.2661</v>
+        <v>-0.2857</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>-0.2791</v>
+        <v>-0.2984</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>-0.1367</v>
+        <v>-0.1189</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>-0.0034</v>
+        <v>-0.0118</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="7" t="n">
@@ -2185,28 +2188,28 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>7.8</v>
+        <v>7.67</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.0152</v>
+        <v>-0.0167</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.2112</v>
+        <v>0.0757</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3079</v>
+        <v>-0.3194</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5329</v>
+        <v>-0.5407</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5667</v>
+        <v>-0.5727</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3362</v>
+        <v>-0.3388</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="4" t="n">
@@ -2241,31 +2244,31 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>7.66</v>
+        <v>7.51</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>-0.0129</v>
+        <v>-0.0196</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>-0.0328</v>
+        <v>-0.0359</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-0.1325</v>
+        <v>-0.1495</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>-0.2446</v>
+        <v>-0.2594</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>-0.1628</v>
+        <v>-0.2002</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>-0.2541</v>
+        <v>-0.28</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>4.41</v>
+        <v>4.32</v>
       </c>
       <c r="K31" s="7" t="n">
         <v>0.3806</v>
@@ -2299,28 +2302,28 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>30.34</v>
+        <v>29.48</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.0219</v>
+        <v>-0.0283</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.0607</v>
+        <v>-0.099</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2066</v>
+        <v>-0.2291</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.401</v>
+        <v>-0.418</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3992</v>
+        <v>-0.3597</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2197</v>
+        <v>-0.2242</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="4" t="n">
@@ -2351,57 +2354,55 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>DOKTA</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>206.9</v>
+        <v>14.98</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>-0.0053</v>
+        <v>-0.0254</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>-0.0043</v>
+        <v>-0.073</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-0.08039999999999999</v>
+        <v>-0.3587</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>0.0832</v>
+        <v>-0.3532</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>0</v>
+        <v>-0.3881</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>0.2345</v>
+        <v>-0.3706</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="J33" s="6" t="n">
-        <v>14.75</v>
-      </c>
+        <v>0.65</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr"/>
       <c r="K33" s="7" t="n">
-        <v>0.3261</v>
+        <v>0.2983</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.5440999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.9423</v>
+        <v>3.5566</v>
       </c>
       <c r="N33" s="7" t="n">
-        <v>5.083299999999999</v>
+        <v>0.6970000000000001</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>0.0646</v>
+        <v>0.0852</v>
       </c>
       <c r="P33" s="7" t="n">
-        <v>0.0771</v>
+        <v>-0.0451</v>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R33" s="5" t="inlineStr"/>
@@ -2409,55 +2410,57 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>DOKTA</t>
+          <t>OSMEN</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>15.37</v>
+        <v>5.35</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.0333</v>
+        <v>-0.0325</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.0071</v>
+        <v>0.0152</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.342</v>
+        <v>-0.2422</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3364</v>
+        <v>-0.3515</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3574</v>
+        <v>-0.307</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3832</v>
+        <v>-0.392</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
+        <v>0.66</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>9.18</v>
+      </c>
       <c r="K34" s="4" t="n">
-        <v>0.2983</v>
+        <v>1.6512</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.25</v>
+        <v>0.1052</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>3.5566</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.6970000000000001</v>
+        <v>5.9134</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.0852</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.0451</v>
+        <v>0.0863</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr"/>
@@ -2465,53 +2468,53 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>OSMEN</t>
+          <t>SEKFK</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>5.53</v>
+        <v>4.11</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>0.0036</v>
+        <v>-0.0191</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.0279</v>
+        <v>-0.0486</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-0.2167</v>
+        <v>-0.0659</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>-0.3297</v>
+        <v>-0.2638</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>-0.2818</v>
+        <v>-0.322</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>-0.3393</v>
+        <v>-0.094</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0.68</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>9.49</v>
+        <v>3.33</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>1.6512</v>
+        <v>0.208</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.1052</v>
+        <v>0.0571</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.04969999999999999</v>
+        <v>0.0025</v>
       </c>
       <c r="N35" s="7" t="n">
-        <v>5.9134</v>
+        <v>0.2707</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.6072</v>
       </c>
       <c r="P35" s="7" t="n">
-        <v>0.0863</v>
+        <v>0.2346</v>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
@@ -2523,57 +2526,57 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TTKOM</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>51.85</v>
+        <v>212.5</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>-0.0086</v>
+        <v>0.0271</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>-0.0152</v>
+        <v>-0.0116</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0556</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>-0.1014</v>
+        <v>0.1126</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.1822</v>
+        <v>0.0167</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.0019</v>
+        <v>0.3085</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.68</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>6.41</v>
+        <v>15.14</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0.4498</v>
+        <v>0.3261</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.4329</v>
+        <v>0.5440999999999999</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.5323</v>
+        <v>0.9423</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.8047</v>
+        <v>5.083299999999999</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>0.4117</v>
+        <v>0.0646</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>1.3041</v>
+        <v>0.0771</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr"/>
@@ -2581,57 +2584,57 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>SEKFK</t>
+          <t>TTKOM</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>4.19</v>
+        <v>52.25</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>-0.0141</v>
+        <v>0.0077</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>-0.0048</v>
+        <v>-0.027</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-0.04769999999999999</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>-0.2495</v>
+        <v>-0.09449999999999999</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>-0.3106</v>
+        <v>-0.1739</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>-0.0764</v>
+        <v>0.0146</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>3.4</v>
+        <v>6.46</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.208</v>
+        <v>0.4498</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>0.0571</v>
+        <v>0.4329</v>
       </c>
       <c r="M37" s="7" t="n">
-        <v>0.0025</v>
+        <v>0.5323</v>
       </c>
       <c r="N37" s="7" t="n">
-        <v>0.2707</v>
+        <v>0.8047</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>0.6072</v>
+        <v>0.4117</v>
       </c>
       <c r="P37" s="7" t="n">
-        <v>0.2346</v>
+        <v>1.3041</v>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R37" s="5" t="inlineStr"/>
@@ -2639,57 +2642,57 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>PNLSN</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>97.25</v>
+        <v>32.48</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>-0.0132</v>
+        <v>-0.0122</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0441</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>-0.04190000000000001</v>
+        <v>-0.2031</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-0.1078</v>
+        <v>-0.2801</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.166</v>
+        <v>-0.2756</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.0371</v>
+        <v>-0.202</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>10.92</v>
+        <v>9.16</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.3971</v>
+        <v>0.306</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.4118</v>
+        <v>0.6481</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.3975</v>
+        <v>0.5497</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.2377</v>
+        <v>7.793600000000001</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0.4333</v>
+        <v>0.1302</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0.1518</v>
+        <v>0.08839999999999999</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr"/>
@@ -2697,53 +2700,53 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TUREX</t>
+          <t>AKMGY</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>5.79</v>
+        <v>208</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>-0.0153</v>
+        <v>-0.0119</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>-0.043</v>
+        <v>-0.0415</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-0.057</v>
+        <v>-0.1713</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>-0.1485</v>
+        <v>-0.1613</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>-0.2982</v>
+        <v>-0.2997</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>-0.2965</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0.7</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>10.89</v>
+        <v>10.25</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.4159</v>
+        <v>0.3886</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>1.3967</v>
+        <v>0.3887</v>
       </c>
       <c r="M39" s="7" t="n">
-        <v>0.8518000000000001</v>
+        <v>0.3141</v>
       </c>
       <c r="N39" s="7" t="n">
-        <v>0.3205</v>
+        <v>0.5958</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>0.2638</v>
+        <v>0.6443000000000001</v>
       </c>
       <c r="P39" s="7" t="n">
-        <v>0.0862</v>
+        <v>0.0781</v>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
@@ -2755,57 +2758,57 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>PNLSN</t>
+          <t>BNTAS</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>32.88</v>
+        <v>5.24</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>-0.0403</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>-0.0335</v>
+        <v>-0.0626</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>-0.1933</v>
+        <v>-0.1748</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>-0.2713</v>
+        <v>-0.1267</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-0.2628</v>
+        <v>-0.2249</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.2077</v>
+        <v>-0.1975</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>9.27</v>
+        <v>4.85</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.306</v>
+        <v>0.2654</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.6481</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.5497</v>
+        <v>0.464</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>7.793600000000001</v>
+        <v>0.3679</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.1302</v>
+        <v>0.1363</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0.08839999999999999</v>
+        <v>0.1657</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr"/>
@@ -2813,57 +2816,57 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>BNTAS</t>
+          <t>TUREX</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>5.27</v>
+        <v>5.85</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>-0.0131</v>
+        <v>0.0104</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>-0.06059999999999999</v>
+        <v>0.0017</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-0.1701</v>
+        <v>-0.0472</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>-0.1217</v>
+        <v>-0.1397</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>-0.2087</v>
+        <v>-0.3641</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>-0.2015</v>
+        <v>-0.2751</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>4.88</v>
+        <v>11</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.2654</v>
+        <v>0.4159</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>0.07690000000000001</v>
+        <v>1.3967</v>
       </c>
       <c r="M41" s="7" t="n">
-        <v>0.464</v>
+        <v>0.8518000000000001</v>
       </c>
       <c r="N41" s="7" t="n">
-        <v>0.3679</v>
+        <v>0.3205</v>
       </c>
       <c r="O41" s="7" t="n">
-        <v>0.1363</v>
+        <v>0.2638</v>
       </c>
       <c r="P41" s="7" t="n">
-        <v>0.1657</v>
+        <v>0.0862</v>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R41" s="5" t="inlineStr"/>
@@ -2871,57 +2874,57 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>AKMGY</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>210.5</v>
+        <v>99.45</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>-0.0075</v>
+        <v>0.0226</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>-0.0291</v>
+        <v>-0.0104</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-0.1614</v>
+        <v>-0.0202</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-0.1512</v>
+        <v>-0.0876</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-0.303</v>
+        <v>-0.1572</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>10.37</v>
+        <v>11.17</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0.3886</v>
+        <v>0.3971</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.3887</v>
+        <v>0.4118</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.3141</v>
+        <v>0.3975</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.5958</v>
+        <v>0.2377</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>0.6443000000000001</v>
+        <v>0.4333</v>
       </c>
       <c r="P42" s="4" t="n">
-        <v>0.0781</v>
+        <v>0.1518</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr"/>
@@ -2933,31 +2936,31 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>10.68</v>
+        <v>10.63</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>-0.0317</v>
+        <v>-0.004699999999999999</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>-0.0761</v>
+        <v>-0.0266</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-0.4283</v>
+        <v>-0.4309000000000001</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>-0.5594</v>
+        <v>-0.5615</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>-0.3743</v>
+        <v>-0.3943</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>-0.633</v>
+        <v>-0.636</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>0.71</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>12.27</v>
+        <v>12.21</v>
       </c>
       <c r="K43" s="7" t="n">
         <v>0.2374</v>
@@ -2991,31 +2994,31 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>288.5</v>
+        <v>294</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>-0.0103</v>
+        <v>0.0191</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>-0.0052</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>-0.1258</v>
+        <v>-0.1091</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.1713</v>
+        <v>0.1937</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>0.0185</v>
+        <v>0.0182</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.537</v>
+        <v>0.5722</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>7.58</v>
+        <v>7.73</v>
       </c>
       <c r="K44" s="4" t="n">
         <v>0.1662</v>
@@ -3045,57 +3048,57 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>BASGZ</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>39.88</v>
+        <v>37.26</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>-0.0124</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>-0.0182</v>
+        <v>-0.0106</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-0.1216</v>
+        <v>-0.0446</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>-0.139</v>
+        <v>-0.08810000000000001</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>-0.2316</v>
+        <v>0.1702</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>0.0358</v>
+        <v>0.3549</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>7.22</v>
+        <v>32.48</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.3163</v>
+        <v>0.1998</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>0.5275</v>
+        <v>0.3838</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>0.4513</v>
+        <v>0.4877</v>
       </c>
       <c r="N45" s="7" t="n">
-        <v>0.3789</v>
+        <v>0.4752</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>0.1301</v>
+        <v>0.104</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>-0.245</v>
+        <v>0.0274</v>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R45" s="5" t="inlineStr"/>
@@ -3103,57 +3106,57 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>BASGZ</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>37.6</v>
+        <v>40.08</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.0075</v>
+        <v>0.005</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>0.0118</v>
+        <v>-0.0133</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>-0.0359</v>
+        <v>-0.1172</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-0.07980000000000001</v>
+        <v>-0.1347</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.1854</v>
+        <v>-0.2126</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.34</v>
+        <v>0.033</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>0.79</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>32.77</v>
+        <v>7.26</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0.1998</v>
+        <v>0.3163</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.3838</v>
+        <v>0.5275</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.4877</v>
+        <v>0.4513</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.4752</v>
+        <v>0.3789</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0.104</v>
+        <v>0.1301</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>0.0274</v>
+        <v>-0.245</v>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr"/>
@@ -3165,31 +3168,31 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>-0.0158</v>
+        <v>-0.0023</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>-0.0169</v>
+        <v>-0.0247</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-0.157</v>
+        <v>-0.1589</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>-0.1675</v>
+        <v>-0.1694</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>-0.3349</v>
+        <v>-0.3122</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>-0.2169</v>
+        <v>-0.2386</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0.8</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>18.34</v>
+        <v>18.3</v>
       </c>
       <c r="K47" s="7" t="n">
         <v>0.2802</v>
@@ -3223,31 +3226,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>16.77</v>
+        <v>16.51</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.0036</v>
+        <v>-0.0155</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>-0.0323</v>
+        <v>-0.044</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>-0.1275</v>
+        <v>-0.141</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-0.1338</v>
+        <v>-0.1472</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-0.1739</v>
+        <v>-0.1923</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>-0.0042</v>
+        <v>-0.0213</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>0.5749</v>
@@ -3281,25 +3284,25 @@
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>-0.0473</v>
+        <v>-0.0014</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>-0.1038</v>
+        <v>-0.095</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>-0.1597</v>
+        <v>-0.1609</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>-0.2352</v>
+        <v>-0.2363</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>-0.2328</v>
+        <v>-0.2482</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0.6004</v>
+        <v>0.5323</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0.86</v>
@@ -3337,31 +3340,31 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>8.5</v>
+        <v>8.49</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>-0.0173</v>
+        <v>-0.0012</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.0751</v>
+        <v>-0.0608</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>-0.1318</v>
+        <v>-0.1328</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>-0.1889</v>
+        <v>-0.1899</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.3732</v>
+        <v>-0.3825</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>-0.4382</v>
+        <v>-0.434</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>0.88</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>8.050000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="K50" s="4" t="n">
         <v>0.2088</v>
@@ -3395,31 +3398,31 @@
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>92.5</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>-0.0542</v>
+        <v>0.0124</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.0709</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-0.1763</v>
+        <v>-0.1661</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>-0.0299</v>
+        <v>-0.0178</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>-0.2324</v>
+        <v>-0.238</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>-0.1998</v>
+        <v>-0.1447</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>12.94</v>
+        <v>13.1</v>
       </c>
       <c r="K51" s="7" t="n">
         <v>0.4926</v>
@@ -3459,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.0063</v>
+        <v>-0.0005</v>
       </c>
       <c r="E52" s="4" t="n">
         <v>-0.03700000000000001</v>
@@ -3468,10 +3471,10 @@
         <v>0.09380000000000001</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.1196</v>
+        <v>-0.1171</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>-0.2024</v>
+        <v>-0.1789</v>
       </c>
       <c r="I52" s="3" t="n">
         <v>0.95</v>
@@ -3511,31 +3514,31 @@
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>501</v>
+        <v>497.5</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>-0.004</v>
+        <v>-0.0075</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>-0.0262</v>
+        <v>-0.0391</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-0.0765</v>
+        <v>-0.0834</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>-0.1984</v>
+        <v>-0.2044</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>-0.2316</v>
+        <v>-0.2449</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>0.1078</v>
+        <v>0.1174</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>15.01</v>
+        <v>14.89</v>
       </c>
       <c r="K53" s="7" t="n">
         <v>0.3804</v>
@@ -3569,31 +3572,31 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>8.81</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>-0.035</v>
+        <v>-0.0034</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>-0.0476</v>
+        <v>-0.0394</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>-0.4644</v>
+        <v>-0.4663</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>-0.1962</v>
+        <v>-0.1989</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-0.1728</v>
+        <v>-0.184</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>-0.1704</v>
+        <v>-0.1558</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>32.79</v>
+        <v>32.68</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>0.8458</v>
@@ -3627,31 +3630,31 @@
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>95.7</v>
+        <v>96</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>-0.0235</v>
+        <v>0.0031</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>-0.0235</v>
+        <v>-0.0395</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-0.2226</v>
+        <v>-0.2201</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>-0.2117</v>
+        <v>-0.2092</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>-0.0868</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>0.8006</v>
+        <v>0.8462000000000001</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>8.720000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="K55" s="7" t="n">
         <v>0.1264</v>
@@ -3685,31 +3688,31 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>40.22</v>
+        <v>39.98</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.0257</v>
+        <v>-0.006</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.0396</v>
+        <v>-0.0584</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>-0.1129</v>
+        <v>-0.1182</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>-0.1351</v>
+        <v>-0.1402</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.2552</v>
+        <v>-0.2569</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>-0.08800000000000001</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>9.529999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K56" s="4" t="n">
         <v>0.3754999999999999</v>
@@ -3743,31 +3746,31 @@
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>11.54</v>
+        <v>11.64</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>-0.0154</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>-0.0103</v>
+        <v>0.0122</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-0.0237</v>
+        <v>-0.0152</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>0.2135</v>
+        <v>0.2291</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>0.416</v>
+        <v>0.4772</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>9.73</v>
+        <v>9.81</v>
       </c>
       <c r="K57" s="7" t="n">
         <v>0.6297</v>
@@ -3797,57 +3800,57 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>CMENT</t>
+          <t>GESAN</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>227.9</v>
+        <v>39.14</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>-0.042</v>
+        <v>-0.0312</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>-0.0555</v>
+        <v>-0.08380000000000001</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>-0.05</v>
+        <v>-0.3687</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>-0.2397</v>
+        <v>-0.5046</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-0.2878</v>
+        <v>-0.1812</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>-0.376</v>
+        <v>-0.09230000000000001</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>22.49</v>
+        <v>10.52</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0.0934</v>
+        <v>0.2641</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.1109</v>
+        <v>0.2931</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.1008</v>
+        <v>0.3273</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.4922</v>
+        <v>0.4479</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>0.1647</v>
+        <v>0.1778</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1266</v>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr"/>
@@ -3859,31 +3862,31 @@
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>25.66</v>
+        <v>25.24</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>0.0516</v>
+        <v>-0.0164</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>0.0039</v>
+        <v>-0.0285</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-0.1378</v>
+        <v>-0.1519</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>0.1334</v>
+        <v>0.1148</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>0.08449999999999999</v>
+        <v>0.0525</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>0.1538</v>
+        <v>0.1238</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>18.99</v>
+        <v>18.68</v>
       </c>
       <c r="K59" s="7" t="n">
         <v>0.4327</v>
@@ -3913,57 +3916,57 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GESAN</t>
+          <t>CMENT</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>40.4</v>
+        <v>230</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>-0.0367</v>
+        <v>0.0092</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>-0.1133</v>
+        <v>-0.04559999999999999</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>-0.3484</v>
+        <v>-0.0413</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>-0.4886</v>
+        <v>-0.2327</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-0.1928</v>
+        <v>-0.3067</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>-0.0717</v>
+        <v>-0.3611</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>1.08</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>10.86</v>
+        <v>22.7</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0.2641</v>
+        <v>0.0934</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.2931</v>
+        <v>0.1109</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.3273</v>
+        <v>0.1008</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.4479</v>
+        <v>0.4922</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>0.1778</v>
+        <v>0.1647</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>0.1266</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr"/>
@@ -3975,31 +3978,31 @@
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>10.43</v>
+        <v>10.32</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>-0.0114</v>
+        <v>-0.0105</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>-0.0298</v>
+        <v>-0.0227</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>-0.0827</v>
+        <v>-0.09230000000000001</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>-0.0993</v>
+        <v>-0.1088</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>0.0068</v>
+        <v>-0.0337</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>-0.1394</v>
+        <v>-0.1443</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>7</v>
+        <v>6.92</v>
       </c>
       <c r="K61" s="7" t="n">
         <v>0.423</v>
@@ -4029,57 +4032,55 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>CWENE</t>
+          <t>YKSLN</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>18.32</v>
+        <v>2.21</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>-0.0393</v>
+        <v>-0.0221</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>-0.1011</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>-0.4094</v>
+        <v>-0.4738</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>-0.5141</v>
+        <v>-0.3006</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-0.479</v>
+        <v>-0.3072</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>-0.303</v>
+        <v>-0.345</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="J62" s="3" t="n">
-        <v>6.81</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="4" t="n">
-        <v>0.5809000000000001</v>
+        <v>0.1126</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.9067000000000001</v>
+        <v>0.0263</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.8432999999999999</v>
+        <v>0.6127</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>5.095899999999999</v>
+        <v>0.8754000000000001</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>0.1918</v>
+        <v>0.1443</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>0.2052</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr"/>
@@ -4087,55 +4088,57 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>YKSLN</t>
+          <t>CWENE</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>2.26</v>
+        <v>18.13</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0104</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>0.08130000000000001</v>
+        <v>-0.0253</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-0.4619</v>
+        <v>-0.4155</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>-0.2848</v>
+        <v>-0.5191</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>-0.2871</v>
+        <v>-0.5019</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>-0.3694</v>
+        <v>-0.2399</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="J63" s="5" t="inlineStr"/>
+        <v>1.1</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>6.74</v>
+      </c>
       <c r="K63" s="7" t="n">
-        <v>0.1126</v>
+        <v>0.5809000000000001</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>0.0263</v>
+        <v>0.9067000000000001</v>
       </c>
       <c r="M63" s="7" t="n">
-        <v>0.6127</v>
+        <v>0.8432999999999999</v>
       </c>
       <c r="N63" s="7" t="n">
-        <v>0.8754000000000001</v>
+        <v>5.095899999999999</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>0.1443</v>
+        <v>0.1918</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>-0.04969999999999999</v>
+        <v>0.2052</v>
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R63" s="5" t="inlineStr"/>
@@ -4143,55 +4146,57 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>BYDNR</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>22.86</v>
+        <v>5.85</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.0395</v>
+        <v>-0.1</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>0.1184</v>
+        <v>-0.4085</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>-0.3685</v>
+        <v>-0.8815000000000001</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>-0.3933</v>
+        <v>-0.8573999999999999</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.4141</v>
+        <v>-0.7225</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.7728</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr"/>
+        <v>1.11</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>3.72</v>
+      </c>
       <c r="K64" s="4" t="n">
-        <v>0.2762</v>
+        <v>7.8666</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.0636</v>
+        <v>3.1929</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.127</v>
+        <v>4.946499999999999</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.7182999999999999</v>
+        <v>1.0979</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>0.1081</v>
+        <v>0.4854</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>-0.0257</v>
+        <v>0.586</v>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr"/>
@@ -4203,31 +4208,31 @@
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>10.52</v>
+        <v>10.34</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>-0.0066</v>
+        <v>-0.0171</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>0.0253</v>
+        <v>0.034</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>-0.2006</v>
+        <v>-0.2143</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>-0.2669</v>
+        <v>-0.2794</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>-0.2371</v>
+        <v>-0.2582</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>0.4672</v>
+        <v>0.3973</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>14.91</v>
+        <v>14.65</v>
       </c>
       <c r="K65" s="7" t="n">
         <v>0.5631</v>
@@ -4257,57 +4262,55 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ISDMR</t>
+          <t>BYDNR</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>63.15</v>
+        <v>23.14</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.0417</v>
+        <v>0.0122</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>0.0352</v>
+        <v>0.1146</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.0429</v>
+        <v>-0.3608</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>0.1503</v>
+        <v>-0.3859</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0.4352</v>
+        <v>-0.4157</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>0.6858</v>
+        <v>0.0956</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>14.89</v>
-      </c>
+        <v>1.15</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="4" t="n">
-        <v>0.1859</v>
+        <v>0.2762</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.3543</v>
+        <v>0.0636</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.4035</v>
+        <v>0.127</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.208</v>
+        <v>0.7182999999999999</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>0.1056</v>
+        <v>0.1081</v>
       </c>
       <c r="P66" s="4" t="n">
-        <v>0.0859</v>
+        <v>-0.0257</v>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr"/>
@@ -4315,57 +4318,57 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>ISDMR</t>
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>266.5</v>
+        <v>62.4</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>-0.03</v>
+        <v>-0.0119</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>-0.0037</v>
+        <v>-0.0295</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>-0.0318</v>
+        <v>0.0306</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>0.0309</v>
+        <v>0.1366</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>-0.1955</v>
+        <v>0.4079</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>0.1283</v>
+        <v>0.7003</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>18.36</v>
+        <v>14.71</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>0.3707</v>
+        <v>0.1859</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>0.4185</v>
+        <v>0.3543</v>
       </c>
       <c r="M67" s="7" t="n">
-        <v>0.4202</v>
+        <v>0.4035</v>
       </c>
       <c r="N67" s="7" t="n">
-        <v>1.8941</v>
+        <v>0.208</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>0.3086</v>
+        <v>0.1056</v>
       </c>
       <c r="P67" s="7" t="n">
-        <v>-0.1688</v>
+        <v>0.0859</v>
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R67" s="5" t="inlineStr"/>
@@ -4373,55 +4376,57 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>DAGI</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>5.46</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.0162</v>
+        <v>-0.0037</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>-0.0197</v>
+        <v>-0.0501</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>-0.4191</v>
+        <v>-0.1014</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>-0.4167</v>
+        <v>-0.1029</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-0.102</v>
+        <v>-0.229</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>-0.3166</v>
+        <v>0.1817</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr"/>
+        <v>1.18</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>12.12</v>
+      </c>
       <c r="K68" s="4" t="n">
-        <v>0.5429999999999999</v>
+        <v>0.4381</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>1.1389</v>
+        <v>0.1539</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>1.8634</v>
+        <v>0.1373</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.5748</v>
+        <v>0.3376</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>0.1561</v>
+        <v>0.2166</v>
       </c>
       <c r="P68" s="4" t="n">
-        <v>-0.0597</v>
+        <v>0.1059</v>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr"/>
@@ -4429,57 +4434,57 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>ENKAI</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>80.95</v>
+        <v>268.25</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>-0.0305</v>
+        <v>0.0066</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>-0.0375</v>
+        <v>-0.0263</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.0254</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>-0.09960000000000001</v>
+        <v>0.0377</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>-0.2268</v>
+        <v>-0.1708</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>0.1843</v>
+        <v>0.1362</v>
       </c>
       <c r="I69" s="6" t="n">
         <v>1.19</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>12.16</v>
+        <v>18.48</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>0.4381</v>
+        <v>0.3707</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>0.1539</v>
+        <v>0.4185</v>
       </c>
       <c r="M69" s="7" t="n">
-        <v>0.1373</v>
+        <v>0.4202</v>
       </c>
       <c r="N69" s="7" t="n">
-        <v>0.3376</v>
+        <v>1.8941</v>
       </c>
       <c r="O69" s="7" t="n">
-        <v>0.2166</v>
+        <v>0.3086</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>0.1059</v>
+        <v>-0.1688</v>
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="R69" s="5" t="inlineStr"/>
@@ -4491,31 +4496,31 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>814.5</v>
+        <v>799</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>-0.0181</v>
+        <v>-0.019</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>-0.0479</v>
+        <v>-0.0725</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>-0.1952</v>
+        <v>-0.2105</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>-0.2568</v>
+        <v>-0.271</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>-0.468</v>
+        <v>-0.4605</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>-0.2649</v>
+        <v>-0.228</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>1755.01</v>
+        <v>1721.61</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>0.248</v>
@@ -4545,57 +4550,57 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>NTGAZ</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>28.82</v>
+        <v>10.51</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>-0.0322</v>
+        <v>-0.0168</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>-0.0463</v>
+        <v>-0.0489</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>-0.1972</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>-0.1699</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>-0.3598</v>
+        <v>-0.1639</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>-0.2901</v>
+        <v>0.1549</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>6.44</v>
+        <v>6.68</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>0.4021</v>
+        <v>0.3448</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>0.2915</v>
+        <v>0.3645</v>
       </c>
       <c r="M71" s="7" t="n">
-        <v>0.201</v>
+        <v>0.4084</v>
       </c>
       <c r="N71" s="7" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.5755</v>
       </c>
       <c r="O71" s="7" t="n">
-        <v>0.8484999999999999</v>
+        <v>0.2148</v>
       </c>
       <c r="P71" s="7" t="n">
-        <v>0.298</v>
+        <v>0.2137</v>
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R71" s="5" t="inlineStr"/>
@@ -4607,31 +4612,31 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>4.9</v>
+        <v>4.87</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>-0.004099999999999999</v>
+        <v>-0.0061</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>-0.022</v>
+        <v>-0.0356</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>-0.1404</v>
+        <v>-0.1456</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>-0.2919</v>
+        <v>-0.2962</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>-0.1312</v>
+        <v>-0.1396</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>-0.2909</v>
+        <v>-0.3217</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>5.19</v>
+        <v>5.15</v>
       </c>
       <c r="K72" s="4" t="n">
         <v>0.6583</v>
@@ -4661,57 +4666,57 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>SELEC</t>
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>6.5</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.0718</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>-0.408</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-0.8683</v>
+        <v>-0.8168000000000001</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>-0.8415</v>
+        <v>-0.6391</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>-0.6937000000000001</v>
+        <v>-0.1817</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>-0.7434999999999999</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="I73" s="6" t="n">
         <v>1.23</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>4.13</v>
+        <v>22.45</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>7.8666</v>
+        <v>0.3781</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>3.1929</v>
+        <v>0.6063000000000001</v>
       </c>
       <c r="M73" s="7" t="n">
-        <v>4.946499999999999</v>
+        <v>1.4267</v>
       </c>
       <c r="N73" s="7" t="n">
-        <v>1.0979</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="O73" s="7" t="n">
-        <v>0.4854</v>
+        <v>0.0158</v>
       </c>
       <c r="P73" s="7" t="n">
-        <v>0.586</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R73" s="5" t="inlineStr"/>
@@ -4719,57 +4724,57 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>NTGAZ</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>10.69</v>
+        <v>29.04</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>-0.0175</v>
+        <v>0.0076</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>-0.0255</v>
+        <v>-0.0638</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>-0.0664</v>
+        <v>-0.1911</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>-0.0506</v>
+        <v>-0.1636</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-0.1908</v>
+        <v>-0.3564</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>0.1532</v>
+        <v>-0.283</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>6.79</v>
+        <v>6.49</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0.3448</v>
+        <v>0.4021</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.3645</v>
+        <v>0.2915</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.4084</v>
+        <v>0.201</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.5755</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>0.2148</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="P74" s="4" t="n">
-        <v>0.2137</v>
+        <v>0.298</v>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr"/>
@@ -4777,57 +4782,57 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>GLCVY</t>
+          <t>GRTHO</t>
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>38.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>-0.0245</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>-0.0591</v>
+        <v>-0.0839</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-0.2939</v>
+        <v>-0.5575</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>-0.2965</v>
+        <v>-0.6038</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>-0.3617</v>
+        <v>-0.6085</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>-0.4264</v>
+        <v>-0.838</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>3.7</v>
+        <v>6.88</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>0.265</v>
+        <v>0.5085000000000001</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>0.2739</v>
+        <v>0.4487</v>
       </c>
       <c r="M75" s="7" t="n">
-        <v>0.2851</v>
+        <v>0.2298</v>
       </c>
       <c r="N75" s="7" t="n">
-        <v>0.0788</v>
+        <v>0.9399</v>
       </c>
       <c r="O75" s="7" t="n">
-        <v>0.7251000000000001</v>
+        <v>0.1089</v>
       </c>
       <c r="P75" s="7" t="n">
-        <v>0.4011</v>
+        <v>0.2287</v>
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R75" s="5" t="inlineStr"/>
@@ -4835,57 +4840,55 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>OBASE</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>71.75</v>
+        <v>22.74</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.0284</v>
+        <v>-0.0453</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>-0.0401</v>
+        <v>-0.1464</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>-0.1037</v>
+        <v>-0.3687</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>-0.221</v>
+        <v>-0.4312</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.1479</v>
+        <v>-0.4205</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>0.7331</v>
+        <v>-0.3701</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="J76" s="3" t="n">
-        <v>26.41</v>
-      </c>
+        <v>1.27</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="4" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.2041</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.3716</v>
+        <v>0.3021</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.4119</v>
+        <v>0.5156000000000001</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.9691</v>
+        <v>0.4873</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>0.3037</v>
+        <v>0.2465</v>
       </c>
       <c r="P76" s="4" t="n">
-        <v>0.0601</v>
+        <v>0.1432</v>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R76" s="2" t="inlineStr"/>
@@ -4893,57 +4896,57 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>SELEC</t>
+          <t>GLCVY</t>
         </is>
       </c>
       <c r="B77" s="6" t="n">
-        <v>79.34999999999999</v>
+        <v>38.1</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>-0.0276</v>
+        <v>-0.0026</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>0.0566</v>
+        <v>-0.0611</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-0.8026000000000001</v>
+        <v>-0.2957</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>-0.6112</v>
+        <v>-0.2983</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>-0.1074</v>
+        <v>-0.3639</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>0.0173</v>
+        <v>-0.4262</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>24.19</v>
+        <v>3.69</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>0.3781</v>
+        <v>0.265</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>0.6063000000000001</v>
+        <v>0.2739</v>
       </c>
       <c r="M77" s="7" t="n">
-        <v>1.4267</v>
+        <v>0.2851</v>
       </c>
       <c r="N77" s="7" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.0788</v>
       </c>
       <c r="O77" s="7" t="n">
-        <v>0.0158</v>
+        <v>0.7251000000000001</v>
       </c>
       <c r="P77" s="7" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.4011</v>
       </c>
       <c r="Q77" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R77" s="5" t="inlineStr"/>
@@ -4951,55 +4954,55 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>OBASE</t>
+          <t>DAGI</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>23.82</v>
+        <v>6</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>-0.0767</v>
+        <v>0.0989</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>-0.1275</v>
+        <v>0.07719999999999999</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>-0.3387</v>
+        <v>-0.3617</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>-0.4042</v>
+        <v>-0.359</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>-0.3648</v>
+        <v>-0.0228</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>-0.3383</v>
+        <v>-0.2611</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="4" t="n">
-        <v>0.2041</v>
+        <v>0.5429999999999999</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>0.3021</v>
+        <v>1.1389</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>0.5156000000000001</v>
+        <v>1.8634</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>0.4873</v>
+        <v>0.5748</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>0.2465</v>
+        <v>0.1561</v>
       </c>
       <c r="P78" s="4" t="n">
-        <v>0.1432</v>
+        <v>-0.0597</v>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr"/>
@@ -5007,57 +5010,57 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>GARFA</t>
+          <t>RALYH</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
-        <v>22.9</v>
+        <v>33.16</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>-0.0129</v>
+        <v>-0.0999</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>0.016</v>
+        <v>-0.4089</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-0.1417</v>
+        <v>-0.8778</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>-0.1365</v>
+        <v>-0.8405</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>-0.1804</v>
+        <v>-0.8828</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>-0.102</v>
+        <v>-0.8079999999999999</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>3.47</v>
+        <v>4.3</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>0.9562999999999999</v>
+        <v>0.7070000000000001</v>
       </c>
       <c r="L79" s="7" t="n">
-        <v>0.9506</v>
+        <v>1.4848</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>0.9429999999999999</v>
+        <v>1.5369</v>
       </c>
       <c r="N79" s="7" t="n">
-        <v>0.5365</v>
+        <v>0.5434</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>0.914</v>
+        <v>0.2854</v>
       </c>
       <c r="P79" s="7" t="n">
-        <v>0.496</v>
+        <v>0.3914</v>
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R79" s="5" t="inlineStr"/>
@@ -5065,57 +5068,57 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>PCILT</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>30.22</v>
+        <v>73.3</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>-0.0059</v>
+        <v>0.0216</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>-0.0702</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>-0.0131</v>
+        <v>-0.0843</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>-0.058</v>
+        <v>-0.2041</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>0.09179999999999999</v>
+        <v>-0.1169</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>0.3952000000000001</v>
+        <v>0.6591</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>6.94</v>
+        <v>26.98</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0.763</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>0.7087</v>
+        <v>0.3716</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>0.7914</v>
+        <v>0.4119</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>1.2232</v>
+        <v>0.9691</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>0.0574</v>
+        <v>0.3037</v>
       </c>
       <c r="P80" s="4" t="n">
-        <v>0.2831</v>
+        <v>0.0601</v>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr"/>
@@ -5123,57 +5126,57 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>KCAER</t>
+          <t>GARFA</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>10.63</v>
+        <v>22.54</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>-0.0203</v>
+        <v>-0.0157</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>0.0124</v>
+        <v>-0.0123</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-0.2519</v>
+        <v>-0.1552</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>-0.1817</v>
+        <v>-0.1501</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.2018</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>-0.2149</v>
+        <v>-0.1195</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>30.96</v>
+        <v>3.42</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>0.1522</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="L81" s="7" t="n">
-        <v>0.2873</v>
+        <v>0.9506</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>0.3247</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="N81" s="7" t="n">
-        <v>1.1982</v>
+        <v>0.5365</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>0.1199</v>
+        <v>0.914</v>
       </c>
       <c r="P81" s="7" t="n">
-        <v>0.0508</v>
+        <v>0.496</v>
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R81" s="5" t="inlineStr"/>
@@ -5185,25 +5188,25 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>6.56</v>
+        <v>6.54</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>-0.0076</v>
+        <v>-0.003</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>-0.0296</v>
+        <v>-0.0268</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>-0.123</v>
+        <v>-0.1257</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>-0.1665</v>
+        <v>-0.169</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>-0.2077</v>
+        <v>-0.2224</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>-0.2227</v>
+        <v>-0.2177</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>1.37</v>
@@ -5237,57 +5240,55 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>GRTHO</t>
+          <t>ACSEL</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>109.8</v>
+        <v>86.5</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>-0.1</v>
+        <v>-0.0052</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>-0.0926</v>
+        <v>-0.0308</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-0.5085000000000001</v>
+        <v>-0.2399</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>-0.5599000000000001</v>
+        <v>-0.3268</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>-0.5871999999999999</v>
+        <v>-0.2619</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>-0.8162</v>
+        <v>-0.1923</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="J83" s="6" t="n">
-        <v>7.64</v>
-      </c>
+        <v>1.37</v>
+      </c>
+      <c r="J83" s="5" t="inlineStr"/>
       <c r="K83" s="7" t="n">
-        <v>0.5085000000000001</v>
+        <v>0.3957</v>
       </c>
       <c r="L83" s="7" t="n">
-        <v>0.4487</v>
+        <v>2.0344</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>0.2298</v>
+        <v>3.8494</v>
       </c>
       <c r="N83" s="7" t="n">
-        <v>0.9399</v>
+        <v>0.889</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>0.1089</v>
+        <v>0.0349</v>
       </c>
       <c r="P83" s="7" t="n">
-        <v>0.2287</v>
+        <v>-0.0175</v>
       </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R83" s="5" t="inlineStr"/>
@@ -5295,55 +5296,57 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>PCILT</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>86.95</v>
+        <v>30.44</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>-0.0307</v>
+        <v>0.0073</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>-0.023</v>
+        <v>-0.0337</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>-0.2359</v>
+        <v>-0.0059</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>-0.3233</v>
+        <v>-0.05110000000000001</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>-0.2556</v>
+        <v>0.0934</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>-0.1859</v>
+        <v>0.4264</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>6.99</v>
+      </c>
       <c r="K84" s="4" t="n">
-        <v>0.3957</v>
+        <v>0.763</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>2.0344</v>
+        <v>0.7087</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>3.8494</v>
+        <v>0.7914</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>0.889</v>
+        <v>1.2232</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>0.0349</v>
+        <v>0.0574</v>
       </c>
       <c r="P84" s="4" t="n">
-        <v>-0.0175</v>
+        <v>0.2831</v>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr"/>
@@ -5355,25 +5358,25 @@
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>11.84</v>
+        <v>11.8</v>
       </c>
       <c r="C85" s="7" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="D85" s="7" t="n">
         <v>0.008500000000000001</v>
       </c>
-      <c r="D85" s="7" t="n">
-        <v>0.0395</v>
-      </c>
       <c r="E85" s="7" t="n">
-        <v>-0.015</v>
+        <v>-0.0183</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>-0.0588</v>
+        <v>-0.062</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>0.0735</v>
+        <v>0.0563</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0.3941</v>
+        <v>0.4459</v>
       </c>
       <c r="I85" s="6" t="n">
         <v>1.38</v>
@@ -5411,31 +5414,31 @@
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>18.88</v>
+        <v>18.91</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>-0.0527</v>
+        <v>0.0016</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>-0.0949</v>
+        <v>-0.108</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>-0.2356</v>
+        <v>-0.2344</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>-0.2676</v>
+        <v>-0.2665</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>-0.338</v>
+        <v>-0.3616</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>0.2173</v>
+        <v>0.2674</v>
       </c>
       <c r="I86" s="3" t="n">
         <v>1.41</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>69.18000000000001</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="K86" s="4" t="n">
         <v>0.5590999999999999</v>
@@ -5465,57 +5468,57 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>RALYH</t>
+          <t>KCAER</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>36.84</v>
+        <v>11.01</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>-0.09970000000000001</v>
+        <v>0.0357</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>-0.4087</v>
+        <v>0.0446</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>-0.8642</v>
+        <v>-0.2252</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>-0.8228</v>
+        <v>-0.1524</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>-0.8694</v>
+        <v>-0.0582</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>-0.7774</v>
+        <v>-0.1646</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>4.77</v>
+        <v>32.06</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>0.7070000000000001</v>
+        <v>0.1522</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>1.4848</v>
+        <v>0.2873</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>1.5369</v>
+        <v>0.3247</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>0.5434</v>
+        <v>1.1982</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>0.2854</v>
+        <v>0.1199</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>0.3914</v>
+        <v>0.0508</v>
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R87" s="5" t="inlineStr"/>
@@ -5527,31 +5530,31 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>28.76</v>
+        <v>28</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>-0.029</v>
+        <v>-0.0264</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>-0.08810000000000001</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>-0.2682</v>
+        <v>-0.2875</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>-0.3654</v>
+        <v>-0.3822</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>-0.2507</v>
+        <v>-0.2893</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>-0.347</v>
+        <v>-0.35</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>34.46</v>
+        <v>33.55</v>
       </c>
       <c r="K88" s="4" t="n">
         <v>0.05019999999999999</v>
@@ -5581,57 +5584,55 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>TUPRS</t>
+          <t>KNFRT</t>
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>384.75</v>
+        <v>9.75</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>-0.0039</v>
+        <v>-0.0191</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>0.0192</v>
+        <v>-0.1522</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-0.08560000000000001</v>
+        <v>-0.2015</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>0.425</v>
+        <v>-0.18</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>0.4492</v>
+        <v>-0.2118</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>1.1013</v>
+        <v>-0.3439</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="J89" s="6" t="n">
-        <v>10.67</v>
-      </c>
+        <v>1.62</v>
+      </c>
+      <c r="J89" s="5" t="inlineStr"/>
       <c r="K89" s="7" t="n">
-        <v>0.465</v>
+        <v>0.7798</v>
       </c>
       <c r="L89" s="7" t="n">
-        <v>1.0453</v>
+        <v>1.3764</v>
       </c>
       <c r="M89" s="7" t="n">
-        <v>1.1002</v>
+        <v>26.3063</v>
       </c>
       <c r="N89" s="7" t="n">
-        <v>2.2351</v>
+        <v>0.625</v>
       </c>
       <c r="O89" s="7" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0124</v>
       </c>
       <c r="P89" s="7" t="n">
-        <v>0.187</v>
+        <v>-0.1091</v>
       </c>
       <c r="Q89" s="5" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R89" s="5" t="inlineStr"/>
@@ -5639,55 +5640,57 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>KNFRT</t>
+          <t>TUPRS</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>9.94</v>
+        <v>385.75</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>-0.0596</v>
+        <v>0.0026</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>-0.2155</v>
+        <v>-0.0103</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>-0.1859</v>
+        <v>-0.0832</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>-0.164</v>
+        <v>0.4287</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>-0.1792</v>
+        <v>0.4709</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>-0.43</v>
+        <v>1.1611</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr"/>
+        <v>1.63</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>10.7</v>
+      </c>
       <c r="K90" s="4" t="n">
-        <v>0.7798</v>
+        <v>0.465</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>1.3764</v>
+        <v>1.0453</v>
       </c>
       <c r="M90" s="4" t="n">
-        <v>26.3063</v>
+        <v>1.1002</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>0.625</v>
+        <v>2.2351</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>0.0124</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="P90" s="4" t="n">
-        <v>-0.1091</v>
+        <v>0.187</v>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="R90" s="2" t="inlineStr"/>
@@ -5699,31 +5702,31 @@
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>32.5</v>
+        <v>31.66</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>-0.0407</v>
+        <v>-0.0258</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>-0.0672</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-0.1393</v>
+        <v>-0.1615</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>-0.1042</v>
+        <v>-0.1273</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>0.0559</v>
+        <v>-0.09539999999999998</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>0.1887</v>
+        <v>0.1546</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>11.57</v>
+        <v>11.27</v>
       </c>
       <c r="K91" s="7" t="n">
         <v>0.3776</v>
@@ -5753,57 +5756,57 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SAFKR</t>
+          <t>KTLEV</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>12</v>
+        <v>7.92</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>-0.0453</v>
+        <v>-0.1</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.0258</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>-0.1519</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>-0.4</v>
+        <v>-0.8632</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>-0.5522</v>
+        <v>-0.6792</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>-0.4575</v>
+        <v>1.0539</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>17.45</v>
+        <v>1.93</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0.7861</v>
+        <v>3.5578</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>0.4555</v>
+        <v>3.6471</v>
       </c>
       <c r="M92" s="4" t="n">
-        <v>0.3309</v>
+        <v>5.174600000000001</v>
       </c>
       <c r="N92" s="4" t="n">
-        <v>0.5716</v>
+        <v>5.7649</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>0.2109</v>
+        <v>0.7222</v>
       </c>
       <c r="P92" s="4" t="n">
-        <v>0.1216</v>
+        <v>1.5072</v>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R92" s="2" t="inlineStr"/>
@@ -5815,31 +5818,31 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>-0.0522</v>
+        <v>-0.0348</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>-0.1154</v>
+        <v>-0.1633</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>-0.2959</v>
+        <v>-0.3204</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>-0.5097</v>
+        <v>-0.5268</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>-0.5951</v>
+        <v>-0.6051</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>-0</v>
+        <v>-0.023</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>7.37</v>
+        <v>7.11</v>
       </c>
       <c r="K93" s="7" t="n">
         <v>0.51</v>
@@ -5869,57 +5872,57 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ORGE</t>
+          <t>SAFKR</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>22.8</v>
+        <v>12.05</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>-0.0155</v>
+        <v>0.0042</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>-0.0256</v>
+        <v>-0.1858</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>-0.0215</v>
+        <v>-0.1484</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>0.0765</v>
+        <v>-0.3975</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>0.4970000000000001</v>
+        <v>-0.5443</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>0.6102000000000001</v>
+        <v>-0.471</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>10.58</v>
+        <v>17.52</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0.251</v>
+        <v>0.7861</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>0.257</v>
+        <v>0.4555</v>
       </c>
       <c r="M94" s="4" t="n">
-        <v>0.2421</v>
+        <v>0.3309</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>0.2676</v>
+        <v>0.5716</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>0.4943</v>
+        <v>0.2109</v>
       </c>
       <c r="P94" s="4" t="n">
-        <v>0.2029</v>
+        <v>0.1216</v>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr"/>
@@ -5927,57 +5930,57 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>GENIL</t>
+          <t>ORGE</t>
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>5.13</v>
+        <v>22.88</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>0.09849999999999999</v>
+        <v>0.0035</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>0.0118</v>
+        <v>-0.0017</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.018</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>-0.421</v>
+        <v>0.0803</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.4993</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>-0.6335999999999999</v>
+        <v>0.6401</v>
       </c>
       <c r="I95" s="6" t="n">
         <v>1.76</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>18.7</v>
+        <v>10.62</v>
       </c>
       <c r="K95" s="7" t="n">
-        <v>0.5049</v>
+        <v>0.251</v>
       </c>
       <c r="L95" s="7" t="n">
-        <v>0.7672</v>
+        <v>0.257</v>
       </c>
       <c r="M95" s="7" t="n">
-        <v>1.1622</v>
+        <v>0.2421</v>
       </c>
       <c r="N95" s="7" t="n">
-        <v>1.2274</v>
+        <v>0.2676</v>
       </c>
       <c r="O95" s="7" t="n">
-        <v>0.0922</v>
+        <v>0.4943</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>0.1305</v>
+        <v>0.2029</v>
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R95" s="5" t="inlineStr"/>
@@ -5985,57 +5988,57 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>GENIL</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>15.57</v>
+        <v>5.24</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>0.09960000000000001</v>
+        <v>0.0214</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>0.6068</v>
+        <v>0.2186</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>-0.3722</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>-0.5792</v>
+        <v>-0.4086</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>-0.4686</v>
+        <v>-0.4863</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>0.4372</v>
+        <v>-0.6361</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>2.01</v>
+        <v>19.1</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>2.1748</v>
+        <v>0.5049</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>2.2285</v>
+        <v>0.7672</v>
       </c>
       <c r="M96" s="4" t="n">
-        <v>2.5519</v>
+        <v>1.1622</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>7.8348</v>
+        <v>1.2274</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>0.887</v>
+        <v>0.0922</v>
       </c>
       <c r="P96" s="4" t="n">
-        <v>1.1538</v>
+        <v>0.1305</v>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr"/>
@@ -6047,28 +6050,28 @@
         </is>
       </c>
       <c r="B97" s="6" t="n">
-        <v>11.03</v>
+        <v>11.1</v>
       </c>
       <c r="C97" s="7" t="n">
-        <v>-0.0375</v>
+        <v>0.0063</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>-0.1083</v>
+        <v>-0.0488</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>-0.2287</v>
+        <v>-0.2238</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>0.2635</v>
+        <v>0.2715</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>0.2534</v>
+        <v>0.2292</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>0.2379</v>
+        <v>0.2759</v>
       </c>
       <c r="I97" s="6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="J97" s="5" t="inlineStr"/>
       <c r="K97" s="7" t="n">
@@ -6099,57 +6102,57 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>KTLEV</t>
+          <t>MPARK</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>429.5</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>0.1</v>
+        <v>-0.0058</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>-0.019</v>
+        <v>-0.0155</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>-0.7889</v>
+        <v>-0.0283</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>-0.848</v>
+        <v>0.0343</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>-0.6423000000000001</v>
+        <v>-0.09390000000000001</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>1.2175</v>
+        <v>0.2735</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>2.14</v>
+        <v>13.41</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>3.5578</v>
+        <v>0.3601</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>3.6471</v>
+        <v>0.3635</v>
       </c>
       <c r="M98" s="4" t="n">
-        <v>5.174600000000001</v>
+        <v>0.5899</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>5.7649</v>
+        <v>0.1175</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>0.7222</v>
+        <v>0.2737</v>
       </c>
       <c r="P98" s="4" t="n">
-        <v>1.5072</v>
+        <v>0.2987</v>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Sağlık hizmetleri</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr"/>
@@ -6161,31 +6164,31 @@
         </is>
       </c>
       <c r="B99" s="6" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="C99" s="7" t="n">
-        <v>0.0024</v>
+        <v>-0.0024</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>-0.0708</v>
+        <v>-0.0278</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>-0.1006</v>
+        <v>-0.1028</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>-0.1549</v>
+        <v>-0.1569</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>-0.0929</v>
+        <v>-0.1066</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>0.505</v>
+        <v>0.458</v>
       </c>
       <c r="I99" s="6" t="n">
         <v>1.88</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>13.65</v>
+        <v>13.61</v>
       </c>
       <c r="K99" s="7" t="n">
         <v>1.0251</v>
@@ -6215,57 +6218,55 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>DURDO</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>432</v>
+        <v>6.38</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>-0.012</v>
+        <v>-0.0031</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>-0.0092</v>
+        <v>0.1292</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>-0.0226</v>
+        <v>0.2269</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>0.0403</v>
+        <v>0.2735</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>-0.0614</v>
+        <v>0.519</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>0.2255</v>
+        <v>0.7972</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="J100" s="3" t="n">
-        <v>13.49</v>
-      </c>
+        <v>1.89</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="4" t="n">
-        <v>0.3601</v>
+        <v>0.3099</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>0.3635</v>
+        <v>0.2862</v>
       </c>
       <c r="M100" s="4" t="n">
-        <v>0.5899</v>
+        <v>0.3279</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>0.1175</v>
+        <v>0.1519</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>0.2737</v>
+        <v>0.0876</v>
       </c>
       <c r="P100" s="4" t="n">
-        <v>0.2987</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>Sağlık hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R100" s="2" t="inlineStr"/>
@@ -6273,55 +6274,57 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>DURDO</t>
+          <t>DERIM</t>
         </is>
       </c>
       <c r="B101" s="6" t="n">
-        <v>6.4</v>
+        <v>25.34</v>
       </c>
       <c r="C101" s="7" t="n">
-        <v>-0.0244</v>
+        <v>-0.0071</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>0.2774</v>
+        <v>-0.0649</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>0.2308</v>
+        <v>-0.2878</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>0.2774</v>
+        <v>-0.3268</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>0.5311</v>
+        <v>-0.363</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>0.8234</v>
+        <v>-0.3565</v>
       </c>
       <c r="I101" s="6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J101" s="5" t="inlineStr"/>
+        <v>1.89</v>
+      </c>
+      <c r="J101" s="6" t="n">
+        <v>13.96</v>
+      </c>
       <c r="K101" s="7" t="n">
-        <v>0.3099</v>
+        <v>0.1436</v>
       </c>
       <c r="L101" s="7" t="n">
-        <v>0.2862</v>
+        <v>0.2539</v>
       </c>
       <c r="M101" s="7" t="n">
-        <v>0.3279</v>
+        <v>0.0263</v>
       </c>
       <c r="N101" s="7" t="n">
-        <v>0.1519</v>
+        <v>0.0576</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>0.0876</v>
+        <v>0.0602</v>
       </c>
       <c r="P101" s="7" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.1637</v>
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R101" s="5" t="inlineStr"/>
@@ -6329,57 +6332,57 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>DERIM</t>
+          <t>ENERY</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>25.52</v>
+        <v>14.46</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>-0.0478</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>-0.08070000000000001</v>
+        <v>0.0463</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>-0.2827</v>
+        <v>0.2563</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>-0.322</v>
+        <v>0.4431</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>-0.314</v>
+        <v>0.6013000000000001</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>-0.361</v>
+        <v>0.4431</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>14.06</v>
+        <v>23.06</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0.1436</v>
+        <v>0.4279</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>0.2539</v>
+        <v>0.7162999999999999</v>
       </c>
       <c r="M102" s="4" t="n">
-        <v>0.0263</v>
+        <v>0.8373999999999999</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>0.0576</v>
+        <v>0.6103000000000001</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>0.0602</v>
+        <v>0.2099</v>
       </c>
       <c r="P102" s="4" t="n">
-        <v>0.1637</v>
+        <v>0.1017</v>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr"/>
@@ -6387,57 +6390,57 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>ENERY</t>
+          <t>SAYAS</t>
         </is>
       </c>
       <c r="B103" s="6" t="n">
-        <v>14.6</v>
+        <v>39.06</v>
       </c>
       <c r="C103" s="7" t="n">
-        <v>0.0224</v>
+        <v>-0.024</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>0.0665</v>
+        <v>-0.06509999999999999</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>0.2685</v>
+        <v>-0.2692</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>0.4571</v>
+        <v>-0.149</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>0.5904</v>
+        <v>-0.1033</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>0.4038</v>
+        <v>-0.2807</v>
       </c>
       <c r="I103" s="6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>23.28</v>
+        <v>15.57</v>
       </c>
       <c r="K103" s="7" t="n">
-        <v>0.4279</v>
+        <v>0.486</v>
       </c>
       <c r="L103" s="7" t="n">
-        <v>0.7162999999999999</v>
+        <v>1.4655</v>
       </c>
       <c r="M103" s="7" t="n">
-        <v>0.8373999999999999</v>
+        <v>2.3632</v>
       </c>
       <c r="N103" s="7" t="n">
-        <v>0.6103000000000001</v>
+        <v>6.118200000000001</v>
       </c>
       <c r="O103" s="7" t="n">
-        <v>0.2099</v>
+        <v>0.1798</v>
       </c>
       <c r="P103" s="7" t="n">
-        <v>0.1017</v>
+        <v>0.1493</v>
       </c>
       <c r="Q103" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R103" s="5" t="inlineStr"/>
@@ -6445,57 +6448,57 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SAYAS</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>40.02</v>
+        <v>17.12</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>-0.0015</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>-0.0561</v>
+        <v>0.6075</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>-0.2513</v>
+        <v>-0.3097</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>-0.1281</v>
+        <v>-0.5373</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>-0.0398</v>
+        <v>-0.4204</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>-0.3112</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>15.95</v>
+        <v>2.21</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0.486</v>
+        <v>2.1748</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>1.4655</v>
+        <v>2.2285</v>
       </c>
       <c r="M104" s="4" t="n">
-        <v>2.3632</v>
+        <v>2.5519</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>6.118200000000001</v>
+        <v>7.8348</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>0.1798</v>
+        <v>0.887</v>
       </c>
       <c r="P104" s="4" t="n">
-        <v>0.1493</v>
+        <v>1.1538</v>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr"/>
@@ -6507,31 +6510,31 @@
         </is>
       </c>
       <c r="B105" s="6" t="n">
-        <v>259.25</v>
+        <v>260.5</v>
       </c>
       <c r="C105" s="7" t="n">
-        <v>-0.0217</v>
+        <v>0.0048</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>-0.0038</v>
+        <v>-0.0142</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>-0.1045</v>
+        <v>-0.1002</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>-0.1351</v>
+        <v>-0.1309</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>-0.1322</v>
+        <v>-0.1309</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>-0.0512</v>
+        <v>-0.0243</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="J105" s="6" t="n">
-        <v>10.2</v>
+        <v>10.25</v>
       </c>
       <c r="K105" s="7" t="n">
         <v>1.7224</v>
@@ -6561,57 +6564,57 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GLYHO</t>
+          <t>SANEL</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>17.78</v>
+        <v>28.54</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>0.026</v>
+        <v>-0.063</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>0.09420000000000001</v>
+        <v>-0.1404</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>0.064</v>
+        <v>-0.4096</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>0.04219999999999999</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>0.0552</v>
+        <v>-0.2328</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>0.8521</v>
+        <v>-0.0028</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>5.94</v>
+        <v>2.75</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0.2312</v>
+        <v>0.309</v>
       </c>
       <c r="L106" s="4" t="n">
-        <v>0.317</v>
+        <v>1.4614</v>
       </c>
       <c r="M106" s="4" t="n">
-        <v>0.3503</v>
+        <v>1.5381</v>
       </c>
       <c r="N106" s="4" t="n">
-        <v>0.4888</v>
+        <v>2.2148</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>0.3457</v>
+        <v>0.1491</v>
       </c>
       <c r="P106" s="4" t="n">
-        <v>-0.2226</v>
+        <v>1.0947</v>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr"/>
@@ -6619,57 +6622,57 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>GRSEL</t>
+          <t>AHGAZ</t>
         </is>
       </c>
       <c r="B107" s="6" t="n">
-        <v>280.25</v>
+        <v>47.68</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>-0.0009</v>
+        <v>-0.0209</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>0.0399</v>
+        <v>0.0343</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>-0.0611</v>
+        <v>0.2132</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>-0.0916</v>
+        <v>0.2721</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>-0.1159</v>
+        <v>0.9784</v>
       </c>
       <c r="H107" s="7" t="n">
-        <v>-0.1947</v>
+        <v>0.7517</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="J107" s="6" t="n">
-        <v>8.51</v>
+        <v>22.56</v>
       </c>
       <c r="K107" s="7" t="n">
-        <v>0.3337</v>
+        <v>0.659</v>
       </c>
       <c r="L107" s="7" t="n">
-        <v>0.6940999999999999</v>
+        <v>1.7979</v>
       </c>
       <c r="M107" s="7" t="n">
-        <v>0.2722</v>
+        <v>2.1313</v>
       </c>
       <c r="N107" s="7" t="n">
-        <v>0.7318000000000001</v>
+        <v>2.8917</v>
       </c>
       <c r="O107" s="7" t="n">
-        <v>0.3275</v>
+        <v>0.1977</v>
       </c>
       <c r="P107" s="7" t="n">
-        <v>0.3613</v>
+        <v>0.1152</v>
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R107" s="5" t="inlineStr"/>
@@ -6677,57 +6680,57 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>AHGAZ</t>
+          <t>GLYHO</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>48.7</v>
+        <v>17.65</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>0.0066</v>
+        <v>-0.0073</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>0.0633</v>
+        <v>0.0697</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>0.2392</v>
+        <v>0.0563</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>0.2994</v>
+        <v>0.0346</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>1.0445</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>0.7319</v>
+        <v>0.7720999999999999</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>23.05</v>
+        <v>5.89</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0.659</v>
+        <v>0.2312</v>
       </c>
       <c r="L108" s="4" t="n">
-        <v>1.7979</v>
+        <v>0.317</v>
       </c>
       <c r="M108" s="4" t="n">
-        <v>2.1313</v>
+        <v>0.3503</v>
       </c>
       <c r="N108" s="4" t="n">
-        <v>2.8917</v>
+        <v>0.4888</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>0.1977</v>
+        <v>0.3457</v>
       </c>
       <c r="P108" s="4" t="n">
-        <v>0.1152</v>
+        <v>-0.2226</v>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr"/>
@@ -6735,57 +6738,57 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>SANEL</t>
+          <t>GRSEL</t>
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>30.46</v>
+        <v>288</v>
       </c>
       <c r="C109" s="7" t="n">
-        <v>-0.0457</v>
+        <v>0.0277</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>-0.0361</v>
+        <v>0.0492</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>-0.3699</v>
+        <v>-0.0352</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>-0.6347999999999999</v>
+        <v>-0.0665</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>-0.1856</v>
+        <v>-0.1007</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>0.0554</v>
+        <v>-0.1652</v>
       </c>
       <c r="I109" s="6" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="J109" s="6" t="n">
-        <v>2.94</v>
+        <v>8.75</v>
       </c>
       <c r="K109" s="7" t="n">
-        <v>0.309</v>
+        <v>0.3337</v>
       </c>
       <c r="L109" s="7" t="n">
-        <v>1.4614</v>
+        <v>0.6940999999999999</v>
       </c>
       <c r="M109" s="7" t="n">
-        <v>1.5381</v>
+        <v>0.2722</v>
       </c>
       <c r="N109" s="7" t="n">
-        <v>2.2148</v>
+        <v>0.7318000000000001</v>
       </c>
       <c r="O109" s="7" t="n">
-        <v>0.1491</v>
+        <v>0.3275</v>
       </c>
       <c r="P109" s="7" t="n">
-        <v>1.0947</v>
+        <v>0.3613</v>
       </c>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R109" s="5" t="inlineStr"/>
@@ -6797,31 +6800,31 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>221.7</v>
+        <v>221.9</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>-0.0276</v>
+        <v>0.0009</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>-0.0276</v>
+        <v>-0.0138</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>-0.04190000000000001</v>
+        <v>-0.0411</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>-0.0509</v>
+        <v>-0.0501</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>-0.1365</v>
+        <v>-0.1441</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>-0.0793</v>
+        <v>-0.0609</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>2.17</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>20.72</v>
+        <v>20.74</v>
       </c>
       <c r="K110" s="4" t="n">
         <v>0.493</v>
@@ -6855,31 +6858,31 @@
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>22.96</v>
+        <v>22.8</v>
       </c>
       <c r="C111" s="7" t="n">
-        <v>-0.0449</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>-0.0757</v>
+        <v>-0.07769999999999999</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>-0.3795</v>
+        <v>-0.3838</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>-0.2055</v>
+        <v>-0.2111</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>0.0581</v>
+        <v>0.0755</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>0.2021</v>
+        <v>0.2324</v>
       </c>
       <c r="I111" s="6" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="J111" s="6" t="n">
-        <v>15.03</v>
+        <v>14.92</v>
       </c>
       <c r="K111" s="7" t="n">
         <v>0.5342</v>
@@ -6909,57 +6912,57 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>BIMAS</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>396.5</v>
+        <v>48</v>
       </c>
       <c r="C112" s="4" t="n">
-        <v>-0.0155</v>
+        <v>-0.0196</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>-0.0428</v>
+        <v>-0.09519999999999999</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>-0.0779</v>
+        <v>-0.337</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>0.0595</v>
+        <v>-0.4555</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>0.0496</v>
+        <v>0.1805</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>0.4524</v>
+        <v>0.7857</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>17.34</v>
+        <v>34.02</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0.4214</v>
+        <v>0.8139</v>
       </c>
       <c r="L112" s="4" t="n">
-        <v>0.5271</v>
+        <v>1.3529</v>
       </c>
       <c r="M112" s="4" t="n">
-        <v>0.8381000000000001</v>
+        <v>2.0375</v>
       </c>
       <c r="N112" s="4" t="n">
-        <v>0.8737999999999999</v>
+        <v>1.6152</v>
       </c>
       <c r="O112" s="4" t="n">
-        <v>0.0611</v>
+        <v>0.1821</v>
       </c>
       <c r="P112" s="4" t="n">
-        <v>0.1613</v>
+        <v>0.09230000000000001</v>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr"/>
@@ -6967,57 +6970,57 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>BIMAS</t>
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>48.96</v>
+        <v>411.25</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>-0.0133</v>
+        <v>0.0372</v>
       </c>
       <c r="D113" s="7" t="n">
-        <v>-0.1178</v>
+        <v>-0.0018</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>-0.3238</v>
+        <v>-0.0436</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>-0.4446</v>
+        <v>0.0989</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>0.1178</v>
+        <v>0.08439999999999999</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>0.8228</v>
+        <v>0.5288</v>
       </c>
       <c r="I113" s="6" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="J113" s="6" t="n">
-        <v>34.7</v>
+        <v>17.99</v>
       </c>
       <c r="K113" s="7" t="n">
-        <v>0.8139</v>
+        <v>0.4214</v>
       </c>
       <c r="L113" s="7" t="n">
-        <v>1.3529</v>
+        <v>0.5271</v>
       </c>
       <c r="M113" s="7" t="n">
-        <v>2.0375</v>
+        <v>0.8381000000000001</v>
       </c>
       <c r="N113" s="7" t="n">
-        <v>1.6152</v>
+        <v>0.8737999999999999</v>
       </c>
       <c r="O113" s="7" t="n">
-        <v>0.1821</v>
+        <v>0.0611</v>
       </c>
       <c r="P113" s="7" t="n">
-        <v>0.09230000000000001</v>
+        <v>0.1613</v>
       </c>
       <c r="Q113" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R113" s="5" t="inlineStr"/>
@@ -7029,31 +7032,31 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>82.45</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>-0.0155</v>
+        <v>0.0146</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>0.0391</v>
+        <v>0.0411</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>0.0319</v>
+        <v>0.0469</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0152</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>0.095</v>
+        <v>0.09269999999999999</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>0.7543000000000001</v>
+        <v>0.7928000000000001</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>11.14</v>
+        <v>11.3</v>
       </c>
       <c r="K114" s="4" t="n">
         <v>0.4257</v>
@@ -7087,31 +7090,31 @@
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>43.48</v>
+        <v>44.56</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0248</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>-0.0132</v>
+        <v>0.0239</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-0.1804</v>
+        <v>-0.16</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>-0.1598</v>
+        <v>-0.1389</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>-0.0548</v>
+        <v>-0.0658</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>0.7091</v>
+        <v>0.7968000000000001</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="J115" s="6" t="n">
-        <v>27.77</v>
+        <v>28.46</v>
       </c>
       <c r="K115" s="7" t="n">
         <v>1.2681</v>
@@ -7145,31 +7148,31 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>31.98</v>
+        <v>32.74</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>-0.0367</v>
+        <v>0.0238</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>-0.0594</v>
+        <v>-0.0751</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>-0.0941</v>
+        <v>-0.0725</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>-0.1495</v>
+        <v>-0.1293</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>-0.2313</v>
+        <v>-0.2057</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>-0.342</v>
+        <v>-0.3162</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>23.33</v>
+        <v>23.89</v>
       </c>
       <c r="K116" s="4" t="n">
         <v>0.3957</v>
@@ -7203,31 +7206,31 @@
         </is>
       </c>
       <c r="B117" s="6" t="n">
-        <v>123.9</v>
+        <v>123.1</v>
       </c>
       <c r="C117" s="7" t="n">
-        <v>0.0049</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>-0.0206</v>
+        <v>-0.016</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>-0.09630000000000001</v>
+        <v>-0.1021</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>0.0257</v>
+        <v>0.019</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>0.2846</v>
+        <v>0.2691</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>1.6508</v>
+        <v>1.7601</v>
       </c>
       <c r="I117" s="6" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>11.11</v>
+        <v>11.03</v>
       </c>
       <c r="K117" s="7" t="n">
         <v>2.4396</v>
@@ -7261,31 +7264,31 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>141.1</v>
+        <v>136.2</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>-0.0098</v>
+        <v>-0.0347</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>-0.0587</v>
+        <v>-0.0747</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>-0.0147</v>
+        <v>-0.0489</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>0.05139999999999999</v>
+        <v>0.0149</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>0.0247</v>
+        <v>-0.0194</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>-0.1526</v>
+        <v>-0.1725</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>15.34</v>
+        <v>14.81</v>
       </c>
       <c r="K118" s="4" t="n">
         <v>0.5617</v>
@@ -7319,31 +7322,31 @@
         </is>
       </c>
       <c r="B119" s="6" t="n">
-        <v>66.3</v>
+        <v>64.2</v>
       </c>
       <c r="C119" s="7" t="n">
-        <v>-0.0119</v>
+        <v>-0.0317</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>-0.0785</v>
+        <v>-0.0489</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>-0.1784</v>
+        <v>-0.2045</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>-0.017</v>
+        <v>-0.0482</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>0.5490999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H119" s="7" t="n">
-        <v>1.5422</v>
+        <v>1.5496</v>
       </c>
       <c r="I119" s="6" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>16.51</v>
+        <v>15.99</v>
       </c>
       <c r="K119" s="7" t="n">
         <v>2.0657</v>
@@ -7373,57 +7376,57 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>PKART</t>
+          <t>ATATP</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>230.2</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>-0.0624</v>
+        <v>-0.0141</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0774</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>-0.2369</v>
+        <v>-0.193</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>-0.3007</v>
+        <v>0.1078</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>0.1244</v>
+        <v>0.5713</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.6778</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>19.59</v>
+        <v>4.74</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0.5093</v>
+        <v>0.3072</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>1.5572</v>
+        <v>0.2985</v>
       </c>
       <c r="M120" s="4" t="n">
-        <v>1.6598</v>
+        <v>0.3487</v>
       </c>
       <c r="N120" s="4" t="n">
-        <v>4.8022</v>
+        <v>0.6609999999999999</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>0.083</v>
+        <v>0.3268</v>
       </c>
       <c r="P120" s="4" t="n">
-        <v>0.2041</v>
+        <v>0.7543000000000001</v>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr"/>
@@ -7435,31 +7438,31 @@
         </is>
       </c>
       <c r="B121" s="6" t="n">
-        <v>403.75</v>
+        <v>406</v>
       </c>
       <c r="C121" s="7" t="n">
-        <v>-0.0341</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>-0.0393</v>
+        <v>-0.0246</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-0.2013</v>
+        <v>-0.1968</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>-0.0152</v>
+        <v>-0.0098</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>-0.1856</v>
+        <v>-0.2397</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>0.3863</v>
+        <v>0.4097</v>
       </c>
       <c r="I121" s="6" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="J121" s="6" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="K121" s="7" t="n">
         <v>0.1897</v>
@@ -7489,57 +7492,57 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>ATATP</t>
+          <t>PKART</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>233.5</v>
+        <v>92</v>
       </c>
       <c r="C122" s="4" t="n">
-        <v>-0.011</v>
+        <v>0.0384</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>-0.08070000000000001</v>
+        <v>-0.0108</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>-0.1814</v>
+        <v>-0.2076</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>0.1237</v>
+        <v>-0.2739</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>0.6238</v>
+        <v>0.1152</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>0.6092</v>
+        <v>0.1429</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>3.41</v>
+        <v>3.46</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>4.8</v>
+        <v>20.34</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0.3072</v>
+        <v>0.5093</v>
       </c>
       <c r="L122" s="4" t="n">
-        <v>0.2985</v>
+        <v>1.5572</v>
       </c>
       <c r="M122" s="4" t="n">
-        <v>0.3487</v>
+        <v>1.6598</v>
       </c>
       <c r="N122" s="4" t="n">
-        <v>0.6609999999999999</v>
+        <v>4.8022</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>0.3268</v>
+        <v>0.083</v>
       </c>
       <c r="P122" s="4" t="n">
-        <v>0.7543000000000001</v>
+        <v>0.2041</v>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr"/>
@@ -7551,31 +7554,31 @@
         </is>
       </c>
       <c r="B123" s="6" t="n">
-        <v>18.9</v>
+        <v>18.79</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>-0.0192</v>
+        <v>-0.0058</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>-0.1</v>
+        <v>-0.1052</v>
       </c>
       <c r="E123" s="7" t="n">
-        <v>-0.1393</v>
+        <v>-0.1444</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>-0.2476</v>
+        <v>-0.252</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>-0.1076</v>
+        <v>-0.0771</v>
       </c>
       <c r="H123" s="7" t="n">
-        <v>0.2418</v>
+        <v>0.2808</v>
       </c>
       <c r="I123" s="6" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="J123" s="6" t="n">
-        <v>24.89</v>
+        <v>24.74</v>
       </c>
       <c r="K123" s="7" t="n">
         <v>0.6388</v>
@@ -7609,28 +7612,28 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>31.26</v>
+        <v>31.52</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>-0.0064</v>
+        <v>0.0083</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>0.0216</v>
+        <v>0.0013</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>-0.2467</v>
+        <v>-0.2405</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>-0.326</v>
+        <v>-0.3204</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>-0.4378</v>
+        <v>-0.4351</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>-0.1033</v>
+        <v>-0.0984</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="4" t="n">
@@ -7665,31 +7668,31 @@
         </is>
       </c>
       <c r="B125" s="6" t="n">
-        <v>129</v>
+        <v>128.5</v>
       </c>
       <c r="C125" s="7" t="n">
         <v>-0.0039</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>0.2124</v>
+        <v>0.0533</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-0.3246</v>
+        <v>-0.3272</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>-0.265</v>
+        <v>-0.2678</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>-0.1389</v>
+        <v>-0.1329</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>2.783</v>
+        <v>2.7794</v>
       </c>
       <c r="I125" s="6" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="J125" s="6" t="n">
-        <v>14.37</v>
+        <v>14.31</v>
       </c>
       <c r="K125" s="7" t="n">
         <v>1.164</v>
@@ -7723,31 +7726,31 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>27.1</v>
+        <v>26.92</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>-0.0308</v>
+        <v>-0.0066</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>-0.0757</v>
+        <v>-0.0296</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>-0.1429</v>
+        <v>-0.1486</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>-0.3224</v>
+        <v>-0.3269</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>0.1921</v>
+        <v>0.1932</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>0.7698</v>
+        <v>0.8044</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>10.1</v>
+        <v>10.03</v>
       </c>
       <c r="K126" s="4" t="n">
         <v>1.4662</v>
@@ -7780,32 +7783,32 @@
           <t>DOCO</t>
         </is>
       </c>
-      <c r="B127" s="6" t="n">
-        <v>10712.5</v>
+      <c r="B127" s="8" t="n">
+        <v>10720</v>
       </c>
       <c r="C127" s="7" t="n">
-        <v>-0.0097</v>
+        <v>0.0007000000000000001</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>0.004500000000000001</v>
+        <v>-0.0104</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>-0.0452</v>
+        <v>-0.0446</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>-0.0297</v>
+        <v>-0.029</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>0.075</v>
+        <v>0.1158</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>-0.0444</v>
+        <v>-0.0074</v>
       </c>
       <c r="I127" s="6" t="n">
         <v>4.2</v>
       </c>
       <c r="J127" s="6" t="n">
-        <v>19.67</v>
+        <v>19.69</v>
       </c>
       <c r="K127" s="7" t="n">
         <v>0.2032</v>
@@ -7835,57 +7838,57 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>ONCSM</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>197.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="C128" s="4" t="n">
-        <v>-0.0338</v>
+        <v>-0.0461</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>-0.1071</v>
+        <v>-0.0466</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>-0.3064</v>
+        <v>-0.4803</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>-0.3779999999999999</v>
+        <v>-0.6363</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>0.0165</v>
+        <v>-0.6772</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>1.162</v>
+        <v>-0.4175</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>19.37</v>
+        <v>30.08</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0.4338</v>
+        <v>0.5028</v>
       </c>
       <c r="L128" s="4" t="n">
-        <v>0.5232</v>
+        <v>1.6135</v>
       </c>
       <c r="M128" s="4" t="n">
-        <v>0.7125</v>
+        <v>2.0025</v>
       </c>
       <c r="N128" s="4" t="n">
-        <v>0.8672</v>
+        <v>9.2562</v>
       </c>
       <c r="O128" s="4" t="n">
-        <v>0.3018</v>
+        <v>0.3063</v>
       </c>
       <c r="P128" s="4" t="n">
-        <v>0.3122</v>
+        <v>0.1832</v>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr"/>
@@ -7893,57 +7896,57 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>ONCSM</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B129" s="6" t="n">
-        <v>95.5</v>
+        <v>196</v>
       </c>
       <c r="C129" s="7" t="n">
-        <v>-0.0999</v>
+        <v>-0.0076</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>-0.061</v>
+        <v>0.0155</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>-0.4552</v>
+        <v>-0.3117</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>-0.6188</v>
+        <v>-0.3827</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>-0.669</v>
+        <v>0</v>
       </c>
       <c r="H129" s="7" t="n">
-        <v>-0.2682</v>
+        <v>1.1645</v>
       </c>
       <c r="I129" s="6" t="n">
-        <v>4.51</v>
+        <v>4.47</v>
       </c>
       <c r="J129" s="6" t="n">
-        <v>31.54</v>
+        <v>19.23</v>
       </c>
       <c r="K129" s="7" t="n">
-        <v>0.5028</v>
+        <v>0.4338</v>
       </c>
       <c r="L129" s="7" t="n">
-        <v>1.6135</v>
+        <v>0.5232</v>
       </c>
       <c r="M129" s="7" t="n">
-        <v>2.0025</v>
+        <v>0.7125</v>
       </c>
       <c r="N129" s="7" t="n">
-        <v>9.2562</v>
+        <v>0.8672</v>
       </c>
       <c r="O129" s="7" t="n">
-        <v>0.3063</v>
+        <v>0.3018</v>
       </c>
       <c r="P129" s="7" t="n">
-        <v>0.1832</v>
+        <v>0.3122</v>
       </c>
       <c r="Q129" s="5" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R129" s="5" t="inlineStr"/>
@@ -7955,31 +7958,31 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>6.96</v>
+        <v>6.53</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>-0.0238</v>
+        <v>-0.06179999999999999</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>-0.1111</v>
+        <v>-0.1755</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>-0.3434</v>
+        <v>-0.384</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>-0.4625</v>
+        <v>-0.4958</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>0.3647</v>
+        <v>0.2486</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>1.1415</v>
+        <v>0.9566</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>4.88</v>
+        <v>4.58</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>59.54</v>
+        <v>55.86</v>
       </c>
       <c r="K130" s="4" t="n">
         <v>0.4591</v>
@@ -8009,57 +8012,57 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>ASELS</t>
+          <t>FMIZP</t>
         </is>
       </c>
       <c r="B131" s="6" t="n">
-        <v>341.75</v>
+        <v>253</v>
       </c>
       <c r="C131" s="7" t="n">
-        <v>-0.027</v>
+        <v>-0.0269</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>-0.0959</v>
+        <v>-0.0766</v>
       </c>
       <c r="E131" s="7" t="n">
-        <v>-0.1424</v>
+        <v>-0.1283</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>-0.0312</v>
+        <v>-0.1283</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>-0.171</v>
+        <v>-0.1343</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>0.5590999999999999</v>
+        <v>-0.2044</v>
       </c>
       <c r="I131" s="6" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="J131" s="6" t="n">
-        <v>41.99</v>
+        <v>25.59</v>
       </c>
       <c r="K131" s="7" t="n">
-        <v>0.5623</v>
+        <v>0.2837</v>
       </c>
       <c r="L131" s="7" t="n">
-        <v>0.5598</v>
+        <v>0.7895</v>
       </c>
       <c r="M131" s="7" t="n">
-        <v>0.606</v>
+        <v>0.1712</v>
       </c>
       <c r="N131" s="7" t="n">
-        <v>1.1295</v>
+        <v>0.9815999999999999</v>
       </c>
       <c r="O131" s="7" t="n">
-        <v>0.2643</v>
+        <v>0.1378</v>
       </c>
       <c r="P131" s="7" t="n">
-        <v>0.1891</v>
+        <v>0.2179</v>
       </c>
       <c r="Q131" s="5" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R131" s="5" t="inlineStr"/>
@@ -8067,57 +8070,57 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>FMIZP</t>
+          <t>ASELS</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>260</v>
+        <v>350.75</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>-0.028</v>
+        <v>0.0263</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>-0.058</v>
+        <v>-0.0609</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>-0.1042</v>
+        <v>-0.1198</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>-0.1042</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>-0.0877</v>
+        <v>-0.1649</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>-0.1545</v>
+        <v>0.66</v>
       </c>
       <c r="I132" s="3" t="n">
         <v>5.21</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>26.3</v>
+        <v>43.09</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0.2837</v>
+        <v>0.5623</v>
       </c>
       <c r="L132" s="4" t="n">
-        <v>0.7895</v>
+        <v>0.5598</v>
       </c>
       <c r="M132" s="4" t="n">
-        <v>0.1712</v>
+        <v>0.606</v>
       </c>
       <c r="N132" s="4" t="n">
-        <v>0.9815999999999999</v>
+        <v>1.1295</v>
       </c>
       <c r="O132" s="4" t="n">
-        <v>0.1378</v>
+        <v>0.2643</v>
       </c>
       <c r="P132" s="4" t="n">
-        <v>0.2179</v>
+        <v>0.1891</v>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R132" s="2" t="inlineStr"/>
@@ -8129,28 +8132,28 @@
         </is>
       </c>
       <c r="B133" s="6" t="n">
-        <v>9.65</v>
+        <v>9.15</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>-0.0153</v>
+        <v>-0.0518</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>0.03759999999999999</v>
+        <v>-0.0108</v>
       </c>
       <c r="E133" s="7" t="n">
-        <v>-0.2956</v>
+        <v>-0.3321</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>-0.2366</v>
+        <v>-0.2761</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>0.3972</v>
+        <v>0.2603</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>0.9109</v>
+        <v>0.7178</v>
       </c>
       <c r="I133" s="6" t="n">
-        <v>6.98</v>
+        <v>6.61</v>
       </c>
       <c r="J133" s="5" t="inlineStr"/>
       <c r="K133" s="7" t="n">
@@ -8185,28 +8188,28 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>24.12</v>
+        <v>24.02</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>-0.0367</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>-0.0429</v>
+        <v>-0.026</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>-0.25</v>
+        <v>-0.2531</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>-0.3017</v>
+        <v>-0.3046</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>-0.4091</v>
+        <v>-0.4121</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>-0.2787</v>
+        <v>-0.2609</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>7</v>
+        <v>6.97</v>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="4" t="n">
@@ -8241,28 +8244,28 @@
         </is>
       </c>
       <c r="B135" s="6" t="n">
-        <v>12.5</v>
+        <v>12.96</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0368</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>0.2994</v>
+        <v>0.3846</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>-0.1097</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>-0.0566</v>
+        <v>-0.0219</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>0.6770999999999999</v>
+        <v>0.7482</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>0.5534</v>
+        <v>0.5754</v>
       </c>
       <c r="I135" s="6" t="n">
-        <v>10.15</v>
+        <v>10.52</v>
       </c>
       <c r="J135" s="5" t="inlineStr"/>
       <c r="K135" s="7" t="n">
@@ -8296,29 +8299,29 @@
           <t>MRSHL</t>
         </is>
       </c>
-      <c r="B136" s="8" t="n">
-        <v>1298</v>
+      <c r="B136" s="9" t="n">
+        <v>1276</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>-0.0248</v>
+        <v>-0.0169</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>-0.0328</v>
+        <v>-0.0185</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>-0.2162</v>
+        <v>-0.2295</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>-0.3497</v>
+        <v>-0.3607</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>-0.117</v>
+        <v>-0.155</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>-0.314</v>
+        <v>-0.3166</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>11.53</v>
+        <v>11.33</v>
       </c>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="4" t="n">
@@ -8353,28 +8356,28 @@
         </is>
       </c>
       <c r="B137" s="6" t="n">
-        <v>273.5</v>
+        <v>271.5</v>
       </c>
       <c r="C137" s="7" t="n">
-        <v>0</v>
+        <v>-0.0073</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>-0.0745</v>
+        <v>-0.0702</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>-0.2296</v>
+        <v>-0.2352</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>-0.2307</v>
+        <v>-0.2363</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>-0.341</v>
+        <v>-0.3759</v>
       </c>
       <c r="H137" s="7" t="n">
-        <v>-0.4675</v>
+        <v>-0.4644</v>
       </c>
       <c r="I137" s="6" t="n">
-        <v>11.77</v>
+        <v>11.69</v>
       </c>
       <c r="J137" s="5" t="inlineStr"/>
       <c r="K137" s="7" t="n">
@@ -8409,31 +8412,31 @@
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>41</v>
+        <v>40.2</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0195</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>-0.0116</v>
+        <v>0</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>-0.0024</v>
+        <v>-0.0219</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.111</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>-0.08810000000000001</v>
+        <v>-0.0776</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>-0.1924</v>
+        <v>-0.2325</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>12.57</v>
+        <v>12.32</v>
       </c>
       <c r="J138" s="3" t="n">
-        <v>45.21</v>
+        <v>44.33</v>
       </c>
       <c r="K138" s="4" t="n">
         <v>0.2618</v>
@@ -8467,28 +8470,28 @@
         </is>
       </c>
       <c r="B139" s="6" t="n">
-        <v>38.54</v>
+        <v>38.82</v>
       </c>
       <c r="C139" s="7" t="n">
-        <v>-0.0133</v>
+        <v>0.0073</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>-0.0418</v>
+        <v>-0.0005</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>-0.1257</v>
+        <v>-0.1193</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>-0.164</v>
+        <v>-0.1579</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>-0.0969</v>
+        <v>-0.0757</v>
       </c>
       <c r="H139" s="7" t="n">
-        <v>0.0713</v>
+        <v>0.1443</v>
       </c>
       <c r="I139" s="6" t="n">
-        <v>14.39</v>
+        <v>14.49</v>
       </c>
       <c r="J139" s="5" t="inlineStr"/>
       <c r="K139" s="7" t="n">
@@ -8523,31 +8526,31 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>105.4</v>
+        <v>103</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>-0.0232</v>
+        <v>-0.0228</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>-0.0572</v>
+        <v>-0.067</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>-0.1867</v>
+        <v>-0.2052</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>-0.1861</v>
+        <v>-0.2046</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>-0.3290999999999999</v>
+        <v>-0.3534</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>-0.3726</v>
+        <v>-0.3836</v>
       </c>
       <c r="I140" s="3" t="n">
-        <v>16.04</v>
+        <v>15.67</v>
       </c>
       <c r="J140" s="3" t="n">
-        <v>60.39</v>
+        <v>59.02</v>
       </c>
       <c r="K140" s="4" t="n">
         <v>0.3045</v>
@@ -8581,25 +8584,25 @@
         </is>
       </c>
       <c r="B141" s="6" t="n">
-        <v>82.05</v>
+        <v>77.8</v>
       </c>
       <c r="C141" s="7" t="n">
-        <v>-0.0114</v>
+        <v>-0.0518</v>
       </c>
       <c r="D141" s="7" t="n">
-        <v>-0.0168</v>
+        <v>-0.0454</v>
       </c>
       <c r="E141" s="7" t="n">
-        <v>-0.1576</v>
+        <v>-0.2012</v>
       </c>
       <c r="F141" s="7" t="n">
-        <v>0.316</v>
+        <v>0.2478</v>
       </c>
       <c r="G141" s="7" t="n">
-        <v>0.2711</v>
+        <v>0.232</v>
       </c>
       <c r="H141" s="7" t="n">
-        <v>0.0231</v>
+        <v>-0.0506</v>
       </c>
       <c r="I141" s="5" t="inlineStr"/>
       <c r="J141" s="5" t="inlineStr"/>
@@ -8650,7 +8653,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>12.10.2026 22:32</t>
+          <t>13.10.2026 20:46</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_latest.xlsx
+++ b/data/bist_screener_latest.xlsx
@@ -76,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -100,9 +100,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -470,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R141"/>
+  <dimension ref="A1:R140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -582,57 +579,55 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MERIT</t>
+          <t>RUBNS</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13.1</v>
+        <v>14.17</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-0.0106</v>
+        <v>-0.0757</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0917</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.1661</v>
+        <v>-0.5144</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-0.2665</v>
+        <v>-0.3464</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.2375</v>
+        <v>-0.5487</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.3597</v>
+        <v>-0.302</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>6.09</v>
-      </c>
+        <v>0.21</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="n">
-        <v>0.9854999999999999</v>
+        <v>0.5189</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>1.0319</v>
+        <v>0.4172999999999999</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>2.0871</v>
+        <v>2.5836</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>1.5834</v>
+        <v>0.7992</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>0.6354</v>
+        <v>0.1688</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.0454</v>
+        <v>-0.0061</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr"/>
@@ -640,57 +635,57 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>SRVGY</t>
+          <t>MERIT</t>
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>2.18</v>
+        <v>13.03</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>-0.0224</v>
+        <v>-0.0053</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>-0.0644</v>
+        <v>-0.0626</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>-0.128</v>
+        <v>-0.1882</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>-0.1835</v>
+        <v>-0.2575</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>-0.323</v>
+        <v>-0.2358</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-0.2899</v>
+        <v>-0.3475</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>2.38</v>
+        <v>6.06</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.7227</v>
+        <v>0.9854999999999999</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>2.5294</v>
+        <v>1.0319</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>2.9903</v>
+        <v>2.0871</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>0.3421</v>
+        <v>1.5834</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>0.6722</v>
+        <v>0.6354</v>
       </c>
       <c r="P3" s="7" t="n">
-        <v>0.1107</v>
+        <v>0.0454</v>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr"/>
@@ -698,55 +693,57 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RUBNS</t>
+          <t>SRVGY</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>15.33</v>
+        <v>2.13</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0229</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0533</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.4768</v>
+        <v>-0.1341</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.2903</v>
+        <v>-0.2198</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.3344</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.2623</v>
+        <v>-0.3195</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
+        <v>0.22</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>2.32</v>
+      </c>
       <c r="K4" s="4" t="n">
-        <v>0.5189</v>
+        <v>2.7227</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.4172999999999999</v>
+        <v>2.5294</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>2.5836</v>
+        <v>2.9903</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.7992</v>
+        <v>0.3421</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.1688</v>
+        <v>0.6722</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>-0.0061</v>
+        <v>0.1107</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr"/>
@@ -758,31 +755,31 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>-0.025</v>
+        <v>-0.0256</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-0.0488</v>
+        <v>-0.0675</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-0.2</v>
+        <v>-0.2362</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>-0.2427</v>
+        <v>-0.2657</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-0.2941</v>
+        <v>-0.3059</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>-0.393</v>
+        <v>-0.4109</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0.23</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>8.73</v>
+        <v>8.51</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>0.2518</v>
@@ -816,31 +813,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>4.21</v>
+        <v>4.11</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.0145</v>
+        <v>-0.0238</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0071</v>
+        <v>-0.0238</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.0788</v>
+        <v>-0.07429999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2535</v>
+        <v>-0.2687</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.2716</v>
+        <v>-0.2852</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1534</v>
+        <v>0.1138</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0.24</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>1.7259</v>
@@ -870,57 +867,55 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>AKFGY</t>
+          <t>SNICA</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2.49</v>
+        <v>2.16</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>0.0163</v>
+        <v>-0.0226</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-0.0311</v>
+        <v>-0.0649</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-0.1531</v>
+        <v>-0.3143</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>-0.09119999999999999</v>
+        <v>-0.468</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-0.117</v>
+        <v>-0.4719</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>-0.0197</v>
+        <v>-0.574</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0.25</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>5.85</v>
-      </c>
+      <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="7" t="n">
-        <v>0.3848</v>
+        <v>0.2451</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.3326</v>
+        <v>0.1328</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.3901</v>
+        <v>0.7476999999999999</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>0.3812</v>
+        <v>0.4518</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>0.8458</v>
+        <v>0.0576</v>
       </c>
       <c r="P7" s="7" t="n">
-        <v>0.0496</v>
+        <v>-0.1748</v>
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr"/>
@@ -928,55 +923,57 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SNICA</t>
+          <t>AKFGY</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>2.21</v>
+        <v>2.49</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.0178</v>
+        <v>0</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.0391</v>
+        <v>-0.008</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.3072</v>
+        <v>-0.1324</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.4557</v>
+        <v>-0.1043</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.4597</v>
+        <v>-0.1107</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.5846</v>
+        <v>-0.0197</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J8" s="3" t="n">
+        <v>5.85</v>
+      </c>
       <c r="K8" s="4" t="n">
-        <v>0.2451</v>
+        <v>0.3848</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1328</v>
+        <v>0.3326</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.7476999999999999</v>
+        <v>0.3901</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4518</v>
+        <v>0.3812</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.0576</v>
+        <v>0.8458</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1748</v>
+        <v>0.0496</v>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr"/>
@@ -988,28 +985,28 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>10.1</v>
+        <v>9.94</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0158</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-0.0326</v>
+        <v>-0.0451</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-0.1842</v>
+        <v>-0.1778</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.1227</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-0.2372</v>
+        <v>-0.2301</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-0.2882</v>
+        <v>-0.3373</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="J9" s="5" t="inlineStr"/>
       <c r="K9" s="7" t="n">
@@ -1044,31 +1041,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.029</v>
+        <v>-0.0258</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.0509</v>
+        <v>-0.05309999999999999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2043</v>
+        <v>-0.2059</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1401</v>
+        <v>-0.1839</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2283</v>
+        <v>-0.2361</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2469</v>
+        <v>-0.2781</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.55</v>
+        <v>11.25</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0.3203</v>
@@ -1102,25 +1099,25 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>6.63</v>
+        <v>6.57</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>-0.0178</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.0015</v>
+        <v>0.0123</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-0.1242</v>
+        <v>-0.1555</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>-0.09300000000000001</v>
+        <v>-0.1275</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-0.1954</v>
+        <v>-0.2132</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-0.1242</v>
+        <v>-0.1181</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0.26</v>
@@ -1158,31 +1155,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.0163</v>
+        <v>-0.0046</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.066</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.0704</v>
+        <v>-0.06059999999999999</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1679</v>
+        <v>-0.1933</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1349</v>
+        <v>-0.1303</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.0046</v>
+        <v>0.0046</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0.27</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>15.62</v>
+        <v>15.55</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0.1479</v>
@@ -1216,28 +1213,28 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>14</v>
+        <v>13.45</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>0.0072</v>
+        <v>-0.0393</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>-0.0547</v>
+        <v>-0.08439999999999999</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>-0.3177</v>
+        <v>-0.3361</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>-0.3346</v>
+        <v>-0.365</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-0.4677</v>
+        <v>-0.4855</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.6481999999999999</v>
+        <v>-0.6629</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
       <c r="K13" s="7" t="n">
@@ -1268,57 +1265,57 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BESLR</t>
+          <t>MHRGY</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>11.01</v>
+        <v>1.87</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.0134</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.0036</v>
+        <v>0.0389</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1659</v>
+        <v>-0.187</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.1472</v>
+        <v>-0.223</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1964</v>
+        <v>-0.2599</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1844</v>
+        <v>-0.2638</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>5.87</v>
+        <v>8.82</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.3789</v>
+        <v>0.9460999999999999</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3175</v>
+        <v>0.9873000000000001</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.3702</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.5778</v>
+        <v>2464.8944</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.1173</v>
+        <v>0.8395999999999999</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0472</v>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr"/>
@@ -1326,55 +1323,57 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>KRTEK</t>
+          <t>BESLR</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>5.82</v>
+        <v>10.82</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>-0.0169</v>
+        <v>-0.0173</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>-0.0284</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-0.0218</v>
+        <v>-0.1658</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>-0.08529999999999999</v>
+        <v>-0.1683</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-0.2103</v>
+        <v>-0.2044</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.3815999999999999</v>
+        <v>-0.1852</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr"/>
+        <v>0.36</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>5.77</v>
+      </c>
       <c r="K15" s="7" t="n">
-        <v>0.1651</v>
+        <v>0.3789</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.5547</v>
+        <v>0.3175</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>3.1915</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="N15" s="7" t="n">
-        <v>0.7</v>
+        <v>0.5778</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>0.0396</v>
+        <v>0.1173</v>
       </c>
       <c r="P15" s="7" t="n">
-        <v>-0.0461</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R15" s="5" t="inlineStr"/>
@@ -1382,57 +1381,55 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RGYAS</t>
+          <t>KRTEK</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>193.6</v>
+        <v>5.72</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.0016</v>
+        <v>-0.0172</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.0222</v>
+        <v>-0.09210000000000002</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.0344</v>
+        <v>-0.0138</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.0202</v>
+        <v>-0.1059</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.0442</v>
+        <v>-0.198</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2821</v>
+        <v>-0.4166</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>3.22</v>
-      </c>
+        <v>0.37</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="4" t="n">
-        <v>0.5672999999999999</v>
+        <v>0.1651</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5787</v>
+        <v>0.5547</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5573</v>
+        <v>3.1915</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>8.1502</v>
+        <v>0.7</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.6512</v>
+        <v>0.0396</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1467</v>
+        <v>-0.0461</v>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr"/>
@@ -1440,53 +1437,53 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>MHRGY</t>
+          <t>RGYAS</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>2.07</v>
+        <v>193.6</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>0.0455</v>
+        <v>0</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.15</v>
+        <v>0.0184</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>-0.08</v>
+        <v>-0.0383</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>-0.1179</v>
+        <v>-0.0232</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>-0.1935</v>
+        <v>0.0516</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-0.2018</v>
+        <v>0.2959</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>9.76</v>
+        <v>3.22</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.9460999999999999</v>
+        <v>0.5672999999999999</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.9873000000000001</v>
+        <v>0.5787</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.3702</v>
+        <v>0.5573</v>
       </c>
       <c r="N17" s="7" t="n">
-        <v>2464.8944</v>
+        <v>8.1502</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>0.8395999999999999</v>
+        <v>0.6512</v>
       </c>
       <c r="P17" s="7" t="n">
-        <v>0.0472</v>
+        <v>0.1467</v>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
@@ -1502,31 +1499,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>37.88</v>
+        <v>37.42</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.0074</v>
+        <v>-0.0121</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.0042</v>
+        <v>-0.0178</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1395</v>
+        <v>-0.1591</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1191</v>
+        <v>-0.1417</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2203</v>
+        <v>-0.2025</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0916</v>
+        <v>0.0809</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>9.52</v>
+        <v>9.4</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>0.2329</v>
@@ -1556,57 +1553,55 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>YYLGD</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>7.46</v>
+        <v>1.74</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>0</v>
+        <v>-0.05429999999999999</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>-0.0171</v>
+        <v>-0.1212</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>-0.2614</v>
+        <v>-0.4238</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>-0.2995</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>-0.385</v>
+        <v>-0.5787</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-0.2636</v>
+        <v>-0.8088</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>3.31</v>
-      </c>
+        <v>0.43</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="7" t="n">
-        <v>0.9081</v>
+        <v>0.2334</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>1.1391</v>
+        <v>0.1468</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>1.4414</v>
+        <v>0.1104</v>
       </c>
       <c r="N19" s="7" t="n">
-        <v>0.9061</v>
+        <v>0.4322</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>0.0974</v>
+        <v>0.1786</v>
       </c>
       <c r="P19" s="7" t="n">
-        <v>0.1661</v>
+        <v>-0.1088</v>
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R19" s="5" t="inlineStr"/>
@@ -1614,55 +1609,57 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>YYLGD</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.95</v>
+        <v>7.34</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.0051</v>
+        <v>-0.0161</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.0152</v>
+        <v>-0.0174</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.5</v>
+        <v>-0.2689</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6518</v>
+        <v>-0.3121</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.7068000000000001</v>
+        <v>-0.3842</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.5278</v>
+        <v>-0.2631</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr"/>
+        <v>0.44</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>3.26</v>
+      </c>
       <c r="K20" s="4" t="n">
-        <v>0.1726</v>
+        <v>0.9081</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3081</v>
+        <v>1.1391</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1357</v>
+        <v>1.4414</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.2328</v>
+        <v>0.9061</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.0837</v>
+        <v>0.0974</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.0244</v>
+        <v>0.1661</v>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr"/>
@@ -1670,51 +1667,51 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0.005500000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>-0.098</v>
+        <v>-0.0103</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-0.4084</v>
+        <v>-0.5064</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>-0.4817</v>
+        <v>-0.6566</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-0.5245000000000001</v>
+        <v>-0.7084999999999999</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-0.8111</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0.45</v>
       </c>
       <c r="J21" s="5" t="inlineStr"/>
       <c r="K21" s="7" t="n">
-        <v>0.2334</v>
+        <v>0.1726</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.1468</v>
+        <v>0.3081</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.1104</v>
+        <v>0.1357</v>
       </c>
       <c r="N21" s="7" t="n">
-        <v>0.4322</v>
+        <v>0.2328</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>0.1786</v>
+        <v>0.0837</v>
       </c>
       <c r="P21" s="7" t="n">
-        <v>-0.1088</v>
+        <v>-0.0244</v>
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
@@ -1730,31 +1727,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>18.41</v>
+        <v>18.08</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.0118</v>
+        <v>-0.0179</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.0446</v>
+        <v>-0.0393</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1493</v>
+        <v>-0.1737</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1258</v>
+        <v>-0.1512</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1555</v>
+        <v>-0.1637</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.049</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>7.44</v>
+        <v>7.3</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>0.1285</v>
@@ -1784,55 +1781,57 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TRILC</t>
+          <t>KIMMR</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.9</v>
+        <v>10.53</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>-0.011</v>
+        <v>-0.0223</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.07139999999999999</v>
+        <v>-0.0366</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>-0.1667</v>
+        <v>-0.1888</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>-0.404</v>
+        <v>-0.3095</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-0.6591</v>
+        <v>-0.3751</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-0.7383</v>
+        <v>-0.2505</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="J23" s="5" t="inlineStr"/>
+        <v>0.48</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>3.96</v>
+      </c>
       <c r="K23" s="7" t="n">
-        <v>0.8809</v>
+        <v>0.4985</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>1.1988</v>
+        <v>0.2399</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>1.821</v>
+        <v>0.6479</v>
       </c>
       <c r="N23" s="7" t="n">
-        <v>0.7378</v>
+        <v>1.3415</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>0.249</v>
+        <v>0.0858</v>
       </c>
       <c r="P23" s="7" t="n">
-        <v>-0.0291</v>
+        <v>0.1449</v>
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R23" s="5" t="inlineStr"/>
@@ -1840,57 +1839,55 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>KIMMR</t>
+          <t>ERBOS</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>10.77</v>
+        <v>108.5</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.0037</v>
+        <v>-0.0364</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.0227</v>
+        <v>-0.0742</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.1753</v>
+        <v>-0.2649</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.2844</v>
+        <v>-0.3344</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3771</v>
+        <v>-0.4623</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2723</v>
+        <v>-0.3904</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>4.05</v>
-      </c>
+        <v>0.55</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="4" t="n">
-        <v>0.4985</v>
+        <v>0.2349</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.2399</v>
+        <v>1.1405</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.6479</v>
+        <v>1.0386</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.3415</v>
+        <v>0.7831999999999999</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.0858</v>
+        <v>0.131</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.1449</v>
+        <v>-0.023</v>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr"/>
@@ -1902,31 +1899,31 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>6.1</v>
+        <v>5.99</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>-0.0113</v>
+        <v>-0.018</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>-0.05860000000000001</v>
+        <v>-0.067</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-0.1921</v>
+        <v>-0.2118</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>-0.3237</v>
+        <v>-0.3359</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>-0.298</v>
+        <v>-0.3255</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-0.1963</v>
+        <v>-0.2149</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>7.32</v>
+        <v>7.19</v>
       </c>
       <c r="K25" s="7" t="n">
         <v>0.6883</v>
@@ -1956,55 +1953,57 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ERBOS</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>112.6</v>
+        <v>32.36</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.0209</v>
+        <v>-0.0212</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.0474</v>
+        <v>0.0112</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2418</v>
+        <v>-0.0538</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3084</v>
+        <v>-0.0134</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4445</v>
+        <v>0.0466</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.383</v>
+        <v>0.2821</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
+        <v>0.59</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>17.69</v>
+      </c>
       <c r="K26" s="4" t="n">
-        <v>0.2349</v>
+        <v>0.3105</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.1405</v>
+        <v>0.3107</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.0386</v>
+        <v>0.4787</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.7831999999999999</v>
+        <v>1.4985</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.131</v>
+        <v>0.0693</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.023</v>
+        <v>-0.0718</v>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr"/>
@@ -2016,31 +2015,31 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>26.54</v>
+        <v>26.48</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>-0.004500000000000001</v>
+        <v>-0.0023</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>-0.046</v>
+        <v>-0.04269999999999999</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-0.2148</v>
+        <v>-0.2086</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>-0.3388</v>
+        <v>-0.3231</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>-0.5218</v>
+        <v>-0.5132</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>-0.4482</v>
+        <v>-0.4563</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="K27" s="7" t="n">
         <v>0.045</v>
@@ -2070,57 +2069,55 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>KORDS</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>33.06</v>
+        <v>2.85</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.0328</v>
+        <v>-0.0206</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.0267</v>
+        <v>-0.0563</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.0271</v>
+        <v>-0.2928</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.0024</v>
+        <v>-0.312</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.0495</v>
+        <v>-0.1585</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.3277</v>
+        <v>-0.0182</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.61</v>
       </c>
-      <c r="J28" s="3" t="n">
-        <v>18.07</v>
-      </c>
+      <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="4" t="n">
-        <v>0.3105</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.3107</v>
+        <v>0.3224</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.4787</v>
+        <v>0.613</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.4985</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.0693</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.0718</v>
+        <v>-0.09820000000000001</v>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr"/>
@@ -2128,55 +2125,57 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>KORDS</t>
+          <t>KRSTL</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>2.91</v>
+        <v>7.22</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>-0.0268</v>
+        <v>-0.0386</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>-0.0703</v>
+        <v>-0.0562</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-0.2857</v>
+        <v>-0.1739</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>-0.2984</v>
+        <v>-0.2935</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>-0.1189</v>
+        <v>-0.2169</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>-0.0118</v>
+        <v>-0.3058</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="J29" s="5" t="inlineStr"/>
+        <v>0.61</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>4.15</v>
+      </c>
       <c r="K29" s="7" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.3806</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.3224</v>
+        <v>0.2571</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.613</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="N29" s="7" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.6774</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.1192</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>-0.09820000000000001</v>
+        <v>0.1788</v>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R29" s="5" t="inlineStr"/>
@@ -2188,28 +2187,28 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>7.67</v>
+        <v>7.47</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.0167</v>
+        <v>-0.0261</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.0757</v>
+        <v>0.06709999999999999</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3194</v>
+        <v>-0.333</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5407</v>
+        <v>-0.5803</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5727</v>
+        <v>-0.5817</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3388</v>
+        <v>-0.3555</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="4" t="n">
@@ -2240,57 +2239,55 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>KRSTL</t>
+          <t>BAKAB</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>7.51</v>
+        <v>28.58</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>-0.0196</v>
+        <v>-0.0305</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>-0.0359</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-0.1495</v>
+        <v>-0.2443</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>-0.2594</v>
+        <v>-0.4461</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>-0.2002</v>
+        <v>-0.3655</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>-0.28</v>
+        <v>-0.2276</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>4.32</v>
-      </c>
+        <v>0.62</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="7" t="n">
-        <v>0.3806</v>
+        <v>0.3479</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.2571</v>
+        <v>0.5443</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.5529999999999999</v>
+        <v>0.7171</v>
       </c>
       <c r="N31" s="7" t="n">
-        <v>0.6774</v>
+        <v>0.97</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>0.1192</v>
+        <v>0.0552</v>
       </c>
       <c r="P31" s="7" t="n">
-        <v>0.1788</v>
+        <v>-0.0031</v>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R31" s="5" t="inlineStr"/>
@@ -2298,55 +2295,57 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>BAKAB</t>
+          <t>OSMEN</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>29.48</v>
+        <v>5.25</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.0283</v>
+        <v>-0.0187</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.099</v>
+        <v>-0.0558</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2291</v>
+        <v>-0.2402</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.418</v>
+        <v>-0.3598</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3597</v>
+        <v>-0.3278</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2242</v>
+        <v>-0.4074</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr"/>
+        <v>0.65</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>9.01</v>
+      </c>
       <c r="K32" s="4" t="n">
-        <v>0.3479</v>
+        <v>1.6512</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.5443</v>
+        <v>0.1052</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.7171</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.97</v>
+        <v>5.9134</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.0552</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.0031</v>
+        <v>0.0863</v>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr"/>
@@ -2358,25 +2357,25 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>14.98</v>
+        <v>15.05</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>-0.0254</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>-0.073</v>
+        <v>-0.0505</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-0.3587</v>
+        <v>-0.3524</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>-0.3532</v>
+        <v>-0.3546</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>-0.3881</v>
+        <v>-0.3745000000000001</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>-0.3706</v>
+        <v>-0.3781</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0.65</v>
@@ -2410,53 +2409,53 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>OSMEN</t>
+          <t>SEKFK</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>5.35</v>
+        <v>3.97</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.0325</v>
+        <v>-0.0341</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.0152</v>
+        <v>-0.0746</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2422</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3515</v>
+        <v>-0.2896</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.307</v>
+        <v>-0.3391</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.392</v>
+        <v>-0.1152</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>9.18</v>
+        <v>3.22</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1.6512</v>
+        <v>0.208</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.1052</v>
+        <v>0.0571</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.04969999999999999</v>
+        <v>0.0025</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.9134</v>
+        <v>0.2707</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.6072</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.0863</v>
+        <v>0.2346</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
@@ -2468,57 +2467,57 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>SEKFK</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>4.11</v>
+        <v>211.2</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>-0.0191</v>
+        <v>-0.0061</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>-0.0486</v>
+        <v>-0.0112</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-0.0659</v>
+        <v>-0.0559</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>-0.2638</v>
+        <v>0.1052</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>-0.322</v>
+        <v>0.0353</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>-0.094</v>
+        <v>0.32</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0.68</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>3.33</v>
+        <v>15.05</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.208</v>
+        <v>0.3261</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.0571</v>
+        <v>0.5440999999999999</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.0025</v>
+        <v>0.9423</v>
       </c>
       <c r="N35" s="7" t="n">
-        <v>0.2707</v>
+        <v>5.083299999999999</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>0.6072</v>
+        <v>0.0646</v>
       </c>
       <c r="P35" s="7" t="n">
-        <v>0.2346</v>
+        <v>0.0771</v>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="R35" s="5" t="inlineStr"/>
@@ -2526,57 +2525,57 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>PNLSN</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>212.5</v>
+        <v>31.8</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.0271</v>
+        <v>-0.0209</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>-0.0116</v>
+        <v>-0.0603</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>-0.0556</v>
+        <v>-0.224</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.1126</v>
+        <v>-0.3288</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.0167</v>
+        <v>-0.3017</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.3085</v>
+        <v>-0.2006</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.68</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>15.14</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0.3261</v>
+        <v>0.306</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.5440999999999999</v>
+        <v>0.6481</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.9423</v>
+        <v>0.5497</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>5.083299999999999</v>
+        <v>7.793600000000001</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>0.0646</v>
+        <v>0.1302</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>0.0771</v>
+        <v>0.08839999999999999</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr"/>
@@ -2584,57 +2583,57 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TTKOM</t>
+          <t>AKMGY</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>52.25</v>
+        <v>205</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>0.0077</v>
+        <v>-0.0144</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>-0.027</v>
+        <v>-0.0348</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-0.05599999999999999</v>
+        <v>-0.148</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>-0.09449999999999999</v>
+        <v>-0.1605</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>-0.1739</v>
+        <v>-0.3068</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0.0146</v>
+        <v>-0.1202</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>6.46</v>
+        <v>10.1</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.4498</v>
+        <v>0.3886</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>0.4329</v>
+        <v>0.3887</v>
       </c>
       <c r="M37" s="7" t="n">
-        <v>0.5323</v>
+        <v>0.3141</v>
       </c>
       <c r="N37" s="7" t="n">
-        <v>0.8047</v>
+        <v>0.5958</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>0.4117</v>
+        <v>0.6443000000000001</v>
       </c>
       <c r="P37" s="7" t="n">
-        <v>1.3041</v>
+        <v>0.0781</v>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R37" s="5" t="inlineStr"/>
@@ -2642,57 +2641,57 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>PNLSN</t>
+          <t>MERCN</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>32.48</v>
+        <v>10.3</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>-0.0122</v>
+        <v>-0.031</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>-0.0441</v>
+        <v>-0.0636</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>-0.2031</v>
+        <v>-0.4568</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-0.2801</v>
+        <v>-0.584</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.2756</v>
+        <v>-0.4787</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.202</v>
+        <v>-0.6513</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>9.16</v>
+        <v>11.83</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.306</v>
+        <v>0.2374</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.6481</v>
+        <v>0.8593999999999999</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.5497</v>
+        <v>1.4059</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>7.793600000000001</v>
+        <v>1.3031</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0.1302</v>
+        <v>0.1784</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0.08839999999999999</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr"/>
@@ -2700,57 +2699,57 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>AKMGY</t>
+          <t>BNTAS</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>208</v>
+        <v>5.17</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>-0.0119</v>
+        <v>-0.0134</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>-0.0415</v>
+        <v>-0.0701</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-0.1713</v>
+        <v>-0.1754</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>-0.1613</v>
+        <v>-0.1426</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>-0.2997</v>
+        <v>-0.2249</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>-0.07139999999999999</v>
+        <v>-0.2496</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>10.25</v>
+        <v>4.79</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.3886</v>
+        <v>0.2654</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>0.3887</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="M39" s="7" t="n">
-        <v>0.3141</v>
+        <v>0.464</v>
       </c>
       <c r="N39" s="7" t="n">
-        <v>0.5958</v>
+        <v>0.3679</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>0.6443000000000001</v>
+        <v>0.1363</v>
       </c>
       <c r="P39" s="7" t="n">
-        <v>0.0781</v>
+        <v>0.1657</v>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R39" s="5" t="inlineStr"/>
@@ -2758,57 +2757,57 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>BNTAS</t>
+          <t>TTKOM</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>5.24</v>
+        <v>52.5</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.0048</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>-0.0626</v>
+        <v>-0.0113</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>-0.1748</v>
+        <v>-0.1117</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>-0.1267</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-0.2249</v>
+        <v>-0.166</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.1975</v>
+        <v>0.0304</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>4.85</v>
+        <v>6.49</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.2654</v>
+        <v>0.4498</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.4329</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.464</v>
+        <v>0.5323</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.3679</v>
+        <v>0.8047</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.1363</v>
+        <v>0.4117</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0.1657</v>
+        <v>1.3041</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr"/>
@@ -2816,57 +2815,57 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TUREX</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>5.85</v>
+        <v>98.3</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>0.0104</v>
+        <v>-0.0116</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0.0017</v>
+        <v>-0.0229</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-0.0472</v>
+        <v>-0.0447</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>-0.1397</v>
+        <v>-0.108</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>-0.3641</v>
+        <v>-0.1634</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>-0.2751</v>
+        <v>0.0036</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>11</v>
+        <v>11.04</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.4159</v>
+        <v>0.3971</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>1.3967</v>
+        <v>0.4118</v>
       </c>
       <c r="M41" s="7" t="n">
-        <v>0.8518000000000001</v>
+        <v>0.3975</v>
       </c>
       <c r="N41" s="7" t="n">
-        <v>0.3205</v>
+        <v>0.2377</v>
       </c>
       <c r="O41" s="7" t="n">
-        <v>0.2638</v>
+        <v>0.4333</v>
       </c>
       <c r="P41" s="7" t="n">
-        <v>0.0862</v>
+        <v>0.1518</v>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R41" s="5" t="inlineStr"/>
@@ -2874,57 +2873,57 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>TUREX</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>99.45</v>
+        <v>5.86</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.0226</v>
+        <v>0.0017</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>-0.0104</v>
+        <v>0.0138</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-0.0202</v>
+        <v>-0.0266</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-0.0876</v>
+        <v>-0.1445</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-0.1572</v>
+        <v>-0.3326</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.004500000000000001</v>
+        <v>-0.262</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>0.71</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>11.17</v>
+        <v>11.02</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0.3971</v>
+        <v>0.4159</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.4118</v>
+        <v>1.3967</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.3975</v>
+        <v>0.8518000000000001</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.2377</v>
+        <v>0.3205</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>0.4333</v>
+        <v>0.2638</v>
       </c>
       <c r="P42" s="4" t="n">
-        <v>0.1518</v>
+        <v>0.0862</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr"/>
@@ -2932,57 +2931,57 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>MERCN</t>
+          <t>AYGAZ</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>10.63</v>
+        <v>291.5</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>-0.0266</v>
+        <v>0.0255</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-0.4309000000000001</v>
+        <v>-0.1126</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>-0.5615</v>
+        <v>0.1721</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>-0.3943</v>
+        <v>0.0052</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>-0.636</v>
+        <v>0.5757</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>12.21</v>
+        <v>7.66</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.2374</v>
+        <v>0.1662</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>0.8593999999999999</v>
+        <v>0.3683</v>
       </c>
       <c r="M43" s="7" t="n">
-        <v>1.4059</v>
+        <v>0.4549</v>
       </c>
       <c r="N43" s="7" t="n">
-        <v>1.3031</v>
+        <v>1.9624</v>
       </c>
       <c r="O43" s="7" t="n">
-        <v>0.1784</v>
+        <v>0.0302</v>
       </c>
       <c r="P43" s="7" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.118</v>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R43" s="5" t="inlineStr"/>
@@ -2990,57 +2989,57 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>AYGAZ</t>
+          <t>PINSU</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>294</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.0191</v>
+        <v>-0.0265</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0474</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>-0.1091</v>
+        <v>-0.1732</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.1937</v>
+        <v>-0.1952</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>0.0182</v>
+        <v>-0.3267</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.5722</v>
+        <v>-0.352</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>0.77</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>7.73</v>
+        <v>17.81</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0.1662</v>
+        <v>0.2802</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.3683</v>
+        <v>0.2234</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.4549</v>
+        <v>0.3074</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>1.9624</v>
+        <v>91.6451</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>0.0302</v>
+        <v>0.1329</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>0.118</v>
+        <v>0.0528</v>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr"/>
@@ -3048,57 +3047,57 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>BASGZ</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>37.26</v>
+        <v>39.76</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>-0.009000000000000001</v>
+        <v>-0.008</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>-0.0106</v>
+        <v>-0.0173</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-0.0446</v>
+        <v>-0.1184</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>-0.08810000000000001</v>
+        <v>-0.1438</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0.1702</v>
+        <v>-0.2088</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>0.3549</v>
+        <v>0.0247</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>32.48</v>
+        <v>7.2</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.1998</v>
+        <v>0.3163</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>0.3838</v>
+        <v>0.5275</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>0.4877</v>
+        <v>0.4513</v>
       </c>
       <c r="N45" s="7" t="n">
-        <v>0.4752</v>
+        <v>0.3789</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>0.104</v>
+        <v>0.1301</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>0.0274</v>
+        <v>-0.245</v>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R45" s="5" t="inlineStr"/>
@@ -3106,57 +3105,57 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>BASGZ</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>40.08</v>
+        <v>37.1</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.005</v>
+        <v>-0.0043</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>-0.0133</v>
+        <v>0</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>-0.1172</v>
+        <v>-0.0512</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-0.1347</v>
+        <v>-0.1233</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-0.2126</v>
+        <v>0.1983</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.033</v>
+        <v>0.357</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>7.26</v>
+        <v>32.34</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0.3163</v>
+        <v>0.1998</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.5275</v>
+        <v>0.3838</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.4513</v>
+        <v>0.4877</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.3789</v>
+        <v>0.4752</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0.1301</v>
+        <v>0.104</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>-0.245</v>
+        <v>0.0274</v>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr"/>
@@ -3164,57 +3163,57 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>PINSU</t>
+          <t>ISFIN</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>8.68</v>
+        <v>16</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>-0.0023</v>
+        <v>-0.0309</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>-0.0247</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-0.1589</v>
+        <v>-0.1667</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>-0.1694</v>
+        <v>-0.1799</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>-0.3122</v>
+        <v>-0.2218</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>-0.2386</v>
+        <v>-0.0703</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0.8</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>18.3</v>
+        <v>2.72</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.2802</v>
+        <v>0.5749</v>
       </c>
       <c r="L47" s="7" t="n">
-        <v>0.2234</v>
+        <v>0.5787</v>
       </c>
       <c r="M47" s="7" t="n">
-        <v>0.3074</v>
+        <v>0.5648</v>
       </c>
       <c r="N47" s="7" t="n">
-        <v>91.6451</v>
+        <v>0.6275999999999999</v>
       </c>
       <c r="O47" s="7" t="n">
-        <v>0.1329</v>
+        <v>0.9556</v>
       </c>
       <c r="P47" s="7" t="n">
-        <v>0.0528</v>
+        <v>0.3468</v>
       </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R47" s="5" t="inlineStr"/>
@@ -3222,57 +3221,57 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ISFIN</t>
+          <t>DESA</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>16.51</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>-0.0155</v>
+        <v>-0.0436</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>-0.044</v>
+        <v>-0.0825</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>-0.141</v>
+        <v>-0.1697</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-0.1472</v>
+        <v>-0.2289</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-0.1923</v>
+        <v>-0.4558</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>-0.0213</v>
+        <v>-0.4583</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.81</v>
+        <v>7.69</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0.5749</v>
+        <v>0.2088</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.5787</v>
+        <v>0.2301</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.5648</v>
+        <v>0.0037</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.6275999999999999</v>
+        <v>0.3571</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>0.9556</v>
+        <v>0.2399</v>
       </c>
       <c r="P48" s="4" t="n">
-        <v>0.3468</v>
+        <v>0.1277</v>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr"/>
@@ -3284,31 +3283,31 @@
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>7.24</v>
+        <v>7.2</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>-0.0014</v>
+        <v>-0.005500000000000001</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>-0.095</v>
+        <v>-0.1262</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>-0.1609</v>
+        <v>-0.1429</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>-0.2363</v>
+        <v>-0.2308</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>-0.2482</v>
+        <v>-0.25</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0.5323</v>
+        <v>0.5094</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0.86</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="K49" s="7" t="n">
         <v>0.4183</v>
@@ -3336,57 +3335,57 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>DESA</t>
+          <t>EGGUB</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>8.49</v>
+        <v>91.55</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>-0.0012</v>
+        <v>-0.0224</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.0608</v>
+        <v>-0.09</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>-0.1328</v>
+        <v>-0.1752</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>-0.1899</v>
+        <v>-0.05860000000000001</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.3825</v>
+        <v>-0.2859</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>-0.434</v>
+        <v>-0.1256</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>8.039999999999999</v>
+        <v>12.81</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0.2088</v>
+        <v>0.4926</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.2301</v>
+        <v>0.6905</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.0037</v>
+        <v>0.7726999999999999</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.3571</v>
+        <v>0.5777</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>0.2399</v>
+        <v>0.4324</v>
       </c>
       <c r="P50" s="4" t="n">
-        <v>0.1277</v>
+        <v>0.0886</v>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr"/>
@@ -3394,57 +3393,57 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>EGGUB</t>
+          <t>KARSN</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>93.65000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>0.0124</v>
+        <v>-0.0444</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>-0.0709</v>
+        <v>-0.0688</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-0.1661</v>
+        <v>-0.3729</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>-0.0178</v>
+        <v>-0.2267</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>-0.238</v>
+        <v>-0.1964</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>-0.1447</v>
+        <v>-0.1799</v>
       </c>
       <c r="I51" s="6" t="n">
         <v>0.92</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>13.1</v>
+        <v>31.22</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.4926</v>
+        <v>0.8458</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>0.6905</v>
+        <v>1.2698</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>0.7726999999999999</v>
+        <v>1.2002</v>
       </c>
       <c r="N51" s="7" t="n">
-        <v>0.5777</v>
+        <v>2.1122</v>
       </c>
       <c r="O51" s="7" t="n">
-        <v>0.4324</v>
+        <v>0.1667</v>
       </c>
       <c r="P51" s="7" t="n">
-        <v>0.0886</v>
+        <v>0.07339999999999999</v>
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R51" s="5" t="inlineStr"/>
@@ -3452,57 +3451,57 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ZRGYO</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>19</v>
+        <v>484.75</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0</v>
+        <v>-0.0251</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.0005</v>
+        <v>-0.0532</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.1097</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.09380000000000001</v>
+        <v>-0.204</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.1171</v>
+        <v>-0.2666</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>-0.1789</v>
+        <v>0.07719999999999999</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>14.38</v>
+        <v>14.52</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>2.3363</v>
+        <v>0.3804</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>3.5944</v>
+        <v>0.3113</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>3.6478</v>
+        <v>1.725</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.2899</v>
+        <v>0.0848</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>0.5917</v>
+        <v>0.0184</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>0.0776</v>
+        <v>0.1216</v>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr"/>
@@ -3510,57 +3509,57 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>ZRGYO</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>497.5</v>
+        <v>19</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>-0.0075</v>
+        <v>0</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>-0.0391</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-0.0834</v>
+        <v>-0.049</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>-0.2044</v>
+        <v>0.09759999999999999</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>-0.2449</v>
+        <v>-0.1038</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>0.1174</v>
+        <v>-0.1457</v>
       </c>
       <c r="I53" s="6" t="n">
         <v>0.95</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>14.89</v>
+        <v>14.38</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>0.3804</v>
+        <v>2.3363</v>
       </c>
       <c r="L53" s="7" t="n">
-        <v>0.3113</v>
+        <v>3.5944</v>
       </c>
       <c r="M53" s="7" t="n">
-        <v>1.725</v>
+        <v>3.6478</v>
       </c>
       <c r="N53" s="7" t="n">
-        <v>0.0848</v>
+        <v>0.2899</v>
       </c>
       <c r="O53" s="7" t="n">
-        <v>0.0184</v>
+        <v>0.5917</v>
       </c>
       <c r="P53" s="7" t="n">
-        <v>0.1216</v>
+        <v>0.0776</v>
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R53" s="5" t="inlineStr"/>
@@ -3568,57 +3567,57 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>KARSN</t>
+          <t>ARASE</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>-0.0034</v>
+        <v>-0.0073</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>-0.0394</v>
+        <v>-0.0175</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>-0.4663</v>
+        <v>-0.2156</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>-0.1989</v>
+        <v>-0.2296</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-0.184</v>
+        <v>-0.062</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>-0.1558</v>
+        <v>0.8015000000000001</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>32.68</v>
+        <v>8.69</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0.8458</v>
+        <v>0.1264</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>1.2698</v>
+        <v>0.596</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>1.2002</v>
+        <v>0.7123999999999999</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>2.1122</v>
+        <v>4.0303</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>0.1667</v>
+        <v>0.25</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>0.07339999999999999</v>
+        <v>0.1463</v>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr"/>
@@ -3626,57 +3625,57 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>ARASE</t>
+          <t>GESAN</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>96</v>
+        <v>36.8</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>0.0031</v>
+        <v>-0.05980000000000001</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>-0.0395</v>
+        <v>-0.1238</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-0.2201</v>
+        <v>-0.3932</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>-0.2092</v>
+        <v>-0.5448</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.212</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>0.8462000000000001</v>
+        <v>-0.1333</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>0.98</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>8.75</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>0.1264</v>
+        <v>0.2641</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>0.596</v>
+        <v>0.2931</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>0.7123999999999999</v>
+        <v>0.3273</v>
       </c>
       <c r="N55" s="7" t="n">
-        <v>4.0303</v>
+        <v>0.4479</v>
       </c>
       <c r="O55" s="7" t="n">
-        <v>0.25</v>
+        <v>0.1778</v>
       </c>
       <c r="P55" s="7" t="n">
-        <v>0.1463</v>
+        <v>0.1266</v>
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R55" s="5" t="inlineStr"/>
@@ -3684,57 +3683,57 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>CIMSA</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>39.98</v>
+        <v>5.27</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.006</v>
+        <v>-0.09910000000000001</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.0584</v>
+        <v>-0.4085</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>-0.1182</v>
+        <v>-0.8891</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>-0.1402</v>
+        <v>-0.8724</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.2569</v>
+        <v>-0.7658</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.8009999999999999</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>9.470000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0.3754999999999999</v>
+        <v>7.8666</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.3037</v>
+        <v>3.1929</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.4933</v>
+        <v>4.946499999999999</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>1.15</v>
+        <v>1.0979</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>0.1807</v>
+        <v>0.4854</v>
       </c>
       <c r="P56" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.586</v>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr"/>
@@ -3742,57 +3741,57 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>INDES</t>
+          <t>CIMSA</t>
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>11.64</v>
+        <v>40.28</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0075</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.0122</v>
+        <v>-0.0336</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-0.0152</v>
+        <v>-0.1124</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.09300000000000001</v>
+        <v>-0.124</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>0.2291</v>
+        <v>-0.2335</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>0.4772</v>
+        <v>-0.07400000000000001</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>9.81</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>0.6297</v>
+        <v>0.3754999999999999</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>0.8554999999999999</v>
+        <v>0.3037</v>
       </c>
       <c r="M57" s="7" t="n">
-        <v>1.0205</v>
+        <v>0.4933</v>
       </c>
       <c r="N57" s="7" t="n">
-        <v>1.9437</v>
+        <v>1.15</v>
       </c>
       <c r="O57" s="7" t="n">
-        <v>0.0374</v>
+        <v>0.1807</v>
       </c>
       <c r="P57" s="7" t="n">
-        <v>0.137</v>
+        <v>0.2729</v>
       </c>
       <c r="Q57" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R57" s="5" t="inlineStr"/>
@@ -3800,57 +3799,57 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GESAN</t>
+          <t>CMENT</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>39.14</v>
+        <v>217.1</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>-0.0312</v>
+        <v>-0.0561</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>-0.08380000000000001</v>
+        <v>-0.0916</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>-0.3687</v>
+        <v>-0.1242</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>-0.5046</v>
+        <v>-0.2787</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-0.1812</v>
+        <v>-0.3421</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>-0.09230000000000001</v>
+        <v>-0.3897</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>10.52</v>
+        <v>21.43</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0.2641</v>
+        <v>0.0934</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.2931</v>
+        <v>0.1109</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.3273</v>
+        <v>0.1008</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.4479</v>
+        <v>0.4922</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>0.1778</v>
+        <v>0.1647</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>0.1266</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr"/>
@@ -3858,57 +3857,57 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TNZTP</t>
+          <t>INDES</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>25.24</v>
+        <v>11.82</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>-0.0164</v>
+        <v>0.0155</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>-0.0285</v>
+        <v>-0.0183</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-0.1519</v>
+        <v>-0.0008</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>0.1148</v>
+        <v>0.0944</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>0.0525</v>
+        <v>0.2534</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>0.1238</v>
+        <v>0.5232</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>18.68</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>0.4327</v>
+        <v>0.6297</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>0.4143</v>
+        <v>0.8554999999999999</v>
       </c>
       <c r="M59" s="7" t="n">
-        <v>0.5201</v>
+        <v>1.0205</v>
       </c>
       <c r="N59" s="7" t="n">
-        <v>0.0702</v>
+        <v>1.9437</v>
       </c>
       <c r="O59" s="7" t="n">
-        <v>0.3617</v>
+        <v>0.0374</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>0.0551</v>
+        <v>0.137</v>
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>Sağlık hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R59" s="5" t="inlineStr"/>
@@ -3916,57 +3915,57 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>CMENT</t>
+          <t>CWENE</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>230</v>
+        <v>17.24</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>0.0092</v>
+        <v>-0.0491</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>-0.04559999999999999</v>
+        <v>-0.0761</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>-0.0413</v>
+        <v>-0.4295</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>-0.2327</v>
+        <v>-0.5534</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-0.3067</v>
+        <v>-0.5235</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>-0.3611</v>
+        <v>-0.2738</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>22.7</v>
+        <v>6.41</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0.0934</v>
+        <v>0.5809000000000001</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.1109</v>
+        <v>0.9067000000000001</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.1008</v>
+        <v>0.8432999999999999</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.4922</v>
+        <v>5.095899999999999</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>0.1647</v>
+        <v>0.1918</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.2052</v>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr"/>
@@ -3974,57 +3973,57 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>TNZTP</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>10.32</v>
+        <v>25.3</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>-0.0105</v>
+        <v>0.0024</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>-0.0227</v>
+        <v>0.0072</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>-0.09230000000000001</v>
+        <v>-0.1938</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>-0.1088</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>-0.0337</v>
+        <v>0.042</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>-0.1443</v>
+        <v>0.1469</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>6.92</v>
+        <v>18.72</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>0.423</v>
+        <v>0.4327</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>0.5552</v>
+        <v>0.4143</v>
       </c>
       <c r="M61" s="7" t="n">
-        <v>0.8170999999999999</v>
+        <v>0.5201</v>
       </c>
       <c r="N61" s="7" t="n">
-        <v>10.0728</v>
+        <v>0.0702</v>
       </c>
       <c r="O61" s="7" t="n">
-        <v>0.179</v>
+        <v>0.3617</v>
       </c>
       <c r="P61" s="7" t="n">
-        <v>0.2236</v>
+        <v>0.0551</v>
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Sağlık hizmetleri</t>
         </is>
       </c>
       <c r="R61" s="5" t="inlineStr"/>
@@ -4032,55 +4031,55 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>YKSLN</t>
+          <t>BYDNR</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>2.21</v>
+        <v>21.6</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>-0.0221</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>-0.07139999999999999</v>
+        <v>-0.0314</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>-0.4738</v>
+        <v>-0.3843</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>-0.3006</v>
+        <v>-0.4331</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-0.3072</v>
+        <v>-0.4444</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>-0.345</v>
+        <v>0.0256</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="4" t="n">
-        <v>0.1126</v>
+        <v>0.2762</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.0263</v>
+        <v>0.0636</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.6127</v>
+        <v>0.127</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0.8754000000000001</v>
+        <v>0.7182999999999999</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>0.1443</v>
+        <v>0.1081</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>-0.04969999999999999</v>
+        <v>-0.0257</v>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr"/>
@@ -4088,57 +4087,57 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>CWENE</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>18.13</v>
+        <v>10.18</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>-0.0104</v>
+        <v>-0.0136</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>-0.0253</v>
+        <v>-0.0183</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-0.4155</v>
+        <v>-0.1054</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>-0.5191</v>
+        <v>-0.1517</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>-0.5019</v>
+        <v>-0.0521</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>-0.2399</v>
+        <v>-0.1453</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>6.74</v>
+        <v>6.83</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>0.5809000000000001</v>
+        <v>0.423</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>0.9067000000000001</v>
+        <v>0.5552</v>
       </c>
       <c r="M63" s="7" t="n">
-        <v>0.8432999999999999</v>
+        <v>0.8170999999999999</v>
       </c>
       <c r="N63" s="7" t="n">
-        <v>5.095899999999999</v>
+        <v>10.0728</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>0.1918</v>
+        <v>0.179</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>0.2052</v>
+        <v>0.2236</v>
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R63" s="5" t="inlineStr"/>
@@ -4146,57 +4145,57 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>GRTHO</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>5.85</v>
+        <v>89</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.09960000000000001</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.4085</v>
+        <v>-0.2294</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>-0.8815000000000001</v>
+        <v>-0.6096</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>-0.8573999999999999</v>
+        <v>-0.6375</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.7225</v>
+        <v>-0.6506000000000001</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>-0.7728</v>
+        <v>-0.8506999999999999</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>3.72</v>
+        <v>6.19</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>7.8666</v>
+        <v>0.5085000000000001</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>3.1929</v>
+        <v>0.4487</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>4.946499999999999</v>
+        <v>0.2298</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>1.0979</v>
+        <v>0.9399</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>0.4854</v>
+        <v>0.1089</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>0.586</v>
+        <v>0.2287</v>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr"/>
@@ -4204,57 +4203,57 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>MOBTL</t>
+          <t>ISDMR</t>
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>10.34</v>
+        <v>61.35</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>-0.0171</v>
+        <v>-0.0168</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>0.034</v>
+        <v>-0.0097</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>-0.2143</v>
+        <v>0.0276</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>-0.2794</v>
+        <v>0.1014</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>-0.2582</v>
+        <v>0.3994</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>0.3973</v>
+        <v>0.6808</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>14.65</v>
+        <v>14.46</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>0.5631</v>
+        <v>0.1859</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>0.4406</v>
+        <v>0.3543</v>
       </c>
       <c r="M65" s="7" t="n">
-        <v>0.5064</v>
+        <v>0.4035</v>
       </c>
       <c r="N65" s="7" t="n">
-        <v>1.6818</v>
+        <v>0.208</v>
       </c>
       <c r="O65" s="7" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.1056</v>
       </c>
       <c r="P65" s="7" t="n">
-        <v>0.08689999999999999</v>
+        <v>0.0859</v>
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R65" s="5" t="inlineStr"/>
@@ -4262,55 +4261,57 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>BYDNR</t>
+          <t>MOBTL</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>23.14</v>
+        <v>10.63</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.0122</v>
+        <v>0.028</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>0.1146</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>-0.3608</v>
+        <v>-0.1916</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>-0.3859</v>
+        <v>-0.2472</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.4157</v>
+        <v>-0.2252</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>0.0956</v>
+        <v>0.5078</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr"/>
+        <v>1.16</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>15.07</v>
+      </c>
       <c r="K66" s="4" t="n">
-        <v>0.2762</v>
+        <v>0.5631</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.0636</v>
+        <v>0.4406</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.127</v>
+        <v>0.5064</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.7182999999999999</v>
+        <v>1.6818</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>0.1081</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="P66" s="4" t="n">
-        <v>-0.0257</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr"/>
@@ -4318,57 +4319,57 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>ISDMR</t>
+          <t>MAALT</t>
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>62.4</v>
+        <v>773</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>-0.0119</v>
+        <v>-0.0325</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>-0.0295</v>
+        <v>-0.09849999999999999</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>0.0306</v>
+        <v>-0.2331</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>0.1366</v>
+        <v>-0.303</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>0.4079</v>
+        <v>-0.484</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>0.7003</v>
+        <v>-0.2392</v>
       </c>
       <c r="I67" s="6" t="n">
         <v>1.16</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>14.71</v>
+        <v>1665.59</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>0.1859</v>
+        <v>0.248</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>0.3543</v>
+        <v>3.5256</v>
       </c>
       <c r="M67" s="7" t="n">
-        <v>0.4035</v>
+        <v>0.3863</v>
       </c>
       <c r="N67" s="7" t="n">
-        <v>0.208</v>
+        <v>0.9832</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>0.1056</v>
+        <v>0.4575</v>
       </c>
       <c r="P67" s="7" t="n">
-        <v>0.0859</v>
+        <v>-0</v>
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R67" s="5" t="inlineStr"/>
@@ -4380,31 +4381,31 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>80.65000000000001</v>
+        <v>79.75</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.0037</v>
+        <v>-0.0112</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>-0.0501</v>
+        <v>-0.0392</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>-0.1014</v>
+        <v>-0.1178</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>-0.1029</v>
+        <v>-0.1163</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-0.229</v>
+        <v>-0.2317</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>0.1817</v>
+        <v>0.1458</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>12.12</v>
+        <v>11.98</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>0.4381</v>
@@ -4434,57 +4435,55 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>OBASE</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>268.25</v>
+        <v>21.04</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>0.0066</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>-0.0263</v>
+        <v>-0.2178</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>-0.0254</v>
+        <v>-0.4149</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>0.0377</v>
+        <v>-0.4979</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>-0.1708</v>
+        <v>-0.4457</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>0.1362</v>
+        <v>-0.4016</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="J69" s="6" t="n">
-        <v>18.48</v>
-      </c>
+        <v>1.18</v>
+      </c>
+      <c r="J69" s="5" t="inlineStr"/>
       <c r="K69" s="7" t="n">
-        <v>0.3707</v>
+        <v>0.2041</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>0.4185</v>
+        <v>0.3021</v>
       </c>
       <c r="M69" s="7" t="n">
-        <v>0.4202</v>
+        <v>0.5156000000000001</v>
       </c>
       <c r="N69" s="7" t="n">
-        <v>1.8941</v>
+        <v>0.4873</v>
       </c>
       <c r="O69" s="7" t="n">
-        <v>0.3086</v>
+        <v>0.2465</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>-0.1688</v>
+        <v>0.1432</v>
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R69" s="5" t="inlineStr"/>
@@ -4492,57 +4491,57 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>MAALT</t>
+          <t>RALYH</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>799</v>
+        <v>29.86</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>-0.019</v>
+        <v>-0.09949999999999999</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>-0.0725</v>
+        <v>-0.4087</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>-0.2105</v>
+        <v>-0.8865999999999999</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>-0.271</v>
+        <v>-0.8641</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>-0.4605</v>
+        <v>-0.9066</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>-0.228</v>
+        <v>-0.8275</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>1721.61</v>
+        <v>3.87</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0.248</v>
+        <v>0.7070000000000001</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>3.5256</v>
+        <v>1.4848</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.3863</v>
+        <v>1.5369</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.9832</v>
+        <v>0.5434</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>0.4575</v>
+        <v>0.2854</v>
       </c>
       <c r="P70" s="4" t="n">
-        <v>-0</v>
+        <v>0.3914</v>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr"/>
@@ -4554,31 +4553,31 @@
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>10.51</v>
+        <v>10.34</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>-0.0168</v>
+        <v>-0.0162</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>-0.0489</v>
+        <v>-0.07429999999999999</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.0858</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>-0.1639</v>
+        <v>-0.1701</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>0.1549</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>6.68</v>
+        <v>6.57</v>
       </c>
       <c r="K71" s="7" t="n">
         <v>0.3448</v>
@@ -4608,57 +4607,57 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GEDIK</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>4.87</v>
+        <v>271.25</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>-0.0061</v>
+        <v>0.0112</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>-0.0356</v>
+        <v>-0.0136</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>-0.1456</v>
+        <v>-0.0018</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>-0.2962</v>
+        <v>0.0443</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>-0.1396</v>
+        <v>-0.1327</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>-0.3217</v>
+        <v>0.1647</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>5.15</v>
+        <v>18.68</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0.6583</v>
+        <v>0.3707</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.4185</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.7293999999999999</v>
+        <v>0.4202</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0.3481</v>
+        <v>1.8941</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>0.6628000000000001</v>
+        <v>0.3086</v>
       </c>
       <c r="P72" s="4" t="n">
-        <v>0.275</v>
+        <v>-0.1688</v>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr"/>
@@ -4670,31 +4669,31 @@
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>73.65000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>-0.0718</v>
+        <v>-0.0238</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0323</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-0.8168000000000001</v>
+        <v>-0.7781</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>-0.6391</v>
+        <v>-0.6717</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>-0.1817</v>
+        <v>-0.1903</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>-0.04969999999999999</v>
+        <v>-0.0413</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>22.45</v>
+        <v>21.92</v>
       </c>
       <c r="K73" s="7" t="n">
         <v>0.3781</v>
@@ -4724,57 +4723,55 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>YKSLN</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>29.04</v>
+        <v>2.43</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>0.0076</v>
+        <v>0.09949999999999999</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>-0.0638</v>
+        <v>-0.1164</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>-0.1911</v>
+        <v>-0.4214</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>-0.1636</v>
+        <v>-0.2636</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-0.3564</v>
+        <v>-0.2286</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>-0.283</v>
+        <v>-0.2957</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>6.49</v>
-      </c>
+        <v>1.21</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="4" t="n">
-        <v>0.4021</v>
+        <v>0.1126</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.2915</v>
+        <v>0.0263</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.201</v>
+        <v>0.6127</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.8754000000000001</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>0.8484999999999999</v>
+        <v>0.1443</v>
       </c>
       <c r="P74" s="4" t="n">
-        <v>0.298</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr"/>
@@ -4782,57 +4779,57 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>GRTHO</t>
+          <t>GEDIK</t>
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>98.90000000000001</v>
+        <v>4.84</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.0062</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>-0.0839</v>
+        <v>-0.051</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-0.5575</v>
+        <v>-0.1418</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>-0.6038</v>
+        <v>-0.2711</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>-0.6085</v>
+        <v>-0.1741</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>-0.838</v>
+        <v>-0.3086</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>6.88</v>
+        <v>5.12</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>0.5085000000000001</v>
+        <v>0.6583</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>0.4487</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="M75" s="7" t="n">
-        <v>0.2298</v>
+        <v>0.7293999999999999</v>
       </c>
       <c r="N75" s="7" t="n">
-        <v>0.9399</v>
+        <v>0.3481</v>
       </c>
       <c r="O75" s="7" t="n">
-        <v>0.1089</v>
+        <v>0.6628000000000001</v>
       </c>
       <c r="P75" s="7" t="n">
-        <v>0.2287</v>
+        <v>0.275</v>
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R75" s="5" t="inlineStr"/>
@@ -4840,55 +4837,57 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>OBASE</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>22.74</v>
+        <v>29.04</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.0453</v>
+        <v>0</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>-0.1464</v>
+        <v>-0.0352</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>-0.3687</v>
+        <v>-0.1829</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>-0.4312</v>
+        <v>-0.1741</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.4205</v>
+        <v>-0.337</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>-0.3701</v>
+        <v>-0.2722</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr"/>
+        <v>1.24</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>6.49</v>
+      </c>
       <c r="K76" s="4" t="n">
-        <v>0.2041</v>
+        <v>0.4021</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.3021</v>
+        <v>0.2915</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.5156000000000001</v>
+        <v>0.201</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.4873</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>0.2465</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="P76" s="4" t="n">
-        <v>0.1432</v>
+        <v>0.298</v>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R76" s="2" t="inlineStr"/>
@@ -4900,31 +4899,31 @@
         </is>
       </c>
       <c r="B77" s="6" t="n">
-        <v>38.1</v>
+        <v>37.52</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>-0.0026</v>
+        <v>-0.0152</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>-0.0611</v>
+        <v>-0.0745</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-0.2957</v>
+        <v>-0.2967</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>-0.2983</v>
+        <v>-0.3282</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>-0.3639</v>
+        <v>-0.3726</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>-0.4262</v>
+        <v>-0.44</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="K77" s="7" t="n">
         <v>0.265</v>
@@ -4954,55 +4953,57 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>DAGI</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>6</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>0.0989</v>
+        <v>-0.005500000000000001</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>0.07719999999999999</v>
+        <v>0.0132</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>-0.3617</v>
+        <v>-0.08990000000000001</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>-0.359</v>
+        <v>-0.2382</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>-0.0228</v>
+        <v>-0.1088</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>-0.2611</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="I78" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="J78" s="2" t="inlineStr"/>
+      <c r="J78" s="3" t="n">
+        <v>26.83</v>
+      </c>
       <c r="K78" s="4" t="n">
-        <v>0.5429999999999999</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>1.1389</v>
+        <v>0.3716</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>1.8634</v>
+        <v>0.4119</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>0.5748</v>
+        <v>0.9691</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>0.1561</v>
+        <v>0.3037</v>
       </c>
       <c r="P78" s="4" t="n">
-        <v>-0.0597</v>
+        <v>0.0601</v>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr"/>
@@ -5010,57 +5011,55 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>RALYH</t>
+          <t>DAGI</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
-        <v>33.16</v>
+        <v>6.01</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>-0.0999</v>
+        <v>0.0017</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>-0.4089</v>
+        <v>0.0562</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-0.8778</v>
+        <v>-0.3432</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>-0.8405</v>
+        <v>-0.3586</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>-0.8828</v>
+        <v>-0.0066</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>-0.8079999999999999</v>
+        <v>-0.2828</v>
       </c>
       <c r="I79" s="6" t="n">
         <v>1.31</v>
       </c>
-      <c r="J79" s="6" t="n">
-        <v>4.3</v>
-      </c>
+      <c r="J79" s="5" t="inlineStr"/>
       <c r="K79" s="7" t="n">
-        <v>0.7070000000000001</v>
+        <v>0.5429999999999999</v>
       </c>
       <c r="L79" s="7" t="n">
-        <v>1.4848</v>
+        <v>1.1389</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>1.5369</v>
+        <v>1.8634</v>
       </c>
       <c r="N79" s="7" t="n">
-        <v>0.5434</v>
+        <v>0.5748</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>0.2854</v>
+        <v>0.1561</v>
       </c>
       <c r="P79" s="7" t="n">
-        <v>0.3914</v>
+        <v>-0.0597</v>
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R79" s="5" t="inlineStr"/>
@@ -5068,57 +5067,57 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>GARFA</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>73.3</v>
+        <v>22.38</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>0.0216</v>
+        <v>-0.0071</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>0.004099999999999999</v>
+        <v>-0.0395</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>-0.0843</v>
+        <v>-0.1868</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>-0.2041</v>
+        <v>-0.1599</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>-0.1169</v>
+        <v>-0.2092</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>0.6591</v>
+        <v>-0.1312</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>26.98</v>
+        <v>3.39</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>0.3716</v>
+        <v>0.9506</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>0.4119</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>0.9691</v>
+        <v>0.5365</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>0.3037</v>
+        <v>0.914</v>
       </c>
       <c r="P80" s="4" t="n">
-        <v>0.0601</v>
+        <v>0.496</v>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr"/>
@@ -5126,57 +5125,55 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>GARFA</t>
+          <t>ACSEL</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>22.54</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>-0.0157</v>
+        <v>-0.0358</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>-0.0123</v>
+        <v>-0.0613</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-0.1552</v>
+        <v>-0.2554</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>-0.1501</v>
+        <v>-0.3505</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>-0.2018</v>
+        <v>-0.2754</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>-0.1195</v>
+        <v>-0.2154</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J81" s="6" t="n">
-        <v>3.42</v>
-      </c>
+        <v>1.32</v>
+      </c>
+      <c r="J81" s="5" t="inlineStr"/>
       <c r="K81" s="7" t="n">
-        <v>0.9562999999999999</v>
+        <v>0.3957</v>
       </c>
       <c r="L81" s="7" t="n">
-        <v>0.9506</v>
+        <v>2.0344</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>0.9429999999999999</v>
+        <v>3.8494</v>
       </c>
       <c r="N81" s="7" t="n">
-        <v>0.5365</v>
+        <v>0.889</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>0.914</v>
+        <v>0.0349</v>
       </c>
       <c r="P81" s="7" t="n">
-        <v>0.496</v>
+        <v>-0.0175</v>
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R81" s="5" t="inlineStr"/>
@@ -5188,28 +5185,28 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>6.54</v>
+        <v>6.37</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>-0.003</v>
+        <v>-0.026</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>-0.0268</v>
+        <v>-0.0464</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>-0.1257</v>
+        <v>-0.1427</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>-0.169</v>
+        <v>-0.1896</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>-0.2224</v>
+        <v>-0.2325</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>-0.2177</v>
+        <v>-0.2241</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="4" t="n">
@@ -5240,55 +5237,57 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>SARKY</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>86.5</v>
+        <v>18.23</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>-0.0052</v>
+        <v>-0.036</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>-0.0308</v>
+        <v>-0.1319</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-0.2399</v>
+        <v>-0.2461</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>-0.3268</v>
+        <v>-0.2967</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>-0.2619</v>
+        <v>-0.3581</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>-0.1923</v>
+        <v>0.2359</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J83" s="5" t="inlineStr"/>
+        <v>1.36</v>
+      </c>
+      <c r="J83" s="6" t="n">
+        <v>66.8</v>
+      </c>
       <c r="K83" s="7" t="n">
-        <v>0.3957</v>
+        <v>0.5590999999999999</v>
       </c>
       <c r="L83" s="7" t="n">
-        <v>2.0344</v>
+        <v>0.3671</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>3.8494</v>
+        <v>0.2342</v>
       </c>
       <c r="N83" s="7" t="n">
-        <v>0.889</v>
+        <v>0.8034</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>0.0349</v>
+        <v>0.0217</v>
       </c>
       <c r="P83" s="7" t="n">
-        <v>-0.0175</v>
+        <v>0.0229</v>
       </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R83" s="5" t="inlineStr"/>
@@ -5296,57 +5295,55 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>PCILT</t>
+          <t>OZYSR</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>30.44</v>
+        <v>11.66</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>0.0073</v>
+        <v>-0.0119</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>-0.0337</v>
+        <v>-0.0034</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>-0.0059</v>
+        <v>-0.0635</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>-0.05110000000000001</v>
+        <v>-0.09609999999999999</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>0.0934</v>
+        <v>0.053</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>0.4264</v>
+        <v>0.3962</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J84" s="3" t="n">
-        <v>6.99</v>
-      </c>
+        <v>1.36</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="4" t="n">
-        <v>0.763</v>
+        <v>0.161</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.7087</v>
+        <v>0.1742</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>0.7914</v>
+        <v>0.6839</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>1.2232</v>
+        <v>0.5105</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>0.0574</v>
+        <v>0.042</v>
       </c>
       <c r="P84" s="4" t="n">
-        <v>0.2831</v>
+        <v>-0.0335</v>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr"/>
@@ -5354,55 +5351,57 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>OZYSR</t>
+          <t>PCILT</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>11.8</v>
+        <v>30.54</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>-0.0034</v>
+        <v>0.0033</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0123</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-0.0183</v>
+        <v>-0.0193</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>-0.062</v>
+        <v>-0.0723</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>0.0563</v>
+        <v>0.113</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0.4459</v>
+        <v>0.4325</v>
       </c>
       <c r="I85" s="6" t="n">
         <v>1.38</v>
       </c>
-      <c r="J85" s="5" t="inlineStr"/>
+      <c r="J85" s="6" t="n">
+        <v>7.02</v>
+      </c>
       <c r="K85" s="7" t="n">
-        <v>0.161</v>
+        <v>0.763</v>
       </c>
       <c r="L85" s="7" t="n">
-        <v>0.1742</v>
+        <v>0.7087</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>0.6839</v>
+        <v>0.7914</v>
       </c>
       <c r="N85" s="7" t="n">
-        <v>0.5105</v>
+        <v>1.2232</v>
       </c>
       <c r="O85" s="7" t="n">
-        <v>0.042</v>
+        <v>0.0574</v>
       </c>
       <c r="P85" s="7" t="n">
-        <v>-0.0335</v>
+        <v>0.2831</v>
       </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R85" s="5" t="inlineStr"/>
@@ -5410,57 +5409,57 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>SARKY</t>
+          <t>KCAER</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>18.91</v>
+        <v>10.71</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>0.0016</v>
+        <v>-0.0272</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>-0.108</v>
+        <v>0.0278</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>-0.2344</v>
+        <v>-0.1972</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>-0.2665</v>
+        <v>-0.199</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>-0.3616</v>
+        <v>-0.0767</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>0.2674</v>
+        <v>-0.1762</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>69.29000000000001</v>
+        <v>31.19</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0.5590999999999999</v>
+        <v>0.1522</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>0.3671</v>
+        <v>0.2873</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>0.2342</v>
+        <v>0.3247</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>0.8034</v>
+        <v>1.1982</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>0.0217</v>
+        <v>0.1199</v>
       </c>
       <c r="P86" s="4" t="n">
-        <v>0.0229</v>
+        <v>0.0508</v>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr"/>
@@ -5468,57 +5467,57 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>KCAER</t>
+          <t>KTLEV</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>11.01</v>
+        <v>7.13</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>0.0357</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>0.0446</v>
+        <v>-0.0083</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>-0.2252</v>
+        <v>-0.7896</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>-0.1524</v>
+        <v>-0.877</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>-0.0582</v>
+        <v>-0.7095</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>-0.1646</v>
+        <v>0.8547</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>32.06</v>
+        <v>1.74</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>0.1522</v>
+        <v>3.5578</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>0.2873</v>
+        <v>3.6471</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>0.3247</v>
+        <v>5.174600000000001</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>1.1982</v>
+        <v>5.7649</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>0.1199</v>
+        <v>0.7222</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>0.0508</v>
+        <v>1.5072</v>
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R87" s="5" t="inlineStr"/>
@@ -5530,31 +5529,31 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>28</v>
+        <v>27.14</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>-0.0264</v>
+        <v>-0.0307</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.0953</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>-0.2875</v>
+        <v>-0.2954</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>-0.3822</v>
+        <v>-0.4061</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>-0.2893</v>
+        <v>-0.2973</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>-0.35</v>
+        <v>-0.3644</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>33.55</v>
+        <v>32.52</v>
       </c>
       <c r="K88" s="4" t="n">
         <v>0.05019999999999999</v>
@@ -5588,28 +5587,28 @@
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>9.75</v>
+        <v>9.33</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>-0.0191</v>
+        <v>-0.0431</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>-0.1522</v>
+        <v>-0.1801</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-0.2015</v>
+        <v>-0.2212</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>-0.18</v>
+        <v>-0.2238</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>-0.2118</v>
+        <v>-0.2583</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>-0.3439</v>
+        <v>-0.3662</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="J89" s="5" t="inlineStr"/>
       <c r="K89" s="7" t="n">
@@ -5640,57 +5639,57 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>TUPRS</t>
+          <t>EGPRO</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>385.75</v>
+        <v>31.12</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>0.0026</v>
+        <v>-0.0171</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>-0.0103</v>
+        <v>-0.0825</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>-0.0832</v>
+        <v>-0.2021</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>0.4287</v>
+        <v>-0.1422</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>0.4709</v>
+        <v>-0.1244</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>1.1611</v>
+        <v>0.1526</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>10.7</v>
+        <v>11.08</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0.465</v>
+        <v>0.3776</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>1.0453</v>
+        <v>0.5127</v>
       </c>
       <c r="M90" s="4" t="n">
-        <v>1.1002</v>
+        <v>0.5197999999999999</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>2.2351</v>
+        <v>1.3047</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.2228</v>
       </c>
       <c r="P90" s="4" t="n">
-        <v>0.187</v>
+        <v>0.1742</v>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R90" s="2" t="inlineStr"/>
@@ -5698,57 +5697,57 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>EGPRO</t>
+          <t>TUPRS</t>
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>31.66</v>
+        <v>391</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>-0.0258</v>
+        <v>0.0136</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.0216</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-0.1615</v>
+        <v>-0.0635</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>-0.1273</v>
+        <v>0.4415</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>-0.09539999999999998</v>
+        <v>0.4603</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>0.1546</v>
+        <v>1.2667</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>11.27</v>
+        <v>10.85</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>0.3776</v>
+        <v>0.465</v>
       </c>
       <c r="L91" s="7" t="n">
-        <v>0.5127</v>
+        <v>1.0453</v>
       </c>
       <c r="M91" s="7" t="n">
-        <v>0.5197999999999999</v>
+        <v>1.1002</v>
       </c>
       <c r="N91" s="7" t="n">
-        <v>1.3047</v>
+        <v>2.2351</v>
       </c>
       <c r="O91" s="7" t="n">
-        <v>0.2228</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="P91" s="7" t="n">
-        <v>0.1742</v>
+        <v>0.187</v>
       </c>
       <c r="Q91" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="R91" s="5" t="inlineStr"/>
@@ -5756,57 +5755,57 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>KTLEV</t>
+          <t>MEGMT</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>7.92</v>
+        <v>3.39</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>-0.1</v>
+        <v>0.018</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>-0.0258</v>
+        <v>-0.1396</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.3061</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>-0.8632</v>
+        <v>-0.5069</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>-0.6792</v>
+        <v>-0.5985</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>1.0539</v>
+        <v>0.0113</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>1.93</v>
+        <v>7.24</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>3.5578</v>
+        <v>0.51</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>3.6471</v>
+        <v>0.4203</v>
       </c>
       <c r="M92" s="4" t="n">
-        <v>5.174600000000001</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="N92" s="4" t="n">
-        <v>5.7649</v>
+        <v>0.2482</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>0.7222</v>
+        <v>0.0483</v>
       </c>
       <c r="P92" s="4" t="n">
-        <v>1.5072</v>
+        <v>0.2852</v>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R92" s="2" t="inlineStr"/>
@@ -5814,57 +5813,57 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>MEGMT</t>
+          <t>SAFKR</t>
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>3.33</v>
+        <v>11.99</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>-0.0348</v>
+        <v>-0.005</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>-0.1633</v>
+        <v>-0.1592</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>-0.3204</v>
+        <v>-0.1604</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>-0.5268</v>
+        <v>-0.4134</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>-0.6051</v>
+        <v>-0.5472</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>-0.023</v>
+        <v>-0.4623</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>7.11</v>
+        <v>17.44</v>
       </c>
       <c r="K93" s="7" t="n">
-        <v>0.51</v>
+        <v>0.7861</v>
       </c>
       <c r="L93" s="7" t="n">
-        <v>0.4203</v>
+        <v>0.4555</v>
       </c>
       <c r="M93" s="7" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.3309</v>
       </c>
       <c r="N93" s="7" t="n">
-        <v>0.2482</v>
+        <v>0.5716</v>
       </c>
       <c r="O93" s="7" t="n">
-        <v>0.0483</v>
+        <v>0.2109</v>
       </c>
       <c r="P93" s="7" t="n">
-        <v>0.2852</v>
+        <v>0.1216</v>
       </c>
       <c r="Q93" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R93" s="5" t="inlineStr"/>
@@ -5872,57 +5871,57 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SAFKR</t>
+          <t>GENIL</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>12.05</v>
+        <v>5.05</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>0.0042</v>
+        <v>-0.0363</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>-0.1858</v>
+        <v>0.3049</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>-0.1484</v>
+        <v>-0.5826</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>-0.3975</v>
+        <v>-0.4389</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>-0.5443</v>
+        <v>-0.5144</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>-0.471</v>
+        <v>-0.6509</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>1.74</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>17.52</v>
+        <v>18.41</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0.7861</v>
+        <v>0.5049</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>0.4555</v>
+        <v>0.7672</v>
       </c>
       <c r="M94" s="4" t="n">
-        <v>0.3309</v>
+        <v>1.1622</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>0.5716</v>
+        <v>1.2274</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>0.2109</v>
+        <v>0.0922</v>
       </c>
       <c r="P94" s="4" t="n">
-        <v>0.1216</v>
+        <v>0.1305</v>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr"/>
@@ -5934,31 +5933,31 @@
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>22.88</v>
+        <v>22.72</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>0.0035</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>-0.0017</v>
+        <v>0</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>-0.018</v>
+        <v>-0.0122</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>0.0803</v>
+        <v>0.0412</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>0.4993</v>
+        <v>0.4928</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>0.6401</v>
+        <v>0.6369</v>
       </c>
       <c r="I95" s="6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>10.62</v>
+        <v>10.55</v>
       </c>
       <c r="K95" s="7" t="n">
         <v>0.251</v>
@@ -5988,57 +5987,57 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GENIL</t>
+          <t>DERIM</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>5.24</v>
+        <v>23.62</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>0.0214</v>
+        <v>-0.0679</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>0.2186</v>
+        <v>-0.1226</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.3232</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>-0.4086</v>
+        <v>-0.3599</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>-0.4863</v>
+        <v>-0.4089</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>-0.6361</v>
+        <v>-0.3738</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>19.1</v>
+        <v>13.01</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0.5049</v>
+        <v>0.1436</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>0.7672</v>
+        <v>0.2539</v>
       </c>
       <c r="M96" s="4" t="n">
-        <v>1.1622</v>
+        <v>0.0263</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>1.2274</v>
+        <v>0.0576</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>0.0922</v>
+        <v>0.0602</v>
       </c>
       <c r="P96" s="4" t="n">
-        <v>0.1305</v>
+        <v>0.1637</v>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr"/>
@@ -6050,28 +6049,28 @@
         </is>
       </c>
       <c r="B97" s="6" t="n">
-        <v>11.1</v>
+        <v>11.01</v>
       </c>
       <c r="C97" s="7" t="n">
-        <v>0.0063</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>-0.0488</v>
+        <v>-0.0549</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>-0.2238</v>
+        <v>-0.1759</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>0.2715</v>
+        <v>0.2343</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>0.2292</v>
+        <v>0.2099</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>0.2759</v>
+        <v>0.2233</v>
       </c>
       <c r="I97" s="6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J97" s="5" t="inlineStr"/>
       <c r="K97" s="7" t="n">
@@ -6102,57 +6101,57 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>FONET</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>429.5</v>
+        <v>4.08</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>-0.0058</v>
+        <v>-0.0263</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>-0.0155</v>
+        <v>-0.0512</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>-0.0283</v>
+        <v>-0.1033</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>0.0343</v>
+        <v>-0.1791</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>-0.09390000000000001</v>
+        <v>-0.2047</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>0.2735</v>
+        <v>0.3394</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>13.41</v>
+        <v>13.26</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0.3601</v>
+        <v>1.0251</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>0.3635</v>
+        <v>2.0469</v>
       </c>
       <c r="M98" s="4" t="n">
-        <v>0.5899</v>
+        <v>1.6971</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>0.1175</v>
+        <v>1.6785</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>0.2737</v>
+        <v>0.4396</v>
       </c>
       <c r="P98" s="4" t="n">
-        <v>0.2987</v>
+        <v>0.8814</v>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>Sağlık hizmetleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr"/>
@@ -6160,57 +6159,57 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>FONET</t>
+          <t>ENERY</t>
         </is>
       </c>
       <c r="B99" s="6" t="n">
-        <v>4.19</v>
+        <v>14.04</v>
       </c>
       <c r="C99" s="7" t="n">
-        <v>-0.0024</v>
+        <v>-0.029</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>-0.0278</v>
+        <v>0.0137</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>-0.1028</v>
+        <v>0.1518</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>-0.1569</v>
+        <v>0.4111</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>-0.1066</v>
+        <v>0.5294</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>0.458</v>
+        <v>0.4283</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>13.61</v>
+        <v>22.39</v>
       </c>
       <c r="K99" s="7" t="n">
-        <v>1.0251</v>
+        <v>0.4279</v>
       </c>
       <c r="L99" s="7" t="n">
-        <v>2.0469</v>
+        <v>0.7162999999999999</v>
       </c>
       <c r="M99" s="7" t="n">
-        <v>1.6971</v>
+        <v>0.8373999999999999</v>
       </c>
       <c r="N99" s="7" t="n">
-        <v>1.6785</v>
+        <v>0.6103000000000001</v>
       </c>
       <c r="O99" s="7" t="n">
-        <v>0.4396</v>
+        <v>0.2099</v>
       </c>
       <c r="P99" s="7" t="n">
-        <v>0.8814</v>
+        <v>0.1017</v>
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R99" s="5" t="inlineStr"/>
@@ -6218,55 +6217,57 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>DURDO</t>
+          <t>MPARK</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>6.38</v>
+        <v>426.75</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>-0.0031</v>
+        <v>-0.0064</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>0.1292</v>
+        <v>0</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>0.2269</v>
+        <v>-0.0323</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>0.2735</v>
+        <v>0.0314</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>0.519</v>
+        <v>-0.0682</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>0.7972</v>
+        <v>0.2777</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr"/>
+        <v>1.86</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>13.33</v>
+      </c>
       <c r="K100" s="4" t="n">
-        <v>0.3099</v>
+        <v>0.3601</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>0.2862</v>
+        <v>0.3635</v>
       </c>
       <c r="M100" s="4" t="n">
-        <v>0.3279</v>
+        <v>0.5899</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>0.1519</v>
+        <v>0.1175</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>0.0876</v>
+        <v>0.2737</v>
       </c>
       <c r="P100" s="4" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.2987</v>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Sağlık hizmetleri</t>
         </is>
       </c>
       <c r="R100" s="2" t="inlineStr"/>
@@ -6274,57 +6275,57 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>DERIM</t>
+          <t>SAYAS</t>
         </is>
       </c>
       <c r="B101" s="6" t="n">
-        <v>25.34</v>
+        <v>38.12</v>
       </c>
       <c r="C101" s="7" t="n">
-        <v>-0.0071</v>
+        <v>-0.0241</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>-0.0649</v>
+        <v>-0.0639</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>-0.2878</v>
+        <v>-0.2941</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>-0.3268</v>
+        <v>-0.1644</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>-0.363</v>
+        <v>-0.1269</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>-0.3565</v>
+        <v>-0.2711</v>
       </c>
       <c r="I101" s="6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>13.96</v>
+        <v>15.19</v>
       </c>
       <c r="K101" s="7" t="n">
-        <v>0.1436</v>
+        <v>0.486</v>
       </c>
       <c r="L101" s="7" t="n">
-        <v>0.2539</v>
+        <v>1.4655</v>
       </c>
       <c r="M101" s="7" t="n">
-        <v>0.0263</v>
+        <v>2.3632</v>
       </c>
       <c r="N101" s="7" t="n">
-        <v>0.0576</v>
+        <v>6.118200000000001</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>0.0602</v>
+        <v>0.1798</v>
       </c>
       <c r="P101" s="7" t="n">
-        <v>0.1637</v>
+        <v>0.1493</v>
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R101" s="5" t="inlineStr"/>
@@ -6332,57 +6333,57 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>ENERY</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>14.46</v>
+        <v>250.25</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0393</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>0.0463</v>
+        <v>-0.0766</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>0.2563</v>
+        <v>-0.1517</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>0.4431</v>
+        <v>-0.1371</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>0.6013000000000001</v>
+        <v>-0.1326</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>0.4431</v>
+        <v>-0.0205</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>23.06</v>
+        <v>9.84</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0.4279</v>
+        <v>1.7224</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>0.7162999999999999</v>
+        <v>1.8184</v>
       </c>
       <c r="M102" s="4" t="n">
-        <v>0.8373999999999999</v>
+        <v>1.3297</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>0.6103000000000001</v>
+        <v>5.0053</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>0.2099</v>
+        <v>0.0381</v>
       </c>
       <c r="P102" s="4" t="n">
-        <v>0.1017</v>
+        <v>0.2862</v>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr"/>
@@ -6390,57 +6391,57 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>SAYAS</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="B103" s="6" t="n">
-        <v>39.06</v>
+        <v>16.89</v>
       </c>
       <c r="C103" s="7" t="n">
-        <v>-0.024</v>
+        <v>-0.0134</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>-0.06509999999999999</v>
+        <v>0.4424</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>-0.2692</v>
+        <v>-0.2998</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>-0.149</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>-0.1033</v>
+        <v>-0.4359</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>-0.2807</v>
+        <v>0.3882</v>
       </c>
       <c r="I103" s="6" t="n">
         <v>1.92</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>15.57</v>
+        <v>2.18</v>
       </c>
       <c r="K103" s="7" t="n">
-        <v>0.486</v>
+        <v>2.1748</v>
       </c>
       <c r="L103" s="7" t="n">
-        <v>1.4655</v>
+        <v>2.2285</v>
       </c>
       <c r="M103" s="7" t="n">
-        <v>2.3632</v>
+        <v>2.5519</v>
       </c>
       <c r="N103" s="7" t="n">
-        <v>6.118200000000001</v>
+        <v>7.8348</v>
       </c>
       <c r="O103" s="7" t="n">
-        <v>0.1798</v>
+        <v>0.887</v>
       </c>
       <c r="P103" s="7" t="n">
-        <v>0.1493</v>
+        <v>1.1538</v>
       </c>
       <c r="Q103" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R103" s="5" t="inlineStr"/>
@@ -6448,57 +6449,57 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>AHGAZ</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>17.12</v>
+        <v>47.16</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>0.09960000000000001</v>
+        <v>-0.0109</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>0.6075</v>
+        <v>0.0021</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>-0.3097</v>
+        <v>0.1633</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>-0.5373</v>
+        <v>0.2603</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>-0.4204</v>
+        <v>0.8925</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>0.5106000000000001</v>
+        <v>0.7676000000000001</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>2.21</v>
+        <v>22.32</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>2.1748</v>
+        <v>0.659</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>2.2285</v>
+        <v>1.7979</v>
       </c>
       <c r="M104" s="4" t="n">
-        <v>2.5519</v>
+        <v>2.1313</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>7.8348</v>
+        <v>2.8917</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>0.887</v>
+        <v>0.1977</v>
       </c>
       <c r="P104" s="4" t="n">
-        <v>1.1538</v>
+        <v>0.1152</v>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr"/>
@@ -6506,57 +6507,57 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>GLYHO</t>
         </is>
       </c>
       <c r="B105" s="6" t="n">
-        <v>260.5</v>
+        <v>17.71</v>
       </c>
       <c r="C105" s="7" t="n">
-        <v>0.0048</v>
+        <v>0.0034</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>-0.0142</v>
+        <v>0.051</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>-0.1002</v>
+        <v>0.0579</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>-0.1309</v>
+        <v>0.0387</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>-0.1309</v>
+        <v>0.1195</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>-0.0243</v>
+        <v>0.6964</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="J105" s="6" t="n">
-        <v>10.25</v>
+        <v>5.91</v>
       </c>
       <c r="K105" s="7" t="n">
-        <v>1.7224</v>
+        <v>0.2312</v>
       </c>
       <c r="L105" s="7" t="n">
-        <v>1.8184</v>
+        <v>0.317</v>
       </c>
       <c r="M105" s="7" t="n">
-        <v>1.3297</v>
+        <v>0.3503</v>
       </c>
       <c r="N105" s="7" t="n">
-        <v>5.0053</v>
+        <v>0.4888</v>
       </c>
       <c r="O105" s="7" t="n">
-        <v>0.0381</v>
+        <v>0.3457</v>
       </c>
       <c r="P105" s="7" t="n">
-        <v>0.2862</v>
+        <v>-0.2226</v>
       </c>
       <c r="Q105" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R105" s="5" t="inlineStr"/>
@@ -6568,31 +6569,31 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>28.54</v>
+        <v>29.3</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>-0.063</v>
+        <v>0.0266</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>-0.1404</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>-0.4096</v>
+        <v>-0.3707</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-0.636</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>-0.2328</v>
+        <v>-0.1861</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>-0.0028</v>
+        <v>0.0375</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="K106" s="4" t="n">
         <v>0.309</v>
@@ -6622,57 +6623,57 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>AHGAZ</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B107" s="6" t="n">
-        <v>47.68</v>
+        <v>210</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>-0.0209</v>
+        <v>-0.0536</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>0.0343</v>
+        <v>-0.0663</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>0.2132</v>
+        <v>-0.1052</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>0.2721</v>
+        <v>-0.1003</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>0.9784</v>
+        <v>-0.1837</v>
       </c>
       <c r="H107" s="7" t="n">
-        <v>0.7517</v>
+        <v>-0.083</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="J107" s="6" t="n">
-        <v>22.56</v>
+        <v>19.63</v>
       </c>
       <c r="K107" s="7" t="n">
-        <v>0.659</v>
+        <v>0.493</v>
       </c>
       <c r="L107" s="7" t="n">
-        <v>1.7979</v>
+        <v>0.3835</v>
       </c>
       <c r="M107" s="7" t="n">
-        <v>2.1313</v>
+        <v>0.4282</v>
       </c>
       <c r="N107" s="7" t="n">
-        <v>2.8917</v>
+        <v>0.1825</v>
       </c>
       <c r="O107" s="7" t="n">
-        <v>0.1977</v>
+        <v>0.2029</v>
       </c>
       <c r="P107" s="7" t="n">
-        <v>0.1152</v>
+        <v>0.1296</v>
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R107" s="5" t="inlineStr"/>
@@ -6680,57 +6681,55 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GLYHO</t>
+          <t>DURDO</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>17.65</v>
+        <v>7.01</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>-0.0073</v>
+        <v>0.0987</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>0.0697</v>
+        <v>0.09359999999999999</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>0.0563</v>
+        <v>0.3378</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>0.0346</v>
+        <v>0.3799</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.6494</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>0.7720999999999999</v>
+        <v>1.0202</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="J108" s="3" t="n">
-        <v>5.89</v>
-      </c>
+        <v>2.08</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="4" t="n">
-        <v>0.2312</v>
+        <v>0.3099</v>
       </c>
       <c r="L108" s="4" t="n">
-        <v>0.317</v>
+        <v>0.2862</v>
       </c>
       <c r="M108" s="4" t="n">
-        <v>0.3503</v>
+        <v>0.3279</v>
       </c>
       <c r="N108" s="4" t="n">
-        <v>0.4888</v>
+        <v>0.1519</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>0.3457</v>
+        <v>0.0876</v>
       </c>
       <c r="P108" s="4" t="n">
-        <v>-0.2226</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr"/>
@@ -6742,31 +6741,31 @@
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>288</v>
+        <v>287.25</v>
       </c>
       <c r="C109" s="7" t="n">
-        <v>0.0277</v>
+        <v>-0.0026</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>0.0492</v>
+        <v>0.0464</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>-0.0352</v>
+        <v>-0.0369</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>-0.0665</v>
+        <v>-0.0974</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>-0.1007</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>-0.1652</v>
+        <v>-0.1746</v>
       </c>
       <c r="I109" s="6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="J109" s="6" t="n">
-        <v>8.75</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="K109" s="7" t="n">
         <v>0.3337</v>
@@ -6796,57 +6795,57 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>VBTYZ</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>221.9</v>
+        <v>21.8</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>0.0009</v>
+        <v>-0.04389999999999999</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>-0.0138</v>
+        <v>-0.1087</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>-0.0411</v>
+        <v>-0.3944</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>-0.0501</v>
+        <v>-0.2399</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>-0.1441</v>
+        <v>0.0158</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>-0.0609</v>
+        <v>0.1945</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>20.74</v>
+        <v>14.27</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0.493</v>
+        <v>0.5342</v>
       </c>
       <c r="L110" s="4" t="n">
-        <v>0.3835</v>
+        <v>0.9976999999999999</v>
       </c>
       <c r="M110" s="4" t="n">
-        <v>0.4282</v>
+        <v>3.6408</v>
       </c>
       <c r="N110" s="4" t="n">
-        <v>0.1825</v>
+        <v>1.3528</v>
       </c>
       <c r="O110" s="4" t="n">
-        <v>0.2029</v>
+        <v>0.2074</v>
       </c>
       <c r="P110" s="4" t="n">
-        <v>0.1296</v>
+        <v>-9.062000000000001</v>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr"/>
@@ -6854,57 +6853,57 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>VBTYZ</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>22.8</v>
+        <v>46.16</v>
       </c>
       <c r="C111" s="7" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.0383</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>-0.07769999999999999</v>
+        <v>-0.1019</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>-0.3838</v>
+        <v>-0.3659000000000001</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>-0.2111</v>
+        <v>-0.4902</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>0.0755</v>
+        <v>0.1569</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>0.2324</v>
+        <v>0.7618</v>
       </c>
       <c r="I111" s="6" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="J111" s="6" t="n">
-        <v>14.92</v>
+        <v>32.72</v>
       </c>
       <c r="K111" s="7" t="n">
-        <v>0.5342</v>
+        <v>0.8139</v>
       </c>
       <c r="L111" s="7" t="n">
-        <v>0.9976999999999999</v>
+        <v>1.3529</v>
       </c>
       <c r="M111" s="7" t="n">
-        <v>3.6408</v>
+        <v>2.0375</v>
       </c>
       <c r="N111" s="7" t="n">
-        <v>1.3528</v>
+        <v>1.6152</v>
       </c>
       <c r="O111" s="7" t="n">
-        <v>0.2074</v>
+        <v>0.1821</v>
       </c>
       <c r="P111" s="7" t="n">
-        <v>-9.062000000000001</v>
+        <v>0.09230000000000001</v>
       </c>
       <c r="Q111" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R111" s="5" t="inlineStr"/>
@@ -6912,57 +6911,57 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>BIMAS</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="C112" s="4" t="n">
-        <v>-0.0196</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>-0.09519999999999999</v>
+        <v>-0.0049</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>-0.337</v>
+        <v>-0.0517</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>-0.4555</v>
+        <v>0.0515</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>0.1805</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>0.7857</v>
+        <v>0.4918</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>34.02</v>
+        <v>17.84</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0.8139</v>
+        <v>0.4214</v>
       </c>
       <c r="L112" s="4" t="n">
-        <v>1.3529</v>
+        <v>0.5271</v>
       </c>
       <c r="M112" s="4" t="n">
-        <v>2.0375</v>
+        <v>0.8381000000000001</v>
       </c>
       <c r="N112" s="4" t="n">
-        <v>1.6152</v>
+        <v>0.8737999999999999</v>
       </c>
       <c r="O112" s="4" t="n">
-        <v>0.1821</v>
+        <v>0.0611</v>
       </c>
       <c r="P112" s="4" t="n">
-        <v>0.09230000000000001</v>
+        <v>0.1613</v>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr"/>
@@ -6970,57 +6969,57 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>BIMAS</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>411.25</v>
+        <v>81.05</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>0.0372</v>
+        <v>-0.0311</v>
       </c>
       <c r="D113" s="7" t="n">
-        <v>-0.0018</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>-0.0436</v>
+        <v>0.01</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>0.0989</v>
+        <v>-0.0351</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>0.08439999999999999</v>
+        <v>0.0144</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>0.5288</v>
+        <v>0.743</v>
       </c>
       <c r="I113" s="6" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="J113" s="6" t="n">
-        <v>17.99</v>
+        <v>10.95</v>
       </c>
       <c r="K113" s="7" t="n">
-        <v>0.4214</v>
+        <v>0.4257</v>
       </c>
       <c r="L113" s="7" t="n">
-        <v>0.5271</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="M113" s="7" t="n">
-        <v>0.8381000000000001</v>
+        <v>0.7781</v>
       </c>
       <c r="N113" s="7" t="n">
-        <v>0.8737999999999999</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="O113" s="7" t="n">
-        <v>0.0611</v>
+        <v>0.177</v>
       </c>
       <c r="P113" s="7" t="n">
-        <v>0.1613</v>
+        <v>0.5497</v>
       </c>
       <c r="Q113" s="5" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R113" s="5" t="inlineStr"/>
@@ -7028,57 +7027,57 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>83.65000000000001</v>
+        <v>42.64</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>0.0146</v>
+        <v>-0.0431</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>0.0411</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>0.0469</v>
+        <v>-0.1985</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>0.0152</v>
+        <v>-0.1606</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>0.09269999999999999</v>
+        <v>-0.0759</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>0.7928000000000001</v>
+        <v>0.7333</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>11.3</v>
+        <v>27.23</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0.4257</v>
+        <v>1.2681</v>
       </c>
       <c r="L114" s="4" t="n">
-        <v>0.5852000000000001</v>
+        <v>2.3445</v>
       </c>
       <c r="M114" s="4" t="n">
-        <v>0.7781</v>
+        <v>3.7256</v>
       </c>
       <c r="N114" s="4" t="n">
-        <v>0.7203000000000001</v>
+        <v>1.0029</v>
       </c>
       <c r="O114" s="4" t="n">
-        <v>0.177</v>
+        <v>0.2964</v>
       </c>
       <c r="P114" s="4" t="n">
-        <v>0.5497</v>
+        <v>0.1126</v>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr"/>
@@ -7086,57 +7085,57 @@
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>TCKRC</t>
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>44.56</v>
+        <v>119.9</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>0.0248</v>
+        <v>-0.026</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>0.0239</v>
+        <v>-0.0559</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-0.16</v>
+        <v>-0.1436</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>-0.1389</v>
+        <v>-0.07629999999999999</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>-0.0658</v>
+        <v>0.238</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>0.7968000000000001</v>
+        <v>1.6609</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="J115" s="6" t="n">
-        <v>28.46</v>
+        <v>10.75</v>
       </c>
       <c r="K115" s="7" t="n">
-        <v>1.2681</v>
+        <v>2.4396</v>
       </c>
       <c r="L115" s="7" t="n">
-        <v>2.3445</v>
+        <v>2.6112</v>
       </c>
       <c r="M115" s="7" t="n">
-        <v>3.7256</v>
+        <v>2.6298</v>
       </c>
       <c r="N115" s="7" t="n">
-        <v>1.0029</v>
+        <v>2.7617</v>
       </c>
       <c r="O115" s="7" t="n">
-        <v>0.2964</v>
+        <v>0.4116</v>
       </c>
       <c r="P115" s="7" t="n">
-        <v>0.1126</v>
+        <v>0.3455</v>
       </c>
       <c r="Q115" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R115" s="5" t="inlineStr"/>
@@ -7144,53 +7143,53 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>HTTBT</t>
+          <t>LOGO</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>32.74</v>
+        <v>132.2</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>0.0238</v>
+        <v>-0.0294</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>-0.0751</v>
+        <v>-0.1187</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>-0.0725</v>
+        <v>-0.0617</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>-0.1293</v>
+        <v>-0.0258</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>-0.2057</v>
+        <v>-0.0571</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>-0.3162</v>
+        <v>-0.2027</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>23.89</v>
+        <v>14.38</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0.3957</v>
+        <v>0.5617</v>
       </c>
       <c r="L116" s="4" t="n">
-        <v>0.3631</v>
+        <v>0.8981999999999999</v>
       </c>
       <c r="M116" s="4" t="n">
-        <v>0.3492</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="N116" s="4" t="n">
-        <v>0.2572</v>
+        <v>267.6647</v>
       </c>
       <c r="O116" s="4" t="n">
-        <v>0.4235</v>
+        <v>0.346</v>
       </c>
       <c r="P116" s="4" t="n">
-        <v>0.5921</v>
+        <v>0.9277</v>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
@@ -7202,57 +7201,57 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>TCKRC</t>
+          <t>HTTBT</t>
         </is>
       </c>
       <c r="B117" s="6" t="n">
-        <v>123.1</v>
+        <v>32.54</v>
       </c>
       <c r="C117" s="7" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.0061</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>-0.016</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>-0.1021</v>
+        <v>-0.06709999999999999</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>0.019</v>
+        <v>-0.1234</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>0.2691</v>
+        <v>-0.2052</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>1.7601</v>
+        <v>-0.3249</v>
       </c>
       <c r="I117" s="6" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>11.03</v>
+        <v>23.74</v>
       </c>
       <c r="K117" s="7" t="n">
-        <v>2.4396</v>
+        <v>0.3957</v>
       </c>
       <c r="L117" s="7" t="n">
-        <v>2.6112</v>
+        <v>0.3631</v>
       </c>
       <c r="M117" s="7" t="n">
-        <v>2.6298</v>
+        <v>0.3492</v>
       </c>
       <c r="N117" s="7" t="n">
-        <v>2.7617</v>
+        <v>0.2572</v>
       </c>
       <c r="O117" s="7" t="n">
-        <v>0.4116</v>
+        <v>0.4235</v>
       </c>
       <c r="P117" s="7" t="n">
-        <v>0.3455</v>
+        <v>0.5921</v>
       </c>
       <c r="Q117" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R117" s="5" t="inlineStr"/>
@@ -7260,53 +7259,53 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>LOGO</t>
+          <t>ARDYZ</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>136.2</v>
+        <v>63</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>-0.0347</v>
+        <v>-0.0187</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>-0.0747</v>
+        <v>-0.0803</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>-0.0489</v>
+        <v>-0.2105</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>0.0149</v>
+        <v>-0.0462</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>-0.0194</v>
+        <v>0.4993</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>-0.1725</v>
+        <v>1.4882</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>14.81</v>
+        <v>15.69</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0.5617</v>
+        <v>2.0657</v>
       </c>
       <c r="L118" s="4" t="n">
-        <v>0.8981999999999999</v>
+        <v>2.0433</v>
       </c>
       <c r="M118" s="4" t="n">
-        <v>0.8614000000000001</v>
+        <v>2.0361</v>
       </c>
       <c r="N118" s="4" t="n">
-        <v>267.6647</v>
+        <v>1.7568</v>
       </c>
       <c r="O118" s="4" t="n">
-        <v>0.346</v>
+        <v>0.4642</v>
       </c>
       <c r="P118" s="4" t="n">
-        <v>0.9277</v>
+        <v>3.4222</v>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
@@ -7318,53 +7317,53 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>ARDYZ</t>
+          <t>ATATP</t>
         </is>
       </c>
       <c r="B119" s="6" t="n">
-        <v>64.2</v>
+        <v>222.7</v>
       </c>
       <c r="C119" s="7" t="n">
-        <v>-0.0317</v>
+        <v>-0.0326</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>-0.0489</v>
+        <v>-0.0678</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>-0.2045</v>
+        <v>-0.1894</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>-0.0482</v>
+        <v>0.0779</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>0.5</v>
+        <v>0.5455</v>
       </c>
       <c r="H119" s="7" t="n">
-        <v>1.5496</v>
+        <v>0.6509</v>
       </c>
       <c r="I119" s="6" t="n">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>15.99</v>
+        <v>4.58</v>
       </c>
       <c r="K119" s="7" t="n">
-        <v>2.0657</v>
+        <v>0.3072</v>
       </c>
       <c r="L119" s="7" t="n">
-        <v>2.0433</v>
+        <v>0.2985</v>
       </c>
       <c r="M119" s="7" t="n">
-        <v>2.0361</v>
+        <v>0.3487</v>
       </c>
       <c r="N119" s="7" t="n">
-        <v>1.7568</v>
+        <v>0.6609999999999999</v>
       </c>
       <c r="O119" s="7" t="n">
-        <v>0.4642</v>
+        <v>0.3268</v>
       </c>
       <c r="P119" s="7" t="n">
-        <v>3.4222</v>
+        <v>0.7543000000000001</v>
       </c>
       <c r="Q119" s="5" t="inlineStr">
         <is>
@@ -7376,57 +7375,57 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ATATP</t>
+          <t>PKART</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>230.2</v>
+        <v>87</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>-0.0141</v>
+        <v>-0.05429999999999999</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>-0.0774</v>
+        <v>-0.045</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>-0.193</v>
+        <v>-0.2461</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>0.1078</v>
+        <v>-0.304</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>0.5713</v>
+        <v>0.0169</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>0.6778</v>
+        <v>0.0482</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>4.74</v>
+        <v>19.24</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0.3072</v>
+        <v>0.5093</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>0.2985</v>
+        <v>1.5572</v>
       </c>
       <c r="M120" s="4" t="n">
-        <v>0.3487</v>
+        <v>1.6598</v>
       </c>
       <c r="N120" s="4" t="n">
-        <v>0.6609999999999999</v>
+        <v>4.8022</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>0.3268</v>
+        <v>0.083</v>
       </c>
       <c r="P120" s="4" t="n">
-        <v>0.7543000000000001</v>
+        <v>0.2041</v>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr"/>
@@ -7438,31 +7437,31 @@
         </is>
       </c>
       <c r="B121" s="6" t="n">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="C121" s="7" t="n">
-        <v>0.005600000000000001</v>
+        <v>-0.0369</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>-0.0246</v>
+        <v>-0.0521</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-0.1968</v>
+        <v>-0.2129</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>-0.0098</v>
+        <v>-0.0544</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>-0.2397</v>
+        <v>-0.2581</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>0.4097</v>
+        <v>0.3541</v>
       </c>
       <c r="I121" s="6" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="J121" s="6" t="n">
-        <v>17.6</v>
+        <v>16.95</v>
       </c>
       <c r="K121" s="7" t="n">
         <v>0.1897</v>
@@ -7492,57 +7491,57 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>PKART</t>
+          <t>KRONT</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>92</v>
+        <v>18.3</v>
       </c>
       <c r="C122" s="4" t="n">
-        <v>0.0384</v>
+        <v>-0.0261</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>-0.0108</v>
+        <v>-0.1073</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>-0.2076</v>
+        <v>-0.1674</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>-0.2739</v>
+        <v>-0.2324</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>0.1152</v>
+        <v>-0.121</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>0.1429</v>
+        <v>0.2621</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>20.34</v>
+        <v>24.1</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0.5093</v>
+        <v>0.6388</v>
       </c>
       <c r="L122" s="4" t="n">
-        <v>1.5572</v>
+        <v>0.5896</v>
       </c>
       <c r="M122" s="4" t="n">
-        <v>1.6598</v>
+        <v>1.5604</v>
       </c>
       <c r="N122" s="4" t="n">
-        <v>4.8022</v>
+        <v>5.569299999999999</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>0.083</v>
+        <v>0.3874</v>
       </c>
       <c r="P122" s="4" t="n">
-        <v>0.2041</v>
+        <v>13.8834</v>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr"/>
@@ -7550,57 +7549,55 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>KRONT</t>
+          <t>OYAYO</t>
         </is>
       </c>
       <c r="B123" s="6" t="n">
-        <v>18.79</v>
+        <v>31.86</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>-0.0058</v>
+        <v>0.0108</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>-0.1052</v>
+        <v>0.0277</v>
       </c>
       <c r="E123" s="7" t="n">
-        <v>-0.1444</v>
+        <v>-0.2129</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>-0.252</v>
+        <v>-0.3148</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>-0.0771</v>
+        <v>-0.4159</v>
       </c>
       <c r="H123" s="7" t="n">
-        <v>0.2808</v>
+        <v>-0.0897</v>
       </c>
       <c r="I123" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J123" s="6" t="n">
-        <v>24.74</v>
-      </c>
+        <v>3.67</v>
+      </c>
+      <c r="J123" s="5" t="inlineStr"/>
       <c r="K123" s="7" t="n">
-        <v>0.6388</v>
+        <v>0.3933</v>
       </c>
       <c r="L123" s="7" t="n">
-        <v>0.5896</v>
+        <v>0.4082</v>
       </c>
       <c r="M123" s="7" t="n">
-        <v>1.5604</v>
+        <v>0.6868000000000001</v>
       </c>
       <c r="N123" s="7" t="n">
-        <v>5.569299999999999</v>
+        <v>0.2959</v>
       </c>
       <c r="O123" s="7" t="n">
-        <v>0.3874</v>
+        <v>0.7368000000000001</v>
       </c>
       <c r="P123" s="7" t="n">
-        <v>13.8834</v>
+        <v>-0.0453</v>
       </c>
       <c r="Q123" s="5" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R123" s="5" t="inlineStr"/>
@@ -7608,55 +7605,57 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>OYAYO</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>31.52</v>
+        <v>133</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>0.0083</v>
+        <v>0.035</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>0.0013</v>
+        <v>0.044</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>-0.2405</v>
+        <v>-0.2528</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>-0.3204</v>
+        <v>-0.2417</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>-0.4351</v>
+        <v>-0.09519999999999999</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>-0.0984</v>
+        <v>2.8506</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr"/>
+        <v>3.92</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>14.81</v>
+      </c>
       <c r="K124" s="4" t="n">
-        <v>0.3933</v>
+        <v>1.164</v>
       </c>
       <c r="L124" s="4" t="n">
-        <v>0.4082</v>
+        <v>0.8115000000000001</v>
       </c>
       <c r="M124" s="4" t="n">
-        <v>0.6868000000000001</v>
+        <v>1.571</v>
       </c>
       <c r="N124" s="4" t="n">
-        <v>0.2959</v>
+        <v>1.7066</v>
       </c>
       <c r="O124" s="4" t="n">
-        <v>0.7368000000000001</v>
+        <v>0.1178</v>
       </c>
       <c r="P124" s="4" t="n">
-        <v>-0.0453</v>
+        <v>0.3402000000000001</v>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr"/>
@@ -7664,57 +7663,57 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>YEOTK</t>
         </is>
       </c>
       <c r="B125" s="6" t="n">
-        <v>128.5</v>
+        <v>26.38</v>
       </c>
       <c r="C125" s="7" t="n">
-        <v>-0.0039</v>
+        <v>-0.0201</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>0.0533</v>
+        <v>-0.0518</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-0.3272</v>
+        <v>-0.2565</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>-0.2678</v>
+        <v>-0.3339</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>-0.1329</v>
+        <v>0.2105</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>2.7794</v>
+        <v>0.7815000000000001</v>
       </c>
       <c r="I125" s="6" t="n">
-        <v>3.79</v>
+        <v>3.98</v>
       </c>
       <c r="J125" s="6" t="n">
-        <v>14.31</v>
+        <v>9.83</v>
       </c>
       <c r="K125" s="7" t="n">
-        <v>1.164</v>
+        <v>1.4662</v>
       </c>
       <c r="L125" s="7" t="n">
-        <v>0.8115000000000001</v>
+        <v>1.5472</v>
       </c>
       <c r="M125" s="7" t="n">
-        <v>1.571</v>
+        <v>1.7095</v>
       </c>
       <c r="N125" s="7" t="n">
-        <v>1.7066</v>
+        <v>3.7317</v>
       </c>
       <c r="O125" s="7" t="n">
-        <v>0.1178</v>
+        <v>0.1898</v>
       </c>
       <c r="P125" s="7" t="n">
-        <v>0.3402000000000001</v>
+        <v>0.7681999999999999</v>
       </c>
       <c r="Q125" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R125" s="5" t="inlineStr"/>
@@ -7722,57 +7721,57 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>YEOTK</t>
+          <t>ONCSM</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>26.92</v>
+        <v>85.95</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>-0.0066</v>
+        <v>-0.0565</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>-0.0296</v>
+        <v>-0.1379</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>-0.1486</v>
+        <v>-0.4932</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>-0.3269</v>
+        <v>-0.6814</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>0.1932</v>
+        <v>-0.6936</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>0.8044</v>
+        <v>-0.5003</v>
       </c>
       <c r="I126" s="3" t="n">
         <v>4.06</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>10.03</v>
+        <v>28.38</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1.4662</v>
+        <v>0.5028</v>
       </c>
       <c r="L126" s="4" t="n">
-        <v>1.5472</v>
+        <v>1.6135</v>
       </c>
       <c r="M126" s="4" t="n">
-        <v>1.7095</v>
+        <v>2.0025</v>
       </c>
       <c r="N126" s="4" t="n">
-        <v>3.7317</v>
+        <v>9.2562</v>
       </c>
       <c r="O126" s="4" t="n">
-        <v>0.1898</v>
+        <v>0.3063</v>
       </c>
       <c r="P126" s="4" t="n">
-        <v>0.7681999999999999</v>
+        <v>0.1832</v>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr"/>
@@ -7784,31 +7783,31 @@
         </is>
       </c>
       <c r="B127" s="8" t="n">
-        <v>10720</v>
+        <v>10685</v>
       </c>
       <c r="C127" s="7" t="n">
-        <v>0.0007000000000000001</v>
+        <v>-0.0033</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>-0.0104</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>-0.0446</v>
+        <v>-0.04190000000000001</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>-0.029</v>
+        <v>-0.0157</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>0.1158</v>
+        <v>0.125</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>-0.0074</v>
+        <v>-0.0278</v>
       </c>
       <c r="I127" s="6" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="J127" s="6" t="n">
-        <v>19.69</v>
+        <v>19.62</v>
       </c>
       <c r="K127" s="7" t="n">
         <v>0.2032</v>
@@ -7838,57 +7837,57 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>ONCSM</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>193</v>
       </c>
       <c r="C128" s="4" t="n">
-        <v>-0.0461</v>
+        <v>-0.0153</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>-0.0466</v>
+        <v>-0.0128</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>-0.4803</v>
+        <v>-0.3345</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>-0.6363</v>
+        <v>-0.4075</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>-0.6772</v>
+        <v>0</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>-0.4175</v>
+        <v>1.1468</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>30.08</v>
+        <v>18.93</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0.5028</v>
+        <v>0.4338</v>
       </c>
       <c r="L128" s="4" t="n">
-        <v>1.6135</v>
+        <v>0.5232</v>
       </c>
       <c r="M128" s="4" t="n">
-        <v>2.0025</v>
+        <v>0.7125</v>
       </c>
       <c r="N128" s="4" t="n">
-        <v>9.2562</v>
+        <v>0.8672</v>
       </c>
       <c r="O128" s="4" t="n">
-        <v>0.3063</v>
+        <v>0.3018</v>
       </c>
       <c r="P128" s="4" t="n">
-        <v>0.1832</v>
+        <v>0.3122</v>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr"/>
@@ -7896,57 +7895,57 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>DMRGD</t>
         </is>
       </c>
       <c r="B129" s="6" t="n">
-        <v>196</v>
+        <v>6.6</v>
       </c>
       <c r="C129" s="7" t="n">
-        <v>-0.0076</v>
+        <v>0.0107</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>0.0155</v>
+        <v>-0.2171</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>-0.3117</v>
+        <v>-0.3714</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>-0.3827</v>
+        <v>-0.5041</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>0</v>
+        <v>0.2916</v>
       </c>
       <c r="H129" s="7" t="n">
-        <v>1.1645</v>
+        <v>0.9984999999999999</v>
       </c>
       <c r="I129" s="6" t="n">
-        <v>4.47</v>
+        <v>4.63</v>
       </c>
       <c r="J129" s="6" t="n">
-        <v>19.23</v>
+        <v>56.46</v>
       </c>
       <c r="K129" s="7" t="n">
-        <v>0.4338</v>
+        <v>0.4591</v>
       </c>
       <c r="L129" s="7" t="n">
-        <v>0.5232</v>
+        <v>0.4162</v>
       </c>
       <c r="M129" s="7" t="n">
-        <v>0.7125</v>
+        <v>3.3554</v>
       </c>
       <c r="N129" s="7" t="n">
-        <v>0.8672</v>
+        <v>0.2283</v>
       </c>
       <c r="O129" s="7" t="n">
-        <v>0.3018</v>
+        <v>0.2808</v>
       </c>
       <c r="P129" s="7" t="n">
-        <v>0.3122</v>
+        <v>0.0866</v>
       </c>
       <c r="Q129" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R129" s="5" t="inlineStr"/>
@@ -7954,57 +7953,57 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>DMRGD</t>
+          <t>FMIZP</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>6.53</v>
+        <v>242.25</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>-0.06179999999999999</v>
+        <v>-0.0423</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>-0.1755</v>
+        <v>-0.1067</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>-0.384</v>
+        <v>-0.2016</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>-0.4958</v>
+        <v>-0.1688</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>0.2486</v>
+        <v>-0.1565</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>0.9566</v>
+        <v>-0.2196</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>4.58</v>
+        <v>4.86</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>55.86</v>
+        <v>24.51</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0.4591</v>
+        <v>0.2837</v>
       </c>
       <c r="L130" s="4" t="n">
-        <v>0.4162</v>
+        <v>0.7895</v>
       </c>
       <c r="M130" s="4" t="n">
-        <v>3.3554</v>
+        <v>0.1712</v>
       </c>
       <c r="N130" s="4" t="n">
-        <v>0.2283</v>
+        <v>0.9815999999999999</v>
       </c>
       <c r="O130" s="4" t="n">
-        <v>0.2808</v>
+        <v>0.1378</v>
       </c>
       <c r="P130" s="4" t="n">
-        <v>0.0866</v>
+        <v>0.2179</v>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr"/>
@@ -8012,57 +8011,57 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>FMIZP</t>
+          <t>ASELS</t>
         </is>
       </c>
       <c r="B131" s="6" t="n">
-        <v>253</v>
+        <v>348</v>
       </c>
       <c r="C131" s="7" t="n">
-        <v>-0.0269</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>-0.0766</v>
+        <v>-0.0775</v>
       </c>
       <c r="E131" s="7" t="n">
-        <v>-0.1283</v>
+        <v>-0.1083</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>-0.1283</v>
+        <v>-0.0029</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>-0.1343</v>
+        <v>-0.1564</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>-0.2044</v>
+        <v>0.6262</v>
       </c>
       <c r="I131" s="6" t="n">
-        <v>5.07</v>
+        <v>5.17</v>
       </c>
       <c r="J131" s="6" t="n">
-        <v>25.59</v>
+        <v>42.76</v>
       </c>
       <c r="K131" s="7" t="n">
-        <v>0.2837</v>
+        <v>0.5623</v>
       </c>
       <c r="L131" s="7" t="n">
-        <v>0.7895</v>
+        <v>0.5598</v>
       </c>
       <c r="M131" s="7" t="n">
-        <v>0.1712</v>
+        <v>0.606</v>
       </c>
       <c r="N131" s="7" t="n">
-        <v>0.9815999999999999</v>
+        <v>1.1295</v>
       </c>
       <c r="O131" s="7" t="n">
-        <v>0.1378</v>
+        <v>0.2643</v>
       </c>
       <c r="P131" s="7" t="n">
-        <v>0.2179</v>
+        <v>0.1891</v>
       </c>
       <c r="Q131" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R131" s="5" t="inlineStr"/>
@@ -8070,57 +8069,55 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>ASELS</t>
+          <t>EUKYO</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>350.75</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>0.0263</v>
+        <v>0.0164</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>-0.0609</v>
+        <v>0</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>-0.1198</v>
+        <v>-0.3446</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.2464</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>-0.1649</v>
+        <v>0.2977</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>0.66</v>
+        <v>0.6043999999999999</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="J132" s="3" t="n">
-        <v>43.09</v>
-      </c>
+        <v>6.72</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="4" t="n">
-        <v>0.5623</v>
+        <v>0.5533</v>
       </c>
       <c r="L132" s="4" t="n">
-        <v>0.5598</v>
+        <v>0.6938</v>
       </c>
       <c r="M132" s="4" t="n">
-        <v>0.606</v>
+        <v>0.6357</v>
       </c>
       <c r="N132" s="4" t="n">
-        <v>1.1295</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="O132" s="4" t="n">
-        <v>0.2643</v>
+        <v>0.2589</v>
       </c>
       <c r="P132" s="4" t="n">
-        <v>0.1891</v>
+        <v>-0.2304</v>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R132" s="2" t="inlineStr"/>
@@ -8128,55 +8125,55 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>EUKYO</t>
+          <t>PRKAB</t>
         </is>
       </c>
       <c r="B133" s="6" t="n">
-        <v>9.15</v>
+        <v>23.54</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>-0.0518</v>
+        <v>-0.02</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>-0.0108</v>
+        <v>-0.04389999999999999</v>
       </c>
       <c r="E133" s="7" t="n">
-        <v>-0.3321</v>
+        <v>-0.2597</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>-0.2761</v>
+        <v>-0.3137</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>0.2603</v>
+        <v>-0.4085</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>0.7178</v>
+        <v>-0.2621</v>
       </c>
       <c r="I133" s="6" t="n">
-        <v>6.61</v>
+        <v>6.83</v>
       </c>
       <c r="J133" s="5" t="inlineStr"/>
       <c r="K133" s="7" t="n">
-        <v>0.5533</v>
+        <v>0.3515</v>
       </c>
       <c r="L133" s="7" t="n">
-        <v>0.6938</v>
+        <v>0.2524</v>
       </c>
       <c r="M133" s="7" t="n">
-        <v>0.6357</v>
+        <v>0.0007000000000000001</v>
       </c>
       <c r="N133" s="7" t="n">
-        <v>0.08689999999999999</v>
+        <v>0.1345</v>
       </c>
       <c r="O133" s="7" t="n">
-        <v>0.2589</v>
+        <v>0.0398</v>
       </c>
       <c r="P133" s="7" t="n">
-        <v>-0.2304</v>
+        <v>-0.5093</v>
       </c>
       <c r="Q133" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R133" s="5" t="inlineStr"/>
@@ -8184,55 +8181,55 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>PRKAB</t>
+          <t>ETYAT</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>24.02</v>
+        <v>12.5</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>-0.004099999999999999</v>
+        <v>-0.0355</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>-0.026</v>
+        <v>0.2563</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>-0.2531</v>
+        <v>-0.1135</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>-0.3046</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>-0.4121</v>
+        <v>0.6681999999999999</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>-0.2609</v>
+        <v>0.5547</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>6.97</v>
+        <v>10.15</v>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="4" t="n">
-        <v>0.3515</v>
+        <v>0.3832</v>
       </c>
       <c r="L134" s="4" t="n">
-        <v>0.2524</v>
+        <v>0.4461</v>
       </c>
       <c r="M134" s="4" t="n">
-        <v>0.0007000000000000001</v>
+        <v>1.0129</v>
       </c>
       <c r="N134" s="4" t="n">
-        <v>0.1345</v>
+        <v>0.5162</v>
       </c>
       <c r="O134" s="4" t="n">
-        <v>0.0398</v>
+        <v>0.053</v>
       </c>
       <c r="P134" s="4" t="n">
-        <v>-0.5093</v>
+        <v>-0.1403</v>
       </c>
       <c r="Q134" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R134" s="2" t="inlineStr"/>
@@ -8240,55 +8237,55 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>ETYAT</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="n">
-        <v>12.96</v>
+          <t>MRSHL</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="n">
+        <v>1255</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>0.0368</v>
+        <v>-0.0165</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>0.3846</v>
+        <v>-0.0391</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>-0.07690000000000001</v>
+        <v>-0.3187</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>-0.0219</v>
+        <v>-0.3845</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>0.7482</v>
+        <v>-0.1903</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>0.5754</v>
+        <v>-0.3028</v>
       </c>
       <c r="I135" s="6" t="n">
-        <v>10.52</v>
+        <v>11.15</v>
       </c>
       <c r="J135" s="5" t="inlineStr"/>
       <c r="K135" s="7" t="n">
-        <v>0.3832</v>
+        <v>0.2605</v>
       </c>
       <c r="L135" s="7" t="n">
-        <v>0.4461</v>
+        <v>0.5011</v>
       </c>
       <c r="M135" s="7" t="n">
-        <v>1.0129</v>
+        <v>0.4026</v>
       </c>
       <c r="N135" s="7" t="n">
-        <v>0.5162</v>
+        <v>0.7501000000000001</v>
       </c>
       <c r="O135" s="7" t="n">
-        <v>0.053</v>
+        <v>0.1503</v>
       </c>
       <c r="P135" s="7" t="n">
-        <v>-0.1403</v>
+        <v>-0.0529</v>
       </c>
       <c r="Q135" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R135" s="5" t="inlineStr"/>
@@ -8296,55 +8293,55 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>MRSHL</t>
-        </is>
-      </c>
-      <c r="B136" s="9" t="n">
-        <v>1276</v>
+          <t>KENT</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="n">
+        <v>268.25</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>-0.0169</v>
+        <v>-0.012</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>-0.0185</v>
+        <v>-0.075</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>-0.2295</v>
+        <v>-0.2314</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>-0.3607</v>
+        <v>-0.2549</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>-0.155</v>
+        <v>-0.3855</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>-0.3166</v>
+        <v>-0.4784</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>11.33</v>
+        <v>11.55</v>
       </c>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="4" t="n">
-        <v>0.2605</v>
+        <v>0.2234</v>
       </c>
       <c r="L136" s="4" t="n">
-        <v>0.5011</v>
+        <v>0.3229</v>
       </c>
       <c r="M136" s="4" t="n">
-        <v>0.4026</v>
+        <v>0.5381</v>
       </c>
       <c r="N136" s="4" t="n">
-        <v>0.7501000000000001</v>
+        <v>0.0256</v>
       </c>
       <c r="O136" s="4" t="n">
-        <v>0.1503</v>
+        <v>0.051</v>
       </c>
       <c r="P136" s="4" t="n">
-        <v>-0.0529</v>
+        <v>-0.1222</v>
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R136" s="2" t="inlineStr"/>
@@ -8352,55 +8349,57 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>KENT</t>
+          <t>QNBFK</t>
         </is>
       </c>
       <c r="B137" s="6" t="n">
-        <v>271.5</v>
+        <v>39.22</v>
       </c>
       <c r="C137" s="7" t="n">
-        <v>-0.0073</v>
+        <v>-0.0244</v>
       </c>
       <c r="D137" s="7" t="n">
         <v>-0.0702</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>-0.2352</v>
+        <v>-0.0604</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>-0.2363</v>
+        <v>-0.2302</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>-0.3759</v>
+        <v>-0.08109999999999999</v>
       </c>
       <c r="H137" s="7" t="n">
-        <v>-0.4644</v>
+        <v>-0.2804</v>
       </c>
       <c r="I137" s="6" t="n">
-        <v>11.69</v>
-      </c>
-      <c r="J137" s="5" t="inlineStr"/>
+        <v>12.02</v>
+      </c>
+      <c r="J137" s="6" t="n">
+        <v>43.25</v>
+      </c>
       <c r="K137" s="7" t="n">
-        <v>0.2234</v>
+        <v>0.2618</v>
       </c>
       <c r="L137" s="7" t="n">
-        <v>0.3229</v>
+        <v>0.2816</v>
       </c>
       <c r="M137" s="7" t="n">
-        <v>0.5381</v>
+        <v>0.285</v>
       </c>
       <c r="N137" s="7" t="n">
-        <v>0.0256</v>
+        <v>0.2688</v>
       </c>
       <c r="O137" s="7" t="n">
-        <v>0.051</v>
+        <v>0.795</v>
       </c>
       <c r="P137" s="7" t="n">
-        <v>-0.1222</v>
+        <v>0.3111</v>
       </c>
       <c r="Q137" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R137" s="5" t="inlineStr"/>
@@ -8408,57 +8407,55 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>QNBFK</t>
+          <t>BMSTL</t>
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>40.2</v>
+        <v>38.22</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>-0.0195</v>
+        <v>-0.0155</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>-0.0219</v>
+        <v>-0.1306</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>-0.111</v>
+        <v>-0.1903</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>-0.0776</v>
+        <v>-0.0922</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>-0.2325</v>
+        <v>0.1778</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="J138" s="3" t="n">
-        <v>44.33</v>
-      </c>
+        <v>14.27</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="4" t="n">
-        <v>0.2618</v>
+        <v>0.3282</v>
       </c>
       <c r="L138" s="4" t="n">
-        <v>0.2816</v>
+        <v>0.4883</v>
       </c>
       <c r="M138" s="4" t="n">
-        <v>0.285</v>
+        <v>0.1412</v>
       </c>
       <c r="N138" s="4" t="n">
-        <v>0.2688</v>
+        <v>0.3482</v>
       </c>
       <c r="O138" s="4" t="n">
-        <v>0.795</v>
+        <v>0.0741</v>
       </c>
       <c r="P138" s="4" t="n">
-        <v>0.3111</v>
+        <v>-0.0293</v>
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R138" s="2" t="inlineStr"/>
@@ -8466,51 +8463,53 @@
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>BMSTL</t>
+          <t>BFREN</t>
         </is>
       </c>
       <c r="B139" s="6" t="n">
-        <v>38.82</v>
+        <v>101.2</v>
       </c>
       <c r="C139" s="7" t="n">
-        <v>0.0073</v>
+        <v>-0.0175</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>-0.0005</v>
+        <v>-0.0638</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>-0.1193</v>
+        <v>-0.2137</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>-0.1579</v>
+        <v>-0.2221</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>-0.0757</v>
+        <v>-0.3325</v>
       </c>
       <c r="H139" s="7" t="n">
-        <v>0.1443</v>
+        <v>-0.3852</v>
       </c>
       <c r="I139" s="6" t="n">
-        <v>14.49</v>
-      </c>
-      <c r="J139" s="5" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="J139" s="6" t="n">
+        <v>57.99</v>
+      </c>
       <c r="K139" s="7" t="n">
-        <v>0.3282</v>
+        <v>0.3045</v>
       </c>
       <c r="L139" s="7" t="n">
-        <v>0.4883</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="M139" s="7" t="n">
-        <v>0.1412</v>
+        <v>0.0075</v>
       </c>
       <c r="N139" s="7" t="n">
-        <v>0.3482</v>
+        <v>1.8021</v>
       </c>
       <c r="O139" s="7" t="n">
-        <v>0.0741</v>
+        <v>0.1153</v>
       </c>
       <c r="P139" s="7" t="n">
-        <v>-0.0293</v>
+        <v>0.3501</v>
       </c>
       <c r="Q139" s="5" t="inlineStr">
         <is>
@@ -8522,114 +8521,56 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>BFREN</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>103</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>-0.0228</v>
+        <v>-0.0154</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>-0.067</v>
+        <v>-0.0443</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>-0.2052</v>
+        <v>-0.1825</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>-0.2046</v>
+        <v>0.2345</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>-0.3534</v>
+        <v>0.2207</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>-0.3836</v>
-      </c>
-      <c r="I140" s="3" t="n">
-        <v>15.67</v>
-      </c>
-      <c r="J140" s="3" t="n">
-        <v>59.02</v>
-      </c>
+        <v>-0.0413</v>
+      </c>
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="4" t="n">
-        <v>0.3045</v>
+        <v>0.3963</v>
       </c>
       <c r="L140" s="4" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.7615999999999999</v>
       </c>
       <c r="M140" s="4" t="n">
-        <v>0.0075</v>
+        <v>1.8006</v>
       </c>
       <c r="N140" s="4" t="n">
-        <v>1.8021</v>
+        <v>0.3182</v>
       </c>
       <c r="O140" s="4" t="n">
-        <v>0.1153</v>
+        <v>0.0233</v>
       </c>
       <c r="P140" s="4" t="n">
-        <v>0.3501</v>
+        <v>0.1274</v>
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t>NETAS</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="C141" s="7" t="n">
-        <v>-0.0518</v>
-      </c>
-      <c r="D141" s="7" t="n">
-        <v>-0.0454</v>
-      </c>
-      <c r="E141" s="7" t="n">
-        <v>-0.2012</v>
-      </c>
-      <c r="F141" s="7" t="n">
-        <v>0.2478</v>
-      </c>
-      <c r="G141" s="7" t="n">
-        <v>0.232</v>
-      </c>
-      <c r="H141" s="7" t="n">
-        <v>-0.0506</v>
-      </c>
-      <c r="I141" s="5" t="inlineStr"/>
-      <c r="J141" s="5" t="inlineStr"/>
-      <c r="K141" s="7" t="n">
-        <v>0.3963</v>
-      </c>
-      <c r="L141" s="7" t="n">
-        <v>0.7615999999999999</v>
-      </c>
-      <c r="M141" s="7" t="n">
-        <v>1.8006</v>
-      </c>
-      <c r="N141" s="7" t="n">
-        <v>0.3182</v>
-      </c>
-      <c r="O141" s="7" t="n">
-        <v>0.0233</v>
-      </c>
-      <c r="P141" s="7" t="n">
-        <v>0.1274</v>
-      </c>
-      <c r="Q141" s="5" t="inlineStr">
-        <is>
-          <t>Teknoloji hizmetleri</t>
-        </is>
-      </c>
-      <c r="R141" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8653,7 +8594,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>13.10.2026 20:46</t>
+          <t>14.10.2026 19:32</t>
         </is>
       </c>
     </row>
@@ -8664,7 +8605,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3">

--- a/data/bist_screener_latest.xlsx
+++ b/data/bist_screener_latest.xlsx
@@ -579,55 +579,57 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RUBNS</t>
+          <t>MERIT</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14.17</v>
+        <v>13.15</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-0.0757</v>
+        <v>0.0092</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.0917</v>
+        <v>-0.0352</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.5144</v>
+        <v>-0.1724</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-0.3464</v>
+        <v>-0.2507</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.5487</v>
+        <v>-0.2287</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.302</v>
+        <v>-0.3236</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
+        <v>0.22</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>6.11</v>
+      </c>
       <c r="K2" s="4" t="n">
-        <v>0.5189</v>
+        <v>0.9854999999999999</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.4172999999999999</v>
+        <v>1.0319</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>2.5836</v>
+        <v>2.0871</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.7992</v>
+        <v>1.5834</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>0.1688</v>
+        <v>0.6354</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>-0.0061</v>
+        <v>0.0454</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr"/>
@@ -635,57 +637,55 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>MERIT</t>
+          <t>RUBNS</t>
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>13.03</v>
+        <v>14.41</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>-0.0053</v>
+        <v>0.0169</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>-0.0626</v>
+        <v>-0.0891</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>-0.1882</v>
+        <v>-0.4997</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>-0.2575</v>
+        <v>-0.3509</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>-0.2358</v>
+        <v>-0.5411</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-0.3475</v>
+        <v>-0.2845</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="J3" s="6" t="n">
-        <v>6.06</v>
-      </c>
+        <v>0.22</v>
+      </c>
+      <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="7" t="n">
-        <v>0.9854999999999999</v>
+        <v>0.5189</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.0319</v>
+        <v>0.4172999999999999</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>2.0871</v>
+        <v>2.5836</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>1.5834</v>
+        <v>0.7992</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>0.6354</v>
+        <v>0.1688</v>
       </c>
       <c r="P3" s="7" t="n">
-        <v>0.0454</v>
+        <v>-0.0061</v>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr"/>
@@ -697,31 +697,31 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.0229</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.0533</v>
+        <v>0</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.1341</v>
+        <v>-0.1157</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.2198</v>
+        <v>-0.2132</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.3344</v>
+        <v>-0.3313</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.3195</v>
+        <v>-0.2914</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0.22</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>2.7227</v>
@@ -755,31 +755,31 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>-0.0256</v>
+        <v>-0.0066</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-0.0675</v>
+        <v>-0.0848</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-0.2362</v>
+        <v>-0.2135</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>-0.2657</v>
+        <v>-0.2705</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-0.3059</v>
+        <v>-0.3105</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>-0.4109</v>
+        <v>-0.3862</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>8.51</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>0.2518</v>
@@ -816,13 +816,13 @@
         <v>4.11</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0238</v>
+        <v>0</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0238</v>
+        <v>-0.0048</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.07429999999999999</v>
+        <v>-0.0508</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>-0.2687</v>
@@ -831,7 +831,7 @@
         <v>-0.2852</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1138</v>
+        <v>0.1577</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0.24</v>
@@ -871,25 +871,25 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>-0.0226</v>
+        <v>-0.0046</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-0.0649</v>
+        <v>-0.04019999999999999</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-0.3143</v>
+        <v>-0.3087</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>-0.468</v>
+        <v>-0.4638</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-0.4719</v>
+        <v>-0.4743</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>-0.574</v>
+        <v>-0.5621</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0.25</v>
@@ -927,31 +927,31 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="C8" s="4" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>-0.1237</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>-0.1143</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>-0.1143</v>
+      </c>
+      <c r="H8" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>-0.1324</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>-0.1043</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>-0.1107</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>-0.0197</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0.25</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>5.85</v>
+        <v>5.83</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>0.3848</v>
@@ -985,25 +985,25 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>9.94</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>-0.0158</v>
+        <v>-0.0161</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-0.0451</v>
+        <v>-0.0307</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-0.1778</v>
+        <v>-0.1605</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>-0.1227</v>
+        <v>-0.1569</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-0.2301</v>
+        <v>-0.2424</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-0.3373</v>
+        <v>-0.3493</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0.25</v>
@@ -1041,31 +1041,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.0258</v>
+        <v>-0.0011</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.05309999999999999</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2059</v>
+        <v>-0.1939</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1839</v>
+        <v>-0.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2361</v>
+        <v>-0.2369</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2781</v>
+        <v>-0.2832</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.25</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.25</v>
+        <v>11.24</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0.3203</v>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>6.57</v>
+        <v>6.63</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.0091</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.0123</v>
+        <v>0.02</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-0.1555</v>
+        <v>-0.1434</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>-0.1275</v>
+        <v>-0.1276</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-0.2132</v>
+        <v>-0.206</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-0.1181</v>
+        <v>-0.0992</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0.26</v>
@@ -1155,31 +1155,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4.34</v>
+        <v>4.37</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.0046</v>
+        <v>0.0069</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0163</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.06059999999999999</v>
+        <v>-0.0742</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1933</v>
+        <v>-0.1952</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1303</v>
+        <v>-0.1242</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0046</v>
+        <v>0.0355</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0.27</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>15.55</v>
+        <v>15.66</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0.1479</v>
@@ -1213,28 +1213,28 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>13.45</v>
+        <v>12.99</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.0393</v>
+        <v>-0.0342</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>-0.08439999999999999</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>-0.3361</v>
+        <v>-0.3576</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>-0.365</v>
+        <v>-0.3986</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-0.4855</v>
+        <v>-0.5031</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.6629</v>
+        <v>-0.6816</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
       <c r="K13" s="7" t="n">
@@ -1269,31 +1269,31 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.0374</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.0389</v>
+        <v>0.0227</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.187</v>
+        <v>-0.2</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.223</v>
+        <v>-0.2562</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2599</v>
+        <v>-0.2876</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2638</v>
+        <v>-0.2643</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>8.82</v>
+        <v>8.49</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>0.9460999999999999</v>
@@ -1323,57 +1323,55 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>BESLR</t>
+          <t>KRTEK</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>10.82</v>
+        <v>5.42</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>-0.0173</v>
+        <v>-0.0524</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.1041</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-0.1658</v>
+        <v>-0.0639</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>-0.1683</v>
+        <v>-0.1536</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-0.2044</v>
+        <v>-0.2401</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.1852</v>
+        <v>-0.4266</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>5.77</v>
-      </c>
+        <v>0.35</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr"/>
       <c r="K15" s="7" t="n">
-        <v>0.3789</v>
+        <v>0.1651</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.3175</v>
+        <v>0.5547</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.07240000000000001</v>
+        <v>3.1915</v>
       </c>
       <c r="N15" s="7" t="n">
-        <v>0.5778</v>
+        <v>0.7</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>0.1173</v>
+        <v>0.0396</v>
       </c>
       <c r="P15" s="7" t="n">
-        <v>0.07580000000000001</v>
+        <v>-0.0461</v>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R15" s="5" t="inlineStr"/>
@@ -1381,55 +1379,57 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KRTEK</t>
+          <t>BESLR</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5.72</v>
+        <v>10.69</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0172</v>
+        <v>-0.012</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.09210000000000002</v>
+        <v>-0.0074</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.0138</v>
+        <v>-0.1713</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.1059</v>
+        <v>-0.1889</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.198</v>
+        <v>-0.214</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4166</v>
+        <v>-0.1681</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
+        <v>0.36</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>5.7</v>
+      </c>
       <c r="K16" s="4" t="n">
-        <v>0.1651</v>
+        <v>0.3789</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5547</v>
+        <v>0.3175</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.1915</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.7</v>
+        <v>0.5778</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.0396</v>
+        <v>0.1173</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.0461</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr"/>
@@ -1441,31 +1441,31 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>193.6</v>
+        <v>195.8</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>0</v>
+        <v>0.0114</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.0184</v>
+        <v>0.0527</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>-0.0383</v>
+        <v>-0.0185</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>-0.0232</v>
+        <v>-0.0449</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.0516</v>
+        <v>0.0636</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0.2959</v>
+        <v>0.3293</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>0.5672999999999999</v>
@@ -1499,31 +1499,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>37.42</v>
+        <v>37.26</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.0121</v>
+        <v>-0.0043</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.0178</v>
+        <v>-0.008</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1591</v>
+        <v>-0.1438</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1417</v>
+        <v>-0.1661</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2025</v>
+        <v>-0.2059</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0809</v>
+        <v>0.0978</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>0.41</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>9.4</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>0.2329</v>
@@ -1557,28 +1557,28 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.023</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>-0.1212</v>
+        <v>-0.1282</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>-0.4238</v>
+        <v>-0.4408</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.5225</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>-0.5787</v>
+        <v>-0.5884</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-0.8088</v>
+        <v>-0.805</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="7" t="n">
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>7.34</v>
+        <v>7.31</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.0161</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.0174</v>
+        <v>0.0097</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.2689</v>
+        <v>-0.2661</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.3121</v>
+        <v>-0.3281</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3842</v>
+        <v>-0.3867</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2631</v>
+        <v>-0.2464</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>0.44</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>0.9081</v>
@@ -1667,55 +1667,57 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>1.93</v>
+        <v>17.8</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>-0.0103</v>
+        <v>-0.0155</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>-0.0103</v>
+        <v>-0.0231</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-0.5064</v>
+        <v>-0.1812</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>-0.6566</v>
+        <v>-0.1729</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-0.7084999999999999</v>
+        <v>-0.1767</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-0.5338000000000001</v>
+        <v>0.0131</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J21" s="5" t="inlineStr"/>
+        <v>0.44</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>7.19</v>
+      </c>
       <c r="K21" s="7" t="n">
-        <v>0.1726</v>
+        <v>0.1285</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.3081</v>
+        <v>0.8243</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.1357</v>
+        <v>1.9048</v>
       </c>
       <c r="N21" s="7" t="n">
-        <v>0.2328</v>
+        <v>2.2086</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>0.0837</v>
+        <v>0.1116</v>
       </c>
       <c r="P21" s="7" t="n">
-        <v>-0.0244</v>
+        <v>0.1027</v>
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R21" s="5" t="inlineStr"/>
@@ -1723,57 +1725,55 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>18.08</v>
+        <v>1.93</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.0179</v>
+        <v>0</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.0393</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1737</v>
+        <v>-0.4826</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1512</v>
+        <v>-0.6584</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1637</v>
+        <v>-0.7084999999999999</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.005600000000000001</v>
+        <v>-0.5257999999999999</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="J22" s="3" t="n">
-        <v>7.3</v>
-      </c>
+      <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="4" t="n">
-        <v>0.1285</v>
+        <v>0.1726</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.8243</v>
+        <v>0.3081</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.9048</v>
+        <v>0.1357</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.2086</v>
+        <v>0.2328</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.1116</v>
+        <v>0.0837</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1027</v>
+        <v>-0.0244</v>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr"/>
@@ -1785,31 +1785,31 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>10.53</v>
+        <v>10.47</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>-0.0223</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>-0.0366</v>
+        <v>-0.0178</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>-0.1888</v>
+        <v>-0.1983</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>-0.3095</v>
+        <v>-0.3197</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-0.3751</v>
+        <v>-0.3786</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-0.2505</v>
+        <v>-0.2462</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0.48</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="K23" s="7" t="n">
         <v>0.4985</v>
@@ -1843,25 +1843,25 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>108.5</v>
+        <v>108.4</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.0364</v>
+        <v>-0.0009</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.0742</v>
+        <v>-0.05</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2649</v>
+        <v>-0.2621</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3344</v>
+        <v>-0.347</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.4623</v>
+        <v>-0.4628</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3904</v>
+        <v>-0.389</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>0.55</v>
@@ -1899,31 +1899,31 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5.99</v>
+        <v>5.94</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>-0.018</v>
+        <v>-0.0083</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>-0.067</v>
+        <v>-0.0341</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-0.2118</v>
+        <v>-0.2215</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>-0.3359</v>
+        <v>-0.3543</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>-0.3255</v>
+        <v>-0.3311</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-0.2149</v>
+        <v>-0.2575</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0.55</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>7.19</v>
+        <v>7.13</v>
       </c>
       <c r="K25" s="7" t="n">
         <v>0.6883</v>
@@ -1957,31 +1957,31 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>32.36</v>
+        <v>31.36</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.0212</v>
+        <v>-0.0309</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.0112</v>
+        <v>-0.0224</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.0538</v>
+        <v>-0.09050000000000001</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.0134</v>
+        <v>-0.0776</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.0466</v>
+        <v>0.0142</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.2821</v>
+        <v>0.2874</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>17.69</v>
+        <v>17.15</v>
       </c>
       <c r="K26" s="4" t="n">
         <v>0.3105</v>
@@ -2015,31 +2015,31 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>26.48</v>
+        <v>26.2</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>-0.0023</v>
+        <v>-0.0106</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>-0.04269999999999999</v>
+        <v>-0.0231</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-0.2086</v>
+        <v>-0.2113</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>-0.3231</v>
+        <v>-0.3553</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>-0.5132</v>
+        <v>-0.5184000000000001</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>-0.4563</v>
+        <v>-0.4754</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="K27" s="7" t="n">
         <v>0.045</v>
@@ -2076,22 +2076,22 @@
         <v>2.85</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.0206</v>
+        <v>0</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.0563</v>
+        <v>-0.0372</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>-0.2928</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.312</v>
+        <v>-0.3</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>-0.1585</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.0182</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.61</v>
@@ -2129,31 +2129,31 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>7.22</v>
+        <v>7.14</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>-0.0386</v>
+        <v>-0.0111</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>-0.0562</v>
+        <v>-0.0467</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-0.1739</v>
+        <v>-0.162</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>-0.2935</v>
+        <v>-0.3167</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>-0.2169</v>
+        <v>-0.2256</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>-0.3058</v>
+        <v>-0.3054</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0.61</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="K29" s="7" t="n">
         <v>0.3806</v>
@@ -2183,51 +2183,51 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SOKE</t>
+          <t>BAKAB</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>7.47</v>
+        <v>28.48</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.0261</v>
+        <v>-0.0035</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.06709999999999999</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.333</v>
+        <v>-0.2385</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5803</v>
+        <v>-0.4586</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5817</v>
+        <v>-0.3677</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3555</v>
+        <v>-0.2049</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="4" t="n">
-        <v>0.5234000000000001</v>
+        <v>0.3479</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.4561</v>
+        <v>0.5443</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.4897</v>
+        <v>0.7171</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.3644</v>
+        <v>0.97</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.032</v>
+        <v>0.0552</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.0429</v>
+        <v>-0.0031</v>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
@@ -2239,51 +2239,51 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>BAKAB</t>
+          <t>SOKE</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>28.58</v>
+        <v>7.72</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>-0.0305</v>
+        <v>0.0335</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>-0.07690000000000001</v>
+        <v>0.0619</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-0.2443</v>
+        <v>-0.2982</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>-0.4461</v>
+        <v>-0.5926</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>-0.3655</v>
+        <v>-0.5677</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>-0.2276</v>
+        <v>-0.3168</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="7" t="n">
-        <v>0.3479</v>
+        <v>0.5234000000000001</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.5443</v>
+        <v>0.4561</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.7171</v>
+        <v>0.4897</v>
       </c>
       <c r="N31" s="7" t="n">
-        <v>0.97</v>
+        <v>0.3644</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>0.0552</v>
+        <v>0.032</v>
       </c>
       <c r="P31" s="7" t="n">
-        <v>-0.0031</v>
+        <v>-0.0429</v>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
@@ -2299,31 +2299,31 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.0187</v>
+        <v>-0.0019</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.0558</v>
+        <v>-0.0473</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2402</v>
+        <v>-0.2328</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3598</v>
+        <v>-0.3762</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3278</v>
+        <v>-0.3290999999999999</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4074</v>
+        <v>-0.4525</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>0.65</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>9.01</v>
+        <v>8.99</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>1.6512</v>
@@ -2353,55 +2353,57 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>DOKTA</t>
+          <t>SEKFK</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>15.05</v>
+        <v>3.95</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>0.004699999999999999</v>
+        <v>-0.005</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>-0.0505</v>
+        <v>-0.0366</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-0.3524</v>
+        <v>-0.0814</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>-0.3546</v>
+        <v>-0.2896</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>-0.3745000000000001</v>
+        <v>-0.3424</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>-0.3781</v>
+        <v>-0.0987</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0.65</v>
       </c>
-      <c r="J33" s="5" t="inlineStr"/>
+      <c r="J33" s="6" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K33" s="7" t="n">
-        <v>0.2983</v>
+        <v>0.208</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>1.25</v>
+        <v>0.0571</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>3.5566</v>
+        <v>0.0025</v>
       </c>
       <c r="N33" s="7" t="n">
-        <v>0.6970000000000001</v>
+        <v>0.2707</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>0.0852</v>
+        <v>0.6072</v>
       </c>
       <c r="P33" s="7" t="n">
-        <v>-0.0451</v>
+        <v>0.2346</v>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R33" s="5" t="inlineStr"/>
@@ -2409,57 +2411,55 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SEKFK</t>
+          <t>DOKTA</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>3.97</v>
+        <v>15</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.0341</v>
+        <v>-0.0033</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.0746</v>
+        <v>-0.0291</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.345</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2896</v>
+        <v>-0.3628</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3391</v>
+        <v>-0.3766</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1152</v>
+        <v>-0.3687</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.65</v>
       </c>
-      <c r="J34" s="3" t="n">
-        <v>3.22</v>
-      </c>
+      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="4" t="n">
-        <v>0.208</v>
+        <v>0.2983</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.0571</v>
+        <v>1.25</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.0025</v>
+        <v>3.5566</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.2707</v>
+        <v>0.6970000000000001</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.6072</v>
+        <v>0.0852</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2346</v>
+        <v>-0.0451</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr"/>
@@ -2471,31 +2471,31 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>211.2</v>
+        <v>210.9</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>-0.0061</v>
+        <v>-0.0014</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>-0.0112</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-0.0559</v>
+        <v>-0.06559999999999999</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>0.1052</v>
+        <v>0.0722</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>0.0353</v>
+        <v>0.0338</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>0.32</v>
+        <v>0.3408</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>15.05</v>
+        <v>15.03</v>
       </c>
       <c r="K35" s="7" t="n">
         <v>0.3261</v>
@@ -2525,57 +2525,57 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>PNLSN</t>
+          <t>MERCN</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>31.8</v>
+        <v>10.13</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>-0.0209</v>
+        <v>-0.0165</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>-0.0603</v>
+        <v>-0.0542</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>-0.224</v>
+        <v>-0.4548</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>-0.3288</v>
+        <v>-0.604</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.3017</v>
+        <v>-0.4873</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.2006</v>
+        <v>-0.6623</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.68</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>8.970000000000001</v>
+        <v>11.64</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0.306</v>
+        <v>0.2374</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.6481</v>
+        <v>0.8593999999999999</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.5497</v>
+        <v>1.4059</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>7.793600000000001</v>
+        <v>1.3031</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>0.1302</v>
+        <v>0.1784</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>0.08839999999999999</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr"/>
@@ -2583,57 +2583,57 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>AKMGY</t>
+          <t>PNLSN</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>205</v>
+        <v>32</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>-0.0144</v>
+        <v>0.0063</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>-0.0348</v>
+        <v>-0.0148</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-0.148</v>
+        <v>-0.1919</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>-0.1605</v>
+        <v>-0.3445</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>-0.3068</v>
+        <v>-0.2973</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>-0.1202</v>
+        <v>-0.182</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>10.1</v>
+        <v>9.02</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.3886</v>
+        <v>0.306</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>0.3887</v>
+        <v>0.6481</v>
       </c>
       <c r="M37" s="7" t="n">
-        <v>0.3141</v>
+        <v>0.5497</v>
       </c>
       <c r="N37" s="7" t="n">
-        <v>0.5958</v>
+        <v>7.793600000000001</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>0.6443000000000001</v>
+        <v>0.1302</v>
       </c>
       <c r="P37" s="7" t="n">
-        <v>0.0781</v>
+        <v>0.08839999999999999</v>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R37" s="5" t="inlineStr"/>
@@ -2641,57 +2641,57 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MERCN</t>
+          <t>AKMGY</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>10.3</v>
+        <v>204.4</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>-0.031</v>
+        <v>-0.0029</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>-0.0636</v>
+        <v>-0.0126</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>-0.4568</v>
+        <v>-0.1623</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-0.584</v>
+        <v>-0.1643</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.4787</v>
+        <v>-0.3089</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.6513</v>
+        <v>-0.1031</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>11.83</v>
+        <v>10.07</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.2374</v>
+        <v>0.3886</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.8593999999999999</v>
+        <v>0.3887</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>1.4059</v>
+        <v>0.3141</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>1.3031</v>
+        <v>0.5958</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0.1784</v>
+        <v>0.6443000000000001</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0781</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr"/>
@@ -2699,57 +2699,57 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>BNTAS</t>
+          <t>TTKOM</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>5.17</v>
+        <v>52.3</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>-0.0134</v>
+        <v>-0.0038</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>-0.0701</v>
+        <v>0.0048</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-0.1754</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>-0.1426</v>
+        <v>-0.106</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>-0.2249</v>
+        <v>-0.1692</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>-0.2496</v>
+        <v>0.0604</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4.79</v>
+        <v>6.47</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.2654</v>
+        <v>0.4498</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.4329</v>
       </c>
       <c r="M39" s="7" t="n">
-        <v>0.464</v>
+        <v>0.5323</v>
       </c>
       <c r="N39" s="7" t="n">
-        <v>0.3679</v>
+        <v>0.8047</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>0.1363</v>
+        <v>0.4117</v>
       </c>
       <c r="P39" s="7" t="n">
-        <v>0.1657</v>
+        <v>1.3041</v>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R39" s="5" t="inlineStr"/>
@@ -2757,57 +2757,57 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TTKOM</t>
+          <t>BNTAS</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>52.5</v>
+        <v>5.17</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.0048</v>
+        <v>0</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>-0.0113</v>
+        <v>-0.0444</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>-0.1117</v>
+        <v>-0.1634</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.1897</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-0.166</v>
+        <v>-0.2249</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.0304</v>
+        <v>-0.2131</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>6.49</v>
+        <v>4.79</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.4498</v>
+        <v>0.2654</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.4329</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.5323</v>
+        <v>0.464</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.8047</v>
+        <v>0.3679</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.4117</v>
+        <v>0.1363</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>1.3041</v>
+        <v>0.1657</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr"/>
@@ -2819,31 +2819,31 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>98.3</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>-0.0116</v>
+        <v>-0.0046</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>-0.0229</v>
+        <v>-0.021</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-0.0447</v>
+        <v>-0.0463</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>-0.108</v>
+        <v>-0.124</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>-0.1634</v>
+        <v>-0.1672</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>0.0036</v>
+        <v>0.0747</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0.7</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>11.04</v>
+        <v>10.99</v>
       </c>
       <c r="K41" s="7" t="n">
         <v>0.3971</v>
@@ -2877,31 +2877,31 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>5.86</v>
+        <v>5.81</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.0017</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>0.0138</v>
+        <v>0.0069</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-0.0266</v>
+        <v>-0.0136</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-0.1445</v>
+        <v>-0.1628</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-0.3326</v>
+        <v>-0.3383</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-0.262</v>
+        <v>-0.2484</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>11.02</v>
+        <v>10.92</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>0.4159</v>
@@ -2935,31 +2935,31 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>291.5</v>
+        <v>288.5</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-0.1126</v>
+        <v>-0.1388</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.1721</v>
+        <v>0.1226</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>0.0052</v>
+        <v>-0.0052</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>0.5757</v>
+        <v>0.5232</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>7.66</v>
+        <v>7.58</v>
       </c>
       <c r="K43" s="7" t="n">
         <v>0.1662</v>
@@ -2993,31 +2993,31 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>8.449999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>-0.0265</v>
+        <v>-0.0189</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>-0.0474</v>
+        <v>-0.04269999999999999</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>-0.1732</v>
+        <v>-0.1751</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>-0.1952</v>
+        <v>-0.226</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-0.3267</v>
+        <v>-0.3394</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>-0.352</v>
+        <v>-0.3882</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>17.81</v>
+        <v>17.47</v>
       </c>
       <c r="K44" s="4" t="n">
         <v>0.2802</v>
@@ -3051,31 +3051,31 @@
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>39.76</v>
+        <v>39.72</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>-0.008</v>
+        <v>-0.001</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>-0.0173</v>
+        <v>0.0102</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-0.1184</v>
+        <v>-0.1228</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>-0.1438</v>
+        <v>-0.1513</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>-0.2088</v>
+        <v>-0.2096</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>0.0247</v>
+        <v>0.0575</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>0.78</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>7.2</v>
+        <v>7.19</v>
       </c>
       <c r="K45" s="7" t="n">
         <v>0.3163</v>
@@ -3109,31 +3109,31 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>37.1</v>
+        <v>37.4</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>-0.0043</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>0</v>
+        <v>0.0241</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>-0.0512</v>
+        <v>-0.0386</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-0.1233</v>
+        <v>-0.1485</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.1983</v>
+        <v>0.208</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.357</v>
+        <v>0.4385</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>32.34</v>
+        <v>32.6</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>0.1998</v>
@@ -3167,31 +3167,31 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>16</v>
+        <v>15.84</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>-0.0309</v>
+        <v>-0.01</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0571</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-0.1667</v>
+        <v>-0.1702</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>-0.1799</v>
+        <v>-0.198</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>-0.2218</v>
+        <v>-0.2296</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>-0.0703</v>
+        <v>-0.06269999999999999</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="K47" s="7" t="n">
         <v>0.5749</v>
@@ -3225,31 +3225,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>8.119999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>-0.0436</v>
+        <v>0.0222</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>-0.0825</v>
+        <v>-0.0247</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>-0.1697</v>
+        <v>-0.1354</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-0.2289</v>
+        <v>-0.2118</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-0.4558</v>
+        <v>-0.4437</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>-0.4583</v>
+        <v>-0.4252</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>7.69</v>
+        <v>7.86</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>0.2088</v>
@@ -3283,31 +3283,31 @@
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>-0.005500000000000001</v>
+        <v>0.0139</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>-0.1262</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>-0.1429</v>
+        <v>-0.079</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>-0.2308</v>
+        <v>-0.2151</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>-0.25</v>
+        <v>-0.2396</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0.5094</v>
+        <v>0.5977</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="K49" s="7" t="n">
         <v>0.4183</v>
@@ -3335,57 +3335,57 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>EGGUB</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>91.55</v>
+        <v>4.75</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>-0.0224</v>
+        <v>-0.0987</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.09</v>
+        <v>-0.4077</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>-0.1752</v>
+        <v>-0.9016</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>-0.05860000000000001</v>
+        <v>-0.8841</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.2859</v>
+        <v>-0.7889</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>-0.1256</v>
+        <v>-0.8343</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>12.81</v>
+        <v>3.02</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0.4926</v>
+        <v>7.8666</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.6905</v>
+        <v>3.1929</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.7726999999999999</v>
+        <v>4.946499999999999</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.5777</v>
+        <v>1.0979</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>0.4324</v>
+        <v>0.4854</v>
       </c>
       <c r="P50" s="4" t="n">
-        <v>0.0886</v>
+        <v>0.586</v>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr"/>
@@ -3393,57 +3393,57 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>KARSN</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>8.390000000000001</v>
+        <v>470</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>-0.0444</v>
+        <v>-0.0304</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>-0.0688</v>
+        <v>-0.0581</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-0.3729</v>
+        <v>-0.1288</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>-0.2267</v>
+        <v>-0.2504</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>-0.1964</v>
+        <v>-0.289</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>-0.1799</v>
+        <v>0.0658</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>31.22</v>
+        <v>14.08</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.8458</v>
+        <v>0.3804</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>1.2698</v>
+        <v>0.3113</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>1.2002</v>
+        <v>1.725</v>
       </c>
       <c r="N51" s="7" t="n">
-        <v>2.1122</v>
+        <v>0.0848</v>
       </c>
       <c r="O51" s="7" t="n">
-        <v>0.1667</v>
+        <v>0.0184</v>
       </c>
       <c r="P51" s="7" t="n">
-        <v>0.07339999999999999</v>
+        <v>0.1216</v>
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R51" s="5" t="inlineStr"/>
@@ -3451,57 +3451,57 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>EGGUB</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>484.75</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>-0.0251</v>
+        <v>0.0038</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.0532</v>
+        <v>-0.05980000000000001</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>-0.1097</v>
+        <v>-0.1795</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>-0.204</v>
+        <v>-0.099</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.2666</v>
+        <v>-0.2832</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.07719999999999999</v>
+        <v>-0.1008</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>14.52</v>
+        <v>12.86</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0.3804</v>
+        <v>0.4926</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.3113</v>
+        <v>0.6905</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>1.725</v>
+        <v>0.7726999999999999</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.0848</v>
+        <v>0.5777</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>0.0184</v>
+        <v>0.4324</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>0.1216</v>
+        <v>0.0886</v>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr"/>
@@ -3509,57 +3509,57 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>ZRGYO</t>
+          <t>KARSN</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>19</v>
+        <v>8.34</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0774</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-0.049</v>
+        <v>-0.4224</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>0.09759999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>-0.1038</v>
+        <v>-0.2011</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>-0.1457</v>
+        <v>-0.1533</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>14.38</v>
+        <v>31.04</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>2.3363</v>
+        <v>0.8458</v>
       </c>
       <c r="L53" s="7" t="n">
-        <v>3.5944</v>
+        <v>1.2698</v>
       </c>
       <c r="M53" s="7" t="n">
-        <v>3.6478</v>
+        <v>1.2002</v>
       </c>
       <c r="N53" s="7" t="n">
-        <v>0.2899</v>
+        <v>2.1122</v>
       </c>
       <c r="O53" s="7" t="n">
-        <v>0.5917</v>
+        <v>0.1667</v>
       </c>
       <c r="P53" s="7" t="n">
-        <v>0.0776</v>
+        <v>0.07339999999999999</v>
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R53" s="5" t="inlineStr"/>
@@ -3567,57 +3567,57 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ARASE</t>
+          <t>ZRGYO</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>95.3</v>
+        <v>18.4</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>-0.0073</v>
+        <v>-0.0316</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>-0.0175</v>
+        <v>-0.0113</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>-0.2156</v>
+        <v>-0.066</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>-0.2296</v>
+        <v>0.0425</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-0.062</v>
+        <v>-0.1321</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>0.8015000000000001</v>
+        <v>-0.1771</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>8.69</v>
+        <v>13.93</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0.1264</v>
+        <v>2.3363</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.596</v>
+        <v>3.5944</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.7123999999999999</v>
+        <v>3.6478</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>4.0303</v>
+        <v>0.2899</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>0.25</v>
+        <v>0.5917</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>0.1463</v>
+        <v>0.0776</v>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr"/>
@@ -3625,57 +3625,57 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>GESAN</t>
+          <t>ARASE</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>36.8</v>
+        <v>95</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>-0.05980000000000001</v>
+        <v>-0.0031</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>-0.1238</v>
+        <v>-0.0301</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-0.3932</v>
+        <v>-0.2024</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>-0.5448</v>
+        <v>-0.2613</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>-0.212</v>
+        <v>-0.065</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>-0.1333</v>
+        <v>0.8887</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>9.890000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>0.2641</v>
+        <v>0.1264</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>0.2931</v>
+        <v>0.596</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>0.3273</v>
+        <v>0.7123999999999999</v>
       </c>
       <c r="N55" s="7" t="n">
-        <v>0.4479</v>
+        <v>4.0303</v>
       </c>
       <c r="O55" s="7" t="n">
-        <v>0.1778</v>
+        <v>0.25</v>
       </c>
       <c r="P55" s="7" t="n">
-        <v>0.1266</v>
+        <v>0.1463</v>
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R55" s="5" t="inlineStr"/>
@@ -3683,57 +3683,57 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>GESAN</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>5.27</v>
+        <v>36.8</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.09910000000000001</v>
+        <v>0</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.4085</v>
+        <v>-0.0795</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>-0.8891</v>
+        <v>-0.3977000000000001</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>-0.8724</v>
+        <v>-0.5474</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.7658</v>
+        <v>-0.212</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>-0.8009999999999999</v>
+        <v>-0.1259</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>3.35</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>7.8666</v>
+        <v>0.2641</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>3.1929</v>
+        <v>0.2931</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>4.946499999999999</v>
+        <v>0.3273</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>1.0979</v>
+        <v>0.4479</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>0.4854</v>
+        <v>0.1778</v>
       </c>
       <c r="P56" s="4" t="n">
-        <v>0.586</v>
+        <v>0.1266</v>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr"/>
@@ -3741,57 +3741,57 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>CIMSA</t>
+          <t>GRTHO</t>
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>40.28</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>0.0075</v>
+        <v>-0.1</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>-0.0336</v>
+        <v>-0.3029</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-0.1124</v>
+        <v>-0.6591</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>-0.124</v>
+        <v>-0.6806</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>-0.2335</v>
+        <v>-0.6856</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>-0.07400000000000001</v>
+        <v>-0.8706999999999999</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>9.539999999999999</v>
+        <v>5.58</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>0.3754999999999999</v>
+        <v>0.5085000000000001</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>0.3037</v>
+        <v>0.4487</v>
       </c>
       <c r="M57" s="7" t="n">
-        <v>0.4933</v>
+        <v>0.2298</v>
       </c>
       <c r="N57" s="7" t="n">
-        <v>1.15</v>
+        <v>0.9399</v>
       </c>
       <c r="O57" s="7" t="n">
-        <v>0.1807</v>
+        <v>0.1089</v>
       </c>
       <c r="P57" s="7" t="n">
-        <v>0.2729</v>
+        <v>0.2287</v>
       </c>
       <c r="Q57" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R57" s="5" t="inlineStr"/>
@@ -3799,53 +3799,53 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>CMENT</t>
+          <t>CIMSA</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>217.1</v>
+        <v>39.84</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>-0.0561</v>
+        <v>-0.0109</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>-0.0916</v>
+        <v>-0.0264</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>-0.1242</v>
+        <v>-0.1115</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>-0.2787</v>
+        <v>-0.1683</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-0.3421</v>
+        <v>-0.2419</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>-0.3897</v>
+        <v>-0.0713</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>21.43</v>
+        <v>9.44</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0.0934</v>
+        <v>0.3754999999999999</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.1109</v>
+        <v>0.3037</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.1008</v>
+        <v>0.4933</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.4922</v>
+        <v>1.15</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>0.1647</v>
+        <v>0.1807</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.2729</v>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
@@ -3857,57 +3857,57 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>INDES</t>
+          <t>CMENT</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>11.82</v>
+        <v>219</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>0.0155</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>-0.0183</v>
+        <v>-0.07519999999999999</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-0.0008</v>
+        <v>-0.124</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>0.0944</v>
+        <v>-0.2474</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>0.2534</v>
+        <v>-0.3364</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>0.5232</v>
+        <v>-0.4036999999999999</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>9.970000000000001</v>
+        <v>21.62</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>0.6297</v>
+        <v>0.0934</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>0.8554999999999999</v>
+        <v>0.1109</v>
       </c>
       <c r="M59" s="7" t="n">
-        <v>1.0205</v>
+        <v>0.1008</v>
       </c>
       <c r="N59" s="7" t="n">
-        <v>1.9437</v>
+        <v>0.4922</v>
       </c>
       <c r="O59" s="7" t="n">
-        <v>0.0374</v>
+        <v>0.1647</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>0.137</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R59" s="5" t="inlineStr"/>
@@ -3919,31 +3919,31 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>17.24</v>
+        <v>17.12</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>-0.0491</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>-0.0761</v>
+        <v>-0.0536</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>-0.4295</v>
+        <v>-0.4189</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>-0.5534</v>
+        <v>-0.5670000000000001</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-0.5235</v>
+        <v>-0.5268</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>-0.2738</v>
+        <v>-0.2184</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>6.41</v>
+        <v>6.37</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>0.5809000000000001</v>
@@ -3977,31 +3977,31 @@
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>0.0024</v>
+        <v>-0.0119</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>0.0072</v>
+        <v>0.0204</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>-0.1938</v>
+        <v>-0.2099</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0566</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>0.042</v>
+        <v>0.0297</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>0.1469</v>
+        <v>0.1671</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>18.72</v>
+        <v>18.5</v>
       </c>
       <c r="K61" s="7" t="n">
         <v>0.4327</v>
@@ -4031,55 +4031,57 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>BYDNR</t>
+          <t>INDES</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>21.6</v>
+        <v>11.97</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0.0127</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>-0.0314</v>
+        <v>0.0593</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>-0.3843</v>
+        <v>0.0266</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>-0.4331</v>
+        <v>0.0697</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-0.4444</v>
+        <v>0.2694</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>0.0256</v>
+        <v>0.5545</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr"/>
+        <v>1.06</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>10.09</v>
+      </c>
       <c r="K62" s="4" t="n">
-        <v>0.2762</v>
+        <v>0.6297</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.0636</v>
+        <v>0.8554999999999999</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.127</v>
+        <v>1.0205</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0.7182999999999999</v>
+        <v>1.9437</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>0.1081</v>
+        <v>0.0374</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>-0.0257</v>
+        <v>0.137</v>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr"/>
@@ -4087,57 +4089,57 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>RALYH</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>10.18</v>
+        <v>26.88</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>-0.0136</v>
+        <v>-0.0998</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>-0.0183</v>
+        <v>-0.4087</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-0.1054</v>
+        <v>-0.9004000000000001</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>-0.1517</v>
+        <v>-0.8831</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>-0.0521</v>
+        <v>-0.9159</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>-0.1453</v>
+        <v>-0.8454999999999999</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>6.83</v>
+        <v>3.48</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>0.423</v>
+        <v>0.7070000000000001</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>0.5552</v>
+        <v>1.4848</v>
       </c>
       <c r="M63" s="7" t="n">
-        <v>0.8170999999999999</v>
+        <v>1.5369</v>
       </c>
       <c r="N63" s="7" t="n">
-        <v>10.0728</v>
+        <v>0.5434</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>0.179</v>
+        <v>0.2854</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>0.2236</v>
+        <v>0.3914</v>
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R63" s="5" t="inlineStr"/>
@@ -4145,57 +4147,55 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GRTHO</t>
+          <t>BYDNR</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>89</v>
+        <v>21.5</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.09960000000000001</v>
+        <v>-0.0046</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.2294</v>
+        <v>0.018</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>-0.6096</v>
+        <v>-0.3882</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>-0.6375</v>
+        <v>-0.4546</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.6506000000000001</v>
+        <v>-0.447</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>-0.8506999999999999</v>
+        <v>0.0287</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="J64" s="3" t="n">
-        <v>6.19</v>
-      </c>
+        <v>1.07</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="4" t="n">
-        <v>0.5085000000000001</v>
+        <v>0.2762</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.4487</v>
+        <v>0.0636</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.2298</v>
+        <v>0.127</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.9399</v>
+        <v>0.7182999999999999</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>0.1089</v>
+        <v>0.1081</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>0.2287</v>
+        <v>-0.0257</v>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr"/>
@@ -4203,57 +4203,57 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>ISDMR</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>61.35</v>
+        <v>10.19</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>-0.0168</v>
+        <v>0.001</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>-0.0097</v>
+        <v>-0.0192</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>0.0276</v>
+        <v>-0.0803</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>0.1014</v>
+        <v>-0.1592</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>0.3994</v>
+        <v>-0.0512</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>0.6808</v>
+        <v>-0.1014</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>14.46</v>
+        <v>6.84</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>0.1859</v>
+        <v>0.423</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>0.3543</v>
+        <v>0.5552</v>
       </c>
       <c r="M65" s="7" t="n">
-        <v>0.4035</v>
+        <v>0.8170999999999999</v>
       </c>
       <c r="N65" s="7" t="n">
-        <v>0.208</v>
+        <v>10.0728</v>
       </c>
       <c r="O65" s="7" t="n">
-        <v>0.1056</v>
+        <v>0.179</v>
       </c>
       <c r="P65" s="7" t="n">
-        <v>0.0859</v>
+        <v>0.2236</v>
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R65" s="5" t="inlineStr"/>
@@ -4261,57 +4261,57 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>MOBTL</t>
+          <t>ISDMR</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>10.63</v>
+        <v>61.25</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.028</v>
+        <v>-0.0016</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>0.04219999999999999</v>
+        <v>-0.02</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>-0.1916</v>
+        <v>0.0208</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>-0.2472</v>
+        <v>0.0506</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.2252</v>
+        <v>0.3971</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>0.5078</v>
+        <v>0.6939</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>15.07</v>
+        <v>14.44</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0.5631</v>
+        <v>0.1859</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.4406</v>
+        <v>0.3543</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.5064</v>
+        <v>0.4035</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>1.6818</v>
+        <v>0.208</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.1056</v>
       </c>
       <c r="P66" s="4" t="n">
-        <v>0.08689999999999999</v>
+        <v>0.0859</v>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr"/>
@@ -4319,57 +4319,57 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>MAALT</t>
+          <t>MOBTL</t>
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>773</v>
+        <v>10.48</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>-0.0325</v>
+        <v>-0.0141</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>-0.09849999999999999</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>-0.2331</v>
+        <v>-0.1683</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>-0.303</v>
+        <v>-0.2697</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>-0.484</v>
+        <v>-0.2362</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>-0.2392</v>
+        <v>0.4886</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>1665.59</v>
+        <v>14.85</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>0.248</v>
+        <v>0.5631</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>3.5256</v>
+        <v>0.4406</v>
       </c>
       <c r="M67" s="7" t="n">
-        <v>0.3863</v>
+        <v>0.5064</v>
       </c>
       <c r="N67" s="7" t="n">
-        <v>0.9832</v>
+        <v>1.6818</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>0.4575</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="P67" s="7" t="n">
-        <v>-0</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R67" s="5" t="inlineStr"/>
@@ -4381,31 +4381,31 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>79.75</v>
+        <v>77.8</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.0112</v>
+        <v>-0.0245</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>-0.0392</v>
+        <v>-0.0371</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>-0.1178</v>
+        <v>-0.1288</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>-0.1163</v>
+        <v>-0.1557</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-0.2317</v>
+        <v>-0.2505</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>0.1458</v>
+        <v>0.1194</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>11.98</v>
+        <v>11.69</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>0.4381</v>
@@ -4435,55 +4435,57 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>OBASE</t>
+          <t>NTGAZ</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>21.04</v>
+        <v>10.24</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.0097</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>-0.2178</v>
+        <v>-0.043</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>-0.4149</v>
+        <v>-0.0906</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>-0.4979</v>
+        <v>-0.1134</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>-0.4457</v>
+        <v>-0.1782</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>-0.4016</v>
+        <v>0.107</v>
       </c>
       <c r="I69" s="6" t="n">
         <v>1.18</v>
       </c>
-      <c r="J69" s="5" t="inlineStr"/>
+      <c r="J69" s="6" t="n">
+        <v>6.51</v>
+      </c>
       <c r="K69" s="7" t="n">
-        <v>0.2041</v>
+        <v>0.3448</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>0.3021</v>
+        <v>0.3645</v>
       </c>
       <c r="M69" s="7" t="n">
-        <v>0.5156000000000001</v>
+        <v>0.4084</v>
       </c>
       <c r="N69" s="7" t="n">
-        <v>0.4873</v>
+        <v>0.5755</v>
       </c>
       <c r="O69" s="7" t="n">
-        <v>0.2465</v>
+        <v>0.2148</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>0.1432</v>
+        <v>0.2137</v>
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R69" s="5" t="inlineStr"/>
@@ -4491,57 +4493,57 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>RALYH</t>
+          <t>MAALT</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>29.86</v>
+        <v>785</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>-0.09949999999999999</v>
+        <v>0.0155</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>-0.4087</v>
+        <v>-0.0374</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>-0.8865999999999999</v>
+        <v>-0.2341</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>-0.8641</v>
+        <v>-0.2864</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>-0.9066</v>
+        <v>-0.476</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>-0.8275</v>
+        <v>-0.2228</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>1.18</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>3.87</v>
+        <v>1691.45</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0.7070000000000001</v>
+        <v>0.248</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>1.4848</v>
+        <v>3.5256</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>1.5369</v>
+        <v>0.3863</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.5434</v>
+        <v>0.9832</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>0.2854</v>
+        <v>0.4575</v>
       </c>
       <c r="P70" s="4" t="n">
-        <v>0.3914</v>
+        <v>-0</v>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr"/>
@@ -4549,57 +4551,57 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>NTGAZ</t>
+          <t>SELEC</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>10.34</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>-0.0162</v>
+        <v>-0.0035</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>-0.07429999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>-0.0858</v>
+        <v>-0.7544</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.7001000000000001</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>-0.1701</v>
+        <v>-0.1931</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>0.09420000000000001</v>
+        <v>-0.0428</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>6.57</v>
+        <v>21.84</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>0.3448</v>
+        <v>0.3781</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>0.3645</v>
+        <v>0.6063000000000001</v>
       </c>
       <c r="M71" s="7" t="n">
-        <v>0.4084</v>
+        <v>1.4267</v>
       </c>
       <c r="N71" s="7" t="n">
-        <v>0.5755</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="O71" s="7" t="n">
-        <v>0.2148</v>
+        <v>0.0158</v>
       </c>
       <c r="P71" s="7" t="n">
-        <v>0.2137</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R71" s="5" t="inlineStr"/>
@@ -4611,31 +4613,31 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>271.25</v>
+        <v>271</v>
       </c>
       <c r="C72" s="4" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>-0.0154</v>
+      </c>
+      <c r="E72" s="4" t="n">
         <v>0.0112</v>
       </c>
-      <c r="D72" s="4" t="n">
-        <v>-0.0136</v>
-      </c>
-      <c r="E72" s="4" t="n">
-        <v>-0.0018</v>
-      </c>
       <c r="F72" s="4" t="n">
-        <v>0.0443</v>
+        <v>0.0009</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>-0.1327</v>
+        <v>-0.1335</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>0.1647</v>
+        <v>0.2268</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>18.68</v>
+        <v>18.67</v>
       </c>
       <c r="K72" s="4" t="n">
         <v>0.3707</v>
@@ -4665,57 +4667,57 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>SELEC</t>
+          <t>GEDIK</t>
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>71.90000000000001</v>
+        <v>4.86</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>-0.0238</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>-0.0323</v>
+        <v>-0.0471</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-0.7781</v>
+        <v>-0.1243</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>-0.6717</v>
+        <v>-0.2811</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>-0.1903</v>
+        <v>-0.1706</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>-0.0413</v>
+        <v>-0.3077</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>21.92</v>
+        <v>5.14</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>0.3781</v>
+        <v>0.6583</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>0.6063000000000001</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="M73" s="7" t="n">
-        <v>1.4267</v>
+        <v>0.7293999999999999</v>
       </c>
       <c r="N73" s="7" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.3481</v>
       </c>
       <c r="O73" s="7" t="n">
-        <v>0.0158</v>
+        <v>0.6628000000000001</v>
       </c>
       <c r="P73" s="7" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.275</v>
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R73" s="5" t="inlineStr"/>
@@ -4723,55 +4725,55 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>YKSLN</t>
+          <t>OBASE</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>2.43</v>
+        <v>21.98</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>0.09949999999999999</v>
+        <v>0.0447</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>-0.1164</v>
+        <v>-0.1623</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>-0.4214</v>
+        <v>-0.377</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>-0.2636</v>
+        <v>-0.4998</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-0.2286</v>
+        <v>-0.421</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>-0.2957</v>
+        <v>-0.3773</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="4" t="n">
-        <v>0.1126</v>
+        <v>0.2041</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.0263</v>
+        <v>0.3021</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.6127</v>
+        <v>0.5156000000000001</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.8754000000000001</v>
+        <v>0.4873</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>0.1443</v>
+        <v>0.2465</v>
       </c>
       <c r="P74" s="4" t="n">
-        <v>-0.04969999999999999</v>
+        <v>0.1432</v>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr"/>
@@ -4779,53 +4781,53 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>GEDIK</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>4.84</v>
+        <v>29.62</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>-0.0062</v>
+        <v>0.02</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>-0.051</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-0.1418</v>
+        <v>-0.1527</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>-0.2711</v>
+        <v>-0.1999</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>-0.1741</v>
+        <v>-0.3237</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>-0.3086</v>
+        <v>-0.2505</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>5.12</v>
+        <v>6.61</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>0.6583</v>
+        <v>0.4021</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.2915</v>
       </c>
       <c r="M75" s="7" t="n">
-        <v>0.7293999999999999</v>
+        <v>0.201</v>
       </c>
       <c r="N75" s="7" t="n">
-        <v>0.3481</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="O75" s="7" t="n">
-        <v>0.6628000000000001</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="P75" s="7" t="n">
-        <v>0.275</v>
+        <v>0.298</v>
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
@@ -4837,53 +4839,53 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>GLCVY</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>29.04</v>
+        <v>37.78</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>0</v>
+        <v>0.0069</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>-0.0352</v>
+        <v>-0.0347</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>-0.1829</v>
+        <v>-0.2756</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>-0.1741</v>
+        <v>-0.3229</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.337</v>
+        <v>-0.3682</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>-0.2722</v>
+        <v>-0.4219</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>6.49</v>
+        <v>3.66</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0.4021</v>
+        <v>0.265</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.2915</v>
+        <v>0.2739</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.201</v>
+        <v>0.2851</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.0788</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>0.8484999999999999</v>
+        <v>0.7251000000000001</v>
       </c>
       <c r="P76" s="4" t="n">
-        <v>0.298</v>
+        <v>0.4011</v>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
@@ -4895,57 +4897,57 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>GLCVY</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B77" s="6" t="n">
-        <v>37.52</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>-0.0152</v>
+        <v>-0.0206</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>-0.0745</v>
+        <v>-0.0049</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-0.2967</v>
+        <v>-0.0864</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>-0.3282</v>
+        <v>-0.3061</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>-0.3726</v>
+        <v>-0.1271</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>-0.44</v>
+        <v>0.5952000000000001</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>3.63</v>
+        <v>26.28</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>0.265</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>0.2739</v>
+        <v>0.3716</v>
       </c>
       <c r="M77" s="7" t="n">
-        <v>0.2851</v>
+        <v>0.4119</v>
       </c>
       <c r="N77" s="7" t="n">
-        <v>0.0788</v>
+        <v>0.9691</v>
       </c>
       <c r="O77" s="7" t="n">
-        <v>0.7251000000000001</v>
+        <v>0.3037</v>
       </c>
       <c r="P77" s="7" t="n">
-        <v>0.4011</v>
+        <v>0.0601</v>
       </c>
       <c r="Q77" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R77" s="5" t="inlineStr"/>
@@ -4953,57 +4955,57 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>GARFA</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>22.12</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>-0.005500000000000001</v>
+        <v>-0.0116</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>0.0132</v>
+        <v>-0.0204</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>-0.08990000000000001</v>
+        <v>-0.1874</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>-0.2382</v>
+        <v>-0.2651</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>-0.1088</v>
+        <v>-0.2184</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>0.6114000000000001</v>
+        <v>-0.1073</v>
       </c>
       <c r="I78" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>26.83</v>
+        <v>3.35</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>0.3716</v>
+        <v>0.9506</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>0.4119</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>0.9691</v>
+        <v>0.5365</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>0.3037</v>
+        <v>0.914</v>
       </c>
       <c r="P78" s="4" t="n">
-        <v>0.0601</v>
+        <v>0.496</v>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr"/>
@@ -5011,55 +5013,55 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>DAGI</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
-        <v>6.01</v>
+        <v>6.28</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>0.0017</v>
+        <v>-0.0141</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>0.0562</v>
+        <v>-0.05139999999999999</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-0.3432</v>
+        <v>-0.1432</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>-0.3586</v>
+        <v>-0.2081</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>-0.0066</v>
+        <v>-0.2434</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>-0.2828</v>
+        <v>-0.2179</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="J79" s="5" t="inlineStr"/>
       <c r="K79" s="7" t="n">
-        <v>0.5429999999999999</v>
+        <v>0.3952000000000001</v>
       </c>
       <c r="L79" s="7" t="n">
-        <v>1.1389</v>
+        <v>0.4088000000000001</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>1.8634</v>
+        <v>0.4094</v>
       </c>
       <c r="N79" s="7" t="n">
-        <v>0.5748</v>
+        <v>0.7489</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>0.1561</v>
+        <v>0.7836</v>
       </c>
       <c r="P79" s="7" t="n">
-        <v>-0.0597</v>
+        <v>-0.0106</v>
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Çeşitli Hizmetler</t>
         </is>
       </c>
       <c r="R79" s="5" t="inlineStr"/>
@@ -5067,57 +5069,55 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GARFA</t>
+          <t>DAGI</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>22.38</v>
+        <v>6.08</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>-0.0071</v>
+        <v>0.0116</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>-0.0395</v>
+        <v>0.0184</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>-0.1868</v>
+        <v>-0.3214</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>-0.1599</v>
+        <v>-0.3518</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>-0.2092</v>
+        <v>0.005</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>-0.1312</v>
+        <v>-0.2494</v>
       </c>
       <c r="I80" s="3" t="n">
         <v>1.32</v>
       </c>
-      <c r="J80" s="3" t="n">
-        <v>3.39</v>
-      </c>
+      <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="4" t="n">
-        <v>0.9562999999999999</v>
+        <v>0.5429999999999999</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>0.9506</v>
+        <v>1.1389</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>0.9429999999999999</v>
+        <v>1.8634</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>0.5365</v>
+        <v>0.5748</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>0.914</v>
+        <v>0.1561</v>
       </c>
       <c r="P80" s="4" t="n">
-        <v>0.496</v>
+        <v>-0.0597</v>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr"/>
@@ -5125,55 +5125,55 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>YKSLN</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>83.40000000000001</v>
+        <v>2.67</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>-0.0358</v>
+        <v>0.09880000000000001</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>-0.0613</v>
+        <v>0.1762</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-0.2554</v>
+        <v>-0.4744</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>-0.3505</v>
+        <v>-0.1785</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>-0.2754</v>
+        <v>-0.1524</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>-0.2154</v>
+        <v>-0.2235</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="J81" s="5" t="inlineStr"/>
       <c r="K81" s="7" t="n">
-        <v>0.3957</v>
+        <v>0.1126</v>
       </c>
       <c r="L81" s="7" t="n">
-        <v>2.0344</v>
+        <v>0.0263</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>3.8494</v>
+        <v>0.6127</v>
       </c>
       <c r="N81" s="7" t="n">
-        <v>0.889</v>
+        <v>0.8754000000000001</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>0.0349</v>
+        <v>0.1443</v>
       </c>
       <c r="P81" s="7" t="n">
-        <v>-0.0175</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R81" s="5" t="inlineStr"/>
@@ -5181,55 +5181,55 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>OZYSR</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>6.37</v>
+        <v>11.4</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>-0.026</v>
+        <v>-0.0223</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>-0.0464</v>
+        <v>-0.0052</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>-0.1427</v>
+        <v>-0.0339</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>-0.1896</v>
+        <v>-0.1304</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>-0.2325</v>
+        <v>0.0295</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>-0.2241</v>
+        <v>0.4215</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>1.33</v>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="4" t="n">
-        <v>0.3952000000000001</v>
+        <v>0.161</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>0.4088000000000001</v>
+        <v>0.1742</v>
       </c>
       <c r="M82" s="4" t="n">
-        <v>0.4094</v>
+        <v>0.6839</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>0.7489</v>
+        <v>0.5105</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>0.7836</v>
+        <v>0.042</v>
       </c>
       <c r="P82" s="4" t="n">
-        <v>-0.0106</v>
+        <v>-0.0335</v>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>Çeşitli Hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R82" s="2" t="inlineStr"/>
@@ -5237,57 +5237,55 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>SARKY</t>
+          <t>ACSEL</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>18.23</v>
+        <v>84.7</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>-0.036</v>
+        <v>0.0156</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>-0.1319</v>
+        <v>-0.0059</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-0.2461</v>
+        <v>-0.2424</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>-0.2967</v>
+        <v>-0.35</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>-0.3581</v>
+        <v>-0.2641</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>0.2359</v>
+        <v>-0.1964</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="J83" s="6" t="n">
-        <v>66.8</v>
-      </c>
+        <v>1.34</v>
+      </c>
+      <c r="J83" s="5" t="inlineStr"/>
       <c r="K83" s="7" t="n">
-        <v>0.5590999999999999</v>
+        <v>0.3957</v>
       </c>
       <c r="L83" s="7" t="n">
-        <v>0.3671</v>
+        <v>2.0344</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>0.2342</v>
+        <v>3.8494</v>
       </c>
       <c r="N83" s="7" t="n">
-        <v>0.8034</v>
+        <v>0.889</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>0.0217</v>
+        <v>0.0349</v>
       </c>
       <c r="P83" s="7" t="n">
-        <v>0.0229</v>
+        <v>-0.0175</v>
       </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R83" s="5" t="inlineStr"/>
@@ -5295,55 +5293,57 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>OZYSR</t>
+          <t>KCAER</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>11.66</v>
+        <v>10.47</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>-0.0119</v>
+        <v>-0.0224</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>-0.0034</v>
+        <v>0.0029</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>-0.0635</v>
+        <v>-0.2244</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>-0.09609999999999999</v>
+        <v>-0.2301</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>0.053</v>
+        <v>-0.0974</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>0.3962</v>
+        <v>-0.1677</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr"/>
+        <v>1.35</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>30.49</v>
+      </c>
       <c r="K84" s="4" t="n">
-        <v>0.161</v>
+        <v>0.1522</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.1742</v>
+        <v>0.2873</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>0.6839</v>
+        <v>0.3247</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>0.5105</v>
+        <v>1.1982</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>0.042</v>
+        <v>0.1199</v>
       </c>
       <c r="P84" s="4" t="n">
-        <v>-0.0335</v>
+        <v>0.0508</v>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr"/>
@@ -5351,57 +5351,57 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>PCILT</t>
+          <t>SARKY</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>30.54</v>
+        <v>18.16</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>0.0033</v>
+        <v>-0.0038</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>-0.0123</v>
+        <v>-0.0786</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-0.0193</v>
+        <v>-0.2246</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>-0.0723</v>
+        <v>-0.3037</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>0.113</v>
+        <v>-0.3606</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0.4325</v>
+        <v>0.2789</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>7.02</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>0.763</v>
+        <v>0.5590999999999999</v>
       </c>
       <c r="L85" s="7" t="n">
-        <v>0.7087</v>
+        <v>0.3671</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>0.7914</v>
+        <v>0.2342</v>
       </c>
       <c r="N85" s="7" t="n">
-        <v>1.2232</v>
+        <v>0.8034</v>
       </c>
       <c r="O85" s="7" t="n">
-        <v>0.0574</v>
+        <v>0.0217</v>
       </c>
       <c r="P85" s="7" t="n">
-        <v>0.2831</v>
+        <v>0.0229</v>
       </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R85" s="5" t="inlineStr"/>
@@ -5409,57 +5409,57 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>KCAER</t>
+          <t>KTLEV</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>10.71</v>
+        <v>6.42</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>-0.0272</v>
+        <v>-0.09960000000000001</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>0.0278</v>
+        <v>-0.0016</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>-0.1972</v>
+        <v>-0.7895</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>-0.199</v>
+        <v>-0.8906000000000001</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>-0.0767</v>
+        <v>-0.7384000000000001</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>-0.1762</v>
+        <v>0.6765000000000001</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>31.19</v>
+        <v>1.56</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0.1522</v>
+        <v>3.5578</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>0.2873</v>
+        <v>3.6471</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>0.3247</v>
+        <v>5.174600000000001</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>1.1982</v>
+        <v>5.7649</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>0.1199</v>
+        <v>0.7222</v>
       </c>
       <c r="P86" s="4" t="n">
-        <v>0.0508</v>
+        <v>1.5072</v>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr"/>
@@ -5467,57 +5467,57 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>KTLEV</t>
+          <t>PCILT</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>7.13</v>
+        <v>31.18</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>-0.09970000000000001</v>
+        <v>0.021</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>-0.0083</v>
+        <v>0.0156</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>-0.7896</v>
+        <v>0.0058</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>-0.877</v>
+        <v>-0.0883</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>-0.7095</v>
+        <v>0.1363</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>0.8547</v>
+        <v>0.4919</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>1.74</v>
+        <v>7.16</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>3.5578</v>
+        <v>0.763</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>3.6471</v>
+        <v>0.7087</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>5.174600000000001</v>
+        <v>0.7914</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>5.7649</v>
+        <v>1.2232</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>0.7222</v>
+        <v>0.0574</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>1.5072</v>
+        <v>0.2831</v>
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R87" s="5" t="inlineStr"/>
@@ -5529,31 +5529,31 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>27.14</v>
+        <v>27.36</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>-0.0307</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>-0.0953</v>
+        <v>-0.063</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>-0.2954</v>
+        <v>-0.277</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>-0.4061</v>
+        <v>-0.4114</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>-0.2973</v>
+        <v>-0.2916</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>-0.3644</v>
+        <v>-0.3504</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>32.52</v>
+        <v>32.78</v>
       </c>
       <c r="K88" s="4" t="n">
         <v>0.05019999999999999</v>
@@ -5587,28 +5587,28 @@
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>9.33</v>
+        <v>9.31</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>-0.0431</v>
+        <v>-0.0021</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>-0.1801</v>
+        <v>-0.1266</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-0.2212</v>
+        <v>-0.2299</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>-0.2238</v>
+        <v>-0.2312</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>-0.2583</v>
+        <v>-0.2599</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>-0.3662</v>
+        <v>-0.357</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="J89" s="5" t="inlineStr"/>
       <c r="K89" s="7" t="n">
@@ -5643,31 +5643,31 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>31.12</v>
+        <v>30.34</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>-0.0171</v>
+        <v>-0.0251</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>-0.0825</v>
+        <v>-0.09050000000000001</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>-0.2021</v>
+        <v>-0.2037</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>-0.1422</v>
+        <v>-0.2028</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>-0.1244</v>
+        <v>-0.1463</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>0.1526</v>
+        <v>0.158</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>11.08</v>
+        <v>10.8</v>
       </c>
       <c r="K90" s="4" t="n">
         <v>0.3776</v>
@@ -5701,31 +5701,31 @@
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>391</v>
+        <v>384.5</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>0.0136</v>
+        <v>-0.0166</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>0.0216</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-0.0635</v>
+        <v>-0.07519999999999999</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>0.4415</v>
+        <v>0.3397</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>0.4603</v>
+        <v>0.436</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>1.2667</v>
+        <v>1.2098</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>10.85</v>
+        <v>10.67</v>
       </c>
       <c r="K91" s="7" t="n">
         <v>0.465</v>
@@ -5759,31 +5759,31 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>3.39</v>
+        <v>3.34</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>0.018</v>
+        <v>-0.0147</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>-0.1396</v>
+        <v>-0.1211</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>-0.3061</v>
+        <v>-0.2646</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>-0.5069</v>
+        <v>-0.5299</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>-0.5985</v>
+        <v>-0.6043999999999999</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>0.0113</v>
+        <v>0.0277</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>7.24</v>
+        <v>7.13</v>
       </c>
       <c r="K92" s="4" t="n">
         <v>0.51</v>
@@ -5817,31 +5817,31 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>11.99</v>
+        <v>11.91</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>-0.005</v>
+        <v>-0.0067</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>-0.1592</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>-0.1604</v>
+        <v>-0.1256</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>-0.4134</v>
+        <v>-0.4235</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>-0.5472</v>
+        <v>-0.5502</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>-0.4623</v>
+        <v>-0.4419</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>17.44</v>
+        <v>17.32</v>
       </c>
       <c r="K93" s="7" t="n">
         <v>0.7861</v>
@@ -5871,57 +5871,57 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GENIL</t>
+          <t>ORGE</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>5.05</v>
+        <v>22.38</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>-0.0363</v>
+        <v>-0.015</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>0.3049</v>
+        <v>0.0182</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>-0.5826</v>
+        <v>-0.0158</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>-0.4389</v>
+        <v>0.0163</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>-0.5144</v>
+        <v>0.4704</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>-0.6509</v>
+        <v>0.6701</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>18.41</v>
+        <v>10.39</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0.5049</v>
+        <v>0.251</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>0.7672</v>
+        <v>0.257</v>
       </c>
       <c r="M94" s="4" t="n">
-        <v>1.1622</v>
+        <v>0.2421</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>1.2274</v>
+        <v>0.2676</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>0.0922</v>
+        <v>0.4943</v>
       </c>
       <c r="P94" s="4" t="n">
-        <v>0.1305</v>
+        <v>0.2029</v>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr"/>
@@ -5929,57 +5929,57 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>ORGE</t>
+          <t>GENIL</t>
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>22.72</v>
+        <v>5.24</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>0</v>
+        <v>0.5014</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>-0.0122</v>
+        <v>-0.5518</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>0.0412</v>
+        <v>-0.442</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>0.4928</v>
+        <v>-0.4962</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>0.6369</v>
+        <v>-0.6203</v>
       </c>
       <c r="I95" s="6" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>10.55</v>
+        <v>19.1</v>
       </c>
       <c r="K95" s="7" t="n">
-        <v>0.251</v>
+        <v>0.5049</v>
       </c>
       <c r="L95" s="7" t="n">
-        <v>0.257</v>
+        <v>0.7672</v>
       </c>
       <c r="M95" s="7" t="n">
-        <v>0.2421</v>
+        <v>1.1622</v>
       </c>
       <c r="N95" s="7" t="n">
-        <v>0.2676</v>
+        <v>1.2274</v>
       </c>
       <c r="O95" s="7" t="n">
-        <v>0.4943</v>
+        <v>0.0922</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>0.2029</v>
+        <v>0.1305</v>
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R95" s="5" t="inlineStr"/>
@@ -5991,31 +5991,31 @@
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>23.62</v>
+        <v>24.3</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>-0.0679</v>
+        <v>0.0288</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>-0.1226</v>
+        <v>-0.083</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>-0.3232</v>
+        <v>-0.2957</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>-0.3599</v>
+        <v>-0.3411</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>-0.4089</v>
+        <v>-0.3919</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>-0.3738</v>
+        <v>-0.3254</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>13.01</v>
+        <v>13.39</v>
       </c>
       <c r="K96" s="4" t="n">
         <v>0.1436</v>
@@ -6045,55 +6045,57 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>KRPLS</t>
+          <t>FONET</t>
         </is>
       </c>
       <c r="B97" s="6" t="n">
-        <v>11.01</v>
+        <v>4.05</v>
       </c>
       <c r="C97" s="7" t="n">
-        <v>-0.008100000000000001</v>
+        <v>-0.0074</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>-0.0549</v>
+        <v>-0.0625</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>-0.1759</v>
+        <v>-0.096</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>0.2343</v>
+        <v>-0.2043</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>0.2099</v>
+        <v>-0.2105</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>0.2233</v>
+        <v>0.4138</v>
       </c>
       <c r="I97" s="6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="J97" s="5" t="inlineStr"/>
+        <v>1.81</v>
+      </c>
+      <c r="J97" s="6" t="n">
+        <v>13.16</v>
+      </c>
       <c r="K97" s="7" t="n">
-        <v>0.3576</v>
+        <v>1.0251</v>
       </c>
       <c r="L97" s="7" t="n">
-        <v>0.6872</v>
+        <v>2.0469</v>
       </c>
       <c r="M97" s="7" t="n">
-        <v>0.9115000000000001</v>
+        <v>1.6971</v>
       </c>
       <c r="N97" s="7" t="n">
-        <v>0.7781999999999999</v>
+        <v>1.6785</v>
       </c>
       <c r="O97" s="7" t="n">
-        <v>0.166</v>
+        <v>0.4396</v>
       </c>
       <c r="P97" s="7" t="n">
-        <v>-0.0342</v>
+        <v>0.8814</v>
       </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R97" s="5" t="inlineStr"/>
@@ -6101,57 +6103,55 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>FONET</t>
+          <t>KRPLS</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>4.08</v>
+        <v>11.03</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>-0.0263</v>
+        <v>0.0018</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>-0.0512</v>
+        <v>-0.0054</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>-0.1033</v>
+        <v>-0.1176</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>-0.1791</v>
+        <v>0.2148</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>-0.2047</v>
+        <v>0.2121</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>0.3394</v>
+        <v>0.1722</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="J98" s="3" t="n">
-        <v>13.26</v>
-      </c>
+        <v>1.82</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="4" t="n">
-        <v>1.0251</v>
+        <v>0.3576</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>2.0469</v>
+        <v>0.6872</v>
       </c>
       <c r="M98" s="4" t="n">
-        <v>1.6971</v>
+        <v>0.9115000000000001</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>1.6785</v>
+        <v>0.7781999999999999</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>0.4396</v>
+        <v>0.166</v>
       </c>
       <c r="P98" s="4" t="n">
-        <v>0.8814</v>
+        <v>-0.0342</v>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr"/>
@@ -6159,57 +6159,57 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>ENERY</t>
+          <t>SAYAS</t>
         </is>
       </c>
       <c r="B99" s="6" t="n">
-        <v>14.04</v>
+        <v>37.7</v>
       </c>
       <c r="C99" s="7" t="n">
-        <v>-0.029</v>
+        <v>-0.011</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>0.0137</v>
+        <v>-0.0348</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>0.1518</v>
+        <v>-0.2637</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>0.4111</v>
+        <v>-0.2063</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>0.5294</v>
+        <v>-0.1365</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>0.4283</v>
+        <v>-0.2557</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>22.39</v>
+        <v>15.02</v>
       </c>
       <c r="K99" s="7" t="n">
-        <v>0.4279</v>
+        <v>0.486</v>
       </c>
       <c r="L99" s="7" t="n">
-        <v>0.7162999999999999</v>
+        <v>1.4655</v>
       </c>
       <c r="M99" s="7" t="n">
-        <v>0.8373999999999999</v>
+        <v>2.3632</v>
       </c>
       <c r="N99" s="7" t="n">
-        <v>0.6103000000000001</v>
+        <v>6.118200000000001</v>
       </c>
       <c r="O99" s="7" t="n">
-        <v>0.2099</v>
+        <v>0.1798</v>
       </c>
       <c r="P99" s="7" t="n">
-        <v>0.1017</v>
+        <v>0.1493</v>
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R99" s="5" t="inlineStr"/>
@@ -6221,31 +6221,31 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>426.75</v>
+        <v>427.5</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>-0.0064</v>
+        <v>0.0018</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>0</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>-0.0323</v>
+        <v>-0.0217</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>0.0314</v>
+        <v>-0.0121</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>-0.0682</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>0.2777</v>
+        <v>0.2648</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>1.86</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>13.33</v>
+        <v>13.35</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>0.3601</v>
@@ -6275,57 +6275,55 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>SAYAS</t>
+          <t>DURDO</t>
         </is>
       </c>
       <c r="B101" s="6" t="n">
-        <v>38.12</v>
+        <v>6.31</v>
       </c>
       <c r="C101" s="7" t="n">
-        <v>-0.0241</v>
+        <v>-0.0999</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>-0.0639</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>-0.2941</v>
+        <v>0.2158</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>-0.1644</v>
+        <v>0.2397</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>-0.1269</v>
+        <v>0.4847</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>-0.2711</v>
+        <v>0.8559</v>
       </c>
       <c r="I101" s="6" t="n">
         <v>1.87</v>
       </c>
-      <c r="J101" s="6" t="n">
-        <v>15.19</v>
-      </c>
+      <c r="J101" s="5" t="inlineStr"/>
       <c r="K101" s="7" t="n">
-        <v>0.486</v>
+        <v>0.3099</v>
       </c>
       <c r="L101" s="7" t="n">
-        <v>1.4655</v>
+        <v>0.2862</v>
       </c>
       <c r="M101" s="7" t="n">
-        <v>2.3632</v>
+        <v>0.3279</v>
       </c>
       <c r="N101" s="7" t="n">
-        <v>6.118200000000001</v>
+        <v>0.1519</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>0.1798</v>
+        <v>0.0876</v>
       </c>
       <c r="P101" s="7" t="n">
-        <v>0.1493</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R101" s="5" t="inlineStr"/>
@@ -6337,31 +6335,31 @@
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>250.25</v>
+        <v>246.25</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>-0.0393</v>
+        <v>-0.0158</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>-0.0766</v>
+        <v>-0.0617</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>-0.1517</v>
+        <v>-0.1411</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>-0.1371</v>
+        <v>-0.1871</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>-0.1326</v>
+        <v>-0.1463</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>-0.0205</v>
+        <v>-0.0207</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>9.84</v>
+        <v>9.69</v>
       </c>
       <c r="K102" s="4" t="n">
         <v>1.7224</v>
@@ -6391,57 +6389,57 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>ENERY</t>
         </is>
       </c>
       <c r="B103" s="6" t="n">
-        <v>16.89</v>
+        <v>14.5</v>
       </c>
       <c r="C103" s="7" t="n">
-        <v>-0.0134</v>
+        <v>0.0328</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>0.4424</v>
+        <v>0.032</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>-0.2998</v>
+        <v>0.1694</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>-0.5489000000000001</v>
+        <v>0.4857</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>-0.4359</v>
+        <v>0.5795</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>0.3882</v>
+        <v>0.5393</v>
       </c>
       <c r="I103" s="6" t="n">
         <v>1.92</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>2.18</v>
+        <v>23.12</v>
       </c>
       <c r="K103" s="7" t="n">
-        <v>2.1748</v>
+        <v>0.4279</v>
       </c>
       <c r="L103" s="7" t="n">
-        <v>2.2285</v>
+        <v>0.7162999999999999</v>
       </c>
       <c r="M103" s="7" t="n">
-        <v>2.5519</v>
+        <v>0.8373999999999999</v>
       </c>
       <c r="N103" s="7" t="n">
-        <v>7.8348</v>
+        <v>0.6103000000000001</v>
       </c>
       <c r="O103" s="7" t="n">
-        <v>0.887</v>
+        <v>0.2099</v>
       </c>
       <c r="P103" s="7" t="n">
-        <v>1.1538</v>
+        <v>0.1017</v>
       </c>
       <c r="Q103" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R103" s="5" t="inlineStr"/>
@@ -6449,57 +6447,57 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>AHGAZ</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>47.16</v>
+        <v>17.3</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>-0.0109</v>
+        <v>0.0243</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>0.0021</v>
+        <v>0.3432</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>0.1633</v>
+        <v>-0.2478</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>0.2603</v>
+        <v>-0.5739</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>0.8925</v>
+        <v>-0.4222</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>0.7676000000000001</v>
+        <v>0.2683</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>22.32</v>
+        <v>2.23</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0.659</v>
+        <v>2.1748</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>1.7979</v>
+        <v>2.2285</v>
       </c>
       <c r="M104" s="4" t="n">
-        <v>2.1313</v>
+        <v>2.5519</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>2.8917</v>
+        <v>7.8348</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>0.1977</v>
+        <v>0.887</v>
       </c>
       <c r="P104" s="4" t="n">
-        <v>0.1152</v>
+        <v>1.1538</v>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr"/>
@@ -6507,57 +6505,57 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>GLYHO</t>
+          <t>SANEL</t>
         </is>
       </c>
       <c r="B105" s="6" t="n">
-        <v>17.71</v>
+        <v>28.26</v>
       </c>
       <c r="C105" s="7" t="n">
-        <v>0.0034</v>
+        <v>-0.0355</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>0.051</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>0.0579</v>
+        <v>-0.393</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>0.0387</v>
+        <v>-0.6303</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>0.1195</v>
+        <v>-0.215</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>0.6964</v>
+        <v>0.0329</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="J105" s="6" t="n">
-        <v>5.91</v>
+        <v>2.72</v>
       </c>
       <c r="K105" s="7" t="n">
-        <v>0.2312</v>
+        <v>0.309</v>
       </c>
       <c r="L105" s="7" t="n">
-        <v>0.317</v>
+        <v>1.4614</v>
       </c>
       <c r="M105" s="7" t="n">
-        <v>0.3503</v>
+        <v>1.5381</v>
       </c>
       <c r="N105" s="7" t="n">
-        <v>0.4888</v>
+        <v>2.2148</v>
       </c>
       <c r="O105" s="7" t="n">
-        <v>0.3457</v>
+        <v>0.1491</v>
       </c>
       <c r="P105" s="7" t="n">
-        <v>-0.2226</v>
+        <v>1.0947</v>
       </c>
       <c r="Q105" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R105" s="5" t="inlineStr"/>
@@ -6565,57 +6563,57 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>SANEL</t>
+          <t>GLYHO</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>29.3</v>
+        <v>17.41</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>0.0266</v>
+        <v>-0.0169</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.0284</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>-0.3707</v>
+        <v>0.0616</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>-0.636</v>
+        <v>-0.0029</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>-0.1861</v>
+        <v>0.1005</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>0.0375</v>
+        <v>0.7170000000000001</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>2.82</v>
+        <v>5.81</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0.309</v>
+        <v>0.2312</v>
       </c>
       <c r="L106" s="4" t="n">
-        <v>1.4614</v>
+        <v>0.317</v>
       </c>
       <c r="M106" s="4" t="n">
-        <v>1.5381</v>
+        <v>0.3503</v>
       </c>
       <c r="N106" s="4" t="n">
-        <v>2.2148</v>
+        <v>0.4888</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>0.1491</v>
+        <v>0.3457</v>
       </c>
       <c r="P106" s="4" t="n">
-        <v>1.0947</v>
+        <v>-0.2226</v>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr"/>
@@ -6623,57 +6621,57 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>AHGAZ</t>
         </is>
       </c>
       <c r="B107" s="6" t="n">
-        <v>210</v>
+        <v>47.9</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>-0.0536</v>
+        <v>0.0157</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>-0.0663</v>
+        <v>-0.0042</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>-0.1052</v>
+        <v>0.1746</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>-0.1003</v>
+        <v>0.3225</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>-0.1837</v>
+        <v>0.9222</v>
       </c>
       <c r="H107" s="7" t="n">
-        <v>-0.083</v>
+        <v>0.9023</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="J107" s="6" t="n">
-        <v>19.63</v>
+        <v>22.67</v>
       </c>
       <c r="K107" s="7" t="n">
-        <v>0.493</v>
+        <v>0.659</v>
       </c>
       <c r="L107" s="7" t="n">
-        <v>0.3835</v>
+        <v>1.7979</v>
       </c>
       <c r="M107" s="7" t="n">
-        <v>0.4282</v>
+        <v>2.1313</v>
       </c>
       <c r="N107" s="7" t="n">
-        <v>0.1825</v>
+        <v>2.8917</v>
       </c>
       <c r="O107" s="7" t="n">
-        <v>0.2029</v>
+        <v>0.1977</v>
       </c>
       <c r="P107" s="7" t="n">
-        <v>0.1296</v>
+        <v>0.1152</v>
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R107" s="5" t="inlineStr"/>
@@ -6681,55 +6679,57 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>DURDO</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>7.01</v>
+        <v>209.8</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>0.0987</v>
+        <v>-0.001</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>0.09359999999999999</v>
+        <v>-0.0717</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>0.3378</v>
+        <v>-0.0953</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>0.3799</v>
+        <v>-0.1023</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>0.6494</v>
+        <v>-0.1845</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>1.0202</v>
+        <v>-0.1095</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="J108" s="2" t="inlineStr"/>
+        <v>2.05</v>
+      </c>
+      <c r="J108" s="3" t="n">
+        <v>19.61</v>
+      </c>
       <c r="K108" s="4" t="n">
-        <v>0.3099</v>
+        <v>0.493</v>
       </c>
       <c r="L108" s="4" t="n">
-        <v>0.2862</v>
+        <v>0.3835</v>
       </c>
       <c r="M108" s="4" t="n">
-        <v>0.3279</v>
+        <v>0.4282</v>
       </c>
       <c r="N108" s="4" t="n">
-        <v>0.1519</v>
+        <v>0.1825</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>0.0876</v>
+        <v>0.2029</v>
       </c>
       <c r="P108" s="4" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.1296</v>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr"/>
@@ -6737,57 +6737,57 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>GRSEL</t>
+          <t>VBTYZ</t>
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>287.25</v>
+        <v>21.04</v>
       </c>
       <c r="C109" s="7" t="n">
-        <v>-0.0026</v>
+        <v>-0.0349</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>0.0464</v>
+        <v>-0.0723</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>-0.0369</v>
+        <v>-0.3738</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>-0.0974</v>
+        <v>-0.2804</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>-0.09669999999999999</v>
+        <v>-0.0196</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>-0.1746</v>
+        <v>0.1631</v>
       </c>
       <c r="I109" s="6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="J109" s="6" t="n">
-        <v>8.720000000000001</v>
+        <v>13.77</v>
       </c>
       <c r="K109" s="7" t="n">
-        <v>0.3337</v>
+        <v>0.5342</v>
       </c>
       <c r="L109" s="7" t="n">
-        <v>0.6940999999999999</v>
+        <v>0.9976999999999999</v>
       </c>
       <c r="M109" s="7" t="n">
-        <v>0.2722</v>
+        <v>3.6408</v>
       </c>
       <c r="N109" s="7" t="n">
-        <v>0.7318000000000001</v>
+        <v>1.3528</v>
       </c>
       <c r="O109" s="7" t="n">
-        <v>0.3275</v>
+        <v>0.2074</v>
       </c>
       <c r="P109" s="7" t="n">
-        <v>0.3613</v>
+        <v>-9.062000000000001</v>
       </c>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R109" s="5" t="inlineStr"/>
@@ -6795,57 +6795,57 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>VBTYZ</t>
+          <t>GRSEL</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>21.8</v>
+        <v>290</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>-0.04389999999999999</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>-0.1087</v>
+        <v>0.0761</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>-0.3944</v>
+        <v>-0.0244</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>-0.2399</v>
+        <v>-0.0801</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>0.0158</v>
+        <v>-0.08810000000000001</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>0.1945</v>
+        <v>-0.157</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>14.27</v>
+        <v>8.81</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0.5342</v>
+        <v>0.3337</v>
       </c>
       <c r="L110" s="4" t="n">
-        <v>0.9976999999999999</v>
+        <v>0.6940999999999999</v>
       </c>
       <c r="M110" s="4" t="n">
-        <v>3.6408</v>
+        <v>0.2722</v>
       </c>
       <c r="N110" s="4" t="n">
-        <v>1.3528</v>
+        <v>0.7318000000000001</v>
       </c>
       <c r="O110" s="4" t="n">
-        <v>0.2074</v>
+        <v>0.3275</v>
       </c>
       <c r="P110" s="4" t="n">
-        <v>-9.062000000000001</v>
+        <v>0.3613</v>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr"/>
@@ -6853,57 +6853,57 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>BIMAS</t>
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>46.16</v>
+        <v>401.5</v>
       </c>
       <c r="C111" s="7" t="n">
-        <v>-0.0383</v>
+        <v>-0.0159</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>-0.1019</v>
+        <v>0.0152</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>-0.3659000000000001</v>
+        <v>-0.0641</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>-0.4902</v>
+        <v>0.0229</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>0.1569</v>
+        <v>0.0735</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>0.7618</v>
+        <v>0.4694</v>
       </c>
       <c r="I111" s="6" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="J111" s="6" t="n">
-        <v>32.72</v>
+        <v>17.56</v>
       </c>
       <c r="K111" s="7" t="n">
-        <v>0.8139</v>
+        <v>0.4214</v>
       </c>
       <c r="L111" s="7" t="n">
-        <v>1.3529</v>
+        <v>0.5271</v>
       </c>
       <c r="M111" s="7" t="n">
-        <v>2.0375</v>
+        <v>0.8381000000000001</v>
       </c>
       <c r="N111" s="7" t="n">
-        <v>1.6152</v>
+        <v>0.8737999999999999</v>
       </c>
       <c r="O111" s="7" t="n">
-        <v>0.1821</v>
+        <v>0.0611</v>
       </c>
       <c r="P111" s="7" t="n">
-        <v>0.09230000000000001</v>
+        <v>0.1613</v>
       </c>
       <c r="Q111" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R111" s="5" t="inlineStr"/>
@@ -6911,57 +6911,57 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>BIMAS</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>408</v>
+        <v>47.22</v>
       </c>
       <c r="C112" s="4" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.023</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>-0.0049</v>
+        <v>-0.0296</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>-0.0517</v>
+        <v>-0.3396</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>0.0515</v>
+        <v>-0.4634</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1835</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>0.4918</v>
+        <v>0.826</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>17.84</v>
+        <v>33.47</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0.4214</v>
+        <v>0.8139</v>
       </c>
       <c r="L112" s="4" t="n">
-        <v>0.5271</v>
+        <v>1.3529</v>
       </c>
       <c r="M112" s="4" t="n">
-        <v>0.8381000000000001</v>
+        <v>2.0375</v>
       </c>
       <c r="N112" s="4" t="n">
-        <v>0.8737999999999999</v>
+        <v>1.6152</v>
       </c>
       <c r="O112" s="4" t="n">
-        <v>0.0611</v>
+        <v>0.1821</v>
       </c>
       <c r="P112" s="4" t="n">
-        <v>0.1613</v>
+        <v>0.09230000000000001</v>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr"/>
@@ -6973,31 +6973,31 @@
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>81.05</v>
+        <v>79.75</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>-0.0311</v>
+        <v>-0.016</v>
       </c>
       <c r="D113" s="7" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0274</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>0.01</v>
+        <v>-0.0112</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>-0.0351</v>
+        <v>-0.1139</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>0.0144</v>
+        <v>-0.0019</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>0.743</v>
+        <v>0.7481</v>
       </c>
       <c r="I113" s="6" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J113" s="6" t="n">
-        <v>10.95</v>
+        <v>10.77</v>
       </c>
       <c r="K113" s="7" t="n">
         <v>0.4257</v>
@@ -7031,31 +7031,31 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>42.64</v>
+        <v>42.86</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>-0.0431</v>
+        <v>0.0052</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0343</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>-0.1985</v>
+        <v>-0.1781</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>-0.1606</v>
+        <v>-0.1774</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>-0.0759</v>
+        <v>-0.0711</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>0.7333</v>
+        <v>0.8008</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>27.23</v>
+        <v>27.37</v>
       </c>
       <c r="K114" s="4" t="n">
         <v>1.2681</v>
@@ -7089,31 +7089,31 @@
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>119.9</v>
+        <v>114.1</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>-0.026</v>
+        <v>-0.0484</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>-0.0559</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-0.1436</v>
+        <v>-0.1762</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>-0.07629999999999999</v>
+        <v>-0.1389</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>0.238</v>
+        <v>0.1781</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>1.6609</v>
+        <v>1.6486</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="J115" s="6" t="n">
-        <v>10.75</v>
+        <v>10.23</v>
       </c>
       <c r="K115" s="7" t="n">
         <v>2.4396</v>
@@ -7143,53 +7143,53 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>LOGO</t>
+          <t>HTTBT</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>132.2</v>
+        <v>32.04</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>-0.0294</v>
+        <v>-0.0154</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>-0.1187</v>
+        <v>-0.0326</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>-0.0617</v>
+        <v>-0.0664</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>-0.0258</v>
+        <v>-0.1515</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>-0.0571</v>
+        <v>-0.2174</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>-0.2027</v>
+        <v>-0.3342</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>14.38</v>
+        <v>23.38</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0.5617</v>
+        <v>0.3957</v>
       </c>
       <c r="L116" s="4" t="n">
-        <v>0.8981999999999999</v>
+        <v>0.3631</v>
       </c>
       <c r="M116" s="4" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.3492</v>
       </c>
       <c r="N116" s="4" t="n">
-        <v>267.6647</v>
+        <v>0.2572</v>
       </c>
       <c r="O116" s="4" t="n">
-        <v>0.346</v>
+        <v>0.4235</v>
       </c>
       <c r="P116" s="4" t="n">
-        <v>0.9277</v>
+        <v>0.5921</v>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
@@ -7201,53 +7201,53 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>HTTBT</t>
+          <t>LOGO</t>
         </is>
       </c>
       <c r="B117" s="6" t="n">
-        <v>32.54</v>
+        <v>133.1</v>
       </c>
       <c r="C117" s="7" t="n">
-        <v>-0.0061</v>
+        <v>0.0068</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.1067</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>-0.06709999999999999</v>
+        <v>-0.0459</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>-0.1234</v>
+        <v>-0.0228</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>-0.2052</v>
+        <v>-0.0506</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>-0.3249</v>
+        <v>-0.1943</v>
       </c>
       <c r="I117" s="6" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>23.74</v>
+        <v>14.47</v>
       </c>
       <c r="K117" s="7" t="n">
-        <v>0.3957</v>
+        <v>0.5617</v>
       </c>
       <c r="L117" s="7" t="n">
-        <v>0.3631</v>
+        <v>0.8981999999999999</v>
       </c>
       <c r="M117" s="7" t="n">
-        <v>0.3492</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="N117" s="7" t="n">
-        <v>0.2572</v>
+        <v>267.6647</v>
       </c>
       <c r="O117" s="7" t="n">
-        <v>0.4235</v>
+        <v>0.346</v>
       </c>
       <c r="P117" s="7" t="n">
-        <v>0.5921</v>
+        <v>0.9277</v>
       </c>
       <c r="Q117" s="5" t="inlineStr">
         <is>
@@ -7263,31 +7263,31 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>63</v>
+        <v>61.95</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>-0.0187</v>
+        <v>-0.0167</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>-0.0803</v>
+        <v>-0.0506</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>-0.2105</v>
+        <v>-0.1975</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>-0.0462</v>
+        <v>-0.1112</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>0.4993</v>
+        <v>0.4743</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>1.4882</v>
+        <v>1.492</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>15.69</v>
+        <v>15.43</v>
       </c>
       <c r="K118" s="4" t="n">
         <v>2.0657</v>
@@ -7321,31 +7321,31 @@
         </is>
       </c>
       <c r="B119" s="6" t="n">
-        <v>222.7</v>
+        <v>221</v>
       </c>
       <c r="C119" s="7" t="n">
-        <v>-0.0326</v>
+        <v>-0.0076</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>-0.0678</v>
+        <v>-0.0608</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>-0.1894</v>
+        <v>-0.2107</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>0.0779</v>
+        <v>0.0284</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>0.5455</v>
+        <v>0.5337</v>
       </c>
       <c r="H119" s="7" t="n">
-        <v>0.6509</v>
+        <v>0.625</v>
       </c>
       <c r="I119" s="6" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="K119" s="7" t="n">
         <v>0.3072</v>
@@ -7375,57 +7375,57 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>PKART</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>87</v>
+        <v>394.5</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>-0.05429999999999999</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>-0.045</v>
+        <v>-0.0113</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>-0.2461</v>
+        <v>-0.1777</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>-0.304</v>
+        <v>-0.06570000000000001</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>0.0169</v>
+        <v>-0.2514</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>0.0482</v>
+        <v>0.4089</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>19.24</v>
+        <v>17.1</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0.5093</v>
+        <v>0.1897</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>1.5572</v>
+        <v>0.4879</v>
       </c>
       <c r="M120" s="4" t="n">
-        <v>1.6598</v>
+        <v>0.6424</v>
       </c>
       <c r="N120" s="4" t="n">
-        <v>4.8022</v>
+        <v>0.5356000000000001</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>0.083</v>
+        <v>0.2097</v>
       </c>
       <c r="P120" s="4" t="n">
-        <v>0.2041</v>
+        <v>0.2503</v>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr"/>
@@ -7433,57 +7433,57 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>PKART</t>
         </is>
       </c>
       <c r="B121" s="6" t="n">
-        <v>391</v>
+        <v>89.2</v>
       </c>
       <c r="C121" s="7" t="n">
-        <v>-0.0369</v>
+        <v>0.0253</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>-0.0521</v>
+        <v>0.02</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-0.2129</v>
+        <v>-0.1679</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>-0.0544</v>
+        <v>-0.3053</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>-0.2581</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>0.3541</v>
+        <v>0.1081</v>
       </c>
       <c r="I121" s="6" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="J121" s="6" t="n">
-        <v>16.95</v>
+        <v>19.72</v>
       </c>
       <c r="K121" s="7" t="n">
-        <v>0.1897</v>
+        <v>0.5093</v>
       </c>
       <c r="L121" s="7" t="n">
-        <v>0.4879</v>
+        <v>1.5572</v>
       </c>
       <c r="M121" s="7" t="n">
-        <v>0.6424</v>
+        <v>1.6598</v>
       </c>
       <c r="N121" s="7" t="n">
-        <v>0.5356000000000001</v>
+        <v>4.8022</v>
       </c>
       <c r="O121" s="7" t="n">
-        <v>0.2097</v>
+        <v>0.083</v>
       </c>
       <c r="P121" s="7" t="n">
-        <v>0.2503</v>
+        <v>0.2041</v>
       </c>
       <c r="Q121" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R121" s="5" t="inlineStr"/>
@@ -7495,31 +7495,31 @@
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>18.3</v>
+        <v>18.48</v>
       </c>
       <c r="C122" s="4" t="n">
-        <v>-0.0261</v>
+        <v>0.0098</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>-0.1073</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>-0.1674</v>
+        <v>-0.1484</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>-0.2324</v>
+        <v>-0.2196</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>-0.121</v>
+        <v>-0.1124</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>0.2621</v>
+        <v>0.3162</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>3.41</v>
+        <v>3.44</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>24.1</v>
+        <v>24.34</v>
       </c>
       <c r="K122" s="4" t="n">
         <v>0.6388</v>
@@ -7549,55 +7549,57 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>OYAYO</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="B123" s="6" t="n">
-        <v>31.86</v>
+        <v>119.7</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>0.0108</v>
+        <v>-0.1</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>0.0277</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="E123" s="7" t="n">
-        <v>-0.2129</v>
+        <v>-0.1874</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>-0.3148</v>
+        <v>-0.3117</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>-0.4159</v>
+        <v>-0.1857</v>
       </c>
       <c r="H123" s="7" t="n">
-        <v>-0.0897</v>
+        <v>2.5144</v>
       </c>
       <c r="I123" s="6" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="J123" s="5" t="inlineStr"/>
+        <v>3.53</v>
+      </c>
+      <c r="J123" s="6" t="n">
+        <v>13.33</v>
+      </c>
       <c r="K123" s="7" t="n">
-        <v>0.3933</v>
+        <v>1.164</v>
       </c>
       <c r="L123" s="7" t="n">
-        <v>0.4082</v>
+        <v>0.8115000000000001</v>
       </c>
       <c r="M123" s="7" t="n">
-        <v>0.6868000000000001</v>
+        <v>1.571</v>
       </c>
       <c r="N123" s="7" t="n">
-        <v>0.2959</v>
+        <v>1.7066</v>
       </c>
       <c r="O123" s="7" t="n">
-        <v>0.7368000000000001</v>
+        <v>0.1178</v>
       </c>
       <c r="P123" s="7" t="n">
-        <v>-0.0453</v>
+        <v>0.3402000000000001</v>
       </c>
       <c r="Q123" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R123" s="5" t="inlineStr"/>
@@ -7605,57 +7607,55 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>OYAYO</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>0.035</v>
+        <v>-0.027</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>0.044</v>
+        <v>0.0197</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>-0.2528</v>
+        <v>-0.2323</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>-0.2417</v>
+        <v>-0.3542</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>-0.09519999999999999</v>
+        <v>-0.4317</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>2.8506</v>
+        <v>-0.1112</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="J124" s="3" t="n">
-        <v>14.81</v>
-      </c>
+        <v>3.57</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="4" t="n">
-        <v>1.164</v>
+        <v>0.3933</v>
       </c>
       <c r="L124" s="4" t="n">
-        <v>0.8115000000000001</v>
+        <v>0.4082</v>
       </c>
       <c r="M124" s="4" t="n">
-        <v>1.571</v>
+        <v>0.6868000000000001</v>
       </c>
       <c r="N124" s="4" t="n">
-        <v>1.7066</v>
+        <v>0.2959</v>
       </c>
       <c r="O124" s="4" t="n">
-        <v>0.1178</v>
+        <v>0.7368000000000001</v>
       </c>
       <c r="P124" s="4" t="n">
-        <v>0.3402000000000001</v>
+        <v>-0.0453</v>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr"/>
@@ -7667,31 +7667,31 @@
         </is>
       </c>
       <c r="B125" s="6" t="n">
-        <v>26.38</v>
+        <v>26.42</v>
       </c>
       <c r="C125" s="7" t="n">
-        <v>-0.0201</v>
+        <v>0.0015</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>-0.0518</v>
+        <v>-0.0393</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-0.2565</v>
+        <v>-0.2297</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>-0.3339</v>
+        <v>-0.3632</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>0.2105</v>
+        <v>0.2124</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>0.7815000000000001</v>
+        <v>0.8472</v>
       </c>
       <c r="I125" s="6" t="n">
         <v>3.98</v>
       </c>
       <c r="J125" s="6" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="K125" s="7" t="n">
         <v>1.4662</v>
@@ -7721,57 +7721,57 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>ONCSM</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>85.95</v>
+        <v>183.2</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>-0.0565</v>
+        <v>-0.0508</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>-0.1379</v>
+        <v>-0.0235</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>-0.4932</v>
+        <v>-0.3515</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>-0.6814</v>
+        <v>-0.4133</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>-0.6936</v>
+        <v>-0.0508</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>-0.5003</v>
+        <v>1.0677</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>4.06</v>
+        <v>4.17</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>28.38</v>
+        <v>17.97</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0.5028</v>
+        <v>0.4338</v>
       </c>
       <c r="L126" s="4" t="n">
-        <v>1.6135</v>
+        <v>0.5232</v>
       </c>
       <c r="M126" s="4" t="n">
-        <v>2.0025</v>
+        <v>0.7125</v>
       </c>
       <c r="N126" s="4" t="n">
-        <v>9.2562</v>
+        <v>0.8672</v>
       </c>
       <c r="O126" s="4" t="n">
-        <v>0.3063</v>
+        <v>0.3018</v>
       </c>
       <c r="P126" s="4" t="n">
-        <v>0.1832</v>
+        <v>0.3122</v>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr"/>
@@ -7783,31 +7783,31 @@
         </is>
       </c>
       <c r="B127" s="8" t="n">
-        <v>10685</v>
+        <v>10945</v>
       </c>
       <c r="C127" s="7" t="n">
-        <v>-0.0033</v>
+        <v>0.0243</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.0316</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>-0.04190000000000001</v>
+        <v>0.0037</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>-0.0157</v>
+        <v>-0.0023</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>0.125</v>
+        <v>0.1524</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>-0.0278</v>
+        <v>0.0151</v>
       </c>
       <c r="I127" s="6" t="n">
-        <v>4.19</v>
+        <v>4.29</v>
       </c>
       <c r="J127" s="6" t="n">
-        <v>19.62</v>
+        <v>20.1</v>
       </c>
       <c r="K127" s="7" t="n">
         <v>0.2032</v>
@@ -7837,57 +7837,57 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>DMRGD</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>193</v>
+        <v>6.2</v>
       </c>
       <c r="C128" s="4" t="n">
-        <v>-0.0153</v>
+        <v>-0.06059999999999999</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>-0.0128</v>
+        <v>-0.293</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>-0.3345</v>
+        <v>-0.3992</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>-0.4075</v>
+        <v>-0.5533</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>0</v>
+        <v>0.2133</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>1.1468</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>18.93</v>
+        <v>53.04</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0.4338</v>
+        <v>0.4591</v>
       </c>
       <c r="L128" s="4" t="n">
-        <v>0.5232</v>
+        <v>0.4162</v>
       </c>
       <c r="M128" s="4" t="n">
-        <v>0.7125</v>
+        <v>3.3554</v>
       </c>
       <c r="N128" s="4" t="n">
-        <v>0.8672</v>
+        <v>0.2283</v>
       </c>
       <c r="O128" s="4" t="n">
-        <v>0.3018</v>
+        <v>0.2808</v>
       </c>
       <c r="P128" s="4" t="n">
-        <v>0.3122</v>
+        <v>0.0866</v>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr"/>
@@ -7895,57 +7895,57 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>DMRGD</t>
+          <t>ONCSM</t>
         </is>
       </c>
       <c r="B129" s="6" t="n">
-        <v>6.6</v>
+        <v>94.5</v>
       </c>
       <c r="C129" s="7" t="n">
-        <v>0.0107</v>
+        <v>0.09949999999999999</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>-0.2171</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>-0.3714</v>
+        <v>-0.4238</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>-0.5041</v>
+        <v>-0.6764</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>0.2916</v>
+        <v>-0.6631</v>
       </c>
       <c r="H129" s="7" t="n">
-        <v>0.9984999999999999</v>
+        <v>-0.4506</v>
       </c>
       <c r="I129" s="6" t="n">
-        <v>4.63</v>
+        <v>4.46</v>
       </c>
       <c r="J129" s="6" t="n">
-        <v>56.46</v>
+        <v>31.21</v>
       </c>
       <c r="K129" s="7" t="n">
-        <v>0.4591</v>
+        <v>0.5028</v>
       </c>
       <c r="L129" s="7" t="n">
-        <v>0.4162</v>
+        <v>1.6135</v>
       </c>
       <c r="M129" s="7" t="n">
-        <v>3.3554</v>
+        <v>2.0025</v>
       </c>
       <c r="N129" s="7" t="n">
-        <v>0.2283</v>
+        <v>9.2562</v>
       </c>
       <c r="O129" s="7" t="n">
-        <v>0.2808</v>
+        <v>0.3063</v>
       </c>
       <c r="P129" s="7" t="n">
-        <v>0.0866</v>
+        <v>0.1832</v>
       </c>
       <c r="Q129" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R129" s="5" t="inlineStr"/>
@@ -7957,31 +7957,31 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>242.25</v>
+        <v>238.2</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>-0.0423</v>
+        <v>-0.0169</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>-0.1067</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>-0.2016</v>
+        <v>-0.1863</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>-0.1688</v>
+        <v>-0.1898</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>-0.1565</v>
+        <v>-0.1708</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>-0.2196</v>
+        <v>-0.2241</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>4.86</v>
+        <v>4.77</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>24.51</v>
+        <v>24.1</v>
       </c>
       <c r="K130" s="4" t="n">
         <v>0.2837</v>
@@ -8015,31 +8015,31 @@
         </is>
       </c>
       <c r="B131" s="6" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C131" s="7" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.0086</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>-0.0775</v>
+        <v>-0.0014</v>
       </c>
       <c r="E131" s="7" t="n">
-        <v>-0.1083</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>-0.0029</v>
+        <v>0.0021</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>-0.1564</v>
+        <v>-0.1491</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>0.6262</v>
+        <v>0.6548999999999999</v>
       </c>
       <c r="I131" s="6" t="n">
-        <v>5.17</v>
+        <v>5.22</v>
       </c>
       <c r="J131" s="6" t="n">
-        <v>42.76</v>
+        <v>43.12</v>
       </c>
       <c r="K131" s="7" t="n">
         <v>0.5623</v>
@@ -8073,28 +8073,28 @@
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>0.0164</v>
+        <v>-0.0215</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>0</v>
+        <v>-0.0215</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>-0.3446</v>
+        <v>-0.3636</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>-0.2464</v>
+        <v>-0.2602</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>0.2977</v>
+        <v>0.2698</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>0.6043999999999999</v>
+        <v>0.7422</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>6.72</v>
+        <v>6.58</v>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="4" t="n">
@@ -8129,28 +8129,28 @@
         </is>
       </c>
       <c r="B133" s="6" t="n">
-        <v>23.54</v>
+        <v>23.1</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>-0.02</v>
+        <v>-0.0187</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>-0.04389999999999999</v>
+        <v>-0.0486</v>
       </c>
       <c r="E133" s="7" t="n">
-        <v>-0.2597</v>
+        <v>-0.2606</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>-0.3137</v>
+        <v>-0.34</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>-0.4085</v>
+        <v>-0.4196</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>-0.2621</v>
+        <v>-0.2558</v>
       </c>
       <c r="I133" s="6" t="n">
-        <v>6.83</v>
+        <v>6.7</v>
       </c>
       <c r="J133" s="5" t="inlineStr"/>
       <c r="K133" s="7" t="n">
@@ -8185,28 +8185,28 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>12.5</v>
+        <v>12.84</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>-0.0355</v>
+        <v>0.0272</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>0.2563</v>
+        <v>0.237</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>-0.1135</v>
+        <v>-0.0552</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.0446</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>0.6681999999999999</v>
+        <v>0.7134999999999999</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>0.5547</v>
+        <v>0.5982999999999999</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>10.15</v>
+        <v>10.42</v>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="4" t="n">
@@ -8241,28 +8241,28 @@
         </is>
       </c>
       <c r="B135" s="8" t="n">
-        <v>1255</v>
+        <v>1245</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>-0.0165</v>
+        <v>-0.008</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>-0.0391</v>
+        <v>-0.0273</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>-0.3187</v>
+        <v>-0.2589</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>-0.3845</v>
+        <v>-0.3342</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>-0.1903</v>
+        <v>-0.1968</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>-0.3028</v>
+        <v>-0.293</v>
       </c>
       <c r="I135" s="6" t="n">
-        <v>11.15</v>
+        <v>11.06</v>
       </c>
       <c r="J135" s="5" t="inlineStr"/>
       <c r="K135" s="7" t="n">
@@ -8297,28 +8297,28 @@
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>268.25</v>
+        <v>261.25</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>-0.012</v>
+        <v>-0.0261</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>-0.075</v>
+        <v>-0.067</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>-0.2314</v>
+        <v>-0.2201</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>-0.2549</v>
+        <v>-0.2783</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>-0.3855</v>
+        <v>-0.4015</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>-0.4784</v>
+        <v>-0.4792</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>11.55</v>
+        <v>11.24</v>
       </c>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="4" t="n">
@@ -8353,31 +8353,31 @@
         </is>
       </c>
       <c r="B137" s="6" t="n">
-        <v>39.22</v>
+        <v>37.9</v>
       </c>
       <c r="C137" s="7" t="n">
-        <v>-0.0244</v>
+        <v>-0.0337</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>-0.0702</v>
+        <v>-0.1132</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>-0.0604</v>
+        <v>-0.0674</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>-0.2302</v>
+        <v>-0.2781</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>-0.08109999999999999</v>
+        <v>-0.112</v>
       </c>
       <c r="H137" s="7" t="n">
-        <v>-0.2804</v>
+        <v>-0.2421</v>
       </c>
       <c r="I137" s="6" t="n">
-        <v>12.02</v>
+        <v>11.62</v>
       </c>
       <c r="J137" s="6" t="n">
-        <v>43.25</v>
+        <v>41.8</v>
       </c>
       <c r="K137" s="7" t="n">
         <v>0.2618</v>
@@ -8411,28 +8411,28 @@
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>38.22</v>
+        <v>38.34</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>-0.0155</v>
+        <v>0.0031</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>0.0095</v>
+        <v>-0.0224</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>-0.1306</v>
+        <v>-0.1555</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>-0.1903</v>
+        <v>-0.178</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>-0.0922</v>
+        <v>-0.08929999999999999</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>0.1778</v>
+        <v>0.2057</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>14.27</v>
+        <v>14.31</v>
       </c>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="4" t="n">
@@ -8467,31 +8467,31 @@
         </is>
       </c>
       <c r="B139" s="6" t="n">
-        <v>101.2</v>
+        <v>101.3</v>
       </c>
       <c r="C139" s="7" t="n">
-        <v>-0.0175</v>
+        <v>0.001</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>-0.0638</v>
+        <v>-0.0416</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>-0.2137</v>
+        <v>-0.2036</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>-0.2221</v>
+        <v>-0.2267</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>-0.3325</v>
+        <v>-0.3318</v>
       </c>
       <c r="H139" s="7" t="n">
-        <v>-0.3852</v>
+        <v>-0.3716</v>
       </c>
       <c r="I139" s="6" t="n">
-        <v>15.4</v>
+        <v>15.41</v>
       </c>
       <c r="J139" s="6" t="n">
-        <v>57.99</v>
+        <v>58.04</v>
       </c>
       <c r="K139" s="7" t="n">
         <v>0.3045</v>
@@ -8525,25 +8525,25 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>-0.0154</v>
+        <v>-0.0209</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>-0.0443</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>-0.1825</v>
+        <v>-0.2424</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>0.2345</v>
+        <v>0.1952</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>0.2207</v>
+        <v>0.1952</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>-0.0413</v>
+        <v>-0.0132</v>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr"/>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>14.10.2026 19:32</t>
+          <t>15.10.2026 19:17</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_latest.xlsx
+++ b/data/bist_screener_latest.xlsx
@@ -583,31 +583,31 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13.15</v>
+        <v>12.87</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0.0092</v>
+        <v>-0.0213</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.0352</v>
+        <v>-0.06059999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.1724</v>
+        <v>-0.1697</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-0.2507</v>
+        <v>-0.2667</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.2287</v>
+        <v>-0.2452</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.3236</v>
+        <v>-0.346</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>6.11</v>
+        <v>5.98</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>0.9854999999999999</v>
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>14.41</v>
+        <v>14.02</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>0.0169</v>
+        <v>-0.0271</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>-0.0891</v>
+        <v>-0.1232</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>-0.4997</v>
+        <v>-0.4989</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>-0.3509</v>
+        <v>-0.3685</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>-0.5411</v>
+        <v>-0.5535</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-0.2845</v>
+        <v>-0.3039</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="7" t="n">
@@ -697,31 +697,31 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.004699999999999999</v>
+        <v>-0.0187</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0</v>
+        <v>-0.0187</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.1157</v>
+        <v>-0.1064</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.2132</v>
+        <v>-0.2279</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.3313</v>
+        <v>-0.3438000000000001</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.2914</v>
+        <v>-0.3115</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0.22</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>2.7227</v>
@@ -755,31 +755,31 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>-0.0066</v>
+        <v>-0.0199</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-0.0848</v>
+        <v>-0.0864</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-0.2135</v>
+        <v>-0.2251</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>-0.2705</v>
+        <v>-0.285</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-0.3105</v>
+        <v>-0.3242</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>-0.3862</v>
+        <v>-0.4127</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0.22</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>8.449999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>0.2518</v>
@@ -813,31 +813,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>-0.0268</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0048</v>
+        <v>-0.0476</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.0508</v>
+        <v>-0.0453</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2687</v>
+        <v>-0.2883</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.2852</v>
+        <v>-0.3043</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1577</v>
+        <v>0.1204</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>1.7259</v>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>-0.0046</v>
+        <v>-0.0372</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-0.04019999999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-0.3087</v>
+        <v>-0.3279</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>-0.4638</v>
+        <v>-0.4838</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-0.4743</v>
+        <v>-0.4939</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>-0.5621</v>
+        <v>-0.581</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="7" t="n">
@@ -923,57 +923,55 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AKFGY</t>
+          <t>PNSUT</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>2.48</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.004</v>
+        <v>-0.0337</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.0164</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1237</v>
+        <v>-0.157</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1143</v>
+        <v>-0.1853</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.1143</v>
+        <v>-0.268</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0</v>
+        <v>-0.3645</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>5.83</v>
-      </c>
+        <v>0.24</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="n">
-        <v>0.3848</v>
+        <v>0.049</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.3326</v>
+        <v>0.8042</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.3901</v>
+        <v>1.0075</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3812</v>
+        <v>0.2634</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.8458</v>
+        <v>0.0384</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.0496</v>
+        <v>-0.09359999999999999</v>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr"/>
@@ -981,55 +979,57 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>PNSUT</t>
+          <t>AKFGY</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>9.779999999999999</v>
+        <v>2.43</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>-0.0161</v>
+        <v>-0.0202</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-0.0307</v>
+        <v>0.0083</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-0.1605</v>
+        <v>-0.1066</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>-0.1569</v>
+        <v>-0.1321</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-0.2424</v>
+        <v>-0.1321</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-0.3493</v>
+        <v>-0.0319</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr"/>
+        <v>0.24</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>5.71</v>
+      </c>
       <c r="K9" s="7" t="n">
-        <v>0.049</v>
+        <v>0.3848</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.8042</v>
+        <v>0.3326</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>1.0075</v>
+        <v>0.3901</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>0.2634</v>
+        <v>0.3812</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>0.0384</v>
+        <v>0.8458</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>-0.09359999999999999</v>
+        <v>0.0496</v>
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R9" s="5" t="inlineStr"/>
@@ -1037,57 +1037,57 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PETUN</t>
+          <t>GSDHO</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9.44</v>
+        <v>4</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.0011</v>
+        <v>-0.08470000000000001</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.05599999999999999</v>
+        <v>-0.0654</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1939</v>
+        <v>-0.1304</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2</v>
+        <v>-0.2634</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2369</v>
+        <v>-0.1984</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2832</v>
+        <v>-0.0521</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.25</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>11.24</v>
+        <v>14.33</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.3203</v>
+        <v>0.1479</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0458</v>
+        <v>0.2201</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0347</v>
+        <v>0.3072</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0183</v>
+        <v>0.5201</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1414</v>
+        <v>0.6869</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.0274</v>
+        <v>0.0197</v>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr"/>
@@ -1095,55 +1095,57 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>AGYO</t>
+          <t>PETUN</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>6.63</v>
+        <v>9.16</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.0091</v>
+        <v>-0.0297</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.02</v>
+        <v>-0.0858</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-0.1434</v>
+        <v>-0.2049</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>-0.1276</v>
+        <v>-0.2237</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-0.206</v>
+        <v>-0.2595</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-0.0992</v>
+        <v>-0.3002</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J11" s="5" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>10.91</v>
+      </c>
       <c r="K11" s="7" t="n">
-        <v>0.4383</v>
+        <v>0.3203</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.5475</v>
+        <v>0.0458</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.6032</v>
+        <v>0.0347</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>0.6481999999999999</v>
+        <v>0.0183</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>0.3352000000000001</v>
+        <v>0.1414</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>-0.0354</v>
+        <v>0.0274</v>
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr"/>
@@ -1151,57 +1153,55 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GSDHO</t>
+          <t>AGYO</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4.37</v>
+        <v>6.7</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.0069</v>
+        <v>0.0106</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.0163</v>
+        <v>0.034</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.0742</v>
+        <v>-0.1332</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1952</v>
+        <v>-0.1184</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1242</v>
+        <v>-0.1976</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.0355</v>
+        <v>-0.09699999999999999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>15.66</v>
-      </c>
+        <v>0.26</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="n">
-        <v>0.1479</v>
+        <v>0.4383</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2201</v>
+        <v>0.5475</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3072</v>
+        <v>0.6032</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.5201</v>
+        <v>0.6481999999999999</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.6869</v>
+        <v>0.3352000000000001</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.0197</v>
+        <v>-0.0354</v>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr"/>
@@ -1213,28 +1213,28 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>12.99</v>
+        <v>12.5</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.0342</v>
+        <v>-0.0377</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.1084</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>-0.3576</v>
+        <v>-0.3747</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>-0.3986</v>
+        <v>-0.4213</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-0.5031</v>
+        <v>-0.5218</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.6816</v>
+        <v>-0.6883</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
       <c r="K13" s="7" t="n">
@@ -1265,57 +1265,55 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MHRGY</t>
+          <t>KRTEK</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1.8</v>
+        <v>5.29</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.0374</v>
+        <v>-0.024</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.0227</v>
+        <v>-0.08789999999999999</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2</v>
+        <v>-0.09880000000000001</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2562</v>
+        <v>-0.1739</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2876</v>
+        <v>-0.2583</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2643</v>
+        <v>-0.4274</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>8.49</v>
-      </c>
+        <v>0.34</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="n">
-        <v>0.9460999999999999</v>
+        <v>0.1651</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.9873000000000001</v>
+        <v>0.5547</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3702</v>
+        <v>3.1915</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2464.8944</v>
+        <v>0.7</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8395999999999999</v>
+        <v>0.0396</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.0472</v>
+        <v>-0.0461</v>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr"/>
@@ -1323,55 +1321,57 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>KRTEK</t>
+          <t>MHRGY</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>5.42</v>
+        <v>1.77</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>-0.0524</v>
+        <v>-0.0167</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>-0.1041</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-0.0639</v>
+        <v>-0.1881</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>-0.1536</v>
+        <v>-0.2686</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-0.2401</v>
+        <v>-0.2995</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.4266</v>
+        <v>-0.2976</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr"/>
+        <v>0.34</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>8.35</v>
+      </c>
       <c r="K15" s="7" t="n">
-        <v>0.1651</v>
+        <v>0.9460999999999999</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.5547</v>
+        <v>0.9873000000000001</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>3.1915</v>
+        <v>0.3702</v>
       </c>
       <c r="N15" s="7" t="n">
-        <v>0.7</v>
+        <v>2464.8944</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>0.0396</v>
+        <v>0.8395999999999999</v>
       </c>
       <c r="P15" s="7" t="n">
-        <v>-0.0461</v>
+        <v>0.0472</v>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R15" s="5" t="inlineStr"/>
@@ -1383,31 +1383,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>10.69</v>
+        <v>10.35</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.012</v>
+        <v>-0.0318</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.0074</v>
+        <v>-0.0599</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1713</v>
+        <v>-0.176</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.1889</v>
+        <v>-0.2147</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.214</v>
+        <v>-0.239</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1681</v>
+        <v>-0.2099</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.7</v>
+        <v>5.52</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>0.3789</v>
@@ -1441,31 +1441,31 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>195.8</v>
+        <v>187</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>0.0114</v>
+        <v>-0.0449</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.0527</v>
+        <v>-0.0142</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>-0.0185</v>
+        <v>-0.0301</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>-0.0449</v>
+        <v>-0.08779999999999999</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.0636</v>
+        <v>0.0158</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0.3293</v>
+        <v>0.2773</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>0.5672999999999999</v>
@@ -1495,57 +1495,55 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>37.26</v>
+        <v>1.6</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.0043</v>
+        <v>-0.0588</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.008</v>
+        <v>-0.1919</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1438</v>
+        <v>-0.4386</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1661</v>
+        <v>-0.5506</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2059</v>
+        <v>-0.6126</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0978</v>
+        <v>-0.8157</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>9.359999999999999</v>
-      </c>
+        <v>0.39</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="4" t="n">
-        <v>0.2329</v>
+        <v>0.2334</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3714</v>
+        <v>0.1468</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2133</v>
+        <v>0.1104</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.0423</v>
+        <v>0.4322</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.1786</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.0601</v>
+        <v>-0.1088</v>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr"/>
@@ -1553,55 +1551,57 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>SISE</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>1.7</v>
+        <v>36.16</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>-0.023</v>
+        <v>-0.0295</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>-0.1282</v>
+        <v>-0.0449</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>-0.4408</v>
+        <v>-0.1484</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>-0.5225</v>
+        <v>-0.1907</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>-0.5884</v>
+        <v>-0.2293</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-0.805</v>
+        <v>0.0698</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="J19" s="5" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>9.08</v>
+      </c>
       <c r="K19" s="7" t="n">
-        <v>0.2334</v>
+        <v>0.2329</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.1468</v>
+        <v>0.3714</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.1104</v>
+        <v>0.2133</v>
       </c>
       <c r="N19" s="7" t="n">
-        <v>0.4322</v>
+        <v>2.0423</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>0.1786</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="P19" s="7" t="n">
-        <v>-0.1088</v>
+        <v>0.0601</v>
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="R19" s="5" t="inlineStr"/>
@@ -1609,57 +1609,55 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>YYLGD</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>7.31</v>
+        <v>1.84</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.004099999999999999</v>
+        <v>-0.0466</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.0097</v>
+        <v>-0.0564</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.2661</v>
+        <v>-0.4743</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.3281</v>
+        <v>-0.6743000000000001</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3867</v>
+        <v>-0.7221</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2464</v>
+        <v>-0.5671</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>3.25</v>
-      </c>
+        <v>0.42</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="4" t="n">
-        <v>0.9081</v>
+        <v>0.1726</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.1391</v>
+        <v>0.3081</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.4414</v>
+        <v>0.1357</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.9061</v>
+        <v>0.2328</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.0974</v>
+        <v>0.0837</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.1661</v>
+        <v>-0.0244</v>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr"/>
@@ -1667,57 +1665,57 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>YYLGD</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>17.8</v>
+        <v>7.1</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>-0.0155</v>
+        <v>-0.0287</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>-0.0231</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-0.1812</v>
+        <v>-0.2695</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>-0.1729</v>
+        <v>-0.3474</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-0.1767</v>
+        <v>-0.4044</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.0131</v>
+        <v>-0.2733</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>7.19</v>
+        <v>3.15</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.1285</v>
+        <v>0.9081</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.8243</v>
+        <v>1.1391</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>1.9048</v>
+        <v>1.4414</v>
       </c>
       <c r="N21" s="7" t="n">
-        <v>2.2086</v>
+        <v>0.9061</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>0.1116</v>
+        <v>0.0974</v>
       </c>
       <c r="P21" s="7" t="n">
-        <v>0.1027</v>
+        <v>0.1661</v>
       </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R21" s="5" t="inlineStr"/>
@@ -1725,55 +1723,57 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>1.93</v>
+        <v>17.5</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0</v>
+        <v>-0.0169</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.03759999999999999</v>
+        <v>-0.0489</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4826</v>
+        <v>-0.1799</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.6584</v>
+        <v>-0.1868</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.7084999999999999</v>
+        <v>-0.1906</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.5257999999999999</v>
+        <v>-0.0406</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
+        <v>0.44</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>7.07</v>
+      </c>
       <c r="K22" s="4" t="n">
-        <v>0.1726</v>
+        <v>0.1285</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3081</v>
+        <v>0.8243</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.1357</v>
+        <v>1.9048</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2328</v>
+        <v>2.2086</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.0837</v>
+        <v>0.1116</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.0244</v>
+        <v>0.1027</v>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr"/>
@@ -1785,31 +1785,31 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>10.47</v>
+        <v>9.83</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0611</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>-0.0178</v>
+        <v>-0.08900000000000001</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>-0.1983</v>
+        <v>-0.2386</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>-0.3197</v>
+        <v>-0.3613</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-0.3786</v>
+        <v>-0.4166</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-0.2462</v>
+        <v>-0.2724</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="K23" s="7" t="n">
         <v>0.4985</v>
@@ -1839,55 +1839,57 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ERBOS</t>
+          <t>YUNSA</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>108.4</v>
+        <v>5.69</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.0009</v>
+        <v>-0.0421</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.05</v>
+        <v>-0.0823</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2621</v>
+        <v>-0.2152</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.347</v>
+        <v>-0.3815</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.4628</v>
+        <v>-0.3592</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.389</v>
+        <v>-0.2464</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
+        <v>0.53</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>6.83</v>
+      </c>
       <c r="K24" s="4" t="n">
-        <v>0.2349</v>
+        <v>0.6883</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.1405</v>
+        <v>0.8734999999999999</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.0386</v>
+        <v>1.1469</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.7831999999999999</v>
+        <v>1.3327</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.131</v>
+        <v>0.1078</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.023</v>
+        <v>0.09</v>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr"/>
@@ -1895,57 +1897,55 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>YUNSA</t>
+          <t>ERBOS</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5.94</v>
+        <v>103.9</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>-0.0083</v>
+        <v>-0.0415</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>-0.0341</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-0.2215</v>
+        <v>-0.2775</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>-0.3543</v>
+        <v>-0.3741</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>-0.3311</v>
+        <v>-0.4851</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-0.2575</v>
+        <v>-0.4313</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J25" s="6" t="n">
-        <v>7.13</v>
-      </c>
+        <v>0.53</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="7" t="n">
-        <v>0.6883</v>
+        <v>0.2349</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.8734999999999999</v>
+        <v>1.1405</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>1.1469</v>
+        <v>1.0386</v>
       </c>
       <c r="N25" s="7" t="n">
-        <v>1.3327</v>
+        <v>0.7831999999999999</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>0.1078</v>
+        <v>0.131</v>
       </c>
       <c r="P25" s="7" t="n">
-        <v>0.09</v>
+        <v>-0.023</v>
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R25" s="5" t="inlineStr"/>
@@ -1957,31 +1957,31 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>31.36</v>
+        <v>29.86</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.0309</v>
+        <v>-0.0478</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.0224</v>
+        <v>-0.0675</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.09050000000000001</v>
+        <v>-0.1145</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.0776</v>
+        <v>-0.1218</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.0142</v>
+        <v>-0.0343</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.2874</v>
+        <v>0.204</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>17.15</v>
+        <v>16.32</v>
       </c>
       <c r="K26" s="4" t="n">
         <v>0.3105</v>
@@ -2015,31 +2015,31 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>26.2</v>
+        <v>25.34</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>-0.0106</v>
+        <v>-0.0328</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>-0.0231</v>
+        <v>-0.0608</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-0.2113</v>
+        <v>-0.239</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>-0.3553</v>
+        <v>-0.3765</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>-0.5184000000000001</v>
+        <v>-0.5342</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>-0.4754</v>
+        <v>-0.5303</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="K27" s="7" t="n">
         <v>0.045</v>
@@ -2073,28 +2073,28 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0</v>
+        <v>-0.04559999999999999</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.0372</v>
+        <v>-0.1365</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2928</v>
+        <v>-0.2727</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3</v>
+        <v>-0.3319</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1585</v>
+        <v>-0.1969</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.009300000000000001</v>
+        <v>-0.0535</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="4" t="n">
@@ -2129,31 +2129,31 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>7.14</v>
+        <v>6.91</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>-0.0111</v>
+        <v>-0.0322</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>-0.0467</v>
+        <v>-0.08960000000000001</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-0.162</v>
+        <v>-0.1553</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>-0.3167</v>
+        <v>-0.3388</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>-0.2256</v>
+        <v>-0.2505</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>-0.3054</v>
+        <v>-0.3349</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>4.11</v>
+        <v>3.97</v>
       </c>
       <c r="K29" s="7" t="n">
         <v>0.3806</v>
@@ -2187,28 +2187,28 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>28.48</v>
+        <v>27.6</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.0035</v>
+        <v>-0.0309</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.1154</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2385</v>
+        <v>-0.2269</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4586</v>
+        <v>-0.4753</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3677</v>
+        <v>-0.3872</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2049</v>
+        <v>-0.2434</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="4" t="n">
@@ -2239,51 +2239,53 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>SOKE</t>
+          <t>MERCN</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>7.72</v>
+        <v>9.35</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>0.0335</v>
+        <v>-0.077</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>0.0619</v>
+        <v>-0.1163</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-0.2982</v>
+        <v>-0.462</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>-0.5926</v>
+        <v>-0.6345000000000001</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>-0.5677</v>
+        <v>-0.5268</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>-0.3168</v>
+        <v>-0.7149</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="J31" s="5" t="inlineStr"/>
+        <v>0.62</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>10.74</v>
+      </c>
       <c r="K31" s="7" t="n">
-        <v>0.5234000000000001</v>
+        <v>0.2374</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.4561</v>
+        <v>0.8593999999999999</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.4897</v>
+        <v>1.4059</v>
       </c>
       <c r="N31" s="7" t="n">
-        <v>0.3644</v>
+        <v>1.3031</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>0.032</v>
+        <v>0.1784</v>
       </c>
       <c r="P31" s="7" t="n">
-        <v>-0.0429</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
@@ -2295,57 +2297,55 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>OSMEN</t>
+          <t>SOKE</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>5.24</v>
+        <v>7.64</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.0019</v>
+        <v>-0.0104</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.0473</v>
+        <v>-0.066</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2328</v>
+        <v>-0.2091</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3762</v>
+        <v>-0.5968</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3290999999999999</v>
+        <v>-0.5722</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4525</v>
+        <v>-0.3292</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>8.99</v>
-      </c>
+        <v>0.63</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="4" t="n">
-        <v>1.6512</v>
+        <v>0.5234000000000001</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1052</v>
+        <v>0.4561</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.04969999999999999</v>
+        <v>0.4897</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.9134</v>
+        <v>0.3644</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.032</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.0863</v>
+        <v>-0.0429</v>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr"/>
@@ -2353,53 +2353,53 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>SEKFK</t>
+          <t>OSMEN</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>3.95</v>
+        <v>5.13</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>-0.005</v>
+        <v>-0.021</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>-0.0366</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-0.0814</v>
+        <v>-0.2377</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>-0.2896</v>
+        <v>-0.3893</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>-0.3424</v>
+        <v>-0.3431</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>-0.0987</v>
+        <v>-0.4429999999999999</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>3.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.208</v>
+        <v>1.6512</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0571</v>
+        <v>0.1052</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.0025</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="N33" s="7" t="n">
-        <v>0.2707</v>
+        <v>5.9134</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>0.6072</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="P33" s="7" t="n">
-        <v>0.2346</v>
+        <v>0.0863</v>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
@@ -2411,55 +2411,57 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>DOKTA</t>
+          <t>SEKFK</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>15</v>
+        <v>3.86</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.0033</v>
+        <v>-0.0228</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.0291</v>
+        <v>-0.0608</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.345</v>
+        <v>-0.1002</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3628</v>
+        <v>-0.3058</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3766</v>
+        <v>-0.3574</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3687</v>
+        <v>-0.1291</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
+        <v>0.64</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>3.13</v>
+      </c>
       <c r="K34" s="4" t="n">
-        <v>0.2983</v>
+        <v>0.208</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.25</v>
+        <v>0.0571</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>3.5566</v>
+        <v>0.0025</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.6970000000000001</v>
+        <v>0.2707</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.0852</v>
+        <v>0.6072</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.0451</v>
+        <v>0.2346</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr"/>
@@ -2467,57 +2469,55 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>DOKTA</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>210.9</v>
+        <v>14.66</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>-0.0014</v>
+        <v>-0.0227</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.005699999999999999</v>
+        <v>-0.0481</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-0.06559999999999999</v>
+        <v>-0.3426</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>0.0722</v>
+        <v>-0.3772</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>0.0338</v>
+        <v>-0.3907</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>0.3408</v>
+        <v>-0.3778</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="J35" s="6" t="n">
-        <v>15.03</v>
-      </c>
+        <v>0.64</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr"/>
       <c r="K35" s="7" t="n">
-        <v>0.3261</v>
+        <v>0.2983</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.5440999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.9423</v>
+        <v>3.5566</v>
       </c>
       <c r="N35" s="7" t="n">
-        <v>5.083299999999999</v>
+        <v>0.6970000000000001</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>0.0646</v>
+        <v>0.0852</v>
       </c>
       <c r="P35" s="7" t="n">
-        <v>0.0771</v>
+        <v>-0.0451</v>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R35" s="5" t="inlineStr"/>
@@ -2525,57 +2525,57 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MERCN</t>
+          <t>PNLSN</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>10.13</v>
+        <v>30.52</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>-0.0165</v>
+        <v>-0.0463</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>-0.0542</v>
+        <v>-0.09</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>-0.4548</v>
+        <v>-0.201</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>-0.604</v>
+        <v>-0.3748</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.4873</v>
+        <v>-0.3298</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.6623</v>
+        <v>-0.2093</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>11.64</v>
+        <v>8.6</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0.2374</v>
+        <v>0.306</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.8593999999999999</v>
+        <v>0.6481</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>1.4059</v>
+        <v>0.5497</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>1.3031</v>
+        <v>7.793600000000001</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>0.1784</v>
+        <v>0.1302</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.08839999999999999</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr"/>
@@ -2583,57 +2583,57 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>PNLSN</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>32</v>
+        <v>204</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>0.0063</v>
+        <v>-0.0327</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>-0.0148</v>
+        <v>-0.0418</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-0.1919</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>-0.3445</v>
+        <v>0.0371</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>-0.2973</v>
+        <v>0</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>-0.182</v>
+        <v>0.2977</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>9.02</v>
+        <v>14.54</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.306</v>
+        <v>0.3261</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>0.6481</v>
+        <v>0.5440999999999999</v>
       </c>
       <c r="M37" s="7" t="n">
-        <v>0.5497</v>
+        <v>0.9423</v>
       </c>
       <c r="N37" s="7" t="n">
-        <v>7.793600000000001</v>
+        <v>5.083299999999999</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>0.1302</v>
+        <v>0.0646</v>
       </c>
       <c r="P37" s="7" t="n">
-        <v>0.08839999999999999</v>
+        <v>0.0771</v>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="R37" s="5" t="inlineStr"/>
@@ -2645,31 +2645,31 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>204.4</v>
+        <v>196.7</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>-0.0029</v>
+        <v>-0.0377</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>-0.0126</v>
+        <v>-0.062</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>-0.1623</v>
+        <v>-0.1835</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-0.1643</v>
+        <v>-0.1958</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.3089</v>
+        <v>-0.3349</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1031</v>
+        <v>-0.1304</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>10.07</v>
+        <v>9.69</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>0.3886</v>
@@ -2703,31 +2703,31 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>52.3</v>
+        <v>50.9</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>-0.0038</v>
+        <v>-0.0268</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0.0048</v>
+        <v>-0.0314</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.0745</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>-0.106</v>
+        <v>-0.1299</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>-0.1692</v>
+        <v>-0.1914</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>0.0604</v>
+        <v>0.0059</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>6.47</v>
+        <v>6.29</v>
       </c>
       <c r="K39" s="7" t="n">
         <v>0.4498</v>
@@ -2757,57 +2757,57 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>BNTAS</t>
+          <t>TUREX</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>5.17</v>
+        <v>5.58</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0</v>
+        <v>-0.0396</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>-0.0444</v>
+        <v>-0.0429</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>-0.1634</v>
+        <v>-0.0396</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>-0.1897</v>
+        <v>-0.196</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-0.2249</v>
+        <v>-0.3645</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.2131</v>
+        <v>-0.3051</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>4.79</v>
+        <v>10.49</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.2654</v>
+        <v>0.4159</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.07690000000000001</v>
+        <v>1.3967</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.464</v>
+        <v>0.8518000000000001</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.3679</v>
+        <v>0.3205</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.1363</v>
+        <v>0.2638</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0.1657</v>
+        <v>0.0862</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr"/>
@@ -2815,57 +2815,57 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>BNTAS</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>97.84999999999999</v>
+        <v>5.06</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>-0.0046</v>
+        <v>-0.0213</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>-0.021</v>
+        <v>-0.0471</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-0.0463</v>
+        <v>-0.1746</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>-0.124</v>
+        <v>-0.2069</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>-0.1672</v>
+        <v>-0.2414</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>0.0747</v>
+        <v>-0.2263</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>10.99</v>
+        <v>4.68</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.3971</v>
+        <v>0.2654</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>0.4118</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="M41" s="7" t="n">
-        <v>0.3975</v>
+        <v>0.464</v>
       </c>
       <c r="N41" s="7" t="n">
-        <v>0.2377</v>
+        <v>0.3679</v>
       </c>
       <c r="O41" s="7" t="n">
-        <v>0.4333</v>
+        <v>0.1363</v>
       </c>
       <c r="P41" s="7" t="n">
-        <v>0.1518</v>
+        <v>0.1657</v>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R41" s="5" t="inlineStr"/>
@@ -2873,57 +2873,57 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TUREX</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>5.81</v>
+        <v>96.8</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0107</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>0.0069</v>
+        <v>-0.0349</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-0.0136</v>
+        <v>-0.0281</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-0.1628</v>
+        <v>-0.1334</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-0.3383</v>
+        <v>-0.1762</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-0.2484</v>
+        <v>0.0189</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>10.92</v>
+        <v>10.87</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0.4159</v>
+        <v>0.3971</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>1.3967</v>
+        <v>0.4118</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.8518000000000001</v>
+        <v>0.3975</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.3205</v>
+        <v>0.2377</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>0.2638</v>
+        <v>0.4333</v>
       </c>
       <c r="P42" s="4" t="n">
-        <v>0.0862</v>
+        <v>0.1518</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr"/>
@@ -2931,57 +2931,57 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>AYGAZ</t>
+          <t>PINSU</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>288.5</v>
+        <v>7.89</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>-0.0103</v>
+        <v>-0.0483</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.0052</v>
+        <v>-0.1003</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-0.1388</v>
+        <v>-0.203</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.1226</v>
+        <v>-0.2633</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>-0.0052</v>
+        <v>-0.3713</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>0.5232</v>
+        <v>-0.3807</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>7.58</v>
+        <v>16.63</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.1662</v>
+        <v>0.2802</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>0.3683</v>
+        <v>0.2234</v>
       </c>
       <c r="M43" s="7" t="n">
-        <v>0.4549</v>
+        <v>0.3074</v>
       </c>
       <c r="N43" s="7" t="n">
-        <v>1.9624</v>
+        <v>91.6451</v>
       </c>
       <c r="O43" s="7" t="n">
-        <v>0.0302</v>
+        <v>0.1329</v>
       </c>
       <c r="P43" s="7" t="n">
-        <v>0.118</v>
+        <v>0.0528</v>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R43" s="5" t="inlineStr"/>
@@ -2989,57 +2989,57 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>PINSU</t>
+          <t>AYGAZ</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>8.289999999999999</v>
+        <v>277.25</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>-0.0189</v>
+        <v>-0.039</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>-0.04269999999999999</v>
+        <v>-0.0546</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>-0.1751</v>
+        <v>-0.1547</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>-0.226</v>
+        <v>0.0788</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-0.3394</v>
+        <v>-0.044</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>-0.3882</v>
+        <v>0.5192</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>17.47</v>
+        <v>7.29</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0.2802</v>
+        <v>0.1662</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.2234</v>
+        <v>0.3683</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.3074</v>
+        <v>0.4549</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>91.6451</v>
+        <v>1.9624</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>0.1329</v>
+        <v>0.0302</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>0.0528</v>
+        <v>0.118</v>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr"/>
@@ -3047,57 +3047,57 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>BASGZ</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>39.72</v>
+        <v>36.26</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>-0.001</v>
+        <v>-0.0305</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0.0102</v>
+        <v>-0.0152</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-0.1228</v>
+        <v>-0.05429999999999999</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>-0.1513</v>
+        <v>-0.1744</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>-0.2096</v>
+        <v>0.1712</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>0.0575</v>
+        <v>0.3331</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>7.19</v>
+        <v>31.6</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.3163</v>
+        <v>0.1998</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>0.5275</v>
+        <v>0.3838</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>0.4513</v>
+        <v>0.4877</v>
       </c>
       <c r="N45" s="7" t="n">
-        <v>0.3789</v>
+        <v>0.4752</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>0.1301</v>
+        <v>0.104</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>-0.245</v>
+        <v>0.0274</v>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R45" s="5" t="inlineStr"/>
@@ -3105,57 +3105,57 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>BASGZ</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>37.4</v>
+        <v>39.08</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.008100000000000001</v>
+        <v>-0.0161</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>0.0241</v>
+        <v>-0.0005</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>-0.0386</v>
+        <v>-0.1065</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-0.1485</v>
+        <v>-0.165</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.208</v>
+        <v>-0.2223</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.4385</v>
+        <v>-0.025</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>32.6</v>
+        <v>7.08</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0.1998</v>
+        <v>0.3163</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.3838</v>
+        <v>0.5275</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.4877</v>
+        <v>0.4513</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.4752</v>
+        <v>0.3789</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0.104</v>
+        <v>0.1301</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>0.0274</v>
+        <v>-0.245</v>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr"/>
@@ -3167,25 +3167,25 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>15.84</v>
+        <v>15.8</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>-0.01</v>
+        <v>-0.0025</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>-0.0571</v>
+        <v>-0.0522</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-0.1702</v>
+        <v>-0.1524</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>-0.198</v>
+        <v>-0.2</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>-0.2296</v>
+        <v>-0.2315</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>-0.06269999999999999</v>
+        <v>-0.0717</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0.79</v>
@@ -3221,57 +3221,57 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>DESA</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>4.28</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.0222</v>
+        <v>-0.0989</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>-0.0247</v>
+        <v>-0.4072</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>-0.1354</v>
+        <v>-0.9105</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-0.2118</v>
+        <v>-0.8956000000000001</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-0.4437</v>
+        <v>-0.8098000000000001</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>-0.4252</v>
+        <v>-0.8654999999999999</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>7.86</v>
+        <v>2.72</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0.2088</v>
+        <v>7.8666</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.2301</v>
+        <v>3.1929</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.0037</v>
+        <v>4.946499999999999</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.3571</v>
+        <v>1.0979</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>0.2399</v>
+        <v>0.4854</v>
       </c>
       <c r="P48" s="4" t="n">
-        <v>0.1277</v>
+        <v>0.586</v>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr"/>
@@ -3279,55 +3279,57 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>AYES</t>
+          <t>DESA</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>7.3</v>
+        <v>8.24</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>0.0139</v>
+        <v>-0.0072</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.0452</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>-0.079</v>
+        <v>-0.1345</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>-0.2151</v>
+        <v>-0.2175</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>-0.2396</v>
+        <v>-0.4477</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0.5977</v>
+        <v>-0.4518</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>2.01</v>
+        <v>7.81</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.4183</v>
+        <v>0.2088</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>0.314</v>
+        <v>0.2301</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0.8128</v>
+        <v>0.0037</v>
       </c>
       <c r="N49" s="7" t="n">
-        <v>42.7724</v>
+        <v>0.3571</v>
       </c>
       <c r="O49" s="7" t="n">
-        <v>0.0208</v>
-      </c>
-      <c r="P49" s="5" t="inlineStr"/>
+        <v>0.2399</v>
+      </c>
+      <c r="P49" s="7" t="n">
+        <v>0.1277</v>
+      </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R49" s="5" t="inlineStr"/>
@@ -3335,57 +3337,55 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>AYES</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>4.75</v>
+        <v>7.15</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>-0.0987</v>
+        <v>-0.0205</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.4077</v>
+        <v>-0.09029999999999999</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>-0.9016</v>
+        <v>-0.1365</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>-0.8841</v>
+        <v>-0.2312</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.7889</v>
+        <v>-0.2552</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>-0.8343</v>
+        <v>0.5577000000000001</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>3.02</v>
+        <v>1.97</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>7.8666</v>
+        <v>0.4183</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>3.1929</v>
+        <v>0.314</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>4.946499999999999</v>
+        <v>0.8128</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>1.0979</v>
+        <v>42.7724</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>0.4854</v>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v>0.586</v>
-      </c>
+        <v>0.0208</v>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr"/>
@@ -3397,31 +3397,31 @@
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>470</v>
+        <v>452.25</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>-0.0304</v>
+        <v>-0.0378</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>-0.0581</v>
+        <v>-0.09910000000000001</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-0.1288</v>
+        <v>-0.1201</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>-0.2504</v>
+        <v>-0.2787</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>-0.289</v>
+        <v>-0.3158</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>0.0658</v>
+        <v>0.0215</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>14.08</v>
+        <v>13.55</v>
       </c>
       <c r="K51" s="7" t="n">
         <v>0.3804</v>
@@ -3451,57 +3451,57 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>EGGUB</t>
+          <t>KARSN</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>7.96</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.0038</v>
+        <v>-0.04559999999999999</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.05980000000000001</v>
+        <v>-0.1165</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>-0.1795</v>
+        <v>-0.39</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>-0.099</v>
+        <v>-0.2842</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.2832</v>
+        <v>-0.2375</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>-0.1008</v>
+        <v>-0.1968</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>12.86</v>
+        <v>29.62</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0.4926</v>
+        <v>0.8458</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.6905</v>
+        <v>1.2698</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.7726999999999999</v>
+        <v>1.2002</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.5777</v>
+        <v>2.1122</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>0.4324</v>
+        <v>0.1667</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>0.0886</v>
+        <v>0.07339999999999999</v>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr"/>
@@ -3509,57 +3509,57 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>KARSN</t>
+          <t>EGGUB</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>8.34</v>
+        <v>91.7</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>-0.006</v>
+        <v>-0.0022</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>-0.0774</v>
+        <v>-0.0779</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-0.4224</v>
+        <v>-0.1556</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>-0.25</v>
+        <v>-0.101</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>-0.2011</v>
+        <v>-0.2847</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>-0.1533</v>
+        <v>-0.108</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>31.04</v>
+        <v>12.83</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>0.8458</v>
+        <v>0.4926</v>
       </c>
       <c r="L53" s="7" t="n">
-        <v>1.2698</v>
+        <v>0.6905</v>
       </c>
       <c r="M53" s="7" t="n">
-        <v>1.2002</v>
+        <v>0.7726999999999999</v>
       </c>
       <c r="N53" s="7" t="n">
-        <v>2.1122</v>
+        <v>0.5777</v>
       </c>
       <c r="O53" s="7" t="n">
-        <v>0.1667</v>
+        <v>0.4324</v>
       </c>
       <c r="P53" s="7" t="n">
-        <v>0.07339999999999999</v>
+        <v>0.0886</v>
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R53" s="5" t="inlineStr"/>
@@ -3567,57 +3567,57 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ZRGYO</t>
+          <t>GRTHO</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>18.4</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>-0.0316</v>
+        <v>-0.0999</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>-0.0113</v>
+        <v>-0.3864</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>-0.066</v>
+        <v>-0.6727</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.0425</v>
+        <v>-0.7125</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-0.1321</v>
+        <v>-0.7170000000000001</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>-0.1771</v>
+        <v>-0.8908</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>13.93</v>
+        <v>5.02</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>2.3363</v>
+        <v>0.5085000000000001</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>3.5944</v>
+        <v>0.4487</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>3.6478</v>
+        <v>0.2298</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.2899</v>
+        <v>0.9399</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>0.5917</v>
+        <v>0.1089</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>0.0776</v>
+        <v>0.2287</v>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr"/>
@@ -3625,57 +3625,57 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>ARASE</t>
+          <t>ZRGYO</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>95</v>
+        <v>18.25</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>-0.0031</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>-0.0301</v>
+        <v>-0.04</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-0.2024</v>
+        <v>-0.0902</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>-0.2613</v>
+        <v>0.034</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>-0.065</v>
+        <v>-0.1392</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>0.8887</v>
+        <v>-0.21</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>8.66</v>
+        <v>13.81</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>0.1264</v>
+        <v>2.3363</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>0.596</v>
+        <v>3.5944</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>0.7123999999999999</v>
+        <v>3.6478</v>
       </c>
       <c r="N55" s="7" t="n">
-        <v>4.0303</v>
+        <v>0.2899</v>
       </c>
       <c r="O55" s="7" t="n">
-        <v>0.25</v>
+        <v>0.5917</v>
       </c>
       <c r="P55" s="7" t="n">
-        <v>0.1463</v>
+        <v>0.0776</v>
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R55" s="5" t="inlineStr"/>
@@ -3683,57 +3683,57 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GESAN</t>
+          <t>ARASE</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>36.8</v>
+        <v>91.2</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.0795</v>
+        <v>-0.0593</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>-0.3977000000000001</v>
+        <v>-0.2042</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>-0.5474</v>
+        <v>-0.2908</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.212</v>
+        <v>-0.1024</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>-0.1259</v>
+        <v>0.7338</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>9.890000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0.2641</v>
+        <v>0.1264</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.2931</v>
+        <v>0.596</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.3273</v>
+        <v>0.7123999999999999</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.4479</v>
+        <v>4.0303</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>0.1778</v>
+        <v>0.25</v>
       </c>
       <c r="P56" s="4" t="n">
-        <v>0.1266</v>
+        <v>0.1463</v>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr"/>
@@ -3741,57 +3741,57 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>GRTHO</t>
+          <t>GESAN</t>
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>80.09999999999999</v>
+        <v>35.36</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>-0.1</v>
+        <v>-0.0391</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>-0.3029</v>
+        <v>-0.1333</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-0.6591</v>
+        <v>-0.4107</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>-0.6806</v>
+        <v>-0.5650999999999999</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>-0.6856</v>
+        <v>-0.2428</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>-0.8706999999999999</v>
+        <v>-0.1819</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>1.01</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>5.58</v>
+        <v>9.5</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>0.5085000000000001</v>
+        <v>0.2641</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>0.4487</v>
+        <v>0.2931</v>
       </c>
       <c r="M57" s="7" t="n">
-        <v>0.2298</v>
+        <v>0.3273</v>
       </c>
       <c r="N57" s="7" t="n">
-        <v>0.9399</v>
+        <v>0.4479</v>
       </c>
       <c r="O57" s="7" t="n">
-        <v>0.1089</v>
+        <v>0.1778</v>
       </c>
       <c r="P57" s="7" t="n">
-        <v>0.2287</v>
+        <v>0.1266</v>
       </c>
       <c r="Q57" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R57" s="5" t="inlineStr"/>
@@ -3799,57 +3799,57 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>CIMSA</t>
+          <t>RALYH</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>39.84</v>
+        <v>24.2</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>-0.0109</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>-0.0264</v>
+        <v>-0.4086</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>-0.1115</v>
+        <v>-0.9087000000000001</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>-0.1683</v>
+        <v>-0.8948</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-0.2419</v>
+        <v>-0.9243000000000001</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>-0.0713</v>
+        <v>-0.8615</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>1.01</v>
+        <v>0.96</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>9.44</v>
+        <v>3.13</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0.3754999999999999</v>
+        <v>0.7070000000000001</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>0.3037</v>
+        <v>1.4848</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.4933</v>
+        <v>1.5369</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>1.15</v>
+        <v>0.5434</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>0.1807</v>
+        <v>0.2854</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.3914</v>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr"/>
@@ -3857,53 +3857,53 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>CMENT</t>
+          <t>CIMSA</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>219</v>
+        <v>38.38</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>0.008800000000000001</v>
+        <v>-0.0366</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>-0.07519999999999999</v>
+        <v>-0.0684</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-0.124</v>
+        <v>-0.1229</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>-0.2474</v>
+        <v>-0.1987</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>-0.3364</v>
+        <v>-0.2696</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>-0.4036999999999999</v>
+        <v>-0.1045</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>21.62</v>
+        <v>9.09</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>0.0934</v>
+        <v>0.3754999999999999</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>0.1109</v>
+        <v>0.3037</v>
       </c>
       <c r="M59" s="7" t="n">
-        <v>0.1008</v>
+        <v>0.4933</v>
       </c>
       <c r="N59" s="7" t="n">
-        <v>0.4922</v>
+        <v>1.15</v>
       </c>
       <c r="O59" s="7" t="n">
-        <v>0.1647</v>
+        <v>0.1807</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.2729</v>
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
@@ -3915,57 +3915,57 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>CWENE</t>
+          <t>TNZTP</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>17.12</v>
+        <v>23.4</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.064</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>-0.0536</v>
+        <v>-0.064</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>-0.4189</v>
+        <v>-0.2642</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>-0.5670000000000001</v>
+        <v>-0.011</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-0.5268</v>
+        <v>-0.0362</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>-0.2184</v>
+        <v>0.07730000000000001</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>6.37</v>
+        <v>17.32</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0.5809000000000001</v>
+        <v>0.4327</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.9067000000000001</v>
+        <v>0.4143</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.8432999999999999</v>
+        <v>0.5201</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>5.095899999999999</v>
+        <v>0.0702</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>0.1918</v>
+        <v>0.3617</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>0.2052</v>
+        <v>0.0551</v>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Sağlık hizmetleri</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr"/>
@@ -3973,57 +3973,57 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>TNZTP</t>
+          <t>CWENE</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>25</v>
+        <v>16.2</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>-0.0119</v>
+        <v>-0.0537</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>0.0204</v>
+        <v>-0.1598</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>-0.2099</v>
+        <v>-0.4394</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>0.0566</v>
+        <v>-0.5903</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>0.0297</v>
+        <v>-0.5522</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>0.1671</v>
+        <v>-0.2691</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>18.5</v>
+        <v>6.02</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>0.4327</v>
+        <v>0.5809000000000001</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>0.4143</v>
+        <v>0.9067000000000001</v>
       </c>
       <c r="M61" s="7" t="n">
-        <v>0.5201</v>
+        <v>0.8432999999999999</v>
       </c>
       <c r="N61" s="7" t="n">
-        <v>0.0702</v>
+        <v>5.095899999999999</v>
       </c>
       <c r="O61" s="7" t="n">
-        <v>0.3617</v>
+        <v>0.1918</v>
       </c>
       <c r="P61" s="7" t="n">
-        <v>0.0551</v>
+        <v>0.2052</v>
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>Sağlık hizmetleri</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R61" s="5" t="inlineStr"/>
@@ -4031,57 +4031,57 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>INDES</t>
+          <t>CMENT</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>11.97</v>
+        <v>215.9</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0.0127</v>
+        <v>-0.0142</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>0.0593</v>
+        <v>-0.1041</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0.0266</v>
+        <v>-0.1347</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.0697</v>
+        <v>-0.2581</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>0.2694</v>
+        <v>-0.3458</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>0.5545</v>
+        <v>-0.4019</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>10.09</v>
+        <v>21.31</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0.6297</v>
+        <v>0.0934</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.8554999999999999</v>
+        <v>0.1109</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>1.0205</v>
+        <v>0.1008</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1.9437</v>
+        <v>0.4922</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>0.0374</v>
+        <v>0.1647</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>0.137</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr"/>
@@ -4089,57 +4089,57 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>RALYH</t>
+          <t>INDES</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>26.88</v>
+        <v>11.53</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>-0.0998</v>
+        <v>-0.0368</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>-0.4087</v>
+        <v>0.0204</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-0.9004000000000001</v>
+        <v>0.0341</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>-0.8831</v>
+        <v>0.0304</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>-0.9159</v>
+        <v>0.2227</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>-0.8454999999999999</v>
+        <v>0.4485</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>3.48</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>0.7070000000000001</v>
+        <v>0.6297</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>1.4848</v>
+        <v>0.8554999999999999</v>
       </c>
       <c r="M63" s="7" t="n">
-        <v>1.5369</v>
+        <v>1.0205</v>
       </c>
       <c r="N63" s="7" t="n">
-        <v>0.5434</v>
+        <v>1.9437</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>0.2854</v>
+        <v>0.0374</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>0.3914</v>
+        <v>0.137</v>
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R63" s="5" t="inlineStr"/>
@@ -4151,28 +4151,28 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.0046</v>
+        <v>-0.0186</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>0.018</v>
+        <v>-0.025</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>-0.3882</v>
+        <v>-0.3492</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>-0.4546</v>
+        <v>-0.4647</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.447</v>
+        <v>-0.4573</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>0.0287</v>
+        <v>0.0048</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="4" t="n">
@@ -4207,31 +4207,31 @@
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>10.19</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>0.001</v>
+        <v>-0.0216</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>-0.0192</v>
+        <v>-0.0505</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>-0.0803</v>
+        <v>-0.0862</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>-0.1592</v>
+        <v>-0.1774</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>-0.0512</v>
+        <v>-0.0717</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>-0.1014</v>
+        <v>-0.1699</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>6.84</v>
+        <v>6.69</v>
       </c>
       <c r="K65" s="7" t="n">
         <v>0.423</v>
@@ -4265,31 +4265,31 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>61.25</v>
+        <v>58.65</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.0016</v>
+        <v>-0.0424</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.0578</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.0208</v>
+        <v>-0.0385</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>0.0506</v>
+        <v>0.006</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0.3971</v>
+        <v>0.3378</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>0.6939</v>
+        <v>0.5775</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>14.44</v>
+        <v>13.83</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>0.1859</v>
@@ -4323,31 +4323,31 @@
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>10.48</v>
+        <v>10.1</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>-0.0141</v>
+        <v>-0.0363</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.0251</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>-0.1683</v>
+        <v>-0.1855</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>-0.2697</v>
+        <v>-0.2962</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>-0.2362</v>
+        <v>-0.2638</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>0.4886</v>
+        <v>0.4367</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>14.85</v>
+        <v>14.31</v>
       </c>
       <c r="K67" s="7" t="n">
         <v>0.5631</v>
@@ -4377,57 +4377,57 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ENKAI</t>
+          <t>MAALT</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>77.8</v>
+        <v>739.5</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.0245</v>
+        <v>-0.058</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>-0.0371</v>
+        <v>-0.09820000000000001</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>-0.1288</v>
+        <v>-0.2937</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>-0.1557</v>
+        <v>-0.3277</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-0.2505</v>
+        <v>-0.5063</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>0.1194</v>
+        <v>-0.2896</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>11.69</v>
+        <v>1593.41</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0.4381</v>
+        <v>0.248</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.1539</v>
+        <v>3.5256</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>0.1373</v>
+        <v>0.3863</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.3376</v>
+        <v>0.9832</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>0.2166</v>
+        <v>0.4575</v>
       </c>
       <c r="P68" s="4" t="n">
-        <v>0.1059</v>
+        <v>-0</v>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr"/>
@@ -4435,57 +4435,57 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>NTGAZ</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>10.24</v>
+        <v>76.2</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>-0.0097</v>
+        <v>-0.0206</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>-0.043</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>-0.0906</v>
+        <v>-0.1134</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>-0.1134</v>
+        <v>-0.1731</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>-0.1782</v>
+        <v>-0.2659</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>0.107</v>
+        <v>0.0346</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>6.51</v>
+        <v>11.45</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>0.3448</v>
+        <v>0.4381</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>0.3645</v>
+        <v>0.1539</v>
       </c>
       <c r="M69" s="7" t="n">
-        <v>0.4084</v>
+        <v>0.1373</v>
       </c>
       <c r="N69" s="7" t="n">
-        <v>0.5755</v>
+        <v>0.3376</v>
       </c>
       <c r="O69" s="7" t="n">
-        <v>0.2148</v>
+        <v>0.2166</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>0.2137</v>
+        <v>0.1059</v>
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R69" s="5" t="inlineStr"/>
@@ -4493,57 +4493,57 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>MAALT</t>
+          <t>NTGAZ</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>785</v>
+        <v>10.05</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0.0155</v>
+        <v>-0.0186</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>-0.0374</v>
+        <v>-0.0703</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>-0.2341</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>-0.2864</v>
+        <v>-0.1299</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>-0.476</v>
+        <v>-0.1934</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>-0.2228</v>
+        <v>0.0646</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>1691.45</v>
+        <v>6.39</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0.248</v>
+        <v>0.3448</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>3.5256</v>
+        <v>0.3645</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.3863</v>
+        <v>0.4084</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.9832</v>
+        <v>0.5755</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>0.4575</v>
+        <v>0.2148</v>
       </c>
       <c r="P70" s="4" t="n">
-        <v>-0</v>
+        <v>0.2137</v>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr"/>
@@ -4551,57 +4551,55 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>SELEC</t>
+          <t>OBASE</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>71.65000000000001</v>
+        <v>20.7</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>-0.0035</v>
+        <v>-0.0582</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>0.012</v>
+        <v>-0.2032</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>-0.7544</v>
+        <v>-0.4086</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>-0.7001000000000001</v>
+        <v>-0.5289</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>-0.1931</v>
+        <v>-0.4547</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>-0.0428</v>
+        <v>-0.4408</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J71" s="6" t="n">
-        <v>21.84</v>
-      </c>
+        <v>1.16</v>
+      </c>
+      <c r="J71" s="5" t="inlineStr"/>
       <c r="K71" s="7" t="n">
-        <v>0.3781</v>
+        <v>0.2041</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>0.6063000000000001</v>
+        <v>0.3021</v>
       </c>
       <c r="M71" s="7" t="n">
-        <v>1.4267</v>
+        <v>0.5156000000000001</v>
       </c>
       <c r="N71" s="7" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.4873</v>
       </c>
       <c r="O71" s="7" t="n">
-        <v>0.0158</v>
+        <v>0.2465</v>
       </c>
       <c r="P71" s="7" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.1432</v>
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R71" s="5" t="inlineStr"/>
@@ -4609,57 +4607,57 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>SELEC</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>271</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>-0.0009</v>
+        <v>-0.0147</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>-0.0154</v>
+        <v>-0.0498</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>0.0112</v>
+        <v>-0.7313</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>0.0009</v>
+        <v>-0.7045</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>-0.1335</v>
+        <v>-0.205</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>0.2268</v>
+        <v>-0.0723</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>18.67</v>
+        <v>21.52</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0.3707</v>
+        <v>0.3781</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.4185</v>
+        <v>0.6063000000000001</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.4202</v>
+        <v>1.4267</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>1.8941</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>0.3086</v>
+        <v>0.0158</v>
       </c>
       <c r="P72" s="4" t="n">
-        <v>-0.1688</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr"/>
@@ -4667,57 +4665,55 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>GEDIK</t>
+          <t>YKSLN</t>
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>4.86</v>
+        <v>2.41</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>0.004099999999999999</v>
+        <v>-0.0974</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>-0.0471</v>
+        <v>0.0478</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-0.1243</v>
+        <v>-0.5275</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>-0.2811</v>
+        <v>-0.2585</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>-0.1706</v>
+        <v>-0.2349</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>-0.3077</v>
+        <v>-0.3254</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="J73" s="6" t="n">
-        <v>5.14</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="J73" s="5" t="inlineStr"/>
       <c r="K73" s="7" t="n">
-        <v>0.6583</v>
+        <v>0.1126</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.0263</v>
       </c>
       <c r="M73" s="7" t="n">
-        <v>0.7293999999999999</v>
+        <v>0.6127</v>
       </c>
       <c r="N73" s="7" t="n">
-        <v>0.3481</v>
+        <v>0.8754000000000001</v>
       </c>
       <c r="O73" s="7" t="n">
-        <v>0.6628000000000001</v>
+        <v>0.1443</v>
       </c>
       <c r="P73" s="7" t="n">
-        <v>0.275</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R73" s="5" t="inlineStr"/>
@@ -4725,55 +4721,57 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>OBASE</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>21.98</v>
+        <v>270.5</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>0.0447</v>
+        <v>-0.0018</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>-0.1623</v>
+        <v>-0.0261</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>-0.377</v>
+        <v>0.0546</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>-0.4998</v>
+        <v>-0.0009</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-0.421</v>
+        <v>-0.1351</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>-0.3773</v>
+        <v>0.198</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>18.63</v>
+      </c>
       <c r="K74" s="4" t="n">
-        <v>0.2041</v>
+        <v>0.3707</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.3021</v>
+        <v>0.4185</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.5156000000000001</v>
+        <v>0.4202</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.4873</v>
+        <v>1.8941</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>0.2465</v>
+        <v>0.3086</v>
       </c>
       <c r="P74" s="4" t="n">
-        <v>0.1432</v>
+        <v>-0.1688</v>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr"/>
@@ -4781,53 +4779,53 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>GEDIK</t>
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>29.62</v>
+        <v>4.82</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>0.02</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>0.004099999999999999</v>
+        <v>-0.0379</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-0.1527</v>
+        <v>-0.1252</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>-0.1999</v>
+        <v>-0.287</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>-0.3237</v>
+        <v>-0.1775</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>-0.2505</v>
+        <v>-0.3451</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>6.61</v>
+        <v>5.1</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>0.4021</v>
+        <v>0.6583</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>0.2915</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="M75" s="7" t="n">
-        <v>0.201</v>
+        <v>0.7293999999999999</v>
       </c>
       <c r="N75" s="7" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.3481</v>
       </c>
       <c r="O75" s="7" t="n">
-        <v>0.8484999999999999</v>
+        <v>0.6628000000000001</v>
       </c>
       <c r="P75" s="7" t="n">
-        <v>0.298</v>
+        <v>0.275</v>
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
@@ -4843,31 +4841,31 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>37.78</v>
+        <v>36.3</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>0.0069</v>
+        <v>-0.0392</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>-0.0347</v>
+        <v>-0.07490000000000001</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>-0.2756</v>
+        <v>-0.3019</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>-0.3229</v>
+        <v>-0.3495</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.3682</v>
+        <v>-0.393</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>-0.4219</v>
+        <v>-0.4398</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>3.66</v>
+        <v>3.52</v>
       </c>
       <c r="K76" s="4" t="n">
         <v>0.265</v>
@@ -4897,57 +4895,57 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B77" s="6" t="n">
-        <v>71.40000000000001</v>
+        <v>28.7</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>-0.0206</v>
+        <v>-0.0311</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>-0.0049</v>
+        <v>-0.0271</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-0.0864</v>
+        <v>-0.1448</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>-0.3061</v>
+        <v>-0.2247</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>-0.1271</v>
+        <v>-0.3447</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>0.5952000000000001</v>
+        <v>-0.2896</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>26.28</v>
+        <v>6.41</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.4021</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>0.3716</v>
+        <v>0.2915</v>
       </c>
       <c r="M77" s="7" t="n">
-        <v>0.4119</v>
+        <v>0.201</v>
       </c>
       <c r="N77" s="7" t="n">
-        <v>0.9691</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="O77" s="7" t="n">
-        <v>0.3037</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="P77" s="7" t="n">
-        <v>0.0601</v>
+        <v>0.298</v>
       </c>
       <c r="Q77" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R77" s="5" t="inlineStr"/>
@@ -4955,53 +4953,53 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GARFA</t>
+          <t>KTLEV</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>22.12</v>
+        <v>5.8</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>-0.0116</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>-0.0204</v>
+        <v>-0.2418</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>-0.1874</v>
+        <v>-0.7887999999999999</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>-0.2651</v>
+        <v>-0.9011</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>-0.2184</v>
+        <v>-0.7637</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>-0.1073</v>
+        <v>0.4714</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>3.35</v>
+        <v>1.41</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0.9562999999999999</v>
+        <v>3.5578</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>0.9506</v>
+        <v>3.6471</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>0.9429999999999999</v>
+        <v>5.174600000000001</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>0.5365</v>
+        <v>5.7649</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>0.914</v>
+        <v>0.7222</v>
       </c>
       <c r="P78" s="4" t="n">
-        <v>0.496</v>
+        <v>1.5072</v>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
@@ -5013,55 +5011,57 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
-        <v>6.28</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>-0.0141</v>
+        <v>-0.035</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>-0.05139999999999999</v>
+        <v>-0.0464</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-0.1432</v>
+        <v>-0.0727</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>-0.2081</v>
+        <v>-0.3304</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>-0.2434</v>
+        <v>-0.1577</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>-0.2179</v>
+        <v>0.4253</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="J79" s="5" t="inlineStr"/>
+        <v>1.23</v>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>25.36</v>
+      </c>
       <c r="K79" s="7" t="n">
-        <v>0.3952000000000001</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="L79" s="7" t="n">
-        <v>0.4088000000000001</v>
+        <v>0.3716</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>0.4094</v>
+        <v>0.4119</v>
       </c>
       <c r="N79" s="7" t="n">
-        <v>0.7489</v>
+        <v>0.9691</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>0.7836</v>
+        <v>0.3037</v>
       </c>
       <c r="P79" s="7" t="n">
-        <v>-0.0106</v>
+        <v>0.0601</v>
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>Çeşitli Hizmetler</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R79" s="5" t="inlineStr"/>
@@ -5069,55 +5069,57 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>DAGI</t>
+          <t>GARFA</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>6.08</v>
+        <v>21.32</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>0.0116</v>
+        <v>-0.0362</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>0.0184</v>
+        <v>-0.06</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>-0.3214</v>
+        <v>-0.1936</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>-0.3518</v>
+        <v>-0.2917</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>0.005</v>
+        <v>-0.2466</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>-0.2494</v>
+        <v>-0.1566</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr"/>
+        <v>1.25</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>3.23</v>
+      </c>
       <c r="K80" s="4" t="n">
-        <v>0.5429999999999999</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>1.1389</v>
+        <v>0.9506</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>1.8634</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>0.5748</v>
+        <v>0.5365</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>0.1561</v>
+        <v>0.914</v>
       </c>
       <c r="P80" s="4" t="n">
-        <v>-0.0597</v>
+        <v>0.496</v>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr"/>
@@ -5125,55 +5127,57 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>YKSLN</t>
+          <t>SARKY</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>2.67</v>
+        <v>17.2</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>0.09880000000000001</v>
+        <v>-0.0529</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>0.1762</v>
+        <v>-0.1224</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-0.4744</v>
+        <v>-0.2308</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>-0.1785</v>
+        <v>-0.3405</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>-0.1524</v>
+        <v>-0.3944</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>-0.2235</v>
+        <v>0.152</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J81" s="5" t="inlineStr"/>
+        <v>1.28</v>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>63.03</v>
+      </c>
       <c r="K81" s="7" t="n">
-        <v>0.1126</v>
+        <v>0.5590999999999999</v>
       </c>
       <c r="L81" s="7" t="n">
-        <v>0.0263</v>
+        <v>0.3671</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>0.6127</v>
+        <v>0.2342</v>
       </c>
       <c r="N81" s="7" t="n">
-        <v>0.8754000000000001</v>
+        <v>0.8034</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>0.1443</v>
+        <v>0.0217</v>
       </c>
       <c r="P81" s="7" t="n">
-        <v>-0.04969999999999999</v>
+        <v>0.0229</v>
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R81" s="5" t="inlineStr"/>
@@ -5181,55 +5185,55 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>OZYSR</t>
+          <t>DAGI</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>11.4</v>
+        <v>5.92</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>-0.0223</v>
+        <v>-0.0263</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>-0.0052</v>
+        <v>-0.0133</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>-0.0339</v>
+        <v>-0.3415</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>-0.1304</v>
+        <v>-0.3689</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>0.0295</v>
+        <v>-0.0215</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>0.4215</v>
+        <v>-0.278</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="4" t="n">
-        <v>0.161</v>
+        <v>0.5429999999999999</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>0.1742</v>
+        <v>1.1389</v>
       </c>
       <c r="M82" s="4" t="n">
-        <v>0.6839</v>
+        <v>1.8634</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>0.5105</v>
+        <v>0.5748</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>0.042</v>
+        <v>0.1561</v>
       </c>
       <c r="P82" s="4" t="n">
-        <v>-0.0335</v>
+        <v>-0.0597</v>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R82" s="2" t="inlineStr"/>
@@ -5237,55 +5241,55 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>84.7</v>
+        <v>6.14</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>0.0156</v>
+        <v>-0.0223</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>-0.0059</v>
+        <v>-0.0711</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-0.2424</v>
+        <v>-0.1612</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>-0.35</v>
+        <v>-0.2257</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>-0.2641</v>
+        <v>-0.2602</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>-0.1964</v>
+        <v>-0.2448</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="J83" s="5" t="inlineStr"/>
       <c r="K83" s="7" t="n">
-        <v>0.3957</v>
+        <v>0.3952000000000001</v>
       </c>
       <c r="L83" s="7" t="n">
-        <v>2.0344</v>
+        <v>0.4088000000000001</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>3.8494</v>
+        <v>0.4094</v>
       </c>
       <c r="N83" s="7" t="n">
-        <v>0.889</v>
+        <v>0.7489</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>0.0349</v>
+        <v>0.7836</v>
       </c>
       <c r="P83" s="7" t="n">
-        <v>-0.0175</v>
+        <v>-0.0106</v>
       </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Çeşitli Hizmetler</t>
         </is>
       </c>
       <c r="R83" s="5" t="inlineStr"/>
@@ -5297,31 +5301,31 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>10.47</v>
+        <v>10.13</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>-0.0224</v>
+        <v>-0.0325</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>0.0029</v>
+        <v>-0.0362</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>-0.2244</v>
+        <v>-0.208</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>-0.2301</v>
+        <v>-0.2551</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>-0.0974</v>
+        <v>-0.1267</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>-0.1677</v>
+        <v>-0.2117</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>30.49</v>
+        <v>29.5</v>
       </c>
       <c r="K84" s="4" t="n">
         <v>0.1522</v>
@@ -5351,57 +5355,55 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>SARKY</t>
+          <t>ACSEL</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>18.16</v>
+        <v>83.45</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>-0.0038</v>
+        <v>-0.0148</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>-0.0786</v>
+        <v>-0.0302</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-0.2246</v>
+        <v>-0.2462</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>-0.3037</v>
+        <v>-0.3596</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>-0.3606</v>
+        <v>-0.275</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0.2789</v>
+        <v>-0.2201</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="J85" s="6" t="n">
-        <v>66.54000000000001</v>
-      </c>
+        <v>1.32</v>
+      </c>
+      <c r="J85" s="5" t="inlineStr"/>
       <c r="K85" s="7" t="n">
-        <v>0.5590999999999999</v>
+        <v>0.3957</v>
       </c>
       <c r="L85" s="7" t="n">
-        <v>0.3671</v>
+        <v>2.0344</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>0.2342</v>
+        <v>3.8494</v>
       </c>
       <c r="N85" s="7" t="n">
-        <v>0.8034</v>
+        <v>0.889</v>
       </c>
       <c r="O85" s="7" t="n">
-        <v>0.0217</v>
+        <v>0.0349</v>
       </c>
       <c r="P85" s="7" t="n">
-        <v>0.0229</v>
+        <v>-0.0175</v>
       </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R85" s="5" t="inlineStr"/>
@@ -5409,57 +5411,57 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>KTLEV</t>
+          <t>PCILT</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>6.42</v>
+        <v>30.68</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>-0.09960000000000001</v>
+        <v>-0.016</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>-0.0016</v>
+        <v>0.002</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>-0.7895</v>
+        <v>0.0199</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>-0.8906000000000001</v>
+        <v>-0.1029</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>-0.7384000000000001</v>
+        <v>0.1181</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>0.6765000000000001</v>
+        <v>0.4499</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>1.56</v>
+        <v>7.05</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>3.5578</v>
+        <v>0.763</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>3.6471</v>
+        <v>0.7087</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>5.174600000000001</v>
+        <v>0.7914</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>5.7649</v>
+        <v>1.2232</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>0.7222</v>
+        <v>0.0574</v>
       </c>
       <c r="P86" s="4" t="n">
-        <v>1.5072</v>
+        <v>0.2831</v>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr"/>
@@ -5467,57 +5469,55 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>PCILT</t>
+          <t>KNFRT</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>31.18</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>0.021</v>
+        <v>-0.0999</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>0.0156</v>
+        <v>-0.2109</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>0.0058</v>
+        <v>-0.3301</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>-0.0883</v>
+        <v>-0.308</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>0.1363</v>
+        <v>-0.3339</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>0.4919</v>
+        <v>-0.4094</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="J87" s="6" t="n">
-        <v>7.16</v>
-      </c>
+        <v>1.39</v>
+      </c>
+      <c r="J87" s="5" t="inlineStr"/>
       <c r="K87" s="7" t="n">
-        <v>0.763</v>
+        <v>0.7798</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>0.7087</v>
+        <v>1.3764</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>0.7914</v>
+        <v>26.3063</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>1.2232</v>
+        <v>0.625</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>0.0574</v>
+        <v>0.0124</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>0.2831</v>
+        <v>-0.1091</v>
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R87" s="5" t="inlineStr"/>
@@ -5525,57 +5525,55 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>ALFAS</t>
+          <t>OZYSR</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>27.36</v>
+        <v>12.02</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0544</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>-0.063</v>
+        <v>0.0461</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>-0.277</v>
+        <v>0.0544</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>-0.4114</v>
+        <v>-0.08310000000000001</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>-0.2916</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>-0.3504</v>
+        <v>0.5566</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="J88" s="3" t="n">
-        <v>32.78</v>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="4" t="n">
-        <v>0.05019999999999999</v>
+        <v>0.161</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>0.4331</v>
+        <v>0.1742</v>
       </c>
       <c r="M88" s="4" t="n">
-        <v>0.8572</v>
+        <v>0.6839</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>40.5101</v>
+        <v>0.5105</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>0.08410000000000001</v>
+        <v>0.042</v>
       </c>
       <c r="P88" s="4" t="n">
-        <v>0.05400000000000001</v>
+        <v>-0.0335</v>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R88" s="2" t="inlineStr"/>
@@ -5583,55 +5581,57 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>KNFRT</t>
+          <t>ALFAS</t>
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>9.31</v>
+        <v>26.14</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>-0.0021</v>
+        <v>-0.0446</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>-0.1266</v>
+        <v>-0.106</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-0.2299</v>
+        <v>-0.2866</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>-0.2312</v>
+        <v>-0.4376</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>-0.2599</v>
+        <v>-0.3231</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>-0.357</v>
+        <v>-0.3767</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="J89" s="5" t="inlineStr"/>
+        <v>1.45</v>
+      </c>
+      <c r="J89" s="6" t="n">
+        <v>31.32</v>
+      </c>
       <c r="K89" s="7" t="n">
-        <v>0.7798</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="L89" s="7" t="n">
-        <v>1.3764</v>
+        <v>0.4331</v>
       </c>
       <c r="M89" s="7" t="n">
-        <v>26.3063</v>
+        <v>0.8572</v>
       </c>
       <c r="N89" s="7" t="n">
-        <v>0.625</v>
+        <v>40.5101</v>
       </c>
       <c r="O89" s="7" t="n">
-        <v>0.0124</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="P89" s="7" t="n">
-        <v>-0.1091</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="Q89" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R89" s="5" t="inlineStr"/>
@@ -5643,31 +5643,31 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>30.34</v>
+        <v>28.56</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>-0.0251</v>
+        <v>-0.0587</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>-0.09050000000000001</v>
+        <v>-0.155</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>-0.2037</v>
+        <v>-0.2298</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>-0.2028</v>
+        <v>-0.2496</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>-0.1463</v>
+        <v>-0.1964</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>0.158</v>
+        <v>0.081</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>10.8</v>
+        <v>10.17</v>
       </c>
       <c r="K90" s="4" t="n">
         <v>0.3776</v>
@@ -5701,31 +5701,31 @@
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>384.5</v>
+        <v>375.5</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>-0.0166</v>
+        <v>-0.0234</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0433</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-0.07519999999999999</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>0.3397</v>
+        <v>0.3084</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>0.436</v>
+        <v>0.4024</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>1.2098</v>
+        <v>1.1084</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>10.67</v>
+        <v>10.42</v>
       </c>
       <c r="K91" s="7" t="n">
         <v>0.465</v>
@@ -5759,31 +5759,31 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>3.34</v>
+        <v>3.19</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>-0.0147</v>
+        <v>-0.0449</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>-0.1211</v>
+        <v>-0.1308</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>-0.2646</v>
+        <v>-0.2698</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>-0.5299</v>
+        <v>-0.551</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>-0.6043999999999999</v>
+        <v>-0.6222</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>0.0277</v>
+        <v>-0.0235</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>7.13</v>
+        <v>6.81</v>
       </c>
       <c r="K92" s="4" t="n">
         <v>0.51</v>
@@ -5813,57 +5813,55 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>SAFKR</t>
+          <t>KRPLS</t>
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>11.91</v>
+        <v>9.93</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>-0.0067</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.103</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>-0.1256</v>
+        <v>-0.1725</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>-0.4235</v>
+        <v>0.09359999999999999</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>-0.5502</v>
+        <v>0.09119999999999999</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>-0.4419</v>
+        <v>0.09849999999999999</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="J93" s="6" t="n">
-        <v>17.32</v>
-      </c>
+        <v>1.64</v>
+      </c>
+      <c r="J93" s="5" t="inlineStr"/>
       <c r="K93" s="7" t="n">
-        <v>0.7861</v>
+        <v>0.3576</v>
       </c>
       <c r="L93" s="7" t="n">
-        <v>0.4555</v>
+        <v>0.6872</v>
       </c>
       <c r="M93" s="7" t="n">
-        <v>0.3309</v>
+        <v>0.9115000000000001</v>
       </c>
       <c r="N93" s="7" t="n">
-        <v>0.5716</v>
+        <v>0.7781999999999999</v>
       </c>
       <c r="O93" s="7" t="n">
-        <v>0.2109</v>
+        <v>0.166</v>
       </c>
       <c r="P93" s="7" t="n">
-        <v>0.1216</v>
+        <v>-0.0342</v>
       </c>
       <c r="Q93" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R93" s="5" t="inlineStr"/>
@@ -5875,31 +5873,31 @@
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>22.38</v>
+        <v>21.4</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>-0.015</v>
+        <v>-0.0438</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>0.0182</v>
+        <v>-0.0564</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>-0.0158</v>
+        <v>-0.0421</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>0.0163</v>
+        <v>-0.0282</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>0.4704</v>
+        <v>0.406</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>0.6701</v>
+        <v>0.5711999999999999</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>10.39</v>
+        <v>9.93</v>
       </c>
       <c r="K94" s="4" t="n">
         <v>0.251</v>
@@ -5929,57 +5927,55 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>GENIL</t>
+          <t>DURDO</t>
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>5.24</v>
+        <v>5.68</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>0.03759999999999999</v>
+        <v>-0.0998</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>0.5014</v>
+        <v>-0.1125</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>-0.5518</v>
+        <v>0.1008</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>-0.442</v>
+        <v>0.1159</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>-0.4962</v>
+        <v>0.3365</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>-0.6203</v>
+        <v>0.6322</v>
       </c>
       <c r="I95" s="6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J95" s="6" t="n">
-        <v>19.1</v>
-      </c>
+        <v>1.68</v>
+      </c>
+      <c r="J95" s="5" t="inlineStr"/>
       <c r="K95" s="7" t="n">
-        <v>0.5049</v>
+        <v>0.3099</v>
       </c>
       <c r="L95" s="7" t="n">
-        <v>0.7672</v>
+        <v>0.2862</v>
       </c>
       <c r="M95" s="7" t="n">
-        <v>1.1622</v>
+        <v>0.3279</v>
       </c>
       <c r="N95" s="7" t="n">
-        <v>1.2274</v>
+        <v>0.1519</v>
       </c>
       <c r="O95" s="7" t="n">
-        <v>0.0922</v>
+        <v>0.0876</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>0.1305</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R95" s="5" t="inlineStr"/>
@@ -5991,31 +5987,31 @@
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>24.3</v>
+        <v>22.88</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>0.0288</v>
+        <v>-0.0584</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>-0.083</v>
+        <v>-0.1475</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>-0.2957</v>
+        <v>-0.319</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>-0.3411</v>
+        <v>-0.3796</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>-0.3919</v>
+        <v>-0.4274</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>-0.3254</v>
+        <v>-0.3783</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>13.39</v>
+        <v>12.61</v>
       </c>
       <c r="K96" s="4" t="n">
         <v>0.1436</v>
@@ -6045,57 +6041,57 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>FONET</t>
+          <t>SAYAS</t>
         </is>
       </c>
       <c r="B97" s="6" t="n">
-        <v>4.05</v>
+        <v>35.64</v>
       </c>
       <c r="C97" s="7" t="n">
-        <v>-0.0074</v>
+        <v>-0.0546</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>-0.0625</v>
+        <v>-0.1005</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>-0.096</v>
+        <v>-0.2872</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>-0.2043</v>
+        <v>-0.2497</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>-0.2105</v>
+        <v>-0.1837</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>0.4138</v>
+        <v>-0.3012</v>
       </c>
       <c r="I97" s="6" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="J97" s="6" t="n">
-        <v>13.16</v>
+        <v>14.2</v>
       </c>
       <c r="K97" s="7" t="n">
-        <v>1.0251</v>
+        <v>0.486</v>
       </c>
       <c r="L97" s="7" t="n">
-        <v>2.0469</v>
+        <v>1.4655</v>
       </c>
       <c r="M97" s="7" t="n">
-        <v>1.6971</v>
+        <v>2.3632</v>
       </c>
       <c r="N97" s="7" t="n">
-        <v>1.6785</v>
+        <v>6.118200000000001</v>
       </c>
       <c r="O97" s="7" t="n">
-        <v>0.4396</v>
+        <v>0.1798</v>
       </c>
       <c r="P97" s="7" t="n">
-        <v>0.8814</v>
+        <v>0.1493</v>
       </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R97" s="5" t="inlineStr"/>
@@ -6103,55 +6099,57 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>KRPLS</t>
+          <t>SAFKR</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>11.03</v>
+        <v>12.16</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>0.0018</v>
+        <v>0.021</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>-0.0054</v>
+        <v>-0.0342</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>-0.1176</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>0.2148</v>
+        <v>-0.4114</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>0.2121</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>0.1722</v>
+        <v>-0.4126</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr"/>
+        <v>1.75</v>
+      </c>
+      <c r="J98" s="3" t="n">
+        <v>17.68</v>
+      </c>
       <c r="K98" s="4" t="n">
-        <v>0.3576</v>
+        <v>0.7861</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>0.6872</v>
+        <v>0.4555</v>
       </c>
       <c r="M98" s="4" t="n">
-        <v>0.9115000000000001</v>
+        <v>0.3309</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>0.7781999999999999</v>
+        <v>0.5716</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>0.166</v>
+        <v>0.2109</v>
       </c>
       <c r="P98" s="4" t="n">
-        <v>-0.0342</v>
+        <v>0.1216</v>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr"/>
@@ -6159,57 +6157,57 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>SAYAS</t>
+          <t>FONET</t>
         </is>
       </c>
       <c r="B99" s="6" t="n">
-        <v>37.7</v>
+        <v>3.92</v>
       </c>
       <c r="C99" s="7" t="n">
-        <v>-0.011</v>
+        <v>-0.0321</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>-0.0348</v>
+        <v>-0.05769999999999999</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>-0.2637</v>
+        <v>-0.07980000000000001</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>-0.2063</v>
+        <v>-0.2299</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>-0.1365</v>
+        <v>-0.2359</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>-0.2557</v>
+        <v>0.334</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>15.02</v>
+        <v>12.74</v>
       </c>
       <c r="K99" s="7" t="n">
-        <v>0.486</v>
+        <v>1.0251</v>
       </c>
       <c r="L99" s="7" t="n">
-        <v>1.4655</v>
+        <v>2.0469</v>
       </c>
       <c r="M99" s="7" t="n">
-        <v>2.3632</v>
+        <v>1.6971</v>
       </c>
       <c r="N99" s="7" t="n">
-        <v>6.118200000000001</v>
+        <v>1.6785</v>
       </c>
       <c r="O99" s="7" t="n">
-        <v>0.1798</v>
+        <v>0.4396</v>
       </c>
       <c r="P99" s="7" t="n">
-        <v>0.1493</v>
+        <v>0.8814</v>
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R99" s="5" t="inlineStr"/>
@@ -6217,57 +6215,57 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>GENIL</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>427.5</v>
+        <v>5.15</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>0.0018</v>
+        <v>-0.0172</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.1573</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>-0.0217</v>
+        <v>-0.5365</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>-0.0121</v>
+        <v>-0.4515</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.5047999999999999</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>0.2648</v>
+        <v>-0.6284000000000001</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>13.35</v>
+        <v>18.78</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0.3601</v>
+        <v>0.5049</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>0.3635</v>
+        <v>0.7672</v>
       </c>
       <c r="M100" s="4" t="n">
-        <v>0.5899</v>
+        <v>1.1622</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>0.1175</v>
+        <v>1.2274</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>0.2737</v>
+        <v>0.0922</v>
       </c>
       <c r="P100" s="4" t="n">
-        <v>0.2987</v>
+        <v>0.1305</v>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>Sağlık hizmetleri</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R100" s="2" t="inlineStr"/>
@@ -6275,55 +6273,57 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>DURDO</t>
+          <t>MPARK</t>
         </is>
       </c>
       <c r="B101" s="6" t="n">
-        <v>6.31</v>
+        <v>416</v>
       </c>
       <c r="C101" s="7" t="n">
-        <v>-0.0999</v>
+        <v>-0.0269</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0183</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>0.2158</v>
+        <v>-0.0263</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>0.2397</v>
+        <v>-0.0387</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>0.4847</v>
+        <v>-0.0917</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>0.8559</v>
+        <v>0.2381</v>
       </c>
       <c r="I101" s="6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="J101" s="5" t="inlineStr"/>
+        <v>1.81</v>
+      </c>
+      <c r="J101" s="6" t="n">
+        <v>12.99</v>
+      </c>
       <c r="K101" s="7" t="n">
-        <v>0.3099</v>
+        <v>0.3601</v>
       </c>
       <c r="L101" s="7" t="n">
-        <v>0.2862</v>
+        <v>0.3635</v>
       </c>
       <c r="M101" s="7" t="n">
-        <v>0.3279</v>
+        <v>0.5899</v>
       </c>
       <c r="N101" s="7" t="n">
-        <v>0.1519</v>
+        <v>0.1175</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>0.0876</v>
+        <v>0.2737</v>
       </c>
       <c r="P101" s="7" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.2987</v>
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Sağlık hizmetleri</t>
         </is>
       </c>
       <c r="R101" s="5" t="inlineStr"/>
@@ -6331,57 +6331,57 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>ENERY</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>246.25</v>
+        <v>13.85</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>-0.0158</v>
+        <v>-0.04480000000000001</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>-0.0617</v>
+        <v>-0.0253</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>-0.1411</v>
+        <v>0.0863</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>-0.1871</v>
+        <v>0.4191</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>-0.1463</v>
+        <v>0.5086999999999999</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>-0.0207</v>
+        <v>0.4147</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>9.69</v>
+        <v>22.09</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>1.7224</v>
+        <v>0.4279</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>1.8184</v>
+        <v>0.7162999999999999</v>
       </c>
       <c r="M102" s="4" t="n">
-        <v>1.3297</v>
+        <v>0.8373999999999999</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>5.0053</v>
+        <v>0.6103000000000001</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>0.0381</v>
+        <v>0.2099</v>
       </c>
       <c r="P102" s="4" t="n">
-        <v>0.2862</v>
+        <v>0.1017</v>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr"/>
@@ -6389,57 +6389,57 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>ENERY</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B103" s="6" t="n">
-        <v>14.5</v>
+        <v>244.4</v>
       </c>
       <c r="C103" s="7" t="n">
-        <v>0.0328</v>
+        <v>-0.0077</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>0.032</v>
+        <v>-0.1015</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>0.1694</v>
+        <v>-0.1425</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>0.4857</v>
+        <v>-0.1934</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>0.5795</v>
+        <v>-0.1529</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>0.5393</v>
+        <v>-0.0472</v>
       </c>
       <c r="I103" s="6" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>23.12</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="K103" s="7" t="n">
-        <v>0.4279</v>
+        <v>1.7224</v>
       </c>
       <c r="L103" s="7" t="n">
-        <v>0.7162999999999999</v>
+        <v>1.8184</v>
       </c>
       <c r="M103" s="7" t="n">
-        <v>0.8373999999999999</v>
+        <v>1.3297</v>
       </c>
       <c r="N103" s="7" t="n">
-        <v>0.6103000000000001</v>
+        <v>5.0053</v>
       </c>
       <c r="O103" s="7" t="n">
-        <v>0.2099</v>
+        <v>0.0381</v>
       </c>
       <c r="P103" s="7" t="n">
-        <v>0.1017</v>
+        <v>0.2862</v>
       </c>
       <c r="Q103" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="R103" s="5" t="inlineStr"/>
@@ -6447,57 +6447,57 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>SANEL</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>17.3</v>
+        <v>27.5</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>0.0243</v>
+        <v>-0.0269</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>0.3432</v>
+        <v>-0.0678</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>-0.2478</v>
+        <v>-0.3834</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>-0.5739</v>
+        <v>-0.6403</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>-0.4222</v>
+        <v>-0.2361</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>0.2683</v>
+        <v>0.0029</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>2.23</v>
+        <v>2.65</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>2.1748</v>
+        <v>0.309</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>2.2285</v>
+        <v>1.4614</v>
       </c>
       <c r="M104" s="4" t="n">
-        <v>2.5519</v>
+        <v>1.5381</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>7.8348</v>
+        <v>2.2148</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>0.887</v>
+        <v>0.1491</v>
       </c>
       <c r="P104" s="4" t="n">
-        <v>1.1538</v>
+        <v>1.0947</v>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr"/>
@@ -6505,57 +6505,57 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>SANEL</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B105" s="6" t="n">
-        <v>28.26</v>
+        <v>200.4</v>
       </c>
       <c r="C105" s="7" t="n">
-        <v>-0.0355</v>
+        <v>-0.04480000000000001</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.1017</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>-0.393</v>
+        <v>-0.1133</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>-0.6303</v>
+        <v>-0.1425</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>-0.215</v>
+        <v>-0.221</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>0.0329</v>
+        <v>-0.1447</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="J105" s="6" t="n">
-        <v>2.72</v>
+        <v>18.73</v>
       </c>
       <c r="K105" s="7" t="n">
-        <v>0.309</v>
+        <v>0.493</v>
       </c>
       <c r="L105" s="7" t="n">
-        <v>1.4614</v>
+        <v>0.3835</v>
       </c>
       <c r="M105" s="7" t="n">
-        <v>1.5381</v>
+        <v>0.4282</v>
       </c>
       <c r="N105" s="7" t="n">
-        <v>2.2148</v>
+        <v>0.1825</v>
       </c>
       <c r="O105" s="7" t="n">
-        <v>0.1491</v>
+        <v>0.2029</v>
       </c>
       <c r="P105" s="7" t="n">
-        <v>1.0947</v>
+        <v>0.1296</v>
       </c>
       <c r="Q105" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R105" s="5" t="inlineStr"/>
@@ -6563,57 +6563,57 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GLYHO</t>
+          <t>AHGAZ</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>17.41</v>
+        <v>46.48</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>-0.0169</v>
+        <v>-0.0296</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>0.0284</v>
+        <v>-0.0353</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>0.0616</v>
+        <v>0.1304</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>-0.0029</v>
+        <v>0.2833</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>0.1005</v>
+        <v>0.8652</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>0.7170000000000001</v>
+        <v>0.7659999999999999</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>5.81</v>
+        <v>22</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0.2312</v>
+        <v>0.659</v>
       </c>
       <c r="L106" s="4" t="n">
-        <v>0.317</v>
+        <v>1.7979</v>
       </c>
       <c r="M106" s="4" t="n">
-        <v>0.3503</v>
+        <v>2.1313</v>
       </c>
       <c r="N106" s="4" t="n">
-        <v>0.4888</v>
+        <v>2.8917</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>0.3457</v>
+        <v>0.1977</v>
       </c>
       <c r="P106" s="4" t="n">
-        <v>-0.2226</v>
+        <v>0.1152</v>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr"/>
@@ -6621,57 +6621,57 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>AHGAZ</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="B107" s="6" t="n">
-        <v>47.9</v>
+        <v>17.33</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>0.0157</v>
+        <v>0.0017</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>-0.0042</v>
+        <v>0.2239</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>0.1746</v>
+        <v>-0.2123</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>0.3225</v>
+        <v>-0.5732</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>0.9222</v>
+        <v>-0.4212</v>
       </c>
       <c r="H107" s="7" t="n">
-        <v>0.9023</v>
+        <v>0.4442</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="J107" s="6" t="n">
-        <v>22.67</v>
+        <v>2.24</v>
       </c>
       <c r="K107" s="7" t="n">
-        <v>0.659</v>
+        <v>2.1748</v>
       </c>
       <c r="L107" s="7" t="n">
-        <v>1.7979</v>
+        <v>2.2285</v>
       </c>
       <c r="M107" s="7" t="n">
-        <v>2.1313</v>
+        <v>2.5519</v>
       </c>
       <c r="N107" s="7" t="n">
-        <v>2.8917</v>
+        <v>7.8348</v>
       </c>
       <c r="O107" s="7" t="n">
-        <v>0.1977</v>
+        <v>0.887</v>
       </c>
       <c r="P107" s="7" t="n">
-        <v>0.1152</v>
+        <v>1.1538</v>
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R107" s="5" t="inlineStr"/>
@@ -6679,57 +6679,57 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>VBTYZ</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>209.8</v>
+        <v>19.92</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>-0.001</v>
+        <v>-0.0537</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>-0.0717</v>
+        <v>-0.1634</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>-0.0953</v>
+        <v>-0.3874</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>-0.1023</v>
+        <v>-0.3191</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>-0.1845</v>
+        <v>-0.0722</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>-0.1095</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>19.61</v>
+        <v>13.03</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0.493</v>
+        <v>0.5342</v>
       </c>
       <c r="L108" s="4" t="n">
-        <v>0.3835</v>
+        <v>0.9976999999999999</v>
       </c>
       <c r="M108" s="4" t="n">
-        <v>0.4282</v>
+        <v>3.6408</v>
       </c>
       <c r="N108" s="4" t="n">
-        <v>0.1825</v>
+        <v>1.3528</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>0.2029</v>
+        <v>0.2074</v>
       </c>
       <c r="P108" s="4" t="n">
-        <v>0.1296</v>
+        <v>-9.062000000000001</v>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr"/>
@@ -6737,57 +6737,57 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>VBTYZ</t>
+          <t>GRSEL</t>
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>21.04</v>
+        <v>275</v>
       </c>
       <c r="C109" s="7" t="n">
-        <v>-0.0349</v>
+        <v>-0.0517</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>-0.0723</v>
+        <v>0.0018</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>-0.3738</v>
+        <v>-0.0614</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>-0.2804</v>
+        <v>-0.1277</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>-0.0196</v>
+        <v>-0.1352</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>0.1631</v>
+        <v>-0.2226</v>
       </c>
       <c r="I109" s="6" t="n">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="J109" s="6" t="n">
-        <v>13.77</v>
+        <v>8.35</v>
       </c>
       <c r="K109" s="7" t="n">
-        <v>0.5342</v>
+        <v>0.3337</v>
       </c>
       <c r="L109" s="7" t="n">
-        <v>0.9976999999999999</v>
+        <v>0.6940999999999999</v>
       </c>
       <c r="M109" s="7" t="n">
-        <v>3.6408</v>
+        <v>0.2722</v>
       </c>
       <c r="N109" s="7" t="n">
-        <v>1.3528</v>
+        <v>0.7318000000000001</v>
       </c>
       <c r="O109" s="7" t="n">
-        <v>0.2074</v>
+        <v>0.3275</v>
       </c>
       <c r="P109" s="7" t="n">
-        <v>-9.062000000000001</v>
+        <v>0.3613</v>
       </c>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R109" s="5" t="inlineStr"/>
@@ -6795,57 +6795,57 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GRSEL</t>
+          <t>GLYHO</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>290</v>
+        <v>17.51</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>0.0761</v>
+        <v>-0.0023</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>-0.0244</v>
+        <v>0.0775</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>-0.0801</v>
+        <v>0.0029</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>-0.08810000000000001</v>
+        <v>0.1068</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>-0.157</v>
+        <v>0.7406</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>8.81</v>
+        <v>5.85</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0.3337</v>
+        <v>0.2312</v>
       </c>
       <c r="L110" s="4" t="n">
-        <v>0.6940999999999999</v>
+        <v>0.317</v>
       </c>
       <c r="M110" s="4" t="n">
-        <v>0.2722</v>
+        <v>0.3503</v>
       </c>
       <c r="N110" s="4" t="n">
-        <v>0.7318000000000001</v>
+        <v>0.4888</v>
       </c>
       <c r="O110" s="4" t="n">
-        <v>0.3275</v>
+        <v>0.3457</v>
       </c>
       <c r="P110" s="4" t="n">
-        <v>0.3613</v>
+        <v>-0.2226</v>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr"/>
@@ -6857,31 +6857,31 @@
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>401.5</v>
+        <v>381</v>
       </c>
       <c r="C111" s="7" t="n">
-        <v>-0.0159</v>
+        <v>-0.05110000000000001</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>0.0152</v>
+        <v>-0.0522</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>-0.0641</v>
+        <v>-0.078</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>0.0229</v>
+        <v>-0.0293</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>0.0735</v>
+        <v>0.0187</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>0.4694</v>
+        <v>0.3943</v>
       </c>
       <c r="I111" s="6" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="J111" s="6" t="n">
-        <v>17.56</v>
+        <v>16.66</v>
       </c>
       <c r="K111" s="7" t="n">
         <v>0.4214</v>
@@ -6915,31 +6915,31 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>47.22</v>
+        <v>46</v>
       </c>
       <c r="C112" s="4" t="n">
-        <v>0.023</v>
+        <v>-0.0258</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>-0.0296</v>
+        <v>-0.0809</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>-0.3396</v>
+        <v>-0.341</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>-0.4634</v>
+        <v>-0.4772999999999999</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>0.1835</v>
+        <v>0.1529</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>0.826</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>33.47</v>
+        <v>32.61</v>
       </c>
       <c r="K112" s="4" t="n">
         <v>0.8139</v>
@@ -6973,31 +6973,31 @@
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>79.75</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>-0.016</v>
+        <v>-0.0364</v>
       </c>
       <c r="D113" s="7" t="n">
-        <v>-0.0274</v>
+        <v>-0.0447</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>-0.0112</v>
+        <v>-0.0039</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>-0.1139</v>
+        <v>-0.1461</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>-0.0019</v>
+        <v>-0.0382</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>0.7481</v>
+        <v>0.6282</v>
       </c>
       <c r="I113" s="6" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="J113" s="6" t="n">
-        <v>10.77</v>
+        <v>10.38</v>
       </c>
       <c r="K113" s="7" t="n">
         <v>0.4257</v>
@@ -7031,31 +7031,31 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>42.86</v>
+        <v>41.3</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>0.0052</v>
+        <v>-0.0364</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>0.0343</v>
+        <v>-0.04</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>-0.1781</v>
+        <v>-0.1902</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>-0.1774</v>
+        <v>-0.2073</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>-0.0711</v>
+        <v>-0.1049</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>0.8008</v>
+        <v>0.7208</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>27.37</v>
+        <v>26.37</v>
       </c>
       <c r="K114" s="4" t="n">
         <v>1.2681</v>
@@ -7089,31 +7089,31 @@
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>114.1</v>
+        <v>114</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>-0.0484</v>
+        <v>-0.0009</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.08800000000000001</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-0.1762</v>
+        <v>-0.1224</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>-0.1389</v>
+        <v>-0.1396</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>0.1781</v>
+        <v>0.1771</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>1.6486</v>
+        <v>1.6723</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="J115" s="6" t="n">
-        <v>10.23</v>
+        <v>10.22</v>
       </c>
       <c r="K115" s="7" t="n">
         <v>2.4396</v>
@@ -7147,31 +7147,31 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>32.04</v>
+        <v>31.14</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>-0.0154</v>
+        <v>-0.0281</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>-0.0326</v>
+        <v>-0.0693</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>-0.0664</v>
+        <v>-0.0529</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>-0.1515</v>
+        <v>-0.1753</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>-0.2174</v>
+        <v>-0.2394</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>-0.3342</v>
+        <v>-0.3422</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>23.38</v>
+        <v>22.72</v>
       </c>
       <c r="K116" s="4" t="n">
         <v>0.3957</v>
@@ -7205,31 +7205,31 @@
         </is>
       </c>
       <c r="B117" s="6" t="n">
-        <v>133.1</v>
+        <v>127.2</v>
       </c>
       <c r="C117" s="7" t="n">
-        <v>0.0068</v>
+        <v>-0.0443</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>-0.1067</v>
+        <v>-0.1317</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>-0.0459</v>
+        <v>-0.0536</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>-0.0228</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>-0.0506</v>
+        <v>-0.09269999999999999</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>-0.1943</v>
+        <v>-0.1794</v>
       </c>
       <c r="I117" s="6" t="n">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>14.47</v>
+        <v>13.83</v>
       </c>
       <c r="K117" s="7" t="n">
         <v>0.5617</v>
@@ -7263,31 +7263,31 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>61.95</v>
+        <v>60.45</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>-0.0167</v>
+        <v>-0.0242</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>-0.0506</v>
+        <v>-0.0664</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>-0.1975</v>
+        <v>-0.182</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>-0.1112</v>
+        <v>-0.1327</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>0.4743</v>
+        <v>0.4386</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>1.492</v>
+        <v>1.365</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>15.43</v>
+        <v>15.05</v>
       </c>
       <c r="K118" s="4" t="n">
         <v>2.0657</v>
@@ -7317,57 +7317,57 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>ATATP</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="B119" s="6" t="n">
-        <v>221</v>
+        <v>372.75</v>
       </c>
       <c r="C119" s="7" t="n">
-        <v>-0.0076</v>
+        <v>-0.0551</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>-0.0608</v>
+        <v>-0.1018</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>-0.2107</v>
+        <v>-0.1808</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>0.0284</v>
+        <v>-0.1172</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>0.5337</v>
+        <v>-0.2927</v>
       </c>
       <c r="H119" s="7" t="n">
-        <v>0.625</v>
+        <v>0.342</v>
       </c>
       <c r="I119" s="6" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>4.55</v>
+        <v>16.16</v>
       </c>
       <c r="K119" s="7" t="n">
-        <v>0.3072</v>
+        <v>0.1897</v>
       </c>
       <c r="L119" s="7" t="n">
-        <v>0.2985</v>
+        <v>0.4879</v>
       </c>
       <c r="M119" s="7" t="n">
-        <v>0.3487</v>
+        <v>0.6424</v>
       </c>
       <c r="N119" s="7" t="n">
-        <v>0.6609999999999999</v>
+        <v>0.5356000000000001</v>
       </c>
       <c r="O119" s="7" t="n">
-        <v>0.3268</v>
+        <v>0.2097</v>
       </c>
       <c r="P119" s="7" t="n">
-        <v>0.7543000000000001</v>
+        <v>0.2503</v>
       </c>
       <c r="Q119" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R119" s="5" t="inlineStr"/>
@@ -7375,57 +7375,57 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>ATATP</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>394.5</v>
+        <v>216.1</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>0.009000000000000001</v>
+        <v>-0.0222</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>-0.0113</v>
+        <v>-0.1125</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>-0.1777</v>
+        <v>-0.1996</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>-0.06570000000000001</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>-0.2514</v>
+        <v>0.4997</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>0.4089</v>
+        <v>0.5774</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>3.33</v>
+        <v>3.16</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>17.1</v>
+        <v>4.45</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0.1897</v>
+        <v>0.3072</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>0.4879</v>
+        <v>0.2985</v>
       </c>
       <c r="M120" s="4" t="n">
-        <v>0.6424</v>
+        <v>0.3487</v>
       </c>
       <c r="N120" s="4" t="n">
-        <v>0.5356000000000001</v>
+        <v>0.6609999999999999</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>0.2097</v>
+        <v>0.3268</v>
       </c>
       <c r="P120" s="4" t="n">
-        <v>0.2503</v>
+        <v>0.7543000000000001</v>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr"/>
@@ -7437,31 +7437,31 @@
         </is>
       </c>
       <c r="B121" s="6" t="n">
-        <v>89.2</v>
+        <v>84.45</v>
       </c>
       <c r="C121" s="7" t="n">
-        <v>0.0253</v>
+        <v>-0.0533</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>0.02</v>
+        <v>-0.03759999999999999</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-0.1679</v>
+        <v>-0.1721</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>-0.3053</v>
+        <v>-0.3423</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>0.04269999999999999</v>
+        <v>-0.0129</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>0.1081</v>
+        <v>0.0491</v>
       </c>
       <c r="I121" s="6" t="n">
-        <v>3.36</v>
+        <v>3.18</v>
       </c>
       <c r="J121" s="6" t="n">
-        <v>19.72</v>
+        <v>18.67</v>
       </c>
       <c r="K121" s="7" t="n">
         <v>0.5093</v>
@@ -7491,57 +7491,57 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>KRONT</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>18.48</v>
+        <v>110.5</v>
       </c>
       <c r="C122" s="4" t="n">
-        <v>0.0098</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.1354</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>-0.1484</v>
+        <v>-0.3915</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>-0.2196</v>
+        <v>-0.3646</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>-0.1124</v>
+        <v>-0.2483</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>0.3162</v>
+        <v>2.1608</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>3.44</v>
+        <v>3.26</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>24.34</v>
+        <v>12.31</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0.6388</v>
+        <v>1.164</v>
       </c>
       <c r="L122" s="4" t="n">
-        <v>0.5896</v>
+        <v>0.8115000000000001</v>
       </c>
       <c r="M122" s="4" t="n">
-        <v>1.5604</v>
+        <v>1.571</v>
       </c>
       <c r="N122" s="4" t="n">
-        <v>5.569299999999999</v>
+        <v>1.7066</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>0.3874</v>
+        <v>0.1178</v>
       </c>
       <c r="P122" s="4" t="n">
-        <v>13.8834</v>
+        <v>0.3402000000000001</v>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr"/>
@@ -7549,57 +7549,57 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>KRONT</t>
         </is>
       </c>
       <c r="B123" s="6" t="n">
-        <v>119.7</v>
+        <v>17.61</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>-0.1</v>
+        <v>-0.0471</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>-0.07139999999999999</v>
+        <v>-0.0727</v>
       </c>
       <c r="E123" s="7" t="n">
-        <v>-0.1874</v>
+        <v>-0.1809</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>-0.3117</v>
+        <v>-0.2563</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>-0.1857</v>
+        <v>-0.1542</v>
       </c>
       <c r="H123" s="7" t="n">
-        <v>2.5144</v>
+        <v>0.2162</v>
       </c>
       <c r="I123" s="6" t="n">
-        <v>3.53</v>
+        <v>3.28</v>
       </c>
       <c r="J123" s="6" t="n">
-        <v>13.33</v>
+        <v>23.19</v>
       </c>
       <c r="K123" s="7" t="n">
-        <v>1.164</v>
+        <v>0.6388</v>
       </c>
       <c r="L123" s="7" t="n">
-        <v>0.8115000000000001</v>
+        <v>0.5896</v>
       </c>
       <c r="M123" s="7" t="n">
-        <v>1.571</v>
+        <v>1.5604</v>
       </c>
       <c r="N123" s="7" t="n">
-        <v>1.7066</v>
+        <v>5.569299999999999</v>
       </c>
       <c r="O123" s="7" t="n">
-        <v>0.1178</v>
+        <v>0.3874</v>
       </c>
       <c r="P123" s="7" t="n">
-        <v>0.3402000000000001</v>
+        <v>13.8834</v>
       </c>
       <c r="Q123" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R123" s="5" t="inlineStr"/>
@@ -7611,28 +7611,28 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>-0.027</v>
+        <v>-0.0323</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>0.0197</v>
+        <v>-0.0323</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>-0.2323</v>
+        <v>-0.2771</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>-0.3542</v>
+        <v>-0.375</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>-0.4317</v>
+        <v>-0.45</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>-0.1112</v>
+        <v>-0.1525</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="4" t="n">
@@ -7667,31 +7667,31 @@
         </is>
       </c>
       <c r="B125" s="6" t="n">
-        <v>26.42</v>
+        <v>24.7</v>
       </c>
       <c r="C125" s="7" t="n">
-        <v>0.0015</v>
+        <v>-0.06509999999999999</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>-0.0393</v>
+        <v>-0.1121</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-0.2297</v>
+        <v>-0.2395</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>-0.3632</v>
+        <v>-0.4047</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>0.2124</v>
+        <v>0.1334</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>0.8472</v>
+        <v>0.7015</v>
       </c>
       <c r="I125" s="6" t="n">
-        <v>3.98</v>
+        <v>3.72</v>
       </c>
       <c r="J125" s="6" t="n">
-        <v>9.85</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K125" s="7" t="n">
         <v>1.4662</v>
@@ -7725,31 +7725,31 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>183.2</v>
+        <v>164.9</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>-0.0508</v>
+        <v>-0.0999</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>-0.0235</v>
+        <v>-0.1663</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>-0.3515</v>
+        <v>-0.3943</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>-0.4133</v>
+        <v>-0.4719</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>-0.0508</v>
+        <v>-0.1456</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>1.0677</v>
+        <v>0.7789</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>4.17</v>
+        <v>3.76</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>17.97</v>
+        <v>16.18</v>
       </c>
       <c r="K126" s="4" t="n">
         <v>0.4338</v>
@@ -7783,31 +7783,31 @@
         </is>
       </c>
       <c r="B127" s="8" t="n">
-        <v>10945</v>
+        <v>11100</v>
       </c>
       <c r="C127" s="7" t="n">
-        <v>0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>0.0316</v>
+        <v>0.0457</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>0.0037</v>
+        <v>0.0128</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>-0.0023</v>
+        <v>0.0119</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>0.1524</v>
+        <v>0.1687</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>0.0151</v>
+        <v>0.0367</v>
       </c>
       <c r="I127" s="6" t="n">
-        <v>4.29</v>
+        <v>4.35</v>
       </c>
       <c r="J127" s="6" t="n">
-        <v>20.1</v>
+        <v>20.38</v>
       </c>
       <c r="K127" s="7" t="n">
         <v>0.2032</v>
@@ -7837,57 +7837,57 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>DMRGD</t>
+          <t>ONCSM</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>6.2</v>
+        <v>93</v>
       </c>
       <c r="C128" s="4" t="n">
-        <v>-0.06059999999999999</v>
+        <v>-0.0159</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>-0.293</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>-0.3992</v>
+        <v>-0.3845</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>-0.5533</v>
+        <v>-0.6815000000000001</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>0.2133</v>
+        <v>-0.6684</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>0.9329999999999999</v>
+        <v>-0.4609</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>4.35</v>
+        <v>4.39</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>53.04</v>
+        <v>30.71</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0.4591</v>
+        <v>0.5028</v>
       </c>
       <c r="L128" s="4" t="n">
-        <v>0.4162</v>
+        <v>1.6135</v>
       </c>
       <c r="M128" s="4" t="n">
-        <v>3.3554</v>
+        <v>2.0025</v>
       </c>
       <c r="N128" s="4" t="n">
-        <v>0.2283</v>
+        <v>9.2562</v>
       </c>
       <c r="O128" s="4" t="n">
-        <v>0.2808</v>
+        <v>0.3063</v>
       </c>
       <c r="P128" s="4" t="n">
-        <v>0.0866</v>
+        <v>0.1832</v>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr"/>
@@ -7895,57 +7895,57 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>ONCSM</t>
+          <t>FMIZP</t>
         </is>
       </c>
       <c r="B129" s="6" t="n">
-        <v>94.5</v>
+        <v>224</v>
       </c>
       <c r="C129" s="7" t="n">
-        <v>0.09949999999999999</v>
+        <v>-0.0596</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.1618</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>-0.4238</v>
+        <v>-0.2195</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>-0.6764</v>
+        <v>-0.2381</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>-0.6631</v>
+        <v>-0.2202</v>
       </c>
       <c r="H129" s="7" t="n">
-        <v>-0.4506</v>
+        <v>-0.2662</v>
       </c>
       <c r="I129" s="6" t="n">
-        <v>4.46</v>
+        <v>4.49</v>
       </c>
       <c r="J129" s="6" t="n">
-        <v>31.21</v>
+        <v>22.66</v>
       </c>
       <c r="K129" s="7" t="n">
-        <v>0.5028</v>
+        <v>0.2837</v>
       </c>
       <c r="L129" s="7" t="n">
-        <v>1.6135</v>
+        <v>0.7895</v>
       </c>
       <c r="M129" s="7" t="n">
-        <v>2.0025</v>
+        <v>0.1712</v>
       </c>
       <c r="N129" s="7" t="n">
-        <v>9.2562</v>
+        <v>0.9815999999999999</v>
       </c>
       <c r="O129" s="7" t="n">
-        <v>0.3063</v>
+        <v>0.1378</v>
       </c>
       <c r="P129" s="7" t="n">
-        <v>0.1832</v>
+        <v>0.2179</v>
       </c>
       <c r="Q129" s="5" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R129" s="5" t="inlineStr"/>
@@ -7953,57 +7953,57 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>FMIZP</t>
+          <t>DMRGD</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>238.2</v>
+        <v>6.74</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>-0.0169</v>
+        <v>0.08710000000000001</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.1359</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>-0.1863</v>
+        <v>-0.3587</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>-0.1898</v>
+        <v>-0.5144</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>-0.1708</v>
+        <v>0.319</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>-0.2241</v>
+        <v>1.0643</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>4.77</v>
+        <v>4.73</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>24.1</v>
+        <v>57.66</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0.2837</v>
+        <v>0.4591</v>
       </c>
       <c r="L130" s="4" t="n">
-        <v>0.7895</v>
+        <v>0.4162</v>
       </c>
       <c r="M130" s="4" t="n">
-        <v>0.1712</v>
+        <v>3.3554</v>
       </c>
       <c r="N130" s="4" t="n">
-        <v>0.9815999999999999</v>
+        <v>0.2283</v>
       </c>
       <c r="O130" s="4" t="n">
-        <v>0.1378</v>
+        <v>0.2808</v>
       </c>
       <c r="P130" s="4" t="n">
-        <v>0.2179</v>
+        <v>0.0866</v>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr"/>
@@ -8015,31 +8015,31 @@
         </is>
       </c>
       <c r="B131" s="6" t="n">
-        <v>351</v>
+        <v>340.25</v>
       </c>
       <c r="C131" s="7" t="n">
-        <v>0.0086</v>
+        <v>-0.0306</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>-0.0014</v>
+        <v>-0.032</v>
       </c>
       <c r="E131" s="7" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0999</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>0.0021</v>
+        <v>-0.0286</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>-0.1491</v>
+        <v>-0.1752</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>0.6548999999999999</v>
+        <v>0.6405</v>
       </c>
       <c r="I131" s="6" t="n">
-        <v>5.22</v>
+        <v>5.06</v>
       </c>
       <c r="J131" s="6" t="n">
-        <v>43.12</v>
+        <v>41.8</v>
       </c>
       <c r="K131" s="7" t="n">
         <v>0.5623</v>
@@ -8069,55 +8069,55 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>EUKYO</t>
+          <t>PRKAB</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>9.1</v>
+        <v>21.54</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>-0.0215</v>
+        <v>-0.0675</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>-0.0215</v>
+        <v>-0.1244</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>-0.3636</v>
+        <v>-0.2988</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>-0.2602</v>
+        <v>-0.3846</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>0.2698</v>
+        <v>-0.4588</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>0.7422</v>
+        <v>-0.3331</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>6.58</v>
+        <v>6.25</v>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="4" t="n">
-        <v>0.5533</v>
+        <v>0.3515</v>
       </c>
       <c r="L132" s="4" t="n">
-        <v>0.6938</v>
+        <v>0.2524</v>
       </c>
       <c r="M132" s="4" t="n">
-        <v>0.6357</v>
+        <v>0.0007000000000000001</v>
       </c>
       <c r="N132" s="4" t="n">
-        <v>0.08689999999999999</v>
+        <v>0.1345</v>
       </c>
       <c r="O132" s="4" t="n">
-        <v>0.2589</v>
+        <v>0.0398</v>
       </c>
       <c r="P132" s="4" t="n">
-        <v>-0.2304</v>
+        <v>-0.5093</v>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R132" s="2" t="inlineStr"/>
@@ -8125,55 +8125,55 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>PRKAB</t>
+          <t>EUKYO</t>
         </is>
       </c>
       <c r="B133" s="6" t="n">
-        <v>23.1</v>
+        <v>9.4</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>-0.0187</v>
+        <v>0.033</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>-0.0486</v>
+        <v>0.0118</v>
       </c>
       <c r="E133" s="7" t="n">
-        <v>-0.2606</v>
+        <v>-0.331</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>-0.34</v>
+        <v>-0.2358</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>-0.4196</v>
+        <v>0.3116</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>-0.2558</v>
+        <v>0.7515999999999999</v>
       </c>
       <c r="I133" s="6" t="n">
-        <v>6.7</v>
+        <v>6.79</v>
       </c>
       <c r="J133" s="5" t="inlineStr"/>
       <c r="K133" s="7" t="n">
-        <v>0.3515</v>
+        <v>0.5533</v>
       </c>
       <c r="L133" s="7" t="n">
-        <v>0.2524</v>
+        <v>0.6938</v>
       </c>
       <c r="M133" s="7" t="n">
-        <v>0.0007000000000000001</v>
+        <v>0.6357</v>
       </c>
       <c r="N133" s="7" t="n">
-        <v>0.1345</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="O133" s="7" t="n">
-        <v>0.0398</v>
+        <v>0.2589</v>
       </c>
       <c r="P133" s="7" t="n">
-        <v>-0.5093</v>
+        <v>-0.2304</v>
       </c>
       <c r="Q133" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R133" s="5" t="inlineStr"/>
@@ -8185,28 +8185,28 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>12.84</v>
+        <v>13.13</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>0.0272</v>
+        <v>0.0226</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>0.237</v>
+        <v>0.2505</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>-0.0552</v>
+        <v>0.1398</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>-0.0446</v>
+        <v>-0.0231</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>0.7134999999999999</v>
+        <v>0.7522</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>0.5982999999999999</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>10.42</v>
+        <v>10.66</v>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="4" t="n">
@@ -8241,28 +8241,28 @@
         </is>
       </c>
       <c r="B135" s="8" t="n">
-        <v>1245</v>
+        <v>1208</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>-0.008</v>
+        <v>-0.0297</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>-0.0273</v>
+        <v>-0.0473</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>-0.2589</v>
+        <v>-0.2607</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>-0.3342</v>
+        <v>-0.354</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>-0.1968</v>
+        <v>-0.2206</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>-0.293</v>
+        <v>-0.3109</v>
       </c>
       <c r="I135" s="6" t="n">
-        <v>11.06</v>
+        <v>10.73</v>
       </c>
       <c r="J135" s="5" t="inlineStr"/>
       <c r="K135" s="7" t="n">
@@ -8297,28 +8297,28 @@
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>261.25</v>
+        <v>255.75</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>-0.0261</v>
+        <v>-0.0211</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>-0.067</v>
+        <v>-0.0649</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>-0.2201</v>
+        <v>-0.2008</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>-0.2783</v>
+        <v>-0.2935</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>-0.4015</v>
+        <v>-0.4141</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>-0.4792</v>
+        <v>-0.4962</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>11.24</v>
+        <v>11.01</v>
       </c>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="4" t="n">
@@ -8353,31 +8353,31 @@
         </is>
       </c>
       <c r="B137" s="6" t="n">
-        <v>37.9</v>
+        <v>37.24</v>
       </c>
       <c r="C137" s="7" t="n">
-        <v>-0.0337</v>
+        <v>-0.0174</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>-0.1132</v>
+        <v>-0.1728</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>-0.0674</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>-0.2781</v>
+        <v>-0.2907</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>-0.112</v>
+        <v>-0.1275</v>
       </c>
       <c r="H137" s="7" t="n">
-        <v>-0.2421</v>
+        <v>-0.2286</v>
       </c>
       <c r="I137" s="6" t="n">
-        <v>11.62</v>
+        <v>11.41</v>
       </c>
       <c r="J137" s="6" t="n">
-        <v>41.8</v>
+        <v>41.07</v>
       </c>
       <c r="K137" s="7" t="n">
         <v>0.2618</v>
@@ -8411,28 +8411,28 @@
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>38.34</v>
+        <v>39</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>0.0031</v>
+        <v>0.0172</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>-0.0224</v>
+        <v>-0.0066</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>-0.1555</v>
+        <v>-0.25</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>-0.178</v>
+        <v>-0.1638</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>-0.08929999999999999</v>
+        <v>-0.0736</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>0.2057</v>
+        <v>0.2235</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>14.31</v>
+        <v>14.56</v>
       </c>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="4" t="n">
@@ -8467,31 +8467,31 @@
         </is>
       </c>
       <c r="B139" s="6" t="n">
-        <v>101.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="C139" s="7" t="n">
-        <v>0.001</v>
+        <v>-0.0291</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>-0.0416</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="E139" s="7" t="n">
         <v>-0.2036</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>-0.2267</v>
+        <v>-0.2492</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>-0.3318</v>
+        <v>-0.3513</v>
       </c>
       <c r="H139" s="7" t="n">
-        <v>-0.3716</v>
+        <v>-0.4054</v>
       </c>
       <c r="I139" s="6" t="n">
-        <v>15.41</v>
+        <v>14.96</v>
       </c>
       <c r="J139" s="6" t="n">
-        <v>58.04</v>
+        <v>56.35</v>
       </c>
       <c r="K139" s="7" t="n">
         <v>0.3045</v>
@@ -8525,25 +8525,25 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>75</v>
+        <v>71.7</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>-0.0209</v>
+        <v>-0.044</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.1277</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>-0.2424</v>
+        <v>-0.2684</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>0.1952</v>
+        <v>0.1426</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>0.1952</v>
+        <v>0.1426</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>-0.0132</v>
+        <v>-0.07719999999999999</v>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr"/>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>15.10.2026 19:17</t>
+          <t>16.10.2026 18:53</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_latest.xlsx
+++ b/data/bist_screener_latest.xlsx
@@ -579,57 +579,55 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MERIT</t>
+          <t>RUBNS</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12.87</v>
+        <v>12.63</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-0.0213</v>
+        <v>-0.09910000000000001</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.06059999999999999</v>
+        <v>-0.2313</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.1697</v>
+        <v>-0.4928</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-0.2667</v>
+        <v>-0.427</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.2452</v>
+        <v>-0.599</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.346</v>
+        <v>-0.3533</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>5.98</v>
-      </c>
+        <v>0.19</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="n">
-        <v>0.9854999999999999</v>
+        <v>0.5189</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>1.0319</v>
+        <v>0.4172999999999999</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>2.0871</v>
+        <v>2.5836</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>1.5834</v>
+        <v>0.7992</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>0.6354</v>
+        <v>0.1688</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.0454</v>
+        <v>-0.0061</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr"/>
@@ -637,55 +635,57 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>RUBNS</t>
+          <t>SRVGY</t>
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>14.02</v>
+        <v>2.05</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>-0.0271</v>
+        <v>-0.0238</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>-0.1232</v>
+        <v>-0.0929</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>-0.4989</v>
+        <v>-0.0596</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>-0.3685</v>
+        <v>-0.2235</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>-0.5535</v>
+        <v>-0.3731</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-0.3039</v>
+        <v>-0.3144</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0.21</v>
       </c>
-      <c r="J3" s="5" t="inlineStr"/>
+      <c r="J3" s="6" t="n">
+        <v>2.23</v>
+      </c>
       <c r="K3" s="7" t="n">
-        <v>0.5189</v>
+        <v>2.7227</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>0.4172999999999999</v>
+        <v>2.5294</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>2.5836</v>
+        <v>2.9903</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>0.7992</v>
+        <v>0.3421</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>0.1688</v>
+        <v>0.6722</v>
       </c>
       <c r="P3" s="7" t="n">
-        <v>-0.0061</v>
+        <v>0.1107</v>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr"/>
@@ -693,57 +693,57 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SRVGY</t>
+          <t>MERIT</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2.1</v>
+        <v>12.99</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.0187</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.0187</v>
+        <v>-0.0449</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.1064</v>
+        <v>-0.1235</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.2279</v>
+        <v>-0.2456</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.3438000000000001</v>
+        <v>-0.2249</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.3115</v>
+        <v>-0.3304</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2.29</v>
+        <v>6.04</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2.7227</v>
+        <v>0.9854999999999999</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>2.5294</v>
+        <v>1.0319</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>2.9903</v>
+        <v>2.0871</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.3421</v>
+        <v>1.5834</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.6722</v>
+        <v>0.6354</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.1107</v>
+        <v>0.0454</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr"/>
@@ -755,31 +755,31 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>-0.0199</v>
+        <v>-0.027</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-0.0864</v>
+        <v>-0.1166</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-0.2251</v>
+        <v>-0.2131</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>-0.285</v>
+        <v>-0.2941</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-0.3242</v>
+        <v>-0.36</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>-0.4127</v>
+        <v>-0.4097999999999999</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>8.279999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>0.2518</v>
@@ -813,31 +813,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0268</v>
+        <v>-0.03</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0476</v>
+        <v>-0.0605</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.0453</v>
+        <v>-0.0583</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2883</v>
+        <v>-0.3009</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3043</v>
+        <v>-0.3379</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1204</v>
+        <v>0.0992</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>1.7259</v>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>-0.0372</v>
+        <v>-0.05309999999999999</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-0.08</v>
+        <v>-0.1588</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-0.3279</v>
+        <v>-0.3194</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>-0.4838</v>
+        <v>-0.5013000000000001</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-0.4939</v>
+        <v>-0.5322</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>-0.581</v>
+        <v>-0.6032</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="7" t="n">
@@ -927,28 +927,28 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.0337</v>
+        <v>-0.0296</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.1509</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.157</v>
+        <v>-0.1446</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1853</v>
+        <v>-0.2575</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.268</v>
+        <v>-0.2902</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.3645</v>
+        <v>-0.3728</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="n">
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>-0.0202</v>
+        <v>-0.0412</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.0083</v>
+        <v>-0.0528</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-0.1066</v>
+        <v>-0.049</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>-0.1321</v>
+        <v>-0.1619</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-0.1321</v>
+        <v>-0.1882</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-0.0319</v>
+        <v>-0.0567</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>5.71</v>
+        <v>5.47</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>0.3848</v>
@@ -1037,57 +1037,57 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GSDHO</t>
+          <t>PETUN</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.08470000000000001</v>
+        <v>-0.0415</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.0654</v>
+        <v>-0.1492</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1304</v>
+        <v>-0.2133</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2634</v>
+        <v>-0.2714</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1984</v>
+        <v>-0.3043</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.0521</v>
+        <v>-0.3167</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>14.33</v>
+        <v>10.45</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1479</v>
+        <v>0.3203</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2201</v>
+        <v>0.0458</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3072</v>
+        <v>0.0347</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.5201</v>
+        <v>0.0183</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.6869</v>
+        <v>0.1414</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.0197</v>
+        <v>0.0274</v>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr"/>
@@ -1095,57 +1095,57 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>PETUN</t>
+          <t>GSDHO</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>9.16</v>
+        <v>3.99</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>-0.0297</v>
+        <v>-0.0025</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>-0.0858</v>
+        <v>-0.0785</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-0.2049</v>
+        <v>-0.0849</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>-0.2237</v>
+        <v>-0.2951</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-0.2595</v>
+        <v>-0.2176</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-0.3002</v>
+        <v>-0.06559999999999999</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0.25</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>10.91</v>
+        <v>14.3</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.3203</v>
+        <v>0.1479</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0458</v>
+        <v>0.2201</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.0347</v>
+        <v>0.3072</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>0.0183</v>
+        <v>0.5201</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>0.1414</v>
+        <v>0.6869</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>0.0274</v>
+        <v>0.0197</v>
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr"/>
@@ -1157,25 +1157,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>6.7</v>
+        <v>6.49</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.0106</v>
+        <v>-0.0313</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.034</v>
+        <v>-0.0539</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1332</v>
+        <v>-0.1347</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1184</v>
+        <v>-0.2017</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1976</v>
+        <v>-0.2383</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.09699999999999999</v>
+        <v>-0.1218</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0.26</v>
@@ -1213,28 +1213,28 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.0377</v>
+        <v>-0.08</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>-0.1084</v>
+        <v>-0.2134</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>-0.3747</v>
+        <v>-0.3723</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>-0.4213</v>
+        <v>-0.4626</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-0.5218</v>
+        <v>-0.5693</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.6883</v>
+        <v>-0.7134999999999999</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
       <c r="K13" s="7" t="n">
@@ -1269,28 +1269,28 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5.29</v>
+        <v>4.93</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.024</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.08789999999999999</v>
+        <v>-0.1918</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.09880000000000001</v>
+        <v>-0.0819</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.1739</v>
+        <v>-0.2245</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2583</v>
+        <v>-0.3154</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4274</v>
+        <v>-0.4909000000000001</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="n">
@@ -1325,31 +1325,31 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>-0.0167</v>
+        <v>-0.0452</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.005699999999999999</v>
+        <v>-0.0559</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-0.1881</v>
+        <v>-0.1378</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>-0.2686</v>
+        <v>-0.2819</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-0.2995</v>
+        <v>-0.3364</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.2976</v>
+        <v>-0.3185</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>8.35</v>
+        <v>7.97</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>0.9460999999999999</v>
@@ -1383,31 +1383,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>10.35</v>
+        <v>9.92</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0318</v>
+        <v>-0.0415</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.0599</v>
+        <v>-0.1244</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.176</v>
+        <v>-0.1935</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2147</v>
+        <v>-0.2652</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.239</v>
+        <v>-0.2919</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2099</v>
+        <v>-0.2238</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.52</v>
+        <v>5.29</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>0.3789</v>
@@ -1441,31 +1441,31 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>187</v>
+        <v>179.2</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>-0.0449</v>
+        <v>-0.0417</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>-0.0142</v>
+        <v>-0.07150000000000001</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>-0.0301</v>
+        <v>-0.0633</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>-0.08779999999999999</v>
+        <v>-0.1326</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.0158</v>
+        <v>-0.0568</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0.2773</v>
+        <v>0.2092</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>3.11</v>
+        <v>2.98</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>0.5672999999999999</v>
@@ -1499,28 +1499,28 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.0588</v>
+        <v>-0.075</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.1919</v>
+        <v>-0.2709</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.4386</v>
+        <v>-0.408</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.5506</v>
+        <v>-0.5647</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6126</v>
+        <v>-0.6309</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.8157</v>
+        <v>-0.8320000000000001</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="4" t="n">
@@ -1551,57 +1551,55 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>SISE</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>36.16</v>
+        <v>1.7</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>-0.0295</v>
+        <v>-0.0761</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>-0.0449</v>
+        <v>-0.1905</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>-0.1484</v>
+        <v>-0.4408</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>-0.1907</v>
+        <v>-0.6862999999999999</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>-0.2293</v>
+        <v>-0.7409</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0.0698</v>
+        <v>-0.5932999999999999</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>9.08</v>
-      </c>
+        <v>0.39</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="7" t="n">
-        <v>0.2329</v>
+        <v>0.1726</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.3714</v>
+        <v>0.3081</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.2133</v>
+        <v>0.1357</v>
       </c>
       <c r="N19" s="7" t="n">
-        <v>2.0423</v>
+        <v>0.2328</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0837</v>
       </c>
       <c r="P19" s="7" t="n">
-        <v>0.0601</v>
+        <v>-0.0244</v>
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R19" s="5" t="inlineStr"/>
@@ -1609,55 +1607,57 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>BTCIM</t>
+          <t>SISE</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.84</v>
+        <v>35.5</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.0466</v>
+        <v>-0.0183</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.0564</v>
+        <v>-0.0697</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.4743</v>
+        <v>-0.1116</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6743000000000001</v>
+        <v>-0.2083</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.7221</v>
+        <v>-0.2526</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.5671</v>
+        <v>0.068</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr"/>
+        <v>0.39</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>8.92</v>
+      </c>
       <c r="K20" s="4" t="n">
-        <v>0.1726</v>
+        <v>0.2329</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3081</v>
+        <v>0.3714</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1357</v>
+        <v>0.2133</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.2328</v>
+        <v>2.0423</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.0837</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.0244</v>
+        <v>0.0601</v>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr"/>
@@ -1669,31 +1669,31 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>7.1</v>
+        <v>6.85</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>-0.0287</v>
+        <v>-0.0352</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.1092</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-0.2695</v>
+        <v>-0.2473</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>-0.3474</v>
+        <v>-0.3704</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-0.4044</v>
+        <v>-0.4219</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-0.2733</v>
+        <v>-0.2842</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>0.9081</v>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.0169</v>
+        <v>-0.0114</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.0489</v>
+        <v>-0.0709</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1799</v>
+        <v>-0.1675</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1868</v>
+        <v>-0.2042</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1906</v>
+        <v>-0.1946</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.0406</v>
+        <v>-0.0431</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>7.07</v>
+        <v>6.99</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>0.1285</v>
@@ -1785,31 +1785,31 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>9.83</v>
+        <v>9.69</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>-0.0611</v>
+        <v>-0.0142</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>-0.08900000000000001</v>
+        <v>-0.1036</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>-0.2386</v>
+        <v>-0.1871</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>-0.3613</v>
+        <v>-0.3654</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-0.4166</v>
+        <v>-0.4479</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-0.2724</v>
+        <v>-0.2763</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K23" s="7" t="n">
         <v>0.4985</v>
@@ -1843,31 +1843,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>5.69</v>
+        <v>5.33</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.0421</v>
+        <v>-0.0633</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.0823</v>
+        <v>-0.1526</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2152</v>
+        <v>-0.2021</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3815</v>
+        <v>-0.433</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3592</v>
+        <v>-0.4051</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2464</v>
+        <v>-0.2577</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>6.83</v>
+        <v>6.4</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>0.6883</v>
@@ -1901,28 +1901,28 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>103.9</v>
+        <v>99</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>-0.0415</v>
+        <v>-0.0472</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.1502</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-0.2775</v>
+        <v>-0.2867</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>-0.3741</v>
+        <v>-0.4111</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>-0.4851</v>
+        <v>-0.5101</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-0.4313</v>
+        <v>-0.4479</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="7" t="n">
@@ -1953,57 +1953,55 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>KORDS</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>29.86</v>
+        <v>2.59</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.0478</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.0675</v>
+        <v>-0.1508</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.1145</v>
+        <v>-0.2292</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1218</v>
+        <v>-0.3719</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.0343</v>
+        <v>-0.2441</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.204</v>
+        <v>-0.0794</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="J26" s="3" t="n">
-        <v>16.32</v>
-      </c>
+      <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="4" t="n">
-        <v>0.3105</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.3107</v>
+        <v>0.3224</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.4787</v>
+        <v>0.613</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.4985</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.0693</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.0718</v>
+        <v>-0.09820000000000001</v>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr"/>
@@ -2011,57 +2009,57 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>OYYAT</t>
+          <t>KRSTL</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>25.34</v>
+        <v>6.5</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>-0.0328</v>
+        <v>-0.0593</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>-0.0608</v>
+        <v>-0.1569</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-0.239</v>
+        <v>-0.1885</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>-0.3765</v>
+        <v>-0.3981</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>-0.5342</v>
+        <v>-0.3078</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>-0.5303</v>
+        <v>-0.3815</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.045</v>
+        <v>0.3806</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.4061999999999999</v>
+        <v>0.2571</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.4311</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="N27" s="7" t="n">
-        <v>3.0744</v>
+        <v>0.6774</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>0.2671</v>
+        <v>0.1192</v>
       </c>
       <c r="P27" s="7" t="n">
-        <v>0.2126</v>
+        <v>0.1788</v>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R27" s="5" t="inlineStr"/>
@@ -2069,55 +2067,57 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KORDS</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>2.72</v>
+        <v>30.3</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.04559999999999999</v>
+        <v>0.0147</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1365</v>
+        <v>-0.079</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2727</v>
+        <v>-0.1308</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3319</v>
+        <v>-0.1387</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1969</v>
+        <v>-0.0537</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.0535</v>
+        <v>0.2307</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr"/>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>16.57</v>
+      </c>
       <c r="K28" s="4" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.3105</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.3224</v>
+        <v>0.3107</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.613</v>
+        <v>0.4787</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.7171999999999999</v>
+        <v>1.4985</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.09820000000000001</v>
+        <v>-0.0718</v>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr"/>
@@ -2125,57 +2125,57 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>KRSTL</t>
+          <t>OYYAT</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>6.91</v>
+        <v>25.14</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>-0.0322</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>-0.08960000000000001</v>
+        <v>-0.0891</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-0.1553</v>
+        <v>-0.162</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>-0.3388</v>
+        <v>-0.36</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>-0.2505</v>
+        <v>-0.5589</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>-0.3349</v>
+        <v>-0.5336</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>3.97</v>
+        <v>3.22</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.3806</v>
+        <v>0.045</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.2571</v>
+        <v>0.4061999999999999</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.5529999999999999</v>
+        <v>0.4311</v>
       </c>
       <c r="N29" s="7" t="n">
-        <v>0.6774</v>
+        <v>3.0744</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>0.1192</v>
+        <v>0.2671</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>0.1788</v>
+        <v>0.2126</v>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R29" s="5" t="inlineStr"/>
@@ -2183,55 +2183,57 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BAKAB</t>
+          <t>SEKFK</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>27.6</v>
+        <v>3.48</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.0309</v>
+        <v>-0.0984</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1154</v>
+        <v>-0.1869</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2269</v>
+        <v>-0.1234</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4753</v>
+        <v>-0.3615</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3872</v>
+        <v>-0.4264</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2434</v>
+        <v>-0.1989</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr"/>
+        <v>0.57</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>2.82</v>
+      </c>
       <c r="K30" s="4" t="n">
-        <v>0.3479</v>
+        <v>0.208</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.5443</v>
+        <v>0.0571</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.7171</v>
+        <v>0.0025</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.97</v>
+        <v>0.2707</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.0552</v>
+        <v>0.6072</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.0031</v>
+        <v>0.2346</v>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr"/>
@@ -2239,53 +2241,51 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>MERCN</t>
+          <t>BAKAB</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>9.35</v>
+        <v>26.76</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>-0.077</v>
+        <v>-0.0304</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>-0.1163</v>
+        <v>-0.139</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-0.462</v>
+        <v>-0.2337</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>-0.6345000000000001</v>
+        <v>-0.4819</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>-0.5268</v>
+        <v>-0.3899</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>-0.7149</v>
+        <v>-0.2648</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>10.74</v>
-      </c>
+        <v>0.58</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="7" t="n">
-        <v>0.2374</v>
+        <v>0.3479</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.8593999999999999</v>
+        <v>0.5443</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>1.4059</v>
+        <v>0.7171</v>
       </c>
       <c r="N31" s="7" t="n">
-        <v>1.3031</v>
+        <v>0.97</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>0.1784</v>
+        <v>0.0552</v>
       </c>
       <c r="P31" s="7" t="n">
-        <v>0.07049999999999999</v>
+        <v>-0.0031</v>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
@@ -2297,55 +2297,55 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SOKE</t>
+          <t>DOKTA</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>7.64</v>
+        <v>14.2</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.0104</v>
+        <v>-0.0314</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.066</v>
+        <v>-0.1041</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2091</v>
+        <v>-0.3315</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.5968</v>
+        <v>-0.3973</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.5722</v>
+        <v>-0.4147</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3292</v>
+        <v>-0.3926</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="4" t="n">
-        <v>0.5234000000000001</v>
+        <v>0.2983</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.4561</v>
+        <v>1.25</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.4897</v>
+        <v>3.5566</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.3644</v>
+        <v>0.6970000000000001</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.032</v>
+        <v>0.0852</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.0429</v>
+        <v>-0.0451</v>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr"/>
@@ -2353,53 +2353,53 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>OSMEN</t>
+          <t>TUREX</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>5.13</v>
+        <v>5.16</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>-0.021</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.1224</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-0.2377</v>
+        <v>-0.0246</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>-0.3893</v>
+        <v>-0.2412</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>-0.3431</v>
+        <v>-0.3958</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>-0.4429999999999999</v>
+        <v>-0.3493</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>1.6512</v>
+        <v>0.4159</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.1052</v>
+        <v>1.3967</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.04969999999999999</v>
+        <v>0.8518000000000001</v>
       </c>
       <c r="N33" s="7" t="n">
-        <v>5.9134</v>
+        <v>0.3205</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.2638</v>
       </c>
       <c r="P33" s="7" t="n">
-        <v>0.0863</v>
+        <v>0.0862</v>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
@@ -2411,53 +2411,53 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SEKFK</t>
+          <t>AKMGY</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>3.86</v>
+        <v>186.2</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.0228</v>
+        <v>-0.0534</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.0608</v>
+        <v>-0.1238</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1002</v>
+        <v>-0.2203</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3058</v>
+        <v>-0.2552</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3574</v>
+        <v>-0.3179</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1291</v>
+        <v>-0.1772</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.13</v>
+        <v>9.17</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.208</v>
+        <v>0.3886</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.0571</v>
+        <v>0.3887</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.0025</v>
+        <v>0.3141</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.2707</v>
+        <v>0.5958</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.6072</v>
+        <v>0.6443000000000001</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.2346</v>
+        <v>0.0781</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
@@ -2469,55 +2469,55 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>DOKTA</t>
+          <t>SOKE</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>14.66</v>
+        <v>7.6</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>-0.0227</v>
+        <v>-0.0052</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>-0.0481</v>
+        <v>-0.06059999999999999</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-0.3426</v>
+        <v>-0.1845</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>-0.3772</v>
+        <v>-0.5968</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>-0.3907</v>
+        <v>-0.597</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>-0.3778</v>
+        <v>-0.3232</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="J35" s="5" t="inlineStr"/>
       <c r="K35" s="7" t="n">
-        <v>0.2983</v>
+        <v>0.5234000000000001</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>1.25</v>
+        <v>0.4561</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>3.5566</v>
+        <v>0.4897</v>
       </c>
       <c r="N35" s="7" t="n">
-        <v>0.6970000000000001</v>
+        <v>0.3644</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>0.0852</v>
+        <v>0.032</v>
       </c>
       <c r="P35" s="7" t="n">
-        <v>-0.0451</v>
+        <v>-0.0429</v>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R35" s="5" t="inlineStr"/>
@@ -2525,57 +2525,57 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>PNLSN</t>
+          <t>OSMEN</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>30.52</v>
+        <v>5.09</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>-0.0463</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>-0.09</v>
+        <v>-0.0911</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>-0.201</v>
+        <v>-0.1387</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>-0.3748</v>
+        <v>-0.3815</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.3298</v>
+        <v>-0.3716</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.2093</v>
+        <v>-0.4449</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>8.6</v>
+        <v>8.73</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0.306</v>
+        <v>1.6512</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.6481</v>
+        <v>0.1052</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.5497</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>7.793600000000001</v>
+        <v>5.9134</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>0.1302</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>0.08839999999999999</v>
+        <v>0.0863</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr"/>
@@ -2583,57 +2583,57 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>PNLSN</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>204</v>
+        <v>29.88</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>-0.0327</v>
+        <v>-0.021</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>-0.0418</v>
+        <v>-0.1278</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.2019</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>0.0371</v>
+        <v>-0.3723</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0</v>
+        <v>-0.3712</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0.2977</v>
+        <v>-0.2087</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>14.54</v>
+        <v>8.42</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.3261</v>
+        <v>0.306</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>0.5440999999999999</v>
+        <v>0.6481</v>
       </c>
       <c r="M37" s="7" t="n">
-        <v>0.9423</v>
+        <v>0.5497</v>
       </c>
       <c r="N37" s="7" t="n">
-        <v>5.083299999999999</v>
+        <v>7.793600000000001</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>0.0646</v>
+        <v>0.1302</v>
       </c>
       <c r="P37" s="7" t="n">
-        <v>0.0771</v>
+        <v>0.08839999999999999</v>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R37" s="5" t="inlineStr"/>
@@ -2641,57 +2641,57 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AKMGY</t>
+          <t>BNTAS</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>196.7</v>
+        <v>4.79</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>-0.0377</v>
+        <v>-0.0534</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>-0.062</v>
+        <v>-0.108</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>-0.1835</v>
+        <v>-0.1741</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-0.1958</v>
+        <v>-0.2324</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.3349</v>
+        <v>-0.2997</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1304</v>
+        <v>-0.2574</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>9.69</v>
+        <v>4.43</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.3886</v>
+        <v>0.2654</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.3887</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.3141</v>
+        <v>0.464</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.5958</v>
+        <v>0.3679</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0.6443000000000001</v>
+        <v>0.1363</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0.0781</v>
+        <v>0.1657</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr"/>
@@ -2699,57 +2699,57 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TTKOM</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>50.9</v>
+        <v>202.9</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>-0.0268</v>
+        <v>-0.0054</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>-0.0314</v>
+        <v>-0.0241</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-0.0745</v>
+        <v>-0.06280000000000001</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>-0.1299</v>
+        <v>0.0095</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>-0.1914</v>
+        <v>-0.0193</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>0.0059</v>
+        <v>0.3065</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>6.29</v>
+        <v>14.46</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.4498</v>
+        <v>0.3261</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>0.4329</v>
+        <v>0.5440999999999999</v>
       </c>
       <c r="M39" s="7" t="n">
-        <v>0.5323</v>
+        <v>0.9423</v>
       </c>
       <c r="N39" s="7" t="n">
-        <v>0.8047</v>
+        <v>5.083299999999999</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>0.4117</v>
+        <v>0.0646</v>
       </c>
       <c r="P39" s="7" t="n">
-        <v>1.3041</v>
+        <v>0.0771</v>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="R39" s="5" t="inlineStr"/>
@@ -2757,57 +2757,57 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TUREX</t>
+          <t>TTKOM</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>5.58</v>
+        <v>50.05</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>-0.0396</v>
+        <v>-0.0167</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>-0.0429</v>
+        <v>-0.04480000000000001</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>-0.0396</v>
+        <v>-0.0476</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>-0.196</v>
+        <v>-0.156</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-0.3645</v>
+        <v>-0.23</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.3051</v>
+        <v>-0.003</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>10.49</v>
+        <v>6.19</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.4159</v>
+        <v>0.4498</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>1.3967</v>
+        <v>0.4329</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.8518000000000001</v>
+        <v>0.5323</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.3205</v>
+        <v>0.8047</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.2638</v>
+        <v>0.4117</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0.0862</v>
+        <v>1.3041</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr"/>
@@ -2815,57 +2815,57 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>BNTAS</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>5.06</v>
+        <v>96.2</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>-0.0213</v>
+        <v>-0.0062</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>-0.0471</v>
+        <v>-0.0248</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-0.1746</v>
+        <v>-0.0224</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>-0.2069</v>
+        <v>-0.127</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>-0.2414</v>
+        <v>-0.1714</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>-0.2263</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0.68</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>4.68</v>
+        <v>10.8</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.2654</v>
+        <v>0.3971</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.4118</v>
       </c>
       <c r="M41" s="7" t="n">
-        <v>0.464</v>
+        <v>0.3975</v>
       </c>
       <c r="N41" s="7" t="n">
-        <v>0.3679</v>
+        <v>0.2377</v>
       </c>
       <c r="O41" s="7" t="n">
-        <v>0.1363</v>
+        <v>0.4333</v>
       </c>
       <c r="P41" s="7" t="n">
-        <v>0.1657</v>
+        <v>0.1518</v>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R41" s="5" t="inlineStr"/>
@@ -2873,57 +2873,57 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>MERCN</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>96.8</v>
+        <v>10.28</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>-0.0107</v>
+        <v>0.09949999999999999</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>-0.0349</v>
+        <v>-0.0764</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-0.0281</v>
+        <v>-0.3575</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-0.1334</v>
+        <v>-0.6006</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-0.1762</v>
+        <v>-0.5443</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.0189</v>
+        <v>-0.6948000000000001</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>10.87</v>
+        <v>11.81</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0.3971</v>
+        <v>0.2374</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.4118</v>
+        <v>0.8593999999999999</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.3975</v>
+        <v>1.4059</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.2377</v>
+        <v>1.3031</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>0.4333</v>
+        <v>0.1784</v>
       </c>
       <c r="P42" s="4" t="n">
-        <v>0.1518</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr"/>
@@ -2935,31 +2935,31 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>7.89</v>
+        <v>7.51</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>-0.0483</v>
+        <v>-0.0482</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>-0.1003</v>
+        <v>-0.159</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-0.203</v>
+        <v>-0.189</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>-0.2633</v>
+        <v>-0.4201</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>-0.3713</v>
+        <v>-0.3968</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>-0.3807</v>
+        <v>-0.4636</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>16.63</v>
+        <v>15.83</v>
       </c>
       <c r="K43" s="7" t="n">
         <v>0.2802</v>
@@ -2993,31 +2993,31 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>277.25</v>
+        <v>267.5</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>-0.039</v>
+        <v>-0.0352</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>-0.0546</v>
+        <v>-0.0776</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>-0.1547</v>
+        <v>-0.1562</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.0788</v>
+        <v>-0.0325</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-0.044</v>
+        <v>0.0075</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.5192</v>
+        <v>0.4944</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>7.29</v>
+        <v>7.03</v>
       </c>
       <c r="K44" s="4" t="n">
         <v>0.1662</v>
@@ -3047,57 +3047,57 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>36.26</v>
+        <v>3.86</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>-0.0305</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>-0.0152</v>
+        <v>-0.4061999999999999</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-0.05429999999999999</v>
+        <v>-0.8893000000000001</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>-0.1744</v>
+        <v>-0.9061</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0.1712</v>
+        <v>-0.8484999999999999</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>0.3331</v>
+        <v>-0.8794</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>31.6</v>
+        <v>2.45</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.1998</v>
+        <v>7.8666</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>0.3838</v>
+        <v>3.1929</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>0.4877</v>
+        <v>4.946499999999999</v>
       </c>
       <c r="N45" s="7" t="n">
-        <v>0.4752</v>
+        <v>1.0979</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>0.104</v>
+        <v>0.4854</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>0.0274</v>
+        <v>0.586</v>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R45" s="5" t="inlineStr"/>
@@ -3109,31 +3109,31 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>39.08</v>
+        <v>38.1</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>-0.0161</v>
+        <v>-0.0251</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>-0.0005</v>
+        <v>-0.0565</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>-0.1065</v>
+        <v>-0.0993</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-0.165</v>
+        <v>-0.1803</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-0.2223</v>
+        <v>-0.2365</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>-0.025</v>
+        <v>-0.0475</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>7.08</v>
+        <v>6.9</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>0.3163</v>
@@ -3163,57 +3163,57 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>ISFIN</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>15.8</v>
+        <v>35.62</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>-0.0025</v>
+        <v>-0.0177</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>-0.0522</v>
+        <v>-0.0517</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-0.1524</v>
+        <v>-0.016</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>-0.2</v>
+        <v>-0.1893</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>-0.2315</v>
+        <v>0.0476</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>-0.0717</v>
+        <v>0.3193</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>2.69</v>
+        <v>31.05</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.5749</v>
+        <v>0.1998</v>
       </c>
       <c r="L47" s="7" t="n">
-        <v>0.5787</v>
+        <v>0.3838</v>
       </c>
       <c r="M47" s="7" t="n">
-        <v>0.5648</v>
+        <v>0.4877</v>
       </c>
       <c r="N47" s="7" t="n">
-        <v>0.6275999999999999</v>
+        <v>0.4752</v>
       </c>
       <c r="O47" s="7" t="n">
-        <v>0.9556</v>
+        <v>0.104</v>
       </c>
       <c r="P47" s="7" t="n">
-        <v>0.3468</v>
+        <v>0.0274</v>
       </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R47" s="5" t="inlineStr"/>
@@ -3221,53 +3221,53 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>ISFIN</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.28</v>
+        <v>15.11</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>-0.0989</v>
+        <v>-0.0437</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>-0.4072</v>
+        <v>-0.09789999999999999</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>-0.9105</v>
+        <v>-0.1854</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-0.8956000000000001</v>
+        <v>-0.2314</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-0.8098000000000001</v>
+        <v>-0.2756</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>-0.8654999999999999</v>
+        <v>-0.0837</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.72</v>
+        <v>2.57</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>7.8666</v>
+        <v>0.5749</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>3.1929</v>
+        <v>0.5787</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>4.946499999999999</v>
+        <v>0.5648</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>1.0979</v>
+        <v>0.6275999999999999</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>0.4854</v>
+        <v>0.9556</v>
       </c>
       <c r="P48" s="4" t="n">
-        <v>0.586</v>
+        <v>0.3468</v>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
@@ -3279,57 +3279,55 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>DESA</t>
+          <t>AYES</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>8.24</v>
+        <v>6.74</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>-0.0072</v>
+        <v>-0.0573</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>-0.0452</v>
+        <v>-0.1013</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>-0.1345</v>
+        <v>-0.1085</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>-0.2175</v>
+        <v>-0.2975</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>-0.4477</v>
+        <v>-0.2913</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>-0.4518</v>
+        <v>0.4024</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>7.81</v>
+        <v>1.85</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.2088</v>
+        <v>0.4183</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>0.2301</v>
+        <v>0.314</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0.0037</v>
+        <v>0.8128</v>
       </c>
       <c r="N49" s="7" t="n">
-        <v>0.3571</v>
+        <v>42.7724</v>
       </c>
       <c r="O49" s="7" t="n">
-        <v>0.2399</v>
-      </c>
-      <c r="P49" s="7" t="n">
-        <v>0.1277</v>
-      </c>
+        <v>0.0208</v>
+      </c>
+      <c r="P49" s="5" t="inlineStr"/>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R49" s="5" t="inlineStr"/>
@@ -3337,55 +3335,57 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AYES</t>
+          <t>GRTHO</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>7.15</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>-0.0205</v>
+        <v>-0.0999</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.09029999999999999</v>
+        <v>-0.4758</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>-0.1365</v>
+        <v>-0.5961</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>-0.2312</v>
+        <v>-0.7284999999999999</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.2552</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0.5577000000000001</v>
+        <v>-0.9046</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>1.97</v>
+        <v>4.52</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0.4183</v>
+        <v>0.5085000000000001</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.314</v>
+        <v>0.4487</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.8128</v>
+        <v>0.2298</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>42.7724</v>
+        <v>0.9399</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>0.0208</v>
-      </c>
-      <c r="P50" s="2" t="inlineStr"/>
+        <v>0.1089</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>0.2287</v>
+      </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr"/>
@@ -3393,57 +3393,57 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>DESA</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>452.25</v>
+        <v>7.95</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>-0.0378</v>
+        <v>-0.0352</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>-0.09910000000000001</v>
+        <v>-0.08199999999999999</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-0.1201</v>
+        <v>-0.1215</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>-0.2787</v>
+        <v>-0.2356</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>-0.3158</v>
+        <v>-0.4338</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>0.0215</v>
+        <v>-0.4664</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>13.55</v>
+        <v>7.53</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.3804</v>
+        <v>0.2088</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>0.3113</v>
+        <v>0.2301</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>1.725</v>
+        <v>0.0037</v>
       </c>
       <c r="N51" s="7" t="n">
-        <v>0.0848</v>
+        <v>0.3571</v>
       </c>
       <c r="O51" s="7" t="n">
-        <v>0.0184</v>
+        <v>0.2399</v>
       </c>
       <c r="P51" s="7" t="n">
-        <v>0.1216</v>
+        <v>0.1277</v>
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R51" s="5" t="inlineStr"/>
@@ -3455,31 +3455,31 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>7.96</v>
+        <v>7.51</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>-0.04559999999999999</v>
+        <v>-0.0565</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.1165</v>
+        <v>-0.1792</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>-0.39</v>
+        <v>-0.2414</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>-0.2842</v>
+        <v>-0.3142</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.2375</v>
+        <v>-0.3526</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>-0.1968</v>
+        <v>-0.2226</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>29.62</v>
+        <v>27.95</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>0.8458</v>
@@ -3513,31 +3513,31 @@
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>91.7</v>
+        <v>86.75</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>-0.0022</v>
+        <v>-0.05400000000000001</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>-0.0779</v>
+        <v>-0.113</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-0.1556</v>
+        <v>-0.1528</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>-0.101</v>
+        <v>-0.1351</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>-0.2847</v>
+        <v>-0.2941</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>-0.108</v>
+        <v>-0.1428</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>12.83</v>
+        <v>12.14</v>
       </c>
       <c r="K53" s="7" t="n">
         <v>0.4926</v>
@@ -3567,57 +3567,57 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GRTHO</t>
+          <t>RALYH</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>21.78</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>-0.0999</v>
+        <v>-0.1</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>-0.3864</v>
+        <v>-0.4088000000000001</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>-0.6727</v>
+        <v>-0.9009999999999999</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>-0.7125</v>
+        <v>-0.9103</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-0.7170000000000001</v>
+        <v>-0.9329999999999999</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>-0.8908</v>
+        <v>-0.8756</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>5.02</v>
+        <v>2.82</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0.5085000000000001</v>
+        <v>0.7070000000000001</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.4487</v>
+        <v>1.4848</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.2298</v>
+        <v>1.5369</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.9399</v>
+        <v>0.5434</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>0.1089</v>
+        <v>0.2854</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>0.2287</v>
+        <v>0.3914</v>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr"/>
@@ -3625,57 +3625,57 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>ZRGYO</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>18.25</v>
+        <v>451.75</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0011</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>-0.04</v>
+        <v>-0.1046</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-0.0902</v>
+        <v>-0.1346</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>0.034</v>
+        <v>-0.3066</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>-0.1392</v>
+        <v>-0.3212</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>-0.21</v>
+        <v>0.0403</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>13.81</v>
+        <v>13.53</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>2.3363</v>
+        <v>0.3804</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>3.5944</v>
+        <v>0.3113</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>3.6478</v>
+        <v>1.725</v>
       </c>
       <c r="N55" s="7" t="n">
-        <v>0.2899</v>
+        <v>0.0848</v>
       </c>
       <c r="O55" s="7" t="n">
-        <v>0.5917</v>
+        <v>0.0184</v>
       </c>
       <c r="P55" s="7" t="n">
-        <v>0.0776</v>
+        <v>0.1216</v>
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R55" s="5" t="inlineStr"/>
@@ -3687,31 +3687,31 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>91.2</v>
+        <v>85.55</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.04</v>
+        <v>-0.062</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.0593</v>
+        <v>-0.1367</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>-0.2042</v>
+        <v>-0.2396</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>-0.2908</v>
+        <v>-0.3117</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.1024</v>
+        <v>-0.1445</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>0.7338</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>8.31</v>
+        <v>7.8</v>
       </c>
       <c r="K56" s="4" t="n">
         <v>0.1264</v>
@@ -3745,31 +3745,31 @@
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>35.36</v>
+        <v>33.08</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>-0.0391</v>
+        <v>-0.0645</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>-0.1333</v>
+        <v>-0.2116</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-0.4107</v>
+        <v>-0.2353</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>-0.5650999999999999</v>
+        <v>-0.6277</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>-0.2428</v>
+        <v>-0.3045</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>-0.1819</v>
+        <v>-0.2311</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>9.5</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K57" s="7" t="n">
         <v>0.2641</v>
@@ -3799,57 +3799,57 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RALYH</t>
+          <t>ZRGYO</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>24.2</v>
+        <v>18.07</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>-0.4086</v>
+        <v>-0.0608</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>-0.9087000000000001</v>
+        <v>-0.079</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>-0.8948</v>
+        <v>-0.0028</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-0.9243000000000001</v>
+        <v>-0.1933</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>-0.8615</v>
+        <v>-0.1926</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>3.13</v>
+        <v>13.68</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0.7070000000000001</v>
+        <v>2.3363</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>1.4848</v>
+        <v>3.5944</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>1.5369</v>
+        <v>3.6478</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.5434</v>
+        <v>0.2899</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>0.2854</v>
+        <v>0.5917</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>0.3914</v>
+        <v>0.0776</v>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr"/>
@@ -3861,31 +3861,31 @@
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>38.38</v>
+        <v>38.42</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>-0.0366</v>
+        <v>0.001</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>-0.0684</v>
+        <v>-0.0697</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-0.1229</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>-0.1987</v>
+        <v>-0.2324</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>-0.2696</v>
+        <v>-0.3248</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>-0.1045</v>
+        <v>-0.1007</v>
       </c>
       <c r="I59" s="6" t="n">
         <v>0.97</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>9.09</v>
+        <v>9.1</v>
       </c>
       <c r="K59" s="7" t="n">
         <v>0.3754999999999999</v>
@@ -3919,31 +3919,31 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>23.4</v>
+        <v>23.18</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>-0.064</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>-0.064</v>
+        <v>-0.0539</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>-0.2642</v>
+        <v>-0.0852</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>-0.011</v>
+        <v>-0.0461</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-0.0362</v>
+        <v>-0.0683</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>0.07730000000000001</v>
+        <v>0.1091</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>17.32</v>
+        <v>17.15</v>
       </c>
       <c r="K60" s="4" t="n">
         <v>0.4327</v>
@@ -3977,31 +3977,31 @@
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>-0.0537</v>
+        <v>-0.0123</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>-0.1598</v>
+        <v>-0.1605</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>-0.4394</v>
+        <v>-0.3443</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>-0.5903</v>
+        <v>-0.6008</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>-0.5522</v>
+        <v>-0.5397</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>-0.2691</v>
+        <v>-0.2763</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>6.02</v>
+        <v>5.95</v>
       </c>
       <c r="K61" s="7" t="n">
         <v>0.5809000000000001</v>
@@ -4031,57 +4031,57 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>CMENT</t>
+          <t>INDES</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>215.9</v>
+        <v>11.42</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>-0.0142</v>
+        <v>-0.0095</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>-0.1041</v>
+        <v>-0.0223</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>-0.1347</v>
+        <v>0.0613</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>-0.2581</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-0.3458</v>
+        <v>0.1594</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>-0.4019</v>
+        <v>0.4831</v>
       </c>
       <c r="I62" s="3" t="n">
         <v>1.01</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>21.31</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0.0934</v>
+        <v>0.6297</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.1109</v>
+        <v>0.8554999999999999</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.1008</v>
+        <v>1.0205</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0.4922</v>
+        <v>1.9437</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>0.1647</v>
+        <v>0.0374</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.137</v>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr"/>
@@ -4089,57 +4089,57 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>INDES</t>
+          <t>CMENT</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>11.53</v>
+        <v>216.8</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>-0.0368</v>
+        <v>0.0042</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>0.0204</v>
+        <v>-0.0833</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>0.0341</v>
+        <v>-0.091</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>0.0304</v>
+        <v>-0.2626</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>0.2227</v>
+        <v>-0.339</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>0.4485</v>
+        <v>-0.3815</v>
       </c>
       <c r="I63" s="6" t="n">
         <v>1.02</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>9.720000000000001</v>
+        <v>21.4</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>0.6297</v>
+        <v>0.0934</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>0.8554999999999999</v>
+        <v>0.1109</v>
       </c>
       <c r="M63" s="7" t="n">
-        <v>1.0205</v>
+        <v>0.1008</v>
       </c>
       <c r="N63" s="7" t="n">
-        <v>1.9437</v>
+        <v>0.4922</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>0.0374</v>
+        <v>0.1647</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>0.137</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R63" s="5" t="inlineStr"/>
@@ -4147,55 +4147,57 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>BYDNR</t>
+          <t>ISDMR</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>21.1</v>
+        <v>55.7</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.0186</v>
+        <v>-0.0503</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.025</v>
+        <v>-0.1541</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>-0.3492</v>
+        <v>-0.1038</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>-0.4647</v>
+        <v>-0.0397</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.4573</v>
+        <v>0.2269</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>0.0048</v>
+        <v>0.5095000000000001</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr"/>
+        <v>1.04</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>13.13</v>
+      </c>
       <c r="K64" s="4" t="n">
-        <v>0.2762</v>
+        <v>0.1859</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.0636</v>
+        <v>0.3543</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.127</v>
+        <v>0.4035</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.7182999999999999</v>
+        <v>0.208</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>0.1081</v>
+        <v>0.1056</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>-0.0257</v>
+        <v>0.0859</v>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr"/>
@@ -4203,57 +4205,57 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>MOBTL</t>
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>9.970000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>-0.0216</v>
+        <v>-0.0505</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>-0.0505</v>
+        <v>-0.0953</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>-0.0862</v>
+        <v>-0.2028</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>-0.1774</v>
+        <v>-0.3368</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>-0.0717</v>
+        <v>-0.2833</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>-0.1699</v>
+        <v>0.3858</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>6.69</v>
+        <v>13.59</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>0.423</v>
+        <v>0.5631</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>0.5552</v>
+        <v>0.4406</v>
       </c>
       <c r="M65" s="7" t="n">
-        <v>0.8170999999999999</v>
+        <v>0.5064</v>
       </c>
       <c r="N65" s="7" t="n">
-        <v>10.0728</v>
+        <v>1.6818</v>
       </c>
       <c r="O65" s="7" t="n">
-        <v>0.179</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="P65" s="7" t="n">
-        <v>0.2236</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R65" s="5" t="inlineStr"/>
@@ -4261,57 +4263,57 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ISDMR</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>58.65</v>
+        <v>9.85</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.0424</v>
+        <v>-0.012</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.0578</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>-0.0385</v>
+        <v>-0.1086</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>0.006</v>
+        <v>-0.2213</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0.3378</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>0.5775</v>
+        <v>-0.1667</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>13.83</v>
+        <v>6.61</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0.1859</v>
+        <v>0.423</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.3543</v>
+        <v>0.5552</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.4035</v>
+        <v>0.8170999999999999</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.208</v>
+        <v>10.0728</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>0.1056</v>
+        <v>0.179</v>
       </c>
       <c r="P66" s="4" t="n">
-        <v>0.0859</v>
+        <v>0.2236</v>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr"/>
@@ -4319,57 +4321,55 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>MOBTL</t>
+          <t>BYDNR</t>
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>10.1</v>
+        <v>21.1</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>-0.0363</v>
+        <v>0</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>-0.0251</v>
+        <v>-0.1388</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>-0.1855</v>
+        <v>-0.1627</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>-0.2962</v>
+        <v>-0.4628</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>-0.2638</v>
+        <v>-0.4567</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>0.4367</v>
+        <v>0.0243</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J67" s="6" t="n">
-        <v>14.31</v>
-      </c>
+        <v>1.05</v>
+      </c>
+      <c r="J67" s="5" t="inlineStr"/>
       <c r="K67" s="7" t="n">
-        <v>0.5631</v>
+        <v>0.2762</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>0.4406</v>
+        <v>0.0636</v>
       </c>
       <c r="M67" s="7" t="n">
-        <v>0.5064</v>
+        <v>0.127</v>
       </c>
       <c r="N67" s="7" t="n">
-        <v>1.6818</v>
+        <v>0.7182999999999999</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.1081</v>
       </c>
       <c r="P67" s="7" t="n">
-        <v>0.08689999999999999</v>
+        <v>-0.0257</v>
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R67" s="5" t="inlineStr"/>
@@ -4381,31 +4381,31 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>739.5</v>
+        <v>709.5</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.058</v>
+        <v>-0.0406</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>-0.09820000000000001</v>
+        <v>-0.1736</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>-0.2937</v>
+        <v>-0.2797</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>-0.3277</v>
+        <v>-0.3461</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-0.5063</v>
+        <v>-0.4752</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>-0.2896</v>
+        <v>-0.3044</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>1593.41</v>
+        <v>1528.77</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>0.248</v>
@@ -4435,57 +4435,57 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>ENKAI</t>
+          <t>SELEC</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>76.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>-0.0206</v>
+        <v>-0.0708</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.2336</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>-0.1134</v>
+        <v>-0.6919</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>-0.1731</v>
+        <v>-0.7371</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>-0.2659</v>
+        <v>-0.2629</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>0.0346</v>
+        <v>-0.1253</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>11.45</v>
+        <v>20</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>0.4381</v>
+        <v>0.3781</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>0.1539</v>
+        <v>0.6063000000000001</v>
       </c>
       <c r="M69" s="7" t="n">
-        <v>0.1373</v>
+        <v>1.4267</v>
       </c>
       <c r="N69" s="7" t="n">
-        <v>0.3376</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="O69" s="7" t="n">
-        <v>0.2166</v>
+        <v>0.0158</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>0.1059</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R69" s="5" t="inlineStr"/>
@@ -4493,57 +4493,57 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>NTGAZ</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>10.05</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>-0.0186</v>
+        <v>-0.0072</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>-0.0703</v>
+        <v>-0.0935</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>-0.09300000000000001</v>
+        <v>-0.1178</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>-0.1299</v>
+        <v>-0.1608</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>-0.1934</v>
+        <v>-0.2836</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>0.0646</v>
+        <v>0.0693</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>6.39</v>
+        <v>11.36</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0.3448</v>
+        <v>0.4381</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>0.3645</v>
+        <v>0.1539</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.4084</v>
+        <v>0.1373</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.5755</v>
+        <v>0.3376</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>0.2148</v>
+        <v>0.2166</v>
       </c>
       <c r="P70" s="4" t="n">
-        <v>0.2137</v>
+        <v>0.1059</v>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr"/>
@@ -4551,55 +4551,55 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>OBASE</t>
+          <t>YKSLN</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>20.7</v>
+        <v>2.24</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>-0.0582</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>-0.2032</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>-0.4086</v>
+        <v>-0.3978</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>-0.5289</v>
+        <v>-0.3</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>-0.4547</v>
+        <v>-0.3043</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>-0.4408</v>
+        <v>-0.3699</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="J71" s="5" t="inlineStr"/>
       <c r="K71" s="7" t="n">
-        <v>0.2041</v>
+        <v>0.1126</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>0.3021</v>
+        <v>0.0263</v>
       </c>
       <c r="M71" s="7" t="n">
-        <v>0.5156000000000001</v>
+        <v>0.6127</v>
       </c>
       <c r="N71" s="7" t="n">
-        <v>0.4873</v>
+        <v>0.8754000000000001</v>
       </c>
       <c r="O71" s="7" t="n">
-        <v>0.2465</v>
+        <v>0.1443</v>
       </c>
       <c r="P71" s="7" t="n">
-        <v>0.1432</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R71" s="5" t="inlineStr"/>
@@ -4607,57 +4607,57 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SELEC</t>
+          <t>NTGAZ</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>-0.0147</v>
+        <v>-0.0299</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>-0.0498</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>-0.7313</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>-0.7045</v>
+        <v>-0.1716</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>-0.205</v>
+        <v>-0.1942</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>-0.0723</v>
+        <v>0.0529</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>21.52</v>
+        <v>6.2</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0.3781</v>
+        <v>0.3448</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.6063000000000001</v>
+        <v>0.3645</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>1.4267</v>
+        <v>0.4084</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5755</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>0.0158</v>
+        <v>0.2148</v>
       </c>
       <c r="P72" s="4" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.2137</v>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr"/>
@@ -4665,55 +4665,57 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>YKSLN</t>
+          <t>GEDIK</t>
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>2.41</v>
+        <v>4.56</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>-0.0974</v>
+        <v>-0.0539</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>0.0478</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-0.5275</v>
+        <v>-0.09699999999999999</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>-0.2585</v>
+        <v>-0.3372</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>-0.2349</v>
+        <v>-0.2178</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>-0.3254</v>
+        <v>-0.3684000000000001</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J73" s="5" t="inlineStr"/>
+        <v>1.14</v>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>4.83</v>
+      </c>
       <c r="K73" s="7" t="n">
-        <v>0.1126</v>
+        <v>0.6583</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>0.0263</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="M73" s="7" t="n">
-        <v>0.6127</v>
+        <v>0.7293999999999999</v>
       </c>
       <c r="N73" s="7" t="n">
-        <v>0.8754000000000001</v>
+        <v>0.3481</v>
       </c>
       <c r="O73" s="7" t="n">
-        <v>0.1443</v>
+        <v>0.6628000000000001</v>
       </c>
       <c r="P73" s="7" t="n">
-        <v>-0.04969999999999999</v>
+        <v>0.275</v>
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R73" s="5" t="inlineStr"/>
@@ -4721,57 +4723,55 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>OBASE</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>270.5</v>
+        <v>20.78</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>-0.0018</v>
+        <v>0.0039</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>-0.0261</v>
+        <v>-0.1952</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>0.0546</v>
+        <v>-0.3756</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>-0.0009</v>
+        <v>-0.5877</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-0.1351</v>
+        <v>-0.4526</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>0.198</v>
+        <v>-0.4156</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>18.63</v>
-      </c>
+        <v>1.16</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="4" t="n">
-        <v>0.3707</v>
+        <v>0.2041</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.4185</v>
+        <v>0.3021</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.4202</v>
+        <v>0.5156000000000001</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>1.8941</v>
+        <v>0.4873</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>0.3086</v>
+        <v>0.2465</v>
       </c>
       <c r="P74" s="4" t="n">
-        <v>-0.1688</v>
+        <v>0.1432</v>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr"/>
@@ -4779,53 +4779,53 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>GEDIK</t>
+          <t>GLCVY</t>
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>4.82</v>
+        <v>35.18</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0309</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>-0.0379</v>
+        <v>-0.1071</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-0.1252</v>
+        <v>-0.2686</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>-0.287</v>
+        <v>-0.3735</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>-0.1775</v>
+        <v>-0.4398</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>-0.3451</v>
+        <v>-0.4596</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>5.1</v>
+        <v>3.41</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>0.6583</v>
+        <v>0.265</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.2739</v>
       </c>
       <c r="M75" s="7" t="n">
-        <v>0.7293999999999999</v>
+        <v>0.2851</v>
       </c>
       <c r="N75" s="7" t="n">
-        <v>0.3481</v>
+        <v>0.0788</v>
       </c>
       <c r="O75" s="7" t="n">
-        <v>0.6628000000000001</v>
+        <v>0.7251000000000001</v>
       </c>
       <c r="P75" s="7" t="n">
-        <v>0.275</v>
+        <v>0.4011</v>
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
@@ -4837,53 +4837,53 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GLCVY</t>
+          <t>GARFA</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>36.3</v>
+        <v>20.3</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.0392</v>
+        <v>-0.0478</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>-0.07490000000000001</v>
+        <v>-0.128</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>-0.3019</v>
+        <v>-0.2192</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>-0.3495</v>
+        <v>-0.3322</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.393</v>
+        <v>-0.275</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>-0.4398</v>
+        <v>-0.1828</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>3.52</v>
+        <v>3.08</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0.265</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.2739</v>
+        <v>0.9506</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.2851</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.0788</v>
+        <v>0.5365</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>0.7251000000000001</v>
+        <v>0.914</v>
       </c>
       <c r="P76" s="4" t="n">
-        <v>0.4011</v>
+        <v>0.496</v>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
@@ -4899,31 +4899,31 @@
         </is>
       </c>
       <c r="B77" s="6" t="n">
-        <v>28.7</v>
+        <v>28.06</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>-0.0311</v>
+        <v>-0.0223</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>-0.0271</v>
+        <v>-0.0578</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-0.1448</v>
+        <v>-0.196</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>-0.2247</v>
+        <v>-0.2354</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>-0.3447</v>
+        <v>-0.3703</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>-0.2896</v>
+        <v>-0.2936</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>6.41</v>
+        <v>6.27</v>
       </c>
       <c r="K77" s="7" t="n">
         <v>0.4021</v>
@@ -4957,31 +4957,31 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>5.8</v>
+        <v>5.66</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.0241</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>-0.2418</v>
+        <v>-0.3568</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>-0.7887999999999999</v>
+        <v>-0.7456999999999999</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>-0.9011</v>
+        <v>-0.8822</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>-0.7637</v>
+        <v>-0.8105</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>0.4714</v>
+        <v>0.4284000000000001</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="K78" s="4" t="n">
         <v>3.5578</v>
@@ -5011,57 +5011,57 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
-        <v>68.90000000000001</v>
+        <v>274</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>-0.035</v>
+        <v>0.0129</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>-0.0464</v>
+        <v>-0.0018</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-0.0727</v>
+        <v>0.0046</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>-0.3304</v>
+        <v>0</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>-0.1577</v>
+        <v>-0.1274</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>0.4253</v>
+        <v>0.2227</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>25.36</v>
+        <v>18.87</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.3707</v>
       </c>
       <c r="L79" s="7" t="n">
-        <v>0.3716</v>
+        <v>0.4185</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>0.4119</v>
+        <v>0.4202</v>
       </c>
       <c r="N79" s="7" t="n">
-        <v>0.9691</v>
+        <v>1.8941</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>0.3037</v>
+        <v>0.3086</v>
       </c>
       <c r="P79" s="7" t="n">
-        <v>0.0601</v>
+        <v>-0.1688</v>
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="R79" s="5" t="inlineStr"/>
@@ -5069,57 +5069,57 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>GARFA</t>
+          <t>KCAER</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>21.32</v>
+        <v>9.52</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>-0.0362</v>
+        <v>-0.0602</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>-0.06</v>
+        <v>-0.1266</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>-0.1936</v>
+        <v>-0.2067</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>-0.2917</v>
+        <v>-0.3181</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>-0.2466</v>
+        <v>-0.1919</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>-0.1566</v>
+        <v>-0.2438</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>3.23</v>
+        <v>27.72</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0.9562999999999999</v>
+        <v>0.1522</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>0.9506</v>
+        <v>0.2873</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.3247</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>0.5365</v>
+        <v>1.1982</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>0.914</v>
+        <v>0.1199</v>
       </c>
       <c r="P80" s="4" t="n">
-        <v>0.496</v>
+        <v>0.0508</v>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr"/>
@@ -5127,57 +5127,57 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>SARKY</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>17.2</v>
+        <v>69</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>-0.0529</v>
+        <v>0.0015</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>-0.1224</v>
+        <v>-0.0707</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-0.2308</v>
+        <v>0.0073</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>-0.3405</v>
+        <v>-0.3527</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>-0.3944</v>
+        <v>-0.1429</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>0.152</v>
+        <v>0.4274</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>63.03</v>
+        <v>25.4</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>0.5590999999999999</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="L81" s="7" t="n">
-        <v>0.3671</v>
+        <v>0.3716</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>0.2342</v>
+        <v>0.4119</v>
       </c>
       <c r="N81" s="7" t="n">
-        <v>0.8034</v>
+        <v>0.9691</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>0.0217</v>
+        <v>0.3037</v>
       </c>
       <c r="P81" s="7" t="n">
-        <v>0.0229</v>
+        <v>0.0601</v>
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R81" s="5" t="inlineStr"/>
@@ -5189,28 +5189,28 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>5.92</v>
+        <v>5.75</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>-0.0263</v>
+        <v>-0.0287</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>-0.0133</v>
+        <v>0.0213</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>-0.3415</v>
+        <v>-0.1606</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>-0.3689</v>
+        <v>-0.4078</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>-0.0215</v>
+        <v>-0.08</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>-0.278</v>
+        <v>-0.2919</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="4" t="n">
@@ -5241,55 +5241,55 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>KNFRT</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>6.14</v>
+        <v>7.56</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>-0.0223</v>
+        <v>-0.09789999999999999</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>-0.0711</v>
+        <v>-0.2766</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-0.1612</v>
+        <v>-0.371</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>-0.2257</v>
+        <v>-0.3726</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>-0.2602</v>
+        <v>-0.4229</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>-0.2448</v>
+        <v>-0.4341</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="J83" s="5" t="inlineStr"/>
       <c r="K83" s="7" t="n">
-        <v>0.3952000000000001</v>
+        <v>0.7798</v>
       </c>
       <c r="L83" s="7" t="n">
-        <v>0.4088000000000001</v>
+        <v>1.3764</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>0.4094</v>
+        <v>26.3063</v>
       </c>
       <c r="N83" s="7" t="n">
-        <v>0.7489</v>
+        <v>0.625</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>0.7836</v>
+        <v>0.0124</v>
       </c>
       <c r="P83" s="7" t="n">
-        <v>-0.0106</v>
+        <v>-0.1091</v>
       </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
-          <t>Çeşitli Hizmetler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R83" s="5" t="inlineStr"/>
@@ -5297,57 +5297,55 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>KCAER</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>10.13</v>
+        <v>6</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>-0.0325</v>
+        <v>-0.0228</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>-0.0362</v>
+        <v>-0.09230000000000001</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>-0.208</v>
+        <v>-0.1549</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>-0.2551</v>
+        <v>-0.2395</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>-0.1267</v>
+        <v>-0.2823</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>-0.2117</v>
+        <v>-0.2583</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="J84" s="3" t="n">
-        <v>29.5</v>
-      </c>
+        <v>1.26</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="4" t="n">
-        <v>0.1522</v>
+        <v>0.3952000000000001</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.2873</v>
+        <v>0.4088000000000001</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>0.3247</v>
+        <v>0.4094</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>1.1982</v>
+        <v>0.7489</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>0.1199</v>
+        <v>0.7836</v>
       </c>
       <c r="P84" s="4" t="n">
-        <v>0.0508</v>
+        <v>-0.0106</v>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Çeşitli Hizmetler</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr"/>
@@ -5355,55 +5353,57 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>SARKY</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>83.45</v>
+        <v>17.07</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>-0.0148</v>
+        <v>-0.0076</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>-0.0302</v>
+        <v>-0.1491</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-0.2462</v>
+        <v>-0.2447</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>-0.3596</v>
+        <v>-0.3358</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>-0.275</v>
+        <v>-0.3977000000000001</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>-0.2201</v>
+        <v>0.1644</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="J85" s="5" t="inlineStr"/>
+        <v>1.27</v>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>62.55</v>
+      </c>
       <c r="K85" s="7" t="n">
-        <v>0.3957</v>
+        <v>0.5590999999999999</v>
       </c>
       <c r="L85" s="7" t="n">
-        <v>2.0344</v>
+        <v>0.3671</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>3.8494</v>
+        <v>0.2342</v>
       </c>
       <c r="N85" s="7" t="n">
-        <v>0.889</v>
+        <v>0.8034</v>
       </c>
       <c r="O85" s="7" t="n">
-        <v>0.0349</v>
+        <v>0.0217</v>
       </c>
       <c r="P85" s="7" t="n">
-        <v>-0.0175</v>
+        <v>0.0229</v>
       </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R85" s="5" t="inlineStr"/>
@@ -5411,57 +5411,55 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>PCILT</t>
+          <t>ACSEL</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>30.68</v>
+        <v>81</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>-0.016</v>
+        <v>-0.0294</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>0.002</v>
+        <v>-0.099</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>0.0199</v>
+        <v>-0.2212</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>-0.1029</v>
+        <v>-0.374</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>0.1181</v>
+        <v>-0.3182</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>0.4499</v>
+        <v>-0.2895</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>7.05</v>
-      </c>
+        <v>1.29</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="4" t="n">
-        <v>0.763</v>
+        <v>0.3957</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>0.7087</v>
+        <v>2.0344</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>0.7914</v>
+        <v>3.8494</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>1.2232</v>
+        <v>0.889</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>0.0574</v>
+        <v>0.0349</v>
       </c>
       <c r="P86" s="4" t="n">
-        <v>0.2831</v>
+        <v>-0.0175</v>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr"/>
@@ -5469,55 +5467,57 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>KNFRT</t>
+          <t>PCILT</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>8.380000000000001</v>
+        <v>28.7</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>-0.0999</v>
+        <v>-0.0645</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>-0.2109</v>
+        <v>-0.0645</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>-0.3301</v>
+        <v>-0.0559</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>-0.308</v>
+        <v>-0.1618</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>-0.3339</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>-0.4094</v>
+        <v>0.3851</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="J87" s="5" t="inlineStr"/>
+        <v>1.3</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>6.59</v>
+      </c>
       <c r="K87" s="7" t="n">
-        <v>0.7798</v>
+        <v>0.763</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>1.3764</v>
+        <v>0.7087</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>26.3063</v>
+        <v>0.7914</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>0.625</v>
+        <v>1.2232</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>0.0124</v>
+        <v>0.0574</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>-0.1091</v>
+        <v>0.2831</v>
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R87" s="5" t="inlineStr"/>
@@ -5529,28 +5529,28 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>12.02</v>
+        <v>11.6</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>0.0544</v>
+        <v>-0.0349</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>0.0461</v>
+        <v>-0.0119</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>0.0544</v>
+        <v>0.0526</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>-0.08310000000000001</v>
+        <v>-0.1212</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>0.08550000000000001</v>
+        <v>-0.0238</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>0.5566</v>
+        <v>0.4909000000000001</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="4" t="n">
@@ -5585,31 +5585,31 @@
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>26.14</v>
+        <v>25.1</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>-0.0446</v>
+        <v>-0.0398</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>-0.106</v>
+        <v>-0.1526</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-0.2866</v>
+        <v>-0.2574</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>-0.4376</v>
+        <v>-0.4555</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>-0.3231</v>
+        <v>-0.379</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>-0.3767</v>
+        <v>-0.3923</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>31.32</v>
+        <v>30.07</v>
       </c>
       <c r="K89" s="7" t="n">
         <v>0.05019999999999999</v>
@@ -5643,31 +5643,31 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>28.56</v>
+        <v>28.18</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>-0.0587</v>
+        <v>-0.0133</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>-0.155</v>
+        <v>-0.1687</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>-0.2298</v>
+        <v>-0.2342</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>-0.2496</v>
+        <v>-0.2384</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>-0.1964</v>
+        <v>-0.3847</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>0.081</v>
+        <v>0.0756</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>10.17</v>
+        <v>10.04</v>
       </c>
       <c r="K90" s="4" t="n">
         <v>0.3776</v>
@@ -5697,57 +5697,55 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>TUPRS</t>
+          <t>KRPLS</t>
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>375.5</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>-0.0234</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>-0.0433</v>
+        <v>-0.2062</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.2462</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>0.3084</v>
+        <v>-0.0011</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>0.4024</v>
+        <v>-0.0164</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>1.1084</v>
+        <v>0.0124</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="J91" s="6" t="n">
-        <v>10.42</v>
-      </c>
+        <v>1.48</v>
+      </c>
+      <c r="J91" s="5" t="inlineStr"/>
       <c r="K91" s="7" t="n">
-        <v>0.465</v>
+        <v>0.3576</v>
       </c>
       <c r="L91" s="7" t="n">
-        <v>1.0453</v>
+        <v>0.6872</v>
       </c>
       <c r="M91" s="7" t="n">
-        <v>1.1002</v>
+        <v>0.9115000000000001</v>
       </c>
       <c r="N91" s="7" t="n">
-        <v>2.2351</v>
+        <v>0.7781999999999999</v>
       </c>
       <c r="O91" s="7" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.166</v>
       </c>
       <c r="P91" s="7" t="n">
-        <v>0.187</v>
+        <v>-0.0342</v>
       </c>
       <c r="Q91" s="5" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R91" s="5" t="inlineStr"/>
@@ -5755,57 +5753,57 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>MEGMT</t>
+          <t>TUPRS</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>3.19</v>
+        <v>356.75</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>-0.0449</v>
+        <v>-0.0499</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>-0.1308</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>-0.2698</v>
+        <v>-0.1299</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>-0.551</v>
+        <v>0.163</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>-0.6222</v>
+        <v>0.4059</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>-0.0235</v>
+        <v>1.0339</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>6.81</v>
+        <v>9.9</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0.51</v>
+        <v>0.465</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>0.4203</v>
+        <v>1.0453</v>
       </c>
       <c r="M92" s="4" t="n">
-        <v>0.8453000000000001</v>
+        <v>1.1002</v>
       </c>
       <c r="N92" s="4" t="n">
-        <v>0.2482</v>
+        <v>2.2351</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>0.0483</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="P92" s="4" t="n">
-        <v>0.2852</v>
+        <v>0.187</v>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="R92" s="2" t="inlineStr"/>
@@ -5813,55 +5811,57 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>KRPLS</t>
+          <t>MEGMT</t>
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>9.93</v>
+        <v>3.1</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.0282</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>-0.103</v>
+        <v>-0.1507</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>-0.1725</v>
+        <v>-0.1692</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>0.09359999999999999</v>
+        <v>-0.5649000000000001</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>0.09119999999999999</v>
+        <v>-0.6247</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>0.09849999999999999</v>
+        <v>-0.0211</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="J93" s="5" t="inlineStr"/>
+        <v>1.56</v>
+      </c>
+      <c r="J93" s="6" t="n">
+        <v>6.62</v>
+      </c>
       <c r="K93" s="7" t="n">
-        <v>0.3576</v>
+        <v>0.51</v>
       </c>
       <c r="L93" s="7" t="n">
-        <v>0.6872</v>
+        <v>0.4203</v>
       </c>
       <c r="M93" s="7" t="n">
-        <v>0.9115000000000001</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="N93" s="7" t="n">
-        <v>0.7781999999999999</v>
+        <v>0.2482</v>
       </c>
       <c r="O93" s="7" t="n">
-        <v>0.166</v>
+        <v>0.0483</v>
       </c>
       <c r="P93" s="7" t="n">
-        <v>-0.0342</v>
+        <v>0.2852</v>
       </c>
       <c r="Q93" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R93" s="5" t="inlineStr"/>
@@ -5869,57 +5869,57 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ORGE</t>
+          <t>FONET</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>21.4</v>
+        <v>3.56</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>-0.0438</v>
+        <v>-0.09179999999999999</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>-0.0564</v>
+        <v>-0.1504</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>-0.0421</v>
+        <v>-0.1166</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>-0.0282</v>
+        <v>-0.3167</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>0.406</v>
+        <v>-0.2537</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>0.5711999999999999</v>
+        <v>0.0509</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>9.93</v>
+        <v>11.57</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0.251</v>
+        <v>1.0251</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>0.257</v>
+        <v>2.0469</v>
       </c>
       <c r="M94" s="4" t="n">
-        <v>0.2421</v>
+        <v>1.6971</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>0.2676</v>
+        <v>1.6785</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>0.4943</v>
+        <v>0.4396</v>
       </c>
       <c r="P94" s="4" t="n">
-        <v>0.2029</v>
+        <v>0.8814</v>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr"/>
@@ -5927,55 +5927,57 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>DURDO</t>
+          <t>GENIL</t>
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>5.68</v>
+        <v>4.64</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>-0.0998</v>
+        <v>-0.099</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>-0.1125</v>
+        <v>-0.0252</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>0.1008</v>
+        <v>-0.4833</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>0.1159</v>
+        <v>-0.489</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>0.3365</v>
+        <v>-0.5323</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>0.6322</v>
+        <v>-0.6598000000000001</v>
       </c>
       <c r="I95" s="6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="J95" s="5" t="inlineStr"/>
+        <v>1.59</v>
+      </c>
+      <c r="J95" s="6" t="n">
+        <v>16.92</v>
+      </c>
       <c r="K95" s="7" t="n">
-        <v>0.3099</v>
+        <v>0.5049</v>
       </c>
       <c r="L95" s="7" t="n">
-        <v>0.2862</v>
+        <v>0.7672</v>
       </c>
       <c r="M95" s="7" t="n">
-        <v>0.3279</v>
+        <v>1.1622</v>
       </c>
       <c r="N95" s="7" t="n">
-        <v>0.1519</v>
+        <v>1.2274</v>
       </c>
       <c r="O95" s="7" t="n">
-        <v>0.0876</v>
+        <v>0.0922</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.1305</v>
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R95" s="5" t="inlineStr"/>
@@ -5983,57 +5985,57 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>DERIM</t>
+          <t>ORGE</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>22.88</v>
+        <v>20.78</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>-0.0584</v>
+        <v>-0.029</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>-0.1475</v>
+        <v>-0.1028</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>-0.319</v>
+        <v>-0.0707</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>-0.3796</v>
+        <v>-0.0142</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>-0.4274</v>
+        <v>0.2632</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>-0.3783</v>
+        <v>0.5589</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>12.61</v>
+        <v>9.65</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0.1436</v>
+        <v>0.251</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>0.2539</v>
+        <v>0.257</v>
       </c>
       <c r="M96" s="4" t="n">
-        <v>0.0263</v>
+        <v>0.2421</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>0.0576</v>
+        <v>0.2676</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>0.0602</v>
+        <v>0.4943</v>
       </c>
       <c r="P96" s="4" t="n">
-        <v>0.1637</v>
+        <v>0.2029</v>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr"/>
@@ -6041,57 +6043,55 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>SAYAS</t>
+          <t>DURDO</t>
         </is>
       </c>
       <c r="B97" s="6" t="n">
-        <v>35.64</v>
+        <v>5.52</v>
       </c>
       <c r="C97" s="7" t="n">
-        <v>-0.0546</v>
+        <v>-0.0282</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>-0.1005</v>
+        <v>-0.1375</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>-0.2872</v>
+        <v>0.1084</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>-0.2497</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>-0.1837</v>
+        <v>0.182</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>-0.3012</v>
+        <v>0.6047</v>
       </c>
       <c r="I97" s="6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J97" s="6" t="n">
-        <v>14.2</v>
-      </c>
+        <v>1.64</v>
+      </c>
+      <c r="J97" s="5" t="inlineStr"/>
       <c r="K97" s="7" t="n">
-        <v>0.486</v>
+        <v>0.3099</v>
       </c>
       <c r="L97" s="7" t="n">
-        <v>1.4655</v>
+        <v>0.2862</v>
       </c>
       <c r="M97" s="7" t="n">
-        <v>2.3632</v>
+        <v>0.3279</v>
       </c>
       <c r="N97" s="7" t="n">
-        <v>6.118200000000001</v>
+        <v>0.1519</v>
       </c>
       <c r="O97" s="7" t="n">
-        <v>0.1798</v>
+        <v>0.0876</v>
       </c>
       <c r="P97" s="7" t="n">
-        <v>0.1493</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R97" s="5" t="inlineStr"/>
@@ -6099,57 +6099,57 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>SAFKR</t>
+          <t>DERIM</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>12.16</v>
+        <v>22.1</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>0.021</v>
+        <v>-0.0341</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>-0.0342</v>
+        <v>-0.1754</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.3059</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>-0.4114</v>
+        <v>-0.3972</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.4578</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>-0.4126</v>
+        <v>-0.3949</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>17.68</v>
+        <v>12.18</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0.7861</v>
+        <v>0.1436</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>0.4555</v>
+        <v>0.2539</v>
       </c>
       <c r="M98" s="4" t="n">
-        <v>0.3309</v>
+        <v>0.0263</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>0.5716</v>
+        <v>0.0576</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>0.2109</v>
+        <v>0.0602</v>
       </c>
       <c r="P98" s="4" t="n">
-        <v>0.1216</v>
+        <v>0.1637</v>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr"/>
@@ -6157,57 +6157,57 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>FONET</t>
+          <t>SAYAS</t>
         </is>
       </c>
       <c r="B99" s="6" t="n">
-        <v>3.92</v>
+        <v>34.3</v>
       </c>
       <c r="C99" s="7" t="n">
-        <v>-0.0321</v>
+        <v>-0.03759999999999999</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>-0.05769999999999999</v>
+        <v>-0.1459</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>-0.07980000000000001</v>
+        <v>-0.2649</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>-0.2299</v>
+        <v>-0.2687</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>-0.2359</v>
+        <v>-0.2197</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>0.334</v>
+        <v>-0.3333</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>12.74</v>
+        <v>13.67</v>
       </c>
       <c r="K99" s="7" t="n">
-        <v>1.0251</v>
+        <v>0.486</v>
       </c>
       <c r="L99" s="7" t="n">
-        <v>2.0469</v>
+        <v>1.4655</v>
       </c>
       <c r="M99" s="7" t="n">
-        <v>1.6971</v>
+        <v>2.3632</v>
       </c>
       <c r="N99" s="7" t="n">
-        <v>1.6785</v>
+        <v>6.118200000000001</v>
       </c>
       <c r="O99" s="7" t="n">
-        <v>0.4396</v>
+        <v>0.1798</v>
       </c>
       <c r="P99" s="7" t="n">
-        <v>0.8814</v>
+        <v>0.1493</v>
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R99" s="5" t="inlineStr"/>
@@ -6215,57 +6215,57 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GENIL</t>
+          <t>SAFKR</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>5.15</v>
+        <v>11.75</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>-0.0172</v>
+        <v>-0.0337</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>0.1573</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>-0.5365</v>
+        <v>-0.0059</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>-0.4515</v>
+        <v>-0.4206</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>-0.5047999999999999</v>
+        <v>-0.546</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>-0.6284000000000001</v>
+        <v>-0.4125</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>18.78</v>
+        <v>17.09</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0.5049</v>
+        <v>0.7861</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>0.7672</v>
+        <v>0.4555</v>
       </c>
       <c r="M100" s="4" t="n">
-        <v>1.1622</v>
+        <v>0.3309</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>1.2274</v>
+        <v>0.5716</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>0.0922</v>
+        <v>0.2109</v>
       </c>
       <c r="P100" s="4" t="n">
-        <v>0.1305</v>
+        <v>0.1216</v>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R100" s="2" t="inlineStr"/>
@@ -6277,31 +6277,31 @@
         </is>
       </c>
       <c r="B101" s="6" t="n">
-        <v>416</v>
+        <v>401.5</v>
       </c>
       <c r="C101" s="7" t="n">
-        <v>-0.0269</v>
+        <v>-0.0349</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>-0.0183</v>
+        <v>-0.0833</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>-0.0263</v>
+        <v>-0.077</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>-0.0387</v>
+        <v>-0.0542</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>-0.0917</v>
+        <v>-0.1389</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>0.2381</v>
+        <v>0.2066</v>
       </c>
       <c r="I101" s="6" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>12.99</v>
+        <v>12.54</v>
       </c>
       <c r="K101" s="7" t="n">
         <v>0.3601</v>
@@ -6335,31 +6335,31 @@
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>13.85</v>
+        <v>13.25</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>-0.04480000000000001</v>
+        <v>-0.0433</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>-0.0253</v>
+        <v>-0.0747</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>0.0863</v>
+        <v>0.0458</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>0.4191</v>
+        <v>0.3947</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>0.5086999999999999</v>
+        <v>0.4309000000000001</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>0.4147</v>
+        <v>0.3947</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>22.09</v>
+        <v>21.13</v>
       </c>
       <c r="K102" s="4" t="n">
         <v>0.4279</v>
@@ -6389,57 +6389,57 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="B103" s="6" t="n">
-        <v>244.4</v>
+        <v>15.6</v>
       </c>
       <c r="C103" s="7" t="n">
-        <v>-0.0077</v>
+        <v>-0.0998</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>-0.1015</v>
+        <v>0.0541</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>-0.1425</v>
+        <v>-0.0736</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>-0.1934</v>
+        <v>-0.5979</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>-0.1529</v>
+        <v>-0.481</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>-0.0472</v>
+        <v>0.4436</v>
       </c>
       <c r="I103" s="6" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>9.609999999999999</v>
+        <v>2.01</v>
       </c>
       <c r="K103" s="7" t="n">
-        <v>1.7224</v>
+        <v>2.1748</v>
       </c>
       <c r="L103" s="7" t="n">
-        <v>1.8184</v>
+        <v>2.2285</v>
       </c>
       <c r="M103" s="7" t="n">
-        <v>1.3297</v>
+        <v>2.5519</v>
       </c>
       <c r="N103" s="7" t="n">
-        <v>5.0053</v>
+        <v>7.8348</v>
       </c>
       <c r="O103" s="7" t="n">
-        <v>0.0381</v>
+        <v>0.887</v>
       </c>
       <c r="P103" s="7" t="n">
-        <v>0.2862</v>
+        <v>1.1538</v>
       </c>
       <c r="Q103" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R103" s="5" t="inlineStr"/>
@@ -6451,31 +6451,31 @@
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>27.5</v>
+        <v>25.48</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>-0.0269</v>
+        <v>-0.0735</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>-0.0678</v>
+        <v>-0.2251</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>-0.3834</v>
+        <v>-0.3467</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>-0.6403</v>
+        <v>-0.6307</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>-0.2361</v>
+        <v>-0.2906</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>0.0029</v>
+        <v>-0.0728</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>2.65</v>
+        <v>2.46</v>
       </c>
       <c r="K104" s="4" t="n">
         <v>0.309</v>
@@ -6505,57 +6505,57 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B105" s="6" t="n">
-        <v>200.4</v>
+        <v>235</v>
       </c>
       <c r="C105" s="7" t="n">
-        <v>-0.04480000000000001</v>
+        <v>-0.0385</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>-0.1017</v>
+        <v>-0.1182</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>-0.1133</v>
+        <v>-0.1725</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>-0.1425</v>
+        <v>-0.2276</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>-0.221</v>
+        <v>-0.1869</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>-0.1447</v>
+        <v>-0.0711</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="J105" s="6" t="n">
-        <v>18.73</v>
+        <v>9.24</v>
       </c>
       <c r="K105" s="7" t="n">
-        <v>0.493</v>
+        <v>1.7224</v>
       </c>
       <c r="L105" s="7" t="n">
-        <v>0.3835</v>
+        <v>1.8184</v>
       </c>
       <c r="M105" s="7" t="n">
-        <v>0.4282</v>
+        <v>1.3297</v>
       </c>
       <c r="N105" s="7" t="n">
-        <v>0.1825</v>
+        <v>5.0053</v>
       </c>
       <c r="O105" s="7" t="n">
-        <v>0.2029</v>
+        <v>0.0381</v>
       </c>
       <c r="P105" s="7" t="n">
-        <v>0.1296</v>
+        <v>0.2862</v>
       </c>
       <c r="Q105" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="R105" s="5" t="inlineStr"/>
@@ -6563,57 +6563,57 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>AHGAZ</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>46.48</v>
+        <v>190.8</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>-0.0296</v>
+        <v>-0.0479</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>-0.0353</v>
+        <v>-0.1632</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>0.1304</v>
+        <v>-0.1836</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>0.2833</v>
+        <v>-0.1829</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>0.8652</v>
+        <v>-0.264</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>0.7659999999999999</v>
+        <v>-0.1864</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>22</v>
+        <v>17.84</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0.659</v>
+        <v>0.493</v>
       </c>
       <c r="L106" s="4" t="n">
-        <v>1.7979</v>
+        <v>0.3835</v>
       </c>
       <c r="M106" s="4" t="n">
-        <v>2.1313</v>
+        <v>0.4282</v>
       </c>
       <c r="N106" s="4" t="n">
-        <v>2.8917</v>
+        <v>0.1825</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>0.1977</v>
+        <v>0.2029</v>
       </c>
       <c r="P106" s="4" t="n">
-        <v>0.1152</v>
+        <v>0.1296</v>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr"/>
@@ -6621,57 +6621,57 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>AHGAZ</t>
         </is>
       </c>
       <c r="B107" s="6" t="n">
-        <v>17.33</v>
+        <v>44.82</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>0.0017</v>
+        <v>-0.0357</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>0.2239</v>
+        <v>-0.07400000000000001</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>-0.2123</v>
+        <v>0.09369999999999999</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>-0.5732</v>
+        <v>0.2784</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>-0.4212</v>
+        <v>0.6575</v>
       </c>
       <c r="H107" s="7" t="n">
-        <v>0.4442</v>
+        <v>0.7772</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="J107" s="6" t="n">
-        <v>2.24</v>
+        <v>21.21</v>
       </c>
       <c r="K107" s="7" t="n">
-        <v>2.1748</v>
+        <v>0.659</v>
       </c>
       <c r="L107" s="7" t="n">
-        <v>2.2285</v>
+        <v>1.7979</v>
       </c>
       <c r="M107" s="7" t="n">
-        <v>2.5519</v>
+        <v>2.1313</v>
       </c>
       <c r="N107" s="7" t="n">
-        <v>7.8348</v>
+        <v>2.8917</v>
       </c>
       <c r="O107" s="7" t="n">
-        <v>0.887</v>
+        <v>0.1977</v>
       </c>
       <c r="P107" s="7" t="n">
-        <v>1.1538</v>
+        <v>0.1152</v>
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R107" s="5" t="inlineStr"/>
@@ -6683,31 +6683,31 @@
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>19.92</v>
+        <v>18.9</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>-0.0537</v>
+        <v>-0.0507</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>-0.1634</v>
+        <v>-0.2138</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>-0.3874</v>
+        <v>-0.3807</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>-0.3191</v>
+        <v>-0.3807</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>-0.0722</v>
+        <v>-0.1346</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.0373</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>13.03</v>
+        <v>12.37</v>
       </c>
       <c r="K108" s="4" t="n">
         <v>0.5342</v>
@@ -6741,31 +6741,31 @@
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>275</v>
+        <v>259.5</v>
       </c>
       <c r="C109" s="7" t="n">
-        <v>-0.0517</v>
+        <v>-0.0564</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>0.0018</v>
+        <v>-0.0757</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>-0.0614</v>
+        <v>-0.05980000000000001</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>-0.1277</v>
+        <v>-0.1859</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>-0.1352</v>
+        <v>-0.1595</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>-0.2226</v>
+        <v>-0.2746</v>
       </c>
       <c r="I109" s="6" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="J109" s="6" t="n">
-        <v>8.35</v>
+        <v>7.88</v>
       </c>
       <c r="K109" s="7" t="n">
         <v>0.3337</v>
@@ -6799,31 +6799,31 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>17.51</v>
+        <v>17.04</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>0.005699999999999999</v>
+        <v>-0.0268</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>-0.0023</v>
+        <v>-0.0179</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>0.0775</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>0.0029</v>
+        <v>-0.011</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>0.1068</v>
+        <v>0.0771</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>0.7406</v>
+        <v>0.6229</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>5.85</v>
+        <v>5.69</v>
       </c>
       <c r="K110" s="4" t="n">
         <v>0.2312</v>
@@ -6853,57 +6853,57 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>BIMAS</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>381</v>
+        <v>42.26</v>
       </c>
       <c r="C111" s="7" t="n">
-        <v>-0.05110000000000001</v>
+        <v>-0.08130000000000001</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>-0.0522</v>
+        <v>-0.149</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>-0.078</v>
+        <v>-0.2224</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>-0.0293</v>
+        <v>-0.5716</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>0.0187</v>
+        <v>0.0178</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>0.3943</v>
+        <v>0.6081</v>
       </c>
       <c r="I111" s="6" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="J111" s="6" t="n">
-        <v>16.66</v>
+        <v>29.95</v>
       </c>
       <c r="K111" s="7" t="n">
-        <v>0.4214</v>
+        <v>0.8139</v>
       </c>
       <c r="L111" s="7" t="n">
-        <v>0.5271</v>
+        <v>1.3529</v>
       </c>
       <c r="M111" s="7" t="n">
-        <v>0.8381000000000001</v>
+        <v>2.0375</v>
       </c>
       <c r="N111" s="7" t="n">
-        <v>0.8737999999999999</v>
+        <v>1.6152</v>
       </c>
       <c r="O111" s="7" t="n">
-        <v>0.0611</v>
+        <v>0.1821</v>
       </c>
       <c r="P111" s="7" t="n">
-        <v>0.1613</v>
+        <v>0.09230000000000001</v>
       </c>
       <c r="Q111" s="5" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R111" s="5" t="inlineStr"/>
@@ -6911,57 +6911,57 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>BIMAS</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>46</v>
+        <v>371</v>
       </c>
       <c r="C112" s="4" t="n">
-        <v>-0.0258</v>
+        <v>-0.0262</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>-0.0809</v>
+        <v>-0.0794</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>-0.341</v>
+        <v>-0.1103</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>-0.4772999999999999</v>
+        <v>-0.0771</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>0.1529</v>
+        <v>-0.0211</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.3818</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>32.61</v>
+        <v>16.23</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0.8139</v>
+        <v>0.4214</v>
       </c>
       <c r="L112" s="4" t="n">
-        <v>1.3529</v>
+        <v>0.5271</v>
       </c>
       <c r="M112" s="4" t="n">
-        <v>2.0375</v>
+        <v>0.8381000000000001</v>
       </c>
       <c r="N112" s="4" t="n">
-        <v>1.6152</v>
+        <v>0.8737999999999999</v>
       </c>
       <c r="O112" s="4" t="n">
-        <v>0.1821</v>
+        <v>0.0611</v>
       </c>
       <c r="P112" s="4" t="n">
-        <v>0.09230000000000001</v>
+        <v>0.1613</v>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr"/>
@@ -6973,31 +6973,31 @@
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>76.84999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>-0.0364</v>
+        <v>-0.0254</v>
       </c>
       <c r="D113" s="7" t="n">
-        <v>-0.0447</v>
+        <v>-0.1057</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>-0.0039</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>-0.1461</v>
+        <v>-0.1769</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>-0.0382</v>
+        <v>-0.0649</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>0.6282</v>
+        <v>0.5909</v>
       </c>
       <c r="I113" s="6" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="J113" s="6" t="n">
-        <v>10.38</v>
+        <v>10.12</v>
       </c>
       <c r="K113" s="7" t="n">
         <v>0.4257</v>
@@ -7031,31 +7031,31 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>41.3</v>
+        <v>40.48</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>-0.0364</v>
+        <v>-0.0199</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>-0.04</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>-0.1902</v>
+        <v>-0.192</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>-0.2073</v>
+        <v>-0.2</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>-0.1049</v>
+        <v>-0.1739</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>0.7208</v>
+        <v>0.6076</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>26.37</v>
+        <v>25.85</v>
       </c>
       <c r="K114" s="4" t="n">
         <v>1.2681</v>
@@ -7089,31 +7089,31 @@
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>114</v>
+        <v>102.6</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>-0.0009</v>
+        <v>-0.1</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>-0.08800000000000001</v>
+        <v>-0.1726</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-0.1224</v>
+        <v>-0.1101</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>-0.1396</v>
+        <v>-0.283</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>0.1771</v>
+        <v>-0.0366</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>1.6723</v>
+        <v>1.4429</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="J115" s="6" t="n">
-        <v>10.22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K115" s="7" t="n">
         <v>2.4396</v>
@@ -7143,53 +7143,53 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>HTTBT</t>
+          <t>ARDYZ</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>31.14</v>
+        <v>54.45</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>-0.0281</v>
+        <v>-0.0993</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>-0.0693</v>
+        <v>-0.1843</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>-0.0529</v>
+        <v>-0.0732</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>-0.1753</v>
+        <v>-0.1993</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>-0.2394</v>
+        <v>0.2692</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>-0.3422</v>
+        <v>1.1641</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>22.72</v>
+        <v>13.56</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0.3957</v>
+        <v>2.0657</v>
       </c>
       <c r="L116" s="4" t="n">
-        <v>0.3631</v>
+        <v>2.0433</v>
       </c>
       <c r="M116" s="4" t="n">
-        <v>0.3492</v>
+        <v>2.0361</v>
       </c>
       <c r="N116" s="4" t="n">
-        <v>0.2572</v>
+        <v>1.7568</v>
       </c>
       <c r="O116" s="4" t="n">
-        <v>0.4235</v>
+        <v>0.4642</v>
       </c>
       <c r="P116" s="4" t="n">
-        <v>0.5921</v>
+        <v>3.4222</v>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
@@ -7205,31 +7205,31 @@
         </is>
       </c>
       <c r="B117" s="6" t="n">
-        <v>127.2</v>
+        <v>120.6</v>
       </c>
       <c r="C117" s="7" t="n">
-        <v>-0.0443</v>
+        <v>-0.0519</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>-0.1317</v>
+        <v>-0.1537</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>-0.0536</v>
+        <v>-0.1286</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.1324</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>-0.09269999999999999</v>
+        <v>-0.1549</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>-0.1794</v>
+        <v>-0.1971</v>
       </c>
       <c r="I117" s="6" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>13.83</v>
+        <v>13.11</v>
       </c>
       <c r="K117" s="7" t="n">
         <v>0.5617</v>
@@ -7259,53 +7259,53 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>ARDYZ</t>
+          <t>HTTBT</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>60.45</v>
+        <v>30.3</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>-0.0242</v>
+        <v>-0.027</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>-0.0664</v>
+        <v>-0.0873</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>-0.182</v>
+        <v>-0.07339999999999999</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>-0.1327</v>
+        <v>-0.1784</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>0.4386</v>
+        <v>-0.2891</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>1.365</v>
+        <v>-0.3378</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>15.05</v>
+        <v>22.11</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>2.0657</v>
+        <v>0.3957</v>
       </c>
       <c r="L118" s="4" t="n">
-        <v>2.0433</v>
+        <v>0.3631</v>
       </c>
       <c r="M118" s="4" t="n">
-        <v>2.0361</v>
+        <v>0.3492</v>
       </c>
       <c r="N118" s="4" t="n">
-        <v>1.7568</v>
+        <v>0.2572</v>
       </c>
       <c r="O118" s="4" t="n">
-        <v>0.4642</v>
+        <v>0.4235</v>
       </c>
       <c r="P118" s="4" t="n">
-        <v>3.4222</v>
+        <v>0.5921</v>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
@@ -7317,57 +7317,57 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>ATATP</t>
         </is>
       </c>
       <c r="B119" s="6" t="n">
-        <v>372.75</v>
+        <v>203</v>
       </c>
       <c r="C119" s="7" t="n">
-        <v>-0.0551</v>
+        <v>-0.06059999999999999</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>-0.1018</v>
+        <v>-0.1409</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>-0.1808</v>
+        <v>-0.234</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>-0.1172</v>
+        <v>-0.1735</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>-0.2927</v>
+        <v>0.3914</v>
       </c>
       <c r="H119" s="7" t="n">
-        <v>0.342</v>
+        <v>0.5172</v>
       </c>
       <c r="I119" s="6" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>16.16</v>
+        <v>4.18</v>
       </c>
       <c r="K119" s="7" t="n">
-        <v>0.1897</v>
+        <v>0.3072</v>
       </c>
       <c r="L119" s="7" t="n">
-        <v>0.4879</v>
+        <v>0.2985</v>
       </c>
       <c r="M119" s="7" t="n">
-        <v>0.6424</v>
+        <v>0.3487</v>
       </c>
       <c r="N119" s="7" t="n">
-        <v>0.5356000000000001</v>
+        <v>0.6609999999999999</v>
       </c>
       <c r="O119" s="7" t="n">
-        <v>0.2097</v>
+        <v>0.3268</v>
       </c>
       <c r="P119" s="7" t="n">
-        <v>0.2503</v>
+        <v>0.7543000000000001</v>
       </c>
       <c r="Q119" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R119" s="5" t="inlineStr"/>
@@ -7375,57 +7375,57 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ATATP</t>
+          <t>PKART</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>216.1</v>
+        <v>79.3</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>-0.0222</v>
+        <v>-0.061</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>-0.1125</v>
+        <v>-0.1688</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>-0.1996</v>
+        <v>-0.1825</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>0.005600000000000001</v>
+        <v>-0.4642</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>0.4997</v>
+        <v>-0.207</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>0.5774</v>
+        <v>-0.027</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>3.16</v>
+        <v>2.98</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>4.45</v>
+        <v>17.53</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0.3072</v>
+        <v>0.5093</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>0.2985</v>
+        <v>1.5572</v>
       </c>
       <c r="M120" s="4" t="n">
-        <v>0.3487</v>
+        <v>1.6598</v>
       </c>
       <c r="N120" s="4" t="n">
-        <v>0.6609999999999999</v>
+        <v>4.8022</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>0.3268</v>
+        <v>0.083</v>
       </c>
       <c r="P120" s="4" t="n">
-        <v>0.7543000000000001</v>
+        <v>0.2041</v>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr"/>
@@ -7433,57 +7433,57 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>PKART</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="B121" s="6" t="n">
-        <v>84.45</v>
+        <v>356.25</v>
       </c>
       <c r="C121" s="7" t="n">
-        <v>-0.0533</v>
+        <v>-0.0443</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.1498</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-0.1721</v>
+        <v>-0.1725</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>-0.3423</v>
+        <v>-0.141</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>-0.0129</v>
+        <v>-0.3129</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>0.0491</v>
+        <v>0.2966</v>
       </c>
       <c r="I121" s="6" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="J121" s="6" t="n">
-        <v>18.67</v>
+        <v>15.44</v>
       </c>
       <c r="K121" s="7" t="n">
-        <v>0.5093</v>
+        <v>0.1897</v>
       </c>
       <c r="L121" s="7" t="n">
-        <v>1.5572</v>
+        <v>0.4879</v>
       </c>
       <c r="M121" s="7" t="n">
-        <v>1.6598</v>
+        <v>0.6424</v>
       </c>
       <c r="N121" s="7" t="n">
-        <v>4.8022</v>
+        <v>0.5356000000000001</v>
       </c>
       <c r="O121" s="7" t="n">
-        <v>0.083</v>
+        <v>0.2097</v>
       </c>
       <c r="P121" s="7" t="n">
-        <v>0.2041</v>
+        <v>0.2503</v>
       </c>
       <c r="Q121" s="5" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R121" s="5" t="inlineStr"/>
@@ -7491,57 +7491,57 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>KRONT</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>110.5</v>
+        <v>17.05</v>
       </c>
       <c r="C122" s="4" t="n">
-        <v>-0.07690000000000001</v>
+        <v>-0.0318</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>-0.1354</v>
+        <v>-0.1157</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>-0.3915</v>
+        <v>-0.1492</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>-0.3646</v>
+        <v>-0.2429</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>-0.2483</v>
+        <v>-0.207</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>2.1608</v>
+        <v>0.1443</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>3.26</v>
+        <v>3.18</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>12.31</v>
+        <v>22.45</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>1.164</v>
+        <v>0.6388</v>
       </c>
       <c r="L122" s="4" t="n">
-        <v>0.8115000000000001</v>
+        <v>0.5896</v>
       </c>
       <c r="M122" s="4" t="n">
-        <v>1.571</v>
+        <v>1.5604</v>
       </c>
       <c r="N122" s="4" t="n">
-        <v>1.7066</v>
+        <v>5.569299999999999</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>0.1178</v>
+        <v>0.3874</v>
       </c>
       <c r="P122" s="4" t="n">
-        <v>0.3402000000000001</v>
+        <v>13.8834</v>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr"/>
@@ -7549,57 +7549,55 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>KRONT</t>
+          <t>OYAYO</t>
         </is>
       </c>
       <c r="B123" s="6" t="n">
-        <v>17.61</v>
+        <v>28.82</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>-0.0471</v>
+        <v>-0.0393</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>-0.0727</v>
+        <v>-0.0851</v>
       </c>
       <c r="E123" s="7" t="n">
-        <v>-0.1809</v>
+        <v>-0.2788</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>-0.2563</v>
+        <v>-0.3802</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>-0.1542</v>
+        <v>-0.4784</v>
       </c>
       <c r="H123" s="7" t="n">
-        <v>0.2162</v>
+        <v>-0.1728</v>
       </c>
       <c r="I123" s="6" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="J123" s="6" t="n">
-        <v>23.19</v>
-      </c>
+        <v>3.32</v>
+      </c>
+      <c r="J123" s="5" t="inlineStr"/>
       <c r="K123" s="7" t="n">
-        <v>0.6388</v>
+        <v>0.3933</v>
       </c>
       <c r="L123" s="7" t="n">
-        <v>0.5896</v>
+        <v>0.4082</v>
       </c>
       <c r="M123" s="7" t="n">
-        <v>1.5604</v>
+        <v>0.6868000000000001</v>
       </c>
       <c r="N123" s="7" t="n">
-        <v>5.569299999999999</v>
+        <v>0.2959</v>
       </c>
       <c r="O123" s="7" t="n">
-        <v>0.3874</v>
+        <v>0.7368000000000001</v>
       </c>
       <c r="P123" s="7" t="n">
-        <v>13.8834</v>
+        <v>-0.0453</v>
       </c>
       <c r="Q123" s="5" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R123" s="5" t="inlineStr"/>
@@ -7607,55 +7605,57 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>OYAYO</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>30</v>
+        <v>121.5</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>-0.0323</v>
+        <v>0.09949999999999999</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>-0.0323</v>
+        <v>-0.0508</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>-0.2771</v>
+        <v>-0.3215999999999999</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>-0.375</v>
+        <v>-0.3988</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>-0.45</v>
+        <v>-0.1321</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>-0.1525</v>
+        <v>2.4814</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr"/>
+        <v>3.58</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>13.53</v>
+      </c>
       <c r="K124" s="4" t="n">
-        <v>0.3933</v>
+        <v>1.164</v>
       </c>
       <c r="L124" s="4" t="n">
-        <v>0.4082</v>
+        <v>0.8115000000000001</v>
       </c>
       <c r="M124" s="4" t="n">
-        <v>0.6868000000000001</v>
+        <v>1.571</v>
       </c>
       <c r="N124" s="4" t="n">
-        <v>0.2959</v>
+        <v>1.7066</v>
       </c>
       <c r="O124" s="4" t="n">
-        <v>0.7368000000000001</v>
+        <v>0.1178</v>
       </c>
       <c r="P124" s="4" t="n">
-        <v>-0.0453</v>
+        <v>0.3402000000000001</v>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr"/>
@@ -7667,31 +7667,31 @@
         </is>
       </c>
       <c r="B125" s="6" t="n">
-        <v>24.7</v>
+        <v>24.08</v>
       </c>
       <c r="C125" s="7" t="n">
-        <v>-0.06509999999999999</v>
+        <v>-0.0251</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>-0.1121</v>
+        <v>-0.1406</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-0.2395</v>
+        <v>-0.1887</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>-0.4047</v>
+        <v>-0.3803</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>0.1334</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>0.7015</v>
+        <v>0.6736</v>
       </c>
       <c r="I125" s="6" t="n">
-        <v>3.72</v>
+        <v>3.63</v>
       </c>
       <c r="J125" s="6" t="n">
-        <v>9.210000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="K125" s="7" t="n">
         <v>1.4662</v>
@@ -7725,31 +7725,31 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>164.9</v>
+        <v>160.6</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>-0.0999</v>
+        <v>-0.0261</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>-0.1663</v>
+        <v>-0.2242</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>-0.3943</v>
+        <v>-0.3763</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>-0.4719</v>
+        <v>-0.4651</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>-0.1456</v>
+        <v>-0.2579</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>0.7789</v>
+        <v>0.7325</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>3.76</v>
+        <v>3.66</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>16.18</v>
+        <v>15.75</v>
       </c>
       <c r="K126" s="4" t="n">
         <v>0.4338</v>
@@ -7779,57 +7779,57 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>DOCO</t>
-        </is>
-      </c>
-      <c r="B127" s="8" t="n">
-        <v>11100</v>
+          <t>ONCSM</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="n">
+        <v>88.8</v>
       </c>
       <c r="C127" s="7" t="n">
-        <v>0.0142</v>
+        <v>-0.0452</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>0.0457</v>
+        <v>-0.1208</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>0.0128</v>
+        <v>-0.2318</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>0.0119</v>
+        <v>-0.6705</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>0.1687</v>
+        <v>-0.6909000000000001</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>0.0367</v>
+        <v>-0.4443</v>
       </c>
       <c r="I127" s="6" t="n">
-        <v>4.35</v>
+        <v>4.19</v>
       </c>
       <c r="J127" s="6" t="n">
-        <v>20.38</v>
+        <v>29.32</v>
       </c>
       <c r="K127" s="7" t="n">
-        <v>0.2032</v>
+        <v>0.5028</v>
       </c>
       <c r="L127" s="7" t="n">
-        <v>0.2156</v>
+        <v>1.6135</v>
       </c>
       <c r="M127" s="7" t="n">
-        <v>0.2435</v>
+        <v>2.0025</v>
       </c>
       <c r="N127" s="7" t="n">
-        <v>0.2464</v>
+        <v>9.2562</v>
       </c>
       <c r="O127" s="7" t="n">
-        <v>0.1211</v>
+        <v>0.3063</v>
       </c>
       <c r="P127" s="7" t="n">
-        <v>0.2497</v>
+        <v>0.1832</v>
       </c>
       <c r="Q127" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R127" s="5" t="inlineStr"/>
@@ -7837,57 +7837,57 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>ONCSM</t>
+          <t>DOCO</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>93</v>
+        <v>10837.5</v>
       </c>
       <c r="C128" s="4" t="n">
-        <v>-0.0159</v>
+        <v>-0.0236</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.0014</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>-0.3845</v>
+        <v>0.0207</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>-0.6815000000000001</v>
+        <v>-0.0048</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>-0.6684</v>
+        <v>0.1155</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>-0.4609</v>
+        <v>0.0162</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>4.39</v>
+        <v>4.25</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>30.71</v>
+        <v>19.9</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0.5028</v>
+        <v>0.2032</v>
       </c>
       <c r="L128" s="4" t="n">
-        <v>1.6135</v>
+        <v>0.2156</v>
       </c>
       <c r="M128" s="4" t="n">
-        <v>2.0025</v>
+        <v>0.2435</v>
       </c>
       <c r="N128" s="4" t="n">
-        <v>9.2562</v>
+        <v>0.2464</v>
       </c>
       <c r="O128" s="4" t="n">
-        <v>0.3063</v>
+        <v>0.1211</v>
       </c>
       <c r="P128" s="4" t="n">
-        <v>0.1832</v>
+        <v>0.2497</v>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr"/>
@@ -7899,31 +7899,31 @@
         </is>
       </c>
       <c r="B129" s="6" t="n">
-        <v>224</v>
+        <v>212.5</v>
       </c>
       <c r="C129" s="7" t="n">
-        <v>-0.0596</v>
+        <v>-0.0513</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>-0.1618</v>
+        <v>-0.2122</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>-0.2195</v>
+        <v>-0.2524</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>-0.2381</v>
+        <v>-0.2685</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>-0.2202</v>
+        <v>-0.2716</v>
       </c>
       <c r="H129" s="7" t="n">
-        <v>-0.2662</v>
+        <v>-0.3056</v>
       </c>
       <c r="I129" s="6" t="n">
-        <v>4.49</v>
+        <v>4.26</v>
       </c>
       <c r="J129" s="6" t="n">
-        <v>22.66</v>
+        <v>21.5</v>
       </c>
       <c r="K129" s="7" t="n">
         <v>0.2837</v>
@@ -7957,31 +7957,31 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>6.74</v>
+        <v>6.83</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>0.08710000000000001</v>
+        <v>0.0134</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>-0.1359</v>
+        <v>-0.05139999999999999</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>-0.3587</v>
+        <v>-0.4265</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>-0.5144</v>
+        <v>-0.4746</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>0.319</v>
+        <v>0.3996</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>1.0643</v>
+        <v>1.0999</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>4.73</v>
+        <v>4.79</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>57.66</v>
+        <v>58.43</v>
       </c>
       <c r="K130" s="4" t="n">
         <v>0.4591</v>
@@ -8015,31 +8015,31 @@
         </is>
       </c>
       <c r="B131" s="6" t="n">
-        <v>340.25</v>
+        <v>322.25</v>
       </c>
       <c r="C131" s="7" t="n">
-        <v>-0.0306</v>
+        <v>-0.0529</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>-0.032</v>
+        <v>-0.08449999999999999</v>
       </c>
       <c r="E131" s="7" t="n">
-        <v>-0.0999</v>
+        <v>-0.1514</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>-0.0286</v>
+        <v>-0.0935</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>-0.1752</v>
+        <v>-0.1924</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>0.6405</v>
+        <v>0.5797</v>
       </c>
       <c r="I131" s="6" t="n">
-        <v>5.06</v>
+        <v>4.79</v>
       </c>
       <c r="J131" s="6" t="n">
-        <v>41.8</v>
+        <v>39.59</v>
       </c>
       <c r="K131" s="7" t="n">
         <v>0.5623</v>
@@ -8073,28 +8073,28 @@
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>21.54</v>
+        <v>20.6</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>-0.0675</v>
+        <v>-0.0436</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>-0.1244</v>
+        <v>-0.178</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>-0.2988</v>
+        <v>-0.2797</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>-0.3846</v>
+        <v>-0.4032</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>-0.4588</v>
+        <v>-0.4966</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>-0.3331</v>
+        <v>-0.3444</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>6.25</v>
+        <v>5.98</v>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="4" t="n">
@@ -8129,28 +8129,28 @@
         </is>
       </c>
       <c r="B133" s="6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>0.033</v>
+        <v>-0.0213</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>0.0118</v>
+        <v>-0.0366</v>
       </c>
       <c r="E133" s="7" t="n">
-        <v>-0.331</v>
+        <v>-0.3255</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>-0.2358</v>
+        <v>-0.2923</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>0.3116</v>
+        <v>0.262</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>0.7515999999999999</v>
+        <v>0.758</v>
       </c>
       <c r="I133" s="6" t="n">
-        <v>6.79</v>
+        <v>6.65</v>
       </c>
       <c r="J133" s="5" t="inlineStr"/>
       <c r="K133" s="7" t="n">
@@ -8185,28 +8185,28 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>13.13</v>
+        <v>12.42</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>0.0226</v>
+        <v>-0.0541</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>0.2505</v>
+        <v>0.08</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>0.1398</v>
+        <v>0.3185</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>-0.0231</v>
+        <v>-0.05690000000000001</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>0.7522</v>
+        <v>0.5296</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.4364</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>10.66</v>
+        <v>10.08</v>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="4" t="n">
@@ -8241,28 +8241,28 @@
         </is>
       </c>
       <c r="B135" s="8" t="n">
-        <v>1208</v>
+        <v>1150</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>-0.0297</v>
+        <v>-0.048</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>-0.0473</v>
+        <v>-0.136</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>-0.2607</v>
+        <v>-0.2754</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>-0.354</v>
+        <v>-0.3618</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>-0.2206</v>
+        <v>-0.2712</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>-0.3109</v>
+        <v>-0.341</v>
       </c>
       <c r="I135" s="6" t="n">
-        <v>10.73</v>
+        <v>10.21</v>
       </c>
       <c r="J135" s="5" t="inlineStr"/>
       <c r="K135" s="7" t="n">
@@ -8293,55 +8293,57 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>KENT</t>
+          <t>QNBFK</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>255.75</v>
+        <v>35.02</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>-0.0211</v>
+        <v>-0.0596</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>-0.0649</v>
+        <v>-0.2016</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>-0.2008</v>
+        <v>-0.08470000000000001</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>-0.2935</v>
+        <v>-0.3515</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>-0.4141</v>
+        <v>-0.176</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>-0.4962</v>
+        <v>-0.208</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>11.01</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr"/>
+        <v>10.73</v>
+      </c>
+      <c r="J136" s="3" t="n">
+        <v>38.62</v>
+      </c>
       <c r="K136" s="4" t="n">
-        <v>0.2234</v>
+        <v>0.2618</v>
       </c>
       <c r="L136" s="4" t="n">
-        <v>0.3229</v>
+        <v>0.2816</v>
       </c>
       <c r="M136" s="4" t="n">
-        <v>0.5381</v>
+        <v>0.285</v>
       </c>
       <c r="N136" s="4" t="n">
-        <v>0.0256</v>
+        <v>0.2688</v>
       </c>
       <c r="O136" s="4" t="n">
-        <v>0.051</v>
+        <v>0.795</v>
       </c>
       <c r="P136" s="4" t="n">
-        <v>-0.1222</v>
+        <v>0.3111</v>
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R136" s="2" t="inlineStr"/>
@@ -8349,57 +8351,55 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>QNBFK</t>
+          <t>KENT</t>
         </is>
       </c>
       <c r="B137" s="6" t="n">
-        <v>37.24</v>
+        <v>249.5</v>
       </c>
       <c r="C137" s="7" t="n">
-        <v>-0.0174</v>
+        <v>-0.0244</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>-0.1728</v>
+        <v>-0.09269999999999999</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.2215</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>-0.2907</v>
+        <v>-0.2972</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>-0.1275</v>
+        <v>-0.4167</v>
       </c>
       <c r="H137" s="7" t="n">
-        <v>-0.2286</v>
+        <v>-0.5207999999999999</v>
       </c>
       <c r="I137" s="6" t="n">
-        <v>11.41</v>
-      </c>
-      <c r="J137" s="6" t="n">
-        <v>41.07</v>
-      </c>
+        <v>10.74</v>
+      </c>
+      <c r="J137" s="5" t="inlineStr"/>
       <c r="K137" s="7" t="n">
-        <v>0.2618</v>
+        <v>0.2234</v>
       </c>
       <c r="L137" s="7" t="n">
-        <v>0.2816</v>
+        <v>0.3229</v>
       </c>
       <c r="M137" s="7" t="n">
-        <v>0.285</v>
+        <v>0.5381</v>
       </c>
       <c r="N137" s="7" t="n">
-        <v>0.2688</v>
+        <v>0.0256</v>
       </c>
       <c r="O137" s="7" t="n">
-        <v>0.795</v>
+        <v>0.051</v>
       </c>
       <c r="P137" s="7" t="n">
-        <v>0.3111</v>
+        <v>-0.1222</v>
       </c>
       <c r="Q137" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R137" s="5" t="inlineStr"/>
@@ -8411,28 +8411,28 @@
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>39</v>
+        <v>38.1</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>0.0172</v>
+        <v>-0.0231</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>-0.0066</v>
+        <v>-0.0241</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>-0.25</v>
+        <v>-0.2062</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>-0.1638</v>
+        <v>-0.1526</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>-0.0736</v>
+        <v>-0.1051</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>0.2235</v>
+        <v>0.1962</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>14.56</v>
+        <v>14.22</v>
       </c>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="4" t="n">
@@ -8467,31 +8467,31 @@
         </is>
       </c>
       <c r="B139" s="6" t="n">
-        <v>98.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="C139" s="7" t="n">
-        <v>-0.0291</v>
+        <v>-0.0381</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.1241</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>-0.2036</v>
+        <v>-0.2143</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>-0.2492</v>
+        <v>-0.2795</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>-0.3513</v>
+        <v>-0.3776</v>
       </c>
       <c r="H139" s="7" t="n">
-        <v>-0.4054</v>
+        <v>-0.4117</v>
       </c>
       <c r="I139" s="6" t="n">
-        <v>14.96</v>
+        <v>14.39</v>
       </c>
       <c r="J139" s="6" t="n">
-        <v>56.35</v>
+        <v>54.21</v>
       </c>
       <c r="K139" s="7" t="n">
         <v>0.3045</v>
@@ -8525,25 +8525,25 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>71.7</v>
+        <v>68.5</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>-0.044</v>
+        <v>-0.0446</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>-0.1277</v>
+        <v>-0.1752</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>-0.2684</v>
+        <v>-0.1438</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>0.1426</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>0.1426</v>
+        <v>0.0873</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>-0.07719999999999999</v>
+        <v>-0.0352</v>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr"/>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>16.10.2026 18:53</t>
+          <t>19.10.2026 20:40</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_latest.xlsx
+++ b/data/bist_screener_latest.xlsx
@@ -583,28 +583,28 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12.63</v>
+        <v>13.05</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-0.09910000000000001</v>
+        <v>0.0333</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.2313</v>
+        <v>-0.2176</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.4928</v>
+        <v>-0.4759</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-0.427</v>
+        <v>-0.41</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.599</v>
+        <v>-0.5857</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.3533</v>
+        <v>-0.3376</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="n">
@@ -635,57 +635,57 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>SRVGY</t>
+          <t>MERIT</t>
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>2.05</v>
+        <v>13.29</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>-0.0238</v>
+        <v>0.0231</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>-0.0929</v>
+        <v>0.0038</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>-0.0596</v>
+        <v>-0.1032</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>-0.2235</v>
+        <v>-0.2037</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>-0.3731</v>
+        <v>-0.207</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-0.3144</v>
+        <v>-0.3247</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>2.23</v>
+        <v>6.18</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>2.7227</v>
+        <v>0.9854999999999999</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>2.5294</v>
+        <v>1.0319</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>2.9903</v>
+        <v>2.0871</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>0.3421</v>
+        <v>1.5834</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>0.6722</v>
+        <v>0.6354</v>
       </c>
       <c r="P3" s="7" t="n">
-        <v>0.1107</v>
+        <v>0.0454</v>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr"/>
@@ -693,57 +693,57 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MERIT</t>
+          <t>SRVGY</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>12.99</v>
+        <v>2.12</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.0341</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.0449</v>
+        <v>-0.0493</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.1235</v>
+        <v>-0.0275</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.2456</v>
+        <v>-0.1783</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.2249</v>
+        <v>-0.3517</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.3304</v>
+        <v>-0.2765</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>6.04</v>
+        <v>2.31</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.9854999999999999</v>
+        <v>2.7227</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1.0319</v>
+        <v>2.5294</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>2.0871</v>
+        <v>2.9903</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>1.5834</v>
+        <v>0.3421</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.6354</v>
+        <v>0.6722</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.0454</v>
+        <v>0.1107</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr"/>
@@ -751,57 +751,57 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IHEVA</t>
+          <t>HLGYO</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>1.44</v>
+        <v>3.97</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>-0.027</v>
+        <v>0.0232</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-0.1166</v>
+        <v>-0.0457</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-0.2131</v>
+        <v>-0.0364</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>-0.2941</v>
+        <v>-0.2808</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-0.36</v>
+        <v>-0.3225</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>-0.4097999999999999</v>
+        <v>0.1507</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>8.06</v>
+        <v>1.18</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.2518</v>
+        <v>1.7259</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>0.322</v>
+        <v>1.4642</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>0.2038</v>
+        <v>2.8476</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>0.1672</v>
+        <v>2.0883</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>0.078</v>
+        <v>0.1249</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>0.0331</v>
+        <v>0.2374</v>
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R5" s="5" t="inlineStr"/>
@@ -809,57 +809,57 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HLGYO</t>
+          <t>IHEVA</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.88</v>
+        <v>1.54</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.03</v>
+        <v>0.0694</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0605</v>
+        <v>-0.0375</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.0583</v>
+        <v>-0.1585</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3009</v>
+        <v>-0.2376</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3379</v>
+        <v>-0.3156</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0992</v>
+        <v>-0.3583</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.16</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.7259</v>
+        <v>0.2518</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.4642</v>
+        <v>0.322</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.8476</v>
+        <v>0.2038</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2.0883</v>
+        <v>0.1672</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1249</v>
+        <v>0.078</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2374</v>
+        <v>0.0331</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr"/>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>-0.05309999999999999</v>
+        <v>0.0357</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-0.1588</v>
+        <v>-0.0978</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-0.3194</v>
+        <v>-0.2951</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>-0.5013000000000001</v>
+        <v>-0.4795</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-0.5322</v>
+        <v>-0.5155</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>-0.6032</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="7" t="n">
@@ -927,28 +927,28 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>9.17</v>
+        <v>9.23</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.0296</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1509</v>
+        <v>-0.1021</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1446</v>
+        <v>-0.139</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2575</v>
+        <v>-0.2111</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2902</v>
+        <v>-0.2856</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.3728</v>
+        <v>-0.2789</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="n">
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>-0.0412</v>
+        <v>0.0258</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-0.0528</v>
+        <v>-0.0245</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-0.049</v>
+        <v>-0.0245</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>-0.1619</v>
+        <v>-0.1372</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-0.1882</v>
+        <v>-0.1672</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-0.0567</v>
+        <v>-0.03240000000000001</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>5.47</v>
+        <v>5.61</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>0.3848</v>
@@ -1041,31 +1041,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.0415</v>
+        <v>0.0273</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1492</v>
+        <v>-0.1034</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2133</v>
+        <v>-0.1918</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2714</v>
+        <v>-0.2231</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3043</v>
+        <v>-0.2853</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3167</v>
+        <v>-0.287</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.24</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>10.45</v>
+        <v>10.74</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0.3203</v>
@@ -1095,57 +1095,55 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>GSDHO</t>
+          <t>AGYO</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3.99</v>
+        <v>6.25</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>-0.0025</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>-0.0785</v>
+        <v>-0.0727</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-0.0849</v>
+        <v>-0.1667</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>-0.2951</v>
+        <v>-0.2586</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-0.2176</v>
+        <v>-0.2664</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-0.06559999999999999</v>
+        <v>-0.1497</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0.25</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="7" t="n">
-        <v>0.1479</v>
+        <v>0.4383</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.2201</v>
+        <v>0.5475</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.3072</v>
+        <v>0.6032</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>0.5201</v>
+        <v>0.6481999999999999</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>0.6869</v>
+        <v>0.3352000000000001</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>0.0197</v>
+        <v>-0.0354</v>
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr"/>
@@ -1153,55 +1151,57 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AGYO</t>
+          <t>GSDHO</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>6.49</v>
+        <v>4.1</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.0313</v>
+        <v>0.0276</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.0539</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1347</v>
+        <v>-0.0596</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2017</v>
+        <v>-0.2665</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2383</v>
+        <v>-0.1961</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1218</v>
+        <v>-0.0353</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>14.69</v>
+      </c>
       <c r="K12" s="4" t="n">
-        <v>0.4383</v>
+        <v>0.1479</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5475</v>
+        <v>0.2201</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6032</v>
+        <v>0.3072</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.6481999999999999</v>
+        <v>0.5201</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.3352000000000001</v>
+        <v>0.6869</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.0354</v>
+        <v>0.0197</v>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr"/>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>11.5</v>
+        <v>11.47</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.08</v>
+        <v>-0.0026</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>-0.2134</v>
+        <v>-0.1754</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>-0.3723</v>
+        <v>-0.3739</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>-0.4626</v>
+        <v>-0.5047</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-0.5693</v>
+        <v>-0.5704</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.7134999999999999</v>
+        <v>-0.715</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0.29</v>
@@ -1269,25 +1269,25 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>4.93</v>
+        <v>4.94</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.06809999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1918</v>
+        <v>-0.1655</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.0819</v>
+        <v>-0.0801</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2245</v>
+        <v>-0.2143</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3154</v>
+        <v>-0.3141</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4909000000000001</v>
+        <v>-0.4326</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.32</v>
@@ -1325,31 +1325,31 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>-0.0452</v>
+        <v>0.0237</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>-0.0559</v>
+        <v>-0.1561</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-0.1378</v>
+        <v>-0.1173</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>-0.2819</v>
+        <v>-0.2586</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-0.3364</v>
+        <v>-0.3207</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.3185</v>
+        <v>-0.2929</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>7.97</v>
+        <v>8.16</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>0.9460999999999999</v>
@@ -1383,31 +1383,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9.92</v>
+        <v>10.17</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0415</v>
+        <v>0.0252</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1244</v>
+        <v>-0.096</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1935</v>
+        <v>-0.1732</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2652</v>
+        <v>-0.2201</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2919</v>
+        <v>-0.2741</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2238</v>
+        <v>-0.211</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.29</v>
+        <v>5.43</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>0.3789</v>
@@ -1437,57 +1437,55 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>RGYAS</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>179.2</v>
+        <v>1.46</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>-0.0417</v>
+        <v>-0.0135</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>-0.07150000000000001</v>
+        <v>-0.2022</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>-0.0633</v>
+        <v>-0.416</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>-0.1326</v>
+        <v>-0.6117</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>-0.0568</v>
+        <v>-0.6359</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0.2092</v>
+        <v>-0.836</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0.36</v>
       </c>
-      <c r="J17" s="6" t="n">
-        <v>2.98</v>
-      </c>
+      <c r="J17" s="5" t="inlineStr"/>
       <c r="K17" s="7" t="n">
-        <v>0.5672999999999999</v>
+        <v>0.2334</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.5787</v>
+        <v>0.1468</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.5573</v>
+        <v>0.1104</v>
       </c>
       <c r="N17" s="7" t="n">
-        <v>8.1502</v>
+        <v>0.4322</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>0.6512</v>
+        <v>0.1786</v>
       </c>
       <c r="P17" s="7" t="n">
-        <v>0.1467</v>
+        <v>-0.1088</v>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R17" s="5" t="inlineStr"/>
@@ -1495,55 +1493,57 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>RGYAS</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1.48</v>
+        <v>185</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.075</v>
+        <v>0.03240000000000001</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2709</v>
+        <v>-0.0474</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.408</v>
+        <v>-0.0329</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.5647</v>
+        <v>-0.0998</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6309</v>
+        <v>-0.0263</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.8320000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr"/>
+        <v>0.37</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>3.07</v>
+      </c>
       <c r="K18" s="4" t="n">
-        <v>0.2334</v>
+        <v>0.5672999999999999</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1468</v>
+        <v>0.5787</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.1104</v>
+        <v>0.5573</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.4322</v>
+        <v>8.1502</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.1786</v>
+        <v>0.6512</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.1088</v>
+        <v>0.1467</v>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr"/>
@@ -1555,25 +1555,25 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>-0.0761</v>
+        <v>-0.0059</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>-0.1905</v>
+        <v>-0.1421</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>-0.4408</v>
+        <v>-0.4440999999999999</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>-0.6862999999999999</v>
+        <v>-0.6756</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>-0.7409</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-0.5932999999999999</v>
+        <v>-0.5928</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0.39</v>
@@ -1611,31 +1611,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>35.5</v>
+        <v>36.24</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.0183</v>
+        <v>0.0208</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.0697</v>
+        <v>-0.0362</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1116</v>
+        <v>-0.0931</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.2083</v>
+        <v>-0.1615</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2526</v>
+        <v>-0.2371</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.068</v>
+        <v>0.1009</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.92</v>
+        <v>9.1</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>0.2329</v>
@@ -1669,31 +1669,31 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>-0.0352</v>
+        <v>0.0219</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>-0.1092</v>
+        <v>-0.0667</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-0.2473</v>
+        <v>-0.2308</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>-0.3704</v>
+        <v>-0.3427</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-0.4219</v>
+        <v>-0.4093</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-0.2842</v>
+        <v>-0.2624</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>0.9081</v>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>17.3</v>
+        <v>17.65</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.0114</v>
+        <v>0.0202</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.0709</v>
+        <v>-0.05110000000000001</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1675</v>
+        <v>-0.1506</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.2042</v>
+        <v>-0.1457</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1946</v>
+        <v>-0.1783</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.0431</v>
+        <v>0.0091</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>6.99</v>
+        <v>7.13</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>0.1285</v>
@@ -1785,31 +1785,31 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>9.69</v>
+        <v>9.9</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>-0.0142</v>
+        <v>0.0217</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>-0.1036</v>
+        <v>-0.0722</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>-0.1871</v>
+        <v>-0.1695</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>-0.3654</v>
+        <v>-0.3465</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-0.4479</v>
+        <v>-0.4359</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-0.2763</v>
+        <v>-0.2302</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>3.65</v>
+        <v>3.72</v>
       </c>
       <c r="K23" s="7" t="n">
         <v>0.4985</v>
@@ -1843,31 +1843,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>5.33</v>
+        <v>5.53</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.0633</v>
+        <v>0.0375</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.1526</v>
+        <v>-0.1037</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2021</v>
+        <v>-0.1722</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.433</v>
+        <v>-0.4172999999999999</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.4051</v>
+        <v>-0.3828</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2577</v>
+        <v>-0.2211</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>6.4</v>
+        <v>6.64</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>0.6883</v>
@@ -1901,28 +1901,28 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>99</v>
+        <v>103.2</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>-0.0472</v>
+        <v>0.0424</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>-0.1502</v>
+        <v>-0.121</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-0.2867</v>
+        <v>-0.2565</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>-0.4111</v>
+        <v>-0.3772</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>-0.5101</v>
+        <v>-0.4894</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-0.4479</v>
+        <v>-0.4267</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="7" t="n">
@@ -1953,55 +1953,57 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>KORDS</t>
+          <t>OYYAT</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2.59</v>
+        <v>24.88</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.0478</v>
+        <v>-0.0103</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.1508</v>
+        <v>-0.0703</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2292</v>
+        <v>-0.1707</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3719</v>
+        <v>-0.3394</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2441</v>
+        <v>-0.5635</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.0794</v>
+        <v>-0.5341</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
+        <v>0.57</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>3.19</v>
+      </c>
       <c r="K26" s="4" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.045</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.3224</v>
+        <v>0.4061999999999999</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.613</v>
+        <v>0.4311</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.7171999999999999</v>
+        <v>3.0744</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.2671</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.09820000000000001</v>
+        <v>0.2126</v>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr"/>
@@ -2009,53 +2011,53 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>KRSTL</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>6.5</v>
+        <v>31.12</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>-0.0593</v>
+        <v>0.0271</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>-0.1569</v>
+        <v>-0.08689999999999999</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-0.1885</v>
+        <v>-0.1073</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>-0.3981</v>
+        <v>-0.1119</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>-0.3078</v>
+        <v>-0.0281</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>-0.3815</v>
+        <v>0.2478</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>3.74</v>
+        <v>17.01</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.3806</v>
+        <v>0.3105</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.2571</v>
+        <v>0.3107</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.5529999999999999</v>
+        <v>0.4787</v>
       </c>
       <c r="N27" s="7" t="n">
-        <v>0.6774</v>
+        <v>1.4985</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>0.1192</v>
+        <v>0.0693</v>
       </c>
       <c r="P27" s="7" t="n">
-        <v>0.1788</v>
+        <v>-0.0718</v>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
@@ -2067,53 +2069,53 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>KRSTL</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>30.3</v>
+        <v>6.72</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.0147</v>
+        <v>0.0338</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.079</v>
+        <v>-0.1227</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1308</v>
+        <v>-0.161</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.1387</v>
+        <v>-0.3606</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.0537</v>
+        <v>-0.2843</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.2307</v>
+        <v>-0.3463000000000001</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>16.57</v>
+        <v>3.87</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.3105</v>
+        <v>0.3806</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.3107</v>
+        <v>0.2571</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.4787</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.4985</v>
+        <v>0.6774</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.0693</v>
+        <v>0.1192</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.0718</v>
+        <v>0.1788</v>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
@@ -2125,53 +2127,53 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>OYYAT</t>
+          <t>SEKFK</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>25.14</v>
+        <v>3.6</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0345</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>-0.0891</v>
+        <v>-0.1408</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-0.162</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>-0.36</v>
+        <v>-0.3231</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>-0.5589</v>
+        <v>-0.4066</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>-0.5336</v>
+        <v>-0.167</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>3.22</v>
+        <v>2.92</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.045</v>
+        <v>0.208</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.4061999999999999</v>
+        <v>0.0571</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.4311</v>
+        <v>0.0025</v>
       </c>
       <c r="N29" s="7" t="n">
-        <v>3.0744</v>
+        <v>0.2707</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>0.2671</v>
+        <v>0.6072</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>0.2126</v>
+        <v>0.2346</v>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
@@ -2183,57 +2185,55 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>SEKFK</t>
+          <t>BAKAB</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>3.48</v>
+        <v>27.5</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.0984</v>
+        <v>0.0277</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1869</v>
+        <v>-0.0864</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1234</v>
+        <v>-0.2125</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3615</v>
+        <v>-0.4712</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.4264</v>
+        <v>-0.373</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.1989</v>
+        <v>-0.26</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>2.82</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="4" t="n">
-        <v>0.208</v>
+        <v>0.3479</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.0571</v>
+        <v>0.5443</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.0025</v>
+        <v>0.7171</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.2707</v>
+        <v>0.97</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.6072</v>
+        <v>0.0552</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2346</v>
+        <v>-0.0031</v>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr"/>
@@ -2241,51 +2241,51 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>BAKAB</t>
+          <t>KORDS</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>26.76</v>
+        <v>2.84</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>-0.0304</v>
+        <v>0.0965</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>-0.139</v>
+        <v>-0.0565</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-0.2337</v>
+        <v>-0.1548</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>-0.4819</v>
+        <v>-0.2639</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>-0.3899</v>
+        <v>-0.1712</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>-0.2648</v>
+        <v>-0.0163</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="7" t="n">
-        <v>0.3479</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.5443</v>
+        <v>0.3224</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.7171</v>
+        <v>0.613</v>
       </c>
       <c r="N31" s="7" t="n">
-        <v>0.97</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>0.0552</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="P31" s="7" t="n">
-        <v>-0.0031</v>
+        <v>-0.09820000000000001</v>
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
@@ -2301,28 +2301,28 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>14.2</v>
+        <v>14.15</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.0314</v>
+        <v>-0.0035</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1041</v>
+        <v>-0.0794</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3315</v>
+        <v>-0.3338</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3973</v>
+        <v>-0.3885</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4147</v>
+        <v>-0.4167</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3926</v>
+        <v>-0.3848</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="4" t="n">
@@ -2357,31 +2357,31 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>5.16</v>
+        <v>5.21</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>-0.07530000000000001</v>
+        <v>0.0097</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>-0.1224</v>
+        <v>-0.1002</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-0.0246</v>
+        <v>-0.0151</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>-0.2412</v>
+        <v>-0.2304</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>-0.3958</v>
+        <v>-0.3899</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>-0.3493</v>
+        <v>-0.3303</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K33" s="7" t="n">
         <v>0.4159</v>
@@ -2411,57 +2411,55 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>AKMGY</t>
+          <t>SOKE</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>186.2</v>
+        <v>7.72</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.0534</v>
+        <v>0.0158</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1238</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2203</v>
+        <v>-0.1717</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2552</v>
+        <v>-0.5774</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3179</v>
+        <v>-0.5907</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1772</v>
+        <v>-0.2975</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>9.17</v>
-      </c>
+        <v>0.63</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="4" t="n">
-        <v>0.3886</v>
+        <v>0.5234000000000001</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.3887</v>
+        <v>0.4561</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.3141</v>
+        <v>0.4897</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.5958</v>
+        <v>0.3644</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.6443000000000001</v>
+        <v>0.032</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.0781</v>
+        <v>-0.0429</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr"/>
@@ -2469,55 +2467,57 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>SOKE</t>
+          <t>AKMGY</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>7.6</v>
+        <v>189.8</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>-0.0052</v>
+        <v>0.0193</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>-0.06059999999999999</v>
+        <v>-0.0983</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-0.1845</v>
+        <v>-0.2052</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>-0.5968</v>
+        <v>-0.231</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>-0.597</v>
+        <v>-0.3048</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>-0.3232</v>
+        <v>-0.1605</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="J35" s="5" t="inlineStr"/>
+        <v>0.64</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>9.35</v>
+      </c>
       <c r="K35" s="7" t="n">
-        <v>0.5234000000000001</v>
+        <v>0.3886</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.4561</v>
+        <v>0.3887</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.4897</v>
+        <v>0.3141</v>
       </c>
       <c r="N35" s="7" t="n">
-        <v>0.3644</v>
+        <v>0.5958</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>0.032</v>
+        <v>0.6443000000000001</v>
       </c>
       <c r="P35" s="7" t="n">
-        <v>-0.0429</v>
+        <v>0.0781</v>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R35" s="5" t="inlineStr"/>
@@ -2529,31 +2529,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>5.09</v>
+        <v>5.16</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.0138</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>-0.0911</v>
+        <v>-0.0703</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>-0.1387</v>
+        <v>-0.1269</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>-0.3815</v>
+        <v>-0.4069</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.3716</v>
+        <v>-0.363</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.4449</v>
+        <v>-0.4481</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>8.73</v>
+        <v>8.85</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>1.6512</v>
@@ -2587,31 +2587,31 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>29.88</v>
+        <v>30.24</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>-0.021</v>
+        <v>0.012</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>-0.1278</v>
+        <v>-0.0814</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-0.2019</v>
+        <v>-0.1923</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>-0.3723</v>
+        <v>-0.3538</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>-0.3712</v>
+        <v>-0.3636</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>-0.2087</v>
+        <v>-0.2008</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0.64</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>8.42</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="K37" s="7" t="n">
         <v>0.306</v>
@@ -2641,57 +2641,57 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>BNTAS</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>4.79</v>
+        <v>3.48</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>-0.0534</v>
+        <v>-0.0984</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>-0.108</v>
+        <v>-0.4051</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>-0.1741</v>
+        <v>-0.9002</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-0.2324</v>
+        <v>-0.9162</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.2997</v>
+        <v>-0.8634000000000001</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.2574</v>
+        <v>-0.8906999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>4.43</v>
+        <v>2.21</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.2654</v>
+        <v>7.8666</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.07690000000000001</v>
+        <v>3.1929</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.464</v>
+        <v>4.946499999999999</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.3679</v>
+        <v>1.0979</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0.1363</v>
+        <v>0.4854</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0.1657</v>
+        <v>0.586</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr"/>
@@ -2699,57 +2699,57 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>MERCN</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>202.9</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>-0.0054</v>
+        <v>-0.0399</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>-0.0241</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-0.06280000000000001</v>
+        <v>-0.3831</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.0095</v>
+        <v>-0.5978</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>-0.0193</v>
+        <v>-0.5625</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>0.3065</v>
+        <v>-0.7341</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>14.46</v>
+        <v>11.34</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.3261</v>
+        <v>0.2374</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>0.5440999999999999</v>
+        <v>0.8593999999999999</v>
       </c>
       <c r="M39" s="7" t="n">
-        <v>0.9423</v>
+        <v>1.4059</v>
       </c>
       <c r="N39" s="7" t="n">
-        <v>5.083299999999999</v>
+        <v>1.3031</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>0.0646</v>
+        <v>0.1784</v>
       </c>
       <c r="P39" s="7" t="n">
-        <v>0.0771</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R39" s="5" t="inlineStr"/>
@@ -2757,57 +2757,57 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TTKOM</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>50.05</v>
+        <v>208.4</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>-0.0167</v>
+        <v>0.0271</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>-0.04480000000000001</v>
+        <v>0.0053</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>-0.0476</v>
+        <v>-0.0374</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>-0.156</v>
+        <v>0.0332</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-0.23</v>
+        <v>0.0072</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.003</v>
+        <v>0.3585</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>6.19</v>
+        <v>14.85</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.4498</v>
+        <v>0.3261</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.4329</v>
+        <v>0.5440999999999999</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.5323</v>
+        <v>0.9423</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.8047</v>
+        <v>5.083299999999999</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.4117</v>
+        <v>0.0646</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>1.3041</v>
+        <v>0.0771</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr"/>
@@ -2815,57 +2815,57 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>BNTAS</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>96.2</v>
+        <v>5.02</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>-0.0062</v>
+        <v>0.048</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>-0.0248</v>
+        <v>-0.051</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-0.0224</v>
+        <v>-0.1345</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>-0.127</v>
+        <v>-0.1851</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>-0.1714</v>
+        <v>-0.2661</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>0.004699999999999999</v>
+        <v>-0.2168</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>10.8</v>
+        <v>4.65</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.3971</v>
+        <v>0.2654</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>0.4118</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="M41" s="7" t="n">
-        <v>0.3975</v>
+        <v>0.464</v>
       </c>
       <c r="N41" s="7" t="n">
-        <v>0.2377</v>
+        <v>0.3679</v>
       </c>
       <c r="O41" s="7" t="n">
-        <v>0.4333</v>
+        <v>0.1363</v>
       </c>
       <c r="P41" s="7" t="n">
-        <v>0.1518</v>
+        <v>0.1657</v>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R41" s="5" t="inlineStr"/>
@@ -2873,57 +2873,57 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>MERCN</t>
+          <t>TTKOM</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>10.28</v>
+        <v>51.2</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.09949999999999999</v>
+        <v>0.023</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>-0.0764</v>
+        <v>-0.0154</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-0.3575</v>
+        <v>-0.0257</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-0.6006</v>
+        <v>-0.13</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-0.5443</v>
+        <v>-0.2123</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-0.6948000000000001</v>
+        <v>0.064</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>11.81</v>
+        <v>6.33</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0.2374</v>
+        <v>0.4498</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.8593999999999999</v>
+        <v>0.4329</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>1.4059</v>
+        <v>0.5323</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>1.3031</v>
+        <v>0.8047</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>0.1784</v>
+        <v>0.4117</v>
       </c>
       <c r="P42" s="4" t="n">
-        <v>0.07049999999999999</v>
+        <v>1.3041</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr"/>
@@ -2931,57 +2931,57 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>PINSU</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>7.51</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>-0.0482</v>
+        <v>0.0151</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>-0.159</v>
+        <v>0.0021</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-0.189</v>
+        <v>-0.0076</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>-0.4201</v>
+        <v>-0.1281</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>-0.3968</v>
+        <v>-0.1589</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>-0.4636</v>
+        <v>0.0355</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>15.83</v>
+        <v>10.97</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.2802</v>
+        <v>0.3971</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>0.2234</v>
+        <v>0.4118</v>
       </c>
       <c r="M43" s="7" t="n">
-        <v>0.3074</v>
+        <v>0.3975</v>
       </c>
       <c r="N43" s="7" t="n">
-        <v>91.6451</v>
+        <v>0.2377</v>
       </c>
       <c r="O43" s="7" t="n">
-        <v>0.1329</v>
+        <v>0.4333</v>
       </c>
       <c r="P43" s="7" t="n">
-        <v>0.0528</v>
+        <v>0.1518</v>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R43" s="5" t="inlineStr"/>
@@ -2989,57 +2989,57 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>AYGAZ</t>
+          <t>PINSU</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>267.5</v>
+        <v>7.6</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>-0.0352</v>
+        <v>0.012</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>-0.0776</v>
+        <v>-0.1264</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>-0.1562</v>
+        <v>-0.1793</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>-0.0325</v>
+        <v>-0.3504</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>0.0075</v>
+        <v>-0.3896</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.4944</v>
+        <v>-0.4847</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>7.03</v>
+        <v>16.02</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0.1662</v>
+        <v>0.2802</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.3683</v>
+        <v>0.2234</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.4549</v>
+        <v>0.3074</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>1.9624</v>
+        <v>91.6451</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>0.0302</v>
+        <v>0.1329</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>0.118</v>
+        <v>0.0528</v>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr"/>
@@ -3047,57 +3047,57 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>AYGAZ</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>3.86</v>
+        <v>272.75</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>-0.09810000000000001</v>
+        <v>0.0196</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>-0.4061999999999999</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-0.8893000000000001</v>
+        <v>-0.1396</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>-0.9061</v>
+        <v>-0.0136</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>-0.8484999999999999</v>
+        <v>0.0273</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>-0.8794</v>
+        <v>0.5254</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>2.45</v>
+        <v>7.17</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>7.8666</v>
+        <v>0.1662</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>3.1929</v>
+        <v>0.3683</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>4.946499999999999</v>
+        <v>0.4549</v>
       </c>
       <c r="N45" s="7" t="n">
-        <v>1.0979</v>
+        <v>1.9624</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>0.4854</v>
+        <v>0.0302</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>0.586</v>
+        <v>0.118</v>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R45" s="5" t="inlineStr"/>
@@ -3105,57 +3105,57 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>BASGZ</t>
+          <t>GRTHO</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>38.1</v>
+        <v>58.45</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>-0.0251</v>
+        <v>-0.09939999999999999</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>-0.0565</v>
+        <v>-0.4087</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>-0.0993</v>
+        <v>-0.6363</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-0.1803</v>
+        <v>-0.752</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-0.2365</v>
+        <v>-0.7598999999999999</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>-0.0475</v>
+        <v>-0.912</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>6.9</v>
+        <v>4.07</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0.3163</v>
+        <v>0.5085000000000001</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.5275</v>
+        <v>0.4487</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.4513</v>
+        <v>0.2298</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.3789</v>
+        <v>0.9399</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0.1301</v>
+        <v>0.1089</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>-0.245</v>
+        <v>0.2287</v>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr"/>
@@ -3163,57 +3163,57 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>BASGZ</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>35.62</v>
+        <v>38.2</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>-0.0177</v>
+        <v>0.0026</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>-0.0517</v>
+        <v>-0.0521</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-0.016</v>
+        <v>-0.0969</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>-0.1893</v>
+        <v>-0.1667</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>0.0476</v>
+        <v>-0.2345</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>0.3193</v>
+        <v>-0.0185</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0.75</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>31.05</v>
+        <v>6.92</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.1998</v>
+        <v>0.3163</v>
       </c>
       <c r="L47" s="7" t="n">
-        <v>0.3838</v>
+        <v>0.5275</v>
       </c>
       <c r="M47" s="7" t="n">
-        <v>0.4877</v>
+        <v>0.4513</v>
       </c>
       <c r="N47" s="7" t="n">
-        <v>0.4752</v>
+        <v>0.3789</v>
       </c>
       <c r="O47" s="7" t="n">
-        <v>0.104</v>
+        <v>0.1301</v>
       </c>
       <c r="P47" s="7" t="n">
-        <v>0.0274</v>
+        <v>-0.245</v>
       </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R47" s="5" t="inlineStr"/>
@@ -3225,28 +3225,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>15.11</v>
+        <v>15.13</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>-0.0437</v>
+        <v>0.0013</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>-0.09789999999999999</v>
+        <v>-0.0946</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>-0.1854</v>
+        <v>-0.1844</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-0.2314</v>
+        <v>-0.2292</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-0.2756</v>
+        <v>-0.2747</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>-0.0837</v>
+        <v>-0.0956</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>2.57</v>
@@ -3279,55 +3279,57 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>AYES</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>6.74</v>
+        <v>37.18</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>-0.0573</v>
+        <v>0.0438</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>-0.1013</v>
+        <v>-0.0164</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>-0.1085</v>
+        <v>0.0271</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>-0.2975</v>
+        <v>-0.1252</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>-0.2913</v>
+        <v>0.0935</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0.4024</v>
+        <v>0.403</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>1.85</v>
+        <v>32.41</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.4183</v>
+        <v>0.1998</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>0.314</v>
+        <v>0.3838</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0.8128</v>
+        <v>0.4877</v>
       </c>
       <c r="N49" s="7" t="n">
-        <v>42.7724</v>
+        <v>0.4752</v>
       </c>
       <c r="O49" s="7" t="n">
-        <v>0.0208</v>
-      </c>
-      <c r="P49" s="5" t="inlineStr"/>
+        <v>0.104</v>
+      </c>
+      <c r="P49" s="7" t="n">
+        <v>0.0274</v>
+      </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R49" s="5" t="inlineStr"/>
@@ -3335,57 +3337,55 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GRTHO</t>
+          <t>AYES</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>64.90000000000001</v>
+        <v>6.83</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>-0.0999</v>
+        <v>0.0134</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.4758</v>
+        <v>-0.1013</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>-0.5961</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>-0.7284999999999999</v>
+        <v>-0.2777</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.2818</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>-0.9046</v>
+        <v>0.4337</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>4.52</v>
+        <v>1.88</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0.5085000000000001</v>
+        <v>0.4183</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.4487</v>
+        <v>0.314</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.2298</v>
+        <v>0.8128</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.9399</v>
+        <v>42.7724</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>0.1089</v>
-      </c>
-      <c r="P50" s="4" t="n">
-        <v>0.2287</v>
-      </c>
+        <v>0.0208</v>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr"/>
@@ -3393,57 +3393,57 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>DESA</t>
+          <t>KARSN</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>7.95</v>
+        <v>7.66</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>-0.0352</v>
+        <v>0.02</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>-0.08199999999999999</v>
+        <v>-0.1345</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-0.1215</v>
+        <v>-0.2263</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>-0.2356</v>
+        <v>-0.2901</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>-0.4338</v>
+        <v>-0.3397</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>-0.4664</v>
+        <v>-0.2184</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>7.53</v>
+        <v>28.51</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.2088</v>
+        <v>0.8458</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>0.2301</v>
+        <v>1.2698</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>0.0037</v>
+        <v>1.2002</v>
       </c>
       <c r="N51" s="7" t="n">
-        <v>0.3571</v>
+        <v>2.1122</v>
       </c>
       <c r="O51" s="7" t="n">
-        <v>0.2399</v>
+        <v>0.1667</v>
       </c>
       <c r="P51" s="7" t="n">
-        <v>0.1277</v>
+        <v>0.07339999999999999</v>
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R51" s="5" t="inlineStr"/>
@@ -3451,57 +3451,57 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>KARSN</t>
+          <t>DESA</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>7.51</v>
+        <v>8.23</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>-0.0565</v>
+        <v>0.0352</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.1792</v>
+        <v>-0.026</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>-0.2414</v>
+        <v>-0.0906</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>-0.3142</v>
+        <v>-0.2048</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.3526</v>
+        <v>-0.4138</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>-0.2226</v>
+        <v>-0.451</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>27.95</v>
+        <v>7.8</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0.8458</v>
+        <v>0.2088</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>1.2698</v>
+        <v>0.2301</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>1.2002</v>
+        <v>0.0037</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>2.1122</v>
+        <v>0.3571</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>0.1667</v>
+        <v>0.2399</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>0.07339999999999999</v>
+        <v>0.1277</v>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr"/>
@@ -3509,57 +3509,57 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>EGGUB</t>
+          <t>RALYH</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>86.75</v>
+        <v>21.78</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>-0.05400000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>-0.113</v>
+        <v>-0.4088000000000001</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-0.1528</v>
+        <v>-0.9009999999999999</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>-0.1351</v>
+        <v>-0.9103</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>-0.2941</v>
+        <v>-0.9329999999999999</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>-0.1428</v>
+        <v>-0.8756</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>12.14</v>
+        <v>2.82</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>0.4926</v>
+        <v>0.7070000000000001</v>
       </c>
       <c r="L53" s="7" t="n">
-        <v>0.6905</v>
+        <v>1.4848</v>
       </c>
       <c r="M53" s="7" t="n">
-        <v>0.7726999999999999</v>
+        <v>1.5369</v>
       </c>
       <c r="N53" s="7" t="n">
-        <v>0.5777</v>
+        <v>0.5434</v>
       </c>
       <c r="O53" s="7" t="n">
-        <v>0.4324</v>
+        <v>0.2854</v>
       </c>
       <c r="P53" s="7" t="n">
-        <v>0.0886</v>
+        <v>0.3914</v>
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R53" s="5" t="inlineStr"/>
@@ -3567,57 +3567,57 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>RALYH</t>
+          <t>ARASE</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>21.78</v>
+        <v>85</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.0064</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>-0.4088000000000001</v>
+        <v>-0.1118</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>-0.9009999999999999</v>
+        <v>-0.2444</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>-0.9103</v>
+        <v>-0.32</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-0.9329999999999999</v>
+        <v>-0.15</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>-0.8756</v>
+        <v>0.6634</v>
       </c>
       <c r="I54" s="3" t="n">
         <v>0.86</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>2.82</v>
+        <v>7.75</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0.7070000000000001</v>
+        <v>0.1264</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>1.4848</v>
+        <v>0.596</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>1.5369</v>
+        <v>0.7123999999999999</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.5434</v>
+        <v>4.0303</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>0.2854</v>
+        <v>0.25</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>0.3914</v>
+        <v>0.1463</v>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr"/>
@@ -3625,57 +3625,57 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>EGGUB</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>451.75</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>-0.0011</v>
+        <v>0.019</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>-0.1046</v>
+        <v>-0.0443</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-0.1346</v>
+        <v>-0.1367</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>-0.3066</v>
+        <v>-0.1299</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>-0.3212</v>
+        <v>-0.2807</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>0.0403</v>
+        <v>-0.1291</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>0.87</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>13.53</v>
+        <v>12.37</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>0.3804</v>
+        <v>0.4926</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>0.3113</v>
+        <v>0.6905</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>1.725</v>
+        <v>0.7726999999999999</v>
       </c>
       <c r="N55" s="7" t="n">
-        <v>0.0848</v>
+        <v>0.5777</v>
       </c>
       <c r="O55" s="7" t="n">
-        <v>0.0184</v>
+        <v>0.4324</v>
       </c>
       <c r="P55" s="7" t="n">
-        <v>0.1216</v>
+        <v>0.0886</v>
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R55" s="5" t="inlineStr"/>
@@ -3683,57 +3683,57 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ARASE</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>85.55</v>
+        <v>465.25</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.062</v>
+        <v>0.0299</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.1367</v>
+        <v>-0.0723</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>-0.2396</v>
+        <v>-0.1087</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>-0.3117</v>
+        <v>-0.269</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.1445</v>
+        <v>-0.3009</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.0858</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>7.8</v>
+        <v>13.94</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0.1264</v>
+        <v>0.3804</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.596</v>
+        <v>0.3113</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.7123999999999999</v>
+        <v>1.725</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>4.0303</v>
+        <v>0.0848</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>0.25</v>
+        <v>0.0184</v>
       </c>
       <c r="P56" s="4" t="n">
-        <v>0.1463</v>
+        <v>0.1216</v>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr"/>
@@ -3745,31 +3745,31 @@
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>33.08</v>
+        <v>33.46</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>-0.0645</v>
+        <v>0.0115</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>-0.2116</v>
+        <v>-0.1718</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-0.2353</v>
+        <v>-0.2265</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>-0.6277</v>
+        <v>-0.6185</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>-0.3045</v>
+        <v>-0.2965</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>-0.2311</v>
+        <v>-0.2153</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>8.890000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="K57" s="7" t="n">
         <v>0.2641</v>
@@ -3803,31 +3803,31 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>18.07</v>
+        <v>18.01</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>-0.009899999999999999</v>
+        <v>-0.0033</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>-0.0608</v>
+        <v>-0.0526</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>-0.079</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>-0.0028</v>
+        <v>-0.04099999999999999</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-0.1933</v>
+        <v>-0.196</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>-0.1926</v>
+        <v>-0.1851</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>13.68</v>
+        <v>13.63</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>2.3363</v>
@@ -3857,57 +3857,57 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>CIMSA</t>
+          <t>TNZTP</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>38.42</v>
+        <v>23.3</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>0.001</v>
+        <v>0.0052</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>-0.0697</v>
+        <v>-0.092</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0805</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>-0.2324</v>
+        <v>-0.0574</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>-0.3248</v>
+        <v>-0.0635</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>-0.1007</v>
+        <v>0.1289</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>9.1</v>
+        <v>17.24</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>0.3754999999999999</v>
+        <v>0.4327</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>0.3037</v>
+        <v>0.4143</v>
       </c>
       <c r="M59" s="7" t="n">
-        <v>0.4933</v>
+        <v>0.5201</v>
       </c>
       <c r="N59" s="7" t="n">
-        <v>1.15</v>
+        <v>0.0702</v>
       </c>
       <c r="O59" s="7" t="n">
-        <v>0.1807</v>
+        <v>0.3617</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>0.2729</v>
+        <v>0.0551</v>
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Sağlık hizmetleri</t>
         </is>
       </c>
       <c r="R59" s="5" t="inlineStr"/>
@@ -3915,57 +3915,57 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>TNZTP</t>
+          <t>SELEC</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>23.18</v>
+        <v>59.05</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0998</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>-0.0539</v>
+        <v>-0.2619</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>-0.0852</v>
+        <v>-0.7226</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>-0.0461</v>
+        <v>-0.7509</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-0.0683</v>
+        <v>-0.3365</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>0.1091</v>
+        <v>-0.223</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>17.15</v>
+        <v>18</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0.4327</v>
+        <v>0.3781</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.4143</v>
+        <v>0.6063000000000001</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.5201</v>
+        <v>1.4267</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.0702</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>0.3617</v>
+        <v>0.0158</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>0.0551</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>Sağlık hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr"/>
@@ -3977,31 +3977,31 @@
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>16</v>
+        <v>16.25</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>-0.0123</v>
+        <v>0.0156</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>-0.1605</v>
+        <v>-0.113</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>-0.3443</v>
+        <v>-0.334</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>-0.6008</v>
+        <v>-0.6013000000000001</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>-0.5397</v>
+        <v>-0.5325</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>-0.2763</v>
+        <v>-0.2729</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>5.95</v>
+        <v>6.04</v>
       </c>
       <c r="K61" s="7" t="n">
         <v>0.5809000000000001</v>
@@ -4031,57 +4031,57 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>INDES</t>
+          <t>CIMSA</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>11.42</v>
+        <v>40.26</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>-0.0095</v>
+        <v>0.0479</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>-0.0223</v>
+        <v>0.0005</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0.0613</v>
+        <v>-0.0437</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.2051</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>0.1594</v>
+        <v>-0.2924</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>0.4831</v>
+        <v>-0.0423</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>9.630000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0.6297</v>
+        <v>0.3754999999999999</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.8554999999999999</v>
+        <v>0.3037</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>1.0205</v>
+        <v>0.4933</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1.9437</v>
+        <v>1.15</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>0.0374</v>
+        <v>0.1807</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>0.137</v>
+        <v>0.2729</v>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr"/>
@@ -4093,31 +4093,31 @@
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>216.8</v>
+        <v>219.1</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>0.0042</v>
+        <v>0.0106</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>-0.0833</v>
+        <v>-0.0219</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-0.091</v>
+        <v>-0.08130000000000001</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>-0.2626</v>
+        <v>-0.2471</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>-0.339</v>
+        <v>-0.332</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>-0.3815</v>
+        <v>-0.3713</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>21.4</v>
+        <v>21.62</v>
       </c>
       <c r="K63" s="7" t="n">
         <v>0.0934</v>
@@ -4147,57 +4147,57 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ISDMR</t>
+          <t>MOBTL</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>55.7</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.0503</v>
+        <v>-0.0042</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.1541</v>
+        <v>-0.0931</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>-0.1038</v>
+        <v>-0.2062</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>-0.0397</v>
+        <v>-0.3409</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>0.2269</v>
+        <v>-0.2862</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>0.5095000000000001</v>
+        <v>0.3921</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>1.04</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>13.13</v>
+        <v>13.53</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0.1859</v>
+        <v>0.5631</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.3543</v>
+        <v>0.4406</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.4035</v>
+        <v>0.5064</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.208</v>
+        <v>1.6818</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>0.1056</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>0.0859</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr"/>
@@ -4205,53 +4205,53 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>MOBTL</t>
+          <t>INDES</t>
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>9.59</v>
+        <v>11.92</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>-0.0505</v>
+        <v>0.0438</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>-0.0953</v>
+        <v>0.0329</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>-0.2028</v>
+        <v>0.1078</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>-0.3368</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>-0.2833</v>
+        <v>0.2102</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>0.3858</v>
+        <v>0.5501</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>13.59</v>
+        <v>10.05</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>0.5631</v>
+        <v>0.6297</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>0.4406</v>
+        <v>0.8554999999999999</v>
       </c>
       <c r="M65" s="7" t="n">
-        <v>0.5064</v>
+        <v>1.0205</v>
       </c>
       <c r="N65" s="7" t="n">
-        <v>1.6818</v>
+        <v>1.9437</v>
       </c>
       <c r="O65" s="7" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.0374</v>
       </c>
       <c r="P65" s="7" t="n">
-        <v>0.08689999999999999</v>
+        <v>0.137</v>
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
@@ -4263,57 +4263,55 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>BYDNR</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>9.85</v>
+        <v>21.4</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.012</v>
+        <v>0.0142</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0581</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>-0.1086</v>
+        <v>-0.1508</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>-0.2213</v>
+        <v>-0.4569</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.449</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>-0.1667</v>
+        <v>0.0542</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>6.61</v>
-      </c>
+        <v>1.06</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="4" t="n">
-        <v>0.423</v>
+        <v>0.2762</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.5552</v>
+        <v>0.0636</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.8170999999999999</v>
+        <v>0.127</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>10.0728</v>
+        <v>0.7182999999999999</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>0.179</v>
+        <v>0.1081</v>
       </c>
       <c r="P66" s="4" t="n">
-        <v>0.2236</v>
+        <v>-0.0257</v>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr"/>
@@ -4321,51 +4319,53 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>BYDNR</t>
+          <t>MAALT</t>
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>21.1</v>
+        <v>716.5</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>0</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>-0.1388</v>
+        <v>-0.1219</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>-0.1627</v>
+        <v>-0.2726</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>-0.4628</v>
+        <v>-0.3322</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>-0.4567</v>
+        <v>-0.47</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>0.0243</v>
+        <v>-0.2871</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="J67" s="5" t="inlineStr"/>
+        <v>1.08</v>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>1543.85</v>
+      </c>
       <c r="K67" s="7" t="n">
-        <v>0.2762</v>
+        <v>0.248</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>0.0636</v>
+        <v>3.5256</v>
       </c>
       <c r="M67" s="7" t="n">
-        <v>0.127</v>
+        <v>0.3863</v>
       </c>
       <c r="N67" s="7" t="n">
-        <v>0.7182999999999999</v>
+        <v>0.9832</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>0.1081</v>
+        <v>0.4575</v>
       </c>
       <c r="P67" s="7" t="n">
-        <v>-0.0257</v>
+        <v>-0</v>
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
@@ -4377,57 +4377,57 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>MAALT</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>709.5</v>
+        <v>10.19</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.0406</v>
+        <v>0.0345</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>-0.1736</v>
+        <v>-0.023</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>-0.2797</v>
+        <v>-0.07780000000000001</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>-0.3461</v>
+        <v>-0.1515</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-0.4752</v>
+        <v>-0.0369</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>-0.3044</v>
+        <v>-0.1648</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>1528.77</v>
+        <v>6.84</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0.248</v>
+        <v>0.423</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>3.5256</v>
+        <v>0.5552</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>0.3863</v>
+        <v>0.8170999999999999</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.9832</v>
+        <v>10.0728</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>0.4575</v>
+        <v>0.179</v>
       </c>
       <c r="P68" s="4" t="n">
-        <v>-0</v>
+        <v>0.2236</v>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr"/>
@@ -4435,57 +4435,57 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>SELEC</t>
+          <t>ISDMR</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>65.59999999999999</v>
+        <v>59.15</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>-0.0708</v>
+        <v>0.0619</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>-0.2336</v>
+        <v>-0.0626</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>-0.6919</v>
+        <v>-0.0483</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>-0.7371</v>
+        <v>0.0377</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>-0.2629</v>
+        <v>0.3029</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>-0.1253</v>
+        <v>0.6349</v>
       </c>
       <c r="I69" s="6" t="n">
         <v>1.1</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>20</v>
+        <v>13.95</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>0.3781</v>
+        <v>0.1859</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>0.6063000000000001</v>
+        <v>0.3543</v>
       </c>
       <c r="M69" s="7" t="n">
-        <v>1.4267</v>
+        <v>0.4035</v>
       </c>
       <c r="N69" s="7" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.208</v>
       </c>
       <c r="O69" s="7" t="n">
-        <v>0.0158</v>
+        <v>0.1056</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.0859</v>
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R69" s="5" t="inlineStr"/>
@@ -4497,31 +4497,31 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>75.65000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>-0.0072</v>
+        <v>0.0297</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>-0.0935</v>
+        <v>-0.0442</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>-0.1178</v>
+        <v>-0.0915</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>-0.1608</v>
+        <v>-0.1496</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>-0.2836</v>
+        <v>-0.2623</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>0.0693</v>
+        <v>0.1011</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>11.36</v>
+        <v>11.7</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>0.4381</v>
@@ -4551,55 +4551,57 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>YKSLN</t>
+          <t>KTLEV</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>2.24</v>
+        <v>5.41</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0442</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.417</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>-0.3978</v>
+        <v>-0.757</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>-0.3</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>-0.3043</v>
+        <v>-0.8189</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>-0.3699</v>
+        <v>0.4061999999999999</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="J71" s="5" t="inlineStr"/>
+        <v>1.14</v>
+      </c>
+      <c r="J71" s="6" t="n">
+        <v>1.32</v>
+      </c>
       <c r="K71" s="7" t="n">
-        <v>0.1126</v>
+        <v>3.5578</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>0.0263</v>
+        <v>3.6471</v>
       </c>
       <c r="M71" s="7" t="n">
-        <v>0.6127</v>
+        <v>5.174600000000001</v>
       </c>
       <c r="N71" s="7" t="n">
-        <v>0.8754000000000001</v>
+        <v>5.7649</v>
       </c>
       <c r="O71" s="7" t="n">
-        <v>0.1443</v>
+        <v>0.7222</v>
       </c>
       <c r="P71" s="7" t="n">
-        <v>-0.04969999999999999</v>
+        <v>1.5072</v>
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R71" s="5" t="inlineStr"/>
@@ -4611,31 +4613,31 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>-0.0299</v>
+        <v>0.0256</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.0557</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0602</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>-0.1716</v>
+        <v>-0.1482</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>-0.1942</v>
+        <v>-0.1736</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>0.0529</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>6.2</v>
+        <v>6.35</v>
       </c>
       <c r="K72" s="4" t="n">
         <v>0.3448</v>
@@ -4665,57 +4667,55 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>GEDIK</t>
+          <t>YKSLN</t>
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>4.56</v>
+        <v>2.34</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>-0.0539</v>
+        <v>0.0446</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>-0.07690000000000001</v>
+        <v>0.0308</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-0.09699999999999999</v>
+        <v>-0.371</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>-0.3372</v>
+        <v>-0.2688</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>-0.2178</v>
+        <v>-0.2733</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>-0.3684000000000001</v>
+        <v>-0.3195</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="J73" s="6" t="n">
-        <v>4.83</v>
-      </c>
+        <v>1.16</v>
+      </c>
+      <c r="J73" s="5" t="inlineStr"/>
       <c r="K73" s="7" t="n">
-        <v>0.6583</v>
+        <v>0.1126</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.0263</v>
       </c>
       <c r="M73" s="7" t="n">
-        <v>0.7293999999999999</v>
+        <v>0.6127</v>
       </c>
       <c r="N73" s="7" t="n">
-        <v>0.3481</v>
+        <v>0.8754000000000001</v>
       </c>
       <c r="O73" s="7" t="n">
-        <v>0.6628000000000001</v>
+        <v>0.1443</v>
       </c>
       <c r="P73" s="7" t="n">
-        <v>0.275</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R73" s="5" t="inlineStr"/>
@@ -4723,55 +4723,57 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>OBASE</t>
+          <t>GARFA</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>20.78</v>
+        <v>20.32</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>0.0039</v>
+        <v>0.001</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>-0.1952</v>
+        <v>-0.1142</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>-0.3756</v>
+        <v>-0.2185</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>-0.5877</v>
+        <v>-0.3093</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-0.4526</v>
+        <v>-0.2743</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>-0.4156</v>
+        <v>-0.1638</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>3.08</v>
+      </c>
       <c r="K74" s="4" t="n">
-        <v>0.2041</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.3021</v>
+        <v>0.9506</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.5156000000000001</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.4873</v>
+        <v>0.5365</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>0.2465</v>
+        <v>0.914</v>
       </c>
       <c r="P74" s="4" t="n">
-        <v>0.1432</v>
+        <v>0.496</v>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr"/>
@@ -4779,57 +4781,55 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>GLCVY</t>
+          <t>OBASE</t>
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>35.18</v>
+        <v>21.44</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>-0.0309</v>
+        <v>0.0318</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>-0.1071</v>
+        <v>-0.1096</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-0.2686</v>
+        <v>-0.3558</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>-0.3735</v>
+        <v>-0.5463</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>-0.4398</v>
+        <v>-0.4352</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>-0.4596</v>
+        <v>-0.3988</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="J75" s="6" t="n">
-        <v>3.41</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="J75" s="5" t="inlineStr"/>
       <c r="K75" s="7" t="n">
-        <v>0.265</v>
+        <v>0.2041</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>0.2739</v>
+        <v>0.3021</v>
       </c>
       <c r="M75" s="7" t="n">
-        <v>0.2851</v>
+        <v>0.5156000000000001</v>
       </c>
       <c r="N75" s="7" t="n">
-        <v>0.0788</v>
+        <v>0.4873</v>
       </c>
       <c r="O75" s="7" t="n">
-        <v>0.7251000000000001</v>
+        <v>0.2465</v>
       </c>
       <c r="P75" s="7" t="n">
-        <v>0.4011</v>
+        <v>0.1432</v>
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R75" s="5" t="inlineStr"/>
@@ -4837,53 +4837,53 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GARFA</t>
+          <t>GEDIK</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>20.3</v>
+        <v>4.8</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.0478</v>
+        <v>0.0526</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>-0.128</v>
+        <v>-0.0244</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>-0.2192</v>
+        <v>-0.0495</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>-0.3322</v>
+        <v>-0.3172</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.275</v>
+        <v>-0.1767</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>-0.1828</v>
+        <v>-0.3182</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>3.08</v>
+        <v>5.08</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0.9562999999999999</v>
+        <v>0.6583</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.9506</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.7293999999999999</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.5365</v>
+        <v>0.3481</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>0.914</v>
+        <v>0.6628000000000001</v>
       </c>
       <c r="P76" s="4" t="n">
-        <v>0.496</v>
+        <v>0.275</v>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
@@ -4895,53 +4895,53 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>GLCVY</t>
         </is>
       </c>
       <c r="B77" s="6" t="n">
-        <v>28.06</v>
+        <v>35.98</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>-0.0223</v>
+        <v>0.0227</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>-0.0578</v>
+        <v>-0.05860000000000001</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-0.196</v>
+        <v>-0.252</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>-0.2354</v>
+        <v>-0.3637</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>-0.3703</v>
+        <v>-0.4271</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>-0.2936</v>
+        <v>-0.4374</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>6.27</v>
+        <v>3.49</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>0.4021</v>
+        <v>0.265</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>0.2915</v>
+        <v>0.2739</v>
       </c>
       <c r="M77" s="7" t="n">
-        <v>0.201</v>
+        <v>0.2851</v>
       </c>
       <c r="N77" s="7" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.0788</v>
       </c>
       <c r="O77" s="7" t="n">
-        <v>0.8484999999999999</v>
+        <v>0.7251000000000001</v>
       </c>
       <c r="P77" s="7" t="n">
-        <v>0.298</v>
+        <v>0.4011</v>
       </c>
       <c r="Q77" s="5" t="inlineStr">
         <is>
@@ -4953,53 +4953,53 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>KTLEV</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>5.66</v>
+        <v>28.5</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>-0.0241</v>
+        <v>0.0157</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>-0.3568</v>
+        <v>-0.0206</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>-0.7456999999999999</v>
+        <v>-0.1834</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>-0.8822</v>
+        <v>-0.2222</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>-0.8105</v>
+        <v>-0.3604</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>0.4284000000000001</v>
+        <v>-0.2796</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>1.38</v>
+        <v>6.36</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>3.5578</v>
+        <v>0.4021</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>3.6471</v>
+        <v>0.2915</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>5.174600000000001</v>
+        <v>0.201</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>5.7649</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>0.7222</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="P78" s="4" t="n">
-        <v>1.5072</v>
+        <v>0.298</v>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
@@ -5011,57 +5011,55 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
-        <v>274</v>
+        <v>6.04</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>0.0129</v>
+        <v>0.0067</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>-0.0018</v>
+        <v>-0.0793</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>0.0046</v>
+        <v>-0.1493</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>0</v>
+        <v>-0.2286</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>-0.1274</v>
+        <v>-0.2775</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>0.2227</v>
+        <v>-0.2488</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="J79" s="6" t="n">
-        <v>18.87</v>
-      </c>
+        <v>1.27</v>
+      </c>
+      <c r="J79" s="5" t="inlineStr"/>
       <c r="K79" s="7" t="n">
-        <v>0.3707</v>
+        <v>0.3952000000000001</v>
       </c>
       <c r="L79" s="7" t="n">
-        <v>0.4185</v>
+        <v>0.4088000000000001</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>0.4202</v>
+        <v>0.4094</v>
       </c>
       <c r="N79" s="7" t="n">
-        <v>1.8941</v>
+        <v>0.7489</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>0.3086</v>
+        <v>0.7836</v>
       </c>
       <c r="P79" s="7" t="n">
-        <v>-0.1688</v>
+        <v>-0.0106</v>
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Çeşitli Hizmetler</t>
         </is>
       </c>
       <c r="R79" s="5" t="inlineStr"/>
@@ -5069,57 +5067,57 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>KCAER</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>9.52</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>-0.0602</v>
+        <v>0.0268</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>-0.1266</v>
+        <v>-0.0139</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>-0.2067</v>
+        <v>0.0343</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>-0.3181</v>
+        <v>-0.3571</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>-0.1919</v>
+        <v>-0.1199</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>-0.2438</v>
+        <v>0.453</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>27.72</v>
+        <v>26.08</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0.1522</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>0.2873</v>
+        <v>0.3716</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>0.3247</v>
+        <v>0.4119</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>1.1982</v>
+        <v>0.9691</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>0.1199</v>
+        <v>0.3037</v>
       </c>
       <c r="P80" s="4" t="n">
-        <v>0.0508</v>
+        <v>0.0601</v>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr"/>
@@ -5127,57 +5125,57 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>69</v>
+        <v>286.25</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>0.0015</v>
+        <v>0.0447</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>-0.0707</v>
+        <v>0.0741</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>0.0073</v>
+        <v>0.0495</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>-0.3527</v>
+        <v>0.0563</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>-0.1429</v>
+        <v>-0.08839999999999999</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>0.4274</v>
+        <v>0.2711</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>25.4</v>
+        <v>19.72</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.3707</v>
       </c>
       <c r="L81" s="7" t="n">
-        <v>0.3716</v>
+        <v>0.4185</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>0.4119</v>
+        <v>0.4202</v>
       </c>
       <c r="N81" s="7" t="n">
-        <v>0.9691</v>
+        <v>1.8941</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>0.3037</v>
+        <v>0.3086</v>
       </c>
       <c r="P81" s="7" t="n">
-        <v>0.0601</v>
+        <v>-0.1688</v>
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="R81" s="5" t="inlineStr"/>
@@ -5189,28 +5187,28 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>5.75</v>
+        <v>5.87</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>-0.0287</v>
+        <v>0.0209</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>0.0213</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>-0.1606</v>
+        <v>-0.1431</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>-0.4078</v>
+        <v>-0.3917</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>-0.08</v>
+        <v>-0.0608</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>-0.2919</v>
+        <v>-0.2978</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="4" t="n">
@@ -5241,55 +5239,57 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>KNFRT</t>
+          <t>SARKY</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>7.56</v>
+        <v>17.1</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>-0.09789999999999999</v>
+        <v>0.0018</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>-0.2766</v>
+        <v>-0.1009</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-0.371</v>
+        <v>-0.2434</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>-0.3726</v>
+        <v>-0.3382</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>-0.4229</v>
+        <v>-0.3966</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>-0.4341</v>
+        <v>0.2068</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J83" s="5" t="inlineStr"/>
+        <v>1.28</v>
+      </c>
+      <c r="J83" s="6" t="n">
+        <v>62.66</v>
+      </c>
       <c r="K83" s="7" t="n">
-        <v>0.7798</v>
+        <v>0.5590999999999999</v>
       </c>
       <c r="L83" s="7" t="n">
-        <v>1.3764</v>
+        <v>0.3671</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>26.3063</v>
+        <v>0.2342</v>
       </c>
       <c r="N83" s="7" t="n">
-        <v>0.625</v>
+        <v>0.8034</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>0.0124</v>
+        <v>0.0217</v>
       </c>
       <c r="P83" s="7" t="n">
-        <v>-0.1091</v>
+        <v>0.0229</v>
       </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R83" s="5" t="inlineStr"/>
@@ -5297,55 +5297,57 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>KCAER</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>6</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>-0.0228</v>
+        <v>0.0452</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>-0.09230000000000001</v>
+        <v>-0.0684</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>-0.1549</v>
+        <v>-0.1708</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>-0.2395</v>
+        <v>-0.2857</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>-0.2823</v>
+        <v>-0.1553</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>-0.2583</v>
+        <v>-0.2046</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr"/>
+        <v>1.28</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>28.97</v>
+      </c>
       <c r="K84" s="4" t="n">
-        <v>0.3952000000000001</v>
+        <v>0.1522</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.4088000000000001</v>
+        <v>0.2873</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>0.4094</v>
+        <v>0.3247</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>0.7489</v>
+        <v>1.1982</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>0.7836</v>
+        <v>0.1199</v>
       </c>
       <c r="P84" s="4" t="n">
-        <v>-0.0106</v>
+        <v>0.0508</v>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>Çeşitli Hizmetler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr"/>
@@ -5353,57 +5355,55 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>SARKY</t>
+          <t>ACSEL</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>17.07</v>
+        <v>82</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>-0.0076</v>
+        <v>0.0123</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>-0.1491</v>
+        <v>-0.05690000000000001</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-0.2447</v>
+        <v>-0.2115</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>-0.3358</v>
+        <v>-0.3876</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>-0.3977000000000001</v>
+        <v>-0.3098</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0.1644</v>
+        <v>-0.2711</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="J85" s="6" t="n">
-        <v>62.55</v>
-      </c>
+        <v>1.3</v>
+      </c>
+      <c r="J85" s="5" t="inlineStr"/>
       <c r="K85" s="7" t="n">
-        <v>0.5590999999999999</v>
+        <v>0.3957</v>
       </c>
       <c r="L85" s="7" t="n">
-        <v>0.3671</v>
+        <v>2.0344</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>0.2342</v>
+        <v>3.8494</v>
       </c>
       <c r="N85" s="7" t="n">
-        <v>0.8034</v>
+        <v>0.889</v>
       </c>
       <c r="O85" s="7" t="n">
-        <v>0.0217</v>
+        <v>0.0349</v>
       </c>
       <c r="P85" s="7" t="n">
-        <v>0.0229</v>
+        <v>-0.0175</v>
       </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R85" s="5" t="inlineStr"/>
@@ -5411,55 +5411,55 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>KNFRT</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>81</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>-0.0294</v>
+        <v>0.0741</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>-0.099</v>
+        <v>-0.1896</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>-0.2212</v>
+        <v>-0.3245</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>-0.374</v>
+        <v>-0.3267</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>-0.3182</v>
+        <v>-0.3802</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>-0.2895</v>
+        <v>-0.3778</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="4" t="n">
-        <v>0.3957</v>
+        <v>0.7798</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>2.0344</v>
+        <v>1.3764</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>3.8494</v>
+        <v>26.3063</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>0.889</v>
+        <v>0.625</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>0.0349</v>
+        <v>0.0124</v>
       </c>
       <c r="P86" s="4" t="n">
-        <v>-0.0175</v>
+        <v>-0.1091</v>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr"/>
@@ -5467,57 +5467,55 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>PCILT</t>
+          <t>OZYSR</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>28.7</v>
+        <v>11.64</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>-0.0645</v>
+        <v>0.0034</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>-0.0645</v>
+        <v>-0.0177</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>-0.0559</v>
+        <v>0.0563</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>-0.1618</v>
+        <v>-0.1222</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>0.09039999999999999</v>
+        <v>-0.0204</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>0.3851</v>
+        <v>0.5093</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J87" s="6" t="n">
-        <v>6.59</v>
-      </c>
+        <v>1.36</v>
+      </c>
+      <c r="J87" s="5" t="inlineStr"/>
       <c r="K87" s="7" t="n">
-        <v>0.763</v>
+        <v>0.161</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>0.7087</v>
+        <v>0.1742</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>0.7914</v>
+        <v>0.6839</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>1.2232</v>
+        <v>0.5105</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>0.0574</v>
+        <v>0.042</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>0.2831</v>
+        <v>-0.0335</v>
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R87" s="5" t="inlineStr"/>
@@ -5525,55 +5523,57 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>OZYSR</t>
+          <t>PCILT</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>11.6</v>
+        <v>30.3</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>-0.0349</v>
+        <v>0.0557</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>-0.0119</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>0.0526</v>
+        <v>-0.0033</v>
       </c>
       <c r="F88" s="4" t="n">
         <v>-0.1212</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>-0.0238</v>
+        <v>0.1512</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>0.4909000000000001</v>
+        <v>0.5881000000000001</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr"/>
+        <v>1.37</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>6.96</v>
+      </c>
       <c r="K88" s="4" t="n">
-        <v>0.161</v>
+        <v>0.763</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>0.1742</v>
+        <v>0.7087</v>
       </c>
       <c r="M88" s="4" t="n">
-        <v>0.6839</v>
+        <v>0.7914</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>0.5105</v>
+        <v>1.2232</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>0.042</v>
+        <v>0.0574</v>
       </c>
       <c r="P88" s="4" t="n">
-        <v>-0.0335</v>
+        <v>0.2831</v>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R88" s="2" t="inlineStr"/>
@@ -5585,31 +5585,31 @@
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>25.1</v>
+        <v>25.34</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>-0.0398</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>-0.1526</v>
+        <v>-0.1256</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-0.2574</v>
+        <v>-0.2503</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>-0.4555</v>
+        <v>-0.4618</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>-0.379</v>
+        <v>-0.3731</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>-0.3923</v>
+        <v>-0.3813</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>30.07</v>
+        <v>30.36</v>
       </c>
       <c r="K89" s="7" t="n">
         <v>0.05019999999999999</v>
@@ -5639,57 +5639,57 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>EGPRO</t>
+          <t>GENIL</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>28.18</v>
+        <v>4.22</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>-0.0133</v>
+        <v>-0.09050000000000001</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>-0.1687</v>
+        <v>-0.1916</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>-0.2342</v>
+        <v>-0.5301</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>-0.2384</v>
+        <v>-0.5347</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>-0.3847</v>
+        <v>-0.5746</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>0.0756</v>
+        <v>-0.6923999999999999</v>
       </c>
       <c r="I90" s="3" t="n">
         <v>1.45</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>10.04</v>
+        <v>15.38</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0.3776</v>
+        <v>0.5049</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>0.5127</v>
+        <v>0.7672</v>
       </c>
       <c r="M90" s="4" t="n">
-        <v>0.5197999999999999</v>
+        <v>1.1622</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>1.3047</v>
+        <v>1.2274</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>0.2228</v>
+        <v>0.0922</v>
       </c>
       <c r="P90" s="4" t="n">
-        <v>0.1742</v>
+        <v>0.1305</v>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R90" s="2" t="inlineStr"/>
@@ -5697,55 +5697,57 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>KRPLS</t>
+          <t>EGPRO</t>
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>8.970000000000001</v>
+        <v>29.16</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.0348</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>-0.2062</v>
+        <v>-0.1028</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-0.2462</v>
+        <v>-0.2076</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>-0.0011</v>
+        <v>-0.2033</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>-0.0164</v>
+        <v>-0.3633</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>0.0124</v>
+        <v>0.1346</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="J91" s="5" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="J91" s="6" t="n">
+        <v>10.38</v>
+      </c>
       <c r="K91" s="7" t="n">
-        <v>0.3576</v>
+        <v>0.3776</v>
       </c>
       <c r="L91" s="7" t="n">
-        <v>0.6872</v>
+        <v>0.5127</v>
       </c>
       <c r="M91" s="7" t="n">
-        <v>0.9115000000000001</v>
+        <v>0.5197999999999999</v>
       </c>
       <c r="N91" s="7" t="n">
-        <v>0.7781999999999999</v>
+        <v>1.3047</v>
       </c>
       <c r="O91" s="7" t="n">
-        <v>0.166</v>
+        <v>0.2228</v>
       </c>
       <c r="P91" s="7" t="n">
-        <v>-0.0342</v>
+        <v>0.1742</v>
       </c>
       <c r="Q91" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R91" s="5" t="inlineStr"/>
@@ -5757,31 +5759,31 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>356.75</v>
+        <v>362</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>-0.0499</v>
+        <v>0.0147</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0542</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>-0.1299</v>
+        <v>-0.1171</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>0.163</v>
+        <v>0.1696</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>0.4059</v>
+        <v>0.4266</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>1.0339</v>
+        <v>1.0877</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>9.9</v>
+        <v>10.04</v>
       </c>
       <c r="K92" s="4" t="n">
         <v>0.465</v>
@@ -5811,57 +5813,55 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>MEGMT</t>
+          <t>KRPLS</t>
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>3.1</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>-0.0282</v>
+        <v>0.04679999999999999</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>-0.1507</v>
+        <v>-0.1563</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>-0.1692</v>
+        <v>-0.2109</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>-0.5649000000000001</v>
+        <v>0.0527</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>-0.6247</v>
+        <v>0.0296</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>-0.0211</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="J93" s="6" t="n">
-        <v>6.62</v>
-      </c>
+        <v>1.55</v>
+      </c>
+      <c r="J93" s="5" t="inlineStr"/>
       <c r="K93" s="7" t="n">
-        <v>0.51</v>
+        <v>0.3576</v>
       </c>
       <c r="L93" s="7" t="n">
-        <v>0.4203</v>
+        <v>0.6872</v>
       </c>
       <c r="M93" s="7" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.9115000000000001</v>
       </c>
       <c r="N93" s="7" t="n">
-        <v>0.2482</v>
+        <v>0.7781999999999999</v>
       </c>
       <c r="O93" s="7" t="n">
-        <v>0.0483</v>
+        <v>0.166</v>
       </c>
       <c r="P93" s="7" t="n">
-        <v>0.2852</v>
+        <v>-0.0342</v>
       </c>
       <c r="Q93" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R93" s="5" t="inlineStr"/>
@@ -5869,57 +5869,57 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>FONET</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>3.56</v>
+        <v>14.04</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>-0.09179999999999999</v>
+        <v>-0.1</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>-0.1504</v>
+        <v>-0.1799</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>-0.1166</v>
+        <v>-0.1663</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>-0.3167</v>
+        <v>-0.6656</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>-0.2537</v>
+        <v>-0.5329</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>0.0509</v>
+        <v>0.2764</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>1.59</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>11.57</v>
+        <v>1.81</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1.0251</v>
+        <v>2.1748</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>2.0469</v>
+        <v>2.2285</v>
       </c>
       <c r="M94" s="4" t="n">
-        <v>1.6971</v>
+        <v>2.5519</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>1.6785</v>
+        <v>7.8348</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>0.4396</v>
+        <v>0.887</v>
       </c>
       <c r="P94" s="4" t="n">
-        <v>0.8814</v>
+        <v>1.1538</v>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr"/>
@@ -5927,57 +5927,57 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>GENIL</t>
+          <t>ORGE</t>
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>4.64</v>
+        <v>20.8</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>-0.099</v>
+        <v>0.001</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>-0.0252</v>
+        <v>-0.0877</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>-0.4833</v>
+        <v>-0.0698</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>-0.489</v>
+        <v>-0.0537</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>-0.5323</v>
+        <v>0.2644</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>-0.6598000000000001</v>
+        <v>0.5581</v>
       </c>
       <c r="I95" s="6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>16.92</v>
+        <v>9.66</v>
       </c>
       <c r="K95" s="7" t="n">
-        <v>0.5049</v>
+        <v>0.251</v>
       </c>
       <c r="L95" s="7" t="n">
-        <v>0.7672</v>
+        <v>0.257</v>
       </c>
       <c r="M95" s="7" t="n">
-        <v>1.1622</v>
+        <v>0.2421</v>
       </c>
       <c r="N95" s="7" t="n">
-        <v>1.2274</v>
+        <v>0.2676</v>
       </c>
       <c r="O95" s="7" t="n">
-        <v>0.0922</v>
+        <v>0.4943</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>0.1305</v>
+        <v>0.2029</v>
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R95" s="5" t="inlineStr"/>
@@ -5985,57 +5985,57 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ORGE</t>
+          <t>MEGMT</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>20.78</v>
+        <v>3.21</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>-0.029</v>
+        <v>0.0355</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>-0.1028</v>
+        <v>-0.07490000000000001</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>-0.0707</v>
+        <v>-0.1397</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>-0.0142</v>
+        <v>-0.5531</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>0.2632</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>0.5589</v>
+        <v>0.0265</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>9.65</v>
+        <v>6.86</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0.251</v>
+        <v>0.51</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>0.257</v>
+        <v>0.4203</v>
       </c>
       <c r="M96" s="4" t="n">
-        <v>0.2421</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>0.2676</v>
+        <v>0.2482</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>0.4943</v>
+        <v>0.0483</v>
       </c>
       <c r="P96" s="4" t="n">
-        <v>0.2029</v>
+        <v>0.2852</v>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr"/>
@@ -6043,55 +6043,57 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>DURDO</t>
+          <t>DERIM</t>
         </is>
       </c>
       <c r="B97" s="6" t="n">
-        <v>5.52</v>
+        <v>21.82</v>
       </c>
       <c r="C97" s="7" t="n">
-        <v>-0.0282</v>
+        <v>-0.0127</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>-0.1375</v>
+        <v>-0.1543</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>0.1084</v>
+        <v>-0.3147</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>0.09089999999999999</v>
+        <v>-0.3871</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>0.182</v>
+        <v>-0.4647</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>0.6047</v>
+        <v>-0.3959</v>
       </c>
       <c r="I97" s="6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="J97" s="5" t="inlineStr"/>
+        <v>1.63</v>
+      </c>
+      <c r="J97" s="6" t="n">
+        <v>12.02</v>
+      </c>
       <c r="K97" s="7" t="n">
-        <v>0.3099</v>
+        <v>0.1436</v>
       </c>
       <c r="L97" s="7" t="n">
-        <v>0.2862</v>
+        <v>0.2539</v>
       </c>
       <c r="M97" s="7" t="n">
-        <v>0.3279</v>
+        <v>0.0263</v>
       </c>
       <c r="N97" s="7" t="n">
-        <v>0.1519</v>
+        <v>0.0576</v>
       </c>
       <c r="O97" s="7" t="n">
-        <v>0.0876</v>
+        <v>0.0602</v>
       </c>
       <c r="P97" s="7" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.1637</v>
       </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R97" s="5" t="inlineStr"/>
@@ -6099,57 +6101,57 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>DERIM</t>
+          <t>FONET</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>22.1</v>
+        <v>3.69</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>-0.0341</v>
+        <v>0.0365</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>-0.1754</v>
+        <v>-0.1214</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>-0.3059</v>
+        <v>-0.08439999999999999</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>-0.3972</v>
+        <v>-0.289</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>-0.4578</v>
+        <v>-0.2264</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>-0.3949</v>
+        <v>0.164</v>
       </c>
       <c r="I98" s="3" t="n">
         <v>1.65</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>12.18</v>
+        <v>11.99</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0.1436</v>
+        <v>1.0251</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>0.2539</v>
+        <v>2.0469</v>
       </c>
       <c r="M98" s="4" t="n">
-        <v>0.0263</v>
+        <v>1.6971</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>0.0576</v>
+        <v>1.6785</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>0.0602</v>
+        <v>0.4396</v>
       </c>
       <c r="P98" s="4" t="n">
-        <v>0.1637</v>
+        <v>0.8814</v>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R98" s="2" t="inlineStr"/>
@@ -6157,53 +6159,53 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>SAYAS</t>
+          <t>SAFKR</t>
         </is>
       </c>
       <c r="B99" s="6" t="n">
-        <v>34.3</v>
+        <v>11.84</v>
       </c>
       <c r="C99" s="7" t="n">
-        <v>-0.03759999999999999</v>
+        <v>0.0077</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>-0.1459</v>
+        <v>-0.0133</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>-0.2649</v>
+        <v>0.0017</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>-0.2687</v>
+        <v>-0.4061999999999999</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>-0.2197</v>
+        <v>-0.5425</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>-0.3333</v>
+        <v>-0.4389</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>13.67</v>
+        <v>17.22</v>
       </c>
       <c r="K99" s="7" t="n">
-        <v>0.486</v>
+        <v>0.7861</v>
       </c>
       <c r="L99" s="7" t="n">
-        <v>1.4655</v>
+        <v>0.4555</v>
       </c>
       <c r="M99" s="7" t="n">
-        <v>2.3632</v>
+        <v>0.3309</v>
       </c>
       <c r="N99" s="7" t="n">
-        <v>6.118200000000001</v>
+        <v>0.5716</v>
       </c>
       <c r="O99" s="7" t="n">
-        <v>0.1798</v>
+        <v>0.2109</v>
       </c>
       <c r="P99" s="7" t="n">
-        <v>0.1493</v>
+        <v>0.1216</v>
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
@@ -6215,53 +6217,53 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>SAFKR</t>
+          <t>SAYAS</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>11.75</v>
+        <v>35.36</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>-0.0337</v>
+        <v>0.0309</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.1208</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>-0.0059</v>
+        <v>-0.2422</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>-0.4206</v>
+        <v>-0.2842</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>-0.546</v>
+        <v>-0.1956</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>-0.4125</v>
+        <v>-0.3476</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>17.09</v>
+        <v>14.09</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0.7861</v>
+        <v>0.486</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>0.4555</v>
+        <v>1.4655</v>
       </c>
       <c r="M100" s="4" t="n">
-        <v>0.3309</v>
+        <v>2.3632</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>0.5716</v>
+        <v>6.118200000000001</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>0.2109</v>
+        <v>0.1798</v>
       </c>
       <c r="P100" s="4" t="n">
-        <v>0.1216</v>
+        <v>0.1493</v>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
@@ -6273,57 +6275,57 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>SANEL</t>
         </is>
       </c>
       <c r="B101" s="6" t="n">
-        <v>401.5</v>
+        <v>25.64</v>
       </c>
       <c r="C101" s="7" t="n">
-        <v>-0.0349</v>
+        <v>0.0063</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>-0.0833</v>
+        <v>-0.1593</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>-0.077</v>
+        <v>-0.3426</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>-0.0542</v>
+        <v>-0.6556000000000001</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>-0.1389</v>
+        <v>-0.2862</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>0.2066</v>
+        <v>-0.05110000000000001</v>
       </c>
       <c r="I101" s="6" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>12.54</v>
+        <v>2.47</v>
       </c>
       <c r="K101" s="7" t="n">
-        <v>0.3601</v>
+        <v>0.309</v>
       </c>
       <c r="L101" s="7" t="n">
-        <v>0.3635</v>
+        <v>1.4614</v>
       </c>
       <c r="M101" s="7" t="n">
-        <v>0.5899</v>
+        <v>1.5381</v>
       </c>
       <c r="N101" s="7" t="n">
-        <v>0.1175</v>
+        <v>2.2148</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>0.2737</v>
+        <v>0.1491</v>
       </c>
       <c r="P101" s="7" t="n">
-        <v>0.2987</v>
+        <v>1.0947</v>
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
-          <t>Sağlık hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R101" s="5" t="inlineStr"/>
@@ -6331,57 +6333,55 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>ENERY</t>
+          <t>DURDO</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>13.25</v>
+        <v>6.07</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>-0.0433</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>-0.0747</v>
+        <v>-0.0501</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>0.0458</v>
+        <v>0.2189</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>0.3947</v>
+        <v>0.154</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>0.4309000000000001</v>
+        <v>0.2998</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>0.3947</v>
+        <v>0.7853</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J102" s="3" t="n">
-        <v>21.13</v>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="4" t="n">
-        <v>0.4279</v>
+        <v>0.3099</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>0.7162999999999999</v>
+        <v>0.2862</v>
       </c>
       <c r="M102" s="4" t="n">
-        <v>0.8373999999999999</v>
+        <v>0.3279</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>0.6103000000000001</v>
+        <v>0.1519</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>0.2099</v>
+        <v>0.0876</v>
       </c>
       <c r="P102" s="4" t="n">
-        <v>0.1017</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr"/>
@@ -6389,57 +6389,57 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>TOASO</t>
         </is>
       </c>
       <c r="B103" s="6" t="n">
-        <v>15.6</v>
+        <v>237.7</v>
       </c>
       <c r="C103" s="7" t="n">
-        <v>-0.0998</v>
+        <v>0.0115</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>0.0541</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>-0.0736</v>
+        <v>-0.163</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>-0.5979</v>
+        <v>-0.2096</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>-0.481</v>
+        <v>-0.1775</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>0.4436</v>
+        <v>-0.0697</v>
       </c>
       <c r="I103" s="6" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>2.01</v>
+        <v>9.35</v>
       </c>
       <c r="K103" s="7" t="n">
-        <v>2.1748</v>
+        <v>1.7224</v>
       </c>
       <c r="L103" s="7" t="n">
-        <v>2.2285</v>
+        <v>1.8184</v>
       </c>
       <c r="M103" s="7" t="n">
-        <v>2.5519</v>
+        <v>1.3297</v>
       </c>
       <c r="N103" s="7" t="n">
-        <v>7.8348</v>
+        <v>5.0053</v>
       </c>
       <c r="O103" s="7" t="n">
-        <v>0.887</v>
+        <v>0.0381</v>
       </c>
       <c r="P103" s="7" t="n">
-        <v>1.1538</v>
+        <v>0.2862</v>
       </c>
       <c r="Q103" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="R103" s="5" t="inlineStr"/>
@@ -6447,57 +6447,57 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SANEL</t>
+          <t>MPARK</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>25.48</v>
+        <v>416.5</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>-0.0735</v>
+        <v>0.0374</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>-0.2251</v>
+        <v>-0.0359</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>-0.3467</v>
+        <v>-0.0425</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>-0.6307</v>
+        <v>0.0048</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>-0.2906</v>
+        <v>-0.1067</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>-0.0728</v>
+        <v>0.2718</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>2.46</v>
+        <v>13.01</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0.309</v>
+        <v>0.3601</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>1.4614</v>
+        <v>0.3635</v>
       </c>
       <c r="M104" s="4" t="n">
-        <v>1.5381</v>
+        <v>0.5899</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>2.2148</v>
+        <v>0.1175</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>0.1491</v>
+        <v>0.2737</v>
       </c>
       <c r="P104" s="4" t="n">
-        <v>1.0947</v>
+        <v>0.2987</v>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Sağlık hizmetleri</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr"/>
@@ -6505,57 +6505,57 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>TOASO</t>
+          <t>ENERY</t>
         </is>
       </c>
       <c r="B105" s="6" t="n">
-        <v>235</v>
+        <v>14.06</v>
       </c>
       <c r="C105" s="7" t="n">
-        <v>-0.0385</v>
+        <v>0.0611</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>-0.1182</v>
+        <v>-0.0403</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>-0.1725</v>
+        <v>0.1097</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>-0.2276</v>
+        <v>0.4816</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>-0.1869</v>
+        <v>0.5184000000000001</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>-0.0711</v>
+        <v>0.5151</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="J105" s="6" t="n">
-        <v>9.24</v>
+        <v>22.42</v>
       </c>
       <c r="K105" s="7" t="n">
-        <v>1.7224</v>
+        <v>0.4279</v>
       </c>
       <c r="L105" s="7" t="n">
-        <v>1.8184</v>
+        <v>0.7162999999999999</v>
       </c>
       <c r="M105" s="7" t="n">
-        <v>1.3297</v>
+        <v>0.8373999999999999</v>
       </c>
       <c r="N105" s="7" t="n">
-        <v>5.0053</v>
+        <v>0.6103000000000001</v>
       </c>
       <c r="O105" s="7" t="n">
-        <v>0.0381</v>
+        <v>0.2099</v>
       </c>
       <c r="P105" s="7" t="n">
-        <v>0.2862</v>
+        <v>0.1017</v>
       </c>
       <c r="Q105" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R105" s="5" t="inlineStr"/>
@@ -6563,53 +6563,53 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>GRSEL</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>190.8</v>
+        <v>268.5</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>-0.0479</v>
+        <v>0.0347</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>-0.1632</v>
+        <v>-0.047</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>-0.1836</v>
+        <v>-0.0272</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>-0.1829</v>
+        <v>-0.1764</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>-0.264</v>
+        <v>-0.1304</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>-0.1864</v>
+        <v>-0.2372</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>17.84</v>
+        <v>8.16</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0.493</v>
+        <v>0.3337</v>
       </c>
       <c r="L106" s="4" t="n">
-        <v>0.3835</v>
+        <v>0.6940999999999999</v>
       </c>
       <c r="M106" s="4" t="n">
-        <v>0.4282</v>
+        <v>0.2722</v>
       </c>
       <c r="N106" s="4" t="n">
-        <v>0.1825</v>
+        <v>0.7318000000000001</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>0.2029</v>
+        <v>0.3275</v>
       </c>
       <c r="P106" s="4" t="n">
-        <v>0.1296</v>
+        <v>0.3613</v>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
@@ -6621,57 +6621,57 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>AHGAZ</t>
+          <t>VBTYZ</t>
         </is>
       </c>
       <c r="B107" s="6" t="n">
-        <v>44.82</v>
+        <v>19.7</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>-0.0357</v>
+        <v>0.0423</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>-0.07400000000000001</v>
+        <v>-0.142</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>0.09369999999999999</v>
+        <v>-0.3545</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>0.2784</v>
+        <v>-0.3477</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>0.6575</v>
+        <v>-0.098</v>
       </c>
       <c r="H107" s="7" t="n">
-        <v>0.7772</v>
+        <v>0.1043</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="J107" s="6" t="n">
-        <v>21.21</v>
+        <v>12.89</v>
       </c>
       <c r="K107" s="7" t="n">
-        <v>0.659</v>
+        <v>0.5342</v>
       </c>
       <c r="L107" s="7" t="n">
-        <v>1.7979</v>
+        <v>0.9976999999999999</v>
       </c>
       <c r="M107" s="7" t="n">
-        <v>2.1313</v>
+        <v>3.6408</v>
       </c>
       <c r="N107" s="7" t="n">
-        <v>2.8917</v>
+        <v>1.3528</v>
       </c>
       <c r="O107" s="7" t="n">
-        <v>0.1977</v>
+        <v>0.2074</v>
       </c>
       <c r="P107" s="7" t="n">
-        <v>0.1152</v>
+        <v>-9.062000000000001</v>
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R107" s="5" t="inlineStr"/>
@@ -6679,57 +6679,57 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>VBTYZ</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>18.9</v>
+        <v>205</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>-0.0507</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>-0.2138</v>
+        <v>-0.077</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>-0.3807</v>
+        <v>-0.1228</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>-0.3807</v>
+        <v>-0.1239</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>-0.1346</v>
+        <v>-0.2093</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>0.0373</v>
+        <v>-0.1224</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>12.37</v>
+        <v>19.16</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0.5342</v>
+        <v>0.493</v>
       </c>
       <c r="L108" s="4" t="n">
-        <v>0.9976999999999999</v>
+        <v>0.3835</v>
       </c>
       <c r="M108" s="4" t="n">
-        <v>3.6408</v>
+        <v>0.4282</v>
       </c>
       <c r="N108" s="4" t="n">
-        <v>1.3528</v>
+        <v>0.1825</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>0.2074</v>
+        <v>0.2029</v>
       </c>
       <c r="P108" s="4" t="n">
-        <v>-9.062000000000001</v>
+        <v>0.1296</v>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R108" s="2" t="inlineStr"/>
@@ -6737,57 +6737,57 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>GRSEL</t>
+          <t>AHGAZ</t>
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>259.5</v>
+        <v>47.62</v>
       </c>
       <c r="C109" s="7" t="n">
-        <v>-0.0564</v>
+        <v>0.0625</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>-0.0757</v>
+        <v>-0.0274</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>-0.05980000000000001</v>
+        <v>0.162</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>-0.1859</v>
+        <v>0.3482</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>-0.1595</v>
+        <v>0.7611</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>-0.2746</v>
+        <v>0.9079</v>
       </c>
       <c r="I109" s="6" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="J109" s="6" t="n">
-        <v>7.88</v>
+        <v>22.53</v>
       </c>
       <c r="K109" s="7" t="n">
-        <v>0.3337</v>
+        <v>0.659</v>
       </c>
       <c r="L109" s="7" t="n">
-        <v>0.6940999999999999</v>
+        <v>1.7979</v>
       </c>
       <c r="M109" s="7" t="n">
-        <v>0.2722</v>
+        <v>2.1313</v>
       </c>
       <c r="N109" s="7" t="n">
-        <v>0.7318000000000001</v>
+        <v>2.8917</v>
       </c>
       <c r="O109" s="7" t="n">
-        <v>0.3275</v>
+        <v>0.1977</v>
       </c>
       <c r="P109" s="7" t="n">
-        <v>0.3613</v>
+        <v>0.1152</v>
       </c>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R109" s="5" t="inlineStr"/>
@@ -6799,31 +6799,31 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>17.04</v>
+        <v>17.47</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>-0.0268</v>
+        <v>0.0252</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>-0.0179</v>
+        <v>-0.024</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1134</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>-0.011</v>
+        <v>0.0128</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>0.0771</v>
+        <v>0.1043</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>0.6229</v>
+        <v>0.7365999999999999</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>5.69</v>
+        <v>5.83</v>
       </c>
       <c r="K110" s="4" t="n">
         <v>0.2312</v>
@@ -6857,31 +6857,31 @@
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>42.26</v>
+        <v>43.38</v>
       </c>
       <c r="C111" s="7" t="n">
-        <v>-0.08130000000000001</v>
+        <v>0.0265</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>-0.149</v>
+        <v>-0.1204</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>-0.2224</v>
+        <v>-0.2018</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>-0.5716</v>
+        <v>-0.5982999999999999</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>0.0178</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>0.6081</v>
+        <v>0.6659</v>
       </c>
       <c r="I111" s="6" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="J111" s="6" t="n">
-        <v>29.95</v>
+        <v>30.75</v>
       </c>
       <c r="K111" s="7" t="n">
         <v>0.8139</v>
@@ -6915,31 +6915,31 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>371</v>
+        <v>385.5</v>
       </c>
       <c r="C112" s="4" t="n">
-        <v>-0.0262</v>
+        <v>0.0391</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>-0.0794</v>
+        <v>-0.0326</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>-0.1103</v>
+        <v>-0.0755</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>-0.0771</v>
+        <v>-0.0228</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>-0.0211</v>
+        <v>0.0172</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>0.3818</v>
+        <v>0.4575</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>16.23</v>
+        <v>16.86</v>
       </c>
       <c r="K112" s="4" t="n">
         <v>0.4214</v>
@@ -6973,31 +6973,31 @@
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>74.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>-0.0254</v>
+        <v>0.024</v>
       </c>
       <c r="D113" s="7" t="n">
-        <v>-0.1057</v>
+        <v>-0.0692</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.0412</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>-0.1769</v>
+        <v>-0.1722</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>-0.0649</v>
+        <v>-0.0424</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>0.5909</v>
+        <v>0.5834</v>
       </c>
       <c r="I113" s="6" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="J113" s="6" t="n">
-        <v>10.12</v>
+        <v>10.36</v>
       </c>
       <c r="K113" s="7" t="n">
         <v>0.4257</v>
@@ -7031,31 +7031,31 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>40.48</v>
+        <v>41.72</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>-0.0199</v>
+        <v>0.0306</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.0484</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>-0.192</v>
+        <v>-0.1673</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>-0.2</v>
+        <v>-0.1653</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>-0.1739</v>
+        <v>-0.1486</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>0.6076</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>25.85</v>
+        <v>26.64</v>
       </c>
       <c r="K114" s="4" t="n">
         <v>1.2681</v>
@@ -7089,31 +7089,31 @@
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>102.6</v>
+        <v>107.3</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>-0.1</v>
+        <v>0.0458</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>-0.1726</v>
+        <v>-0.134</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-0.1101</v>
+        <v>-0.0694</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>-0.283</v>
+        <v>-0.2308</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>-0.0366</v>
+        <v>0.0075</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>1.4429</v>
+        <v>1.4644</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="J115" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="K115" s="7" t="n">
         <v>2.4396</v>
@@ -7143,53 +7143,53 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>ARDYZ</t>
+          <t>LOGO</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>54.45</v>
+        <v>125.2</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>-0.0993</v>
+        <v>0.0381</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>-0.1843</v>
+        <v>-0.1121</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>-0.0732</v>
+        <v>-0.09539999999999998</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>-0.1993</v>
+        <v>-0.0861</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>0.2692</v>
+        <v>-0.1226</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>1.1641</v>
+        <v>-0.1714</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>13.56</v>
+        <v>13.61</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>2.0657</v>
+        <v>0.5617</v>
       </c>
       <c r="L116" s="4" t="n">
-        <v>2.0433</v>
+        <v>0.8981999999999999</v>
       </c>
       <c r="M116" s="4" t="n">
-        <v>2.0361</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="N116" s="4" t="n">
-        <v>1.7568</v>
+        <v>267.6647</v>
       </c>
       <c r="O116" s="4" t="n">
-        <v>0.4642</v>
+        <v>0.346</v>
       </c>
       <c r="P116" s="4" t="n">
-        <v>3.4222</v>
+        <v>0.9277</v>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
@@ -7201,53 +7201,53 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>LOGO</t>
+          <t>HTTBT</t>
         </is>
       </c>
       <c r="B117" s="6" t="n">
-        <v>120.6</v>
+        <v>30.82</v>
       </c>
       <c r="C117" s="7" t="n">
-        <v>-0.0519</v>
+        <v>0.0172</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>-0.1537</v>
+        <v>-0.0393</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>-0.1286</v>
+        <v>-0.0575</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>-0.1324</v>
+        <v>-0.1746</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>-0.1549</v>
+        <v>-0.2769</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>-0.1971</v>
+        <v>-0.3343</v>
       </c>
       <c r="I117" s="6" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>13.11</v>
+        <v>22.49</v>
       </c>
       <c r="K117" s="7" t="n">
-        <v>0.5617</v>
+        <v>0.3957</v>
       </c>
       <c r="L117" s="7" t="n">
-        <v>0.8981999999999999</v>
+        <v>0.3631</v>
       </c>
       <c r="M117" s="7" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.3492</v>
       </c>
       <c r="N117" s="7" t="n">
-        <v>267.6647</v>
+        <v>0.2572</v>
       </c>
       <c r="O117" s="7" t="n">
-        <v>0.346</v>
+        <v>0.4235</v>
       </c>
       <c r="P117" s="7" t="n">
-        <v>0.9277</v>
+        <v>0.5921</v>
       </c>
       <c r="Q117" s="5" t="inlineStr">
         <is>
@@ -7259,53 +7259,53 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>HTTBT</t>
+          <t>ARDYZ</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>30.3</v>
+        <v>59.85</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>-0.027</v>
+        <v>0.0992</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>-0.0873</v>
+        <v>-0.0973</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>-0.07339999999999999</v>
+        <v>0.0187</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>-0.1784</v>
+        <v>-0.1351</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>-0.2891</v>
+        <v>0.3951</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>-0.3378</v>
+        <v>1.3959</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>22.11</v>
+        <v>14.9</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0.3957</v>
+        <v>2.0657</v>
       </c>
       <c r="L118" s="4" t="n">
-        <v>0.3631</v>
+        <v>2.0433</v>
       </c>
       <c r="M118" s="4" t="n">
-        <v>0.3492</v>
+        <v>2.0361</v>
       </c>
       <c r="N118" s="4" t="n">
-        <v>0.2572</v>
+        <v>1.7568</v>
       </c>
       <c r="O118" s="4" t="n">
-        <v>0.4235</v>
+        <v>0.4642</v>
       </c>
       <c r="P118" s="4" t="n">
-        <v>0.5921</v>
+        <v>3.4222</v>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
@@ -7317,57 +7317,57 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>ATATP</t>
+          <t>PKART</t>
         </is>
       </c>
       <c r="B119" s="6" t="n">
-        <v>203</v>
+        <v>80</v>
       </c>
       <c r="C119" s="7" t="n">
-        <v>-0.06059999999999999</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>-0.1409</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>-0.234</v>
+        <v>-0.1753</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>-0.1735</v>
+        <v>-0.4118</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>0.3914</v>
+        <v>-0.2</v>
       </c>
       <c r="H119" s="7" t="n">
-        <v>0.5172</v>
+        <v>0.0139</v>
       </c>
       <c r="I119" s="6" t="n">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>4.18</v>
+        <v>17.69</v>
       </c>
       <c r="K119" s="7" t="n">
-        <v>0.3072</v>
+        <v>0.5093</v>
       </c>
       <c r="L119" s="7" t="n">
-        <v>0.2985</v>
+        <v>1.5572</v>
       </c>
       <c r="M119" s="7" t="n">
-        <v>0.3487</v>
+        <v>1.6598</v>
       </c>
       <c r="N119" s="7" t="n">
-        <v>0.6609999999999999</v>
+        <v>4.8022</v>
       </c>
       <c r="O119" s="7" t="n">
-        <v>0.3268</v>
+        <v>0.083</v>
       </c>
       <c r="P119" s="7" t="n">
-        <v>0.7543000000000001</v>
+        <v>0.2041</v>
       </c>
       <c r="Q119" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R119" s="5" t="inlineStr"/>
@@ -7375,57 +7375,57 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>PKART</t>
+          <t>ATATP</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>79.3</v>
+        <v>208.8</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>-0.061</v>
+        <v>0.0286</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>-0.1688</v>
+        <v>-0.1062</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>-0.1825</v>
+        <v>-0.2121</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>-0.4642</v>
+        <v>-0.1411</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>-0.207</v>
+        <v>0.4311</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>-0.027</v>
+        <v>0.6286999999999999</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>17.53</v>
+        <v>4.3</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0.5093</v>
+        <v>0.3072</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>1.5572</v>
+        <v>0.2985</v>
       </c>
       <c r="M120" s="4" t="n">
-        <v>1.6598</v>
+        <v>0.3487</v>
       </c>
       <c r="N120" s="4" t="n">
-        <v>4.8022</v>
+        <v>0.6609999999999999</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>0.083</v>
+        <v>0.3268</v>
       </c>
       <c r="P120" s="4" t="n">
-        <v>0.2041</v>
+        <v>0.7543000000000001</v>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr"/>
@@ -7437,31 +7437,31 @@
         </is>
       </c>
       <c r="B121" s="6" t="n">
-        <v>356.25</v>
+        <v>373.25</v>
       </c>
       <c r="C121" s="7" t="n">
-        <v>-0.0443</v>
+        <v>0.04769999999999999</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>-0.1498</v>
+        <v>-0.08460000000000001</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-0.1725</v>
+        <v>-0.133</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>-0.141</v>
+        <v>-0.1166</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>-0.3129</v>
+        <v>-0.2801</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>0.2966</v>
+        <v>0.3786</v>
       </c>
       <c r="I121" s="6" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="J121" s="6" t="n">
-        <v>15.44</v>
+        <v>16.18</v>
       </c>
       <c r="K121" s="7" t="n">
         <v>0.1897</v>
@@ -7495,31 +7495,31 @@
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>17.05</v>
+        <v>17</v>
       </c>
       <c r="C122" s="4" t="n">
-        <v>-0.0318</v>
+        <v>-0.0029</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>-0.1157</v>
+        <v>-0.09570000000000001</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>-0.1492</v>
+        <v>-0.1517</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>-0.2429</v>
+        <v>-0.2342</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>-0.207</v>
+        <v>-0.2093</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>0.1443</v>
+        <v>0.1806</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>22.45</v>
+        <v>22.39</v>
       </c>
       <c r="K122" s="4" t="n">
         <v>0.6388</v>
@@ -7553,28 +7553,28 @@
         </is>
       </c>
       <c r="B123" s="6" t="n">
-        <v>28.82</v>
+        <v>28.52</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>-0.0393</v>
+        <v>-0.0104</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>-0.0851</v>
+        <v>-0.08650000000000001</v>
       </c>
       <c r="E123" s="7" t="n">
-        <v>-0.2788</v>
+        <v>-0.2863</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>-0.3802</v>
+        <v>-0.3776</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>-0.4784</v>
+        <v>-0.4838</v>
       </c>
       <c r="H123" s="7" t="n">
-        <v>-0.1728</v>
+        <v>-0.1781</v>
       </c>
       <c r="I123" s="6" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="J123" s="5" t="inlineStr"/>
       <c r="K123" s="7" t="n">
@@ -7605,57 +7605,57 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>YEOTK</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>121.5</v>
+        <v>24.96</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>0.09949999999999999</v>
+        <v>0.0365</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>-0.0508</v>
+        <v>-0.0803</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>-0.3215999999999999</v>
+        <v>-0.159</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>-0.3988</v>
+        <v>-0.3937</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>-0.1321</v>
+        <v>0.08470000000000001</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>2.4814</v>
+        <v>0.7748</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>3.58</v>
+        <v>3.76</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>13.53</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1.164</v>
+        <v>1.4662</v>
       </c>
       <c r="L124" s="4" t="n">
-        <v>0.8115000000000001</v>
+        <v>1.5472</v>
       </c>
       <c r="M124" s="4" t="n">
-        <v>1.571</v>
+        <v>1.7095</v>
       </c>
       <c r="N124" s="4" t="n">
-        <v>1.7066</v>
+        <v>3.7317</v>
       </c>
       <c r="O124" s="4" t="n">
-        <v>0.1178</v>
+        <v>0.1898</v>
       </c>
       <c r="P124" s="4" t="n">
-        <v>0.3402000000000001</v>
+        <v>0.7681999999999999</v>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr"/>
@@ -7663,57 +7663,57 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>YEOTK</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B125" s="6" t="n">
-        <v>24.08</v>
+        <v>165.9</v>
       </c>
       <c r="C125" s="7" t="n">
-        <v>-0.0251</v>
+        <v>0.033</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>-0.1406</v>
+        <v>-0.1553</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-0.1887</v>
+        <v>-0.3557</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>-0.3803</v>
+        <v>-0.4484</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>0.04650000000000001</v>
+        <v>-0.2334</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>0.6736</v>
+        <v>0.7121</v>
       </c>
       <c r="I125" s="6" t="n">
-        <v>3.63</v>
+        <v>3.78</v>
       </c>
       <c r="J125" s="6" t="n">
-        <v>8.98</v>
+        <v>16.27</v>
       </c>
       <c r="K125" s="7" t="n">
-        <v>1.4662</v>
+        <v>0.4338</v>
       </c>
       <c r="L125" s="7" t="n">
-        <v>1.5472</v>
+        <v>0.5232</v>
       </c>
       <c r="M125" s="7" t="n">
-        <v>1.7095</v>
+        <v>0.7125</v>
       </c>
       <c r="N125" s="7" t="n">
-        <v>3.7317</v>
+        <v>0.8672</v>
       </c>
       <c r="O125" s="7" t="n">
-        <v>0.1898</v>
+        <v>0.3018</v>
       </c>
       <c r="P125" s="7" t="n">
-        <v>0.7681999999999999</v>
+        <v>0.3122</v>
       </c>
       <c r="Q125" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R125" s="5" t="inlineStr"/>
@@ -7721,57 +7721,57 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>160.6</v>
+        <v>131</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>-0.0261</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>-0.2242</v>
+        <v>0.0108</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>-0.3763</v>
+        <v>-0.2686</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>-0.4651</v>
+        <v>-0.3327000000000001</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>-0.2579</v>
+        <v>-0.0643</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>0.7325</v>
+        <v>2.649</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>3.66</v>
+        <v>3.86</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>15.75</v>
+        <v>14.59</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0.4338</v>
+        <v>1.164</v>
       </c>
       <c r="L126" s="4" t="n">
-        <v>0.5232</v>
+        <v>0.8115000000000001</v>
       </c>
       <c r="M126" s="4" t="n">
-        <v>0.7125</v>
+        <v>1.571</v>
       </c>
       <c r="N126" s="4" t="n">
-        <v>0.8672</v>
+        <v>1.7066</v>
       </c>
       <c r="O126" s="4" t="n">
-        <v>0.3018</v>
+        <v>0.1178</v>
       </c>
       <c r="P126" s="4" t="n">
-        <v>0.3122</v>
+        <v>0.3402000000000001</v>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr"/>
@@ -7783,31 +7783,31 @@
         </is>
       </c>
       <c r="B127" s="6" t="n">
-        <v>88.8</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="C127" s="7" t="n">
-        <v>-0.0452</v>
+        <v>0.0175</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>-0.1208</v>
+        <v>-0.0185</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>-0.2318</v>
+        <v>-0.2184</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>-0.6705</v>
+        <v>-0.6618999999999999</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>-0.6909000000000001</v>
+        <v>-0.6855</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>-0.4443</v>
+        <v>-0.4786</v>
       </c>
       <c r="I127" s="6" t="n">
-        <v>4.19</v>
+        <v>4.27</v>
       </c>
       <c r="J127" s="6" t="n">
-        <v>29.32</v>
+        <v>29.84</v>
       </c>
       <c r="K127" s="7" t="n">
         <v>0.5028</v>
@@ -7837,57 +7837,57 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>DOCO</t>
+          <t>FMIZP</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>10837.5</v>
+        <v>216.2</v>
       </c>
       <c r="C128" s="4" t="n">
-        <v>-0.0236</v>
+        <v>0.0174</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>0.0014</v>
+        <v>-0.1685</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>0.0207</v>
+        <v>-0.2394</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>-0.0048</v>
+        <v>-0.2467</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>0.1155</v>
+        <v>-0.259</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>0.0162</v>
+        <v>-0.2935</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>19.9</v>
+        <v>21.87</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0.2032</v>
+        <v>0.2837</v>
       </c>
       <c r="L128" s="4" t="n">
-        <v>0.2156</v>
+        <v>0.7895</v>
       </c>
       <c r="M128" s="4" t="n">
-        <v>0.2435</v>
+        <v>0.1712</v>
       </c>
       <c r="N128" s="4" t="n">
-        <v>0.2464</v>
+        <v>0.9815999999999999</v>
       </c>
       <c r="O128" s="4" t="n">
-        <v>0.1211</v>
+        <v>0.1378</v>
       </c>
       <c r="P128" s="4" t="n">
-        <v>0.2497</v>
+        <v>0.2179</v>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr"/>
@@ -7895,57 +7895,57 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>FMIZP</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="n">
-        <v>212.5</v>
+          <t>DOCO</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="n">
+        <v>11200</v>
       </c>
       <c r="C129" s="7" t="n">
-        <v>-0.0513</v>
+        <v>0.0334</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>-0.2122</v>
+        <v>0.0443</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>-0.2524</v>
+        <v>0.0549</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>-0.2685</v>
+        <v>0.0226</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>-0.2716</v>
+        <v>0.1529</v>
       </c>
       <c r="H129" s="7" t="n">
-        <v>-0.3056</v>
+        <v>0.0669</v>
       </c>
       <c r="I129" s="6" t="n">
-        <v>4.26</v>
+        <v>4.39</v>
       </c>
       <c r="J129" s="6" t="n">
-        <v>21.5</v>
+        <v>20.57</v>
       </c>
       <c r="K129" s="7" t="n">
-        <v>0.2837</v>
+        <v>0.2032</v>
       </c>
       <c r="L129" s="7" t="n">
-        <v>0.7895</v>
+        <v>0.2156</v>
       </c>
       <c r="M129" s="7" t="n">
-        <v>0.1712</v>
+        <v>0.2435</v>
       </c>
       <c r="N129" s="7" t="n">
-        <v>0.9815999999999999</v>
+        <v>0.2464</v>
       </c>
       <c r="O129" s="7" t="n">
-        <v>0.1378</v>
+        <v>0.1211</v>
       </c>
       <c r="P129" s="7" t="n">
-        <v>0.2179</v>
+        <v>0.2497</v>
       </c>
       <c r="Q129" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R129" s="5" t="inlineStr"/>
@@ -7960,22 +7960,22 @@
         <v>6.83</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>0.0134</v>
+        <v>0</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>-0.05139999999999999</v>
+        <v>0.0044</v>
       </c>
       <c r="E130" s="4" t="n">
         <v>-0.4265</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>-0.4746</v>
+        <v>-0.4685</v>
       </c>
       <c r="G130" s="4" t="n">
         <v>0.3996</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>1.0999</v>
+        <v>1.1614</v>
       </c>
       <c r="I130" s="3" t="n">
         <v>4.79</v>
@@ -8015,31 +8015,31 @@
         </is>
       </c>
       <c r="B131" s="6" t="n">
-        <v>322.25</v>
+        <v>342.75</v>
       </c>
       <c r="C131" s="7" t="n">
-        <v>-0.0529</v>
+        <v>0.0636</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>-0.08449999999999999</v>
+        <v>0.0007000000000000001</v>
       </c>
       <c r="E131" s="7" t="n">
-        <v>-0.1514</v>
+        <v>-0.0974</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>-0.0935</v>
+        <v>-0.0532</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>-0.1924</v>
+        <v>-0.141</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>0.5797</v>
+        <v>0.755</v>
       </c>
       <c r="I131" s="6" t="n">
-        <v>4.79</v>
+        <v>5.1</v>
       </c>
       <c r="J131" s="6" t="n">
-        <v>39.59</v>
+        <v>42.11</v>
       </c>
       <c r="K131" s="7" t="n">
         <v>0.5623</v>
@@ -8073,28 +8073,28 @@
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>20.6</v>
+        <v>20.64</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>-0.0436</v>
+        <v>0.0019</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>-0.178</v>
+        <v>-0.1527</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>-0.2797</v>
+        <v>-0.2783</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>-0.4032</v>
+        <v>-0.4169</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>-0.4966</v>
+        <v>-0.4956</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>-0.3444</v>
+        <v>-0.3359</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>5.98</v>
+        <v>5.99</v>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="4" t="n">
@@ -8129,28 +8129,28 @@
         </is>
       </c>
       <c r="B133" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>-0.0213</v>
+        <v>0.0022</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>-0.0366</v>
+        <v>-0.0446</v>
       </c>
       <c r="E133" s="7" t="n">
-        <v>-0.3255</v>
+        <v>-0.324</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>-0.2923</v>
+        <v>-0.3119</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>0.262</v>
+        <v>0.2647</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>0.758</v>
+        <v>0.7845</v>
       </c>
       <c r="I133" s="6" t="n">
-        <v>6.65</v>
+        <v>6.66</v>
       </c>
       <c r="J133" s="5" t="inlineStr"/>
       <c r="K133" s="7" t="n">
@@ -8185,28 +8185,28 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>12.42</v>
+        <v>12.36</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>-0.0541</v>
+        <v>-0.0048</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>0.08</v>
+        <v>-0.0214</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>0.3185</v>
+        <v>0.3121</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>-0.05690000000000001</v>
+        <v>-0.0594</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>0.5296</v>
+        <v>0.5222</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>0.4364</v>
+        <v>0.4284000000000001</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>10.08</v>
+        <v>10.03</v>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="4" t="n">
@@ -8241,28 +8241,28 @@
         </is>
       </c>
       <c r="B135" s="8" t="n">
-        <v>1150</v>
+        <v>1163</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>-0.048</v>
+        <v>0.0113</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>-0.136</v>
+        <v>-0.1026</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>-0.2754</v>
+        <v>-0.2672</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>-0.3618</v>
+        <v>-0.34</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>-0.2712</v>
+        <v>-0.263</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>-0.341</v>
+        <v>-0.3135</v>
       </c>
       <c r="I135" s="6" t="n">
-        <v>10.21</v>
+        <v>10.33</v>
       </c>
       <c r="J135" s="5" t="inlineStr"/>
       <c r="K135" s="7" t="n">
@@ -8297,31 +8297,31 @@
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>35.02</v>
+        <v>34.98</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>-0.0596</v>
+        <v>-0.0011</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>-0.2016</v>
+        <v>-0.1468</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>-0.08470000000000001</v>
+        <v>-0.0857</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>-0.3515</v>
+        <v>-0.34</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>-0.176</v>
+        <v>-0.1769</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>-0.208</v>
+        <v>-0.2976</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>10.73</v>
+        <v>10.72</v>
       </c>
       <c r="J136" s="3" t="n">
-        <v>38.62</v>
+        <v>38.58</v>
       </c>
       <c r="K136" s="4" t="n">
         <v>0.2618</v>
@@ -8355,28 +8355,28 @@
         </is>
       </c>
       <c r="B137" s="6" t="n">
-        <v>249.5</v>
+        <v>249.4</v>
       </c>
       <c r="C137" s="7" t="n">
-        <v>-0.0244</v>
+        <v>-0.0004</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>-0.09269999999999999</v>
+        <v>-0.09880000000000001</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>-0.2215</v>
+        <v>-0.2218</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>-0.2972</v>
+        <v>-0.3004</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>-0.4167</v>
+        <v>-0.4169</v>
       </c>
       <c r="H137" s="7" t="n">
-        <v>-0.5207999999999999</v>
+        <v>-0.5203</v>
       </c>
       <c r="I137" s="6" t="n">
-        <v>10.74</v>
+        <v>10.73</v>
       </c>
       <c r="J137" s="5" t="inlineStr"/>
       <c r="K137" s="7" t="n">
@@ -8411,28 +8411,28 @@
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>38.1</v>
+        <v>38.3</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>-0.0231</v>
+        <v>0.0052</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>-0.0241</v>
+        <v>-0.0052</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>-0.2062</v>
+        <v>-0.2021</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>-0.1526</v>
+        <v>-0.1515</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>-0.1051</v>
+        <v>-0.1004</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>0.1962</v>
+        <v>0.2035</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>14.22</v>
+        <v>14.3</v>
       </c>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="4" t="n">
@@ -8467,31 +8467,31 @@
         </is>
       </c>
       <c r="B139" s="6" t="n">
-        <v>94.59999999999999</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="C139" s="7" t="n">
-        <v>-0.0381</v>
+        <v>0.0132</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>-0.1241</v>
+        <v>-0.0906</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>-0.2143</v>
+        <v>-0.2039</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>-0.2795</v>
+        <v>-0.2564</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>-0.3776</v>
+        <v>-0.3694</v>
       </c>
       <c r="H139" s="7" t="n">
-        <v>-0.4117</v>
+        <v>-0.4047</v>
       </c>
       <c r="I139" s="6" t="n">
-        <v>14.39</v>
+        <v>14.58</v>
       </c>
       <c r="J139" s="6" t="n">
-        <v>54.21</v>
+        <v>54.92</v>
       </c>
       <c r="K139" s="7" t="n">
         <v>0.3045</v>
@@ -8525,25 +8525,25 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>68.5</v>
+        <v>70</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>-0.0446</v>
+        <v>0.0219</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>-0.1752</v>
+        <v>-0.1463</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>-0.1438</v>
+        <v>-0.125</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.1111</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>0.0873</v>
+        <v>0.1111</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>-0.0352</v>
+        <v>-0.0014</v>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr"/>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>19.10.2026 20:40</t>
+          <t>20.10.2026 19:27</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_latest.xlsx
+++ b/data/bist_screener_latest.xlsx
@@ -583,28 +583,28 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13.05</v>
+        <v>12.13</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0.0333</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.2176</v>
+        <v>-0.2123</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.4759</v>
+        <v>-0.4908</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-0.41</v>
+        <v>-0.4661</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.5857</v>
+        <v>-0.6095</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.3376</v>
+        <v>-0.3767</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="4" t="n">
@@ -635,57 +635,57 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>MERIT</t>
+          <t>SRVGY</t>
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>13.29</v>
+        <v>2.05</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>0.0231</v>
+        <v>-0.033</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>0.0038</v>
+        <v>-0.0682</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>-0.1032</v>
+        <v>-0.0421</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>-0.2037</v>
+        <v>-0.2054</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>-0.207</v>
+        <v>-0.3653</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-0.3247</v>
+        <v>-0.3121</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>6.18</v>
+        <v>2.23</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>0.9854999999999999</v>
+        <v>2.7227</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>1.0319</v>
+        <v>2.5294</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>2.0871</v>
+        <v>2.9903</v>
       </c>
       <c r="N3" s="7" t="n">
-        <v>1.5834</v>
+        <v>0.3421</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>0.6354</v>
+        <v>0.6722</v>
       </c>
       <c r="P3" s="7" t="n">
-        <v>0.0454</v>
+        <v>0.1107</v>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr"/>
@@ -693,57 +693,57 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SRVGY</t>
+          <t>MERIT</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2.12</v>
+        <v>13.4</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.0341</v>
+        <v>0.0083</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.0493</v>
+        <v>0.019</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.0275</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.1783</v>
+        <v>-0.1884</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.3517</v>
+        <v>-0.1859</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.2765</v>
+        <v>-0.3463000000000001</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0.22</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>2.31</v>
+        <v>6.23</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2.7227</v>
+        <v>0.9854999999999999</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>2.5294</v>
+        <v>1.0319</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>2.9903</v>
+        <v>2.0871</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.3421</v>
+        <v>1.5834</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.6722</v>
+        <v>0.6354</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.1107</v>
+        <v>0.0454</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr"/>
@@ -751,57 +751,55 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>HLGYO</t>
+          <t>SNICA</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>3.97</v>
+        <v>1.95</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>0.0232</v>
+        <v>-0.0394</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-0.0457</v>
+        <v>-0.1295</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-0.0364</v>
+        <v>-0.2323</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>-0.2808</v>
+        <v>-0.4961</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-0.3225</v>
+        <v>-0.529</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.1507</v>
+        <v>-0.6061</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>1.18</v>
-      </c>
+        <v>0.22</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr"/>
       <c r="K5" s="7" t="n">
-        <v>1.7259</v>
+        <v>0.2451</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.4642</v>
+        <v>0.1328</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>2.8476</v>
+        <v>0.7476999999999999</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>2.0883</v>
+        <v>0.4518</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>0.1249</v>
+        <v>0.0576</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>0.2374</v>
+        <v>-0.1748</v>
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R5" s="5" t="inlineStr"/>
@@ -809,57 +807,57 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IHEVA</t>
+          <t>HLGYO</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1.54</v>
+        <v>3.91</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.0694</v>
+        <v>-0.0151</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0375</v>
+        <v>-0.0713</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1585</v>
+        <v>-0.0322</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2376</v>
+        <v>-0.2904</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3156</v>
+        <v>-0.3224</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3583</v>
+        <v>0.1108</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>8.619999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2518</v>
+        <v>1.7259</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.322</v>
+        <v>1.4642</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2038</v>
+        <v>2.8476</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1672</v>
+        <v>2.0883</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.078</v>
+        <v>0.1249</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.0331</v>
+        <v>0.2374</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr"/>
@@ -867,55 +865,57 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>SNICA</t>
+          <t>IHEVA</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2.03</v>
+        <v>1.52</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>0.0357</v>
+        <v>-0.013</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-0.0978</v>
+        <v>-0.0256</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-0.2951</v>
+        <v>-0.1314</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>-0.4795</v>
+        <v>-0.2475</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-0.5155</v>
+        <v>-0.3184</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.3821</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0.23</v>
       </c>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="J7" s="6" t="n">
+        <v>8.51</v>
+      </c>
       <c r="K7" s="7" t="n">
-        <v>0.2451</v>
+        <v>0.2518</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.1328</v>
+        <v>0.322</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.7476999999999999</v>
+        <v>0.2038</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>0.4518</v>
+        <v>0.1672</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>0.0576</v>
+        <v>0.078</v>
       </c>
       <c r="P7" s="7" t="n">
-        <v>-0.1748</v>
+        <v>0.0331</v>
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr"/>
@@ -927,28 +927,28 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>9.23</v>
+        <v>9.08</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.006500000000000001</v>
+        <v>-0.0163</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1021</v>
+        <v>-0.1019</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.139</v>
+        <v>-0.1303</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2111</v>
+        <v>-0.2292</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2856</v>
+        <v>-0.2906</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2789</v>
+        <v>-0.2906</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="4" t="n">
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.0258</v>
+        <v>-0.0293</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-0.0245</v>
+        <v>-0.0683</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-0.0245</v>
+        <v>-0.05690000000000001</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>-0.1372</v>
+        <v>-0.1714</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-0.1672</v>
+        <v>-0.1831</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-0.03240000000000001</v>
+        <v>-0.1179</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>5.61</v>
+        <v>5.45</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>0.3848</v>
@@ -1041,31 +1041,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9.02</v>
+        <v>8.82</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.0273</v>
+        <v>-0.0222</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1034</v>
+        <v>-0.0851</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1918</v>
+        <v>-0.1718</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2231</v>
+        <v>-0.2644</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2853</v>
+        <v>-0.2989</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.287</v>
+        <v>-0.3039</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.24</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>10.74</v>
+        <v>10.5</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0.3203</v>
@@ -1095,55 +1095,57 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>AGYO</t>
+          <t>GSDHO</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>6.25</v>
+        <v>3.93</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0415</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>-0.0727</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-0.1667</v>
+        <v>-0.05980000000000001</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>-0.2586</v>
+        <v>-0.2944</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-0.2664</v>
+        <v>-0.2202</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-0.1497</v>
+        <v>-0.0796</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J11" s="5" t="inlineStr"/>
+        <v>0.24</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>14.08</v>
+      </c>
       <c r="K11" s="7" t="n">
-        <v>0.4383</v>
+        <v>0.1479</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.5475</v>
+        <v>0.2201</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.6032</v>
+        <v>0.3072</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>0.6481999999999999</v>
+        <v>0.5201</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>0.3352000000000001</v>
+        <v>0.6869</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>-0.0354</v>
+        <v>0.0197</v>
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr"/>
@@ -1151,57 +1153,55 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GSDHO</t>
+          <t>AGYO</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4.1</v>
+        <v>6.29</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.0276</v>
+        <v>0.0064</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.04650000000000001</v>
+        <v>-0.0513</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.0596</v>
+        <v>-0.1348</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2665</v>
+        <v>-0.2244</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1961</v>
+        <v>-0.266</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.0353</v>
+        <v>-0.15</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="J12" s="3" t="n">
-        <v>14.69</v>
-      </c>
+      <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="n">
-        <v>0.1479</v>
+        <v>0.4383</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.2201</v>
+        <v>0.5475</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3072</v>
+        <v>0.6032</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.5201</v>
+        <v>0.6481999999999999</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.6869</v>
+        <v>0.3352000000000001</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.0197</v>
+        <v>-0.0354</v>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr"/>
@@ -1213,28 +1213,28 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>11.47</v>
+        <v>11.06</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.0026</v>
+        <v>-0.0357</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>-0.1754</v>
+        <v>-0.21</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>-0.3739</v>
+        <v>-0.3577</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>-0.5047</v>
+        <v>-0.5212</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-0.5704</v>
+        <v>-0.5710000000000001</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.715</v>
+        <v>-0.7241</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
       <c r="K13" s="7" t="n">
@@ -1269,28 +1269,28 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.002</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1655</v>
+        <v>-0.1581</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.0801</v>
+        <v>-0.05769999999999999</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2143</v>
+        <v>-0.212</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3141</v>
+        <v>-0.3196</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4326</v>
+        <v>-0.4372</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="n">
@@ -1325,31 +1325,31 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.0237</v>
+        <v>-0.0462</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>-0.1561</v>
+        <v>-0.2029</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-0.1173</v>
+        <v>-0.1316</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>-0.2586</v>
+        <v>-0.3028</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-0.3207</v>
+        <v>-0.3571</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.2929</v>
+        <v>-0.3293</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>8.16</v>
+        <v>7.78</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>0.9460999999999999</v>
@@ -1383,31 +1383,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>10.17</v>
+        <v>9.99</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.0252</v>
+        <v>-0.0177</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.096</v>
+        <v>-0.0843</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1732</v>
+        <v>-0.1633</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2201</v>
+        <v>-0.242</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2741</v>
+        <v>-0.2808</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.211</v>
+        <v>-0.2403</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.43</v>
+        <v>5.33</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>0.3789</v>
@@ -1441,28 +1441,28 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>-0.0135</v>
+        <v>-0.0479</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>-0.2022</v>
+        <v>-0.2446</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>-0.416</v>
+        <v>-0.4303</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>-0.6117</v>
+        <v>-0.6551</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>-0.6359</v>
+        <v>-0.6426999999999999</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-0.836</v>
+        <v>-0.8482999999999999</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="J17" s="5" t="inlineStr"/>
       <c r="K17" s="7" t="n">
@@ -1497,31 +1497,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>185</v>
+        <v>178.7</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.03240000000000001</v>
+        <v>-0.0341</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.0474</v>
+        <v>-0.0741</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.0329</v>
+        <v>-0.0614</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.0998</v>
+        <v>-0.147</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.0263</v>
+        <v>-0.0545</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.25</v>
+        <v>0.1993</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>0.5672999999999999</v>
@@ -1555,28 +1555,28 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>-0.0059</v>
+        <v>-0.0355</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>-0.1421</v>
+        <v>-0.1641</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>-0.4440999999999999</v>
+        <v>-0.3963</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>-0.6756</v>
+        <v>-0.6936</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.7495999999999999</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-0.5928</v>
+        <v>-0.6082</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="7" t="n">
@@ -1611,31 +1611,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>36.24</v>
+        <v>35.26</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.0208</v>
+        <v>-0.027</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.0362</v>
+        <v>-0.06570000000000001</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.0931</v>
+        <v>-0.11</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.1615</v>
+        <v>-0.1917</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2371</v>
+        <v>-0.2542</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.1009</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>9.1</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>0.2329</v>
@@ -1669,31 +1669,31 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>7</v>
+        <v>6.83</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>0.0219</v>
+        <v>-0.0243</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>-0.0667</v>
+        <v>-0.0808</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-0.2308</v>
+        <v>-0.2058</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>-0.3427</v>
+        <v>-0.3647</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-0.4093</v>
+        <v>-0.4132</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-0.2624</v>
+        <v>-0.2973</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>3.11</v>
+        <v>3.03</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>0.9081</v>
@@ -1723,53 +1723,53 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>DOHOL</t>
+          <t>KIMMR</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>17.65</v>
+        <v>9.34</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.0202</v>
+        <v>-0.0566</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.05110000000000001</v>
+        <v>-0.123</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1506</v>
+        <v>-0.185</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1457</v>
+        <v>-0.3931</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1783</v>
+        <v>-0.4663</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.0091</v>
+        <v>-0.303</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>7.13</v>
+        <v>3.51</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.1285</v>
+        <v>0.4985</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.8243</v>
+        <v>0.2399</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.9048</v>
+        <v>0.6479</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.2086</v>
+        <v>1.3415</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.1116</v>
+        <v>0.0858</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1027</v>
+        <v>0.1449</v>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
@@ -1781,53 +1781,53 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>KIMMR</t>
+          <t>DOHOL</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>9.9</v>
+        <v>17.29</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>0.0217</v>
+        <v>-0.0204</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>-0.0722</v>
+        <v>-0.0613</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>-0.1695</v>
+        <v>-0.1441</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>-0.3465</v>
+        <v>-0.1898</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-0.4359</v>
+        <v>-0.1852</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-0.2302</v>
+        <v>-0.0052</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>3.72</v>
+        <v>6.99</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.4985</v>
+        <v>0.1285</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.2399</v>
+        <v>0.8243</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.6479</v>
+        <v>1.9048</v>
       </c>
       <c r="N23" s="7" t="n">
-        <v>1.3415</v>
+        <v>2.2086</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>0.0858</v>
+        <v>0.1116</v>
       </c>
       <c r="P23" s="7" t="n">
-        <v>0.1449</v>
+        <v>0.1027</v>
       </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
@@ -1839,57 +1839,55 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>YUNSA</t>
+          <t>ERBOS</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>5.53</v>
+        <v>97.5</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.0375</v>
+        <v>-0.0552</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.1037</v>
+        <v>-0.1341</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.1722</v>
+        <v>-0.1882</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.4172999999999999</v>
+        <v>-0.4119</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3828</v>
+        <v>-0.5196999999999999</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2211</v>
+        <v>-0.4637</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>6.64</v>
-      </c>
+        <v>0.49</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="4" t="n">
-        <v>0.6883</v>
+        <v>0.2349</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.8734999999999999</v>
+        <v>1.1405</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.1469</v>
+        <v>1.0386</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.3327</v>
+        <v>0.7831999999999999</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.1078</v>
+        <v>0.131</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.09</v>
+        <v>-0.023</v>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr"/>
@@ -1897,55 +1895,57 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>ERBOS</t>
+          <t>YUNSA</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>103.2</v>
+        <v>5.38</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>0.0424</v>
+        <v>-0.0271</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>-0.121</v>
+        <v>-0.1166</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-0.2565</v>
+        <v>-0.1836</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>-0.3772</v>
+        <v>-0.4152</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>-0.4894</v>
+        <v>-0.3935</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-0.4267</v>
+        <v>-0.2412</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="J25" s="5" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>6.46</v>
+      </c>
       <c r="K25" s="7" t="n">
-        <v>0.2349</v>
+        <v>0.6883</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>1.1405</v>
+        <v>0.8734999999999999</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>1.0386</v>
+        <v>1.1469</v>
       </c>
       <c r="N25" s="7" t="n">
-        <v>0.7831999999999999</v>
+        <v>1.3327</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>0.131</v>
+        <v>0.1078</v>
       </c>
       <c r="P25" s="7" t="n">
-        <v>-0.023</v>
+        <v>0.09</v>
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R25" s="5" t="inlineStr"/>
@@ -1953,53 +1953,53 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>OYYAT</t>
+          <t>SEKFK</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>24.88</v>
+        <v>3.24</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.0103</v>
+        <v>-0.1</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.0703</v>
+        <v>-0.2059</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.1707</v>
+        <v>-0.19</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3394</v>
+        <v>-0.3684000000000001</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5635</v>
+        <v>-0.4815</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.5341</v>
+        <v>-0.2671</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>3.19</v>
+        <v>2.63</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.045</v>
+        <v>0.208</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.4061999999999999</v>
+        <v>0.0571</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.4311</v>
+        <v>0.0025</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3.0744</v>
+        <v>0.2707</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.2671</v>
+        <v>0.6072</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.2126</v>
+        <v>0.2346</v>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
@@ -2015,31 +2015,31 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>31.12</v>
+        <v>29.28</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>0.0271</v>
+        <v>-0.0591</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>-0.08689999999999999</v>
+        <v>-0.1133</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-0.1073</v>
+        <v>-0.1368</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>-0.1119</v>
+        <v>-0.1625</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>-0.0281</v>
+        <v>-0.0645</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>0.2478</v>
+        <v>0.142</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>17.01</v>
+        <v>16.01</v>
       </c>
       <c r="K27" s="7" t="n">
         <v>0.3105</v>
@@ -2069,57 +2069,57 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KRSTL</t>
+          <t>OYYAT</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>6.72</v>
+        <v>23.74</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.0338</v>
+        <v>-0.0458</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1227</v>
+        <v>-0.1062</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.161</v>
+        <v>-0.0925</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3606</v>
+        <v>-0.3818</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2843</v>
+        <v>-0.5817</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.3463000000000001</v>
+        <v>-0.5542</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.87</v>
+        <v>3.04</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.3806</v>
+        <v>0.045</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2571</v>
+        <v>0.4061999999999999</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.5529999999999999</v>
+        <v>0.4311</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.6774</v>
+        <v>3.0744</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.1192</v>
+        <v>0.2671</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.1788</v>
+        <v>0.2126</v>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr"/>
@@ -2127,57 +2127,57 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>SEKFK</t>
+          <t>KRSTL</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>3.6</v>
+        <v>6.36</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>0.0345</v>
+        <v>-0.0536</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>-0.1408</v>
+        <v>-0.152</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.204</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>-0.3231</v>
+        <v>-0.4011</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>-0.4066</v>
+        <v>-0.3139</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>-0.167</v>
+        <v>-0.3994</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>2.92</v>
+        <v>3.66</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.208</v>
+        <v>0.3806</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0571</v>
+        <v>0.2571</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.0025</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="N29" s="7" t="n">
-        <v>0.2707</v>
+        <v>0.6774</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>0.6072</v>
+        <v>0.1192</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>0.2346</v>
+        <v>0.1788</v>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R29" s="5" t="inlineStr"/>
@@ -2189,28 +2189,28 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>27.5</v>
+        <v>26.68</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.0277</v>
+        <v>-0.0298</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.0864</v>
+        <v>-0.1011</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2125</v>
+        <v>-0.2162</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4712</v>
+        <v>-0.463</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.373</v>
+        <v>-0.3878</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.26</v>
+        <v>-0.2746</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="4" t="n">
@@ -2245,28 +2245,28 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>0.0965</v>
+        <v>-0.0282</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>-0.0565</v>
+        <v>-0.0548</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-0.1548</v>
+        <v>-0.0951</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>-0.2639</v>
+        <v>-0.2747</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>-0.1712</v>
+        <v>-0.1876</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>-0.0163</v>
+        <v>-0.0449</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="7" t="n">
@@ -2297,55 +2297,57 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DOKTA</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>14.15</v>
+        <v>3.14</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.0035</v>
+        <v>-0.0977</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.0794</v>
+        <v>-0.4042</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3338</v>
+        <v>-0.9</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3885</v>
+        <v>-0.9266</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4167</v>
+        <v>-0.8745999999999999</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3848</v>
+        <v>-0.9036</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr"/>
+        <v>0.59</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="K32" s="4" t="n">
-        <v>0.2983</v>
+        <v>7.8666</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.25</v>
+        <v>3.1929</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.5566</v>
+        <v>4.946499999999999</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.6970000000000001</v>
+        <v>1.0979</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.0852</v>
+        <v>0.4854</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.0451</v>
+        <v>0.586</v>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr"/>
@@ -2353,57 +2355,55 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TUREX</t>
+          <t>SOKE</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>5.21</v>
+        <v>7.4</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>0.0097</v>
+        <v>-0.0415</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>-0.1002</v>
+        <v>-0.0352</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-0.0151</v>
+        <v>-0.1284</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>-0.2304</v>
+        <v>-0.6076</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>-0.3899</v>
+        <v>-0.5889</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>-0.3303</v>
+        <v>-0.3333</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="J33" s="6" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>0.61</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr"/>
       <c r="K33" s="7" t="n">
-        <v>0.4159</v>
+        <v>0.5234000000000001</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>1.3967</v>
+        <v>0.4561</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.8518000000000001</v>
+        <v>0.4897</v>
       </c>
       <c r="N33" s="7" t="n">
-        <v>0.3205</v>
+        <v>0.3644</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>0.2638</v>
+        <v>0.032</v>
       </c>
       <c r="P33" s="7" t="n">
-        <v>0.0862</v>
+        <v>-0.0429</v>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R33" s="5" t="inlineStr"/>
@@ -2411,55 +2411,55 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SOKE</t>
+          <t>DOKTA</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>7.72</v>
+        <v>14.27</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0158</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.009000000000000001</v>
+        <v>-0.0499</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1717</v>
+        <v>-0.2915</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.5774</v>
+        <v>-0.3823</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.5907</v>
+        <v>-0.4232</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2975</v>
+        <v>-0.3812</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="4" t="n">
-        <v>0.5234000000000001</v>
+        <v>0.2983</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.4561</v>
+        <v>1.25</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.4897</v>
+        <v>3.5566</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.3644</v>
+        <v>0.6970000000000001</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.032</v>
+        <v>0.0852</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.0429</v>
+        <v>-0.0451</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr"/>
@@ -2467,57 +2467,57 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>AKMGY</t>
+          <t>PNLSN</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>189.8</v>
+        <v>29.22</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>0.0193</v>
+        <v>-0.0337</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>-0.0983</v>
+        <v>-0.1015</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-0.2052</v>
+        <v>-0.1722</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>-0.231</v>
+        <v>-0.4068</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>-0.3048</v>
+        <v>-0.377</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>-0.1605</v>
+        <v>-0.2343</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>9.35</v>
+        <v>8.24</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.3886</v>
+        <v>0.306</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.3887</v>
+        <v>0.6481</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.3141</v>
+        <v>0.5497</v>
       </c>
       <c r="N35" s="7" t="n">
-        <v>0.5958</v>
+        <v>7.793600000000001</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>0.6443000000000001</v>
+        <v>0.1302</v>
       </c>
       <c r="P35" s="7" t="n">
-        <v>0.0781</v>
+        <v>0.08839999999999999</v>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R35" s="5" t="inlineStr"/>
@@ -2529,31 +2529,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>5.16</v>
+        <v>5.04</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.0138</v>
+        <v>-0.0233</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>-0.0703</v>
+        <v>-0.0597</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>-0.1269</v>
+        <v>-0.1295</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>-0.4069</v>
+        <v>-0.4474</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.363</v>
+        <v>-0.362</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.4481</v>
+        <v>-0.4873</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>8.85</v>
+        <v>8.65</v>
       </c>
       <c r="K36" s="4" t="n">
         <v>1.6512</v>
@@ -2583,57 +2583,57 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>PNLSN</t>
+          <t>AKMGY</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>30.24</v>
+        <v>187.5</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>0.012</v>
+        <v>-0.0121</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>-0.0814</v>
+        <v>-0.0959</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-0.1923</v>
+        <v>-0.1848</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>-0.3538</v>
+        <v>-0.2322</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>-0.3636</v>
+        <v>-0.3249</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>-0.2008</v>
+        <v>-0.1607</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>8.529999999999999</v>
+        <v>9.24</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.306</v>
+        <v>0.3886</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>0.6481</v>
+        <v>0.3887</v>
       </c>
       <c r="M37" s="7" t="n">
-        <v>0.5497</v>
+        <v>0.3141</v>
       </c>
       <c r="N37" s="7" t="n">
-        <v>7.793600000000001</v>
+        <v>0.5958</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>0.1302</v>
+        <v>0.6443000000000001</v>
       </c>
       <c r="P37" s="7" t="n">
-        <v>0.08839999999999999</v>
+        <v>0.0781</v>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R37" s="5" t="inlineStr"/>
@@ -2641,57 +2641,57 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>MERCN</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>3.48</v>
+        <v>9.43</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>-0.0984</v>
+        <v>-0.0446</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>-0.4051</v>
+        <v>-0.1154</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>-0.9002</v>
+        <v>-0.382</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-0.9162</v>
+        <v>-0.6103000000000001</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.8634000000000001</v>
+        <v>-0.5846</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.8906999999999999</v>
+        <v>-0.7134</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>2.21</v>
+        <v>10.84</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>7.8666</v>
+        <v>0.2374</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>3.1929</v>
+        <v>0.8593999999999999</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>4.946499999999999</v>
+        <v>1.4059</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>1.0979</v>
+        <v>1.3031</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0.4854</v>
+        <v>0.1784</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0.586</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr"/>
@@ -2699,57 +2699,57 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>MERCN</t>
+          <t>TUREX</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>9.869999999999999</v>
+        <v>5.26</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>-0.0399</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.1009</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-0.3831</v>
+        <v>0.0499</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>-0.5978</v>
+        <v>-0.2581</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>-0.5625</v>
+        <v>-0.3701</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>-0.7341</v>
+        <v>-0.3222</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>11.34</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.2374</v>
+        <v>0.4159</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>0.8593999999999999</v>
+        <v>1.3967</v>
       </c>
       <c r="M39" s="7" t="n">
-        <v>1.4059</v>
+        <v>0.8518000000000001</v>
       </c>
       <c r="N39" s="7" t="n">
-        <v>1.3031</v>
+        <v>0.3205</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>0.1784</v>
+        <v>0.2638</v>
       </c>
       <c r="P39" s="7" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0862</v>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R39" s="5" t="inlineStr"/>
@@ -2757,57 +2757,57 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>BNTAS</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>208.4</v>
+        <v>4.84</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.0271</v>
+        <v>-0.0359</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0.0053</v>
+        <v>-0.0692</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>-0.0374</v>
+        <v>-0.1232</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.0332</v>
+        <v>-0.213</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.0072</v>
+        <v>-0.2882</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.3585</v>
+        <v>-0.2611</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>14.85</v>
+        <v>4.48</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.3261</v>
+        <v>0.2654</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.5440999999999999</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.9423</v>
+        <v>0.464</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>5.083299999999999</v>
+        <v>0.3679</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.0646</v>
+        <v>0.1363</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0.0771</v>
+        <v>0.1657</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr"/>
@@ -2815,57 +2815,57 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>BNTAS</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>5.02</v>
+        <v>203.3</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>0.048</v>
+        <v>-0.0245</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>-0.051</v>
+        <v>-0.0424</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-0.1345</v>
+        <v>-0.05309999999999999</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>-0.1851</v>
+        <v>-0.0068</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>-0.2661</v>
+        <v>-0.002</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>-0.2168</v>
+        <v>0.3074</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>4.65</v>
+        <v>14.49</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.2654</v>
+        <v>0.3261</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.5440999999999999</v>
       </c>
       <c r="M41" s="7" t="n">
-        <v>0.464</v>
+        <v>0.9423</v>
       </c>
       <c r="N41" s="7" t="n">
-        <v>0.3679</v>
+        <v>5.083299999999999</v>
       </c>
       <c r="O41" s="7" t="n">
-        <v>0.1363</v>
+        <v>0.0646</v>
       </c>
       <c r="P41" s="7" t="n">
-        <v>0.1657</v>
+        <v>0.0771</v>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="R41" s="5" t="inlineStr"/>
@@ -2877,31 +2877,31 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>51.2</v>
+        <v>49.4</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.023</v>
+        <v>-0.0352</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>-0.0154</v>
+        <v>-0.0509</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-0.0257</v>
+        <v>-0.0582</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-0.13</v>
+        <v>-0.1584</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-0.2123</v>
+        <v>-0.2214</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.064</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>6.33</v>
+        <v>6.11</v>
       </c>
       <c r="K42" s="4" t="n">
         <v>0.4498</v>
@@ -2931,57 +2931,57 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>PINSU</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>97.65000000000001</v>
+        <v>7.33</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>0.0151</v>
+        <v>-0.0355</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.0021</v>
+        <v>-0.1555</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-0.0076</v>
+        <v>-0.1989</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>-0.1281</v>
+        <v>-0.3659000000000001</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>-0.1589</v>
+        <v>-0.3992</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>0.0355</v>
+        <v>-0.482</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>10.97</v>
+        <v>15.45</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.3971</v>
+        <v>0.2802</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>0.4118</v>
+        <v>0.2234</v>
       </c>
       <c r="M43" s="7" t="n">
-        <v>0.3975</v>
+        <v>0.3074</v>
       </c>
       <c r="N43" s="7" t="n">
-        <v>0.2377</v>
+        <v>91.6451</v>
       </c>
       <c r="O43" s="7" t="n">
-        <v>0.4333</v>
+        <v>0.1329</v>
       </c>
       <c r="P43" s="7" t="n">
-        <v>0.1518</v>
+        <v>0.0528</v>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R43" s="5" t="inlineStr"/>
@@ -2989,57 +2989,57 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>PINSU</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>7.6</v>
+        <v>95</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.012</v>
+        <v>-0.0271</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>-0.1264</v>
+        <v>-0.0404</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>-0.1793</v>
+        <v>-0.0226</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>-0.3504</v>
+        <v>-0.1395</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-0.3896</v>
+        <v>-0.1645</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>-0.4847</v>
+        <v>-0.0186</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>16.02</v>
+        <v>10.67</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0.2802</v>
+        <v>0.3971</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.2234</v>
+        <v>0.4118</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.3074</v>
+        <v>0.3975</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>91.6451</v>
+        <v>0.2377</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>0.1329</v>
+        <v>0.4333</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>0.0528</v>
+        <v>0.1518</v>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr"/>
@@ -3047,57 +3047,57 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>AYGAZ</t>
+          <t>GRTHO</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>272.75</v>
+        <v>56.05</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>0.0196</v>
+        <v>-0.0411</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>-0.04969999999999999</v>
+        <v>-0.3702</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-0.1396</v>
+        <v>-0.6126</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>-0.0136</v>
+        <v>-0.7722</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0.0273</v>
+        <v>-0.769</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>0.5254</v>
+        <v>-0.9151</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>7.17</v>
+        <v>3.9</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.1662</v>
+        <v>0.5085000000000001</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>0.3683</v>
+        <v>0.4487</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>0.4549</v>
+        <v>0.2298</v>
       </c>
       <c r="N45" s="7" t="n">
-        <v>1.9624</v>
+        <v>0.9399</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>0.0302</v>
+        <v>0.1089</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>0.118</v>
+        <v>0.2287</v>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R45" s="5" t="inlineStr"/>
@@ -3105,57 +3105,57 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GRTHO</t>
+          <t>AYGAZ</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>58.45</v>
+        <v>270.25</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>-0.09939999999999999</v>
+        <v>-0.0092</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>-0.4087</v>
+        <v>-0.0808</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>-0.6363</v>
+        <v>-0.164</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-0.752</v>
+        <v>-0.0434</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-0.7598999999999999</v>
+        <v>-0.0173</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>-0.912</v>
+        <v>0.4931</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>4.07</v>
+        <v>7.1</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0.5085000000000001</v>
+        <v>0.1662</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.4487</v>
+        <v>0.3683</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.2298</v>
+        <v>0.4549</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.9399</v>
+        <v>1.9624</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0.1089</v>
+        <v>0.0302</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>0.2287</v>
+        <v>0.118</v>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr"/>
@@ -3167,31 +3167,31 @@
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>38.2</v>
+        <v>36.5</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>0.0026</v>
+        <v>-0.0445</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>-0.0521</v>
+        <v>-0.0898</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-0.0969</v>
+        <v>-0.123</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>-0.1667</v>
+        <v>-0.2086</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>-0.2345</v>
+        <v>-0.2632</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>-0.0185</v>
+        <v>-0.0568</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>6.92</v>
+        <v>6.61</v>
       </c>
       <c r="K47" s="7" t="n">
         <v>0.3163</v>
@@ -3225,31 +3225,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>15.13</v>
+        <v>15.21</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.0013</v>
+        <v>0.0053</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>-0.0946</v>
+        <v>-0.08259999999999999</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>-0.1844</v>
+        <v>-0.1743</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-0.2292</v>
+        <v>-0.2172</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-0.2747</v>
+        <v>-0.2659</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>-0.0956</v>
+        <v>-0.1147</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.76</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>0.5749</v>
@@ -3283,31 +3283,31 @@
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>37.18</v>
+        <v>36.52</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>0.0438</v>
+        <v>-0.0178</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>-0.0164</v>
+        <v>-0.0178</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>0.0271</v>
+        <v>0.0038</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>-0.1252</v>
+        <v>-0.1354</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0.0935</v>
+        <v>0.123</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0.403</v>
+        <v>0.3556</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>32.41</v>
+        <v>31.83</v>
       </c>
       <c r="K49" s="7" t="n">
         <v>0.1998</v>
@@ -3337,55 +3337,57 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>AYES</t>
+          <t>RALYH</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>6.83</v>
+        <v>19.62</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.0134</v>
+        <v>-0.09960000000000001</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.1013</v>
+        <v>-0.3433</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.89</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>-0.2777</v>
+        <v>-0.9254000000000001</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.2818</v>
+        <v>-0.9399</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0.4337</v>
+        <v>-0.8905</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>1.88</v>
+        <v>2.54</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0.4183</v>
+        <v>0.7070000000000001</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.314</v>
+        <v>1.4848</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.8128</v>
+        <v>1.5369</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>42.7724</v>
+        <v>0.5434</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>0.0208</v>
-      </c>
-      <c r="P50" s="2" t="inlineStr"/>
+        <v>0.2854</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>0.3914</v>
+      </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr"/>
@@ -3393,54 +3395,52 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>KARSN</t>
+          <t>AYES</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>7.66</v>
+        <v>6.51</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>0.02</v>
+        <v>-0.0469</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>-0.1345</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-0.2263</v>
+        <v>-0.132</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>-0.2901</v>
+        <v>-0.2995</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>-0.3397</v>
+        <v>-0.3</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>-0.2184</v>
+        <v>0.3691</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>28.51</v>
+        <v>1.79</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.8458</v>
+        <v>0.4183</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>1.2698</v>
+        <v>0.314</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>1.2002</v>
+        <v>0.8128</v>
       </c>
       <c r="N51" s="7" t="n">
-        <v>2.1122</v>
+        <v>42.7724</v>
       </c>
       <c r="O51" s="7" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="P51" s="7" t="n">
-        <v>0.07339999999999999</v>
-      </c>
+        <v>0.0208</v>
+      </c>
+      <c r="P51" s="5" t="inlineStr"/>
       <c r="Q51" s="5" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -3451,57 +3451,57 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>DESA</t>
+          <t>ARASE</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>8.23</v>
+        <v>76.5</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.0352</v>
+        <v>-0.1</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.026</v>
+        <v>-0.2073</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>-0.0906</v>
+        <v>-0.2884</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>-0.2048</v>
+        <v>-0.3806</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.4138</v>
+        <v>-0.2403</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>-0.451</v>
+        <v>0.474</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>7.8</v>
+        <v>6.97</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0.2088</v>
+        <v>0.1264</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.2301</v>
+        <v>0.596</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.0037</v>
+        <v>0.7123999999999999</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.3571</v>
+        <v>4.0303</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>0.2399</v>
+        <v>0.25</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>0.1277</v>
+        <v>0.1463</v>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr"/>
@@ -3509,57 +3509,57 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>RALYH</t>
+          <t>KARSN</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>21.78</v>
+        <v>7.3</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>-0.1</v>
+        <v>-0.047</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>-0.4088000000000001</v>
+        <v>-0.159</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-0.9009999999999999</v>
+        <v>-0.1609</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>-0.9103</v>
+        <v>-0.3345</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>-0.9329999999999999</v>
+        <v>-0.3546</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>-0.8756</v>
+        <v>-0.2678</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>2.82</v>
+        <v>27.17</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>0.7070000000000001</v>
+        <v>0.8458</v>
       </c>
       <c r="L53" s="7" t="n">
-        <v>1.4848</v>
+        <v>1.2698</v>
       </c>
       <c r="M53" s="7" t="n">
-        <v>1.5369</v>
+        <v>1.2002</v>
       </c>
       <c r="N53" s="7" t="n">
-        <v>0.5434</v>
+        <v>2.1122</v>
       </c>
       <c r="O53" s="7" t="n">
-        <v>0.2854</v>
+        <v>0.1667</v>
       </c>
       <c r="P53" s="7" t="n">
-        <v>0.3914</v>
+        <v>0.07339999999999999</v>
       </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R53" s="5" t="inlineStr"/>
@@ -3567,57 +3567,57 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ARASE</t>
+          <t>DESA</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>-0.0064</v>
+        <v>-0.0279</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>-0.1118</v>
+        <v>-0.0566</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>-0.2444</v>
+        <v>-0.1031</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>-0.32</v>
+        <v>-0.2308</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.4318</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>0.6634</v>
+        <v>-0.4667</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>7.75</v>
+        <v>7.58</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0.1264</v>
+        <v>0.2088</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.596</v>
+        <v>0.2301</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.7123999999999999</v>
+        <v>0.0037</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>4.0303</v>
+        <v>0.3571</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>0.25</v>
+        <v>0.2399</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>0.1463</v>
+        <v>0.1277</v>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr"/>
@@ -3629,31 +3629,31 @@
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>88.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>0.019</v>
+        <v>-0.0362</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>-0.0443</v>
+        <v>-0.0834</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-0.1367</v>
+        <v>-0.1606</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>-0.1299</v>
+        <v>-0.1647</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>-0.2807</v>
+        <v>-0.3016</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>-0.1291</v>
+        <v>-0.1548</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>12.37</v>
+        <v>11.92</v>
       </c>
       <c r="K55" s="7" t="n">
         <v>0.4926</v>
@@ -3683,57 +3683,57 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>GESAN</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>465.25</v>
+        <v>31.4</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.0299</v>
+        <v>-0.0616</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.0723</v>
+        <v>-0.1982</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>-0.1087</v>
+        <v>-0.3319</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>-0.269</v>
+        <v>-0.6253</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.3009</v>
+        <v>-0.3189</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>0.0858</v>
+        <v>-0.2738</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>13.94</v>
+        <v>8.44</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0.3804</v>
+        <v>0.2641</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.3113</v>
+        <v>0.2931</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>1.725</v>
+        <v>0.3273</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.0848</v>
+        <v>0.4479</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>0.0184</v>
+        <v>0.1778</v>
       </c>
       <c r="P56" s="4" t="n">
-        <v>0.1216</v>
+        <v>0.1266</v>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr"/>
@@ -3741,57 +3741,57 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>GESAN</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>33.46</v>
+        <v>454</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>0.0115</v>
+        <v>-0.0242</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>-0.1718</v>
+        <v>-0.08560000000000001</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-0.2265</v>
+        <v>-0.1352</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>-0.6185</v>
+        <v>-0.2895</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>-0.2965</v>
+        <v>-0.3074</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>-0.2153</v>
+        <v>0.0248</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>8.99</v>
+        <v>13.6</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>0.2641</v>
+        <v>0.3804</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>0.2931</v>
+        <v>0.3113</v>
       </c>
       <c r="M57" s="7" t="n">
-        <v>0.3273</v>
+        <v>1.725</v>
       </c>
       <c r="N57" s="7" t="n">
-        <v>0.4479</v>
+        <v>0.0848</v>
       </c>
       <c r="O57" s="7" t="n">
-        <v>0.1778</v>
+        <v>0.0184</v>
       </c>
       <c r="P57" s="7" t="n">
-        <v>0.1266</v>
+        <v>0.1216</v>
       </c>
       <c r="Q57" s="5" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R57" s="5" t="inlineStr"/>
@@ -3803,31 +3803,31 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>18.01</v>
+        <v>17.6</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>-0.0033</v>
+        <v>-0.0228</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>-0.0526</v>
+        <v>-0.0737</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.0974</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>-0.04099999999999999</v>
+        <v>-0.0335</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-0.196</v>
+        <v>-0.1927</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>-0.1851</v>
+        <v>-0.2129</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>13.63</v>
+        <v>13.32</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>2.3363</v>
@@ -3857,57 +3857,57 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>TNZTP</t>
+          <t>CWENE</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>23.3</v>
+        <v>15.11</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>0.0052</v>
+        <v>-0.0702</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>-0.092</v>
+        <v>-0.1652</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-0.0805</v>
+        <v>-0.3587</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>-0.0574</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>-0.0635</v>
+        <v>-0.5732</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>0.1289</v>
+        <v>-0.3211</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>17.24</v>
+        <v>5.62</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>0.4327</v>
+        <v>0.5809000000000001</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>0.4143</v>
+        <v>0.9067000000000001</v>
       </c>
       <c r="M59" s="7" t="n">
-        <v>0.5201</v>
+        <v>0.8432999999999999</v>
       </c>
       <c r="N59" s="7" t="n">
-        <v>0.0702</v>
+        <v>5.095899999999999</v>
       </c>
       <c r="O59" s="7" t="n">
-        <v>0.3617</v>
+        <v>0.1918</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>0.0551</v>
+        <v>0.2052</v>
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>Sağlık hizmetleri</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R59" s="5" t="inlineStr"/>
@@ -3915,57 +3915,57 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SELEC</t>
+          <t>TNZTP</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>59.05</v>
+        <v>23.2</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>-0.0998</v>
+        <v>-0.0043</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>-0.2619</v>
+        <v>-0.0823</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>-0.7226</v>
+        <v>-0.1407</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>-0.7509</v>
+        <v>-0.05690000000000001</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-0.3365</v>
+        <v>-0.0668</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>-0.223</v>
+        <v>0.0741</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>18</v>
+        <v>17.17</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0.3781</v>
+        <v>0.4327</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.6063000000000001</v>
+        <v>0.4143</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>1.4267</v>
+        <v>0.5201</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.0702</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>0.0158</v>
+        <v>0.3617</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.0551</v>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Sağlık hizmetleri</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr"/>
@@ -3973,57 +3973,57 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>CWENE</t>
+          <t>MOBTL</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>16.25</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>0.0156</v>
+        <v>-0.045</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>-0.113</v>
+        <v>-0.118</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>-0.334</v>
+        <v>-0.1128</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>-0.6013000000000001</v>
+        <v>-0.3762</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>-0.5325</v>
+        <v>-0.3148</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>-0.2729</v>
+        <v>0.2476</v>
       </c>
       <c r="I61" s="6" t="n">
         <v>0.99</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>6.04</v>
+        <v>12.93</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>0.5809000000000001</v>
+        <v>0.5631</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>0.9067000000000001</v>
+        <v>0.4406</v>
       </c>
       <c r="M61" s="7" t="n">
-        <v>0.8432999999999999</v>
+        <v>0.5064</v>
       </c>
       <c r="N61" s="7" t="n">
-        <v>5.095899999999999</v>
+        <v>1.6818</v>
       </c>
       <c r="O61" s="7" t="n">
-        <v>0.1918</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="P61" s="7" t="n">
-        <v>0.2052</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R61" s="5" t="inlineStr"/>
@@ -4035,31 +4035,31 @@
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>40.26</v>
+        <v>39.56</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0.0479</v>
+        <v>-0.0174</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>0.0005</v>
+        <v>-0.0105</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>-0.0437</v>
+        <v>-0.0361</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>-0.2051</v>
+        <v>-0.2159</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-0.2924</v>
+        <v>-0.2973</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>-0.0423</v>
+        <v>-0.0735</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>0.3754999999999999</v>
@@ -4089,57 +4089,57 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>CMENT</t>
+          <t>SELEC</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>219.1</v>
+        <v>60.3</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>0.0106</v>
+        <v>0.0212</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>-0.0219</v>
+        <v>-0.1796</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-0.08130000000000001</v>
+        <v>-0.6854</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>-0.2471</v>
+        <v>-0.7573000000000001</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>-0.332</v>
+        <v>-0.3315</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>-0.3713</v>
+        <v>-0.242</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>21.62</v>
+        <v>18.38</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>0.0934</v>
+        <v>0.3781</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>0.1109</v>
+        <v>0.6063000000000001</v>
       </c>
       <c r="M63" s="7" t="n">
-        <v>0.1008</v>
+        <v>1.4267</v>
       </c>
       <c r="N63" s="7" t="n">
-        <v>0.4922</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>0.1647</v>
+        <v>0.0158</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R63" s="5" t="inlineStr"/>
@@ -4147,57 +4147,57 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>MOBTL</t>
+          <t>CMENT</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>9.550000000000001</v>
+        <v>215.1</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.0042</v>
+        <v>-0.0183</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.0931</v>
+        <v>-0.06480000000000001</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>-0.2062</v>
+        <v>-0.0346</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>-0.3409</v>
+        <v>-0.2564</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.2862</v>
+        <v>-0.3655</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>0.3921</v>
+        <v>-0.3937</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>13.53</v>
+        <v>21.23</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0.5631</v>
+        <v>0.0934</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.4406</v>
+        <v>0.1109</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.5064</v>
+        <v>0.1008</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>1.6818</v>
+        <v>0.4922</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.1647</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>0.08689999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr"/>
@@ -4209,31 +4209,31 @@
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>11.92</v>
+        <v>11.47</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>0.0438</v>
+        <v>-0.0378</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>0.0329</v>
+        <v>-0.0146</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>0.1078</v>
+        <v>0.1029</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0241</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>0.2102</v>
+        <v>0.168</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>0.5501</v>
+        <v>0.4668</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>10.05</v>
+        <v>9.67</v>
       </c>
       <c r="K65" s="7" t="n">
         <v>0.6297</v>
@@ -4267,28 +4267,28 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>21.4</v>
+        <v>20.46</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.0142</v>
+        <v>-0.04389999999999999</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.0581</v>
+        <v>-0.1143</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>-0.1508</v>
+        <v>-0.1976</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>-0.4569</v>
+        <v>-0.4732</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.449</v>
+        <v>-0.4564</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>0.0542</v>
+        <v>0</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="4" t="n">
@@ -4319,57 +4319,57 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>MAALT</t>
+          <t>KTLEV</t>
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>716.5</v>
+        <v>4.94</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>0.009899999999999999</v>
+        <v>-0.08689999999999999</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>-0.1219</v>
+        <v>-0.3413</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>-0.2726</v>
+        <v>-0.7534999999999999</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>-0.3322</v>
+        <v>-0.9061</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>-0.47</v>
+        <v>-0.8409</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>-0.2871</v>
+        <v>0.2523</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>1543.85</v>
+        <v>1.2</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>0.248</v>
+        <v>3.5578</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>3.5256</v>
+        <v>3.6471</v>
       </c>
       <c r="M67" s="7" t="n">
-        <v>0.3863</v>
+        <v>5.174600000000001</v>
       </c>
       <c r="N67" s="7" t="n">
-        <v>0.9832</v>
+        <v>5.7649</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>0.4575</v>
+        <v>0.7222</v>
       </c>
       <c r="P67" s="7" t="n">
-        <v>-0</v>
+        <v>1.5072</v>
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R67" s="5" t="inlineStr"/>
@@ -4377,57 +4377,57 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>ISDMR</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>10.19</v>
+        <v>56.85</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0.0345</v>
+        <v>-0.0389</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>-0.023</v>
+        <v>-0.08380000000000001</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>-0.07780000000000001</v>
+        <v>-0.06269999999999999</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>-0.1515</v>
+        <v>0.0252</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-0.0369</v>
+        <v>0.2622</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>-0.1648</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>6.84</v>
+        <v>13.4</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0.423</v>
+        <v>0.1859</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.5552</v>
+        <v>0.3543</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>0.8170999999999999</v>
+        <v>0.4035</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>10.0728</v>
+        <v>0.208</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>0.179</v>
+        <v>0.1056</v>
       </c>
       <c r="P68" s="4" t="n">
-        <v>0.2236</v>
+        <v>0.0859</v>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr"/>
@@ -4435,57 +4435,57 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>ISDMR</t>
+          <t>MAALT</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>59.15</v>
+        <v>707</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>0.0619</v>
+        <v>-0.0133</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>-0.0626</v>
+        <v>-0.1163</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>-0.0483</v>
+        <v>-0.2455</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>0.0377</v>
+        <v>-0.3502</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>0.3029</v>
+        <v>-0.4688000000000001</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>0.6349</v>
+        <v>-0.2898</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>13.95</v>
+        <v>1523.38</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>0.1859</v>
+        <v>0.248</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>0.3543</v>
+        <v>3.5256</v>
       </c>
       <c r="M69" s="7" t="n">
-        <v>0.4035</v>
+        <v>0.3863</v>
       </c>
       <c r="N69" s="7" t="n">
-        <v>0.208</v>
+        <v>0.9832</v>
       </c>
       <c r="O69" s="7" t="n">
-        <v>0.1056</v>
+        <v>0.4575</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>0.0859</v>
+        <v>-0</v>
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R69" s="5" t="inlineStr"/>
@@ -4493,57 +4493,57 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>ENKAI</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0.0297</v>
+        <v>0.001</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>-0.0442</v>
+        <v>-0.0116</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>-0.0915</v>
+        <v>-0.0599</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>-0.1496</v>
+        <v>-0.1486</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>-0.2623</v>
+        <v>-0.023</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>0.1011</v>
+        <v>-0.1612</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>11.7</v>
+        <v>6.84</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0.4381</v>
+        <v>0.423</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>0.1539</v>
+        <v>0.5552</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.1373</v>
+        <v>0.8170999999999999</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.3376</v>
+        <v>10.0728</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>0.2166</v>
+        <v>0.179</v>
       </c>
       <c r="P70" s="4" t="n">
-        <v>0.1059</v>
+        <v>0.2236</v>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr"/>
@@ -4551,57 +4551,55 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>KTLEV</t>
+          <t>YKSLN</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>5.41</v>
+        <v>2.2</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>-0.0442</v>
+        <v>-0.05980000000000001</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>-0.417</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>-0.757</v>
+        <v>-0.3433</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-0.306</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>-0.8189</v>
+        <v>-0.321</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>0.4061999999999999</v>
+        <v>-0.3569</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="J71" s="6" t="n">
-        <v>1.32</v>
-      </c>
+        <v>1.09</v>
+      </c>
+      <c r="J71" s="5" t="inlineStr"/>
       <c r="K71" s="7" t="n">
-        <v>3.5578</v>
+        <v>0.1126</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>3.6471</v>
+        <v>0.0263</v>
       </c>
       <c r="M71" s="7" t="n">
-        <v>5.174600000000001</v>
+        <v>0.6127</v>
       </c>
       <c r="N71" s="7" t="n">
-        <v>5.7649</v>
+        <v>0.8754000000000001</v>
       </c>
       <c r="O71" s="7" t="n">
-        <v>0.7222</v>
+        <v>0.1443</v>
       </c>
       <c r="P71" s="7" t="n">
-        <v>1.5072</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R71" s="5" t="inlineStr"/>
@@ -4609,57 +4607,57 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>NTGAZ</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>10</v>
+        <v>75.8</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>0.0256</v>
+        <v>-0.027</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>-0.0557</v>
+        <v>-0.0601</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>-0.0602</v>
+        <v>-0.1186</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>-0.1482</v>
+        <v>-0.1675</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>-0.1736</v>
+        <v>-0.2896</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0455</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>6.35</v>
+        <v>11.39</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0.3448</v>
+        <v>0.4381</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.3645</v>
+        <v>0.1539</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.4084</v>
+        <v>0.1373</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0.5755</v>
+        <v>0.3376</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>0.2148</v>
+        <v>0.2166</v>
       </c>
       <c r="P72" s="4" t="n">
-        <v>0.2137</v>
+        <v>0.1059</v>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr"/>
@@ -4667,55 +4665,57 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>YKSLN</t>
+          <t>NTGAZ</t>
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>2.34</v>
+        <v>9.85</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>0.0446</v>
+        <v>-0.015</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>0.0308</v>
+        <v>-0.0646</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-0.371</v>
+        <v>-0.0725</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>-0.2688</v>
+        <v>-0.1617</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>-0.2733</v>
+        <v>-0.1939</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>-0.3195</v>
+        <v>0.0524</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="J73" s="5" t="inlineStr"/>
+        <v>1.13</v>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>6.26</v>
+      </c>
       <c r="K73" s="7" t="n">
-        <v>0.1126</v>
+        <v>0.3448</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>0.0263</v>
+        <v>0.3645</v>
       </c>
       <c r="M73" s="7" t="n">
-        <v>0.6127</v>
+        <v>0.4084</v>
       </c>
       <c r="N73" s="7" t="n">
-        <v>0.8754000000000001</v>
+        <v>0.5755</v>
       </c>
       <c r="O73" s="7" t="n">
-        <v>0.1443</v>
+        <v>0.2148</v>
       </c>
       <c r="P73" s="7" t="n">
-        <v>-0.04969999999999999</v>
+        <v>0.2137</v>
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R73" s="5" t="inlineStr"/>
@@ -4723,57 +4723,55 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GARFA</t>
+          <t>OBASE</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>20.32</v>
+        <v>20.44</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>0.001</v>
+        <v>-0.0466</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>-0.1142</v>
+        <v>-0.1019</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>-0.2185</v>
+        <v>-0.3482</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>-0.3093</v>
+        <v>-0.5553</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-0.2743</v>
+        <v>-0.4691</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>-0.1638</v>
+        <v>-0.4332</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>3.08</v>
-      </c>
+        <v>1.14</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="4" t="n">
-        <v>0.9562999999999999</v>
+        <v>0.2041</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.9506</v>
+        <v>0.3021</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.5156000000000001</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.5365</v>
+        <v>0.4873</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>0.914</v>
+        <v>0.2465</v>
       </c>
       <c r="P74" s="4" t="n">
-        <v>0.496</v>
+        <v>0.1432</v>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr"/>
@@ -4781,55 +4779,57 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>OBASE</t>
+          <t>GLCVY</t>
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>21.44</v>
+        <v>34.46</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>0.0318</v>
+        <v>-0.04219999999999999</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>-0.1096</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-0.3558</v>
+        <v>-0.2589</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>-0.5463</v>
+        <v>-0.3785</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>-0.4352</v>
+        <v>-0.4486</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>-0.3988</v>
+        <v>-0.4795</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J75" s="5" t="inlineStr"/>
+        <v>1.16</v>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>3.34</v>
+      </c>
       <c r="K75" s="7" t="n">
-        <v>0.2041</v>
+        <v>0.265</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>0.3021</v>
+        <v>0.2739</v>
       </c>
       <c r="M75" s="7" t="n">
-        <v>0.5156000000000001</v>
+        <v>0.2851</v>
       </c>
       <c r="N75" s="7" t="n">
-        <v>0.4873</v>
+        <v>0.0788</v>
       </c>
       <c r="O75" s="7" t="n">
-        <v>0.2465</v>
+        <v>0.7251000000000001</v>
       </c>
       <c r="P75" s="7" t="n">
-        <v>0.1432</v>
+        <v>0.4011</v>
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R75" s="5" t="inlineStr"/>
@@ -4837,57 +4837,55 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GEDIK</t>
+          <t>DAGI</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>4.8</v>
+        <v>5.42</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>0.0526</v>
+        <v>-0.0767</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>-0.0244</v>
+        <v>-0.1597</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>-0.0495</v>
+        <v>-0.1187</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>-0.3172</v>
+        <v>-0.4354</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.1767</v>
+        <v>-0.17</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>-0.3182</v>
+        <v>-0.3547999999999999</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J76" s="3" t="n">
-        <v>5.08</v>
-      </c>
+        <v>1.18</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="4" t="n">
-        <v>0.6583</v>
+        <v>0.5429999999999999</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.6568000000000001</v>
+        <v>1.1389</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.7293999999999999</v>
+        <v>1.8634</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.3481</v>
+        <v>0.5748</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>0.6628000000000001</v>
+        <v>0.1561</v>
       </c>
       <c r="P76" s="4" t="n">
-        <v>0.275</v>
+        <v>-0.0597</v>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R76" s="2" t="inlineStr"/>
@@ -4895,53 +4893,53 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>GLCVY</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B77" s="6" t="n">
-        <v>35.98</v>
+        <v>27.96</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>0.0227</v>
+        <v>-0.0189</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>-0.05860000000000001</v>
+        <v>-0.0372</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-0.252</v>
+        <v>-0.1693</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>-0.3637</v>
+        <v>-0.2348</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>-0.4271</v>
+        <v>-0.3566</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>-0.4374</v>
+        <v>-0.3065</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>3.49</v>
+        <v>6.24</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>0.265</v>
+        <v>0.4021</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>0.2739</v>
+        <v>0.2915</v>
       </c>
       <c r="M77" s="7" t="n">
-        <v>0.2851</v>
+        <v>0.201</v>
       </c>
       <c r="N77" s="7" t="n">
-        <v>0.0788</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="O77" s="7" t="n">
-        <v>0.7251000000000001</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="P77" s="7" t="n">
-        <v>0.4011</v>
+        <v>0.298</v>
       </c>
       <c r="Q77" s="5" t="inlineStr">
         <is>
@@ -4953,53 +4951,53 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>GEDIK</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>28.5</v>
+        <v>4.78</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>0.0157</v>
+        <v>-0.0042</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>-0.0206</v>
+        <v>-0.0225</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>-0.1834</v>
+        <v>-0.0895</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>-0.2222</v>
+        <v>-0.2939</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>-0.3604</v>
+        <v>-0.1857</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>-0.2796</v>
+        <v>-0.3434</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>6.36</v>
+        <v>5.06</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0.4021</v>
+        <v>0.6583</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>0.2915</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>0.201</v>
+        <v>0.7293999999999999</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.3481</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>0.8484999999999999</v>
+        <v>0.6628000000000001</v>
       </c>
       <c r="P78" s="4" t="n">
-        <v>0.298</v>
+        <v>0.275</v>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
@@ -5011,55 +5009,57 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>KCAER</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
-        <v>6.04</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>0.0067</v>
+        <v>-0.0573</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>-0.0793</v>
+        <v>-0.1488</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-0.1493</v>
+        <v>-0.2051</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>-0.2286</v>
+        <v>-0.3531</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>-0.2775</v>
+        <v>-0.1836</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>-0.2488</v>
+        <v>-0.2591</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="J79" s="5" t="inlineStr"/>
+        <v>1.21</v>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>27.32</v>
+      </c>
       <c r="K79" s="7" t="n">
-        <v>0.3952000000000001</v>
+        <v>0.1522</v>
       </c>
       <c r="L79" s="7" t="n">
-        <v>0.4088000000000001</v>
+        <v>0.2873</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>0.4094</v>
+        <v>0.3247</v>
       </c>
       <c r="N79" s="7" t="n">
-        <v>0.7489</v>
+        <v>1.1982</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>0.7836</v>
+        <v>0.1199</v>
       </c>
       <c r="P79" s="7" t="n">
-        <v>-0.0106</v>
+        <v>0.0508</v>
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>Çeşitli Hizmetler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R79" s="5" t="inlineStr"/>
@@ -5067,57 +5067,55 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>KNFRT</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>70.84999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>0.0268</v>
+        <v>-0.08869999999999999</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>-0.0139</v>
+        <v>-0.2402</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>0.0343</v>
+        <v>-0.3451</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>-0.3571</v>
+        <v>-0.3954</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>-0.1199</v>
+        <v>-0.4196</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>0.453</v>
+        <v>-0.4665</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="J80" s="3" t="n">
-        <v>26.08</v>
-      </c>
+        <v>1.23</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="4" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.7798</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>0.3716</v>
+        <v>1.3764</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>0.4119</v>
+        <v>26.3063</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>0.9691</v>
+        <v>0.625</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>0.3037</v>
+        <v>0.0124</v>
       </c>
       <c r="P80" s="4" t="n">
-        <v>0.0601</v>
+        <v>-0.1091</v>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr"/>
@@ -5125,57 +5123,55 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>286.25</v>
+        <v>5.89</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>0.0447</v>
+        <v>-0.0248</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>0.0741</v>
+        <v>-0.09939999999999999</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>0.0495</v>
+        <v>-0.161</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>0.0563</v>
+        <v>-0.2468</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>-0.08839999999999999</v>
+        <v>-0.2971</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>0.2711</v>
+        <v>-0.2843</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="J81" s="6" t="n">
-        <v>19.72</v>
-      </c>
+        <v>1.23</v>
+      </c>
+      <c r="J81" s="5" t="inlineStr"/>
       <c r="K81" s="7" t="n">
-        <v>0.3707</v>
+        <v>0.3952000000000001</v>
       </c>
       <c r="L81" s="7" t="n">
-        <v>0.4185</v>
+        <v>0.4088000000000001</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>0.4202</v>
+        <v>0.4094</v>
       </c>
       <c r="N81" s="7" t="n">
-        <v>1.8941</v>
+        <v>0.7489</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>0.3086</v>
+        <v>0.7836</v>
       </c>
       <c r="P81" s="7" t="n">
-        <v>-0.1688</v>
+        <v>-0.0106</v>
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Çeşitli Hizmetler</t>
         </is>
       </c>
       <c r="R81" s="5" t="inlineStr"/>
@@ -5183,55 +5179,57 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>DAGI</t>
+          <t>SARKY</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>5.87</v>
+        <v>16.55</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>0.0209</v>
+        <v>-0.0322</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.1289</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>-0.1431</v>
+        <v>-0.2464</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>-0.3917</v>
+        <v>-0.3722</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>-0.0608</v>
+        <v>-0.4038</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>-0.2978</v>
+        <v>0.1582</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr"/>
+        <v>1.23</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>60.64</v>
+      </c>
       <c r="K82" s="4" t="n">
-        <v>0.5429999999999999</v>
+        <v>0.5590999999999999</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>1.1389</v>
+        <v>0.3671</v>
       </c>
       <c r="M82" s="4" t="n">
-        <v>1.8634</v>
+        <v>0.2342</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>0.5748</v>
+        <v>0.8034</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>0.1561</v>
+        <v>0.0217</v>
       </c>
       <c r="P82" s="4" t="n">
-        <v>-0.0597</v>
+        <v>0.0229</v>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R82" s="2" t="inlineStr"/>
@@ -5239,57 +5237,57 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>SARKY</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>17.1</v>
+        <v>69.05</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>0.0018</v>
+        <v>-0.0254</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>-0.1009</v>
+        <v>-0.0541</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-0.2434</v>
+        <v>0.0534</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>-0.3382</v>
+        <v>-0.4047</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>-0.3966</v>
+        <v>-0.1265</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>0.2068</v>
+        <v>0.404</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>62.66</v>
+        <v>25.41</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>0.5590999999999999</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="L83" s="7" t="n">
-        <v>0.3671</v>
+        <v>0.3716</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>0.2342</v>
+        <v>0.4119</v>
       </c>
       <c r="N83" s="7" t="n">
-        <v>0.8034</v>
+        <v>0.9691</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>0.0217</v>
+        <v>0.3037</v>
       </c>
       <c r="P83" s="7" t="n">
-        <v>0.0229</v>
+        <v>0.0601</v>
       </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R83" s="5" t="inlineStr"/>
@@ -5297,57 +5295,57 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>KCAER</t>
+          <t>GARFA</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>9.949999999999999</v>
+        <v>21.34</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>0.0452</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>-0.0684</v>
+        <v>-0.0473</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>-0.1708</v>
+        <v>-0.1332</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>-0.2857</v>
+        <v>-0.2496</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>-0.1553</v>
+        <v>-0.2486</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>-0.2046</v>
+        <v>-0.1395</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>28.97</v>
+        <v>3.23</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0.1522</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.2873</v>
+        <v>0.9506</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>0.3247</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>1.1982</v>
+        <v>0.5365</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>0.1199</v>
+        <v>0.914</v>
       </c>
       <c r="P84" s="4" t="n">
-        <v>0.0508</v>
+        <v>0.496</v>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr"/>
@@ -5355,55 +5353,57 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>0.0123</v>
+        <v>0.0026</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>-0.05690000000000001</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-0.2115</v>
+        <v>0.0446</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>-0.3876</v>
+        <v>0.0503</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>-0.3098</v>
+        <v>-0.0674</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>-0.2711</v>
+        <v>0.2381</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J85" s="5" t="inlineStr"/>
+        <v>1.27</v>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>19.77</v>
+      </c>
       <c r="K85" s="7" t="n">
-        <v>0.3957</v>
+        <v>0.3707</v>
       </c>
       <c r="L85" s="7" t="n">
-        <v>2.0344</v>
+        <v>0.4185</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>3.8494</v>
+        <v>0.4202</v>
       </c>
       <c r="N85" s="7" t="n">
-        <v>0.889</v>
+        <v>1.8941</v>
       </c>
       <c r="O85" s="7" t="n">
-        <v>0.0349</v>
+        <v>0.3086</v>
       </c>
       <c r="P85" s="7" t="n">
-        <v>-0.0175</v>
+        <v>-0.1688</v>
       </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="R85" s="5" t="inlineStr"/>
@@ -5411,55 +5411,55 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>KNFRT</t>
+          <t>ACSEL</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>8.119999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>0.0741</v>
+        <v>-0.0159</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>-0.1896</v>
+        <v>-0.06709999999999999</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>-0.3245</v>
+        <v>-0.179</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>-0.3267</v>
+        <v>-0.3835</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>-0.3802</v>
+        <v>-0.3297</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>-0.3778</v>
+        <v>-0.2877</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="4" t="n">
-        <v>0.7798</v>
+        <v>0.3957</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>1.3764</v>
+        <v>2.0344</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>26.3063</v>
+        <v>3.8494</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>0.625</v>
+        <v>0.889</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>0.0124</v>
+        <v>0.0349</v>
       </c>
       <c r="P86" s="4" t="n">
-        <v>-0.1091</v>
+        <v>-0.0175</v>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr"/>
@@ -5467,55 +5467,57 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>OZYSR</t>
+          <t>PCILT</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>11.64</v>
+        <v>29</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>0.0034</v>
+        <v>-0.0429</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>-0.0177</v>
+        <v>-0.0473</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>0.0563</v>
+        <v>-0.0333</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>-0.1222</v>
+        <v>-0.1623</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>-0.0204</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>0.5093</v>
+        <v>0.5057</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="J87" s="5" t="inlineStr"/>
+        <v>1.31</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>6.66</v>
+      </c>
       <c r="K87" s="7" t="n">
-        <v>0.161</v>
+        <v>0.763</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>0.1742</v>
+        <v>0.7087</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>0.6839</v>
+        <v>0.7914</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>0.5105</v>
+        <v>1.2232</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>0.042</v>
+        <v>0.0574</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>-0.0335</v>
+        <v>0.2831</v>
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R87" s="5" t="inlineStr"/>
@@ -5523,57 +5525,55 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>PCILT</t>
+          <t>OZYSR</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>30.3</v>
+        <v>11.6</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>0.0557</v>
+        <v>-0.0034</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0178</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>-0.0033</v>
+        <v>0.0507</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>-0.1212</v>
+        <v>-0.1185</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>0.1512</v>
+        <v>-0.0219</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>0.5881000000000001</v>
+        <v>0.5127</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="J88" s="3" t="n">
-        <v>6.96</v>
-      </c>
+        <v>1.36</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="4" t="n">
-        <v>0.763</v>
+        <v>0.161</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>0.7087</v>
+        <v>0.1742</v>
       </c>
       <c r="M88" s="4" t="n">
-        <v>0.7914</v>
+        <v>0.6839</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>1.2232</v>
+        <v>0.5105</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>0.0574</v>
+        <v>0.042</v>
       </c>
       <c r="P88" s="4" t="n">
-        <v>0.2831</v>
+        <v>-0.0335</v>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R88" s="2" t="inlineStr"/>
@@ -5585,31 +5585,31 @@
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>25.34</v>
+        <v>24.68</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.026</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>-0.1256</v>
+        <v>-0.1236</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-0.2503</v>
+        <v>-0.2646</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>-0.4618</v>
+        <v>-0.4672</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>-0.3731</v>
+        <v>-0.3736</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>-0.3813</v>
+        <v>-0.4024</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>30.36</v>
+        <v>29.57</v>
       </c>
       <c r="K89" s="7" t="n">
         <v>0.05019999999999999</v>
@@ -5643,31 +5643,31 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>-0.09050000000000001</v>
+        <v>-0.0118</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>-0.1916</v>
+        <v>-0.2042</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>-0.5301</v>
+        <v>-0.4633</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>-0.5347</v>
+        <v>-0.5502</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>-0.5746</v>
+        <v>-0.5679</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>-0.6923999999999999</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>15.38</v>
+        <v>15.2</v>
       </c>
       <c r="K90" s="4" t="n">
         <v>0.5049</v>
@@ -5697,57 +5697,57 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>EGPRO</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>29.16</v>
+        <v>12.64</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>0.0348</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>-0.1028</v>
+        <v>-0.297</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-0.2076</v>
+        <v>-0.1662</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>-0.2033</v>
+        <v>-0.7</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>-0.3633</v>
+        <v>-0.5809000000000001</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>0.1346</v>
+        <v>0.1146</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>10.38</v>
+        <v>1.63</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>0.3776</v>
+        <v>2.1748</v>
       </c>
       <c r="L91" s="7" t="n">
-        <v>0.5127</v>
+        <v>2.2285</v>
       </c>
       <c r="M91" s="7" t="n">
-        <v>0.5197999999999999</v>
+        <v>2.5519</v>
       </c>
       <c r="N91" s="7" t="n">
-        <v>1.3047</v>
+        <v>7.8348</v>
       </c>
       <c r="O91" s="7" t="n">
-        <v>0.2228</v>
+        <v>0.887</v>
       </c>
       <c r="P91" s="7" t="n">
-        <v>0.1742</v>
+        <v>1.1538</v>
       </c>
       <c r="Q91" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R91" s="5" t="inlineStr"/>
@@ -5755,57 +5755,57 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>TUPRS</t>
+          <t>EGPRO</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>362</v>
+        <v>28.02</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>0.0147</v>
+        <v>-0.0391</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>-0.0542</v>
+        <v>-0.1155</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>-0.1171</v>
+        <v>-0.1468</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>0.1696</v>
+        <v>-0.2386</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>0.4266</v>
+        <v>-0.3529</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>1.0877</v>
+        <v>0.0785</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>10.04</v>
+        <v>9.98</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0.465</v>
+        <v>0.3776</v>
       </c>
       <c r="L92" s="4" t="n">
-        <v>1.0453</v>
+        <v>0.5127</v>
       </c>
       <c r="M92" s="4" t="n">
-        <v>1.1002</v>
+        <v>0.5197999999999999</v>
       </c>
       <c r="N92" s="4" t="n">
-        <v>2.2351</v>
+        <v>1.3047</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.2228</v>
       </c>
       <c r="P92" s="4" t="n">
-        <v>0.187</v>
+        <v>0.1742</v>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R92" s="2" t="inlineStr"/>
@@ -5817,28 +5817,28 @@
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>9.390000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>0.04679999999999999</v>
+        <v>-0.0405</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>-0.1563</v>
+        <v>-0.189</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>-0.2109</v>
+        <v>-0.1603</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>0.0527</v>
+        <v>-0.0238</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>0.0296</v>
+        <v>-0.0044</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>0.05980000000000001</v>
+        <v>0</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="J93" s="5" t="inlineStr"/>
       <c r="K93" s="7" t="n">
@@ -5869,57 +5869,57 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>MEGMT</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>14.04</v>
+        <v>3</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.0654</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>-0.1799</v>
+        <v>-0.09910000000000001</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>-0.1663</v>
+        <v>-0.1429</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>-0.6656</v>
+        <v>-0.5941</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>-0.5329</v>
+        <v>-0.6308</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>0.2764</v>
+        <v>-0.0757</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>1.81</v>
+        <v>6.41</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>2.1748</v>
+        <v>0.51</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>2.2285</v>
+        <v>0.4203</v>
       </c>
       <c r="M94" s="4" t="n">
-        <v>2.5519</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>7.8348</v>
+        <v>0.2482</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>0.887</v>
+        <v>0.0483</v>
       </c>
       <c r="P94" s="4" t="n">
-        <v>1.1538</v>
+        <v>0.2852</v>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr"/>
@@ -5927,57 +5927,57 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>ORGE</t>
+          <t>TUPRS</t>
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>20.8</v>
+        <v>359.25</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>0.001</v>
+        <v>-0.0076</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>-0.0877</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>-0.0698</v>
+        <v>-0.1369</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>-0.0537</v>
+        <v>0.1441</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>0.2644</v>
+        <v>0.3506</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>0.5581</v>
+        <v>1.0239</v>
       </c>
       <c r="I95" s="6" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>9.66</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="K95" s="7" t="n">
-        <v>0.251</v>
+        <v>0.465</v>
       </c>
       <c r="L95" s="7" t="n">
-        <v>0.257</v>
+        <v>1.0453</v>
       </c>
       <c r="M95" s="7" t="n">
-        <v>0.2421</v>
+        <v>1.1002</v>
       </c>
       <c r="N95" s="7" t="n">
-        <v>0.2676</v>
+        <v>2.2351</v>
       </c>
       <c r="O95" s="7" t="n">
-        <v>0.4943</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>0.2029</v>
+        <v>0.187</v>
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="R95" s="5" t="inlineStr"/>
@@ -5985,57 +5985,57 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>MEGMT</t>
+          <t>ORGE</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>3.21</v>
+        <v>20</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>0.0355</v>
+        <v>-0.0385</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>-0.07490000000000001</v>
+        <v>-0.1304</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>-0.1397</v>
+        <v>-0.08839999999999999</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>-0.5531</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.2048</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>0.0265</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>6.86</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0.51</v>
+        <v>0.251</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>0.4203</v>
+        <v>0.257</v>
       </c>
       <c r="M96" s="4" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.2421</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>0.2482</v>
+        <v>0.2676</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>0.0483</v>
+        <v>0.4943</v>
       </c>
       <c r="P96" s="4" t="n">
-        <v>0.2852</v>
+        <v>0.2029</v>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr"/>
@@ -6047,31 +6047,31 @@
         </is>
       </c>
       <c r="B97" s="6" t="n">
-        <v>21.82</v>
+        <v>21.04</v>
       </c>
       <c r="C97" s="7" t="n">
-        <v>-0.0127</v>
+        <v>-0.0357</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>-0.1543</v>
+        <v>-0.1781</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>-0.3147</v>
+        <v>-0.2868</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>-0.3871</v>
+        <v>-0.4106</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>-0.4647</v>
+        <v>-0.4856</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>-0.3959</v>
+        <v>-0.4236</v>
       </c>
       <c r="I97" s="6" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="J97" s="6" t="n">
-        <v>12.02</v>
+        <v>11.59</v>
       </c>
       <c r="K97" s="7" t="n">
         <v>0.1436</v>
@@ -6105,31 +6105,31 @@
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>0.0365</v>
+        <v>-0.0163</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>-0.1214</v>
+        <v>-0.1378</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>-0.08439999999999999</v>
+        <v>-0.1059</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>-0.289</v>
+        <v>-0.34</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>-0.2264</v>
+        <v>-0.2681</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>0.164</v>
+        <v>0.21</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>11.99</v>
+        <v>11.79</v>
       </c>
       <c r="K98" s="4" t="n">
         <v>1.0251</v>
@@ -6163,31 +6163,31 @@
         </is>
       </c>
       <c r="B99" s="6" t="n">
-        <v>11.84</v>
+        <v>11.28</v>
       </c>
       <c r="C99" s="7" t="n">
-        <v>0.0077</v>
+        <v>-0.0473</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>-0.0133</v>
+        <v>-0.0521</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>0.0017</v>
+        <v>-0.0359</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>-0.4061999999999999</v>
+        <v>-0.414</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>-0.5425</v>
+        <v>-0.5517</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>-0.4389</v>
+        <v>-0.4471</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>17.22</v>
+        <v>16.4</v>
       </c>
       <c r="K99" s="7" t="n">
         <v>0.7861</v>
@@ -6217,53 +6217,53 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>SAYAS</t>
+          <t>SANEL</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>35.36</v>
+        <v>23.8</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>0.0309</v>
+        <v>-0.0718</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>-0.1208</v>
+        <v>-0.1793</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>-0.2422</v>
+        <v>-0.4121</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>-0.2842</v>
+        <v>-0.6955</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>-0.1956</v>
+        <v>-0.3227</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>-0.3476</v>
+        <v>-0.1185</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>14.09</v>
+        <v>2.29</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0.486</v>
+        <v>0.309</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>1.4655</v>
+        <v>1.4614</v>
       </c>
       <c r="M100" s="4" t="n">
-        <v>2.3632</v>
+        <v>1.5381</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>6.118200000000001</v>
+        <v>2.2148</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>0.1798</v>
+        <v>0.1491</v>
       </c>
       <c r="P100" s="4" t="n">
-        <v>0.1493</v>
+        <v>1.0947</v>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
@@ -6275,57 +6275,57 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>SANEL</t>
+          <t>ENERY</t>
         </is>
       </c>
       <c r="B101" s="6" t="n">
-        <v>25.64</v>
+        <v>12.79</v>
       </c>
       <c r="C101" s="7" t="n">
-        <v>0.0063</v>
+        <v>-0.09029999999999999</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>-0.1593</v>
+        <v>-0.1191</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>-0.3426</v>
+        <v>-0.0039</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>-0.6556000000000001</v>
+        <v>0.3534</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>-0.2862</v>
+        <v>0.4009</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>-0.05110000000000001</v>
+        <v>0.3577</v>
       </c>
       <c r="I101" s="6" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>2.47</v>
+        <v>20.4</v>
       </c>
       <c r="K101" s="7" t="n">
-        <v>0.309</v>
+        <v>0.4279</v>
       </c>
       <c r="L101" s="7" t="n">
-        <v>1.4614</v>
+        <v>0.7162999999999999</v>
       </c>
       <c r="M101" s="7" t="n">
-        <v>1.5381</v>
+        <v>0.8373999999999999</v>
       </c>
       <c r="N101" s="7" t="n">
-        <v>2.2148</v>
+        <v>0.6103000000000001</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>0.1491</v>
+        <v>0.2099</v>
       </c>
       <c r="P101" s="7" t="n">
-        <v>1.0947</v>
+        <v>0.1017</v>
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R101" s="5" t="inlineStr"/>
@@ -6333,55 +6333,57 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>DURDO</t>
+          <t>SAYAS</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>6.07</v>
+        <v>34.48</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>0.09960000000000001</v>
+        <v>-0.0249</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>-0.0501</v>
+        <v>-0.1177</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>0.2189</v>
+        <v>-0.2495</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>0.154</v>
+        <v>-0.2888</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>0.2998</v>
+        <v>-0.211</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>0.7853</v>
+        <v>-0.3513</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr"/>
+        <v>1.7</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>13.74</v>
+      </c>
       <c r="K102" s="4" t="n">
-        <v>0.3099</v>
+        <v>0.486</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>0.2862</v>
+        <v>1.4655</v>
       </c>
       <c r="M102" s="4" t="n">
-        <v>0.3279</v>
+        <v>2.3632</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>0.1519</v>
+        <v>6.118200000000001</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>0.0876</v>
+        <v>0.1798</v>
       </c>
       <c r="P102" s="4" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.1493</v>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr"/>
@@ -6393,31 +6395,31 @@
         </is>
       </c>
       <c r="B103" s="6" t="n">
-        <v>237.7</v>
+        <v>227.9</v>
       </c>
       <c r="C103" s="7" t="n">
-        <v>0.0115</v>
+        <v>-0.0412</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.126</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>-0.163</v>
+        <v>-0.1918</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>-0.2096</v>
+        <v>-0.2327</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>-0.1775</v>
+        <v>-0.2228</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>-0.0697</v>
+        <v>-0.1132</v>
       </c>
       <c r="I103" s="6" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>9.35</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="K103" s="7" t="n">
         <v>1.7224</v>
@@ -6451,31 +6453,31 @@
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>416.5</v>
+        <v>402.25</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>0.0374</v>
+        <v>-0.0342</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>-0.0359</v>
+        <v>-0.064</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>-0.0425</v>
+        <v>-0.0694</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>0.0048</v>
+        <v>-0.0171</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>-0.1067</v>
+        <v>-0.1312</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>0.2718</v>
+        <v>0.2226</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>13.01</v>
+        <v>12.56</v>
       </c>
       <c r="K104" s="4" t="n">
         <v>0.3601</v>
@@ -6505,57 +6507,55 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>ENERY</t>
+          <t>DURDO</t>
         </is>
       </c>
       <c r="B105" s="6" t="n">
-        <v>14.06</v>
+        <v>5.99</v>
       </c>
       <c r="C105" s="7" t="n">
-        <v>0.0611</v>
+        <v>-0.0132</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>-0.0403</v>
+        <v>-0.0611</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>0.1097</v>
+        <v>0.2718</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>0.4816</v>
+        <v>0.1815</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>0.5184000000000001</v>
+        <v>0.2827</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>0.5151</v>
+        <v>0.7212999999999999</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="J105" s="6" t="n">
-        <v>22.42</v>
-      </c>
+        <v>1.78</v>
+      </c>
+      <c r="J105" s="5" t="inlineStr"/>
       <c r="K105" s="7" t="n">
-        <v>0.4279</v>
+        <v>0.3099</v>
       </c>
       <c r="L105" s="7" t="n">
-        <v>0.7162999999999999</v>
+        <v>0.2862</v>
       </c>
       <c r="M105" s="7" t="n">
-        <v>0.8373999999999999</v>
+        <v>0.3279</v>
       </c>
       <c r="N105" s="7" t="n">
-        <v>0.6103000000000001</v>
+        <v>0.1519</v>
       </c>
       <c r="O105" s="7" t="n">
-        <v>0.2099</v>
+        <v>0.0876</v>
       </c>
       <c r="P105" s="7" t="n">
-        <v>0.1017</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="Q105" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R105" s="5" t="inlineStr"/>
@@ -6563,57 +6563,57 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GRSEL</t>
+          <t>AHGAZ</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>268.5</v>
+        <v>44.2</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>0.0347</v>
+        <v>-0.0718</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>-0.047</v>
+        <v>-0.073</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>-0.0272</v>
+        <v>0.0625</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>-0.1764</v>
+        <v>0.2271</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>-0.1304</v>
+        <v>0.6073</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>-0.2372</v>
+        <v>0.7707999999999999</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>8.16</v>
+        <v>20.92</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0.3337</v>
+        <v>0.659</v>
       </c>
       <c r="L106" s="4" t="n">
-        <v>0.6940999999999999</v>
+        <v>1.7979</v>
       </c>
       <c r="M106" s="4" t="n">
-        <v>0.2722</v>
+        <v>2.1313</v>
       </c>
       <c r="N106" s="4" t="n">
-        <v>0.7318000000000001</v>
+        <v>2.8917</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>0.3275</v>
+        <v>0.1977</v>
       </c>
       <c r="P106" s="4" t="n">
-        <v>0.3613</v>
+        <v>0.1152</v>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr"/>
@@ -6621,57 +6621,57 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>VBTYZ</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B107" s="6" t="n">
-        <v>19.7</v>
+        <v>196</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>0.0423</v>
+        <v>-0.04389999999999999</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>-0.142</v>
+        <v>-0.1067</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>-0.3545</v>
+        <v>-0.1366</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>-0.3477</v>
+        <v>-0.1765</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>-0.098</v>
+        <v>-0.2447</v>
       </c>
       <c r="H107" s="7" t="n">
-        <v>0.1043</v>
+        <v>-0.1638</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="J107" s="6" t="n">
-        <v>12.89</v>
+        <v>18.32</v>
       </c>
       <c r="K107" s="7" t="n">
-        <v>0.5342</v>
+        <v>0.493</v>
       </c>
       <c r="L107" s="7" t="n">
-        <v>0.9976999999999999</v>
+        <v>0.3835</v>
       </c>
       <c r="M107" s="7" t="n">
-        <v>3.6408</v>
+        <v>0.4282</v>
       </c>
       <c r="N107" s="7" t="n">
-        <v>1.3528</v>
+        <v>0.1825</v>
       </c>
       <c r="O107" s="7" t="n">
-        <v>0.2074</v>
+        <v>0.2029</v>
       </c>
       <c r="P107" s="7" t="n">
-        <v>-9.062000000000001</v>
+        <v>0.1296</v>
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R107" s="5" t="inlineStr"/>
@@ -6679,53 +6679,53 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>GRSEL</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>205</v>
+        <v>262.5</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>0.07440000000000001</v>
+        <v>-0.0223</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>-0.077</v>
+        <v>-0.0917</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>-0.1228</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>-0.1239</v>
+        <v>-0.1797</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>-0.2093</v>
+        <v>-0.1315</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>-0.1224</v>
+        <v>-0.2558</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>19.16</v>
+        <v>7.97</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0.493</v>
+        <v>0.3337</v>
       </c>
       <c r="L108" s="4" t="n">
-        <v>0.3835</v>
+        <v>0.6940999999999999</v>
       </c>
       <c r="M108" s="4" t="n">
-        <v>0.4282</v>
+        <v>0.2722</v>
       </c>
       <c r="N108" s="4" t="n">
-        <v>0.1825</v>
+        <v>0.7318000000000001</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>0.2029</v>
+        <v>0.3275</v>
       </c>
       <c r="P108" s="4" t="n">
-        <v>0.1296</v>
+        <v>0.3613</v>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
@@ -6737,57 +6737,57 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>AHGAZ</t>
+          <t>GLYHO</t>
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>47.62</v>
+        <v>16.7</v>
       </c>
       <c r="C109" s="7" t="n">
-        <v>0.0625</v>
+        <v>-0.0441</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>-0.0274</v>
+        <v>-0.0533</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>0.162</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>0.3482</v>
+        <v>-0.0441</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>0.7611</v>
+        <v>0.057</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>0.9079</v>
+        <v>0.6535</v>
       </c>
       <c r="I109" s="6" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="J109" s="6" t="n">
-        <v>22.53</v>
+        <v>5.58</v>
       </c>
       <c r="K109" s="7" t="n">
-        <v>0.659</v>
+        <v>0.2312</v>
       </c>
       <c r="L109" s="7" t="n">
-        <v>1.7979</v>
+        <v>0.317</v>
       </c>
       <c r="M109" s="7" t="n">
-        <v>2.1313</v>
+        <v>0.3503</v>
       </c>
       <c r="N109" s="7" t="n">
-        <v>2.8917</v>
+        <v>0.4888</v>
       </c>
       <c r="O109" s="7" t="n">
-        <v>0.1977</v>
+        <v>0.3457</v>
       </c>
       <c r="P109" s="7" t="n">
-        <v>0.1152</v>
+        <v>-0.2226</v>
       </c>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R109" s="5" t="inlineStr"/>
@@ -6795,57 +6795,57 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GLYHO</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>17.47</v>
+        <v>39.06</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>0.0252</v>
+        <v>-0.09960000000000001</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>-0.024</v>
+        <v>-0.1846</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>0.1134</v>
+        <v>-0.3685</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>0.0128</v>
+        <v>-0.6121</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>0.1043</v>
+        <v>-0.045</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>0.7365999999999999</v>
+        <v>0.492</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>5.83</v>
+        <v>27.69</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0.2312</v>
+        <v>0.8139</v>
       </c>
       <c r="L110" s="4" t="n">
-        <v>0.317</v>
+        <v>1.3529</v>
       </c>
       <c r="M110" s="4" t="n">
-        <v>0.3503</v>
+        <v>2.0375</v>
       </c>
       <c r="N110" s="4" t="n">
-        <v>0.4888</v>
+        <v>1.6152</v>
       </c>
       <c r="O110" s="4" t="n">
-        <v>0.3457</v>
+        <v>0.1821</v>
       </c>
       <c r="P110" s="4" t="n">
-        <v>-0.2226</v>
+        <v>0.09230000000000001</v>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr"/>
@@ -6853,57 +6853,57 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>VBTYZ</t>
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>43.38</v>
+        <v>19.75</v>
       </c>
       <c r="C111" s="7" t="n">
-        <v>0.0265</v>
+        <v>0.0025</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>-0.1204</v>
+        <v>-0.1338</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>-0.2018</v>
+        <v>-0.3021</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>-0.5982999999999999</v>
+        <v>-0.3813</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>0.04480000000000001</v>
+        <v>-0.0745</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>0.6659</v>
+        <v>0.1003</v>
       </c>
       <c r="I111" s="6" t="n">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="J111" s="6" t="n">
-        <v>30.75</v>
+        <v>12.93</v>
       </c>
       <c r="K111" s="7" t="n">
-        <v>0.8139</v>
+        <v>0.5342</v>
       </c>
       <c r="L111" s="7" t="n">
-        <v>1.3529</v>
+        <v>0.9976999999999999</v>
       </c>
       <c r="M111" s="7" t="n">
-        <v>2.0375</v>
+        <v>3.6408</v>
       </c>
       <c r="N111" s="7" t="n">
-        <v>1.6152</v>
+        <v>1.3528</v>
       </c>
       <c r="O111" s="7" t="n">
-        <v>0.1821</v>
+        <v>0.2074</v>
       </c>
       <c r="P111" s="7" t="n">
-        <v>0.09230000000000001</v>
+        <v>-9.062000000000001</v>
       </c>
       <c r="Q111" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R111" s="5" t="inlineStr"/>
@@ -6918,22 +6918,22 @@
         <v>385.5</v>
       </c>
       <c r="C112" s="4" t="n">
-        <v>0.0391</v>
+        <v>0</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>-0.0326</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>-0.0755</v>
+        <v>-0.08380000000000001</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>-0.0228</v>
+        <v>-0.0338</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>0.0172</v>
+        <v>0.0131</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>0.4575</v>
+        <v>0.4318</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>2.27</v>
@@ -6976,22 +6976,22 @@
         <v>76.7</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="D113" s="7" t="n">
-        <v>-0.0692</v>
+        <v>-0.08310000000000001</v>
       </c>
       <c r="E113" s="7" t="n">
+        <v>-0.05309999999999999</v>
+      </c>
+      <c r="F113" s="7" t="n">
+        <v>-0.1699</v>
+      </c>
+      <c r="G113" s="7" t="n">
         <v>-0.0412</v>
       </c>
-      <c r="F113" s="7" t="n">
-        <v>-0.1722</v>
-      </c>
-      <c r="G113" s="7" t="n">
-        <v>-0.0424</v>
-      </c>
       <c r="H113" s="7" t="n">
-        <v>0.5834</v>
+        <v>0.5233</v>
       </c>
       <c r="I113" s="6" t="n">
         <v>2.34</v>
@@ -7031,31 +7031,31 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>41.72</v>
+        <v>40.26</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>0.0306</v>
+        <v>-0.035</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>-0.0484</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>-0.1673</v>
+        <v>-0.1964</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>-0.1653</v>
+        <v>-0.1964</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>-0.1486</v>
+        <v>-0.1289</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.6078</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>26.64</v>
+        <v>25.71</v>
       </c>
       <c r="K114" s="4" t="n">
         <v>1.2681</v>
@@ -7089,31 +7089,31 @@
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>107.3</v>
+        <v>104.5</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>0.0458</v>
+        <v>-0.0261</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>-0.134</v>
+        <v>-0.1511</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-0.0694</v>
+        <v>-0.09759999999999999</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>-0.2308</v>
+        <v>-0.2718</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>0.0075</v>
+        <v>0.0029</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>1.4644</v>
+        <v>1.3536</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="J115" s="6" t="n">
-        <v>9.619999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="K115" s="7" t="n">
         <v>2.4396</v>
@@ -7147,31 +7147,31 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>125.2</v>
+        <v>118.5</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>0.0381</v>
+        <v>-0.0535</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>-0.1121</v>
+        <v>-0.13</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>-0.09539999999999998</v>
+        <v>-0.1742</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>-0.0861</v>
+        <v>-0.1331</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>-0.1226</v>
+        <v>-0.156</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>-0.1714</v>
+        <v>-0.195</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>13.61</v>
+        <v>12.89</v>
       </c>
       <c r="K116" s="4" t="n">
         <v>0.5617</v>
@@ -7205,31 +7205,31 @@
         </is>
       </c>
       <c r="B117" s="6" t="n">
-        <v>30.82</v>
+        <v>30.08</v>
       </c>
       <c r="C117" s="7" t="n">
-        <v>0.0172</v>
+        <v>-0.024</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>-0.0393</v>
+        <v>-0.08289999999999999</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>-0.0575</v>
+        <v>-0.0176</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>-0.1746</v>
+        <v>-0.2051</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>-0.2769</v>
+        <v>-0.2865</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>-0.3343</v>
+        <v>-0.3603</v>
       </c>
       <c r="I117" s="6" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>22.49</v>
+        <v>21.95</v>
       </c>
       <c r="K117" s="7" t="n">
         <v>0.3957</v>
@@ -7263,31 +7263,31 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>59.85</v>
+        <v>59.55</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>0.0992</v>
+        <v>-0.005</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>-0.0973</v>
+        <v>-0.0688</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>0.0187</v>
+        <v>-0.0278</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>-0.1351</v>
+        <v>-0.1613</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>0.3951</v>
+        <v>0.3734</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>1.3959</v>
+        <v>1.3538</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>14.9</v>
+        <v>14.83</v>
       </c>
       <c r="K118" s="4" t="n">
         <v>2.0657</v>
@@ -7321,31 +7321,31 @@
         </is>
       </c>
       <c r="B119" s="6" t="n">
-        <v>80</v>
+        <v>74.5</v>
       </c>
       <c r="C119" s="7" t="n">
-        <v>0.008800000000000001</v>
+        <v>-0.0688</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.1911</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>-0.1753</v>
+        <v>-0.1994</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>-0.4118</v>
+        <v>-0.4609</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>-0.2</v>
+        <v>-0.3221</v>
       </c>
       <c r="H119" s="7" t="n">
-        <v>0.0139</v>
+        <v>-0.0318</v>
       </c>
       <c r="I119" s="6" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>17.69</v>
+        <v>16.47</v>
       </c>
       <c r="K119" s="7" t="n">
         <v>0.5093</v>
@@ -7375,57 +7375,57 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>ATATP</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>208.8</v>
+        <v>354.5</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>0.0286</v>
+        <v>-0.05019999999999999</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>-0.1062</v>
+        <v>-0.1149</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>-0.2121</v>
+        <v>-0.1897</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>-0.1411</v>
+        <v>-0.1761</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>0.4311</v>
+        <v>-0.315</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>0.6286999999999999</v>
+        <v>0.2582</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>4.3</v>
+        <v>15.37</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0.3072</v>
+        <v>0.1897</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>0.2985</v>
+        <v>0.4879</v>
       </c>
       <c r="M120" s="4" t="n">
-        <v>0.3487</v>
+        <v>0.6424</v>
       </c>
       <c r="N120" s="4" t="n">
-        <v>0.6609999999999999</v>
+        <v>0.5356000000000001</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>0.3268</v>
+        <v>0.2097</v>
       </c>
       <c r="P120" s="4" t="n">
-        <v>0.7543000000000001</v>
+        <v>0.2503</v>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr"/>
@@ -7433,57 +7433,55 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>OYAYO</t>
         </is>
       </c>
       <c r="B121" s="6" t="n">
-        <v>373.25</v>
+        <v>26</v>
       </c>
       <c r="C121" s="7" t="n">
-        <v>0.04769999999999999</v>
+        <v>-0.08839999999999999</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>-0.08460000000000001</v>
+        <v>-0.1667</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-0.133</v>
+        <v>-0.3197</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>-0.1166</v>
+        <v>-0.4468</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>-0.2801</v>
+        <v>-0.5212</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>0.3786</v>
+        <v>-0.2622</v>
       </c>
       <c r="I121" s="6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J121" s="6" t="n">
-        <v>16.18</v>
-      </c>
+        <v>2.99</v>
+      </c>
+      <c r="J121" s="5" t="inlineStr"/>
       <c r="K121" s="7" t="n">
-        <v>0.1897</v>
+        <v>0.3933</v>
       </c>
       <c r="L121" s="7" t="n">
-        <v>0.4879</v>
+        <v>0.4082</v>
       </c>
       <c r="M121" s="7" t="n">
-        <v>0.6424</v>
+        <v>0.6868000000000001</v>
       </c>
       <c r="N121" s="7" t="n">
-        <v>0.5356000000000001</v>
+        <v>0.2959</v>
       </c>
       <c r="O121" s="7" t="n">
-        <v>0.2097</v>
+        <v>0.7368000000000001</v>
       </c>
       <c r="P121" s="7" t="n">
-        <v>0.2503</v>
+        <v>-0.0453</v>
       </c>
       <c r="Q121" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R121" s="5" t="inlineStr"/>
@@ -7495,31 +7493,31 @@
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>17</v>
+        <v>16.94</v>
       </c>
       <c r="C122" s="4" t="n">
-        <v>-0.0029</v>
+        <v>-0.0035</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>-0.09570000000000001</v>
+        <v>-0.09849999999999999</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>-0.1517</v>
+        <v>-0.1177</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>-0.2342</v>
+        <v>-0.2404</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>-0.2093</v>
+        <v>-0.2698</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>0.1806</v>
+        <v>0.1563</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>22.39</v>
+        <v>22.31</v>
       </c>
       <c r="K122" s="4" t="n">
         <v>0.6388</v>
@@ -7549,55 +7547,57 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>OYAYO</t>
+          <t>ATATP</t>
         </is>
       </c>
       <c r="B123" s="6" t="n">
-        <v>28.52</v>
+        <v>218.5</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>-0.0104</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>-0.08650000000000001</v>
+        <v>-0.0433</v>
       </c>
       <c r="E123" s="7" t="n">
-        <v>-0.2863</v>
+        <v>-0.1052</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>-0.3776</v>
+        <v>-0.1564</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>-0.4838</v>
+        <v>0.5453</v>
       </c>
       <c r="H123" s="7" t="n">
-        <v>-0.1781</v>
+        <v>0.7232</v>
       </c>
       <c r="I123" s="6" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="J123" s="5" t="inlineStr"/>
+        <v>3.19</v>
+      </c>
+      <c r="J123" s="6" t="n">
+        <v>4.49</v>
+      </c>
       <c r="K123" s="7" t="n">
-        <v>0.3933</v>
+        <v>0.3072</v>
       </c>
       <c r="L123" s="7" t="n">
-        <v>0.4082</v>
+        <v>0.2985</v>
       </c>
       <c r="M123" s="7" t="n">
-        <v>0.6868000000000001</v>
+        <v>0.3487</v>
       </c>
       <c r="N123" s="7" t="n">
-        <v>0.2959</v>
+        <v>0.6609999999999999</v>
       </c>
       <c r="O123" s="7" t="n">
-        <v>0.7368000000000001</v>
+        <v>0.3268</v>
       </c>
       <c r="P123" s="7" t="n">
-        <v>-0.0453</v>
+        <v>0.7543000000000001</v>
       </c>
       <c r="Q123" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R123" s="5" t="inlineStr"/>
@@ -7605,57 +7605,57 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>YEOTK</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>24.96</v>
+        <v>117.9</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>0.0365</v>
+        <v>-0.1</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>-0.0803</v>
+        <v>-0.0796</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>-0.159</v>
+        <v>-0.1784</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>-0.3937</v>
+        <v>-0.4238</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>0.08470000000000001</v>
+        <v>-0.1875</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>0.7748</v>
+        <v>2.1524</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>3.76</v>
+        <v>3.48</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>13.13</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1.4662</v>
+        <v>1.164</v>
       </c>
       <c r="L124" s="4" t="n">
-        <v>1.5472</v>
+        <v>0.8115000000000001</v>
       </c>
       <c r="M124" s="4" t="n">
-        <v>1.7095</v>
+        <v>1.571</v>
       </c>
       <c r="N124" s="4" t="n">
-        <v>3.7317</v>
+        <v>1.7066</v>
       </c>
       <c r="O124" s="4" t="n">
-        <v>0.1898</v>
+        <v>0.1178</v>
       </c>
       <c r="P124" s="4" t="n">
-        <v>0.7681999999999999</v>
+        <v>0.3402000000000001</v>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr"/>
@@ -7663,57 +7663,57 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>YEOTK</t>
         </is>
       </c>
       <c r="B125" s="6" t="n">
-        <v>165.9</v>
+        <v>23.66</v>
       </c>
       <c r="C125" s="7" t="n">
-        <v>0.033</v>
+        <v>-0.0521</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>-0.1553</v>
+        <v>-0.1218</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-0.3557</v>
+        <v>-0.2268</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>-0.4484</v>
+        <v>-0.43</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>-0.2334</v>
+        <v>0.06480000000000001</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>0.7121</v>
+        <v>0.6631999999999999</v>
       </c>
       <c r="I125" s="6" t="n">
-        <v>3.78</v>
+        <v>3.57</v>
       </c>
       <c r="J125" s="6" t="n">
-        <v>16.27</v>
+        <v>8.82</v>
       </c>
       <c r="K125" s="7" t="n">
-        <v>0.4338</v>
+        <v>1.4662</v>
       </c>
       <c r="L125" s="7" t="n">
-        <v>0.5232</v>
+        <v>1.5472</v>
       </c>
       <c r="M125" s="7" t="n">
-        <v>0.7125</v>
+        <v>1.7095</v>
       </c>
       <c r="N125" s="7" t="n">
-        <v>0.8672</v>
+        <v>3.7317</v>
       </c>
       <c r="O125" s="7" t="n">
-        <v>0.3018</v>
+        <v>0.1898</v>
       </c>
       <c r="P125" s="7" t="n">
-        <v>0.3122</v>
+        <v>0.7681999999999999</v>
       </c>
       <c r="Q125" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R125" s="5" t="inlineStr"/>
@@ -7721,57 +7721,57 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>131</v>
+        <v>156.6</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>0.07820000000000001</v>
+        <v>-0.0561</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>0.0108</v>
+        <v>-0.1977</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>-0.2686</v>
+        <v>-0.3786</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>-0.3327000000000001</v>
+        <v>-0.478</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>-0.0643</v>
+        <v>-0.2507</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>2.649</v>
+        <v>0.6045</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>3.86</v>
+        <v>3.57</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>14.59</v>
+        <v>15.36</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1.164</v>
+        <v>0.4338</v>
       </c>
       <c r="L126" s="4" t="n">
-        <v>0.8115000000000001</v>
+        <v>0.5232</v>
       </c>
       <c r="M126" s="4" t="n">
-        <v>1.571</v>
+        <v>0.7125</v>
       </c>
       <c r="N126" s="4" t="n">
-        <v>1.7066</v>
+        <v>0.8672</v>
       </c>
       <c r="O126" s="4" t="n">
-        <v>0.1178</v>
+        <v>0.3018</v>
       </c>
       <c r="P126" s="4" t="n">
-        <v>0.3402000000000001</v>
+        <v>0.3122</v>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr"/>
@@ -7783,31 +7783,31 @@
         </is>
       </c>
       <c r="B127" s="6" t="n">
-        <v>90.34999999999999</v>
+        <v>85</v>
       </c>
       <c r="C127" s="7" t="n">
-        <v>0.0175</v>
+        <v>-0.0592</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>-0.0185</v>
+        <v>-0.0561</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>-0.2184</v>
+        <v>-0.1835</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>-0.6618999999999999</v>
+        <v>-0.6875</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>-0.6855</v>
+        <v>-0.7015</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>-0.4786</v>
+        <v>-0.5025999999999999</v>
       </c>
       <c r="I127" s="6" t="n">
-        <v>4.27</v>
+        <v>4.01</v>
       </c>
       <c r="J127" s="6" t="n">
-        <v>29.84</v>
+        <v>28.07</v>
       </c>
       <c r="K127" s="7" t="n">
         <v>0.5028</v>
@@ -7841,31 +7841,31 @@
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>216.2</v>
+        <v>210.3</v>
       </c>
       <c r="C128" s="4" t="n">
-        <v>0.0174</v>
+        <v>-0.0273</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>-0.1685</v>
+        <v>-0.1769</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>-0.2394</v>
+        <v>-0.2087</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>-0.2467</v>
+        <v>-0.2717</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>-0.259</v>
+        <v>-0.2704</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>-0.2935</v>
+        <v>-0.3211</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>4.33</v>
+        <v>4.21</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>21.87</v>
+        <v>21.27</v>
       </c>
       <c r="K128" s="4" t="n">
         <v>0.2837</v>
@@ -7899,31 +7899,31 @@
         </is>
       </c>
       <c r="B129" s="8" t="n">
-        <v>11200</v>
+        <v>11220</v>
       </c>
       <c r="C129" s="7" t="n">
-        <v>0.0334</v>
+        <v>0.0018</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>0.0443</v>
+        <v>0.0289</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>0.0549</v>
+        <v>0.1008</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>0.0226</v>
+        <v>0.0207</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>0.1529</v>
+        <v>0.2029</v>
       </c>
       <c r="H129" s="7" t="n">
-        <v>0.0669</v>
+        <v>0.0665</v>
       </c>
       <c r="I129" s="6" t="n">
-        <v>4.39</v>
+        <v>4.4</v>
       </c>
       <c r="J129" s="6" t="n">
-        <v>20.57</v>
+        <v>20.6</v>
       </c>
       <c r="K129" s="7" t="n">
         <v>0.2032</v>
@@ -7957,31 +7957,31 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>6.83</v>
+        <v>6.61</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>0</v>
+        <v>-0.0322</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>0.0044</v>
+        <v>0.0138</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>-0.4265</v>
+        <v>-0.3675</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>-0.4685</v>
+        <v>-0.4931</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>0.3996</v>
+        <v>0.3857</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>1.1614</v>
+        <v>1.064</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>4.79</v>
+        <v>4.64</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>58.43</v>
+        <v>56.54</v>
       </c>
       <c r="K130" s="4" t="n">
         <v>0.4591</v>
@@ -8015,31 +8015,31 @@
         </is>
       </c>
       <c r="B131" s="6" t="n">
-        <v>342.75</v>
+        <v>345.75</v>
       </c>
       <c r="C131" s="7" t="n">
-        <v>0.0636</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>0.0007000000000000001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="E131" s="7" t="n">
-        <v>-0.0974</v>
+        <v>-0.0731</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>-0.0532</v>
+        <v>-0.0693</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>-0.141</v>
+        <v>-0.1335</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>0.755</v>
+        <v>0.6940000000000001</v>
       </c>
       <c r="I131" s="6" t="n">
-        <v>5.1</v>
+        <v>5.14</v>
       </c>
       <c r="J131" s="6" t="n">
-        <v>42.11</v>
+        <v>42.48</v>
       </c>
       <c r="K131" s="7" t="n">
         <v>0.5623</v>
@@ -8073,28 +8073,28 @@
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>20.64</v>
+        <v>19.86</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>0.0019</v>
+        <v>-0.0378</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>-0.1527</v>
+        <v>-0.1841</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>-0.2783</v>
+        <v>-0.2856</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>-0.4169</v>
+        <v>-0.4658</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>-0.4956</v>
+        <v>-0.5115999999999999</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>-0.3359</v>
+        <v>-0.3663</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>5.99</v>
+        <v>5.76</v>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="4" t="n">
@@ -8129,28 +8129,28 @@
         </is>
       </c>
       <c r="B133" s="6" t="n">
-        <v>9.220000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>0.0022</v>
+        <v>-0.0184</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>-0.0446</v>
+        <v>-0.0216</v>
       </c>
       <c r="E133" s="7" t="n">
-        <v>-0.324</v>
+        <v>-0.1963</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>-0.3119</v>
+        <v>-0.2902</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>0.2647</v>
+        <v>0.2067</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>0.7845</v>
+        <v>0.6258</v>
       </c>
       <c r="I133" s="6" t="n">
-        <v>6.66</v>
+        <v>6.54</v>
       </c>
       <c r="J133" s="5" t="inlineStr"/>
       <c r="K133" s="7" t="n">
@@ -8185,28 +8185,28 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>12.36</v>
+        <v>11.13</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>-0.0048</v>
+        <v>-0.09949999999999999</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>-0.0214</v>
+        <v>-0.1345</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>0.3121</v>
+        <v>0.3234</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>-0.0594</v>
+        <v>-0.1536</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>0.5222</v>
+        <v>0.3219</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>0.4284000000000001</v>
+        <v>0.244</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>10.03</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="4" t="n">
@@ -8241,28 +8241,28 @@
         </is>
       </c>
       <c r="B135" s="8" t="n">
-        <v>1163</v>
+        <v>1120</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>0.0113</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>-0.1026</v>
+        <v>-0.1223</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>-0.2672</v>
+        <v>-0.2727</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>-0.34</v>
+        <v>-0.3711</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>-0.263</v>
+        <v>-0.3013</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>-0.3135</v>
+        <v>-0.3477</v>
       </c>
       <c r="I135" s="6" t="n">
-        <v>10.33</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="J135" s="5" t="inlineStr"/>
       <c r="K135" s="7" t="n">
@@ -8297,31 +8297,31 @@
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>34.98</v>
+        <v>34.66</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>-0.0011</v>
+        <v>-0.0091</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>-0.1468</v>
+        <v>-0.1326</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>-0.0857</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>-0.34</v>
+        <v>-0.2815</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>-0.1769</v>
+        <v>-0.1648</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>-0.2976</v>
+        <v>-0.2686</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>10.72</v>
+        <v>10.62</v>
       </c>
       <c r="J136" s="3" t="n">
-        <v>38.58</v>
+        <v>38.22</v>
       </c>
       <c r="K136" s="4" t="n">
         <v>0.2618</v>
@@ -8355,28 +8355,28 @@
         </is>
       </c>
       <c r="B137" s="6" t="n">
-        <v>249.4</v>
+        <v>247.5</v>
       </c>
       <c r="C137" s="7" t="n">
-        <v>-0.0004</v>
+        <v>-0.0076</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>-0.09880000000000001</v>
+        <v>-0.0833</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>-0.2218</v>
+        <v>-0.2016</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>-0.3004</v>
+        <v>-0.2918</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>-0.4169</v>
+        <v>-0.4107</v>
       </c>
       <c r="H137" s="7" t="n">
-        <v>-0.5203</v>
+        <v>-0.4986</v>
       </c>
       <c r="I137" s="6" t="n">
-        <v>10.73</v>
+        <v>10.65</v>
       </c>
       <c r="J137" s="5" t="inlineStr"/>
       <c r="K137" s="7" t="n">
@@ -8411,28 +8411,28 @@
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>38.3</v>
+        <v>37.74</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>0.0052</v>
+        <v>-0.0146</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>-0.0052</v>
+        <v>-0.0243</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>-0.2021</v>
+        <v>-0.1831</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>-0.1515</v>
+        <v>-0.1511</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>-0.1004</v>
+        <v>-0.1078</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>0.2035</v>
+        <v>0.1849</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>14.3</v>
+        <v>14.09</v>
       </c>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="4" t="n">
@@ -8467,31 +8467,31 @@
         </is>
       </c>
       <c r="B139" s="6" t="n">
-        <v>95.84999999999999</v>
+        <v>93.55</v>
       </c>
       <c r="C139" s="7" t="n">
-        <v>0.0132</v>
+        <v>-0.024</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>-0.0906</v>
+        <v>-0.0654</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>-0.2039</v>
+        <v>-0.2004</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>-0.2564</v>
+        <v>-0.2754</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>-0.3694</v>
+        <v>-0.3792</v>
       </c>
       <c r="H139" s="7" t="n">
-        <v>-0.4047</v>
+        <v>-0.4222</v>
       </c>
       <c r="I139" s="6" t="n">
-        <v>14.58</v>
+        <v>14.23</v>
       </c>
       <c r="J139" s="6" t="n">
-        <v>54.92</v>
+        <v>53.6</v>
       </c>
       <c r="K139" s="7" t="n">
         <v>0.3045</v>
@@ -8525,25 +8525,25 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>0.0219</v>
+        <v>-0.0143</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>-0.1463</v>
+        <v>-0.1176</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>-0.125</v>
+        <v>-0.1529</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>0.1111</v>
+        <v>0.0935</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>0.1111</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>-0.0014</v>
+        <v>0.0051</v>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr"/>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>20.10.2026 19:27</t>
+          <t>21.10.2026 19:26</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_latest.xlsx
+++ b/data/bist_screener_latest.xlsx
@@ -586,22 +586,22 @@
         <v>12.13</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-0.07049999999999999</v>
+        <v>0</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.2123</v>
+        <v>-0.1354</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.4908</v>
+        <v>-0.4486</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-0.4661</v>
+        <v>-0.4599</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>-0.6095</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.3767</v>
+        <v>-0.3728</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0.18</v>
@@ -639,31 +639,31 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>-0.033</v>
+        <v>-0.0244</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>-0.0682</v>
+        <v>-0.061</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>-0.0421</v>
+        <v>-0.0385</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>-0.2054</v>
+        <v>-0.2337</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>-0.3653</v>
+        <v>-0.3808</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-0.3121</v>
+        <v>-0.3243</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0.21</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>2.7227</v>
@@ -693,57 +693,57 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MERIT</t>
+          <t>HLGYO</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13.4</v>
+        <v>3.73</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.0083</v>
+        <v>-0.046</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.019</v>
+        <v>-0.08800000000000001</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.07139999999999999</v>
+        <v>-0.0721</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.1884</v>
+        <v>-0.2657</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.1859</v>
+        <v>-0.3536</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.3463000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>6.23</v>
+        <v>1.11</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.9854999999999999</v>
+        <v>1.7259</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>1.0319</v>
+        <v>1.4642</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>2.0871</v>
+        <v>2.8476</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>1.5834</v>
+        <v>2.0883</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.6354</v>
+        <v>0.1249</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.0454</v>
+        <v>0.2374</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr"/>
@@ -751,55 +751,57 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>SNICA</t>
+          <t>MERIT</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>1.95</v>
+        <v>13.15</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>-0.0394</v>
+        <v>-0.0187</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-0.1295</v>
+        <v>0.0092</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-0.2323</v>
+        <v>-0.09119999999999999</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>-0.4961</v>
+        <v>-0.2011</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-0.529</v>
+        <v>-0.2011</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>-0.6061</v>
+        <v>-0.3541</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0.22</v>
       </c>
-      <c r="J5" s="5" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>6.11</v>
+      </c>
       <c r="K5" s="7" t="n">
-        <v>0.2451</v>
+        <v>0.9854999999999999</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>0.1328</v>
+        <v>1.0319</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>0.7476999999999999</v>
+        <v>2.0871</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>0.4518</v>
+        <v>1.5834</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>0.0576</v>
+        <v>0.6354</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>-0.1748</v>
+        <v>0.0454</v>
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R5" s="5" t="inlineStr"/>
@@ -807,57 +809,55 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HLGYO</t>
+          <t>SNICA</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.91</v>
+        <v>1.9</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0151</v>
+        <v>-0.0256</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.0713</v>
+        <v>-0.108</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.0322</v>
+        <v>-0.2664</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2904</v>
+        <v>-0.5128</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3224</v>
+        <v>-0.5411</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1108</v>
+        <v>-0.6192</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0.22</v>
       </c>
-      <c r="J6" s="3" t="n">
-        <v>1.17</v>
-      </c>
+      <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="4" t="n">
-        <v>1.7259</v>
+        <v>0.2451</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.4642</v>
+        <v>0.1328</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.8476</v>
+        <v>0.7476999999999999</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2.0883</v>
+        <v>0.4518</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1249</v>
+        <v>0.0576</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2374</v>
+        <v>-0.1748</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr"/>
@@ -869,31 +869,31 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>-0.013</v>
+        <v>-0.0197</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-0.0256</v>
+        <v>-0.0132</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-0.1314</v>
+        <v>-0.1078</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>-0.2475</v>
+        <v>-0.2587</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-0.3184</v>
+        <v>-0.3318</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>-0.3821</v>
+        <v>-0.4134</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>8.51</v>
+        <v>8.34</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>0.2518</v>
@@ -927,25 +927,25 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>9.08</v>
+        <v>8.94</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.0163</v>
+        <v>-0.0154</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1019</v>
+        <v>-0.0924</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1303</v>
+        <v>-0.127</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2292</v>
+        <v>-0.232</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2906</v>
+        <v>-0.3016</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2906</v>
+        <v>-0.2732</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0.23</v>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>-0.0293</v>
+        <v>-0.0216</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-0.0683</v>
+        <v>-0.08839999999999999</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-0.05690000000000001</v>
+        <v>-0.0581</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>-0.1714</v>
+        <v>-0.1864</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-0.1831</v>
+        <v>-0.2007</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-0.1179</v>
+        <v>-0.0992</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0.23</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>5.45</v>
+        <v>5.33</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>0.3848</v>
@@ -1041,31 +1041,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8.82</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.0222</v>
+        <v>-0.0204</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.0851</v>
+        <v>-0.0464</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1718</v>
+        <v>-0.162</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2644</v>
+        <v>-0.2558</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2989</v>
+        <v>-0.3132</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3039</v>
+        <v>-0.3032</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>10.5</v>
+        <v>10.29</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0.3203</v>
@@ -1099,31 +1099,31 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3.93</v>
+        <v>3.83</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>-0.0415</v>
+        <v>-0.0254</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.1155</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-0.05980000000000001</v>
+        <v>-0.0567</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>-0.2944</v>
+        <v>-0.2921</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-0.2202</v>
+        <v>-0.2401</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-0.0796</v>
+        <v>-0.1937</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0.24</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>14.08</v>
+        <v>13.72</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>0.1479</v>
@@ -1157,25 +1157,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>6.29</v>
+        <v>6.27</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.0064</v>
+        <v>-0.0032</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.0513</v>
+        <v>-0.0457</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1348</v>
+        <v>-0.1328</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2244</v>
+        <v>-0.1793</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.266</v>
+        <v>-0.2684</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.15</v>
+        <v>-0.1504</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0.25</v>
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>11.06</v>
+        <v>11</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.0357</v>
+        <v>-0.0054</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>-0.21</v>
+        <v>-0.1822</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>-0.3577</v>
+        <v>-0.3529</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>-0.5212</v>
+        <v>-0.5205</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-0.5710000000000001</v>
+        <v>-0.5733</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.7241</v>
+        <v>-0.7253000000000001</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0.28</v>
@@ -1269,25 +1269,25 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>4.9</v>
+        <v>4.79</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.008100000000000001</v>
+        <v>-0.0224</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1581</v>
+        <v>-0.1626</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.05769999999999999</v>
+        <v>-0.0663</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.212</v>
+        <v>-0.2403</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3196</v>
+        <v>-0.3349</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4372</v>
+        <v>-0.4375</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.31</v>
@@ -1325,31 +1325,31 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>-0.0462</v>
+        <v>0.0242</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>-0.2029</v>
+        <v>-0.0815</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-0.1316</v>
+        <v>-0.1289</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>-0.3028</v>
+        <v>-0.3258</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-0.3571</v>
+        <v>-0.3416</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.3293</v>
+        <v>-0.3017</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0.32</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>7.78</v>
+        <v>7.97</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>0.9460999999999999</v>
@@ -1383,31 +1383,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9.99</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0177</v>
+        <v>-0.02</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.0843</v>
+        <v>-0.101</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1633</v>
+        <v>-0.1661</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.242</v>
+        <v>-0.2555</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2808</v>
+        <v>-0.2952</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2403</v>
+        <v>-0.2611</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.33</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.33</v>
+        <v>5.22</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>0.3789</v>
@@ -1441,28 +1441,28 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>-0.0479</v>
+        <v>-0.0216</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>-0.2446</v>
+        <v>-0.2184</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>-0.4303</v>
+        <v>-0.431</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>-0.6551</v>
+        <v>-0.6504000000000001</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>-0.6426999999999999</v>
+        <v>-0.6504000000000001</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-0.8482999999999999</v>
+        <v>-0.8473999999999999</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="J17" s="5" t="inlineStr"/>
       <c r="K17" s="7" t="n">
@@ -1497,31 +1497,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>178.7</v>
+        <v>173.8</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.0341</v>
+        <v>-0.0274</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.0741</v>
+        <v>-0.09849999999999999</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.0614</v>
+        <v>-0.0886</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.147</v>
+        <v>-0.1563</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.0545</v>
+        <v>-0.08039999999999999</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1993</v>
+        <v>0.1587</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>2.97</v>
+        <v>2.89</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>0.5672999999999999</v>
@@ -1555,28 +1555,28 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>-0.0355</v>
+        <v>-0.0184</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>-0.1641</v>
+        <v>-0.1623</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>-0.3963</v>
+        <v>-0.3388</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>-0.6936</v>
+        <v>-0.6911</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>-0.7495999999999999</v>
+        <v>-0.7542</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-0.6082</v>
+        <v>-0.619</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="7" t="n">
@@ -1611,31 +1611,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>35.26</v>
+        <v>34.08</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.027</v>
+        <v>-0.0335</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.06570000000000001</v>
+        <v>-0.0888</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.11</v>
+        <v>-0.1531</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.1917</v>
+        <v>-0.2201</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2542</v>
+        <v>-0.2792</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.859999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>0.2329</v>
@@ -1669,31 +1669,31 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>6.83</v>
+        <v>6.64</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>-0.0243</v>
+        <v>-0.0278</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>-0.0808</v>
+        <v>-0.1015</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-0.2058</v>
+        <v>-0.2188</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>-0.3647</v>
+        <v>-0.3718</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-0.4132</v>
+        <v>-0.4296</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-0.2973</v>
+        <v>-0.3176</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>3.03</v>
+        <v>2.95</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>0.9081</v>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>9.34</v>
+        <v>8.99</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.0566</v>
+        <v>-0.0375</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.123</v>
+        <v>-0.1479</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.185</v>
+        <v>-0.2445</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.3931</v>
+        <v>-0.4027000000000001</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4663</v>
+        <v>-0.4863</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.303</v>
+        <v>-0.3331</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3.51</v>
+        <v>3.38</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>0.4985</v>
@@ -1785,31 +1785,31 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>17.29</v>
+        <v>16.57</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>-0.0204</v>
+        <v>-0.0416</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>-0.0613</v>
+        <v>-0.0794</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>-0.1441</v>
+        <v>-0.1715</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>-0.1898</v>
+        <v>-0.2235</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-0.1852</v>
+        <v>-0.2191</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-0.0052</v>
+        <v>-0.0389</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>6.99</v>
+        <v>6.69</v>
       </c>
       <c r="K23" s="7" t="n">
         <v>0.1285</v>
@@ -1839,55 +1839,57 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ERBOS</t>
+          <t>SEKFK</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>97.5</v>
+        <v>2.92</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.0552</v>
+        <v>-0.09880000000000001</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.1341</v>
+        <v>-0.2736</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.1882</v>
+        <v>-0.2416</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.4119</v>
+        <v>-0.4172</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5196999999999999</v>
+        <v>-0.5327000000000001</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.4637</v>
+        <v>-0.3329</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
+        <v>0.48</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>2.37</v>
+      </c>
       <c r="K24" s="4" t="n">
-        <v>0.2349</v>
+        <v>0.208</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.1405</v>
+        <v>0.0571</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.0386</v>
+        <v>0.0025</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.7831999999999999</v>
+        <v>0.2707</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.131</v>
+        <v>0.6072</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.023</v>
+        <v>0.2346</v>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr"/>
@@ -1899,31 +1901,31 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5.38</v>
+        <v>5.23</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>-0.0271</v>
+        <v>-0.0279</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>-0.1166</v>
+        <v>-0.1269</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-0.1836</v>
+        <v>-0.1866</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>-0.4152</v>
+        <v>-0.4253</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>-0.3935</v>
+        <v>-0.4104</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-0.2412</v>
+        <v>-0.2913</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>6.46</v>
+        <v>6.28</v>
       </c>
       <c r="K25" s="7" t="n">
         <v>0.6883</v>
@@ -1953,57 +1955,55 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SEKFK</t>
+          <t>ERBOS</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>3.24</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.0062</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.2059</v>
+        <v>-0.127</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.19</v>
+        <v>-0.2064</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3684000000000001</v>
+        <v>-0.4323</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4815</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2671</v>
+        <v>-0.4719</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>2.63</v>
-      </c>
+        <v>0.49</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="4" t="n">
-        <v>0.208</v>
+        <v>0.2349</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.0571</v>
+        <v>1.1405</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.0025</v>
+        <v>1.0386</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.2707</v>
+        <v>0.7831999999999999</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.6072</v>
+        <v>0.131</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.2346</v>
+        <v>-0.023</v>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr"/>
@@ -2015,31 +2015,31 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>29.28</v>
+        <v>28.18</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>-0.0591</v>
+        <v>-0.03759999999999999</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>-0.1133</v>
+        <v>-0.1292</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-0.1368</v>
+        <v>-0.1717</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>-0.1625</v>
+        <v>-0.1898</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>-0.0645</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>0.142</v>
+        <v>0.1209</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>16.01</v>
+        <v>15.41</v>
       </c>
       <c r="K27" s="7" t="n">
         <v>0.3105</v>
@@ -2069,57 +2069,57 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>OYYAT</t>
+          <t>KRSTL</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>23.74</v>
+        <v>6.13</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.0458</v>
+        <v>-0.0362</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1062</v>
+        <v>-0.1462</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.0925</v>
+        <v>-0.2161</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3818</v>
+        <v>-0.4083</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.5817</v>
+        <v>-0.3387</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5542</v>
+        <v>-0.4335</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.04</v>
+        <v>3.53</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.045</v>
+        <v>0.3806</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.4061999999999999</v>
+        <v>0.2571</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.4311</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.0744</v>
+        <v>0.6774</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.2671</v>
+        <v>0.1192</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.2126</v>
+        <v>0.1788</v>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr"/>
@@ -2127,57 +2127,57 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>KRSTL</t>
+          <t>OYYAT</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>6.36</v>
+        <v>23.34</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>-0.0536</v>
+        <v>-0.0168</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>-0.152</v>
+        <v>-0.1285</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-0.204</v>
+        <v>-0.1782</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>-0.4011</v>
+        <v>-0.3825</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>-0.3139</v>
+        <v>-0.5887</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>-0.3994</v>
+        <v>-0.5637</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>3.66</v>
+        <v>2.99</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.3806</v>
+        <v>0.045</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.2571</v>
+        <v>0.4061999999999999</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.5529999999999999</v>
+        <v>0.4311</v>
       </c>
       <c r="N29" s="7" t="n">
-        <v>0.6774</v>
+        <v>3.0744</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>0.1192</v>
+        <v>0.2671</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>0.1788</v>
+        <v>0.2126</v>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R29" s="5" t="inlineStr"/>
@@ -2185,55 +2185,57 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BAKAB</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>26.68</v>
+        <v>2.83</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.0298</v>
+        <v>-0.0987</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1011</v>
+        <v>-0.4042</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2162</v>
+        <v>-0.8998999999999999</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.463</v>
+        <v>-0.9342</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3878</v>
+        <v>-0.887</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2746</v>
+        <v>-0.9217</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr"/>
+        <v>0.53</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="K30" s="4" t="n">
-        <v>0.3479</v>
+        <v>7.8666</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.5443</v>
+        <v>3.1929</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.7171</v>
+        <v>4.946499999999999</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.97</v>
+        <v>1.0979</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.0552</v>
+        <v>0.4854</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.0031</v>
+        <v>0.586</v>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr"/>
@@ -2245,28 +2247,28 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>-0.0282</v>
+        <v>-0.029</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>-0.0548</v>
+        <v>-0.053</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-0.0951</v>
+        <v>-0.127</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>-0.2747</v>
+        <v>-0.2884</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>-0.1876</v>
+        <v>-0.2112</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>-0.0449</v>
+        <v>-0.0717</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="7" t="n">
@@ -2297,57 +2299,55 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>BAKAB</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>3.14</v>
+        <v>26.24</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.0977</v>
+        <v>-0.0165</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.4042</v>
+        <v>-0.092</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.9</v>
+        <v>-0.2282</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.9266</v>
+        <v>-0.4587</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.8745999999999999</v>
+        <v>-0.3979</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.9036</v>
+        <v>-0.2795</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>0.57</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="4" t="n">
-        <v>7.8666</v>
+        <v>0.3479</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3.1929</v>
+        <v>0.5443</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.946499999999999</v>
+        <v>0.7171</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>1.0979</v>
+        <v>0.97</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.4854</v>
+        <v>0.0552</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.586</v>
+        <v>-0.0031</v>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr"/>
@@ -2355,55 +2355,55 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>SOKE</t>
+          <t>DOKTA</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>7.4</v>
+        <v>13.67</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>-0.0415</v>
+        <v>-0.042</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>-0.0352</v>
+        <v>-0.0917</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-0.1284</v>
+        <v>-0.2876</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>-0.6076</v>
+        <v>-0.4108</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>-0.5889</v>
+        <v>-0.4475</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>-0.3333</v>
+        <v>-0.4183</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="J33" s="5" t="inlineStr"/>
       <c r="K33" s="7" t="n">
-        <v>0.5234000000000001</v>
+        <v>0.2983</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.4561</v>
+        <v>1.25</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.4897</v>
+        <v>3.5566</v>
       </c>
       <c r="N33" s="7" t="n">
-        <v>0.3644</v>
+        <v>0.6970000000000001</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>0.032</v>
+        <v>0.0852</v>
       </c>
       <c r="P33" s="7" t="n">
-        <v>-0.0429</v>
+        <v>-0.0451</v>
       </c>
       <c r="Q33" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R33" s="5" t="inlineStr"/>
@@ -2411,55 +2411,55 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>DOKTA</t>
+          <t>SOKE</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>14.27</v>
+        <v>7.26</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0189</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.0499</v>
+        <v>-0.032</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2915</v>
+        <v>-0.0959</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3823</v>
+        <v>-0.5967</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.4232</v>
+        <v>-0.5967</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3812</v>
+        <v>-0.3506</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="4" t="n">
-        <v>0.2983</v>
+        <v>0.5234000000000001</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.25</v>
+        <v>0.4561</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>3.5566</v>
+        <v>0.4897</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.6970000000000001</v>
+        <v>0.3644</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.0852</v>
+        <v>0.032</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.0451</v>
+        <v>-0.0429</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr"/>
@@ -2471,31 +2471,31 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>29.22</v>
+        <v>28.08</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>-0.0337</v>
+        <v>-0.039</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>-0.1015</v>
+        <v>-0.1247</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-0.1722</v>
+        <v>-0.1628</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>-0.4068</v>
+        <v>-0.4106</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>-0.377</v>
+        <v>-0.4013</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>-0.2343</v>
+        <v>-0.2622</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>8.24</v>
+        <v>7.92</v>
       </c>
       <c r="K35" s="7" t="n">
         <v>0.306</v>
@@ -2525,57 +2525,57 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>OSMEN</t>
+          <t>MERCN</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>5.04</v>
+        <v>8.99</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>-0.0233</v>
+        <v>-0.0467</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>-0.0597</v>
+        <v>-0.1272</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>-0.1295</v>
+        <v>-0.3638</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>-0.4474</v>
+        <v>-0.6294</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.362</v>
+        <v>-0.604</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.4873</v>
+        <v>-0.7387</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>8.65</v>
+        <v>10.33</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1.6512</v>
+        <v>0.2374</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.1052</v>
+        <v>0.8593999999999999</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.04969999999999999</v>
+        <v>1.4059</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>5.9134</v>
+        <v>1.3031</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.1784</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>0.0863</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr"/>
@@ -2583,53 +2583,53 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>AKMGY</t>
+          <t>OSMEN</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>187.5</v>
+        <v>4.87</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>-0.0121</v>
+        <v>-0.0337</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>-0.0959</v>
+        <v>-0.0562</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-0.1848</v>
+        <v>-0.1048</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>-0.2322</v>
+        <v>-0.4631</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>-0.3249</v>
+        <v>-0.3835</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>-0.1607</v>
+        <v>-0.4906</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>9.24</v>
+        <v>8.35</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.3886</v>
+        <v>1.6512</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>0.3887</v>
+        <v>0.1052</v>
       </c>
       <c r="M37" s="7" t="n">
-        <v>0.3141</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="N37" s="7" t="n">
-        <v>0.5958</v>
+        <v>5.9134</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>0.6443000000000001</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="P37" s="7" t="n">
-        <v>0.0781</v>
+        <v>0.0863</v>
       </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
@@ -2641,57 +2641,57 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MERCN</t>
+          <t>AKMGY</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>9.43</v>
+        <v>181</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>-0.0446</v>
+        <v>-0.0347</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>-0.1154</v>
+        <v>-0.1171</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>-0.382</v>
+        <v>-0.2072</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-0.6103000000000001</v>
+        <v>-0.2555</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.5846</v>
+        <v>-0.3483</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.7134</v>
+        <v>-0.1902</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>10.84</v>
+        <v>8.92</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.2374</v>
+        <v>0.3886</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.8593999999999999</v>
+        <v>0.3887</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>1.4059</v>
+        <v>0.3141</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>1.3031</v>
+        <v>0.5958</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0.1784</v>
+        <v>0.6443000000000001</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0781</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr"/>
@@ -2703,31 +2703,31 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>5.26</v>
+        <v>5.1</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.0304</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>-0.1009</v>
+        <v>-0.1297</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>0.0499</v>
+        <v>-0.0135</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>-0.2581</v>
+        <v>-0.2995</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>-0.3701</v>
+        <v>-0.3892</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>-0.3222</v>
+        <v>-0.3316</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>9.890000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="K39" s="7" t="n">
         <v>0.4159</v>
@@ -2757,57 +2757,57 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>BNTAS</t>
+          <t>TTKOM</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>4.84</v>
+        <v>47.38</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>-0.0359</v>
+        <v>-0.0409</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>-0.0692</v>
+        <v>-0.0958</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>-0.1232</v>
+        <v>-0.1127</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>-0.213</v>
+        <v>-0.1509</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-0.2882</v>
+        <v>-0.2533</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.2611</v>
+        <v>-0.0486</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>4.48</v>
+        <v>5.86</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.2654</v>
+        <v>0.4498</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.4329</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.464</v>
+        <v>0.5323</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.3679</v>
+        <v>0.8047</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.1363</v>
+        <v>0.4117</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>0.1657</v>
+        <v>1.3041</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr"/>
@@ -2819,31 +2819,31 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>203.3</v>
+        <v>196.1</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>-0.0245</v>
+        <v>-0.0354</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>-0.0424</v>
+        <v>-0.06570000000000001</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-0.05309999999999999</v>
+        <v>-0.1175</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>-0.0068</v>
+        <v>-0.0111</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>-0.002</v>
+        <v>-0.0373</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>0.3074</v>
+        <v>0.2404</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>14.49</v>
+        <v>13.98</v>
       </c>
       <c r="K41" s="7" t="n">
         <v>0.3261</v>
@@ -2873,57 +2873,57 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TTKOM</t>
+          <t>BNTAS</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>49.4</v>
+        <v>4.73</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>-0.0352</v>
+        <v>-0.0227</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>-0.0509</v>
+        <v>-0.0851</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-0.0582</v>
+        <v>-0.1142</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-0.1584</v>
+        <v>-0.222</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-0.2214</v>
+        <v>-0.3044</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.2701</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>6.11</v>
+        <v>4.38</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0.4498</v>
+        <v>0.2654</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.4329</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.5323</v>
+        <v>0.464</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.8047</v>
+        <v>0.3679</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>0.4117</v>
+        <v>0.1363</v>
       </c>
       <c r="P42" s="4" t="n">
-        <v>1.3041</v>
+        <v>0.1657</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr"/>
@@ -2931,57 +2931,57 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>PINSU</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>7.33</v>
+        <v>93.3</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>-0.0355</v>
+        <v>-0.0179</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>-0.1555</v>
+        <v>-0.0431</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-0.1989</v>
+        <v>-0.06179999999999999</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>-0.3659000000000001</v>
+        <v>-0.1114</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>-0.3992</v>
+        <v>-0.1794</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>-0.482</v>
+        <v>-0.0411</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>15.45</v>
+        <v>10.48</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.2802</v>
+        <v>0.3971</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>0.2234</v>
+        <v>0.4118</v>
       </c>
       <c r="M43" s="7" t="n">
-        <v>0.3074</v>
+        <v>0.3975</v>
       </c>
       <c r="N43" s="7" t="n">
-        <v>91.6451</v>
+        <v>0.2377</v>
       </c>
       <c r="O43" s="7" t="n">
-        <v>0.1329</v>
+        <v>0.4333</v>
       </c>
       <c r="P43" s="7" t="n">
-        <v>0.0528</v>
+        <v>0.1518</v>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R43" s="5" t="inlineStr"/>
@@ -2989,57 +2989,57 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>PINSU</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>95</v>
+        <v>7.25</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>-0.0271</v>
+        <v>-0.0109</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>-0.0404</v>
+        <v>-0.142</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>-0.0226</v>
+        <v>-0.1927</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>-0.1395</v>
+        <v>-0.3584000000000001</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-0.1645</v>
+        <v>-0.4057</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>-0.0186</v>
+        <v>-0.4545</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>10.67</v>
+        <v>15.28</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0.3971</v>
+        <v>0.2802</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.4118</v>
+        <v>0.2234</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.3975</v>
+        <v>0.3074</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.2377</v>
+        <v>91.6451</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>0.4333</v>
+        <v>0.1329</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>0.1518</v>
+        <v>0.0528</v>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr"/>
@@ -3047,57 +3047,57 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>GRTHO</t>
+          <t>BASGZ</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>56.05</v>
+        <v>34.88</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>-0.0411</v>
+        <v>-0.0444</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>-0.3702</v>
+        <v>-0.1254</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-0.6126</v>
+        <v>-0.1627</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>-0.7722</v>
+        <v>-0.2579</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>-0.769</v>
+        <v>-0.2959</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>-0.9151</v>
+        <v>-0.09449999999999999</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>3.9</v>
+        <v>6.32</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.5085000000000001</v>
+        <v>0.3163</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>0.4487</v>
+        <v>0.5275</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>0.2298</v>
+        <v>0.4513</v>
       </c>
       <c r="N45" s="7" t="n">
-        <v>0.9399</v>
+        <v>0.3789</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>0.1089</v>
+        <v>0.1301</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>0.2287</v>
+        <v>-0.245</v>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R45" s="5" t="inlineStr"/>
@@ -3109,31 +3109,31 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>270.25</v>
+        <v>263.75</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>-0.0092</v>
+        <v>-0.0241</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>-0.0808</v>
+        <v>-0.09519999999999999</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>-0.164</v>
+        <v>-0.1553</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-0.0434</v>
+        <v>-0.081</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-0.0173</v>
+        <v>-0.0409</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.4931</v>
+        <v>0.4452</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>7.1</v>
+        <v>6.93</v>
       </c>
       <c r="K46" s="4" t="n">
         <v>0.1662</v>
@@ -3163,57 +3163,57 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>BASGZ</t>
+          <t>RALYH</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>36.5</v>
+        <v>17.65</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>-0.0445</v>
+        <v>-0.0999</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>-0.0898</v>
+        <v>-0.3434</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-0.123</v>
+        <v>-0.89</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>-0.2086</v>
+        <v>-0.9308</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>-0.2632</v>
+        <v>-0.9459000000000001</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>-0.0568</v>
+        <v>-0.9059999999999999</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>6.61</v>
+        <v>2.29</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.3163</v>
+        <v>0.7070000000000001</v>
       </c>
       <c r="L47" s="7" t="n">
-        <v>0.5275</v>
+        <v>1.4848</v>
       </c>
       <c r="M47" s="7" t="n">
-        <v>0.4513</v>
+        <v>1.5369</v>
       </c>
       <c r="N47" s="7" t="n">
-        <v>0.3789</v>
+        <v>0.5434</v>
       </c>
       <c r="O47" s="7" t="n">
-        <v>0.1301</v>
+        <v>0.2854</v>
       </c>
       <c r="P47" s="7" t="n">
-        <v>-0.245</v>
+        <v>0.3914</v>
       </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R47" s="5" t="inlineStr"/>
@@ -3221,57 +3221,55 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>ISFIN</t>
+          <t>AYES</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>15.21</v>
+        <v>6</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.0053</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>-0.08259999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>-0.1743</v>
+        <v>-0.1174</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-0.2172</v>
+        <v>-0.3573</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-0.2659</v>
+        <v>-0.3547999999999999</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>-0.1147</v>
+        <v>0.2755</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.59</v>
+        <v>1.65</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0.5749</v>
+        <v>0.4183</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.5787</v>
+        <v>0.314</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.5648</v>
+        <v>0.8128</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.6275999999999999</v>
+        <v>42.7724</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>0.9556</v>
-      </c>
-      <c r="P48" s="4" t="n">
-        <v>0.3468</v>
-      </c>
+        <v>0.0208</v>
+      </c>
+      <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr"/>
@@ -3279,57 +3277,57 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>ARASE</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>36.52</v>
+        <v>70.75</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>-0.0178</v>
+        <v>-0.07519999999999999</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>-0.0178</v>
+        <v>-0.2576</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>0.0038</v>
+        <v>-0.303</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>-0.1354</v>
+        <v>-0.4182</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0.123</v>
+        <v>-0.2974</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0.3556</v>
+        <v>0.3554</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>31.83</v>
+        <v>6.45</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.1998</v>
+        <v>0.1264</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>0.3838</v>
+        <v>0.596</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0.4877</v>
+        <v>0.7123999999999999</v>
       </c>
       <c r="N49" s="7" t="n">
-        <v>0.4752</v>
+        <v>4.0303</v>
       </c>
       <c r="O49" s="7" t="n">
-        <v>0.104</v>
+        <v>0.25</v>
       </c>
       <c r="P49" s="7" t="n">
-        <v>0.0274</v>
+        <v>0.1463</v>
       </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R49" s="5" t="inlineStr"/>
@@ -3337,57 +3335,57 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>RALYH</t>
+          <t>GRTHO</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>19.62</v>
+        <v>57.6</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>-0.09960000000000001</v>
+        <v>0.0277</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.3433</v>
+        <v>-0.2809</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>-0.89</v>
+        <v>-0.5579</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>-0.9254000000000001</v>
+        <v>-0.7664</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.9399</v>
+        <v>-0.7626000000000001</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>-0.8905</v>
+        <v>-0.9054000000000001</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>2.54</v>
+        <v>4.01</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0.7070000000000001</v>
+        <v>0.5085000000000001</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>1.4848</v>
+        <v>0.4487</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>1.5369</v>
+        <v>0.2298</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.5434</v>
+        <v>0.9399</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>0.2854</v>
+        <v>0.1089</v>
       </c>
       <c r="P50" s="4" t="n">
-        <v>0.3914</v>
+        <v>0.2287</v>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr"/>
@@ -3395,55 +3393,57 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>AYES</t>
+          <t>ISFIN</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>6.51</v>
+        <v>14.77</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>-0.0469</v>
+        <v>-0.0289</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-0.132</v>
+        <v>-0.2164</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>-0.2995</v>
+        <v>-0.2433</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>-0.3</v>
+        <v>-0.2872</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>0.3691</v>
+        <v>-0.1794</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>1.79</v>
+        <v>2.51</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.4183</v>
+        <v>0.5749</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>0.314</v>
+        <v>0.5787</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>0.8128</v>
+        <v>0.5648</v>
       </c>
       <c r="N51" s="7" t="n">
-        <v>42.7724</v>
+        <v>0.6275999999999999</v>
       </c>
       <c r="O51" s="7" t="n">
-        <v>0.0208</v>
-      </c>
-      <c r="P51" s="5" t="inlineStr"/>
+        <v>0.9556</v>
+      </c>
+      <c r="P51" s="7" t="n">
+        <v>0.3468</v>
+      </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R51" s="5" t="inlineStr"/>
@@ -3451,57 +3451,57 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ARASE</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>76.5</v>
+        <v>35.1</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.0389</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.2073</v>
+        <v>-0.05139999999999999</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>-0.2884</v>
+        <v>-0.059</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>-0.3806</v>
+        <v>-0.203</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-0.2403</v>
+        <v>0.0793</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.474</v>
+        <v>0.2801</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>6.97</v>
+        <v>30.59</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0.1264</v>
+        <v>0.1998</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.596</v>
+        <v>0.3838</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.7123999999999999</v>
+        <v>0.4877</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>4.0303</v>
+        <v>0.4752</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>0.25</v>
+        <v>0.104</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>0.1463</v>
+        <v>0.0274</v>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr"/>
@@ -3513,31 +3513,31 @@
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>7.3</v>
+        <v>7.01</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>-0.047</v>
+        <v>-0.0397</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>-0.159</v>
+        <v>-0.1645</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-0.1609</v>
+        <v>-0.2446</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>-0.3345</v>
+        <v>-0.3592</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>-0.3546</v>
+        <v>-0.3802</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>-0.2678</v>
+        <v>-0.2919</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>27.17</v>
+        <v>26.09</v>
       </c>
       <c r="K53" s="7" t="n">
         <v>0.8458</v>
@@ -3571,31 +3571,31 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>8</v>
+        <v>7.72</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>-0.0279</v>
+        <v>-0.035</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>-0.0566</v>
+        <v>-0.0493</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>-0.1031</v>
+        <v>-0.1247</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>-0.2308</v>
+        <v>-0.2202</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-0.4318</v>
+        <v>-0.4517</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>-0.4667</v>
+        <v>-0.4766</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>7.58</v>
+        <v>7.31</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>0.2088</v>
@@ -3629,31 +3629,31 @@
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>85.2</v>
+        <v>82.05</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>-0.0362</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>-0.0834</v>
+        <v>-0.1033</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-0.1606</v>
+        <v>-0.1741</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>-0.1647</v>
+        <v>-0.2034</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>-0.3016</v>
+        <v>-0.3275</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>-0.1548</v>
+        <v>-0.1541</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>11.92</v>
+        <v>11.48</v>
       </c>
       <c r="K55" s="7" t="n">
         <v>0.4926</v>
@@ -3687,31 +3687,31 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>31.4</v>
+        <v>30.3</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.0616</v>
+        <v>-0.035</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.1982</v>
+        <v>-0.1739</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>-0.3319</v>
+        <v>-0.3129</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>-0.6253</v>
+        <v>-0.6343</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.3189</v>
+        <v>-0.3427</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>-0.2738</v>
+        <v>-0.2957</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>8.44</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="K56" s="4" t="n">
         <v>0.2641</v>
@@ -3745,31 +3745,31 @@
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>454</v>
+        <v>440.5</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>-0.0242</v>
+        <v>-0.0297</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>-0.08560000000000001</v>
+        <v>-0.08990000000000001</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-0.1352</v>
+        <v>-0.1812</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>-0.2895</v>
+        <v>-0.2991</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>-0.3074</v>
+        <v>-0.328</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>0.0248</v>
+        <v>0.0109</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>13.6</v>
+        <v>13.19</v>
       </c>
       <c r="K57" s="7" t="n">
         <v>0.3804</v>
@@ -3803,31 +3803,31 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>-0.0228</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>-0.0737</v>
+        <v>-0.0789</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>-0.0974</v>
+        <v>-0.1026</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>-0.0335</v>
+        <v>-0.0369</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-0.1927</v>
+        <v>-0.1972</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>-0.2129</v>
+        <v>-0.2074</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>0.88</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>13.32</v>
+        <v>13.24</v>
       </c>
       <c r="K58" s="4" t="n">
         <v>2.3363</v>
@@ -3857,57 +3857,57 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>CWENE</t>
+          <t>MOBTL</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>15.11</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>-0.0702</v>
+        <v>-0.0998</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>-0.1652</v>
+        <v>-0.2255</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-0.3587</v>
+        <v>-0.2106</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>-0.6264999999999999</v>
+        <v>-0.4440999999999999</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>-0.5732</v>
+        <v>-0.3832</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>-0.3211</v>
+        <v>0.102</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>5.62</v>
+        <v>11.64</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>0.5809000000000001</v>
+        <v>0.5631</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>0.9067000000000001</v>
+        <v>0.4406</v>
       </c>
       <c r="M59" s="7" t="n">
-        <v>0.8432999999999999</v>
+        <v>0.5064</v>
       </c>
       <c r="N59" s="7" t="n">
-        <v>5.095899999999999</v>
+        <v>1.6818</v>
       </c>
       <c r="O59" s="7" t="n">
-        <v>0.1918</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>0.2052</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R59" s="5" t="inlineStr"/>
@@ -3915,57 +3915,57 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>TNZTP</t>
+          <t>CWENE</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>23.2</v>
+        <v>15</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>-0.0043</v>
+        <v>-0.0073</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>-0.0823</v>
+        <v>-0.1187</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>-0.1407</v>
+        <v>-0.359</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>-0.05690000000000001</v>
+        <v>-0.6193</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-0.0668</v>
+        <v>-0.5763</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>0.0741</v>
+        <v>-0.3123</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>17.17</v>
+        <v>5.58</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0.4327</v>
+        <v>0.5809000000000001</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.4143</v>
+        <v>0.9067000000000001</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.5201</v>
+        <v>0.8432999999999999</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.0702</v>
+        <v>5.095899999999999</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>0.3617</v>
+        <v>0.1918</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>0.0551</v>
+        <v>0.2052</v>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>Sağlık hizmetleri</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr"/>
@@ -3973,57 +3973,55 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>MOBTL</t>
+          <t>BYDNR</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>9.119999999999999</v>
+        <v>18.42</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>-0.045</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>-0.118</v>
+        <v>-0.1058</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>-0.1128</v>
+        <v>-0.1311</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>-0.3762</v>
+        <v>-0.5274</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>-0.3148</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>0.2476</v>
+        <v>-0.08810000000000001</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="J61" s="6" t="n">
-        <v>12.93</v>
-      </c>
+        <v>0.92</v>
+      </c>
+      <c r="J61" s="5" t="inlineStr"/>
       <c r="K61" s="7" t="n">
-        <v>0.5631</v>
+        <v>0.2762</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>0.4406</v>
+        <v>0.0636</v>
       </c>
       <c r="M61" s="7" t="n">
-        <v>0.5064</v>
+        <v>0.127</v>
       </c>
       <c r="N61" s="7" t="n">
-        <v>1.6818</v>
+        <v>0.7182999999999999</v>
       </c>
       <c r="O61" s="7" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.1081</v>
       </c>
       <c r="P61" s="7" t="n">
-        <v>0.08689999999999999</v>
+        <v>-0.0257</v>
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R61" s="5" t="inlineStr"/>
@@ -4031,57 +4029,57 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>CIMSA</t>
+          <t>KTLEV</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>39.56</v>
+        <v>4.45</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>-0.0174</v>
+        <v>-0.0992</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>-0.0105</v>
+        <v>-0.3288</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>-0.0361</v>
+        <v>-0.7533</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>-0.2159</v>
+        <v>-0.9112</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-0.2973</v>
+        <v>-0.8567</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>-0.0735</v>
+        <v>0.1576</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>9.369999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0.3754999999999999</v>
+        <v>3.5578</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0.3037</v>
+        <v>3.6471</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.4933</v>
+        <v>5.174600000000001</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1.15</v>
+        <v>5.7649</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>0.1807</v>
+        <v>0.7222</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>0.2729</v>
+        <v>1.5072</v>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr"/>
@@ -4089,57 +4087,57 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>SELEC</t>
+          <t>TNZTP</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>60.3</v>
+        <v>22.94</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>0.0212</v>
+        <v>-0.0112</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>-0.1796</v>
+        <v>-0.09179999999999999</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-0.6854</v>
+        <v>-0.209</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>-0.7573000000000001</v>
+        <v>-0.0824</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>-0.3315</v>
+        <v>-0.07719999999999999</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>-0.242</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>1.01</v>
+        <v>0.96</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>18.38</v>
+        <v>16.97</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>0.3781</v>
+        <v>0.4327</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>0.6063000000000001</v>
+        <v>0.4143</v>
       </c>
       <c r="M63" s="7" t="n">
-        <v>1.4267</v>
+        <v>0.5201</v>
       </c>
       <c r="N63" s="7" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.0702</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>0.0158</v>
+        <v>0.3617</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.0551</v>
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Sağlık hizmetleri</t>
         </is>
       </c>
       <c r="R63" s="5" t="inlineStr"/>
@@ -4147,53 +4145,53 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>CMENT</t>
+          <t>CIMSA</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>215.1</v>
+        <v>38.54</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.0183</v>
+        <v>-0.0258</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.06480000000000001</v>
+        <v>-0.0432</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>-0.0346</v>
+        <v>-0.0704</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>-0.2564</v>
+        <v>-0.23</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.3655</v>
+        <v>-0.3155</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>-0.3937</v>
+        <v>-0.1099</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>21.23</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0.0934</v>
+        <v>0.3754999999999999</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.1109</v>
+        <v>0.3037</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.1008</v>
+        <v>0.4933</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.4922</v>
+        <v>1.15</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>0.1647</v>
+        <v>0.1807</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.2729</v>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
@@ -4205,57 +4203,57 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>INDES</t>
+          <t>MAALT</t>
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>11.47</v>
+        <v>649.5</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>-0.0378</v>
+        <v>-0.08130000000000001</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>-0.0146</v>
+        <v>-0.1592</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>0.1029</v>
+        <v>-0.2859</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>0.0241</v>
+        <v>-0.3814</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>0.168</v>
+        <v>-0.512</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>0.4668</v>
+        <v>-0.3569</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>9.67</v>
+        <v>1399.48</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>0.6297</v>
+        <v>0.248</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>0.8554999999999999</v>
+        <v>3.5256</v>
       </c>
       <c r="M65" s="7" t="n">
-        <v>1.0205</v>
+        <v>0.3863</v>
       </c>
       <c r="N65" s="7" t="n">
-        <v>1.9437</v>
+        <v>0.9832</v>
       </c>
       <c r="O65" s="7" t="n">
-        <v>0.0374</v>
+        <v>0.4575</v>
       </c>
       <c r="P65" s="7" t="n">
-        <v>0.137</v>
+        <v>-0</v>
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R65" s="5" t="inlineStr"/>
@@ -4263,55 +4261,57 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>BYDNR</t>
+          <t>INDES</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>20.46</v>
+        <v>11.36</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.04389999999999999</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.1143</v>
+        <v>-0.0348</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>-0.1976</v>
+        <v>0.0955</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>-0.4732</v>
+        <v>0.0299</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-0.4564</v>
+        <v>0.1568</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>0</v>
+        <v>0.4362</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>9.58</v>
+      </c>
       <c r="K66" s="4" t="n">
-        <v>0.2762</v>
+        <v>0.6297</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>0.0636</v>
+        <v>0.8554999999999999</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.127</v>
+        <v>1.0205</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.7182999999999999</v>
+        <v>1.9437</v>
       </c>
       <c r="O66" s="4" t="n">
-        <v>0.1081</v>
+        <v>0.0374</v>
       </c>
       <c r="P66" s="4" t="n">
-        <v>-0.0257</v>
+        <v>0.137</v>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr"/>
@@ -4319,57 +4319,57 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>KTLEV</t>
+          <t>CMENT</t>
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>4.94</v>
+        <v>215</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>-0.08689999999999999</v>
+        <v>-0.0005</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>-0.3413</v>
+        <v>-0.0106</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.0142</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>-0.9061</v>
+        <v>-0.2456</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>-0.8409</v>
+        <v>-0.3658</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>0.2523</v>
+        <v>-0.3831</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>1.2</v>
+        <v>21.22</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>3.5578</v>
+        <v>0.0934</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>3.6471</v>
+        <v>0.1109</v>
       </c>
       <c r="M67" s="7" t="n">
-        <v>5.174600000000001</v>
+        <v>0.1008</v>
       </c>
       <c r="N67" s="7" t="n">
-        <v>5.7649</v>
+        <v>0.4922</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>0.7222</v>
+        <v>0.1647</v>
       </c>
       <c r="P67" s="7" t="n">
-        <v>1.5072</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R67" s="5" t="inlineStr"/>
@@ -4381,31 +4381,31 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>56.85</v>
+        <v>55.25</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.0389</v>
+        <v>-0.0281</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>-0.08380000000000001</v>
+        <v>-0.0935</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>-0.06269999999999999</v>
+        <v>-0.1153</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>0.0252</v>
+        <v>-0.0247</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>0.2622</v>
+        <v>0.2267</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.4741</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>13.4</v>
+        <v>13.03</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>0.1859</v>
@@ -4435,57 +4435,55 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>MAALT</t>
+          <t>OBASE</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>707</v>
+        <v>18.64</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>-0.0133</v>
+        <v>-0.0876</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>-0.1163</v>
+        <v>-0.1111</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>-0.2455</v>
+        <v>-0.3783</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>-0.3502</v>
+        <v>-0.5946</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>-0.4688000000000001</v>
+        <v>-0.5156000000000001</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>-0.2898</v>
+        <v>-0.4714</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="J69" s="6" t="n">
-        <v>1523.38</v>
-      </c>
+        <v>1.04</v>
+      </c>
+      <c r="J69" s="5" t="inlineStr"/>
       <c r="K69" s="7" t="n">
-        <v>0.248</v>
+        <v>0.2041</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>3.5256</v>
+        <v>0.3021</v>
       </c>
       <c r="M69" s="7" t="n">
-        <v>0.3863</v>
+        <v>0.5156000000000001</v>
       </c>
       <c r="N69" s="7" t="n">
-        <v>0.9832</v>
+        <v>0.4873</v>
       </c>
       <c r="O69" s="7" t="n">
-        <v>0.4575</v>
+        <v>0.2465</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>-0</v>
+        <v>0.1432</v>
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R69" s="5" t="inlineStr"/>
@@ -4497,31 +4495,31 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>10.2</v>
+        <v>10.12</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0.001</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>-0.0116</v>
+        <v>-0.0059</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>-0.0599</v>
+        <v>-0.05860000000000001</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>-0.1486</v>
+        <v>-0.1574</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>-0.023</v>
+        <v>-0.0307</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>-0.1612</v>
+        <v>-0.165</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>6.84</v>
+        <v>6.79</v>
       </c>
       <c r="K70" s="4" t="n">
         <v>0.423</v>
@@ -4555,28 +4553,28 @@
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>-0.05980000000000001</v>
+        <v>-0.0136</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>-0.009000000000000001</v>
+        <v>-0.149</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>-0.3433</v>
+        <v>-0.2815</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>-0.306</v>
+        <v>-0.3282</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>-0.321</v>
+        <v>-0.3302</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>-0.3569</v>
+        <v>-0.3635</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="J71" s="5" t="inlineStr"/>
       <c r="K71" s="7" t="n">
@@ -4611,31 +4609,31 @@
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>75.8</v>
+        <v>73.5</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>-0.027</v>
+        <v>-0.0303</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>-0.0601</v>
+        <v>-0.0731</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>-0.1186</v>
+        <v>-0.1488</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>-0.1675</v>
+        <v>-0.1865</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>-0.2896</v>
+        <v>-0.3112</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>0.0455</v>
+        <v>0.0294</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>11.39</v>
+        <v>11.04</v>
       </c>
       <c r="K72" s="4" t="n">
         <v>0.4381</v>
@@ -4669,31 +4667,31 @@
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>9.85</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>-0.015</v>
+        <v>-0.0244</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>-0.0646</v>
+        <v>-0.0706</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-0.0725</v>
+        <v>-0.0925</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>-0.1617</v>
+        <v>-0.18</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>-0.1939</v>
+        <v>-0.2136</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>0.0524</v>
+        <v>-0.0113</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>6.26</v>
+        <v>6.11</v>
       </c>
       <c r="K73" s="7" t="n">
         <v>0.3448</v>
@@ -4723,55 +4721,57 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>OBASE</t>
+          <t>SELEC</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>20.44</v>
+        <v>66.3</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>-0.0466</v>
+        <v>0.09949999999999999</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>-0.1019</v>
+        <v>-0.09119999999999999</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>-0.3482</v>
+        <v>-0.6159</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>-0.5553</v>
+        <v>-0.725</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-0.4691</v>
+        <v>-0.265</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>-0.4332</v>
+        <v>-0.1929</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr"/>
+        <v>1.11</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>20.21</v>
+      </c>
       <c r="K74" s="4" t="n">
-        <v>0.2041</v>
+        <v>0.3781</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.3021</v>
+        <v>0.6063000000000001</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.5156000000000001</v>
+        <v>1.4267</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.4873</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>0.2465</v>
+        <v>0.0158</v>
       </c>
       <c r="P74" s="4" t="n">
-        <v>0.1432</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr"/>
@@ -4783,31 +4783,31 @@
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>34.46</v>
+        <v>34.32</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>-0.04219999999999999</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0843</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-0.2589</v>
+        <v>-0.2559</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>-0.3785</v>
+        <v>-0.3597</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>-0.4486</v>
+        <v>-0.4509</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>-0.4795</v>
+        <v>-0.4881</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="K75" s="7" t="n">
         <v>0.265</v>
@@ -4837,55 +4837,57 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>DAGI</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>5.42</v>
+        <v>27.16</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.0767</v>
+        <v>-0.0286</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>-0.1597</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>-0.1187</v>
+        <v>-0.1931</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>-0.4354</v>
+        <v>-0.2497</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.17</v>
+        <v>-0.3751</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>-0.3547999999999999</v>
+        <v>-0.3376</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr"/>
+        <v>1.16</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>6.07</v>
+      </c>
       <c r="K76" s="4" t="n">
-        <v>0.5429999999999999</v>
+        <v>0.4021</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>1.1389</v>
+        <v>0.2915</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>1.8634</v>
+        <v>0.201</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.5748</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>0.1561</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="P76" s="4" t="n">
-        <v>-0.0597</v>
+        <v>0.298</v>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R76" s="2" t="inlineStr"/>
@@ -4893,57 +4895,55 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="B77" s="6" t="n">
-        <v>27.96</v>
+        <v>5.56</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>-0.0189</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>-0.0372</v>
+        <v>-0.1272</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-0.1693</v>
+        <v>-0.1907</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>-0.2348</v>
+        <v>-0.2853</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>-0.3566</v>
+        <v>-0.3365</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>-0.3065</v>
+        <v>-0.3269</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="J77" s="6" t="n">
-        <v>6.24</v>
-      </c>
+        <v>1.16</v>
+      </c>
+      <c r="J77" s="5" t="inlineStr"/>
       <c r="K77" s="7" t="n">
-        <v>0.4021</v>
+        <v>0.3952000000000001</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>0.2915</v>
+        <v>0.4088000000000001</v>
       </c>
       <c r="M77" s="7" t="n">
-        <v>0.201</v>
+        <v>0.4094</v>
       </c>
       <c r="N77" s="7" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.7489</v>
       </c>
       <c r="O77" s="7" t="n">
-        <v>0.8484999999999999</v>
+        <v>0.7836</v>
       </c>
       <c r="P77" s="7" t="n">
-        <v>0.298</v>
+        <v>-0.0106</v>
       </c>
       <c r="Q77" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Çeşitli Hizmetler</t>
         </is>
       </c>
       <c r="R77" s="5" t="inlineStr"/>
@@ -4951,57 +4951,57 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GEDIK</t>
+          <t>SARKY</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>4.78</v>
+        <v>15.64</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>-0.0042</v>
+        <v>-0.055</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>-0.0225</v>
+        <v>-0.143</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>-0.0895</v>
+        <v>-0.2949</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>-0.2939</v>
+        <v>-0.4008</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>-0.1857</v>
+        <v>-0.4366</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>-0.3434</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>5.06</v>
+        <v>57.31</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0.6583</v>
+        <v>0.5590999999999999</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.3671</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>0.7293999999999999</v>
+        <v>0.2342</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>0.3481</v>
+        <v>0.8034</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>0.6628000000000001</v>
+        <v>0.0217</v>
       </c>
       <c r="P78" s="4" t="n">
-        <v>0.275</v>
+        <v>0.0229</v>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr"/>
@@ -5009,57 +5009,55 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>KCAER</t>
+          <t>KNFRT</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
-        <v>9.380000000000001</v>
+        <v>7.04</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>-0.0573</v>
+        <v>-0.0486</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>-0.1488</v>
+        <v>-0.2454</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-0.2051</v>
+        <v>-0.3185</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>-0.3531</v>
+        <v>-0.4147999999999999</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>-0.1836</v>
+        <v>-0.4478</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>-0.2591</v>
+        <v>-0.4785</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="J79" s="6" t="n">
-        <v>27.32</v>
-      </c>
+        <v>1.17</v>
+      </c>
+      <c r="J79" s="5" t="inlineStr"/>
       <c r="K79" s="7" t="n">
-        <v>0.1522</v>
+        <v>0.7798</v>
       </c>
       <c r="L79" s="7" t="n">
-        <v>0.2873</v>
+        <v>1.3764</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>0.3247</v>
+        <v>26.3063</v>
       </c>
       <c r="N79" s="7" t="n">
-        <v>1.1982</v>
+        <v>0.625</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>0.1199</v>
+        <v>0.0124</v>
       </c>
       <c r="P79" s="7" t="n">
-        <v>0.0508</v>
+        <v>-0.1091</v>
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R79" s="5" t="inlineStr"/>
@@ -5067,55 +5065,55 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>KNFRT</t>
+          <t>ACSEL</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>7.4</v>
+        <v>73.7</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>-0.08869999999999999</v>
+        <v>-0.0867</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>-0.2402</v>
+        <v>-0.1329</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>-0.3451</v>
+        <v>-0.2032</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>-0.3954</v>
+        <v>-0.4282</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>-0.4196</v>
+        <v>-0.3879</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>-0.4665</v>
+        <v>-0.336</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="4" t="n">
-        <v>0.7798</v>
+        <v>0.3957</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>1.3764</v>
+        <v>2.0344</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>26.3063</v>
+        <v>3.8494</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>0.625</v>
+        <v>0.889</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>0.0124</v>
+        <v>0.0349</v>
       </c>
       <c r="P80" s="4" t="n">
-        <v>-0.1091</v>
+        <v>-0.0175</v>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr"/>
@@ -5123,55 +5121,57 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>KCAER</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>5.89</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>-0.0248</v>
+        <v>-0.0288</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>-0.09939999999999999</v>
+        <v>-0.1478</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-0.161</v>
+        <v>-0.165</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>-0.2468</v>
+        <v>-0.3815</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>-0.2971</v>
+        <v>-0.2071</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>-0.2843</v>
+        <v>-0.277</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="J81" s="5" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="J81" s="6" t="n">
+        <v>26.53</v>
+      </c>
       <c r="K81" s="7" t="n">
-        <v>0.3952000000000001</v>
+        <v>0.1522</v>
       </c>
       <c r="L81" s="7" t="n">
-        <v>0.4088000000000001</v>
+        <v>0.2873</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>0.4094</v>
+        <v>0.3247</v>
       </c>
       <c r="N81" s="7" t="n">
-        <v>0.7489</v>
+        <v>1.1982</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>0.7836</v>
+        <v>0.1199</v>
       </c>
       <c r="P81" s="7" t="n">
-        <v>-0.0106</v>
+        <v>0.0508</v>
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>Çeşitli Hizmetler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R81" s="5" t="inlineStr"/>
@@ -5179,57 +5179,55 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>SARKY</t>
+          <t>DAGI</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>16.55</v>
+        <v>5.42</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>-0.0322</v>
+        <v>0</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>-0.1289</v>
+        <v>-0.08449999999999999</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>-0.2464</v>
+        <v>-0.0073</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>-0.3722</v>
+        <v>-0.4407</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>-0.4038</v>
+        <v>-0.17</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>0.1582</v>
+        <v>-0.3524</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>60.64</v>
-      </c>
+        <v>1.18</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="4" t="n">
-        <v>0.5590999999999999</v>
+        <v>0.5429999999999999</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>0.3671</v>
+        <v>1.1389</v>
       </c>
       <c r="M82" s="4" t="n">
-        <v>0.2342</v>
+        <v>1.8634</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>0.8034</v>
+        <v>0.5748</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>0.0217</v>
+        <v>0.1561</v>
       </c>
       <c r="P82" s="4" t="n">
-        <v>0.0229</v>
+        <v>-0.0597</v>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R82" s="2" t="inlineStr"/>
@@ -5237,57 +5235,57 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>GEDIK</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>69.05</v>
+        <v>4.7</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>-0.0254</v>
+        <v>-0.0167</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>-0.0541</v>
+        <v>-0.0309</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>0.0534</v>
+        <v>-0.1264</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>-0.4047</v>
+        <v>-0.2943</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>-0.1265</v>
+        <v>-0.1993</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>0.404</v>
+        <v>-0.3588</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>25.41</v>
+        <v>4.97</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.6583</v>
       </c>
       <c r="L83" s="7" t="n">
-        <v>0.3716</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>0.4119</v>
+        <v>0.7293999999999999</v>
       </c>
       <c r="N83" s="7" t="n">
-        <v>0.9691</v>
+        <v>0.3481</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>0.3037</v>
+        <v>0.6628000000000001</v>
       </c>
       <c r="P83" s="7" t="n">
-        <v>0.0601</v>
+        <v>0.275</v>
       </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R83" s="5" t="inlineStr"/>
@@ -5295,57 +5293,57 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GARFA</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>21.34</v>
+        <v>267</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>0.05019999999999999</v>
+        <v>-0.0697</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>-0.0473</v>
+        <v>-0.0102</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>-0.1332</v>
+        <v>-0.0335</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>-0.2496</v>
+        <v>0.0299</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>-0.2486</v>
+        <v>-0.1324</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>-0.1395</v>
+        <v>0.1314</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>3.23</v>
+        <v>18.39</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0.9562999999999999</v>
+        <v>0.3707</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.9506</v>
+        <v>0.4185</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.4202</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>0.5365</v>
+        <v>1.8941</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>0.914</v>
+        <v>0.3086</v>
       </c>
       <c r="P84" s="4" t="n">
-        <v>0.496</v>
+        <v>-0.1688</v>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr"/>
@@ -5353,57 +5351,57 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>287</v>
+        <v>66.2</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>0.0026</v>
+        <v>-0.0413</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.0806</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>0.0446</v>
+        <v>-0.0134</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>0.0503</v>
+        <v>-0.3635</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>-0.0674</v>
+        <v>-0.1626</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0.2381</v>
+        <v>0.3734</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>19.77</v>
+        <v>24.37</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>0.3707</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="L85" s="7" t="n">
-        <v>0.4185</v>
+        <v>0.3716</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>0.4202</v>
+        <v>0.4119</v>
       </c>
       <c r="N85" s="7" t="n">
-        <v>1.8941</v>
+        <v>0.9691</v>
       </c>
       <c r="O85" s="7" t="n">
-        <v>0.3086</v>
+        <v>0.3037</v>
       </c>
       <c r="P85" s="7" t="n">
-        <v>-0.1688</v>
+        <v>0.0601</v>
       </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R85" s="5" t="inlineStr"/>
@@ -5411,55 +5409,57 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>GARFA</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>80.7</v>
+        <v>20.62</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>-0.0159</v>
+        <v>-0.0337</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>-0.06709999999999999</v>
+        <v>-0.06269999999999999</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>-0.179</v>
+        <v>-0.1528</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>-0.3835</v>
+        <v>-0.2672</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>-0.3297</v>
+        <v>-0.2739</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>-0.2877</v>
+        <v>-0.1563</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr"/>
+        <v>1.21</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>3.12</v>
+      </c>
       <c r="K86" s="4" t="n">
-        <v>0.3957</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>2.0344</v>
+        <v>0.9506</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>3.8494</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>0.889</v>
+        <v>0.5365</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>0.0349</v>
+        <v>0.914</v>
       </c>
       <c r="P86" s="4" t="n">
-        <v>-0.0175</v>
+        <v>0.496</v>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr"/>
@@ -5467,57 +5467,55 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>PCILT</t>
+          <t>OZYSR</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>29</v>
+        <v>10.58</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>-0.0429</v>
+        <v>-0.08789999999999999</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>-0.0473</v>
+        <v>-0.09029999999999999</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>-0.0333</v>
+        <v>-0.0294</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>-0.1623</v>
+        <v>-0.1887</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.1079</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>0.5057</v>
+        <v>0.3347</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="J87" s="6" t="n">
-        <v>6.66</v>
-      </c>
+        <v>1.24</v>
+      </c>
+      <c r="J87" s="5" t="inlineStr"/>
       <c r="K87" s="7" t="n">
-        <v>0.763</v>
+        <v>0.161</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>0.7087</v>
+        <v>0.1742</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>0.7914</v>
+        <v>0.6839</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>1.2232</v>
+        <v>0.5105</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>0.0574</v>
+        <v>0.042</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>0.2831</v>
+        <v>-0.0335</v>
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R87" s="5" t="inlineStr"/>
@@ -5525,55 +5523,57 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>OZYSR</t>
+          <t>PCILT</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>11.6</v>
+        <v>28.04</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>-0.0034</v>
+        <v>-0.0331</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>-0.0178</v>
+        <v>-0.08070000000000001</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>0.0507</v>
+        <v>-0.0463</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>-0.1185</v>
+        <v>-0.1849</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>-0.0219</v>
+        <v>0.051</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>0.5127</v>
+        <v>0.4379</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr"/>
+        <v>1.27</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>6.44</v>
+      </c>
       <c r="K88" s="4" t="n">
-        <v>0.161</v>
+        <v>0.763</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>0.1742</v>
+        <v>0.7087</v>
       </c>
       <c r="M88" s="4" t="n">
-        <v>0.6839</v>
+        <v>0.7914</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>0.5105</v>
+        <v>1.2232</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>0.042</v>
+        <v>0.0574</v>
       </c>
       <c r="P88" s="4" t="n">
-        <v>-0.0335</v>
+        <v>0.2831</v>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R88" s="2" t="inlineStr"/>
@@ -5581,57 +5581,57 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>ALFAS</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>24.68</v>
+        <v>11.38</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>-0.026</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>-0.1236</v>
+        <v>-0.2518</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-0.2646</v>
+        <v>-0.1663</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>-0.4672</v>
+        <v>-0.7437</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>-0.3736</v>
+        <v>-0.6227</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>-0.4024</v>
+        <v>0.0252</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>29.57</v>
+        <v>1.47</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>0.05019999999999999</v>
+        <v>2.1748</v>
       </c>
       <c r="L89" s="7" t="n">
-        <v>0.4331</v>
+        <v>2.2285</v>
       </c>
       <c r="M89" s="7" t="n">
-        <v>0.8572</v>
+        <v>2.5519</v>
       </c>
       <c r="N89" s="7" t="n">
-        <v>40.5101</v>
+        <v>7.8348</v>
       </c>
       <c r="O89" s="7" t="n">
-        <v>0.08410000000000001</v>
+        <v>0.887</v>
       </c>
       <c r="P89" s="7" t="n">
-        <v>0.05400000000000001</v>
+        <v>1.1538</v>
       </c>
       <c r="Q89" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R89" s="5" t="inlineStr"/>
@@ -5639,57 +5639,57 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GENIL</t>
+          <t>ALFAS</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>4.17</v>
+        <v>23.82</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>-0.0118</v>
+        <v>-0.0348</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>-0.2042</v>
+        <v>-0.1204</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>-0.4633</v>
+        <v>-0.2847</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>-0.5502</v>
+        <v>-0.4945000000000001</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>-0.5679</v>
+        <v>-0.3954</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>-0.6798999999999999</v>
+        <v>-0.4274</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>15.2</v>
+        <v>28.54</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0.5049</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>0.7672</v>
+        <v>0.4331</v>
       </c>
       <c r="M90" s="4" t="n">
-        <v>1.1622</v>
+        <v>0.8572</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>1.2274</v>
+        <v>40.5101</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>0.0922</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="P90" s="4" t="n">
-        <v>0.1305</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R90" s="2" t="inlineStr"/>
@@ -5697,57 +5697,57 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>GENIL</t>
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>12.64</v>
+        <v>4.02</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.036</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>-0.297</v>
+        <v>-0.204</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-0.1662</v>
+        <v>-0.3927</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>-0.7</v>
+        <v>-0.5700999999999999</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>-0.5809000000000001</v>
+        <v>-0.5834</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>0.1146</v>
+        <v>-0.6846</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>1.63</v>
+        <v>14.66</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>2.1748</v>
+        <v>0.5049</v>
       </c>
       <c r="L91" s="7" t="n">
-        <v>2.2285</v>
+        <v>0.7672</v>
       </c>
       <c r="M91" s="7" t="n">
-        <v>2.5519</v>
+        <v>1.1622</v>
       </c>
       <c r="N91" s="7" t="n">
-        <v>7.8348</v>
+        <v>1.2274</v>
       </c>
       <c r="O91" s="7" t="n">
-        <v>0.887</v>
+        <v>0.0922</v>
       </c>
       <c r="P91" s="7" t="n">
-        <v>1.1538</v>
+        <v>0.1305</v>
       </c>
       <c r="Q91" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R91" s="5" t="inlineStr"/>
@@ -5759,31 +5759,31 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>28.02</v>
+        <v>27.3</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>-0.0391</v>
+        <v>-0.0257</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>-0.1155</v>
+        <v>-0.13</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>-0.1468</v>
+        <v>-0.1942</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>-0.2386</v>
+        <v>-0.2222</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>-0.3529</v>
+        <v>-0.3695000000000001</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>0.0785</v>
+        <v>0.0428</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>9.98</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K92" s="4" t="n">
         <v>0.3776</v>
@@ -5813,55 +5813,57 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>KRPLS</t>
+          <t>ORGE</t>
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>9.01</v>
+        <v>18.8</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>-0.0405</v>
+        <v>-0.0605</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>-0.189</v>
+        <v>-0.1686</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>-0.1603</v>
+        <v>-0.1582</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>-0.0238</v>
+        <v>-0.1325</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>-0.0044</v>
+        <v>0.1319</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>0</v>
+        <v>0.3981</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="J93" s="5" t="inlineStr"/>
+        <v>1.44</v>
+      </c>
+      <c r="J93" s="6" t="n">
+        <v>8.720000000000001</v>
+      </c>
       <c r="K93" s="7" t="n">
-        <v>0.3576</v>
+        <v>0.251</v>
       </c>
       <c r="L93" s="7" t="n">
-        <v>0.6872</v>
+        <v>0.257</v>
       </c>
       <c r="M93" s="7" t="n">
-        <v>0.9115000000000001</v>
+        <v>0.2421</v>
       </c>
       <c r="N93" s="7" t="n">
-        <v>0.7781999999999999</v>
+        <v>0.2676</v>
       </c>
       <c r="O93" s="7" t="n">
-        <v>0.166</v>
+        <v>0.4943</v>
       </c>
       <c r="P93" s="7" t="n">
-        <v>-0.0342</v>
+        <v>0.2029</v>
       </c>
       <c r="Q93" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R93" s="5" t="inlineStr"/>
@@ -5873,31 +5875,31 @@
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>-0.0654</v>
+        <v>-0.0333</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>-0.09910000000000001</v>
+        <v>-0.1471</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>-0.1429</v>
+        <v>-0.1808</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>-0.5941</v>
+        <v>-0.637</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>-0.6308</v>
+        <v>-0.6431</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>-0.0757</v>
+        <v>-0.1845</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>6.41</v>
+        <v>6.19</v>
       </c>
       <c r="K94" s="4" t="n">
         <v>0.51</v>
@@ -5927,57 +5929,57 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>TUPRS</t>
+          <t>DERIM</t>
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>359.25</v>
+        <v>19.62</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>-0.0076</v>
+        <v>-0.0675</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.1665</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>-0.1369</v>
+        <v>-0.3381</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>0.1441</v>
+        <v>-0.4529</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>0.3506</v>
+        <v>-0.5203</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>1.0239</v>
+        <v>-0.4668</v>
       </c>
       <c r="I95" s="6" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>9.970000000000001</v>
+        <v>10.81</v>
       </c>
       <c r="K95" s="7" t="n">
-        <v>0.465</v>
+        <v>0.1436</v>
       </c>
       <c r="L95" s="7" t="n">
-        <v>1.0453</v>
+        <v>0.2539</v>
       </c>
       <c r="M95" s="7" t="n">
-        <v>1.1002</v>
+        <v>0.0263</v>
       </c>
       <c r="N95" s="7" t="n">
-        <v>2.2351</v>
+        <v>0.0576</v>
       </c>
       <c r="O95" s="7" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0602</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>0.187</v>
+        <v>0.1637</v>
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R95" s="5" t="inlineStr"/>
@@ -5985,57 +5987,55 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>ORGE</t>
+          <t>KRPLS</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>20</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>-0.0385</v>
+        <v>-0.005500000000000001</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>-0.1304</v>
+        <v>-0.178</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>-0.08839999999999999</v>
+        <v>-0.2283</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.0519</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>0.2048</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>0.5014999999999999</v>
+        <v>-0.0261</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="J96" s="3" t="n">
-        <v>9.279999999999999</v>
-      </c>
+        <v>1.48</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="4" t="n">
-        <v>0.251</v>
+        <v>0.3576</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>0.257</v>
+        <v>0.6872</v>
       </c>
       <c r="M96" s="4" t="n">
-        <v>0.2421</v>
+        <v>0.9115000000000001</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>0.2676</v>
+        <v>0.7781999999999999</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>0.4943</v>
+        <v>0.166</v>
       </c>
       <c r="P96" s="4" t="n">
-        <v>0.2029</v>
+        <v>-0.0342</v>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R96" s="2" t="inlineStr"/>
@@ -6043,57 +6043,57 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>DERIM</t>
+          <t>TUPRS</t>
         </is>
       </c>
       <c r="B97" s="6" t="n">
-        <v>21.04</v>
+        <v>352.25</v>
       </c>
       <c r="C97" s="7" t="n">
-        <v>-0.0357</v>
+        <v>-0.0195</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>-0.1781</v>
+        <v>-0.09210000000000002</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>-0.2868</v>
+        <v>-0.1507</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>-0.4106</v>
+        <v>0.1254</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>-0.4856</v>
+        <v>0.3242</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>-0.4236</v>
+        <v>0.9845</v>
       </c>
       <c r="I97" s="6" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="J97" s="6" t="n">
-        <v>11.59</v>
+        <v>9.77</v>
       </c>
       <c r="K97" s="7" t="n">
-        <v>0.1436</v>
+        <v>0.465</v>
       </c>
       <c r="L97" s="7" t="n">
-        <v>0.2539</v>
+        <v>1.0453</v>
       </c>
       <c r="M97" s="7" t="n">
-        <v>0.0263</v>
+        <v>1.1002</v>
       </c>
       <c r="N97" s="7" t="n">
-        <v>0.0576</v>
+        <v>2.2351</v>
       </c>
       <c r="O97" s="7" t="n">
-        <v>0.0602</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="P97" s="7" t="n">
-        <v>0.1637</v>
+        <v>0.187</v>
       </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="R97" s="5" t="inlineStr"/>
@@ -6105,31 +6105,31 @@
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>3.63</v>
+        <v>3.52</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>-0.0163</v>
+        <v>-0.0303</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>-0.1378</v>
+        <v>-0.1373</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>-0.1059</v>
+        <v>-0.1373</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>-0.34</v>
+        <v>-0.3408</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>-0.2681</v>
+        <v>-0.2903</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>0.21</v>
+        <v>0.1617</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>11.79</v>
+        <v>11.44</v>
       </c>
       <c r="K98" s="4" t="n">
         <v>1.0251</v>
@@ -6159,57 +6159,57 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>SAFKR</t>
+          <t>ENERY</t>
         </is>
       </c>
       <c r="B99" s="6" t="n">
-        <v>11.28</v>
+        <v>12.12</v>
       </c>
       <c r="C99" s="7" t="n">
-        <v>-0.0473</v>
+        <v>-0.0524</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>-0.0521</v>
+        <v>-0.1386</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>-0.0359</v>
+        <v>0.01</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>-0.414</v>
+        <v>0.2704</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>-0.5517</v>
+        <v>0.3275</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>-0.4471</v>
+        <v>0.3089</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>16.4</v>
+        <v>19.33</v>
       </c>
       <c r="K99" s="7" t="n">
-        <v>0.7861</v>
+        <v>0.4279</v>
       </c>
       <c r="L99" s="7" t="n">
-        <v>0.4555</v>
+        <v>0.7162999999999999</v>
       </c>
       <c r="M99" s="7" t="n">
-        <v>0.3309</v>
+        <v>0.8373999999999999</v>
       </c>
       <c r="N99" s="7" t="n">
-        <v>0.5716</v>
+        <v>0.6103000000000001</v>
       </c>
       <c r="O99" s="7" t="n">
-        <v>0.2109</v>
+        <v>0.2099</v>
       </c>
       <c r="P99" s="7" t="n">
-        <v>0.1216</v>
+        <v>0.1017</v>
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R99" s="5" t="inlineStr"/>
@@ -6217,53 +6217,53 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>SANEL</t>
+          <t>SAYAS</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>23.8</v>
+        <v>32.82</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>-0.0718</v>
+        <v>-0.0481</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>-0.1793</v>
+        <v>-0.1363</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>-0.4121</v>
+        <v>-0.2739</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>-0.6955</v>
+        <v>-0.3343</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>-0.3227</v>
+        <v>-0.249</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>-0.1185</v>
+        <v>-0.3772</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>2.29</v>
+        <v>13.08</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0.309</v>
+        <v>0.486</v>
       </c>
       <c r="L100" s="4" t="n">
-        <v>1.4614</v>
+        <v>1.4655</v>
       </c>
       <c r="M100" s="4" t="n">
-        <v>1.5381</v>
+        <v>2.3632</v>
       </c>
       <c r="N100" s="4" t="n">
-        <v>2.2148</v>
+        <v>6.118200000000001</v>
       </c>
       <c r="O100" s="4" t="n">
-        <v>0.1491</v>
+        <v>0.1798</v>
       </c>
       <c r="P100" s="4" t="n">
-        <v>1.0947</v>
+        <v>0.1493</v>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
@@ -6275,57 +6275,57 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>ENERY</t>
+          <t>SANEL</t>
         </is>
       </c>
       <c r="B101" s="6" t="n">
-        <v>12.79</v>
+        <v>23.42</v>
       </c>
       <c r="C101" s="7" t="n">
-        <v>-0.09029999999999999</v>
+        <v>-0.016</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>-0.1191</v>
+        <v>-0.1857</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>-0.0039</v>
+        <v>-0.3674</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>0.3534</v>
+        <v>-0.7034999999999999</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>0.4009</v>
+        <v>-0.3335</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>0.3577</v>
+        <v>-0.1182</v>
       </c>
       <c r="I101" s="6" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>20.4</v>
+        <v>2.26</v>
       </c>
       <c r="K101" s="7" t="n">
-        <v>0.4279</v>
+        <v>0.309</v>
       </c>
       <c r="L101" s="7" t="n">
-        <v>0.7162999999999999</v>
+        <v>1.4614</v>
       </c>
       <c r="M101" s="7" t="n">
-        <v>0.8373999999999999</v>
+        <v>1.5381</v>
       </c>
       <c r="N101" s="7" t="n">
-        <v>0.6103000000000001</v>
+        <v>2.2148</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>0.2099</v>
+        <v>0.1491</v>
       </c>
       <c r="P101" s="7" t="n">
-        <v>0.1017</v>
+        <v>1.0947</v>
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R101" s="5" t="inlineStr"/>
@@ -6333,53 +6333,53 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SAYAS</t>
+          <t>SAFKR</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>34.48</v>
+        <v>11.4</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>-0.0249</v>
+        <v>0.0106</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>-0.1177</v>
+        <v>-0.0492</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>-0.2495</v>
+        <v>0.044</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>-0.2888</v>
+        <v>-0.4105</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>-0.211</v>
+        <v>-0.5468999999999999</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>-0.3513</v>
+        <v>-0.4406</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>13.74</v>
+        <v>16.58</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0.486</v>
+        <v>0.7861</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>1.4655</v>
+        <v>0.4555</v>
       </c>
       <c r="M102" s="4" t="n">
-        <v>2.3632</v>
+        <v>0.3309</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>6.118200000000001</v>
+        <v>0.5716</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>0.1798</v>
+        <v>0.2109</v>
       </c>
       <c r="P102" s="4" t="n">
-        <v>0.1493</v>
+        <v>0.1216</v>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
@@ -6395,31 +6395,31 @@
         </is>
       </c>
       <c r="B103" s="6" t="n">
-        <v>227.9</v>
+        <v>223.7</v>
       </c>
       <c r="C103" s="7" t="n">
-        <v>-0.0412</v>
+        <v>-0.0184</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>-0.126</v>
+        <v>-0.1016</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>-0.1918</v>
+        <v>-0.2233</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>-0.2327</v>
+        <v>-0.2192</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>-0.2228</v>
+        <v>-0.2372</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>-0.1132</v>
+        <v>-0.1236</v>
       </c>
       <c r="I103" s="6" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>8.960000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K103" s="7" t="n">
         <v>1.7224</v>
@@ -6453,31 +6453,31 @@
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>402.25</v>
+        <v>394.75</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>-0.0342</v>
+        <v>-0.0186</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>-0.064</v>
+        <v>-0.0755</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>-0.0694</v>
+        <v>-0.1013</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>-0.0171</v>
+        <v>-0.04190000000000001</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>-0.1312</v>
+        <v>-0.1474</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>0.2226</v>
+        <v>0.2109</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>12.56</v>
+        <v>12.33</v>
       </c>
       <c r="K104" s="4" t="n">
         <v>0.3601</v>
@@ -6511,28 +6511,28 @@
         </is>
       </c>
       <c r="B105" s="6" t="n">
-        <v>5.99</v>
+        <v>5.9</v>
       </c>
       <c r="C105" s="7" t="n">
-        <v>-0.0132</v>
+        <v>-0.015</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>-0.0611</v>
+        <v>-0.1667</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>0.2718</v>
+        <v>0.4532</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>0.1815</v>
+        <v>0.1069</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>0.2827</v>
+        <v>0.2634</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>0.7212999999999999</v>
+        <v>0.7101000000000001</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="J105" s="5" t="inlineStr"/>
       <c r="K105" s="7" t="n">
@@ -6567,31 +6567,31 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>44.2</v>
+        <v>42.72</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>-0.0718</v>
+        <v>-0.0335</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>-0.073</v>
+        <v>-0.09449999999999999</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>0.0625</v>
+        <v>0.0269</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>0.2271</v>
+        <v>0.1711</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>0.6073</v>
+        <v>0.5535</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>0.7707999999999999</v>
+        <v>0.7240000000000001</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>20.92</v>
+        <v>20.22</v>
       </c>
       <c r="K106" s="4" t="n">
         <v>0.659</v>
@@ -6621,57 +6621,57 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>GLYHO</t>
         </is>
       </c>
       <c r="B107" s="6" t="n">
-        <v>196</v>
+        <v>15.97</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>-0.04389999999999999</v>
+        <v>-0.0437</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>-0.1067</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>-0.1366</v>
+        <v>0.0237</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>-0.1765</v>
+        <v>-0.0895</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>-0.2447</v>
+        <v>0.0108</v>
       </c>
       <c r="H107" s="7" t="n">
-        <v>-0.1638</v>
+        <v>0.5341</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="J107" s="6" t="n">
-        <v>18.32</v>
+        <v>5.33</v>
       </c>
       <c r="K107" s="7" t="n">
-        <v>0.493</v>
+        <v>0.2312</v>
       </c>
       <c r="L107" s="7" t="n">
-        <v>0.3835</v>
+        <v>0.317</v>
       </c>
       <c r="M107" s="7" t="n">
-        <v>0.4282</v>
+        <v>0.3503</v>
       </c>
       <c r="N107" s="7" t="n">
-        <v>0.1825</v>
+        <v>0.4888</v>
       </c>
       <c r="O107" s="7" t="n">
-        <v>0.2029</v>
+        <v>0.3457</v>
       </c>
       <c r="P107" s="7" t="n">
-        <v>0.1296</v>
+        <v>-0.2226</v>
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R107" s="5" t="inlineStr"/>
@@ -6679,53 +6679,53 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GRSEL</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>262.5</v>
+        <v>191.3</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>-0.0223</v>
+        <v>-0.024</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>-0.0917</v>
+        <v>-0.08470000000000001</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.1591</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>-0.1797</v>
+        <v>-0.179</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>-0.1315</v>
+        <v>-0.2628</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>-0.2558</v>
+        <v>-0.2131</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>7.97</v>
+        <v>17.88</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0.3337</v>
+        <v>0.493</v>
       </c>
       <c r="L108" s="4" t="n">
-        <v>0.6940999999999999</v>
+        <v>0.3835</v>
       </c>
       <c r="M108" s="4" t="n">
-        <v>0.2722</v>
+        <v>0.4282</v>
       </c>
       <c r="N108" s="4" t="n">
-        <v>0.7318000000000001</v>
+        <v>0.1825</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>0.3275</v>
+        <v>0.2029</v>
       </c>
       <c r="P108" s="4" t="n">
-        <v>0.3613</v>
+        <v>0.1296</v>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
@@ -6737,57 +6737,57 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>GLYHO</t>
+          <t>GRSEL</t>
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>16.7</v>
+        <v>256</v>
       </c>
       <c r="C109" s="7" t="n">
-        <v>-0.0441</v>
+        <v>-0.0248</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>-0.0533</v>
+        <v>-0.1018</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>0.08939999999999999</v>
+        <v>-0.0623</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>-0.0441</v>
+        <v>-0.195</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>0.057</v>
+        <v>-0.153</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>0.6535</v>
+        <v>-0.2364</v>
       </c>
       <c r="I109" s="6" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="J109" s="6" t="n">
-        <v>5.58</v>
+        <v>7.78</v>
       </c>
       <c r="K109" s="7" t="n">
-        <v>0.2312</v>
+        <v>0.3337</v>
       </c>
       <c r="L109" s="7" t="n">
-        <v>0.317</v>
+        <v>0.6940999999999999</v>
       </c>
       <c r="M109" s="7" t="n">
-        <v>0.3503</v>
+        <v>0.2722</v>
       </c>
       <c r="N109" s="7" t="n">
-        <v>0.4888</v>
+        <v>0.7318000000000001</v>
       </c>
       <c r="O109" s="7" t="n">
-        <v>0.3457</v>
+        <v>0.3275</v>
       </c>
       <c r="P109" s="7" t="n">
-        <v>-0.2226</v>
+        <v>0.3613</v>
       </c>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R109" s="5" t="inlineStr"/>
@@ -6799,31 +6799,31 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>39.06</v>
+        <v>37.62</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>-0.09960000000000001</v>
+        <v>-0.0369</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>-0.1846</v>
+        <v>-0.1804</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>-0.3685</v>
+        <v>-0.3807</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>-0.6121</v>
+        <v>-0.6181</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>-0.045</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>0.492</v>
+        <v>0.4381</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>27.69</v>
+        <v>26.67</v>
       </c>
       <c r="K110" s="4" t="n">
         <v>0.8139</v>
@@ -6857,31 +6857,31 @@
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>19.75</v>
+        <v>19.2</v>
       </c>
       <c r="C111" s="7" t="n">
-        <v>0.0025</v>
+        <v>-0.0278</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>-0.1338</v>
+        <v>-0.1652</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>-0.3021</v>
+        <v>-0.3074</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>-0.3813</v>
+        <v>-0.4213</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>-0.0745</v>
+        <v>-0.1003</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>0.1003</v>
+        <v>0.0738</v>
       </c>
       <c r="I111" s="6" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="J111" s="6" t="n">
-        <v>12.93</v>
+        <v>12.57</v>
       </c>
       <c r="K111" s="7" t="n">
         <v>0.5342</v>
@@ -6911,57 +6911,57 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>BIMAS</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>385.5</v>
+        <v>36.48</v>
       </c>
       <c r="C112" s="4" t="n">
-        <v>0</v>
+        <v>-0.09390000000000001</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.1497</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>-0.08380000000000001</v>
+        <v>-0.2985</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>-0.0338</v>
+        <v>-0.2826</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>0.0131</v>
+        <v>-0.2107</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>0.4318</v>
+        <v>0.4926</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>16.86</v>
+        <v>23.3</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0.4214</v>
+        <v>1.2681</v>
       </c>
       <c r="L112" s="4" t="n">
-        <v>0.5271</v>
+        <v>2.3445</v>
       </c>
       <c r="M112" s="4" t="n">
-        <v>0.8381000000000001</v>
+        <v>3.7256</v>
       </c>
       <c r="N112" s="4" t="n">
-        <v>0.8737999999999999</v>
+        <v>1.0029</v>
       </c>
       <c r="O112" s="4" t="n">
-        <v>0.0611</v>
+        <v>0.2964</v>
       </c>
       <c r="P112" s="4" t="n">
-        <v>0.1613</v>
+        <v>0.1126</v>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr"/>
@@ -6969,57 +6969,57 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>BIMAS</t>
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>76.7</v>
+        <v>369</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>0</v>
+        <v>-0.0428</v>
       </c>
       <c r="D113" s="7" t="n">
-        <v>-0.08310000000000001</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>-0.05309999999999999</v>
+        <v>-0.1473</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>-0.1699</v>
+        <v>-0.0538</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>-0.0412</v>
+        <v>-0.0302</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>0.5233</v>
+        <v>0.4004</v>
       </c>
       <c r="I113" s="6" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="J113" s="6" t="n">
-        <v>10.36</v>
+        <v>16.14</v>
       </c>
       <c r="K113" s="7" t="n">
-        <v>0.4257</v>
+        <v>0.4214</v>
       </c>
       <c r="L113" s="7" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5271</v>
       </c>
       <c r="M113" s="7" t="n">
-        <v>0.7781</v>
+        <v>0.8381000000000001</v>
       </c>
       <c r="N113" s="7" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.8737999999999999</v>
       </c>
       <c r="O113" s="7" t="n">
-        <v>0.177</v>
+        <v>0.0611</v>
       </c>
       <c r="P113" s="7" t="n">
-        <v>0.5497</v>
+        <v>0.1613</v>
       </c>
       <c r="Q113" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R113" s="5" t="inlineStr"/>
@@ -7027,57 +7027,57 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>40.26</v>
+        <v>74.2</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>-0.035</v>
+        <v>-0.0326</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.08449999999999999</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>-0.1964</v>
+        <v>-0.0737</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>-0.1964</v>
+        <v>-0.186</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>-0.1289</v>
+        <v>-0.0725</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>0.6078</v>
+        <v>0.465</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>25.71</v>
+        <v>10.02</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>1.2681</v>
+        <v>0.4257</v>
       </c>
       <c r="L114" s="4" t="n">
-        <v>2.3445</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="M114" s="4" t="n">
-        <v>3.7256</v>
+        <v>0.7781</v>
       </c>
       <c r="N114" s="4" t="n">
-        <v>1.0029</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="O114" s="4" t="n">
-        <v>0.2964</v>
+        <v>0.177</v>
       </c>
       <c r="P114" s="4" t="n">
-        <v>0.1126</v>
+        <v>0.5497</v>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr"/>
@@ -7089,31 +7089,31 @@
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>104.5</v>
+        <v>100</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>-0.0261</v>
+        <v>-0.0431</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>-0.1511</v>
+        <v>-0.1379</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-0.09759999999999999</v>
+        <v>-0.1135</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>-0.2718</v>
+        <v>-0.2811</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>0.0029</v>
+        <v>-0.0403</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>1.3536</v>
+        <v>1.2978</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="J115" s="6" t="n">
-        <v>9.369999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="K115" s="7" t="n">
         <v>2.4396</v>
@@ -7147,31 +7147,31 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>118.5</v>
+        <v>116.3</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>-0.0535</v>
+        <v>-0.0186</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>-0.13</v>
+        <v>-0.1183</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>-0.1742</v>
+        <v>-0.1621</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>-0.1331</v>
+        <v>-0.1353</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>-0.156</v>
+        <v>-0.1717</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>-0.195</v>
+        <v>-0.2061</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>12.89</v>
+        <v>12.65</v>
       </c>
       <c r="K116" s="4" t="n">
         <v>0.5617</v>
@@ -7205,31 +7205,31 @@
         </is>
       </c>
       <c r="B117" s="6" t="n">
-        <v>30.08</v>
+        <v>29.08</v>
       </c>
       <c r="C117" s="7" t="n">
-        <v>-0.024</v>
+        <v>-0.0332</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>-0.08289999999999999</v>
+        <v>-0.1129</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>-0.0176</v>
+        <v>-0.0447</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>-0.2051</v>
+        <v>-0.2153</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>-0.2865</v>
+        <v>-0.3102</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>-0.3603</v>
+        <v>-0.3678</v>
       </c>
       <c r="I117" s="6" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>21.95</v>
+        <v>21.22</v>
       </c>
       <c r="K117" s="7" t="n">
         <v>0.3957</v>
@@ -7259,57 +7259,57 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>ARDYZ</t>
+          <t>PKART</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>59.55</v>
+        <v>68.75</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>-0.005</v>
+        <v>-0.07719999999999999</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>-0.0688</v>
+        <v>-0.2271</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>-0.0278</v>
+        <v>-0.2353</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>-0.1613</v>
+        <v>-0.4907</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>0.3734</v>
+        <v>-0.3744</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>1.3538</v>
+        <v>-0.1406</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>2.79</v>
+        <v>2.59</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>14.83</v>
+        <v>15.2</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>2.0657</v>
+        <v>0.5093</v>
       </c>
       <c r="L118" s="4" t="n">
-        <v>2.0433</v>
+        <v>1.5572</v>
       </c>
       <c r="M118" s="4" t="n">
-        <v>2.0361</v>
+        <v>1.6598</v>
       </c>
       <c r="N118" s="4" t="n">
-        <v>1.7568</v>
+        <v>4.8022</v>
       </c>
       <c r="O118" s="4" t="n">
-        <v>0.4642</v>
+        <v>0.083</v>
       </c>
       <c r="P118" s="4" t="n">
-        <v>3.4222</v>
+        <v>0.2041</v>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr"/>
@@ -7317,57 +7317,57 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>PKART</t>
+          <t>ARDYZ</t>
         </is>
       </c>
       <c r="B119" s="6" t="n">
-        <v>74.5</v>
+        <v>56.85</v>
       </c>
       <c r="C119" s="7" t="n">
-        <v>-0.0688</v>
+        <v>-0.0453</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>-0.1911</v>
+        <v>-0.0897</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>-0.1994</v>
+        <v>-0.08310000000000001</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>-0.4609</v>
+        <v>-0.2055</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>-0.3221</v>
+        <v>0.3111</v>
       </c>
       <c r="H119" s="7" t="n">
-        <v>-0.0318</v>
+        <v>1.285</v>
       </c>
       <c r="I119" s="6" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>16.47</v>
+        <v>14.16</v>
       </c>
       <c r="K119" s="7" t="n">
-        <v>0.5093</v>
+        <v>2.0657</v>
       </c>
       <c r="L119" s="7" t="n">
-        <v>1.5572</v>
+        <v>2.0433</v>
       </c>
       <c r="M119" s="7" t="n">
-        <v>1.6598</v>
+        <v>2.0361</v>
       </c>
       <c r="N119" s="7" t="n">
-        <v>4.8022</v>
+        <v>1.7568</v>
       </c>
       <c r="O119" s="7" t="n">
-        <v>0.083</v>
+        <v>0.4642</v>
       </c>
       <c r="P119" s="7" t="n">
-        <v>0.2041</v>
+        <v>3.4222</v>
       </c>
       <c r="Q119" s="5" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R119" s="5" t="inlineStr"/>
@@ -7375,57 +7375,55 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>OYAYO</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>354.5</v>
+        <v>24.02</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>-0.05019999999999999</v>
+        <v>-0.0762</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>-0.1149</v>
+        <v>-0.2447</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>-0.1897</v>
+        <v>-0.3234</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>-0.1761</v>
+        <v>-0.4812</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>-0.315</v>
+        <v>-0.5576</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>0.2582</v>
+        <v>-0.3272</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="J120" s="3" t="n">
-        <v>15.37</v>
-      </c>
+        <v>2.76</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="4" t="n">
-        <v>0.1897</v>
+        <v>0.3933</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>0.4879</v>
+        <v>0.4082</v>
       </c>
       <c r="M120" s="4" t="n">
-        <v>0.6424</v>
+        <v>0.6868000000000001</v>
       </c>
       <c r="N120" s="4" t="n">
-        <v>0.5356000000000001</v>
+        <v>0.2959</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>0.2097</v>
+        <v>0.7368000000000001</v>
       </c>
       <c r="P120" s="4" t="n">
-        <v>0.2503</v>
+        <v>-0.0453</v>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr"/>
@@ -7433,55 +7431,57 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>OYAYO</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="B121" s="6" t="n">
-        <v>26</v>
+        <v>331.5</v>
       </c>
       <c r="C121" s="7" t="n">
-        <v>-0.08839999999999999</v>
+        <v>-0.0649</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>-0.1667</v>
+        <v>-0.1608</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-0.3197</v>
+        <v>-0.247</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>-0.4468</v>
+        <v>-0.2163</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>-0.5212</v>
+        <v>-0.3594</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>-0.2622</v>
+        <v>0.185</v>
       </c>
       <c r="I121" s="6" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="J121" s="5" t="inlineStr"/>
+        <v>2.79</v>
+      </c>
+      <c r="J121" s="6" t="n">
+        <v>14.37</v>
+      </c>
       <c r="K121" s="7" t="n">
-        <v>0.3933</v>
+        <v>0.1897</v>
       </c>
       <c r="L121" s="7" t="n">
-        <v>0.4082</v>
+        <v>0.4879</v>
       </c>
       <c r="M121" s="7" t="n">
-        <v>0.6868000000000001</v>
+        <v>0.6424</v>
       </c>
       <c r="N121" s="7" t="n">
-        <v>0.2959</v>
+        <v>0.5356000000000001</v>
       </c>
       <c r="O121" s="7" t="n">
-        <v>0.7368000000000001</v>
+        <v>0.2097</v>
       </c>
       <c r="P121" s="7" t="n">
-        <v>-0.0453</v>
+        <v>0.2503</v>
       </c>
       <c r="Q121" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R121" s="5" t="inlineStr"/>
@@ -7489,57 +7489,57 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>KRONT</t>
+          <t>ATATP</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>16.94</v>
+        <v>205.5</v>
       </c>
       <c r="C122" s="4" t="n">
-        <v>-0.0035</v>
+        <v>-0.0595</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>-0.09849999999999999</v>
+        <v>-0.0693</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>-0.1177</v>
+        <v>-0.1508</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>-0.2404</v>
+        <v>-0.2119</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>-0.2698</v>
+        <v>0.4533</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>0.1563</v>
+        <v>0.5844</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>22.31</v>
+        <v>4.23</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0.6388</v>
+        <v>0.3072</v>
       </c>
       <c r="L122" s="4" t="n">
-        <v>0.5896</v>
+        <v>0.2985</v>
       </c>
       <c r="M122" s="4" t="n">
-        <v>1.5604</v>
+        <v>0.3487</v>
       </c>
       <c r="N122" s="4" t="n">
-        <v>5.569299999999999</v>
+        <v>0.6609999999999999</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>0.3874</v>
+        <v>0.3268</v>
       </c>
       <c r="P122" s="4" t="n">
-        <v>13.8834</v>
+        <v>0.7543000000000001</v>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr"/>
@@ -7547,57 +7547,57 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>ATATP</t>
+          <t>KRONT</t>
         </is>
       </c>
       <c r="B123" s="6" t="n">
-        <v>218.5</v>
+        <v>16.46</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>0.04650000000000001</v>
+        <v>-0.0283</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>-0.0433</v>
+        <v>-0.09609999999999999</v>
       </c>
       <c r="E123" s="7" t="n">
-        <v>-0.1052</v>
+        <v>-0.1305</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>-0.1564</v>
+        <v>-0.3276</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>0.5453</v>
+        <v>-0.2905</v>
       </c>
       <c r="H123" s="7" t="n">
-        <v>0.7232</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="I123" s="6" t="n">
-        <v>3.19</v>
+        <v>3.07</v>
       </c>
       <c r="J123" s="6" t="n">
-        <v>4.49</v>
+        <v>21.68</v>
       </c>
       <c r="K123" s="7" t="n">
-        <v>0.3072</v>
+        <v>0.6388</v>
       </c>
       <c r="L123" s="7" t="n">
-        <v>0.2985</v>
+        <v>0.5896</v>
       </c>
       <c r="M123" s="7" t="n">
-        <v>0.3487</v>
+        <v>1.5604</v>
       </c>
       <c r="N123" s="7" t="n">
-        <v>0.6609999999999999</v>
+        <v>5.569299999999999</v>
       </c>
       <c r="O123" s="7" t="n">
-        <v>0.3268</v>
+        <v>0.3874</v>
       </c>
       <c r="P123" s="7" t="n">
-        <v>0.7543000000000001</v>
+        <v>13.8834</v>
       </c>
       <c r="Q123" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R123" s="5" t="inlineStr"/>
@@ -7609,31 +7609,31 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>117.9</v>
+        <v>110.1</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>-0.0796</v>
+        <v>-0.1722</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>-0.1784</v>
+        <v>-0.266</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>-0.4238</v>
+        <v>-0.4587</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>-0.1875</v>
+        <v>-0.2412</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>2.1524</v>
+        <v>1.9854</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>13.13</v>
+        <v>12.26</v>
       </c>
       <c r="K124" s="4" t="n">
         <v>1.164</v>
@@ -7663,57 +7663,57 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>YEOTK</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B125" s="6" t="n">
-        <v>23.66</v>
+        <v>150</v>
       </c>
       <c r="C125" s="7" t="n">
-        <v>-0.0521</v>
+        <v>-0.0421</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>-0.1218</v>
+        <v>-0.2097</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-0.2268</v>
+        <v>-0.4307</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>-0.43</v>
+        <v>-0.5122</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>0.06480000000000001</v>
+        <v>-0.2823</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>0.6631999999999999</v>
+        <v>0.5609000000000001</v>
       </c>
       <c r="I125" s="6" t="n">
-        <v>3.57</v>
+        <v>3.42</v>
       </c>
       <c r="J125" s="6" t="n">
-        <v>8.82</v>
+        <v>14.72</v>
       </c>
       <c r="K125" s="7" t="n">
-        <v>1.4662</v>
+        <v>0.4338</v>
       </c>
       <c r="L125" s="7" t="n">
-        <v>1.5472</v>
+        <v>0.5232</v>
       </c>
       <c r="M125" s="7" t="n">
-        <v>1.7095</v>
+        <v>0.7125</v>
       </c>
       <c r="N125" s="7" t="n">
-        <v>3.7317</v>
+        <v>0.8672</v>
       </c>
       <c r="O125" s="7" t="n">
-        <v>0.1898</v>
+        <v>0.3018</v>
       </c>
       <c r="P125" s="7" t="n">
-        <v>0.7681999999999999</v>
+        <v>0.3122</v>
       </c>
       <c r="Q125" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R125" s="5" t="inlineStr"/>
@@ -7721,57 +7721,57 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>YEOTK</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>156.6</v>
+        <v>23.7</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>-0.0561</v>
+        <v>0.0017</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>-0.1977</v>
+        <v>-0.09539999999999998</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>-0.3786</v>
+        <v>-0.1922</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>-0.478</v>
+        <v>-0.4552</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>-0.2507</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>0.6045</v>
+        <v>0.6729999999999999</v>
       </c>
       <c r="I126" s="3" t="n">
         <v>3.57</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>15.36</v>
+        <v>8.83</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0.4338</v>
+        <v>1.4662</v>
       </c>
       <c r="L126" s="4" t="n">
-        <v>0.5232</v>
+        <v>1.5472</v>
       </c>
       <c r="M126" s="4" t="n">
-        <v>0.7125</v>
+        <v>1.7095</v>
       </c>
       <c r="N126" s="4" t="n">
-        <v>0.8672</v>
+        <v>3.7317</v>
       </c>
       <c r="O126" s="4" t="n">
-        <v>0.3018</v>
+        <v>0.1898</v>
       </c>
       <c r="P126" s="4" t="n">
-        <v>0.3122</v>
+        <v>0.7681999999999999</v>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr"/>
@@ -7779,57 +7779,57 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>ONCSM</t>
+          <t>FMIZP</t>
         </is>
       </c>
       <c r="B127" s="6" t="n">
-        <v>85</v>
+        <v>200.8</v>
       </c>
       <c r="C127" s="7" t="n">
-        <v>-0.0592</v>
+        <v>-0.0452</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>-0.0561</v>
+        <v>-0.1801</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>-0.1835</v>
+        <v>-0.2269</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>-0.6875</v>
+        <v>-0.2985</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>-0.7015</v>
+        <v>-0.3034</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>-0.5025999999999999</v>
+        <v>-0.3502</v>
       </c>
       <c r="I127" s="6" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="J127" s="6" t="n">
-        <v>28.07</v>
+        <v>20.31</v>
       </c>
       <c r="K127" s="7" t="n">
-        <v>0.5028</v>
+        <v>0.2837</v>
       </c>
       <c r="L127" s="7" t="n">
-        <v>1.6135</v>
+        <v>0.7895</v>
       </c>
       <c r="M127" s="7" t="n">
-        <v>2.0025</v>
+        <v>0.1712</v>
       </c>
       <c r="N127" s="7" t="n">
-        <v>9.2562</v>
+        <v>0.9815999999999999</v>
       </c>
       <c r="O127" s="7" t="n">
-        <v>0.3063</v>
+        <v>0.1378</v>
       </c>
       <c r="P127" s="7" t="n">
-        <v>0.1832</v>
+        <v>0.2179</v>
       </c>
       <c r="Q127" s="5" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R127" s="5" t="inlineStr"/>
@@ -7837,57 +7837,57 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>FMIZP</t>
+          <t>ONCSM</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>210.3</v>
+        <v>87</v>
       </c>
       <c r="C128" s="4" t="n">
-        <v>-0.0273</v>
+        <v>0.0235</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>-0.1769</v>
+        <v>-0.0091</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>-0.2087</v>
+        <v>-0.07150000000000001</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>-0.2717</v>
+        <v>-0.6686</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>-0.2704</v>
+        <v>-0.6945</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>-0.3211</v>
+        <v>-0.5057</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>4.21</v>
+        <v>4.11</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>21.27</v>
+        <v>28.73</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0.2837</v>
+        <v>0.5028</v>
       </c>
       <c r="L128" s="4" t="n">
-        <v>0.7895</v>
+        <v>1.6135</v>
       </c>
       <c r="M128" s="4" t="n">
-        <v>0.1712</v>
+        <v>2.0025</v>
       </c>
       <c r="N128" s="4" t="n">
-        <v>0.9815999999999999</v>
+        <v>9.2562</v>
       </c>
       <c r="O128" s="4" t="n">
-        <v>0.1378</v>
+        <v>0.3063</v>
       </c>
       <c r="P128" s="4" t="n">
-        <v>0.2179</v>
+        <v>0.1832</v>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr"/>
@@ -7898,32 +7898,32 @@
           <t>DOCO</t>
         </is>
       </c>
-      <c r="B129" s="8" t="n">
-        <v>11220</v>
+      <c r="B129" s="6" t="n">
+        <v>10997.5</v>
       </c>
       <c r="C129" s="7" t="n">
-        <v>0.0018</v>
+        <v>-0.0198</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>0.0289</v>
+        <v>0.0309</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>0.1008</v>
+        <v>0.028</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>0.0207</v>
+        <v>0.0176</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>0.2029</v>
+        <v>0.179</v>
       </c>
       <c r="H129" s="7" t="n">
-        <v>0.0665</v>
+        <v>0.0519</v>
       </c>
       <c r="I129" s="6" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="J129" s="6" t="n">
-        <v>20.6</v>
+        <v>20.19</v>
       </c>
       <c r="K129" s="7" t="n">
         <v>0.2032</v>
@@ -7957,31 +7957,31 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>6.61</v>
+        <v>6.21</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>-0.0322</v>
+        <v>-0.0605</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>0.0138</v>
+        <v>-0.0605</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>-0.3675</v>
+        <v>-0.3123</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>-0.4931</v>
+        <v>-0.5285</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>0.3857</v>
+        <v>0.3019</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>1.064</v>
+        <v>0.9256</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>4.64</v>
+        <v>4.36</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>56.54</v>
+        <v>53.12</v>
       </c>
       <c r="K130" s="4" t="n">
         <v>0.4591</v>
@@ -8015,31 +8015,31 @@
         </is>
       </c>
       <c r="B131" s="6" t="n">
-        <v>345.75</v>
+        <v>338.25</v>
       </c>
       <c r="C131" s="7" t="n">
-        <v>0.008800000000000001</v>
+        <v>-0.0217</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0196</v>
       </c>
       <c r="E131" s="7" t="n">
-        <v>-0.0731</v>
+        <v>-0.1052</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>-0.0693</v>
+        <v>-0.101</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>-0.1335</v>
+        <v>-0.1523</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>0.6940000000000001</v>
+        <v>0.6428</v>
       </c>
       <c r="I131" s="6" t="n">
-        <v>5.14</v>
+        <v>5.03</v>
       </c>
       <c r="J131" s="6" t="n">
-        <v>42.48</v>
+        <v>41.56</v>
       </c>
       <c r="K131" s="7" t="n">
         <v>0.5623</v>
@@ -8073,28 +8073,28 @@
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>19.86</v>
+        <v>17.88</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>-0.0378</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>-0.1841</v>
+        <v>-0.2385</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>-0.2856</v>
+        <v>-0.3465</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>-0.4658</v>
+        <v>-0.5006</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>-0.5115999999999999</v>
+        <v>-0.5603</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>-0.3663</v>
+        <v>-0.4195</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>5.76</v>
+        <v>5.19</v>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="4" t="n">
@@ -8129,28 +8129,28 @@
         </is>
       </c>
       <c r="B133" s="6" t="n">
-        <v>9.050000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>-0.0184</v>
+        <v>-0.0663</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>-0.0216</v>
+        <v>-0.09630000000000001</v>
       </c>
       <c r="E133" s="7" t="n">
-        <v>-0.1963</v>
+        <v>-0.1667</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>-0.2902</v>
+        <v>-0.3475</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>0.2067</v>
+        <v>0.1267</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>0.6258</v>
+        <v>0.4282</v>
       </c>
       <c r="I133" s="6" t="n">
-        <v>6.54</v>
+        <v>6.11</v>
       </c>
       <c r="J133" s="5" t="inlineStr"/>
       <c r="K133" s="7" t="n">
@@ -8185,28 +8185,28 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>11.13</v>
+        <v>10.02</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>-0.09949999999999999</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>-0.1345</v>
+        <v>-0.1919</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>0.3234</v>
+        <v>0.3236</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>-0.1536</v>
+        <v>-0.2147</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>0.3219</v>
+        <v>0.19</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>0.244</v>
+        <v>0.0955</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>9.029999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="4" t="n">
@@ -8241,28 +8241,28 @@
         </is>
       </c>
       <c r="B135" s="8" t="n">
-        <v>1120</v>
+        <v>1103</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0152</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>-0.1223</v>
+        <v>-0.1204</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>-0.2727</v>
+        <v>-0.2522</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>-0.3711</v>
+        <v>-0.3635</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>-0.3013</v>
+        <v>-0.3119</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>-0.3477</v>
+        <v>-0.3512</v>
       </c>
       <c r="I135" s="6" t="n">
-        <v>9.949999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J135" s="5" t="inlineStr"/>
       <c r="K135" s="7" t="n">
@@ -8293,57 +8293,55 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>QNBFK</t>
+          <t>KENT</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>34.66</v>
+        <v>233</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>-0.0091</v>
+        <v>-0.05860000000000001</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>-0.1326</v>
+        <v>-0.1314</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.2336</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>-0.2815</v>
+        <v>-0.3065</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>-0.1648</v>
+        <v>-0.4452</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>-0.2686</v>
+        <v>-0.5324</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="J136" s="3" t="n">
-        <v>38.22</v>
-      </c>
+        <v>10.03</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="4" t="n">
-        <v>0.2618</v>
+        <v>0.2234</v>
       </c>
       <c r="L136" s="4" t="n">
-        <v>0.2816</v>
+        <v>0.3229</v>
       </c>
       <c r="M136" s="4" t="n">
-        <v>0.285</v>
+        <v>0.5381</v>
       </c>
       <c r="N136" s="4" t="n">
-        <v>0.2688</v>
+        <v>0.0256</v>
       </c>
       <c r="O136" s="4" t="n">
-        <v>0.795</v>
+        <v>0.051</v>
       </c>
       <c r="P136" s="4" t="n">
-        <v>0.3111</v>
+        <v>-0.1222</v>
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R136" s="2" t="inlineStr"/>
@@ -8351,55 +8349,57 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>KENT</t>
+          <t>QNBFK</t>
         </is>
       </c>
       <c r="B137" s="6" t="n">
-        <v>247.5</v>
+        <v>33.96</v>
       </c>
       <c r="C137" s="7" t="n">
-        <v>-0.0076</v>
+        <v>-0.0202</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>-0.0833</v>
+        <v>-0.1341</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>-0.2016</v>
+        <v>-0.0567</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>-0.2918</v>
+        <v>-0.2995</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>-0.4107</v>
+        <v>-0.1817</v>
       </c>
       <c r="H137" s="7" t="n">
-        <v>-0.4986</v>
+        <v>-0.2457</v>
       </c>
       <c r="I137" s="6" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="J137" s="5" t="inlineStr"/>
+        <v>10.41</v>
+      </c>
+      <c r="J137" s="6" t="n">
+        <v>37.45</v>
+      </c>
       <c r="K137" s="7" t="n">
-        <v>0.2234</v>
+        <v>0.2618</v>
       </c>
       <c r="L137" s="7" t="n">
-        <v>0.3229</v>
+        <v>0.2816</v>
       </c>
       <c r="M137" s="7" t="n">
-        <v>0.5381</v>
+        <v>0.285</v>
       </c>
       <c r="N137" s="7" t="n">
-        <v>0.0256</v>
+        <v>0.2688</v>
       </c>
       <c r="O137" s="7" t="n">
-        <v>0.051</v>
+        <v>0.795</v>
       </c>
       <c r="P137" s="7" t="n">
-        <v>-0.1222</v>
+        <v>0.3111</v>
       </c>
       <c r="Q137" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R137" s="5" t="inlineStr"/>
@@ -8411,28 +8411,28 @@
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>37.74</v>
+        <v>35.74</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>-0.0146</v>
+        <v>-0.053</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>-0.0243</v>
+        <v>-0.0717</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>-0.1831</v>
+        <v>-0.1987</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>-0.1511</v>
+        <v>-0.1885</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>-0.1078</v>
+        <v>-0.1551</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>0.1849</v>
+        <v>0.1239</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>14.09</v>
+        <v>13.34</v>
       </c>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="4" t="n">
@@ -8467,31 +8467,31 @@
         </is>
       </c>
       <c r="B139" s="6" t="n">
-        <v>93.55</v>
+        <v>90.55</v>
       </c>
       <c r="C139" s="7" t="n">
-        <v>-0.024</v>
+        <v>-0.0321</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>-0.0654</v>
+        <v>-0.1035</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>-0.2004</v>
+        <v>-0.2029</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>-0.2754</v>
+        <v>-0.2948</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>-0.3792</v>
+        <v>-0.3991</v>
       </c>
       <c r="H139" s="7" t="n">
-        <v>-0.4222</v>
+        <v>-0.4379</v>
       </c>
       <c r="I139" s="6" t="n">
-        <v>14.23</v>
+        <v>13.78</v>
       </c>
       <c r="J139" s="6" t="n">
-        <v>53.6</v>
+        <v>51.89</v>
       </c>
       <c r="K139" s="7" t="n">
         <v>0.3045</v>
@@ -8525,25 +8525,25 @@
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>-0.0143</v>
+        <v>-0.029</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>-0.1176</v>
+        <v>-0.1184</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>-0.1529</v>
+        <v>-0.162</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>0.0935</v>
+        <v>0.0075</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0559</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>0.0051</v>
+        <v>-0.0067</v>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr"/>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>21.10.2026 19:26</t>
+          <t>22.10.2026 19:20</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_latest.xlsx
+++ b/data/bist_screener_latest.xlsx
@@ -99,7 +99,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R140"/>
+  <dimension ref="A1:R141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -583,25 +583,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12.13</v>
+        <v>11.68</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0</v>
+        <v>-0.0371</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.1354</v>
+        <v>-0.1923</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.4486</v>
+        <v>-0.5059</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-0.4599</v>
+        <v>-0.48</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.6095</v>
+        <v>-0.624</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.3728</v>
+        <v>-0.3995</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0.18</v>
@@ -639,31 +639,31 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>-0.0244</v>
+        <v>-0.075</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>-0.061</v>
+        <v>-0.119</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>-0.0385</v>
+        <v>-0.1514</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>-0.2337</v>
+        <v>-0.2912</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>-0.3808</v>
+        <v>-0.4272</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-0.3243</v>
+        <v>-0.3833</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>2.7227</v>
@@ -697,31 +697,31 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3.73</v>
+        <v>3.61</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.046</v>
+        <v>-0.0322</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.08800000000000001</v>
+        <v>-0.1195</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.0721</v>
+        <v>-0.1384</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.2657</v>
+        <v>-0.2894</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.3536</v>
+        <v>-0.3744</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>0.039</v>
+        <v>-0.09519999999999999</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0.21</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>1.7259</v>
@@ -755,31 +755,31 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>13.15</v>
+        <v>12.8</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>-0.0187</v>
+        <v>-0.0266</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0.0092</v>
+        <v>-0.0039</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-0.09119999999999999</v>
+        <v>-0.1239</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>-0.2011</v>
+        <v>-0.2224</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-0.2011</v>
+        <v>-0.2224</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>-0.3541</v>
+        <v>-0.3657</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>6.11</v>
+        <v>5.95</v>
       </c>
       <c r="K5" s="7" t="n">
         <v>0.9854999999999999</v>
@@ -809,55 +809,57 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SNICA</t>
+          <t>IHEVA</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0256</v>
+        <v>-0.0336</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.108</v>
+        <v>-0.04</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2664</v>
+        <v>-0.1429</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.5128</v>
+        <v>-0.2836</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.5411</v>
+        <v>-0.3543</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.6192</v>
+        <v>-0.4194</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
+        <v>0.21</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>8.06</v>
+      </c>
       <c r="K6" s="4" t="n">
-        <v>0.2451</v>
+        <v>0.2518</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1328</v>
+        <v>0.322</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.7476999999999999</v>
+        <v>0.2038</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.4518</v>
+        <v>0.1672</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.0576</v>
+        <v>0.078</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1748</v>
+        <v>0.0331</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr"/>
@@ -865,57 +867,55 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>IHEVA</t>
+          <t>SNICA</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>-0.0197</v>
+        <v>-0.0105</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-0.0132</v>
+        <v>-0.1215</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-0.1078</v>
+        <v>-0.2713</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>-0.2587</v>
+        <v>-0.5179</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-0.3318</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>-0.4134</v>
+        <v>-0.6154999999999999</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0.22</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>8.34</v>
-      </c>
+      <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="7" t="n">
-        <v>0.2518</v>
+        <v>0.2451</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.322</v>
+        <v>0.1328</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.2038</v>
+        <v>0.7476999999999999</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>0.1672</v>
+        <v>0.4518</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>0.078</v>
+        <v>0.0576</v>
       </c>
       <c r="P7" s="7" t="n">
-        <v>0.0331</v>
+        <v>-0.1748</v>
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr"/>
@@ -923,55 +923,57 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PNSUT</t>
+          <t>AKFGY</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>8.94</v>
+        <v>2.21</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.0154</v>
+        <v>-0.0264</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.0924</v>
+        <v>-0.1016</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.127</v>
+        <v>-0.116</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.232</v>
+        <v>-0.2079</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3016</v>
+        <v>-0.2218</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2732</v>
+        <v>-0.1195</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
+        <v>0.22</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>5.19</v>
+      </c>
       <c r="K8" s="4" t="n">
-        <v>0.049</v>
+        <v>0.3848</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.8042</v>
+        <v>0.3326</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.0075</v>
+        <v>0.3901</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2634</v>
+        <v>0.3812</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.0384</v>
+        <v>0.8458</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.09359999999999999</v>
+        <v>0.0496</v>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr"/>
@@ -979,57 +981,55 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>AKFGY</t>
+          <t>PNSUT</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>2.27</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>-0.0216</v>
+        <v>-0.0246</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-0.08839999999999999</v>
+        <v>-0.0917</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-0.0581</v>
+        <v>-0.1615</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>-0.1864</v>
+        <v>-0.2509</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-0.2007</v>
+        <v>-0.3188</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-0.0992</v>
+        <v>-0.2968</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>5.33</v>
-      </c>
+        <v>0.22</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr"/>
       <c r="K9" s="7" t="n">
-        <v>0.3848</v>
+        <v>0.049</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.3326</v>
+        <v>0.8042</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.3901</v>
+        <v>1.0075</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>0.3812</v>
+        <v>0.2634</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>0.8458</v>
+        <v>0.0384</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>0.0496</v>
+        <v>-0.09359999999999999</v>
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R9" s="5" t="inlineStr"/>
@@ -1041,31 +1041,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.0204</v>
+        <v>-0.022</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.0464</v>
+        <v>-0.08650000000000001</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.162</v>
+        <v>-0.1998</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2558</v>
+        <v>-0.2722</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3132</v>
+        <v>-0.3283</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3032</v>
+        <v>-0.3207</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.23</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>10.29</v>
+        <v>10.06</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0.3203</v>
@@ -1099,31 +1099,31 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3.83</v>
+        <v>3.75</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>-0.0254</v>
+        <v>-0.0209</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>-0.1155</v>
+        <v>-0.1299</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-0.0567</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>-0.2921</v>
+        <v>-0.3068</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-0.2401</v>
+        <v>-0.256</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-0.1937</v>
+        <v>-0.1776</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>13.72</v>
+        <v>13.44</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>0.1479</v>
@@ -1157,25 +1157,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>6.27</v>
+        <v>6.26</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.0032</v>
+        <v>-0.0016</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.0457</v>
+        <v>-0.0558</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1328</v>
+        <v>-0.1133</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1793</v>
+        <v>-0.1806</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2684</v>
+        <v>-0.2695</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1504</v>
+        <v>-0.1448</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0.25</v>
@@ -1213,28 +1213,28 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>11</v>
+        <v>10.72</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.0054</v>
+        <v>-0.0255</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>-0.1822</v>
+        <v>-0.1741</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>-0.3529</v>
+        <v>-0.3519</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>-0.5205</v>
+        <v>-0.5327000000000001</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-0.5733</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.7253000000000001</v>
+        <v>-0.7323000000000001</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
       <c r="K13" s="7" t="n">
@@ -1269,28 +1269,28 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>4.79</v>
+        <v>4.53</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.0224</v>
+        <v>-0.05429999999999999</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1626</v>
+        <v>-0.1703</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.0663</v>
+        <v>-0.208</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2403</v>
+        <v>-0.2815</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3349</v>
+        <v>-0.371</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4375</v>
+        <v>-0.4709</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="4" t="n">
@@ -1321,57 +1321,57 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>MHRGY</t>
+          <t>BESLR</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1.69</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>0.0242</v>
+        <v>-0.0245</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>-0.0815</v>
+        <v>-0.0965</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-0.1289</v>
+        <v>-0.181</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>-0.3258</v>
+        <v>-0.2738</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-0.3416</v>
+        <v>-0.3125</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.3017</v>
+        <v>-0.2743</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0.32</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>7.97</v>
+        <v>5.09</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.9460999999999999</v>
+        <v>0.3789</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.9873000000000001</v>
+        <v>0.3175</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.3702</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="N15" s="7" t="n">
-        <v>2464.8944</v>
+        <v>0.5778</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>0.8395999999999999</v>
+        <v>0.1173</v>
       </c>
       <c r="P15" s="7" t="n">
-        <v>0.0472</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R15" s="5" t="inlineStr"/>
@@ -1379,57 +1379,55 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BESLR</t>
+          <t>QUAGR</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9.789999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.0441</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.101</v>
+        <v>-0.2169</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1661</v>
+        <v>-0.4468</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2555</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2952</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2611</v>
+        <v>-0.8582</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>5.22</v>
-      </c>
+        <v>0.32</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="4" t="n">
-        <v>0.3789</v>
+        <v>0.2334</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.3175</v>
+        <v>0.1468</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.1104</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5778</v>
+        <v>0.4322</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1173</v>
+        <v>0.1786</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.07580000000000001</v>
+        <v>-0.1088</v>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr"/>
@@ -1437,55 +1435,57 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>MHRGY</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>-0.0216</v>
+        <v>0.0178</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>-0.2184</v>
+        <v>-0.0444</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>-0.431</v>
+        <v>-0.09949999999999999</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>-0.6504000000000001</v>
+        <v>-0.3138</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>-0.6504000000000001</v>
+        <v>-0.3299</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-0.8473999999999999</v>
+        <v>-0.3065</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0.33</v>
       </c>
-      <c r="J17" s="5" t="inlineStr"/>
+      <c r="J17" s="6" t="n">
+        <v>8.109999999999999</v>
+      </c>
       <c r="K17" s="7" t="n">
-        <v>0.2334</v>
+        <v>0.9460999999999999</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.1468</v>
+        <v>0.9873000000000001</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.1104</v>
+        <v>0.3702</v>
       </c>
       <c r="N17" s="7" t="n">
-        <v>0.4322</v>
+        <v>2464.8944</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>0.1786</v>
+        <v>0.8395999999999999</v>
       </c>
       <c r="P17" s="7" t="n">
-        <v>-0.1088</v>
+        <v>0.0472</v>
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R17" s="5" t="inlineStr"/>
@@ -1497,31 +1497,31 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>173.8</v>
+        <v>174.7</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.0274</v>
+        <v>0.0052</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.09849999999999999</v>
+        <v>-0.0915</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.0886</v>
+        <v>-0.133</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1563</v>
+        <v>-0.1519</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.08039999999999999</v>
+        <v>-0.0757</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1587</v>
+        <v>0.1701</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>0.35</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="K18" s="4" t="n">
         <v>0.5672999999999999</v>
@@ -1555,28 +1555,28 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>-0.0184</v>
+        <v>-0.025</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>-0.1623</v>
+        <v>-0.1789</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>-0.3388</v>
+        <v>-0.3128</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>-0.6911</v>
+        <v>-0.6988</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>-0.7542</v>
+        <v>-0.7604000000000001</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-0.619</v>
+        <v>-0.6303</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="J19" s="5" t="inlineStr"/>
       <c r="K19" s="7" t="n">
@@ -1611,31 +1611,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>34.08</v>
+        <v>33.88</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.0335</v>
+        <v>-0.0059</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.0888</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1531</v>
+        <v>-0.161</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.2201</v>
+        <v>-0.2247</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2792</v>
+        <v>-0.2834</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.004699999999999999</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>0.38</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.56</v>
+        <v>8.51</v>
       </c>
       <c r="K20" s="4" t="n">
         <v>0.2329</v>
@@ -1669,31 +1669,31 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>6.64</v>
+        <v>6.45</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>-0.0278</v>
+        <v>-0.0286</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>-0.1015</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-0.2188</v>
+        <v>-0.2809</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>-0.3718</v>
+        <v>-0.3898</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>-0.4296</v>
+        <v>-0.4459</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-0.3176</v>
+        <v>-0.3505</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="K21" s="7" t="n">
         <v>0.9081</v>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>8.99</v>
+        <v>8.9</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.0375</v>
+        <v>-0.01</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.1479</v>
+        <v>-0.1179</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.2445</v>
+        <v>-0.2261</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.4027000000000001</v>
+        <v>-0.4086</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4863</v>
+        <v>-0.4914</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.3331</v>
+        <v>-0.3456</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>0.41</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>0.4985</v>
@@ -1785,31 +1785,31 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>16.57</v>
+        <v>16.38</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>-0.0416</v>
+        <v>-0.0115</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>-0.0794</v>
+        <v>-0.0693</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>-0.1715</v>
+        <v>-0.1915</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>-0.2235</v>
+        <v>-0.2324</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>-0.2191</v>
+        <v>-0.2281</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-0.0389</v>
+        <v>-0.0262</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0.41</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>6.69</v>
+        <v>6.62</v>
       </c>
       <c r="K23" s="7" t="n">
         <v>0.1285</v>
@@ -1843,31 +1843,31 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.09880000000000001</v>
+        <v>-0.0993</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2736</v>
+        <v>-0.3342</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2416</v>
+        <v>-0.3425</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.4172</v>
+        <v>-0.475</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5327000000000001</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3329</v>
+        <v>-0.4252</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>2.37</v>
+        <v>2.13</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>0.208</v>
@@ -1897,57 +1897,55 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>YUNSA</t>
+          <t>ERBOS</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5.23</v>
+        <v>93.75</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>-0.0279</v>
+        <v>-0.0325</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>-0.1269</v>
+        <v>-0.1335</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-0.1866</v>
+        <v>-0.2524</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>-0.4253</v>
+        <v>-0.4508</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>-0.4104</v>
+        <v>-0.5382</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-0.2913</v>
+        <v>-0.4874</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0.48</v>
       </c>
-      <c r="J25" s="6" t="n">
-        <v>6.28</v>
-      </c>
+      <c r="J25" s="5" t="inlineStr"/>
       <c r="K25" s="7" t="n">
-        <v>0.6883</v>
+        <v>0.2349</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.8734999999999999</v>
+        <v>1.1405</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>1.1469</v>
+        <v>1.0386</v>
       </c>
       <c r="N25" s="7" t="n">
-        <v>1.3327</v>
+        <v>0.7831999999999999</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>0.1078</v>
+        <v>0.131</v>
       </c>
       <c r="P25" s="7" t="n">
-        <v>0.09</v>
+        <v>-0.023</v>
       </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R25" s="5" t="inlineStr"/>
@@ -1955,55 +1953,57 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ERBOS</t>
+          <t>YUNSA</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>5.14</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.0062</v>
+        <v>-0.0172</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.127</v>
+        <v>-0.09820000000000001</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2064</v>
+        <v>-0.243</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.4323</v>
+        <v>-0.4352</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5227000000000001</v>
+        <v>-0.4205</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.4719</v>
+        <v>-0.293</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
+        <v>0.48</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>6.17</v>
+      </c>
       <c r="K26" s="4" t="n">
-        <v>0.2349</v>
+        <v>0.6883</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.1405</v>
+        <v>0.8734999999999999</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.0386</v>
+        <v>1.1469</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.7831999999999999</v>
+        <v>1.3327</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.131</v>
+        <v>0.1078</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.023</v>
+        <v>0.09</v>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr"/>
@@ -2011,57 +2011,57 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>AGHOL</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>28.18</v>
+        <v>2.55</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.0989</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>-0.1292</v>
+        <v>-0.4042</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-0.1717</v>
+        <v>-0.8998</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>-0.1898</v>
+        <v>-0.9407</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.8981999999999999</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>0.1209</v>
+        <v>-0.9368000000000001</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>15.41</v>
+        <v>1.62</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.3105</v>
+        <v>7.8666</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.3107</v>
+        <v>3.1929</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.4787</v>
+        <v>4.946499999999999</v>
       </c>
       <c r="N27" s="7" t="n">
-        <v>1.4985</v>
+        <v>1.0979</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>0.0693</v>
+        <v>0.4854</v>
       </c>
       <c r="P27" s="7" t="n">
-        <v>-0.0718</v>
+        <v>0.586</v>
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R27" s="5" t="inlineStr"/>
@@ -2069,57 +2069,57 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KRSTL</t>
+          <t>OYYAT</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>6.13</v>
+        <v>22.02</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.0362</v>
+        <v>-0.0566</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1462</v>
+        <v>-0.1371</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.2161</v>
+        <v>-0.3075</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.4083</v>
+        <v>-0.4175</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3387</v>
+        <v>-0.612</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4335</v>
+        <v>-0.5814</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.53</v>
+        <v>2.82</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.3806</v>
+        <v>0.045</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2571</v>
+        <v>0.4061999999999999</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.5529999999999999</v>
+        <v>0.4311</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.6774</v>
+        <v>3.0744</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.1192</v>
+        <v>0.2671</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.1788</v>
+        <v>0.2126</v>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr"/>
@@ -2127,57 +2127,57 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>OYYAT</t>
+          <t>KRSTL</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>23.34</v>
+        <v>6.1</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>-0.0168</v>
+        <v>-0.0049</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>-0.1285</v>
+        <v>-0.1408</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-0.1782</v>
+        <v>-0.2403</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>-0.3825</v>
+        <v>-0.4112</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>-0.5887</v>
+        <v>-0.342</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>-0.5637</v>
+        <v>-0.4587</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>2.99</v>
+        <v>3.51</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.045</v>
+        <v>0.3806</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.4061999999999999</v>
+        <v>0.2571</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.4311</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="N29" s="7" t="n">
-        <v>3.0744</v>
+        <v>0.6774</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>0.2671</v>
+        <v>0.1192</v>
       </c>
       <c r="P29" s="7" t="n">
-        <v>0.2126</v>
+        <v>0.1788</v>
       </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R29" s="5" t="inlineStr"/>
@@ -2185,57 +2185,57 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>AGHOL</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>2.83</v>
+        <v>28.82</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.0987</v>
+        <v>0.0227</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.4042</v>
+        <v>-0.0786</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.8998999999999999</v>
+        <v>-0.1548</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.9342</v>
+        <v>-0.1714</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.887</v>
+        <v>-0.07919999999999999</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.9217</v>
+        <v>0.1197</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>0.53</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.8</v>
+        <v>15.76</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>7.8666</v>
+        <v>0.3105</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>3.1929</v>
+        <v>0.3107</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.946499999999999</v>
+        <v>0.4787</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.0979</v>
+        <v>1.4985</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.4854</v>
+        <v>0.0693</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.586</v>
+        <v>-0.0718</v>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr"/>
@@ -2247,28 +2247,28 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>-0.029</v>
+        <v>-0.04849999999999999</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>-0.053</v>
+        <v>-0.0827</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>-0.127</v>
+        <v>-0.2031</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>-0.2884</v>
+        <v>-0.3229</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>-0.2112</v>
+        <v>-0.2495</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>-0.0717</v>
+        <v>-0.1135</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="7" t="n">
@@ -2303,28 +2303,28 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>26.24</v>
+        <v>25.5</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.0165</v>
+        <v>-0.0282</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.092</v>
+        <v>-0.0867</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2282</v>
+        <v>-0.2478</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.4587</v>
+        <v>-0.474</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.3979</v>
+        <v>-0.4149</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2795</v>
+        <v>-0.2921</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="4" t="n">
@@ -2359,28 +2359,28 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>13.67</v>
+        <v>13.23</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>-0.042</v>
+        <v>-0.0322</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>-0.0917</v>
+        <v>-0.1168</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>-0.2876</v>
+        <v>-0.3091</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>-0.4108</v>
+        <v>-0.4297</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>-0.4475</v>
+        <v>-0.4652000000000001</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>-0.4183</v>
+        <v>-0.4551</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="J33" s="5" t="inlineStr"/>
       <c r="K33" s="7" t="n">
@@ -2411,55 +2411,57 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>SOKE</t>
+          <t>PNLSN</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>7.26</v>
+        <v>27.16</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.0189</v>
+        <v>-0.0328</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.032</v>
+        <v>-0.1502</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.0959</v>
+        <v>-0.2118</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.5967</v>
+        <v>-0.4299</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.5967</v>
+        <v>-0.4209000000000001</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3506</v>
+        <v>-0.2923</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
+        <v>0.58</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>7.66</v>
+      </c>
       <c r="K34" s="4" t="n">
-        <v>0.5234000000000001</v>
+        <v>0.306</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.4561</v>
+        <v>0.6481</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.4897</v>
+        <v>0.5497</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.3644</v>
+        <v>7.793600000000001</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.032</v>
+        <v>0.1302</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.0429</v>
+        <v>0.08839999999999999</v>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr"/>
@@ -2467,57 +2469,57 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>PNLSN</t>
+          <t>MERCN</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>28.08</v>
+        <v>8.81</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>-0.039</v>
+        <v>-0.02</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>-0.1247</v>
+        <v>-0.119</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>-0.1628</v>
+        <v>-0.4031</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>-0.4106</v>
+        <v>-0.6369</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>-0.4013</v>
+        <v>-0.6119</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>-0.2622</v>
+        <v>-0.7062999999999999</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>7.92</v>
+        <v>10.12</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.306</v>
+        <v>0.2374</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.6481</v>
+        <v>0.8593999999999999</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.5497</v>
+        <v>1.4059</v>
       </c>
       <c r="N35" s="7" t="n">
-        <v>7.793600000000001</v>
+        <v>1.3031</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>0.1302</v>
+        <v>0.1784</v>
       </c>
       <c r="P35" s="7" t="n">
-        <v>0.08839999999999999</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R35" s="5" t="inlineStr"/>
@@ -2525,57 +2527,57 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MERCN</t>
+          <t>AKMGY</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>8.99</v>
+        <v>176.5</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>-0.0467</v>
+        <v>-0.0249</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>-0.1272</v>
+        <v>-0.1365</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>-0.3638</v>
+        <v>-0.2286</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>-0.6294</v>
+        <v>-0.274</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.604</v>
+        <v>-0.3645</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-0.7387</v>
+        <v>-0.1999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>10.33</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0.2374</v>
+        <v>0.3886</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>0.8593999999999999</v>
+        <v>0.3887</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>1.4059</v>
+        <v>0.3141</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>1.3031</v>
+        <v>0.5958</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>0.1784</v>
+        <v>0.6443000000000001</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0781</v>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr"/>
@@ -2587,31 +2589,31 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>4.87</v>
+        <v>4.8</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>-0.0337</v>
+        <v>-0.0144</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>-0.0562</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>-0.1048</v>
+        <v>-0.1257</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>-0.4631</v>
+        <v>-0.4708</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>-0.3835</v>
+        <v>-0.3924</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>-0.4906</v>
+        <v>-0.5127</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>8.35</v>
+        <v>8.23</v>
       </c>
       <c r="K37" s="7" t="n">
         <v>1.6512</v>
@@ -2641,53 +2643,53 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AKMGY</t>
+          <t>TUREX</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>181</v>
+        <v>4.98</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>-0.0347</v>
+        <v>-0.0235</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>-0.1171</v>
+        <v>-0.1399</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>-0.2072</v>
+        <v>-0.0197</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-0.2555</v>
+        <v>-0.3159</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-0.3483</v>
+        <v>-0.4036</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-0.1902</v>
+        <v>-0.3472999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>8.92</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.3886</v>
+        <v>0.4159</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>0.3887</v>
+        <v>1.3967</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.3141</v>
+        <v>0.8518000000000001</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.5958</v>
+        <v>0.3205</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0.6443000000000001</v>
+        <v>0.2638</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>0.0781</v>
+        <v>0.0862</v>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
@@ -2699,57 +2701,57 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TUREX</t>
+          <t>TTKOM</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>5.1</v>
+        <v>46.04</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>-0.0304</v>
+        <v>-0.0283</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>-0.1297</v>
+        <v>-0.1138</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-0.0135</v>
+        <v>-0.1474</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>-0.2995</v>
+        <v>-0.1749</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>-0.3892</v>
+        <v>-0.2744</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>-0.3316</v>
+        <v>-0.09369999999999999</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0.61</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>9.59</v>
+        <v>5.69</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.4159</v>
+        <v>0.4498</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>1.3967</v>
+        <v>0.4329</v>
       </c>
       <c r="M39" s="7" t="n">
-        <v>0.8518000000000001</v>
+        <v>0.5323</v>
       </c>
       <c r="N39" s="7" t="n">
-        <v>0.3205</v>
+        <v>0.8047</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>0.2638</v>
+        <v>0.4117</v>
       </c>
       <c r="P39" s="7" t="n">
-        <v>0.0862</v>
+        <v>1.3041</v>
       </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R39" s="5" t="inlineStr"/>
@@ -2757,57 +2759,55 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TTKOM</t>
+          <t>SOKE</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>47.38</v>
+        <v>7.44</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>-0.0409</v>
+        <v>0.0248</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>-0.0958</v>
+        <v>0.0109</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>-0.1127</v>
+        <v>-0.08710000000000001</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>-0.1509</v>
+        <v>-0.5867</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-0.2533</v>
+        <v>-0.5867</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.0486</v>
+        <v>-0.3375</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>5.86</v>
-      </c>
+        <v>0.61</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="4" t="n">
-        <v>0.4498</v>
+        <v>0.5234000000000001</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>0.4329</v>
+        <v>0.4561</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.5323</v>
+        <v>0.4897</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.8047</v>
+        <v>0.3644</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.4117</v>
+        <v>0.032</v>
       </c>
       <c r="P40" s="4" t="n">
-        <v>1.3041</v>
+        <v>-0.0429</v>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr"/>
@@ -2815,57 +2815,57 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>KCHOL</t>
+          <t>BNTAS</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>196.1</v>
+        <v>4.65</v>
       </c>
       <c r="C41" s="7" t="n">
-        <v>-0.0354</v>
+        <v>-0.0169</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>-0.06570000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-0.1175</v>
+        <v>-0.1637</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>-0.0111</v>
+        <v>-0.2352</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>-0.0373</v>
+        <v>-0.3162</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>0.2404</v>
+        <v>-0.2813</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>13.98</v>
+        <v>4.31</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.3261</v>
+        <v>0.2654</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>0.5440999999999999</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="M41" s="7" t="n">
-        <v>0.9423</v>
+        <v>0.464</v>
       </c>
       <c r="N41" s="7" t="n">
-        <v>5.083299999999999</v>
+        <v>0.3679</v>
       </c>
       <c r="O41" s="7" t="n">
-        <v>0.0646</v>
+        <v>0.1363</v>
       </c>
       <c r="P41" s="7" t="n">
-        <v>0.0771</v>
+        <v>0.1657</v>
       </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R41" s="5" t="inlineStr"/>
@@ -2873,57 +2873,57 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>BNTAS</t>
+          <t>RALYH</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>4.73</v>
+        <v>15.89</v>
       </c>
       <c r="C42" s="4" t="n">
-        <v>-0.0227</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>-0.0851</v>
+        <v>-0.3434</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-0.1142</v>
+        <v>-0.89</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-0.222</v>
+        <v>-0.9377</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-0.3044</v>
+        <v>-0.9512999999999999</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-0.2701</v>
+        <v>-0.9161</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>0.63</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>4.38</v>
+        <v>2.06</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0.2654</v>
+        <v>0.7070000000000001</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>0.07690000000000001</v>
+        <v>1.4848</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.464</v>
+        <v>1.5369</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.3679</v>
+        <v>0.5434</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>0.1363</v>
+        <v>0.2854</v>
       </c>
       <c r="P42" s="4" t="n">
-        <v>0.1657</v>
+        <v>0.3914</v>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr"/>
@@ -2931,57 +2931,57 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>EREGL</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>93.3</v>
+        <v>31.6</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>-0.0179</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>-0.0431</v>
+        <v>-0.1436</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-0.06179999999999999</v>
+        <v>-0.1645</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>-0.1114</v>
+        <v>-0.2825</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>-0.1794</v>
+        <v>-0.0283</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>-0.0411</v>
+        <v>0.1747</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>10.48</v>
+        <v>22.91</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.3971</v>
+        <v>0.2651</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>0.4118</v>
+        <v>0.5514</v>
       </c>
       <c r="M43" s="7" t="n">
-        <v>0.3975</v>
+        <v>0.6056</v>
       </c>
       <c r="N43" s="7" t="n">
-        <v>0.2377</v>
+        <v>0.8258</v>
       </c>
       <c r="O43" s="7" t="n">
-        <v>0.4333</v>
+        <v>0.104</v>
       </c>
       <c r="P43" s="7" t="n">
-        <v>0.1518</v>
+        <v>0.0312</v>
       </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R43" s="5" t="inlineStr"/>
@@ -2989,57 +2989,57 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>PINSU</t>
+          <t>KCHOL</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>7.25</v>
+        <v>197.5</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>-0.0109</v>
+        <v>0.0071</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>-0.142</v>
+        <v>-0.055</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>-0.1927</v>
+        <v>-0.1063</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>-0.3584000000000001</v>
+        <v>-0.004</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-0.4057</v>
+        <v>-0.0304</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>-0.4545</v>
+        <v>0.2275</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>15.28</v>
+        <v>14.08</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0.2802</v>
+        <v>0.3261</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>0.2234</v>
+        <v>0.5440999999999999</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.3074</v>
+        <v>0.9423</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>91.6451</v>
+        <v>5.083299999999999</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>0.1329</v>
+        <v>0.0646</v>
       </c>
       <c r="P44" s="4" t="n">
-        <v>0.0528</v>
+        <v>0.0771</v>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr"/>
@@ -3047,57 +3047,57 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>BASGZ</t>
+          <t>ULUFA</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>34.88</v>
+        <v>1.47</v>
       </c>
       <c r="C45" s="7" t="n">
-        <v>-0.0444</v>
+        <v>-0.0329</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>-0.1254</v>
+        <v>-0.02</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-0.1627</v>
+        <v>-0.0134</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>-0.2579</v>
+        <v>-0.1742</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>-0.2959</v>
+        <v>-0.3581</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>-0.09449999999999999</v>
+        <v>-0.2364</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>6.32</v>
+        <v>1.76</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>0.3163</v>
+        <v>0.3562</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>0.5275</v>
+        <v>0.3545</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>0.4513</v>
+        <v>0.3386</v>
       </c>
       <c r="N45" s="7" t="n">
-        <v>0.3789</v>
+        <v>0.395</v>
       </c>
       <c r="O45" s="7" t="n">
-        <v>0.1301</v>
+        <v>0.8595999999999999</v>
       </c>
       <c r="P45" s="7" t="n">
-        <v>-0.245</v>
+        <v>0.4314</v>
       </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R45" s="5" t="inlineStr"/>
@@ -3105,57 +3105,57 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>AYGAZ</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>263.75</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="C46" s="4" t="n">
-        <v>-0.0241</v>
+        <v>-0.0343</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>-0.09519999999999999</v>
+        <v>-0.0711</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>-0.1553</v>
+        <v>-0.1035</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>-0.081</v>
+        <v>-0.1419</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-0.0409</v>
+        <v>-0.2076</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.4452</v>
+        <v>-0.08529999999999999</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>6.93</v>
+        <v>10.12</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0.1662</v>
+        <v>0.3971</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>0.3683</v>
+        <v>0.4118</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.4549</v>
+        <v>0.3975</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>1.9624</v>
+        <v>0.2377</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0.0302</v>
+        <v>0.4333</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>0.118</v>
+        <v>0.1518</v>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr"/>
@@ -3163,57 +3163,57 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>RALYH</t>
+          <t>PINSU</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>17.65</v>
+        <v>7.03</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>-0.0999</v>
+        <v>-0.0303</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>-0.3434</v>
+        <v>-0.1353</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-0.89</v>
+        <v>-0.2189</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>-0.9308</v>
+        <v>-0.3779</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>-0.9459000000000001</v>
+        <v>-0.4238</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>-0.9059999999999999</v>
+        <v>-0.4979</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>2.29</v>
+        <v>14.82</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>0.7070000000000001</v>
+        <v>0.2802</v>
       </c>
       <c r="L47" s="7" t="n">
-        <v>1.4848</v>
+        <v>0.2234</v>
       </c>
       <c r="M47" s="7" t="n">
-        <v>1.5369</v>
+        <v>0.3074</v>
       </c>
       <c r="N47" s="7" t="n">
-        <v>0.5434</v>
+        <v>91.6451</v>
       </c>
       <c r="O47" s="7" t="n">
-        <v>0.2854</v>
+        <v>0.1329</v>
       </c>
       <c r="P47" s="7" t="n">
-        <v>0.3914</v>
+        <v>0.0528</v>
       </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R47" s="5" t="inlineStr"/>
@@ -3221,55 +3221,57 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AYES</t>
+          <t>BASGZ</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.0252</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>-0.2</v>
+        <v>-0.1392</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>-0.1174</v>
+        <v>-0.1768</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>-0.3573</v>
+        <v>-0.2766</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-0.3547999999999999</v>
+        <v>-0.3137</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.2755</v>
+        <v>-0.1563</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.65</v>
+        <v>6.16</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0.4183</v>
+        <v>0.3163</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>0.314</v>
+        <v>0.5275</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.8128</v>
+        <v>0.4513</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>42.7724</v>
+        <v>0.3789</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>0.0208</v>
-      </c>
-      <c r="P48" s="2" t="inlineStr"/>
+        <v>0.1301</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>-0.245</v>
+      </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr"/>
@@ -3277,57 +3279,55 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>ARASE</t>
+          <t>AYES</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>70.75</v>
+        <v>5.7</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>-0.07519999999999999</v>
+        <v>-0.05</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>-0.2576</v>
+        <v>-0.1739</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>-0.303</v>
+        <v>-0.1782</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>-0.4182</v>
+        <v>-0.3895</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>-0.2974</v>
+        <v>-0.3871</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0.3554</v>
+        <v>0.25</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>6.45</v>
+        <v>1.57</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>0.1264</v>
+        <v>0.4183</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>0.596</v>
+        <v>0.314</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0.7123999999999999</v>
+        <v>0.8128</v>
       </c>
       <c r="N49" s="7" t="n">
-        <v>4.0303</v>
+        <v>42.7724</v>
       </c>
       <c r="O49" s="7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P49" s="7" t="n">
-        <v>0.1463</v>
-      </c>
+        <v>0.0208</v>
+      </c>
+      <c r="P49" s="5" t="inlineStr"/>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R49" s="5" t="inlineStr"/>
@@ -3335,57 +3335,57 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GRTHO</t>
+          <t>AYGAZ</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>57.6</v>
+        <v>269</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.0277</v>
+        <v>0.0199</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>-0.2809</v>
+        <v>-0.0578</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>-0.5579</v>
+        <v>-0.1003</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>-0.7664</v>
+        <v>-0.06269999999999999</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-0.7626000000000001</v>
+        <v>-0.0218</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>-0.9054000000000001</v>
+        <v>0.4424</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>4.01</v>
+        <v>7.07</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0.5085000000000001</v>
+        <v>0.1662</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>0.4487</v>
+        <v>0.3683</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.2298</v>
+        <v>0.4549</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.9399</v>
+        <v>1.9624</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>0.1089</v>
+        <v>0.0302</v>
       </c>
       <c r="P50" s="4" t="n">
-        <v>0.2287</v>
+        <v>0.118</v>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr"/>
@@ -3393,57 +3393,57 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>ISFIN</t>
+          <t>ARASE</t>
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>14.77</v>
+        <v>69.95</v>
       </c>
       <c r="C51" s="7" t="n">
-        <v>-0.0289</v>
+        <v>-0.0113</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.2559</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-0.2164</v>
+        <v>-0.3033</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>-0.2433</v>
+        <v>-0.4248</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>-0.2872</v>
+        <v>-0.3054</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>-0.1794</v>
+        <v>0.3337</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>2.51</v>
+        <v>6.38</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>0.5749</v>
+        <v>0.1264</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>0.5787</v>
+        <v>0.596</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>0.5648</v>
+        <v>0.7123999999999999</v>
       </c>
       <c r="N51" s="7" t="n">
-        <v>0.6275999999999999</v>
+        <v>4.0303</v>
       </c>
       <c r="O51" s="7" t="n">
-        <v>0.9556</v>
+        <v>0.25</v>
       </c>
       <c r="P51" s="7" t="n">
-        <v>0.3468</v>
+        <v>0.1463</v>
       </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R51" s="5" t="inlineStr"/>
@@ -3451,57 +3451,57 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>EREGL</t>
+          <t>ISFIN</t>
         </is>
       </c>
       <c r="B52" s="3" t="n">
-        <v>35.1</v>
+        <v>14.54</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>-0.0389</v>
+        <v>-0.0156</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>-0.05139999999999999</v>
+        <v>-0.06849999999999999</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>-0.059</v>
+        <v>-0.2282</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>-0.203</v>
+        <v>-0.2551</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>0.0793</v>
+        <v>-0.2983</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.2801</v>
+        <v>-0.1813</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>30.59</v>
+        <v>2.47</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0.1998</v>
+        <v>0.5749</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>0.3838</v>
+        <v>0.5787</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.4877</v>
+        <v>0.5648</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.4752</v>
+        <v>0.6275999999999999</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>0.104</v>
+        <v>0.9556</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>0.0274</v>
+        <v>0.3468</v>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr"/>
@@ -3513,31 +3513,31 @@
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>7.01</v>
+        <v>6.76</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>-0.0397</v>
+        <v>-0.0357</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>-0.1645</v>
+        <v>-0.1654</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-0.2446</v>
+        <v>-0.3353</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>-0.3592</v>
+        <v>-0.3821</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>-0.3802</v>
+        <v>-0.4023</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>-0.2919</v>
+        <v>-0.3024</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>26.09</v>
+        <v>25.16</v>
       </c>
       <c r="K53" s="7" t="n">
         <v>0.8458</v>
@@ -3567,57 +3567,57 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>DESA</t>
+          <t>EGGUB</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>7.72</v>
+        <v>76.75</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>-0.035</v>
+        <v>-0.0646</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>-0.0493</v>
+        <v>-0.1566</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>-0.1247</v>
+        <v>-0.2599</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>-0.2202</v>
+        <v>-0.2549</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-0.4517</v>
+        <v>-0.3709</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>-0.4766</v>
+        <v>-0.2022</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>7.31</v>
+        <v>10.74</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0.2088</v>
+        <v>0.4926</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>0.2301</v>
+        <v>0.6905</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.0037</v>
+        <v>0.7726999999999999</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.3571</v>
+        <v>0.5777</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>0.2399</v>
+        <v>0.4324</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>0.1277</v>
+        <v>0.0886</v>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr"/>
@@ -3625,57 +3625,57 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>EGGUB</t>
+          <t>GRTHO</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>82.05</v>
+        <v>60.55</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>-0.03700000000000001</v>
+        <v>0.0512</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>-0.1033</v>
+        <v>-0.1602</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-0.1741</v>
+        <v>-0.4838</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>-0.2034</v>
+        <v>-0.7545000000000001</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>-0.3275</v>
+        <v>-0.7504000000000001</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>-0.1541</v>
+        <v>-0.8987000000000001</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>11.48</v>
+        <v>4.21</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>0.4926</v>
+        <v>0.5085000000000001</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>0.6905</v>
+        <v>0.4487</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>0.7726999999999999</v>
+        <v>0.2298</v>
       </c>
       <c r="N55" s="7" t="n">
-        <v>0.5777</v>
+        <v>0.9399</v>
       </c>
       <c r="O55" s="7" t="n">
-        <v>0.4324</v>
+        <v>0.1089</v>
       </c>
       <c r="P55" s="7" t="n">
-        <v>0.0886</v>
+        <v>0.2287</v>
       </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R55" s="5" t="inlineStr"/>
@@ -3683,57 +3683,57 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GESAN</t>
+          <t>MOBTL</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>30.3</v>
+        <v>7.39</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>-0.035</v>
+        <v>-0.0999</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>-0.1739</v>
+        <v>-0.2901</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>-0.3129</v>
+        <v>-0.2436</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>-0.6343</v>
+        <v>-0.4997</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>-0.3427</v>
+        <v>-0.4448</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>-0.2957</v>
+        <v>0.0123</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>8.140000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0.2641</v>
+        <v>0.5631</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>0.2931</v>
+        <v>0.4406</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.3273</v>
+        <v>0.5064</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.4479</v>
+        <v>1.6818</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>0.1778</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="P56" s="4" t="n">
-        <v>0.1266</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R56" s="2" t="inlineStr"/>
@@ -3741,57 +3741,57 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>MGROS</t>
+          <t>GESAN</t>
         </is>
       </c>
       <c r="B57" s="6" t="n">
-        <v>440.5</v>
+        <v>30.12</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>-0.0297</v>
+        <v>-0.0059</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>-0.08990000000000001</v>
+        <v>-0.1633</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-0.1812</v>
+        <v>-0.4174</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>-0.2991</v>
+        <v>-0.6365</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>-0.328</v>
+        <v>-0.3466</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>0.0109</v>
+        <v>-0.3021</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>13.19</v>
+        <v>8.09</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>0.3804</v>
+        <v>0.2641</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>0.3113</v>
+        <v>0.2931</v>
       </c>
       <c r="M57" s="7" t="n">
-        <v>1.725</v>
+        <v>0.3273</v>
       </c>
       <c r="N57" s="7" t="n">
-        <v>0.0848</v>
+        <v>0.4479</v>
       </c>
       <c r="O57" s="7" t="n">
-        <v>0.0184</v>
+        <v>0.1778</v>
       </c>
       <c r="P57" s="7" t="n">
-        <v>0.1216</v>
+        <v>0.1266</v>
       </c>
       <c r="Q57" s="5" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R57" s="5" t="inlineStr"/>
@@ -3799,57 +3799,57 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ZRGYO</t>
+          <t>MGROS</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>17.5</v>
+        <v>431.5</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0204</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>-0.0789</v>
+        <v>-0.068</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>-0.1026</v>
+        <v>-0.1994</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>-0.0369</v>
+        <v>-0.3134</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-0.1972</v>
+        <v>-0.3417</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>-0.2074</v>
+        <v>-0.0416</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>13.24</v>
+        <v>12.92</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>2.3363</v>
+        <v>0.3804</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>3.5944</v>
+        <v>0.3113</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>3.6478</v>
+        <v>1.725</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.2899</v>
+        <v>0.0848</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>0.5917</v>
+        <v>0.0184</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>0.0776</v>
+        <v>0.1216</v>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R58" s="2" t="inlineStr"/>
@@ -3857,57 +3857,57 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>MOBTL</t>
+          <t>DESA</t>
         </is>
       </c>
       <c r="B59" s="6" t="n">
-        <v>8.210000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="C59" s="7" t="n">
-        <v>-0.0998</v>
+        <v>0.0453</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>-0.2255</v>
+        <v>-0.0277</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-0.2106</v>
+        <v>-0.07769999999999999</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>-0.4440999999999999</v>
+        <v>-0.1848</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>-0.3832</v>
+        <v>-0.4268</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>0.102</v>
+        <v>-0.445</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>11.64</v>
+        <v>7.65</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>0.5631</v>
+        <v>0.2088</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>0.4406</v>
+        <v>0.2301</v>
       </c>
       <c r="M59" s="7" t="n">
-        <v>0.5064</v>
+        <v>0.0037</v>
       </c>
       <c r="N59" s="7" t="n">
-        <v>1.6818</v>
+        <v>0.3571</v>
       </c>
       <c r="O59" s="7" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.2399</v>
       </c>
       <c r="P59" s="7" t="n">
-        <v>0.08689999999999999</v>
+        <v>0.1277</v>
       </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R59" s="5" t="inlineStr"/>
@@ -3915,57 +3915,57 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>CWENE</t>
+          <t>KTLEV</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>15</v>
+        <v>4.07</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>-0.0073</v>
+        <v>-0.08539999999999999</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>-0.1187</v>
+        <v>-0.3748</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>-0.359</v>
+        <v>-0.7494</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>-0.6193</v>
+        <v>-0.9188</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-0.5763</v>
+        <v>-0.8689</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>-0.3123</v>
+        <v>0.0727</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>5.58</v>
+        <v>0.99</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0.5809000000000001</v>
+        <v>3.5578</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>0.9067000000000001</v>
+        <v>3.6471</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.8432999999999999</v>
+        <v>5.174600000000001</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>5.095899999999999</v>
+        <v>5.7649</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>0.1918</v>
+        <v>0.7222</v>
       </c>
       <c r="P60" s="4" t="n">
-        <v>0.2052</v>
+        <v>1.5072</v>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr"/>
@@ -3973,55 +3973,57 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>BYDNR</t>
+          <t>TNZTP</t>
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>18.42</v>
+        <v>20.78</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>-0.1058</v>
+        <v>-0.1484</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>-0.1311</v>
+        <v>-0.283</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>-0.5274</v>
+        <v>-0.1688</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.1641</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>-0.08810000000000001</v>
+        <v>-0.0389</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="J61" s="5" t="inlineStr"/>
+        <v>0.87</v>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>15.38</v>
+      </c>
       <c r="K61" s="7" t="n">
-        <v>0.2762</v>
+        <v>0.4327</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>0.0636</v>
+        <v>0.4143</v>
       </c>
       <c r="M61" s="7" t="n">
-        <v>0.127</v>
+        <v>0.5201</v>
       </c>
       <c r="N61" s="7" t="n">
-        <v>0.7182999999999999</v>
+        <v>0.0702</v>
       </c>
       <c r="O61" s="7" t="n">
-        <v>0.1081</v>
+        <v>0.3617</v>
       </c>
       <c r="P61" s="7" t="n">
-        <v>-0.0257</v>
+        <v>0.0551</v>
       </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Sağlık hizmetleri</t>
         </is>
       </c>
       <c r="R61" s="5" t="inlineStr"/>
@@ -4029,57 +4031,55 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>KTLEV</t>
+          <t>BYDNR</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>4.45</v>
+        <v>17.6</v>
       </c>
       <c r="C62" s="4" t="n">
-        <v>-0.0992</v>
+        <v>-0.0445</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>-0.3288</v>
+        <v>-0.2043</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>-0.7533</v>
+        <v>-0.1776</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>-0.9112</v>
+        <v>-0.5485</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-0.8567</v>
+        <v>-0.5324</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>0.1576</v>
+        <v>-0.1244</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="J62" s="3" t="n">
-        <v>1.08</v>
-      </c>
+        <v>0.87</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="4" t="n">
-        <v>3.5578</v>
+        <v>0.2762</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>3.6471</v>
+        <v>0.0636</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>5.174600000000001</v>
+        <v>0.127</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>5.7649</v>
+        <v>0.7182999999999999</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>0.7222</v>
+        <v>0.1081</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>1.5072</v>
+        <v>-0.0257</v>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr"/>
@@ -4087,57 +4087,57 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>TNZTP</t>
+          <t>CWENE</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>22.94</v>
+        <v>14.64</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>-0.0112</v>
+        <v>-0.024</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>-0.09179999999999999</v>
+        <v>-0.1383</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-0.209</v>
+        <v>-0.4049</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>-0.0824</v>
+        <v>-0.6284000000000001</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>-0.07719999999999999</v>
+        <v>-0.5864</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>0.04269999999999999</v>
+        <v>-0.3288</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>16.97</v>
+        <v>5.44</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>0.4327</v>
+        <v>0.5809000000000001</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>0.4143</v>
+        <v>0.9067000000000001</v>
       </c>
       <c r="M63" s="7" t="n">
-        <v>0.5201</v>
+        <v>0.8432999999999999</v>
       </c>
       <c r="N63" s="7" t="n">
-        <v>0.0702</v>
+        <v>5.095899999999999</v>
       </c>
       <c r="O63" s="7" t="n">
-        <v>0.3617</v>
+        <v>0.1918</v>
       </c>
       <c r="P63" s="7" t="n">
-        <v>0.0551</v>
+        <v>0.2052</v>
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>Sağlık hizmetleri</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R63" s="5" t="inlineStr"/>
@@ -4145,57 +4145,57 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>CIMSA</t>
+          <t>ZRGYO</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>38.54</v>
+        <v>17.84</v>
       </c>
       <c r="C64" s="4" t="n">
-        <v>-0.0258</v>
+        <v>0.0194</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>-0.0432</v>
+        <v>-0.0611</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>-0.0704</v>
+        <v>-0.0766</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>-0.23</v>
+        <v>-0.0182</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-0.3155</v>
+        <v>-0.1817</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>-0.1099</v>
+        <v>-0.2</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>9.130000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0.3754999999999999</v>
+        <v>2.3363</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>0.3037</v>
+        <v>3.5944</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.4933</v>
+        <v>3.6478</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>1.15</v>
+        <v>0.2899</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>0.1807</v>
+        <v>0.5917</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>0.2729</v>
+        <v>0.0776</v>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr"/>
@@ -4203,57 +4203,57 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>MAALT</t>
+          <t>CIMSA</t>
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>649.5</v>
+        <v>37.44</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>-0.08130000000000001</v>
+        <v>-0.0285</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>-0.1592</v>
+        <v>-0.0522</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>-0.2859</v>
+        <v>-0.1211</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>-0.3814</v>
+        <v>-0.2519</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>-0.512</v>
+        <v>-0.335</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>-0.3569</v>
+        <v>-0.1261</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>1399.48</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>0.248</v>
+        <v>0.3754999999999999</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>3.5256</v>
+        <v>0.3037</v>
       </c>
       <c r="M65" s="7" t="n">
-        <v>0.3863</v>
+        <v>0.4933</v>
       </c>
       <c r="N65" s="7" t="n">
-        <v>0.9832</v>
+        <v>1.15</v>
       </c>
       <c r="O65" s="7" t="n">
-        <v>0.4575</v>
+        <v>0.1807</v>
       </c>
       <c r="P65" s="7" t="n">
-        <v>-0</v>
+        <v>0.2729</v>
       </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R65" s="5" t="inlineStr"/>
@@ -4265,31 +4265,31 @@
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>11.36</v>
+        <v>10.97</v>
       </c>
       <c r="C66" s="4" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0343</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>-0.0348</v>
+        <v>-0.0624</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.0955</v>
+        <v>0.0167</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>0.0299</v>
+        <v>-0.0054</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0.1568</v>
+        <v>0.1171</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>0.4362</v>
+        <v>0.3678</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>9.58</v>
+        <v>9.25</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>0.6297</v>
@@ -4319,53 +4319,53 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>CMENT</t>
+          <t>ISDMR</t>
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>215</v>
+        <v>52.25</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>-0.0005</v>
+        <v>-0.05429999999999999</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>-0.0106</v>
+        <v>-0.1335</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>0.0142</v>
+        <v>-0.1627</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>-0.2456</v>
+        <v>-0.07769999999999999</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>-0.3658</v>
+        <v>0.1601</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>-0.3831</v>
+        <v>0.4091</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>21.22</v>
+        <v>12.32</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>0.0934</v>
+        <v>0.1859</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>0.1109</v>
+        <v>0.3543</v>
       </c>
       <c r="M67" s="7" t="n">
-        <v>0.1008</v>
+        <v>0.4035</v>
       </c>
       <c r="N67" s="7" t="n">
-        <v>0.4922</v>
+        <v>0.208</v>
       </c>
       <c r="O67" s="7" t="n">
-        <v>0.1647</v>
+        <v>0.1056</v>
       </c>
       <c r="P67" s="7" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0859</v>
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
@@ -4377,57 +4377,57 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>ISDMR</t>
+          <t>MAALT</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>55.25</v>
+        <v>661</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>-0.0281</v>
+        <v>0.0177</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>-0.0935</v>
+        <v>-0.1504</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>-0.1153</v>
+        <v>-0.2792</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>-0.0247</v>
+        <v>-0.3705</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>0.2267</v>
+        <v>-0.5034000000000001</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>0.4741</v>
+        <v>-0.3475</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>13.03</v>
+        <v>1424.26</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0.1859</v>
+        <v>0.248</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>0.3543</v>
+        <v>3.5256</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>0.4035</v>
+        <v>0.3863</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.208</v>
+        <v>0.9832</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>0.1056</v>
+        <v>0.4575</v>
       </c>
       <c r="P68" s="4" t="n">
-        <v>0.0859</v>
+        <v>-0</v>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R68" s="2" t="inlineStr"/>
@@ -4435,55 +4435,57 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>OBASE</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>18.64</v>
+        <v>265</v>
       </c>
       <c r="C69" s="7" t="n">
-        <v>-0.0876</v>
+        <v>-0.0075</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>-0.1111</v>
+        <v>0</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>-0.3783</v>
+        <v>-0.0459</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>-0.5946</v>
+        <v>0.0222</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>-0.5156000000000001</v>
+        <v>-0.1389</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>-0.4714</v>
+        <v>0.09050000000000001</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J69" s="5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J69" s="6" t="n">
+        <v>11.45</v>
+      </c>
       <c r="K69" s="7" t="n">
-        <v>0.2041</v>
+        <v>0.2923</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>0.3021</v>
+        <v>0.3038</v>
       </c>
       <c r="M69" s="7" t="n">
-        <v>0.5156000000000001</v>
+        <v>0.325</v>
       </c>
       <c r="N69" s="7" t="n">
-        <v>0.4873</v>
+        <v>1.1251</v>
       </c>
       <c r="O69" s="7" t="n">
-        <v>0.2465</v>
+        <v>0.3086</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>0.1432</v>
+        <v>-0.3704</v>
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="R69" s="5" t="inlineStr"/>
@@ -4491,57 +4493,55 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>OBASE</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>10.12</v>
+        <v>18.03</v>
       </c>
       <c r="C70" s="4" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0332</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>-0.0059</v>
+        <v>-0.179</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>-0.05860000000000001</v>
+        <v>-0.377</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>-0.1574</v>
+        <v>-0.608</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>-0.0307</v>
+        <v>-0.5317000000000001</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>-0.165</v>
+        <v>-0.5047</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="J70" s="3" t="n">
-        <v>6.79</v>
-      </c>
+        <v>1.01</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="4" t="n">
-        <v>0.423</v>
+        <v>0.2041</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>0.5552</v>
+        <v>0.3021</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.8170999999999999</v>
+        <v>0.5156000000000001</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>10.0728</v>
+        <v>0.4873</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>0.179</v>
+        <v>0.2465</v>
       </c>
       <c r="P70" s="4" t="n">
-        <v>0.2236</v>
+        <v>0.1432</v>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R70" s="2" t="inlineStr"/>
@@ -4549,55 +4549,57 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>YKSLN</t>
+          <t>CMENT</t>
         </is>
       </c>
       <c r="B71" s="6" t="n">
-        <v>2.17</v>
+        <v>217.4</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>-0.0136</v>
+        <v>0.0112</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>-0.149</v>
+        <v>-0.0073</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>-0.2815</v>
+        <v>-0.0207</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>-0.3282</v>
+        <v>-0.2372</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>-0.3302</v>
+        <v>-0.3587</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>-0.3635</v>
+        <v>-0.3789</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="J71" s="5" t="inlineStr"/>
+        <v>1.02</v>
+      </c>
+      <c r="J71" s="6" t="n">
+        <v>21.46</v>
+      </c>
       <c r="K71" s="7" t="n">
-        <v>0.1126</v>
+        <v>0.0934</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>0.0263</v>
+        <v>0.1109</v>
       </c>
       <c r="M71" s="7" t="n">
-        <v>0.6127</v>
+        <v>0.1008</v>
       </c>
       <c r="N71" s="7" t="n">
-        <v>0.8754000000000001</v>
+        <v>0.4922</v>
       </c>
       <c r="O71" s="7" t="n">
-        <v>0.1443</v>
+        <v>0.1647</v>
       </c>
       <c r="P71" s="7" t="n">
-        <v>-0.04969999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R71" s="5" t="inlineStr"/>
@@ -4605,57 +4607,55 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>ENKAI</t>
+          <t>YKSLN</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>73.5</v>
+        <v>2.1</v>
       </c>
       <c r="C72" s="4" t="n">
-        <v>-0.0303</v>
+        <v>-0.0323</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>-0.0731</v>
+        <v>-0.25</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>-0.1488</v>
+        <v>-0.2527</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>-0.1865</v>
+        <v>-0.3497999999999999</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>-0.3112</v>
+        <v>-0.3519</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>0.0294</v>
+        <v>-0.3964</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="J72" s="3" t="n">
-        <v>11.04</v>
-      </c>
+        <v>1.04</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="4" t="n">
-        <v>0.4381</v>
+        <v>0.1126</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>0.1539</v>
+        <v>0.0263</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.1373</v>
+        <v>0.6127</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0.3376</v>
+        <v>0.8754000000000001</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>0.2166</v>
+        <v>0.1443</v>
       </c>
       <c r="P72" s="4" t="n">
-        <v>0.1059</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R72" s="2" t="inlineStr"/>
@@ -4663,53 +4663,53 @@
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>NTGAZ</t>
+          <t>AKSEN</t>
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>9.609999999999999</v>
+        <v>60.6</v>
       </c>
       <c r="C73" s="7" t="n">
-        <v>-0.0244</v>
+        <v>-0.08460000000000001</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>-0.0706</v>
+        <v>-0.1477</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-0.0925</v>
+        <v>-0.1312</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>-0.18</v>
+        <v>-0.4172999999999999</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>-0.2136</v>
+        <v>-0.2334</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>-0.0113</v>
+        <v>0.2567</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>6.11</v>
+        <v>22.3</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>0.3448</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>0.3645</v>
+        <v>0.3716</v>
       </c>
       <c r="M73" s="7" t="n">
-        <v>0.4084</v>
+        <v>0.4119</v>
       </c>
       <c r="N73" s="7" t="n">
-        <v>0.5755</v>
+        <v>0.9691</v>
       </c>
       <c r="O73" s="7" t="n">
-        <v>0.2148</v>
+        <v>0.3037</v>
       </c>
       <c r="P73" s="7" t="n">
-        <v>0.2137</v>
+        <v>0.0601</v>
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
@@ -4721,57 +4721,55 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SELEC</t>
+          <t>ISYAT</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>66.3</v>
+        <v>5.21</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>0.09949999999999999</v>
+        <v>-0.0629</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>-0.09119999999999999</v>
+        <v>-0.1691</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>-0.6159</v>
+        <v>-0.2557</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>-0.725</v>
+        <v>-0.3303</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>-0.265</v>
+        <v>-0.3783</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>-0.1929</v>
+        <v>-0.3677</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>20.21</v>
-      </c>
+        <v>1.09</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="4" t="n">
-        <v>0.3781</v>
+        <v>0.3952000000000001</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>0.6063000000000001</v>
+        <v>0.4088000000000001</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>1.4267</v>
+        <v>0.4094</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.7489</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>0.0158</v>
+        <v>0.7836</v>
       </c>
       <c r="P74" s="4" t="n">
-        <v>0.06559999999999999</v>
+        <v>-0.0106</v>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Çeşitli Hizmetler</t>
         </is>
       </c>
       <c r="R74" s="2" t="inlineStr"/>
@@ -4779,57 +4777,57 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>GLCVY</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="B75" s="6" t="n">
-        <v>34.32</v>
+        <v>74.5</v>
       </c>
       <c r="C75" s="7" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.0136</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>-0.0843</v>
+        <v>-0.0261</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>-0.2559</v>
+        <v>-0.1452</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>-0.3597</v>
+        <v>-0.1754</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>-0.4509</v>
+        <v>-0.3018</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>-0.4881</v>
+        <v>-0.0013</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>3.32</v>
+        <v>11.19</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>0.265</v>
+        <v>0.4381</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>0.2739</v>
+        <v>0.1539</v>
       </c>
       <c r="M75" s="7" t="n">
-        <v>0.2851</v>
+        <v>0.1373</v>
       </c>
       <c r="N75" s="7" t="n">
-        <v>0.0788</v>
+        <v>0.3376</v>
       </c>
       <c r="O75" s="7" t="n">
-        <v>0.7251000000000001</v>
+        <v>0.2166</v>
       </c>
       <c r="P75" s="7" t="n">
-        <v>0.4011</v>
+        <v>0.1059</v>
       </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R75" s="5" t="inlineStr"/>
@@ -4837,57 +4835,57 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>ISMEN</t>
+          <t>AKSA</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>27.16</v>
+        <v>10.3</v>
       </c>
       <c r="C76" s="4" t="n">
-        <v>-0.0286</v>
+        <v>0.0178</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.0239</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>-0.1931</v>
+        <v>-0.0559</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>-0.2497</v>
+        <v>-0.1424</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>-0.3751</v>
+        <v>-0.0134</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>-0.3376</v>
+        <v>-0.1619</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>6.07</v>
+        <v>6.91</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0.4021</v>
+        <v>0.423</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>0.2915</v>
+        <v>0.5552</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.201</v>
+        <v>0.8170999999999999</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>0.07690000000000001</v>
+        <v>10.0728</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>0.8484999999999999</v>
+        <v>0.179</v>
       </c>
       <c r="P76" s="4" t="n">
-        <v>0.298</v>
+        <v>0.2236</v>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R76" s="2" t="inlineStr"/>
@@ -4895,55 +4893,57 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>ISYAT</t>
+          <t>NTGAZ</t>
         </is>
       </c>
       <c r="B77" s="6" t="n">
-        <v>5.56</v>
+        <v>9.68</v>
       </c>
       <c r="C77" s="7" t="n">
-        <v>-0.05599999999999999</v>
+        <v>0.0073</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>-0.1272</v>
+        <v>-0.0463</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>-0.1907</v>
+        <v>-0.0919</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>-0.2853</v>
+        <v>-0.1741</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>-0.3365</v>
+        <v>-0.2079</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>-0.3269</v>
+        <v>-0.0378</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="J77" s="5" t="inlineStr"/>
+        <v>1.11</v>
+      </c>
+      <c r="J77" s="6" t="n">
+        <v>6.15</v>
+      </c>
       <c r="K77" s="7" t="n">
-        <v>0.3952000000000001</v>
+        <v>0.3448</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>0.4088000000000001</v>
+        <v>0.3645</v>
       </c>
       <c r="M77" s="7" t="n">
-        <v>0.4094</v>
+        <v>0.4084</v>
       </c>
       <c r="N77" s="7" t="n">
-        <v>0.7489</v>
+        <v>0.5755</v>
       </c>
       <c r="O77" s="7" t="n">
-        <v>0.7836</v>
+        <v>0.2148</v>
       </c>
       <c r="P77" s="7" t="n">
-        <v>-0.0106</v>
+        <v>0.2137</v>
       </c>
       <c r="Q77" s="5" t="inlineStr">
         <is>
-          <t>Çeşitli Hizmetler</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R77" s="5" t="inlineStr"/>
@@ -4951,57 +4951,57 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SARKY</t>
+          <t>ISMEN</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>15.64</v>
+        <v>26.24</v>
       </c>
       <c r="C78" s="4" t="n">
-        <v>-0.055</v>
+        <v>-0.0339</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>-0.143</v>
+        <v>-0.0964</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>-0.2949</v>
+        <v>-0.2214</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>-0.4008</v>
+        <v>-0.2751</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>-0.4366</v>
+        <v>-0.3962</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>0.06610000000000001</v>
+        <v>-0.3817</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>57.31</v>
+        <v>5.86</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0.5590999999999999</v>
+        <v>0.4021</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>0.3671</v>
+        <v>0.2915</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>0.2342</v>
+        <v>0.201</v>
       </c>
       <c r="N78" s="4" t="n">
-        <v>0.8034</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="O78" s="4" t="n">
-        <v>0.0217</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="P78" s="4" t="n">
-        <v>0.0229</v>
+        <v>0.298</v>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R78" s="2" t="inlineStr"/>
@@ -5009,55 +5009,57 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>KNFRT</t>
+          <t>KCAER</t>
         </is>
       </c>
       <c r="B79" s="6" t="n">
-        <v>7.04</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C79" s="7" t="n">
-        <v>-0.0486</v>
+        <v>-0.045</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>-0.2454</v>
+        <v>-0.1594</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>-0.3185</v>
+        <v>-0.2468</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>-0.4147999999999999</v>
+        <v>-0.4094</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>-0.4478</v>
+        <v>-0.2428</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>-0.4785</v>
+        <v>-0.3224</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="J79" s="5" t="inlineStr"/>
+        <v>1.12</v>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>25.33</v>
+      </c>
       <c r="K79" s="7" t="n">
-        <v>0.7798</v>
+        <v>0.1522</v>
       </c>
       <c r="L79" s="7" t="n">
-        <v>1.3764</v>
+        <v>0.2873</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>26.3063</v>
+        <v>0.3247</v>
       </c>
       <c r="N79" s="7" t="n">
-        <v>0.625</v>
+        <v>1.1982</v>
       </c>
       <c r="O79" s="7" t="n">
-        <v>0.0124</v>
+        <v>0.1199</v>
       </c>
       <c r="P79" s="7" t="n">
-        <v>-0.1091</v>
+        <v>0.0508</v>
       </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R79" s="5" t="inlineStr"/>
@@ -5065,55 +5067,55 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>KNFRT</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>73.7</v>
+        <v>6.8</v>
       </c>
       <c r="C80" s="4" t="n">
-        <v>-0.0867</v>
+        <v>-0.0341</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>-0.1329</v>
+        <v>-0.2609</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>-0.2032</v>
+        <v>-0.3807</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>-0.4282</v>
+        <v>-0.4347</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>-0.3879</v>
+        <v>-0.4667</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>-0.336</v>
+        <v>-0.4785</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="4" t="n">
-        <v>0.3957</v>
+        <v>0.7798</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>2.0344</v>
+        <v>1.3764</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>3.8494</v>
+        <v>26.3063</v>
       </c>
       <c r="N80" s="4" t="n">
-        <v>0.889</v>
+        <v>0.625</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>0.0349</v>
+        <v>0.0124</v>
       </c>
       <c r="P80" s="4" t="n">
-        <v>-0.0175</v>
+        <v>-0.1091</v>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R80" s="2" t="inlineStr"/>
@@ -5121,57 +5123,57 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>KCAER</t>
+          <t>GLCVY</t>
         </is>
       </c>
       <c r="B81" s="6" t="n">
-        <v>9.109999999999999</v>
+        <v>33.64</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>-0.0288</v>
+        <v>-0.0198</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>-0.1478</v>
+        <v>-0.1096</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>-0.165</v>
+        <v>-0.2775</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>-0.3815</v>
+        <v>-0.3724</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>-0.2071</v>
+        <v>-0.4618</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>-0.277</v>
+        <v>-0.4903</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>26.53</v>
+        <v>3.26</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>0.1522</v>
+        <v>0.265</v>
       </c>
       <c r="L81" s="7" t="n">
-        <v>0.2873</v>
+        <v>0.2739</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>0.3247</v>
+        <v>0.2851</v>
       </c>
       <c r="N81" s="7" t="n">
-        <v>1.1982</v>
+        <v>0.0788</v>
       </c>
       <c r="O81" s="7" t="n">
-        <v>0.1199</v>
+        <v>0.7251000000000001</v>
       </c>
       <c r="P81" s="7" t="n">
-        <v>0.0508</v>
+        <v>0.4011</v>
       </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R81" s="5" t="inlineStr"/>
@@ -5183,28 +5185,28 @@
         </is>
       </c>
       <c r="B82" s="3" t="n">
-        <v>5.42</v>
+        <v>5.27</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>0</v>
+        <v>-0.0277</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>-0.08449999999999999</v>
+        <v>-0.1128</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>-0.0073</v>
+        <v>-0.09140000000000001</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>-0.4407</v>
+        <v>-0.4561</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>-0.17</v>
+        <v>-0.193</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>-0.3524</v>
+        <v>-0.3494</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="4" t="n">
@@ -5235,53 +5237,53 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>GEDIK</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="B83" s="6" t="n">
-        <v>4.7</v>
+        <v>10.25</v>
       </c>
       <c r="C83" s="7" t="n">
-        <v>-0.0167</v>
+        <v>-0.0993</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>-0.0309</v>
+        <v>-0.3417</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>-0.1264</v>
+        <v>-0.166</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>-0.2943</v>
+        <v>-0.7691</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>-0.1993</v>
+        <v>-0.6601</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>-0.3588</v>
+        <v>-0.1087</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>4.97</v>
+        <v>1.32</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>0.6583</v>
+        <v>2.1748</v>
       </c>
       <c r="L83" s="7" t="n">
-        <v>0.6568000000000001</v>
+        <v>2.2285</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>0.7293999999999999</v>
+        <v>2.5519</v>
       </c>
       <c r="N83" s="7" t="n">
-        <v>0.3481</v>
+        <v>7.8348</v>
       </c>
       <c r="O83" s="7" t="n">
-        <v>0.6628000000000001</v>
+        <v>0.887</v>
       </c>
       <c r="P83" s="7" t="n">
-        <v>0.275</v>
+        <v>1.1538</v>
       </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
@@ -5293,57 +5295,57 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>GEDIK</t>
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>267</v>
+        <v>4.66</v>
       </c>
       <c r="C84" s="4" t="n">
-        <v>-0.0697</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>-0.0102</v>
+        <v>-0.0231</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>-0.0335</v>
+        <v>-0.1073</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>0.0299</v>
+        <v>-0.3003</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>-0.1324</v>
+        <v>-0.2061</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>0.1314</v>
+        <v>-0.3711</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>18.39</v>
+        <v>4.93</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0.3707</v>
+        <v>0.6583</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>0.4185</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>0.4202</v>
+        <v>0.7293999999999999</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>1.8941</v>
+        <v>0.3481</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>0.3086</v>
+        <v>0.6628000000000001</v>
       </c>
       <c r="P84" s="4" t="n">
-        <v>-0.1688</v>
+        <v>0.275</v>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R84" s="2" t="inlineStr"/>
@@ -5351,57 +5353,55 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>AKSEN</t>
+          <t>ACSEL</t>
         </is>
       </c>
       <c r="B85" s="6" t="n">
-        <v>66.2</v>
+        <v>74.5</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>-0.0413</v>
+        <v>0.0109</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>-0.0806</v>
+        <v>-0.1147</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-0.0134</v>
+        <v>-0.2058</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>-0.3635</v>
+        <v>-0.422</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>-0.1626</v>
+        <v>-0.3812</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>0.3734</v>
+        <v>-0.3258</v>
       </c>
       <c r="I85" s="6" t="n">
         <v>1.18</v>
       </c>
-      <c r="J85" s="6" t="n">
-        <v>24.37</v>
-      </c>
+      <c r="J85" s="5" t="inlineStr"/>
       <c r="K85" s="7" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.3957</v>
       </c>
       <c r="L85" s="7" t="n">
-        <v>0.3716</v>
+        <v>2.0344</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>0.4119</v>
+        <v>3.8494</v>
       </c>
       <c r="N85" s="7" t="n">
-        <v>0.9691</v>
+        <v>0.889</v>
       </c>
       <c r="O85" s="7" t="n">
-        <v>0.3037</v>
+        <v>0.0349</v>
       </c>
       <c r="P85" s="7" t="n">
-        <v>0.0601</v>
+        <v>-0.0175</v>
       </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R85" s="5" t="inlineStr"/>
@@ -5409,57 +5409,57 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GARFA</t>
+          <t>SARKY</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>20.62</v>
+        <v>16</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>-0.0337</v>
+        <v>0.023</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>-0.06269999999999999</v>
+        <v>-0.118</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>-0.1528</v>
+        <v>-0.2767</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>-0.2672</v>
+        <v>-0.387</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>-0.2739</v>
+        <v>-0.4236</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>-0.1563</v>
+        <v>0.1173</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>3.12</v>
+        <v>58.63</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0.9562999999999999</v>
+        <v>0.5590999999999999</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>0.9506</v>
+        <v>0.3671</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.2342</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>0.5365</v>
+        <v>0.8034</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>0.914</v>
+        <v>0.0217</v>
       </c>
       <c r="P86" s="4" t="n">
-        <v>0.496</v>
+        <v>0.0229</v>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr"/>
@@ -5467,55 +5467,57 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>OZYSR</t>
+          <t>GARFA</t>
         </is>
       </c>
       <c r="B87" s="6" t="n">
-        <v>10.58</v>
+        <v>20.68</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>-0.08789999999999999</v>
+        <v>0.0029</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>-0.09029999999999999</v>
+        <v>-0.0452</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>-0.0294</v>
+        <v>-0.1661</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>-0.1887</v>
+        <v>-0.2651</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>-0.1079</v>
+        <v>-0.2718</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>0.3347</v>
+        <v>-0.1532</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="J87" s="5" t="inlineStr"/>
+        <v>1.22</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>3.13</v>
+      </c>
       <c r="K87" s="7" t="n">
-        <v>0.161</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="L87" s="7" t="n">
-        <v>0.1742</v>
+        <v>0.9506</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>0.6839</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="N87" s="7" t="n">
-        <v>0.5105</v>
+        <v>0.5365</v>
       </c>
       <c r="O87" s="7" t="n">
-        <v>0.042</v>
+        <v>0.914</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>-0.0335</v>
+        <v>0.496</v>
       </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R87" s="5" t="inlineStr"/>
@@ -5523,57 +5525,57 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>PCILT</t>
+          <t>SELEC</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>28.04</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="C88" s="4" t="n">
-        <v>-0.0331</v>
+        <v>0.09949999999999999</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>-0.08070000000000001</v>
+        <v>0.0414</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>-0.0463</v>
+        <v>-0.5309</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>-0.1849</v>
+        <v>-0.6976</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>0.051</v>
+        <v>-0.1918</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>0.4379</v>
+        <v>-0.1039</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>6.44</v>
+        <v>22.22</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0.763</v>
+        <v>0.3781</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>0.7087</v>
+        <v>0.6063000000000001</v>
       </c>
       <c r="M88" s="4" t="n">
-        <v>0.7914</v>
+        <v>1.4267</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>1.2232</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>0.0574</v>
+        <v>0.0158</v>
       </c>
       <c r="P88" s="4" t="n">
-        <v>0.2831</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="R88" s="2" t="inlineStr"/>
@@ -5581,57 +5583,57 @@
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>PCILT</t>
         </is>
       </c>
       <c r="B89" s="6" t="n">
-        <v>11.38</v>
+        <v>27.06</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.035</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>-0.2518</v>
+        <v>-0.1293</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>-0.1663</v>
+        <v>-0.1293</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>-0.7437</v>
+        <v>-0.2134</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>-0.6227</v>
+        <v>0.0142</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>0.0252</v>
+        <v>0.3743</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>1.47</v>
+        <v>6.22</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>2.1748</v>
+        <v>0.763</v>
       </c>
       <c r="L89" s="7" t="n">
-        <v>2.2285</v>
+        <v>0.7087</v>
       </c>
       <c r="M89" s="7" t="n">
-        <v>2.5519</v>
+        <v>0.7914</v>
       </c>
       <c r="N89" s="7" t="n">
-        <v>7.8348</v>
+        <v>1.2232</v>
       </c>
       <c r="O89" s="7" t="n">
-        <v>0.887</v>
+        <v>0.0574</v>
       </c>
       <c r="P89" s="7" t="n">
-        <v>1.1538</v>
+        <v>0.2831</v>
       </c>
       <c r="Q89" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R89" s="5" t="inlineStr"/>
@@ -5643,31 +5645,31 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>23.82</v>
+        <v>23.34</v>
       </c>
       <c r="C90" s="4" t="n">
-        <v>-0.0348</v>
+        <v>-0.0202</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>-0.1204</v>
+        <v>-0.1356</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>-0.2847</v>
+        <v>-0.3183</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>-0.4945000000000001</v>
+        <v>-0.5047</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>-0.3954</v>
+        <v>-0.4076</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>-0.4274</v>
+        <v>-0.436</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>28.54</v>
+        <v>27.97</v>
       </c>
       <c r="K90" s="4" t="n">
         <v>0.05019999999999999</v>
@@ -5697,57 +5699,55 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>GENIL</t>
+          <t>OZYSR</t>
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>4.02</v>
+        <v>11.5</v>
       </c>
       <c r="C91" s="7" t="n">
-        <v>-0.036</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>-0.204</v>
+        <v>0.0132</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>-0.3927</v>
+        <v>0.025</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>-0.5700999999999999</v>
+        <v>-0.1181</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>-0.5834</v>
+        <v>-0.0304</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>-0.6846</v>
+        <v>0.4463</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="J91" s="6" t="n">
-        <v>14.66</v>
-      </c>
+        <v>1.34</v>
+      </c>
+      <c r="J91" s="5" t="inlineStr"/>
       <c r="K91" s="7" t="n">
-        <v>0.5049</v>
+        <v>0.161</v>
       </c>
       <c r="L91" s="7" t="n">
-        <v>0.7672</v>
+        <v>0.1742</v>
       </c>
       <c r="M91" s="7" t="n">
-        <v>1.1622</v>
+        <v>0.6839</v>
       </c>
       <c r="N91" s="7" t="n">
-        <v>1.2274</v>
+        <v>0.5105</v>
       </c>
       <c r="O91" s="7" t="n">
-        <v>0.0922</v>
+        <v>0.042</v>
       </c>
       <c r="P91" s="7" t="n">
-        <v>0.1305</v>
+        <v>-0.0335</v>
       </c>
       <c r="Q91" s="5" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R91" s="5" t="inlineStr"/>
@@ -5759,31 +5759,31 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>27.3</v>
+        <v>26.52</v>
       </c>
       <c r="C92" s="4" t="n">
-        <v>-0.0257</v>
+        <v>-0.0286</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>-0.13</v>
+        <v>-0.116</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>-0.1942</v>
+        <v>-0.2349</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>-0.2222</v>
+        <v>-0.2444</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>-0.3695000000000001</v>
+        <v>-0.3875</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>0.0428</v>
+        <v>0.0279</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>9.720000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="K92" s="4" t="n">
         <v>0.3776</v>
@@ -5813,57 +5813,57 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>ORGE</t>
+          <t>GENIL</t>
         </is>
       </c>
       <c r="B93" s="6" t="n">
-        <v>18.8</v>
+        <v>4</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>-0.0605</v>
+        <v>-0.005</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>-0.1686</v>
+        <v>-0.2157</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>-0.1582</v>
+        <v>-0.4652000000000001</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>-0.1325</v>
+        <v>-0.5722</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>0.1319</v>
+        <v>-0.5855</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>0.3981</v>
+        <v>-0.6801999999999999</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>8.720000000000001</v>
+        <v>14.58</v>
       </c>
       <c r="K93" s="7" t="n">
-        <v>0.251</v>
+        <v>0.5049</v>
       </c>
       <c r="L93" s="7" t="n">
-        <v>0.257</v>
+        <v>0.7672</v>
       </c>
       <c r="M93" s="7" t="n">
-        <v>0.2421</v>
+        <v>1.1622</v>
       </c>
       <c r="N93" s="7" t="n">
-        <v>0.2676</v>
+        <v>1.2274</v>
       </c>
       <c r="O93" s="7" t="n">
-        <v>0.4943</v>
+        <v>0.0922</v>
       </c>
       <c r="P93" s="7" t="n">
-        <v>0.2029</v>
+        <v>0.1305</v>
       </c>
       <c r="Q93" s="5" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R93" s="5" t="inlineStr"/>
@@ -5871,57 +5871,55 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>MEGMT</t>
+          <t>KRPLS</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>2.9</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="C94" s="4" t="n">
-        <v>-0.0333</v>
+        <v>-0.0658</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>-0.1471</v>
+        <v>-0.2391</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>-0.1808</v>
+        <v>-0.2877</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>-0.637</v>
+        <v>-0.1143</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>-0.6431</v>
+        <v>-0.0751</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>-0.1845</v>
+        <v>-0.0423</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="J94" s="3" t="n">
-        <v>6.19</v>
-      </c>
+        <v>1.38</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="4" t="n">
-        <v>0.51</v>
+        <v>0.3576</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>0.4203</v>
+        <v>0.6872</v>
       </c>
       <c r="M94" s="4" t="n">
-        <v>0.8453000000000001</v>
+        <v>0.9115000000000001</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>0.2482</v>
+        <v>0.7781999999999999</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>0.0483</v>
+        <v>0.166</v>
       </c>
       <c r="P94" s="4" t="n">
-        <v>0.2852</v>
+        <v>-0.0342</v>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R94" s="2" t="inlineStr"/>
@@ -5929,57 +5927,57 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>DERIM</t>
+          <t>ORGE</t>
         </is>
       </c>
       <c r="B95" s="6" t="n">
-        <v>19.62</v>
+        <v>18.37</v>
       </c>
       <c r="C95" s="7" t="n">
-        <v>-0.0675</v>
+        <v>-0.0224</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>-0.1665</v>
+        <v>-0.1597</v>
       </c>
       <c r="E95" s="7" t="n">
-        <v>-0.3381</v>
+        <v>-0.1943</v>
       </c>
       <c r="F95" s="7" t="n">
-        <v>-0.4529</v>
+        <v>-0.1519</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>-0.5203</v>
+        <v>0.1066</v>
       </c>
       <c r="H95" s="7" t="n">
-        <v>-0.4668</v>
+        <v>0.374</v>
       </c>
       <c r="I95" s="6" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>10.81</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="K95" s="7" t="n">
-        <v>0.1436</v>
+        <v>0.251</v>
       </c>
       <c r="L95" s="7" t="n">
-        <v>0.2539</v>
+        <v>0.257</v>
       </c>
       <c r="M95" s="7" t="n">
-        <v>0.0263</v>
+        <v>0.2421</v>
       </c>
       <c r="N95" s="7" t="n">
-        <v>0.0576</v>
+        <v>0.2676</v>
       </c>
       <c r="O95" s="7" t="n">
-        <v>0.0602</v>
+        <v>0.4943</v>
       </c>
       <c r="P95" s="7" t="n">
-        <v>0.1637</v>
+        <v>0.2029</v>
       </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="R95" s="5" t="inlineStr"/>
@@ -5987,51 +5985,53 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>KRPLS</t>
+          <t>DERIM</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>8.960000000000001</v>
+        <v>19.02</v>
       </c>
       <c r="C96" s="4" t="n">
-        <v>-0.005500000000000001</v>
+        <v>-0.0306</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>-0.178</v>
+        <v>-0.2173</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>-0.2283</v>
+        <v>-0.3491</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>-0.0519</v>
+        <v>-0.4696</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>-0.009899999999999999</v>
+        <v>-0.535</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>-0.0261</v>
+        <v>-0.4837</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr"/>
+        <v>1.42</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>10.48</v>
+      </c>
       <c r="K96" s="4" t="n">
-        <v>0.3576</v>
+        <v>0.1436</v>
       </c>
       <c r="L96" s="4" t="n">
-        <v>0.6872</v>
+        <v>0.2539</v>
       </c>
       <c r="M96" s="4" t="n">
-        <v>0.9115000000000001</v>
+        <v>0.0263</v>
       </c>
       <c r="N96" s="4" t="n">
-        <v>0.7781999999999999</v>
+        <v>0.0576</v>
       </c>
       <c r="O96" s="4" t="n">
-        <v>0.166</v>
+        <v>0.0602</v>
       </c>
       <c r="P96" s="4" t="n">
-        <v>-0.0342</v>
+        <v>0.1637</v>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
@@ -6043,57 +6043,57 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>TUPRS</t>
+          <t>MEGMT</t>
         </is>
       </c>
       <c r="B97" s="6" t="n">
-        <v>352.25</v>
+        <v>2.87</v>
       </c>
       <c r="C97" s="7" t="n">
-        <v>-0.0195</v>
+        <v>-0.0103</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>-0.09210000000000002</v>
+        <v>-0.1223</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>-0.1507</v>
+        <v>-0.1223</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>0.1254</v>
+        <v>-0.6408</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>0.3242</v>
+        <v>-0.6468</v>
       </c>
       <c r="H97" s="7" t="n">
-        <v>0.9845</v>
+        <v>-0.2078</v>
       </c>
       <c r="I97" s="6" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="J97" s="6" t="n">
-        <v>9.77</v>
+        <v>6.13</v>
       </c>
       <c r="K97" s="7" t="n">
-        <v>0.465</v>
+        <v>0.51</v>
       </c>
       <c r="L97" s="7" t="n">
-        <v>1.0453</v>
+        <v>0.4203</v>
       </c>
       <c r="M97" s="7" t="n">
-        <v>1.1002</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="N97" s="7" t="n">
-        <v>2.2351</v>
+        <v>0.2482</v>
       </c>
       <c r="O97" s="7" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0483</v>
       </c>
       <c r="P97" s="7" t="n">
-        <v>0.187</v>
+        <v>0.2852</v>
       </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
-          <t>Enerji mineralleri</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R97" s="5" t="inlineStr"/>
@@ -6105,31 +6105,31 @@
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>3.52</v>
+        <v>3.39</v>
       </c>
       <c r="C98" s="4" t="n">
-        <v>-0.0303</v>
+        <v>-0.0369</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>-0.1373</v>
+        <v>-0.1525</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>-0.1373</v>
+        <v>-0.2079</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>-0.3408</v>
+        <v>-0.3652</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>-0.2903</v>
+        <v>-0.3165</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>0.1617</v>
+        <v>0.2064</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>11.44</v>
+        <v>11.01</v>
       </c>
       <c r="K98" s="4" t="n">
         <v>1.0251</v>
@@ -6159,57 +6159,57 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>ENERY</t>
+          <t>TUPRS</t>
         </is>
       </c>
       <c r="B99" s="6" t="n">
-        <v>12.12</v>
+        <v>360.75</v>
       </c>
       <c r="C99" s="7" t="n">
-        <v>-0.0524</v>
+        <v>0.0241</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>-0.1386</v>
+        <v>-0.0525</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>0.01</v>
+        <v>-0.08380000000000001</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>0.2704</v>
+        <v>0.1526</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>0.3275</v>
+        <v>0.3562</v>
       </c>
       <c r="H99" s="7" t="n">
-        <v>0.3089</v>
+        <v>0.98</v>
       </c>
       <c r="I99" s="6" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>19.33</v>
+        <v>10.01</v>
       </c>
       <c r="K99" s="7" t="n">
-        <v>0.4279</v>
+        <v>0.465</v>
       </c>
       <c r="L99" s="7" t="n">
-        <v>0.7162999999999999</v>
+        <v>1.0453</v>
       </c>
       <c r="M99" s="7" t="n">
-        <v>0.8373999999999999</v>
+        <v>1.1002</v>
       </c>
       <c r="N99" s="7" t="n">
-        <v>0.6103000000000001</v>
+        <v>2.2351</v>
       </c>
       <c r="O99" s="7" t="n">
-        <v>0.2099</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="P99" s="7" t="n">
-        <v>0.1017</v>
+        <v>0.187</v>
       </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Enerji mineralleri</t>
         </is>
       </c>
       <c r="R99" s="5" t="inlineStr"/>
@@ -6221,31 +6221,31 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>32.82</v>
+        <v>31.58</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>-0.0481</v>
+        <v>-0.0378</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>-0.1363</v>
+        <v>-0.1579</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>-0.2739</v>
+        <v>-0.336</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>-0.3343</v>
+        <v>-0.3594</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>-0.249</v>
+        <v>-0.2773</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>-0.3772</v>
+        <v>-0.3939</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>13.08</v>
+        <v>12.59</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>0.486</v>
@@ -6275,57 +6275,57 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>SANEL</t>
+          <t>ENERY</t>
         </is>
       </c>
       <c r="B101" s="6" t="n">
-        <v>23.42</v>
+        <v>12.25</v>
       </c>
       <c r="C101" s="7" t="n">
-        <v>-0.016</v>
+        <v>0.0107</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>-0.1857</v>
+        <v>-0.1511</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>-0.3674</v>
+        <v>-0.03240000000000001</v>
       </c>
       <c r="F101" s="7" t="n">
-        <v>-0.7034999999999999</v>
+        <v>0.2841</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>-0.3335</v>
+        <v>0.3417</v>
       </c>
       <c r="H101" s="7" t="n">
-        <v>-0.1182</v>
+        <v>0.3272</v>
       </c>
       <c r="I101" s="6" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>2.26</v>
+        <v>19.53</v>
       </c>
       <c r="K101" s="7" t="n">
-        <v>0.309</v>
+        <v>0.4279</v>
       </c>
       <c r="L101" s="7" t="n">
-        <v>1.4614</v>
+        <v>0.7162999999999999</v>
       </c>
       <c r="M101" s="7" t="n">
-        <v>1.5381</v>
+        <v>0.8373999999999999</v>
       </c>
       <c r="N101" s="7" t="n">
-        <v>2.2148</v>
+        <v>0.6103000000000001</v>
       </c>
       <c r="O101" s="7" t="n">
-        <v>0.1491</v>
+        <v>0.2099</v>
       </c>
       <c r="P101" s="7" t="n">
-        <v>1.0947</v>
+        <v>0.1017</v>
       </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R101" s="5" t="inlineStr"/>
@@ -6333,57 +6333,57 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SAFKR</t>
+          <t>MPARK</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>11.4</v>
+        <v>387</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>0.0106</v>
+        <v>-0.0196</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>-0.0492</v>
+        <v>-0.0873</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>0.044</v>
+        <v>-0.1179</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>-0.4105</v>
+        <v>-0.0607</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>-0.5468999999999999</v>
+        <v>-0.1641</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>-0.4406</v>
+        <v>0.1853</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>16.58</v>
+        <v>12.09</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0.7861</v>
+        <v>0.3601</v>
       </c>
       <c r="L102" s="4" t="n">
-        <v>0.4555</v>
+        <v>0.3635</v>
       </c>
       <c r="M102" s="4" t="n">
-        <v>0.3309</v>
+        <v>0.5899</v>
       </c>
       <c r="N102" s="4" t="n">
-        <v>0.5716</v>
+        <v>0.1175</v>
       </c>
       <c r="O102" s="4" t="n">
-        <v>0.2109</v>
+        <v>0.2737</v>
       </c>
       <c r="P102" s="4" t="n">
-        <v>0.1216</v>
+        <v>0.2987</v>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Sağlık hizmetleri</t>
         </is>
       </c>
       <c r="R102" s="2" t="inlineStr"/>
@@ -6395,31 +6395,31 @@
         </is>
       </c>
       <c r="B103" s="6" t="n">
-        <v>223.7</v>
+        <v>222.6</v>
       </c>
       <c r="C103" s="7" t="n">
-        <v>-0.0184</v>
+        <v>-0.0049</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>-0.1016</v>
+        <v>-0.0725</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>-0.2233</v>
+        <v>-0.2155</v>
       </c>
       <c r="F103" s="7" t="n">
-        <v>-0.2192</v>
+        <v>-0.223</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>-0.2372</v>
+        <v>-0.2409</v>
       </c>
       <c r="H103" s="7" t="n">
-        <v>-0.1236</v>
+        <v>-0.1438</v>
       </c>
       <c r="I103" s="6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="K103" s="7" t="n">
         <v>1.7224</v>
@@ -6449,57 +6449,55 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>DURDO</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>394.75</v>
+        <v>6.01</v>
       </c>
       <c r="C104" s="4" t="n">
-        <v>-0.0186</v>
+        <v>0.0186</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>-0.0755</v>
+        <v>0.0581</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>-0.1013</v>
+        <v>0.2787</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>-0.04190000000000001</v>
+        <v>0.1276</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>-0.1474</v>
+        <v>0.2869</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>0.2109</v>
+        <v>0.7025</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="J104" s="3" t="n">
-        <v>12.33</v>
-      </c>
+        <v>1.78</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="4" t="n">
-        <v>0.3601</v>
+        <v>0.3099</v>
       </c>
       <c r="L104" s="4" t="n">
-        <v>0.3635</v>
+        <v>0.2862</v>
       </c>
       <c r="M104" s="4" t="n">
-        <v>0.5899</v>
+        <v>0.3279</v>
       </c>
       <c r="N104" s="4" t="n">
-        <v>0.1175</v>
+        <v>0.1519</v>
       </c>
       <c r="O104" s="4" t="n">
-        <v>0.2737</v>
+        <v>0.0876</v>
       </c>
       <c r="P104" s="4" t="n">
-        <v>0.2987</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>Sağlık hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R104" s="2" t="inlineStr"/>
@@ -6507,55 +6505,57 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>DURDO</t>
+          <t>GLYHO</t>
         </is>
       </c>
       <c r="B105" s="6" t="n">
-        <v>5.9</v>
+        <v>15.46</v>
       </c>
       <c r="C105" s="7" t="n">
-        <v>-0.015</v>
+        <v>-0.0319</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>-0.1667</v>
+        <v>-0.0857</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>0.4532</v>
+        <v>-0.0277</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>0.1069</v>
+        <v>-0.1186</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>0.2634</v>
+        <v>-0.0215</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>0.7101000000000001</v>
+        <v>0.417</v>
       </c>
       <c r="I105" s="6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J105" s="5" t="inlineStr"/>
+        <v>1.78</v>
+      </c>
+      <c r="J105" s="6" t="n">
+        <v>5.16</v>
+      </c>
       <c r="K105" s="7" t="n">
-        <v>0.3099</v>
+        <v>0.2312</v>
       </c>
       <c r="L105" s="7" t="n">
-        <v>0.2862</v>
+        <v>0.317</v>
       </c>
       <c r="M105" s="7" t="n">
-        <v>0.3279</v>
+        <v>0.3503</v>
       </c>
       <c r="N105" s="7" t="n">
-        <v>0.1519</v>
+        <v>0.4888</v>
       </c>
       <c r="O105" s="7" t="n">
-        <v>0.0876</v>
+        <v>0.3457</v>
       </c>
       <c r="P105" s="7" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.2226</v>
       </c>
       <c r="Q105" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R105" s="5" t="inlineStr"/>
@@ -6563,57 +6563,57 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>AHGAZ</t>
+          <t>SANEL</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>42.72</v>
+        <v>25.76</v>
       </c>
       <c r="C106" s="4" t="n">
-        <v>-0.0335</v>
+        <v>0.0999</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>-0.09449999999999999</v>
+        <v>-0.064</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>0.0269</v>
+        <v>-0.3652</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>0.1711</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>0.5535</v>
+        <v>-0.2669</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>0.7240000000000001</v>
+        <v>-0.0388</v>
       </c>
       <c r="I106" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>20.22</v>
+        <v>2.48</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0.659</v>
+        <v>0.309</v>
       </c>
       <c r="L106" s="4" t="n">
-        <v>1.7979</v>
+        <v>1.4614</v>
       </c>
       <c r="M106" s="4" t="n">
-        <v>2.1313</v>
+        <v>1.5381</v>
       </c>
       <c r="N106" s="4" t="n">
-        <v>2.8917</v>
+        <v>2.2148</v>
       </c>
       <c r="O106" s="4" t="n">
-        <v>0.1977</v>
+        <v>0.1491</v>
       </c>
       <c r="P106" s="4" t="n">
-        <v>0.1152</v>
+        <v>1.0947</v>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R106" s="2" t="inlineStr"/>
@@ -6621,57 +6621,57 @@
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>GLYHO</t>
+          <t>SAFKR</t>
         </is>
       </c>
       <c r="B107" s="6" t="n">
-        <v>15.97</v>
+        <v>12.54</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>-0.0437</v>
+        <v>0.1</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>-0.09619999999999999</v>
+        <v>0.06269999999999999</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>0.0237</v>
+        <v>0.1157</v>
       </c>
       <c r="F107" s="7" t="n">
-        <v>-0.0895</v>
+        <v>-0.3516</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>0.0108</v>
+        <v>-0.5015999999999999</v>
       </c>
       <c r="H107" s="7" t="n">
-        <v>0.5341</v>
+        <v>-0.409</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="J107" s="6" t="n">
-        <v>5.33</v>
+        <v>18.24</v>
       </c>
       <c r="K107" s="7" t="n">
-        <v>0.2312</v>
+        <v>0.7861</v>
       </c>
       <c r="L107" s="7" t="n">
-        <v>0.317</v>
+        <v>0.4555</v>
       </c>
       <c r="M107" s="7" t="n">
-        <v>0.3503</v>
+        <v>0.3309</v>
       </c>
       <c r="N107" s="7" t="n">
-        <v>0.4888</v>
+        <v>0.5716</v>
       </c>
       <c r="O107" s="7" t="n">
-        <v>0.3457</v>
+        <v>0.2109</v>
       </c>
       <c r="P107" s="7" t="n">
-        <v>-0.2226</v>
+        <v>0.1216</v>
       </c>
       <c r="Q107" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R107" s="5" t="inlineStr"/>
@@ -6679,53 +6679,53 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>TABGD</t>
+          <t>GRSEL</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>191.3</v>
+        <v>247</v>
       </c>
       <c r="C108" s="4" t="n">
-        <v>-0.024</v>
+        <v>-0.0352</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>-0.08470000000000001</v>
+        <v>-0.1438</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>-0.1591</v>
+        <v>-0.1155</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>-0.179</v>
+        <v>-0.2233</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>-0.2628</v>
+        <v>-0.1828</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>-0.2131</v>
+        <v>-0.2778</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>17.88</v>
+        <v>7.5</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0.493</v>
+        <v>0.3337</v>
       </c>
       <c r="L108" s="4" t="n">
-        <v>0.3835</v>
+        <v>0.6940999999999999</v>
       </c>
       <c r="M108" s="4" t="n">
-        <v>0.4282</v>
+        <v>0.2722</v>
       </c>
       <c r="N108" s="4" t="n">
-        <v>0.1825</v>
+        <v>0.7318000000000001</v>
       </c>
       <c r="O108" s="4" t="n">
-        <v>0.2029</v>
+        <v>0.3275</v>
       </c>
       <c r="P108" s="4" t="n">
-        <v>0.1296</v>
+        <v>0.3613</v>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
@@ -6737,57 +6737,57 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>GRSEL</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B109" s="6" t="n">
-        <v>256</v>
+        <v>36.18</v>
       </c>
       <c r="C109" s="7" t="n">
-        <v>-0.0248</v>
+        <v>-0.0383</v>
       </c>
       <c r="D109" s="7" t="n">
-        <v>-0.1018</v>
+        <v>-0.2135</v>
       </c>
       <c r="E109" s="7" t="n">
-        <v>-0.0623</v>
+        <v>-0.473</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>-0.195</v>
+        <v>-0.6327</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>-0.153</v>
+        <v>-0.1154</v>
       </c>
       <c r="H109" s="7" t="n">
-        <v>-0.2364</v>
+        <v>0.3883</v>
       </c>
       <c r="I109" s="6" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="J109" s="6" t="n">
-        <v>7.78</v>
+        <v>25.65</v>
       </c>
       <c r="K109" s="7" t="n">
-        <v>0.3337</v>
+        <v>0.8139</v>
       </c>
       <c r="L109" s="7" t="n">
-        <v>0.6940999999999999</v>
+        <v>1.3529</v>
       </c>
       <c r="M109" s="7" t="n">
-        <v>0.2722</v>
+        <v>2.0375</v>
       </c>
       <c r="N109" s="7" t="n">
-        <v>0.7318000000000001</v>
+        <v>1.6152</v>
       </c>
       <c r="O109" s="7" t="n">
-        <v>0.3275</v>
+        <v>0.1821</v>
       </c>
       <c r="P109" s="7" t="n">
-        <v>0.3613</v>
+        <v>0.09230000000000001</v>
       </c>
       <c r="Q109" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R109" s="5" t="inlineStr"/>
@@ -6795,57 +6795,57 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>AHGAZ</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>37.62</v>
+        <v>43.8</v>
       </c>
       <c r="C110" s="4" t="n">
-        <v>-0.0369</v>
+        <v>0.0253</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>-0.1804</v>
+        <v>-0.0848</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>-0.3807</v>
+        <v>-0.004500000000000001</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>-0.6181</v>
+        <v>0.2007</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.5927</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>0.4381</v>
+        <v>0.7562000000000001</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>26.67</v>
+        <v>20.73</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0.8139</v>
+        <v>0.659</v>
       </c>
       <c r="L110" s="4" t="n">
-        <v>1.3529</v>
+        <v>1.7979</v>
       </c>
       <c r="M110" s="4" t="n">
-        <v>2.0375</v>
+        <v>2.1313</v>
       </c>
       <c r="N110" s="4" t="n">
-        <v>1.6152</v>
+        <v>2.8917</v>
       </c>
       <c r="O110" s="4" t="n">
-        <v>0.1821</v>
+        <v>0.1977</v>
       </c>
       <c r="P110" s="4" t="n">
-        <v>0.09230000000000001</v>
+        <v>0.1152</v>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R110" s="2" t="inlineStr"/>
@@ -6853,57 +6853,57 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>VBTYZ</t>
+          <t>TABGD</t>
         </is>
       </c>
       <c r="B111" s="6" t="n">
-        <v>19.2</v>
+        <v>191.7</v>
       </c>
       <c r="C111" s="7" t="n">
-        <v>-0.0278</v>
+        <v>0.0021</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>-0.1652</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="E111" s="7" t="n">
-        <v>-0.3074</v>
+        <v>-0.1574</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>-0.4213</v>
+        <v>-0.1773</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>-0.1003</v>
+        <v>-0.2613</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>0.0738</v>
+        <v>-0.2069</v>
       </c>
       <c r="I111" s="6" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="J111" s="6" t="n">
-        <v>12.57</v>
+        <v>17.92</v>
       </c>
       <c r="K111" s="7" t="n">
-        <v>0.5342</v>
+        <v>0.493</v>
       </c>
       <c r="L111" s="7" t="n">
-        <v>0.9976999999999999</v>
+        <v>0.3835</v>
       </c>
       <c r="M111" s="7" t="n">
-        <v>3.6408</v>
+        <v>0.4282</v>
       </c>
       <c r="N111" s="7" t="n">
-        <v>1.3528</v>
+        <v>0.1825</v>
       </c>
       <c r="O111" s="7" t="n">
-        <v>0.2074</v>
+        <v>0.2029</v>
       </c>
       <c r="P111" s="7" t="n">
-        <v>-9.062000000000001</v>
+        <v>0.1296</v>
       </c>
       <c r="Q111" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R111" s="5" t="inlineStr"/>
@@ -6911,57 +6911,57 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>TRALT</t>
+          <t>VBTYZ</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>36.48</v>
+        <v>19.28</v>
       </c>
       <c r="C112" s="4" t="n">
-        <v>-0.09390000000000001</v>
+        <v>0.0042</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>-0.1497</v>
+        <v>-0.0417</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>-0.2985</v>
+        <v>-0.3045</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>-0.2826</v>
+        <v>-0.4189</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>-0.2107</v>
+        <v>-0.0965</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>0.4926</v>
+        <v>0.0771</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>23.3</v>
+        <v>12.62</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1.2681</v>
+        <v>0.5342</v>
       </c>
       <c r="L112" s="4" t="n">
-        <v>2.3445</v>
+        <v>0.9976999999999999</v>
       </c>
       <c r="M112" s="4" t="n">
-        <v>3.7256</v>
+        <v>3.6408</v>
       </c>
       <c r="N112" s="4" t="n">
-        <v>1.0029</v>
+        <v>1.3528</v>
       </c>
       <c r="O112" s="4" t="n">
-        <v>0.2964</v>
+        <v>0.2074</v>
       </c>
       <c r="P112" s="4" t="n">
-        <v>0.1126</v>
+        <v>-9.062000000000001</v>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr"/>
@@ -6969,57 +6969,57 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>BIMAS</t>
+          <t>TRALT</t>
         </is>
       </c>
       <c r="B113" s="6" t="n">
-        <v>369</v>
+        <v>35.94</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>-0.0428</v>
+        <v>-0.0148</v>
       </c>
       <c r="D113" s="7" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.1463</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>-0.1473</v>
+        <v>-0.2833</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>-0.0538</v>
+        <v>-0.2932</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>-0.0302</v>
+        <v>-0.2224</v>
       </c>
       <c r="H113" s="7" t="n">
-        <v>0.4004</v>
+        <v>0.4987</v>
       </c>
       <c r="I113" s="6" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="J113" s="6" t="n">
-        <v>16.14</v>
+        <v>22.95</v>
       </c>
       <c r="K113" s="7" t="n">
-        <v>0.4214</v>
+        <v>1.2681</v>
       </c>
       <c r="L113" s="7" t="n">
-        <v>0.5271</v>
+        <v>2.3445</v>
       </c>
       <c r="M113" s="7" t="n">
-        <v>0.8381000000000001</v>
+        <v>3.7256</v>
       </c>
       <c r="N113" s="7" t="n">
-        <v>0.8737999999999999</v>
+        <v>1.0029</v>
       </c>
       <c r="O113" s="7" t="n">
-        <v>0.0611</v>
+        <v>0.2964</v>
       </c>
       <c r="P113" s="7" t="n">
-        <v>0.1613</v>
+        <v>0.1126</v>
       </c>
       <c r="Q113" s="5" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="R113" s="5" t="inlineStr"/>
@@ -7027,57 +7027,57 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>CCOLA</t>
+          <t>BIMAS</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>74.2</v>
+        <v>373</v>
       </c>
       <c r="C114" s="4" t="n">
-        <v>-0.0326</v>
+        <v>0.0108</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>-0.08449999999999999</v>
+        <v>-0.0593</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>-0.0737</v>
+        <v>-0.1331</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>-0.186</v>
+        <v>-0.0436</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>-0.0725</v>
+        <v>-0.0197</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>0.465</v>
+        <v>0.3853</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>10.02</v>
+        <v>16.31</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0.4257</v>
+        <v>0.4214</v>
       </c>
       <c r="L114" s="4" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5271</v>
       </c>
       <c r="M114" s="4" t="n">
-        <v>0.7781</v>
+        <v>0.8381000000000001</v>
       </c>
       <c r="N114" s="4" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.8737999999999999</v>
       </c>
       <c r="O114" s="4" t="n">
-        <v>0.177</v>
+        <v>0.0611</v>
       </c>
       <c r="P114" s="4" t="n">
-        <v>0.5497</v>
+        <v>0.1613</v>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr"/>
@@ -7089,31 +7089,31 @@
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>100</v>
+        <v>94.8</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>-0.0431</v>
+        <v>-0.0525</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>-0.1379</v>
+        <v>-0.1585</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>-0.1135</v>
+        <v>-0.2202</v>
       </c>
       <c r="F115" s="7" t="n">
-        <v>-0.2811</v>
+        <v>-0.3188</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>-0.0403</v>
+        <v>-0.0907</v>
       </c>
       <c r="H115" s="7" t="n">
-        <v>1.2978</v>
+        <v>1.1292</v>
       </c>
       <c r="I115" s="6" t="n">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="J115" s="6" t="n">
-        <v>8.960000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="K115" s="7" t="n">
         <v>2.4396</v>
@@ -7143,57 +7143,57 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>LOGO</t>
+          <t>CCOLA</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>116.3</v>
+        <v>74.75</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>-0.0186</v>
+        <v>0.0074</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>-0.1183</v>
+        <v>-0.0478</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>-0.1621</v>
+        <v>-0.0538</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>-0.1353</v>
+        <v>-0.1799</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>-0.1717</v>
+        <v>-0.06559999999999999</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>-0.2061</v>
+        <v>0.4543</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>2.49</v>
+        <v>2.28</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>12.65</v>
+        <v>10.1</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0.5617</v>
+        <v>0.4257</v>
       </c>
       <c r="L116" s="4" t="n">
-        <v>0.8981999999999999</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="M116" s="4" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.7781</v>
       </c>
       <c r="N116" s="4" t="n">
-        <v>267.6647</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="O116" s="4" t="n">
-        <v>0.346</v>
+        <v>0.177</v>
       </c>
       <c r="P116" s="4" t="n">
-        <v>0.9277</v>
+        <v>0.5497</v>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr"/>
@@ -7201,53 +7201,53 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>HTTBT</t>
+          <t>LOGO</t>
         </is>
       </c>
       <c r="B117" s="6" t="n">
-        <v>29.08</v>
+        <v>114.5</v>
       </c>
       <c r="C117" s="7" t="n">
-        <v>-0.0332</v>
+        <v>-0.0155</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>-0.1129</v>
+        <v>-0.1179</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>-0.0447</v>
+        <v>-0.2168</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>-0.2153</v>
+        <v>-0.1487</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>-0.3102</v>
+        <v>-0.1845</v>
       </c>
       <c r="H117" s="7" t="n">
-        <v>-0.3678</v>
+        <v>-0.2274</v>
       </c>
       <c r="I117" s="6" t="n">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>21.22</v>
+        <v>12.45</v>
       </c>
       <c r="K117" s="7" t="n">
-        <v>0.3957</v>
+        <v>0.5617</v>
       </c>
       <c r="L117" s="7" t="n">
-        <v>0.3631</v>
+        <v>0.8981999999999999</v>
       </c>
       <c r="M117" s="7" t="n">
-        <v>0.3492</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="N117" s="7" t="n">
-        <v>0.2572</v>
+        <v>267.6647</v>
       </c>
       <c r="O117" s="7" t="n">
-        <v>0.4235</v>
+        <v>0.346</v>
       </c>
       <c r="P117" s="7" t="n">
-        <v>0.5921</v>
+        <v>0.9277</v>
       </c>
       <c r="Q117" s="5" t="inlineStr">
         <is>
@@ -7259,57 +7259,57 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>PKART</t>
+          <t>HTTBT</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>68.75</v>
+        <v>28.4</v>
       </c>
       <c r="C118" s="4" t="n">
-        <v>-0.07719999999999999</v>
+        <v>-0.0234</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>-0.2271</v>
+        <v>-0.1035</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>-0.2353</v>
+        <v>-0.09210000000000002</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>-0.4907</v>
+        <v>-0.2337</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>-0.3744</v>
+        <v>-0.3264</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>-0.1406</v>
+        <v>-0.3779999999999999</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>15.2</v>
+        <v>20.72</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0.5093</v>
+        <v>0.3957</v>
       </c>
       <c r="L118" s="4" t="n">
-        <v>1.5572</v>
+        <v>0.3631</v>
       </c>
       <c r="M118" s="4" t="n">
-        <v>1.6598</v>
+        <v>0.3492</v>
       </c>
       <c r="N118" s="4" t="n">
-        <v>4.8022</v>
+        <v>0.2572</v>
       </c>
       <c r="O118" s="4" t="n">
-        <v>0.083</v>
+        <v>0.4235</v>
       </c>
       <c r="P118" s="4" t="n">
-        <v>0.2041</v>
+        <v>0.5921</v>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr"/>
@@ -7317,57 +7317,57 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>ARDYZ</t>
+          <t>GUBRF</t>
         </is>
       </c>
       <c r="B119" s="6" t="n">
-        <v>56.85</v>
+        <v>298.5</v>
       </c>
       <c r="C119" s="7" t="n">
-        <v>-0.0453</v>
+        <v>-0.09949999999999999</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>-0.0897</v>
+        <v>-0.2322</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>-0.08310000000000001</v>
+        <v>-0.3215999999999999</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>-0.2055</v>
+        <v>-0.2943</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>0.3111</v>
+        <v>-0.4232</v>
       </c>
       <c r="H119" s="7" t="n">
-        <v>1.285</v>
+        <v>0.0492</v>
       </c>
       <c r="I119" s="6" t="n">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>14.16</v>
+        <v>12.94</v>
       </c>
       <c r="K119" s="7" t="n">
-        <v>2.0657</v>
+        <v>0.1897</v>
       </c>
       <c r="L119" s="7" t="n">
-        <v>2.0433</v>
+        <v>0.4879</v>
       </c>
       <c r="M119" s="7" t="n">
-        <v>2.0361</v>
+        <v>0.6424</v>
       </c>
       <c r="N119" s="7" t="n">
-        <v>1.7568</v>
+        <v>0.5356000000000001</v>
       </c>
       <c r="O119" s="7" t="n">
-        <v>0.4642</v>
+        <v>0.2097</v>
       </c>
       <c r="P119" s="7" t="n">
-        <v>3.4222</v>
+        <v>0.2503</v>
       </c>
       <c r="Q119" s="5" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R119" s="5" t="inlineStr"/>
@@ -7375,55 +7375,57 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>OYAYO</t>
+          <t>ARDYZ</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>24.02</v>
+        <v>54.45</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>-0.0762</v>
+        <v>-0.04219999999999999</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>-0.2447</v>
+        <v>-0.0795</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>-0.3234</v>
+        <v>-0.2109</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>-0.4812</v>
+        <v>-0.239</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>-0.5576</v>
+        <v>0.2558</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>-0.3272</v>
+        <v>1.1624</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr"/>
+        <v>2.56</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>13.56</v>
+      </c>
       <c r="K120" s="4" t="n">
-        <v>0.3933</v>
+        <v>2.0657</v>
       </c>
       <c r="L120" s="4" t="n">
-        <v>0.4082</v>
+        <v>2.0433</v>
       </c>
       <c r="M120" s="4" t="n">
-        <v>0.6868000000000001</v>
+        <v>2.0361</v>
       </c>
       <c r="N120" s="4" t="n">
-        <v>0.2959</v>
+        <v>1.7568</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>0.7368000000000001</v>
+        <v>0.4642</v>
       </c>
       <c r="P120" s="4" t="n">
-        <v>-0.0453</v>
+        <v>3.4222</v>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr"/>
@@ -7431,57 +7433,57 @@
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>GUBRF</t>
+          <t>PKART</t>
         </is>
       </c>
       <c r="B121" s="6" t="n">
-        <v>331.5</v>
+        <v>68.05</v>
       </c>
       <c r="C121" s="7" t="n">
-        <v>-0.0649</v>
+        <v>-0.0102</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>-0.1608</v>
+        <v>-0.235</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>-0.247</v>
+        <v>-0.2501</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>-0.2163</v>
+        <v>-0.4959</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>-0.3594</v>
+        <v>-0.3808</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>0.185</v>
+        <v>-0.1353</v>
       </c>
       <c r="I121" s="6" t="n">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="J121" s="6" t="n">
-        <v>14.37</v>
+        <v>15.05</v>
       </c>
       <c r="K121" s="7" t="n">
-        <v>0.1897</v>
+        <v>0.5093</v>
       </c>
       <c r="L121" s="7" t="n">
-        <v>0.4879</v>
+        <v>1.5572</v>
       </c>
       <c r="M121" s="7" t="n">
-        <v>0.6424</v>
+        <v>1.6598</v>
       </c>
       <c r="N121" s="7" t="n">
-        <v>0.5356000000000001</v>
+        <v>4.8022</v>
       </c>
       <c r="O121" s="7" t="n">
-        <v>0.2097</v>
+        <v>0.083</v>
       </c>
       <c r="P121" s="7" t="n">
-        <v>0.2503</v>
+        <v>0.2041</v>
       </c>
       <c r="Q121" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="R121" s="5" t="inlineStr"/>
@@ -7489,57 +7491,55 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>ATATP</t>
+          <t>OYAYO</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>205.5</v>
+        <v>23.06</v>
       </c>
       <c r="C122" s="4" t="n">
-        <v>-0.0595</v>
+        <v>-0.04</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>-0.0693</v>
+        <v>-0.2561</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>-0.1508</v>
+        <v>-0.3737</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>-0.2119</v>
+        <v>-0.5019</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>0.4533</v>
+        <v>-0.5753</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>0.5844</v>
+        <v>-0.3626</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J122" s="3" t="n">
-        <v>4.23</v>
-      </c>
+        <v>2.65</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="4" t="n">
-        <v>0.3072</v>
+        <v>0.3933</v>
       </c>
       <c r="L122" s="4" t="n">
-        <v>0.2985</v>
+        <v>0.4082</v>
       </c>
       <c r="M122" s="4" t="n">
-        <v>0.3487</v>
+        <v>0.6868000000000001</v>
       </c>
       <c r="N122" s="4" t="n">
-        <v>0.6609999999999999</v>
+        <v>0.2959</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>0.3268</v>
+        <v>0.7368000000000001</v>
       </c>
       <c r="P122" s="4" t="n">
-        <v>0.7543000000000001</v>
+        <v>-0.0453</v>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr"/>
@@ -7547,57 +7547,57 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>KRONT</t>
+          <t>ATATP</t>
         </is>
       </c>
       <c r="B123" s="6" t="n">
-        <v>16.46</v>
+        <v>200.6</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>-0.0283</v>
+        <v>-0.0238</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>-0.09609999999999999</v>
+        <v>-0.0626</v>
       </c>
       <c r="E123" s="7" t="n">
-        <v>-0.1305</v>
+        <v>-0.1704</v>
       </c>
       <c r="F123" s="7" t="n">
-        <v>-0.3276</v>
+        <v>-0.2307</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>-0.2905</v>
+        <v>0.4187</v>
       </c>
       <c r="H123" s="7" t="n">
-        <v>0.07440000000000001</v>
+        <v>0.5611</v>
       </c>
       <c r="I123" s="6" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="J123" s="6" t="n">
-        <v>21.68</v>
+        <v>4.13</v>
       </c>
       <c r="K123" s="7" t="n">
-        <v>0.6388</v>
+        <v>0.3072</v>
       </c>
       <c r="L123" s="7" t="n">
-        <v>0.5896</v>
+        <v>0.2985</v>
       </c>
       <c r="M123" s="7" t="n">
-        <v>1.5604</v>
+        <v>0.3487</v>
       </c>
       <c r="N123" s="7" t="n">
-        <v>5.569299999999999</v>
+        <v>0.6609999999999999</v>
       </c>
       <c r="O123" s="7" t="n">
-        <v>0.3874</v>
+        <v>0.3268</v>
       </c>
       <c r="P123" s="7" t="n">
-        <v>13.8834</v>
+        <v>0.7543000000000001</v>
       </c>
       <c r="Q123" s="5" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="R123" s="5" t="inlineStr"/>
@@ -7605,57 +7605,57 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>ARMGD</t>
+          <t>KRONT</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>110.1</v>
+        <v>16.14</v>
       </c>
       <c r="C124" s="4" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.0194</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>-0.1722</v>
+        <v>-0.1228</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>-0.266</v>
+        <v>-0.1676</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>-0.4587</v>
+        <v>-0.3407</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>-0.2412</v>
+        <v>-0.3043</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>1.9854</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>3.25</v>
+        <v>3.01</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>12.26</v>
+        <v>21.25</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1.164</v>
+        <v>0.6388</v>
       </c>
       <c r="L124" s="4" t="n">
-        <v>0.8115000000000001</v>
+        <v>0.5896</v>
       </c>
       <c r="M124" s="4" t="n">
-        <v>1.571</v>
+        <v>1.5604</v>
       </c>
       <c r="N124" s="4" t="n">
-        <v>1.7066</v>
+        <v>5.569299999999999</v>
       </c>
       <c r="O124" s="4" t="n">
-        <v>0.1178</v>
+        <v>0.3874</v>
       </c>
       <c r="P124" s="4" t="n">
-        <v>0.3402000000000001</v>
+        <v>13.8834</v>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr"/>
@@ -7663,57 +7663,57 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>ASTOR</t>
+          <t>ARMGD</t>
         </is>
       </c>
       <c r="B125" s="6" t="n">
-        <v>150</v>
+        <v>103.2</v>
       </c>
       <c r="C125" s="7" t="n">
-        <v>-0.0421</v>
+        <v>-0.06269999999999999</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>-0.2097</v>
+        <v>-0.0541</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>-0.4307</v>
+        <v>-0.1506</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>-0.5122</v>
+        <v>-0.4926</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>-0.2823</v>
+        <v>-0.2888</v>
       </c>
       <c r="H125" s="7" t="n">
-        <v>0.5609000000000001</v>
+        <v>1.7847</v>
       </c>
       <c r="I125" s="6" t="n">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="J125" s="6" t="n">
-        <v>14.72</v>
+        <v>11.49</v>
       </c>
       <c r="K125" s="7" t="n">
-        <v>0.4338</v>
+        <v>1.164</v>
       </c>
       <c r="L125" s="7" t="n">
-        <v>0.5232</v>
+        <v>0.8115000000000001</v>
       </c>
       <c r="M125" s="7" t="n">
-        <v>0.7125</v>
+        <v>1.571</v>
       </c>
       <c r="N125" s="7" t="n">
-        <v>0.8672</v>
+        <v>1.7066</v>
       </c>
       <c r="O125" s="7" t="n">
-        <v>0.3018</v>
+        <v>0.1178</v>
       </c>
       <c r="P125" s="7" t="n">
-        <v>0.3122</v>
+        <v>0.3402000000000001</v>
       </c>
       <c r="Q125" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R125" s="5" t="inlineStr"/>
@@ -7721,57 +7721,57 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>YEOTK</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>23.7</v>
+        <v>142.6</v>
       </c>
       <c r="C126" s="4" t="n">
-        <v>0.0017</v>
+        <v>-0.0493</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>-0.09539999999999998</v>
+        <v>-0.1719</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>-0.1922</v>
+        <v>-0.451</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>-0.4552</v>
+        <v>-0.5363</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>0.06660000000000001</v>
+        <v>-0.3177</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>0.6729999999999999</v>
+        <v>0.5114</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>8.83</v>
+        <v>13.99</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1.4662</v>
+        <v>0.4338</v>
       </c>
       <c r="L126" s="4" t="n">
-        <v>1.5472</v>
+        <v>0.5232</v>
       </c>
       <c r="M126" s="4" t="n">
-        <v>1.7095</v>
+        <v>0.7125</v>
       </c>
       <c r="N126" s="4" t="n">
-        <v>3.7317</v>
+        <v>0.8672</v>
       </c>
       <c r="O126" s="4" t="n">
-        <v>0.1898</v>
+        <v>0.3018</v>
       </c>
       <c r="P126" s="4" t="n">
-        <v>0.7681999999999999</v>
+        <v>0.3122</v>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr"/>
@@ -7779,57 +7779,57 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>FMIZP</t>
+          <t>YEOTK</t>
         </is>
       </c>
       <c r="B127" s="6" t="n">
-        <v>200.8</v>
+        <v>22.02</v>
       </c>
       <c r="C127" s="7" t="n">
-        <v>-0.0452</v>
+        <v>-0.0709</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>-0.1801</v>
+        <v>-0.1439</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>-0.2269</v>
+        <v>-0.3265999999999999</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>-0.2985</v>
+        <v>-0.4938</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>-0.3034</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>-0.3502</v>
+        <v>0.5648</v>
       </c>
       <c r="I127" s="6" t="n">
-        <v>4.02</v>
+        <v>3.32</v>
       </c>
       <c r="J127" s="6" t="n">
-        <v>20.31</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="K127" s="7" t="n">
-        <v>0.2837</v>
+        <v>1.4662</v>
       </c>
       <c r="L127" s="7" t="n">
-        <v>0.7895</v>
+        <v>1.5472</v>
       </c>
       <c r="M127" s="7" t="n">
-        <v>0.1712</v>
+        <v>1.7095</v>
       </c>
       <c r="N127" s="7" t="n">
-        <v>0.9815999999999999</v>
+        <v>3.7317</v>
       </c>
       <c r="O127" s="7" t="n">
-        <v>0.1378</v>
+        <v>0.1898</v>
       </c>
       <c r="P127" s="7" t="n">
-        <v>0.2179</v>
+        <v>0.7681999999999999</v>
       </c>
       <c r="Q127" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="R127" s="5" t="inlineStr"/>
@@ -7837,57 +7837,57 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>ONCSM</t>
+          <t>FMIZP</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>87</v>
+        <v>197</v>
       </c>
       <c r="C128" s="4" t="n">
-        <v>0.0235</v>
+        <v>-0.0189</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>-0.0091</v>
+        <v>-0.1653</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>-0.07150000000000001</v>
+        <v>-0.2416</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>-0.6686</v>
+        <v>-0.3118</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>-0.6945</v>
+        <v>-0.3166</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>-0.5057</v>
+        <v>-0.3691</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>4.11</v>
+        <v>3.95</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>28.73</v>
+        <v>19.93</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0.5028</v>
+        <v>0.2837</v>
       </c>
       <c r="L128" s="4" t="n">
-        <v>1.6135</v>
+        <v>0.7895</v>
       </c>
       <c r="M128" s="4" t="n">
-        <v>2.0025</v>
+        <v>0.1712</v>
       </c>
       <c r="N128" s="4" t="n">
-        <v>9.2562</v>
+        <v>0.9815999999999999</v>
       </c>
       <c r="O128" s="4" t="n">
-        <v>0.3063</v>
+        <v>0.1378</v>
       </c>
       <c r="P128" s="4" t="n">
-        <v>0.1832</v>
+        <v>0.2179</v>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr"/>
@@ -7895,57 +7895,57 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>DOCO</t>
+          <t>ONCSM</t>
         </is>
       </c>
       <c r="B129" s="6" t="n">
-        <v>10997.5</v>
+        <v>91</v>
       </c>
       <c r="C129" s="7" t="n">
-        <v>-0.0198</v>
+        <v>0.046</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>0.0309</v>
+        <v>-0.0594</v>
       </c>
       <c r="E129" s="7" t="n">
-        <v>0.028</v>
+        <v>0.0788</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>0.0176</v>
+        <v>-0.6533</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>0.179</v>
+        <v>-0.6804000000000001</v>
       </c>
       <c r="H129" s="7" t="n">
-        <v>0.0519</v>
+        <v>-0.465</v>
       </c>
       <c r="I129" s="6" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="J129" s="6" t="n">
-        <v>20.19</v>
+        <v>30.05</v>
       </c>
       <c r="K129" s="7" t="n">
-        <v>0.2032</v>
+        <v>0.5028</v>
       </c>
       <c r="L129" s="7" t="n">
-        <v>0.2156</v>
+        <v>1.6135</v>
       </c>
       <c r="M129" s="7" t="n">
-        <v>0.2435</v>
+        <v>2.0025</v>
       </c>
       <c r="N129" s="7" t="n">
-        <v>0.2464</v>
+        <v>9.2562</v>
       </c>
       <c r="O129" s="7" t="n">
-        <v>0.1211</v>
+        <v>0.3063</v>
       </c>
       <c r="P129" s="7" t="n">
-        <v>0.2497</v>
+        <v>0.1832</v>
       </c>
       <c r="Q129" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="R129" s="5" t="inlineStr"/>
@@ -7957,31 +7957,31 @@
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>6.21</v>
+        <v>6.3</v>
       </c>
       <c r="C130" s="4" t="n">
-        <v>-0.0605</v>
+        <v>0.0145</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>-0.0605</v>
+        <v>0.0624</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>-0.3123</v>
+        <v>-0.2251</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>-0.5285</v>
+        <v>-0.5216</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>0.3019</v>
+        <v>0.3208</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>0.9256</v>
+        <v>0.9952</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>53.12</v>
+        <v>53.89</v>
       </c>
       <c r="K130" s="4" t="n">
         <v>0.4591</v>
@@ -8011,57 +8011,57 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>ASELS</t>
+          <t>DOCO</t>
         </is>
       </c>
       <c r="B131" s="6" t="n">
-        <v>338.25</v>
+        <v>11732.5</v>
       </c>
       <c r="C131" s="7" t="n">
-        <v>-0.0217</v>
+        <v>0.0668</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>-0.0196</v>
+        <v>0.0445</v>
       </c>
       <c r="E131" s="7" t="n">
-        <v>-0.1052</v>
+        <v>0.1009</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>-0.101</v>
+        <v>0.08560000000000001</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>-0.1523</v>
+        <v>0.2578</v>
       </c>
       <c r="H131" s="7" t="n">
-        <v>0.6428</v>
+        <v>0.1019</v>
       </c>
       <c r="I131" s="6" t="n">
-        <v>5.03</v>
+        <v>4.6</v>
       </c>
       <c r="J131" s="6" t="n">
-        <v>41.56</v>
+        <v>21.54</v>
       </c>
       <c r="K131" s="7" t="n">
-        <v>0.5623</v>
+        <v>0.2032</v>
       </c>
       <c r="L131" s="7" t="n">
-        <v>0.5598</v>
+        <v>0.2156</v>
       </c>
       <c r="M131" s="7" t="n">
-        <v>0.606</v>
+        <v>0.2435</v>
       </c>
       <c r="N131" s="7" t="n">
-        <v>1.1295</v>
+        <v>0.2464</v>
       </c>
       <c r="O131" s="7" t="n">
-        <v>0.2643</v>
+        <v>0.1211</v>
       </c>
       <c r="P131" s="7" t="n">
-        <v>0.1891</v>
+        <v>0.2497</v>
       </c>
       <c r="Q131" s="5" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R131" s="5" t="inlineStr"/>
@@ -8073,28 +8073,28 @@
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>17.88</v>
+        <v>17.26</v>
       </c>
       <c r="C132" s="4" t="n">
-        <v>-0.09970000000000001</v>
+        <v>-0.0347</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>-0.2385</v>
+        <v>-0.2463</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>-0.3465</v>
+        <v>-0.3692</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>-0.5006</v>
+        <v>-0.5179</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>-0.5603</v>
+        <v>-0.5755</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>-0.4195</v>
+        <v>-0.4552</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>5.19</v>
+        <v>5.01</v>
       </c>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="4" t="n">
@@ -8125,55 +8125,57 @@
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>EUKYO</t>
+          <t>ASELS</t>
         </is>
       </c>
       <c r="B133" s="6" t="n">
-        <v>8.449999999999999</v>
+        <v>338</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>-0.0663</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>-0.09630000000000001</v>
+        <v>-0.0259</v>
       </c>
       <c r="E133" s="7" t="n">
-        <v>-0.1667</v>
+        <v>-0.1082</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>-0.3475</v>
+        <v>-0.1017</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>0.1267</v>
+        <v>-0.1529</v>
       </c>
       <c r="H133" s="7" t="n">
-        <v>0.4282</v>
+        <v>0.6172</v>
       </c>
       <c r="I133" s="6" t="n">
-        <v>6.11</v>
-      </c>
-      <c r="J133" s="5" t="inlineStr"/>
+        <v>5.02</v>
+      </c>
+      <c r="J133" s="6" t="n">
+        <v>41.53</v>
+      </c>
       <c r="K133" s="7" t="n">
-        <v>0.5533</v>
+        <v>0.5623</v>
       </c>
       <c r="L133" s="7" t="n">
-        <v>0.6938</v>
+        <v>0.5598</v>
       </c>
       <c r="M133" s="7" t="n">
-        <v>0.6357</v>
+        <v>0.606</v>
       </c>
       <c r="N133" s="7" t="n">
-        <v>0.08689999999999999</v>
+        <v>1.1295</v>
       </c>
       <c r="O133" s="7" t="n">
-        <v>0.2589</v>
+        <v>0.2643</v>
       </c>
       <c r="P133" s="7" t="n">
-        <v>-0.2304</v>
+        <v>0.1891</v>
       </c>
       <c r="Q133" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="R133" s="5" t="inlineStr"/>
@@ -8181,51 +8183,51 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>ETYAT</t>
+          <t>EUKYO</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>10.02</v>
+        <v>9</v>
       </c>
       <c r="C134" s="4" t="n">
-        <v>-0.09970000000000001</v>
+        <v>0.06509999999999999</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>-0.1919</v>
+        <v>-0.0217</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>0.3236</v>
+        <v>-0.0142</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>-0.2147</v>
+        <v>-0.305</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>0.0955</v>
+        <v>0.6071</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>8.130000000000001</v>
+        <v>6.51</v>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="4" t="n">
-        <v>0.3832</v>
+        <v>0.5533</v>
       </c>
       <c r="L134" s="4" t="n">
-        <v>0.4461</v>
+        <v>0.6938</v>
       </c>
       <c r="M134" s="4" t="n">
-        <v>1.0129</v>
+        <v>0.6357</v>
       </c>
       <c r="N134" s="4" t="n">
-        <v>0.5162</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="O134" s="4" t="n">
-        <v>0.053</v>
+        <v>0.2589</v>
       </c>
       <c r="P134" s="4" t="n">
-        <v>-0.1403</v>
+        <v>-0.2304</v>
       </c>
       <c r="Q134" s="2" t="inlineStr">
         <is>
@@ -8237,55 +8239,55 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>MRSHL</t>
-        </is>
-      </c>
-      <c r="B135" s="8" t="n">
-        <v>1103</v>
+          <t>ETYAT</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="n">
+        <v>9.99</v>
       </c>
       <c r="C135" s="7" t="n">
-        <v>-0.0152</v>
+        <v>-0.003</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>-0.1204</v>
+        <v>-0.2292</v>
       </c>
       <c r="E135" s="7" t="n">
-        <v>-0.2522</v>
+        <v>0.4648</v>
       </c>
       <c r="F135" s="7" t="n">
-        <v>-0.3635</v>
+        <v>-0.2171</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>-0.3119</v>
+        <v>0.1865</v>
       </c>
       <c r="H135" s="7" t="n">
-        <v>-0.3512</v>
+        <v>0.1108</v>
       </c>
       <c r="I135" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="J135" s="5" t="inlineStr"/>
       <c r="K135" s="7" t="n">
-        <v>0.2605</v>
+        <v>0.3832</v>
       </c>
       <c r="L135" s="7" t="n">
-        <v>0.5011</v>
+        <v>0.4461</v>
       </c>
       <c r="M135" s="7" t="n">
-        <v>0.4026</v>
+        <v>1.0129</v>
       </c>
       <c r="N135" s="7" t="n">
-        <v>0.7501000000000001</v>
+        <v>0.5162</v>
       </c>
       <c r="O135" s="7" t="n">
-        <v>0.1503</v>
+        <v>0.053</v>
       </c>
       <c r="P135" s="7" t="n">
-        <v>-0.0529</v>
+        <v>-0.1403</v>
       </c>
       <c r="Q135" s="5" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R135" s="5" t="inlineStr"/>
@@ -8293,55 +8295,55 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>KENT</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="n">
-        <v>233</v>
+          <t>MRSHL</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="n">
+        <v>1082</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>-0.05860000000000001</v>
+        <v>-0.019</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>-0.1314</v>
+        <v>-0.1309</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>-0.2336</v>
+        <v>-0.2787</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>-0.3065</v>
+        <v>-0.3756</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>-0.4452</v>
+        <v>-0.325</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>-0.5324</v>
+        <v>-0.3728</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>10.03</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="4" t="n">
-        <v>0.2234</v>
+        <v>0.2605</v>
       </c>
       <c r="L136" s="4" t="n">
-        <v>0.3229</v>
+        <v>0.5011</v>
       </c>
       <c r="M136" s="4" t="n">
-        <v>0.5381</v>
+        <v>0.4026</v>
       </c>
       <c r="N136" s="4" t="n">
-        <v>0.0256</v>
+        <v>0.7501000000000001</v>
       </c>
       <c r="O136" s="4" t="n">
-        <v>0.051</v>
+        <v>0.1503</v>
       </c>
       <c r="P136" s="4" t="n">
-        <v>-0.1222</v>
+        <v>-0.0529</v>
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="R136" s="2" t="inlineStr"/>
@@ -8349,57 +8351,55 @@
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>QNBFK</t>
+          <t>KENT</t>
         </is>
       </c>
       <c r="B137" s="6" t="n">
-        <v>33.96</v>
+        <v>232</v>
       </c>
       <c r="C137" s="7" t="n">
-        <v>-0.0202</v>
+        <v>-0.0043</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>-0.1341</v>
+        <v>-0.112</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>-0.0567</v>
+        <v>-0.2169</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>-0.2995</v>
+        <v>-0.3095</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>-0.1817</v>
+        <v>-0.4476</v>
       </c>
       <c r="H137" s="7" t="n">
-        <v>-0.2457</v>
+        <v>-0.5347</v>
       </c>
       <c r="I137" s="6" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="J137" s="6" t="n">
-        <v>37.45</v>
-      </c>
+        <v>9.99</v>
+      </c>
+      <c r="J137" s="5" t="inlineStr"/>
       <c r="K137" s="7" t="n">
-        <v>0.2618</v>
+        <v>0.2234</v>
       </c>
       <c r="L137" s="7" t="n">
-        <v>0.2816</v>
+        <v>0.3229</v>
       </c>
       <c r="M137" s="7" t="n">
-        <v>0.285</v>
+        <v>0.5381</v>
       </c>
       <c r="N137" s="7" t="n">
-        <v>0.2688</v>
+        <v>0.0256</v>
       </c>
       <c r="O137" s="7" t="n">
-        <v>0.795</v>
+        <v>0.051</v>
       </c>
       <c r="P137" s="7" t="n">
-        <v>0.3111</v>
+        <v>-0.1222</v>
       </c>
       <c r="Q137" s="5" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R137" s="5" t="inlineStr"/>
@@ -8407,55 +8407,57 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>BMSTL</t>
+          <t>QNBFK</t>
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>35.74</v>
+        <v>33.9</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>-0.053</v>
+        <v>-0.0018</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>-0.0717</v>
+        <v>-0.1055</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>-0.1987</v>
+        <v>-0.0728</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>-0.1885</v>
+        <v>-0.3007</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>-0.1551</v>
+        <v>-0.1831</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>0.1239</v>
+        <v>-0.2615</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>13.34</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr"/>
+        <v>10.39</v>
+      </c>
+      <c r="J138" s="3" t="n">
+        <v>37.38</v>
+      </c>
       <c r="K138" s="4" t="n">
-        <v>0.3282</v>
+        <v>0.2618</v>
       </c>
       <c r="L138" s="4" t="n">
-        <v>0.4883</v>
+        <v>0.2816</v>
       </c>
       <c r="M138" s="4" t="n">
-        <v>0.1412</v>
+        <v>0.285</v>
       </c>
       <c r="N138" s="4" t="n">
-        <v>0.3482</v>
+        <v>0.2688</v>
       </c>
       <c r="O138" s="4" t="n">
-        <v>0.0741</v>
+        <v>0.795</v>
       </c>
       <c r="P138" s="4" t="n">
-        <v>-0.0293</v>
+        <v>0.3111</v>
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="R138" s="2" t="inlineStr"/>
@@ -8467,31 +8469,31 @@
         </is>
       </c>
       <c r="B139" s="6" t="n">
-        <v>90.55</v>
+        <v>88.8</v>
       </c>
       <c r="C139" s="7" t="n">
-        <v>-0.0321</v>
+        <v>-0.0193</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>-0.1035</v>
+        <v>-0.1225</v>
       </c>
       <c r="E139" s="7" t="n">
-        <v>-0.2029</v>
+        <v>-0.2278</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>-0.2948</v>
+        <v>-0.3084</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>-0.3991</v>
+        <v>-0.4107</v>
       </c>
       <c r="H139" s="7" t="n">
-        <v>-0.4379</v>
+        <v>-0.4585</v>
       </c>
       <c r="I139" s="6" t="n">
-        <v>13.78</v>
+        <v>13.51</v>
       </c>
       <c r="J139" s="6" t="n">
-        <v>51.89</v>
+        <v>50.88</v>
       </c>
       <c r="K139" s="7" t="n">
         <v>0.3045</v>
@@ -8521,56 +8523,112 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>BMSTL</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>67</v>
+        <v>36.44</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>-0.029</v>
+        <v>0.0196</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>-0.1184</v>
+        <v>-0.0436</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>-0.162</v>
+        <v>-0.1877</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>0.0075</v>
+        <v>-0.1726</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>0.0559</v>
+        <v>-0.1385</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>-0.0067</v>
-      </c>
-      <c r="I140" s="2" t="inlineStr"/>
+        <v>0.1523</v>
+      </c>
+      <c r="I140" s="3" t="n">
+        <v>13.6</v>
+      </c>
       <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="4" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="L140" s="4" t="n">
+        <v>0.4883</v>
+      </c>
+      <c r="M140" s="4" t="n">
+        <v>0.1412</v>
+      </c>
+      <c r="N140" s="4" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="O140" s="4" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="P140" s="4" t="n">
+        <v>-0.0293</v>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>Üretici imalatı</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>NETAS</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="C141" s="7" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="D141" s="7" t="n">
+        <v>-0.1144</v>
+      </c>
+      <c r="E141" s="7" t="n">
+        <v>-0.1273</v>
+      </c>
+      <c r="F141" s="7" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="G141" s="7" t="n">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="H141" s="7" t="n">
+        <v>-0.0223</v>
+      </c>
+      <c r="I141" s="5" t="inlineStr"/>
+      <c r="J141" s="5" t="inlineStr"/>
+      <c r="K141" s="7" t="n">
         <v>0.3963</v>
       </c>
-      <c r="L140" s="4" t="n">
+      <c r="L141" s="7" t="n">
         <v>0.7615999999999999</v>
       </c>
-      <c r="M140" s="4" t="n">
+      <c r="M141" s="7" t="n">
         <v>1.8006</v>
       </c>
-      <c r="N140" s="4" t="n">
+      <c r="N141" s="7" t="n">
         <v>0.3182</v>
       </c>
-      <c r="O140" s="4" t="n">
+      <c r="O141" s="7" t="n">
         <v>0.0233</v>
       </c>
-      <c r="P140" s="4" t="n">
+      <c r="P141" s="7" t="n">
         <v>0.1274</v>
       </c>
-      <c r="Q140" s="2" t="inlineStr">
+      <c r="Q141" s="5" t="inlineStr">
         <is>
           <t>Teknoloji hizmetleri</t>
         </is>
       </c>
-      <c r="R140" s="2" t="inlineStr"/>
+      <c r="R141" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8594,7 +8652,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>22.10.2026 19:20</t>
+          <t>23.10.2026 19:25</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8663,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3">

--- a/data/bist_screener_latest.xlsx
+++ b/data/bist_screener_latest.xlsx
@@ -76,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +97,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -583,25 +586,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11.68</v>
+        <v>11.65</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>-0.0371</v>
+        <v>-0.0026</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.1923</v>
+        <v>-0.169</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.5059</v>
+        <v>-0.4822</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>-0.48</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.624</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>-0.3995</v>
+        <v>-0.397</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0.18</v>
@@ -639,31 +642,31 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>-0.075</v>
+        <v>-0.0378</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>-0.119</v>
+        <v>-0.1524</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>-0.1514</v>
+        <v>-0.1872</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>-0.2912</v>
+        <v>-0.3074</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>-0.4272</v>
+        <v>-0.4557</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>-0.3833</v>
+        <v>-0.4086</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="K3" s="7" t="n">
         <v>2.7227</v>
@@ -697,31 +700,31 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-0.0322</v>
+        <v>-0.005500000000000001</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.1195</v>
+        <v>-0.1025</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.1384</v>
+        <v>-0.1286</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-0.2894</v>
+        <v>-0.2474</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.3744</v>
+        <v>-0.3757</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.09519999999999999</v>
+        <v>-0.1158</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>0.21</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>1.7259</v>
@@ -751,57 +754,55 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>MERIT</t>
+          <t>SNICA</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>12.8</v>
+        <v>1.84</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>-0.0266</v>
+        <v>-0.0213</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-0.0039</v>
+        <v>-0.1068</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>-0.1239</v>
+        <v>-0.252</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>-0.2224</v>
+        <v>-0.5027</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-0.2224</v>
+        <v>-0.5468</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>-0.3657</v>
+        <v>-0.6297999999999999</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0.21</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>5.95</v>
-      </c>
+      <c r="J5" s="5" t="inlineStr"/>
       <c r="K5" s="7" t="n">
-        <v>0.9854999999999999</v>
+        <v>0.2451</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>1.0319</v>
+        <v>0.1328</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>2.0871</v>
+        <v>0.7476999999999999</v>
       </c>
       <c r="N5" s="7" t="n">
-        <v>1.5834</v>
+        <v>0.4518</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>0.6354</v>
+        <v>0.0576</v>
       </c>
       <c r="P5" s="7" t="n">
-        <v>0.0454</v>
+        <v>-0.1748</v>
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="R5" s="5" t="inlineStr"/>
@@ -813,31 +814,31 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0336</v>
+        <v>-0.0069</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.04</v>
+        <v>-0.0403</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1429</v>
+        <v>-0.1227</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2836</v>
+        <v>-0.2886</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3543</v>
+        <v>-0.3889</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.4194</v>
+        <v>-0.428</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0.21</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>8.06</v>
+        <v>8</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>0.2518</v>
@@ -867,55 +868,57 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>SNICA</t>
+          <t>MERIT</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1.88</v>
+        <v>13.04</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>-0.0105</v>
+        <v>0.0187</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-0.1215</v>
+        <v>0.0116</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>-0.2713</v>
+        <v>-0.07519999999999999</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>-0.5179</v>
+        <v>-0.2196</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.1835</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>-0.6154999999999999</v>
+        <v>-0.3664</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr"/>
+        <v>0.21</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>6.06</v>
+      </c>
       <c r="K7" s="7" t="n">
-        <v>0.2451</v>
+        <v>0.9854999999999999</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.1328</v>
+        <v>1.0319</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.7476999999999999</v>
+        <v>2.0871</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>0.4518</v>
+        <v>1.5834</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>0.0576</v>
+        <v>0.6354</v>
       </c>
       <c r="P7" s="7" t="n">
-        <v>-0.1748</v>
+        <v>0.0454</v>
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr"/>
@@ -930,22 +933,22 @@
         <v>2.21</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.0264</v>
+        <v>0</v>
       </c>
       <c r="D8" s="4" t="n">
+        <v>-0.09050000000000001</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>-0.098</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>-0.2022</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>-0.2246</v>
+      </c>
+      <c r="H8" s="4" t="n">
         <v>-0.1016</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>-0.116</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>-0.2079</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>-0.2218</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>-0.1195</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0.22</v>
@@ -985,25 +988,25 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>8.720000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>-0.0246</v>
+        <v>0.0092</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-0.0917</v>
+        <v>-0.0814</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>-0.1615</v>
+        <v>-0.1768</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>-0.2509</v>
+        <v>-0.215</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-0.3188</v>
+        <v>-0.3152</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-0.2968</v>
+        <v>-0.3021</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0.22</v>
@@ -1037,57 +1040,57 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PETUN</t>
+          <t>GSDHO</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8.449999999999999</v>
+        <v>3.69</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.022</v>
+        <v>-0.016</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.08650000000000001</v>
+        <v>-0.0775</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1998</v>
+        <v>-0.0911</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2722</v>
+        <v>-0.2958</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3283</v>
+        <v>-0.275</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3207</v>
+        <v>-0.1854</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.23</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>10.06</v>
+        <v>13.22</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.3203</v>
+        <v>0.1479</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.0458</v>
+        <v>0.2201</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.0347</v>
+        <v>0.3072</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.0183</v>
+        <v>0.5201</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1414</v>
+        <v>0.6869</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.0274</v>
+        <v>0.0197</v>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr"/>
@@ -1095,57 +1098,57 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>GSDHO</t>
+          <t>PETUN</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3.75</v>
+        <v>8.59</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>-0.0209</v>
+        <v>0.0166</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>-0.1299</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.1972</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>-0.3068</v>
+        <v>-0.2391</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>-0.256</v>
+        <v>-0.3073</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-0.1776</v>
+        <v>-0.3215</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0.23</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>13.44</v>
+        <v>10.23</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.1479</v>
+        <v>0.3203</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.2201</v>
+        <v>0.0458</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.3072</v>
+        <v>0.0347</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>0.5201</v>
+        <v>0.0183</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>0.6869</v>
+        <v>0.1414</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>0.0197</v>
+        <v>0.0274</v>
       </c>
       <c r="Q11" s="5" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="R11" s="5" t="inlineStr"/>
@@ -1157,28 +1160,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>6.26</v>
+        <v>6.1</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.0016</v>
+        <v>-0.0256</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.0558</v>
+        <v>-0.08960000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1133</v>
+        <v>-0.1348</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1806</v>
+        <v>-0.2057</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2695</v>
+        <v>-0.3068</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1448</v>
+        <v>-0.179</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="4" t="n">
@@ -1213,25 +1216,25 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>10.72</v>
+        <v>10.82</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>-0.0255</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>-0.1741</v>
+        <v>-0.1167</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>-0.3519</v>
+        <v>-0.3186</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>-0.5327000000000001</v>
+        <v>-0.4991</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.5147999999999999</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.7323000000000001</v>
+        <v>-0.7306</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0.27</v>
@@ -1269,25 +1272,25 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>4.53</v>
+        <v>4.6</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.05429999999999999</v>
+        <v>0.0155</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1703</v>
+        <v>-0.1304</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.208</v>
+        <v>-0.303</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2815</v>
+        <v>-0.2547</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.371</v>
+        <v>-0.3582</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4709</v>
+        <v>-0.4747999999999999</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.29</v>
@@ -1325,25 +1328,25 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>-0.0245</v>
+        <v>-0.001</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>-0.0965</v>
+        <v>-0.0684</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>-0.181</v>
+        <v>-0.1846</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>-0.2738</v>
+        <v>-0.2773</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>-0.3125</v>
+        <v>-0.3112</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.2743</v>
+        <v>-0.2773</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0.32</v>
@@ -1379,55 +1382,57 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>QUAGR</t>
+          <t>MHRGY</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.0441</v>
+        <v>-0.0116</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.2169</v>
+        <v>-0.0395</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4468</v>
+        <v>-0.0608</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-0.3071</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-0.3236</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.8582</v>
+        <v>-0.3108</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
+        <v>0.33</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>8.02</v>
+      </c>
       <c r="K16" s="4" t="n">
-        <v>0.2334</v>
+        <v>0.9460999999999999</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1468</v>
+        <v>0.9873000000000001</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1104</v>
+        <v>0.3702</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.4322</v>
+        <v>2464.8944</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1786</v>
+        <v>0.8395999999999999</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1088</v>
+        <v>0.0472</v>
       </c>
       <c r="Q16" s="2" 